--- a/docs/design/domain-model/domain-model.xlsx
+++ b/docs/design/domain-model/domain-model.xlsx
@@ -65,12 +65,12 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'organizations'!$A$7:$I$20</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'organization_history'!$A$7:$I$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'organization_history'!$A$7:$I$24</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'users'!$A$8:$I$18</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'user_history'!$A$7:$I$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'user_history'!$A$7:$I$21</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'user_state'!$A$7:$I$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'memberships'!$A$7:$I$17</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'membership_history'!$A$7:$I$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'membership_history'!$A$7:$I$21</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'user_credentials'!$A$6:$I$12</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'user_sessions'!$A$6:$I$17</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'one_time_codes'!$A$6:$I$16</definedName>
@@ -606,7 +606,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I93"/>
+  <dimension ref="A1:I92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -797,7 +797,7 @@
         </is>
       </c>
       <c r="H8" s="6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I8" s="7" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         </is>
       </c>
       <c r="H10" s="6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I10" s="7" t="inlineStr">
         <is>
@@ -1022,7 +1022,7 @@
         </is>
       </c>
       <c r="H13" s="6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I13" s="7" t="inlineStr">
         <is>
@@ -3671,23 +3671,6 @@
       <c r="C92" s="6" t="inlineStr">
         <is>
           <t>chủ sở hữu telematics</t>
-        </is>
-      </c>
-    </row>
-    <row r="93" ht="108" customHeight="1">
-      <c r="A93" s="6" t="inlineStr">
-        <is>
-          <t>D7</t>
-        </is>
-      </c>
-      <c r="B93" s="6" t="inlineStr">
-        <is>
-          <t>Với người dùng nội bộ (xem được mọi tổ chức), mỗi chức danh được những tính năng nào - nhất là dữ liệu cá nhân như lịch sử vị trí và clip camera (ví dụ ACCOUNTANT không được mở clip camera)? vai trò nào chỉ xem một phần?</t>
-        </is>
-      </c>
-      <c r="C93" s="6" t="inlineStr">
-        <is>
-          <t>user_role_assignments, feature list in code</t>
         </is>
       </c>
     </row>
@@ -9657,7 +9640,7 @@
       <c r="F9" s="6" t="n"/>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>TRUE với (các) tổ chức của chính chúng ta, đơn vị vận hành nền tảng (nhân sự thuê ngoài làm thay chúng ta, ví dụ một công ty bán hàng thuê ngoài, cũng là thành viên của tổ chức này). Người dùng của tổ chức này xem được dữ liệu của mọi tổ chức và dùng được mọi tính năng (không giới hạn theo gói), vẫn trong phạm vi vai trò (quyết định D7); chỉ tổ chức nội bộ mới được có HEAD_ADMIN và CO_ADMIN. FALSE với mọi tổ chức khác (khách hàng, đối tác): người dùng chỉ thấy dữ liệu liên quan tới tổ chức của mình, tính năng giới hạn theo gói dịch vụ. Đối tác được nhận biết bằng hồ sơ repair_partners, không bằng cờ này. Cột nhạy cảm nhất của bảng: bật cờ này là cấp quyền xem dữ liệu của mọi tổ chức.</t>
+          <t>TRUE với (các) tổ chức của chính chúng ta, đơn vị vận hành nền tảng (nhân sự thuê ngoài làm thay chúng ta, ví dụ một công ty bán hàng thuê ngoài, cũng là thành viên của tổ chức này). Người dùng của tổ chức này xem được dữ liệu của mọi tổ chức và dùng được mọi tính năng (không giới hạn theo gói), vẫn trong phạm vi vai trò (quyết định ID-44); chỉ tổ chức nội bộ mới được có HEAD_ADMIN và CO_ADMIN. FALSE với mọi tổ chức khác (khách hàng, đối tác): người dùng chỉ thấy dữ liệu liên quan tới tổ chức của mình, tính năng giới hạn theo gói dịch vụ. Đối tác được nhận biết bằng hồ sơ repair_partners, không bằng cờ này. Cột nhạy cảm nhất của bảng: bật cờ này là cấp quyền xem dữ liệu của mọi tổ chức.</t>
         </is>
       </c>
       <c r="H9" s="6" t="inlineStr">
@@ -16275,7 +16258,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -16920,53 +16903,86 @@
       </c>
       <c r="I23" s="6" t="n"/>
     </row>
-    <row r="24"/>
-    <row r="25">
-      <c r="A25" s="4" t="n"/>
-      <c r="B25" s="4" t="inlineStr">
+    <row r="24" ht="40.5" customHeight="1">
+      <c r="A24" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>change_reason</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>varchar(200)</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E24" s="6" t="n"/>
+      <c r="F24" s="6" t="n"/>
+      <c r="G24" s="6" t="inlineStr">
+        <is>
+          <t>Lý do thay đổi dòng, do ứng dụng đặt cho giao dịch: người dùng nhập với quyết định quản trị, văn bản cố định với thao tác thường lệ. Thay đổi không có lý do sẽ bị từ chối.</t>
+        </is>
+      </c>
+      <c r="H24" s="6" t="inlineStr">
+        <is>
+          <t>Customer moved to a new office</t>
+        </is>
+      </c>
+      <c r="I24" s="6" t="n"/>
+    </row>
+    <row r="25"/>
+    <row r="26">
+      <c r="A26" s="4" t="n"/>
+      <c r="B26" s="4" t="inlineStr">
         <is>
           <t>Chỉ mục (index)</t>
         </is>
       </c>
-      <c r="C25" s="4" t="inlineStr">
+      <c r="C26" s="4" t="inlineStr">
         <is>
           <t>Các cột</t>
         </is>
       </c>
-      <c r="D25" s="4" t="inlineStr">
+      <c r="D26" s="4" t="inlineStr">
         <is>
           <t>Duy nhất</t>
         </is>
       </c>
-      <c r="E25" s="4" t="n"/>
-      <c r="F25" s="4" t="inlineStr">
+      <c r="E26" s="4" t="n"/>
+      <c r="F26" s="4" t="inlineStr">
         <is>
           <t>Ghi chú</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="27" customHeight="1">
-      <c r="A26" s="6" t="n"/>
-      <c r="B26" s="6" t="inlineStr">
+    <row r="27" ht="27" customHeight="1">
+      <c r="A27" s="6" t="n"/>
+      <c r="B27" s="6" t="inlineStr">
         <is>
           <t>ix_organization_history_organization_id_time</t>
         </is>
       </c>
-      <c r="C26" s="6" t="inlineStr">
+      <c r="C27" s="6" t="inlineStr">
         <is>
           <t>organization_id, changed_at</t>
         </is>
       </c>
-      <c r="D26" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E26" s="6" t="n"/>
-      <c r="F26" s="6" t="n"/>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E27" s="6" t="n"/>
+      <c r="F27" s="6" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A7:I23"/>
+  <autoFilter ref="A7:I24"/>
   <hyperlinks>
     <hyperlink ref="A2" location="'Tổng quan'!A1"/>
     <hyperlink ref="A5" location="'organizations'!A1"/>
@@ -27579,7 +27595,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:I24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -28125,53 +28141,86 @@
       </c>
       <c r="I20" s="6" t="n"/>
     </row>
-    <row r="21"/>
-    <row r="22">
-      <c r="A22" s="4" t="n"/>
-      <c r="B22" s="4" t="inlineStr">
+    <row r="21" ht="40.5" customHeight="1">
+      <c r="A21" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>change_reason</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>varchar(200)</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="n"/>
+      <c r="F21" s="6" t="n"/>
+      <c r="G21" s="6" t="inlineStr">
+        <is>
+          <t>Lý do thay đổi dòng, do ứng dụng đặt cho giao dịch: người dùng nhập với quyết định quản trị, văn bản cố định với thao tác thường lệ. Thay đổi không có lý do sẽ bị từ chối.</t>
+        </is>
+      </c>
+      <c r="H21" s="6" t="inlineStr">
+        <is>
+          <t>Customer moved to a new office</t>
+        </is>
+      </c>
+      <c r="I21" s="6" t="n"/>
+    </row>
+    <row r="22"/>
+    <row r="23">
+      <c r="A23" s="4" t="n"/>
+      <c r="B23" s="4" t="inlineStr">
         <is>
           <t>Chỉ mục (index)</t>
         </is>
       </c>
-      <c r="C22" s="4" t="inlineStr">
+      <c r="C23" s="4" t="inlineStr">
         <is>
           <t>Các cột</t>
         </is>
       </c>
-      <c r="D22" s="4" t="inlineStr">
+      <c r="D23" s="4" t="inlineStr">
         <is>
           <t>Duy nhất</t>
         </is>
       </c>
-      <c r="E22" s="4" t="n"/>
-      <c r="F22" s="4" t="inlineStr">
+      <c r="E23" s="4" t="n"/>
+      <c r="F23" s="4" t="inlineStr">
         <is>
           <t>Ghi chú</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="27" customHeight="1">
-      <c r="A23" s="6" t="n"/>
-      <c r="B23" s="6" t="inlineStr">
+    <row r="24" ht="27" customHeight="1">
+      <c r="A24" s="6" t="n"/>
+      <c r="B24" s="6" t="inlineStr">
         <is>
           <t>ix_user_history_user_id_time</t>
         </is>
       </c>
-      <c r="C23" s="6" t="inlineStr">
+      <c r="C24" s="6" t="inlineStr">
         <is>
           <t>user_id, changed_at</t>
         </is>
       </c>
-      <c r="D23" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E23" s="6" t="n"/>
-      <c r="F23" s="6" t="n"/>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E24" s="6" t="n"/>
+      <c r="F24" s="6" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A7:I20"/>
+  <autoFilter ref="A7:I21"/>
   <hyperlinks>
     <hyperlink ref="A2" location="'Tổng quan'!A1"/>
     <hyperlink ref="A5" location="'users'!A1"/>
@@ -31376,7 +31425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:I24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -31922,53 +31971,86 @@
       </c>
       <c r="I20" s="6" t="n"/>
     </row>
-    <row r="21"/>
-    <row r="22">
-      <c r="A22" s="4" t="n"/>
-      <c r="B22" s="4" t="inlineStr">
+    <row r="21" ht="40.5" customHeight="1">
+      <c r="A21" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>change_reason</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>varchar(200)</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="n"/>
+      <c r="F21" s="6" t="n"/>
+      <c r="G21" s="6" t="inlineStr">
+        <is>
+          <t>Lý do thay đổi dòng, do ứng dụng đặt cho giao dịch: người dùng nhập với quyết định quản trị, văn bản cố định với thao tác thường lệ. Thay đổi không có lý do sẽ bị từ chối.</t>
+        </is>
+      </c>
+      <c r="H21" s="6" t="inlineStr">
+        <is>
+          <t>Customer moved to a new office</t>
+        </is>
+      </c>
+      <c r="I21" s="6" t="n"/>
+    </row>
+    <row r="22"/>
+    <row r="23">
+      <c r="A23" s="4" t="n"/>
+      <c r="B23" s="4" t="inlineStr">
         <is>
           <t>Chỉ mục (index)</t>
         </is>
       </c>
-      <c r="C22" s="4" t="inlineStr">
+      <c r="C23" s="4" t="inlineStr">
         <is>
           <t>Các cột</t>
         </is>
       </c>
-      <c r="D22" s="4" t="inlineStr">
+      <c r="D23" s="4" t="inlineStr">
         <is>
           <t>Duy nhất</t>
         </is>
       </c>
-      <c r="E22" s="4" t="n"/>
-      <c r="F22" s="4" t="inlineStr">
+      <c r="E23" s="4" t="n"/>
+      <c r="F23" s="4" t="inlineStr">
         <is>
           <t>Ghi chú</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="27" customHeight="1">
-      <c r="A23" s="6" t="n"/>
-      <c r="B23" s="6" t="inlineStr">
+    <row r="24" ht="27" customHeight="1">
+      <c r="A24" s="6" t="n"/>
+      <c r="B24" s="6" t="inlineStr">
         <is>
           <t>ix_membership_history_membership_id_time</t>
         </is>
       </c>
-      <c r="C23" s="6" t="inlineStr">
+      <c r="C24" s="6" t="inlineStr">
         <is>
           <t>membership_id, changed_at</t>
         </is>
       </c>
-      <c r="D23" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E23" s="6" t="n"/>
-      <c r="F23" s="6" t="n"/>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E24" s="6" t="n"/>
+      <c r="F24" s="6" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A7:I20"/>
+  <autoFilter ref="A7:I21"/>
   <hyperlinks>
     <hyperlink ref="A2" location="'Tổng quan'!A1"/>
     <hyperlink ref="A5" location="'memberships'!A1"/>

--- a/docs/design/domain-model/domain-model.xlsx
+++ b/docs/design/domain-model/domain-model.xlsx
@@ -1852,7 +1852,7 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="108" customHeight="1">
+    <row r="34" ht="135" customHeight="1">
       <c r="A34" s="6" t="inlineStr">
         <is>
           <t>19</t>
@@ -1885,7 +1885,7 @@
       </c>
       <c r="G34" s="6" t="inlineStr">
         <is>
-          <t>Ai cầm lái xe nào, trong khoảng thời gian nào (DR-07): tài xế nhận xe bằng cách quét mã QR trên xe hoặc chọn xe ở gần trên ứng dụng, hoặc quản lý nhận xe giúp trên portal. Thay thế driver_vehicle_assignments. Phiên kết thúc khi tài xế trả xe, tài xế khác nhận xe, tài xế nhận xe khác, hoặc xe không di chuyển quá thời gian tự kết thúc của tổ chức (organization_settings). Các sự kiện cần biết tài xế (điểm, chuyến, phiên sạc) lấy tài xế từ đây. Cảnh báo cho tài xế gửi tới tài xế đang nhận xe và portal; xe chạy mà không ai nhận xe sẽ cảnh báo lên portal. Dòng đã đóng không bao giờ bị sửa nên không cần lịch sử thay đổi.</t>
+          <t>Ai cầm lái xe nào, trong khoảng thời gian nào (DR-07): tài xế nhận xe bằng cách quét mã QR trên xe hoặc chọn xe ở gần trên ứng dụng, hoặc quản lý nhận xe giúp trên portal. Thay thế driver_vehicle_assignments. Phiên kết thúc khi tài xế trả xe, tài xế khác nhận xe, tài xế nhận xe khác, hoặc xe không di chuyển quá thời gian tự kết thúc của tổ chức (organization_settings). Các sự kiện cần biết tài xế (điểm, chuyến, phiên sạc) lấy tài xế từ đây. Cảnh báo cho tài xế gửi tới tài xế đang nhận xe và portal; xe chạy mà không ai nhận xe sẽ cảnh báo lên portal. Tổ chức sở hữu xe và chính tài xế (trên ứng dụng) xem được phiên lái; tổ chức tuyển dụng tài xế không xem được phiên lái trên xe của tổ chức khác (DR-08). Dòng đã đóng không bao giờ bị sửa nên không cần lịch sử thay đổi.</t>
         </is>
       </c>
       <c r="H34" s="6" t="n">
@@ -13821,7 +13821,7 @@
     <row r="4">
       <c r="A4" s="11" t="inlineStr">
         <is>
-          <t>Ai cầm lái xe nào, trong khoảng thời gian nào (DR-07): tài xế nhận xe bằng cách quét mã QR trên xe hoặc chọn xe ở gần trên ứng dụng, hoặc quản lý nhận xe giúp trên portal. Thay thế driver_vehicle_assignments. Phiên kết thúc khi tài xế trả xe, tài xế khác nhận xe, tài xế nhận xe khác, hoặc xe không di chuyển quá thời gian tự kết thúc của tổ chức (organization_settings). Các sự kiện cần biết tài xế (điểm, chuyến, phiên sạc) lấy tài xế từ đây. Cảnh báo cho tài xế gửi tới tài xế đang nhận xe và portal; xe chạy mà không ai nhận xe sẽ cảnh báo lên portal. Dòng đã đóng không bao giờ bị sửa nên không cần lịch sử thay đổi.</t>
+          <t>Ai cầm lái xe nào, trong khoảng thời gian nào (DR-07): tài xế nhận xe bằng cách quét mã QR trên xe hoặc chọn xe ở gần trên ứng dụng, hoặc quản lý nhận xe giúp trên portal. Thay thế driver_vehicle_assignments. Phiên kết thúc khi tài xế trả xe, tài xế khác nhận xe, tài xế nhận xe khác, hoặc xe không di chuyển quá thời gian tự kết thúc của tổ chức (organization_settings). Các sự kiện cần biết tài xế (điểm, chuyến, phiên sạc) lấy tài xế từ đây. Cảnh báo cho tài xế gửi tới tài xế đang nhận xe và portal; xe chạy mà không ai nhận xe sẽ cảnh báo lên portal. Tổ chức sở hữu xe và chính tài xế (trên ứng dụng) xem được phiên lái; tổ chức tuyển dụng tài xế không xem được phiên lái trên xe của tổ chức khác (DR-08). Dòng đã đóng không bao giờ bị sửa nên không cần lịch sử thay đổi.</t>
         </is>
       </c>
     </row>

--- a/docs/design/domain-model/domain-model.xlsx
+++ b/docs/design/domain-model/domain-model.xlsx
@@ -87,8 +87,8 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="16" hidden="1">'organization_setting_history'!$A$7:$I$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'vehicles'!$A$7:$I$23</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="18" hidden="1">'vehicle_history'!$A$7:$I$24</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'vehicle_models'!$A$7:$I$18</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'vehicle_model_history'!$A$7:$I$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'vehicle_models'!$A$7:$I$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'vehicle_model_history'!$A$7:$I$21</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'telematics'!$A$6:$I$16</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="22" hidden="1">'vehicle_telemetry'!$A$6:$I$29</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="23" hidden="1">'drivers'!$A$6:$I$16</definedName>
@@ -1559,7 +1559,7 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="67.5" customHeight="1">
+    <row r="26" ht="81" customHeight="1">
       <c r="A26" s="6" t="inlineStr">
         <is>
           <t>14</t>
@@ -1592,11 +1592,11 @@
       </c>
       <c r="G26" s="6" t="inlineStr">
         <is>
-          <t>Danh mục dòng xe và thông số kỹ thuật (VEH-03, VH-15), dùng chung cho mọi tổ chức, do bộ phận vận hành của chúng ta quản lý. Chỉ xe điện: không có số liệu diesel (đường cơ sở diesel cho báo cáo carbon là tính năng riêng). Mọi dòng xe hiện tại đều là đầu kéo; cột loại thân xe sẽ được thêm khi có loại khác. Có lưu lịch sử thay đổi vì báo cáo dựa vào các số liệu này.</t>
+          <t>Danh mục dòng xe và thông số kỹ thuật (VEH-03, VH-15), dùng chung cho mọi tổ chức, do bộ phận vận hành của chúng ta quản lý. Số liệu chỉ được nhập khi đã xác nhận và có thể cập nhật sau (lịch sử lưu các giá trị trước). Chỉ xe điện: không có số liệu diesel (đường cơ sở diesel cho báo cáo carbon là tính năng riêng). Mọi dòng xe hiện tại đều là đầu kéo; cột loại thân xe sẽ được thêm khi có loại khác. Có lưu lịch sử thay đổi vì báo cáo dựa vào các số liệu này.</t>
         </is>
       </c>
       <c r="H26" s="6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I26" s="7" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="H27" s="6" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I27" s="7" t="inlineStr">
         <is>
@@ -10662,7 +10662,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I25"/>
+  <dimension ref="A1:I24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -10700,7 +10700,7 @@
     <row r="4">
       <c r="A4" s="11" t="inlineStr">
         <is>
-          <t>Danh mục dòng xe và thông số kỹ thuật (VEH-03, VH-15), dùng chung cho mọi tổ chức, do bộ phận vận hành của chúng ta quản lý. Chỉ xe điện: không có số liệu diesel (đường cơ sở diesel cho báo cáo carbon là tính năng riêng). Mọi dòng xe hiện tại đều là đầu kéo; cột loại thân xe sẽ được thêm khi có loại khác. Có lưu lịch sử thay đổi vì báo cáo dựa vào các số liệu này.</t>
+          <t>Danh mục dòng xe và thông số kỹ thuật (VEH-03, VH-15), dùng chung cho mọi tổ chức, do bộ phận vận hành của chúng ta quản lý. Số liệu chỉ được nhập khi đã xác nhận và có thể cập nhật sau (lịch sử lưu các giá trị trước). Chỉ xe điện: không có số liệu diesel (đường cơ sở diesel cho báo cáo carbon là tính năng riêng). Mọi dòng xe hiện tại đều là đầu kéo; cột loại thân xe sẽ được thêm khi có loại khác. Có lưu lịch sử thay đổi vì báo cáo dựa vào các số liệu này.</t>
         </is>
       </c>
     </row>
@@ -11018,13 +11018,13 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="27" customHeight="1">
+    <row r="15">
       <c r="A15" s="6" t="n">
         <v>8</v>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>spec_confirmed_at</t>
+          <t>created_at</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
@@ -11034,19 +11034,19 @@
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>có</t>
+          <t>không</t>
         </is>
       </c>
       <c r="E15" s="6" t="n"/>
       <c r="F15" s="6" t="n"/>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>Thời điểm nhà sản xuất xác nhận bằng văn bản các thông số này; NULL khi còn là ước tính, báo cáo sẽ đánh dấu.</t>
+          <t>Thời điểm tạo bản ghi (UTC).</t>
         </is>
       </c>
       <c r="H15" s="6" t="inlineStr">
         <is>
-          <t>2026-08-15T00:00:00Z</t>
+          <t>2026-09-01T02:00:00Z</t>
         </is>
       </c>
       <c r="I15" s="6" t="inlineStr">
@@ -11061,7 +11061,7 @@
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>updated_at</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
@@ -11078,12 +11078,12 @@
       <c r="F16" s="6" t="n"/>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>Thời điểm tạo bản ghi (UTC).</t>
+          <t>Thời điểm bản ghi được sửa gần nhất (UTC).</t>
         </is>
       </c>
       <c r="H16" s="6" t="inlineStr">
         <is>
-          <t>2026-09-01T02:00:00Z</t>
+          <t>2026-09-10T07:15:00Z</t>
         </is>
       </c>
       <c r="I16" s="6" t="inlineStr">
@@ -11092,13 +11092,13 @@
         </is>
       </c>
     </row>
-    <row r="17">
+    <row r="17" ht="27" customHeight="1">
       <c r="A17" s="6" t="n">
         <v>10</v>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>updated_at</t>
+          <t>deleted_at</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
@@ -11108,19 +11108,19 @@
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>không</t>
+          <t>có</t>
         </is>
       </c>
       <c r="E17" s="6" t="n"/>
       <c r="F17" s="6" t="n"/>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>Thời điểm bản ghi được sửa gần nhất (UTC).</t>
+          <t>Thời điểm xóa mềm, chỉ dùng cho dòng xe nhập nhầm; NULL khi bản ghi còn hiệu lực.</t>
         </is>
       </c>
       <c r="H17" s="6" t="inlineStr">
         <is>
-          <t>2026-09-10T07:15:00Z</t>
+          <t>NULL</t>
         </is>
       </c>
       <c r="I17" s="6" t="inlineStr">
@@ -11129,103 +11129,79 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="27" customHeight="1">
-      <c r="A18" s="6" t="n">
-        <v>11</v>
-      </c>
-      <c r="B18" s="6" t="inlineStr">
-        <is>
-          <t>deleted_at</t>
-        </is>
-      </c>
-      <c r="C18" s="6" t="inlineStr">
-        <is>
-          <t>timestamptz</t>
-        </is>
-      </c>
-      <c r="D18" s="6" t="inlineStr">
+    <row r="18"/>
+    <row r="19">
+      <c r="A19" s="4" t="n"/>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>Chỉ mục (index)</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>Các cột</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>Duy nhất</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="n"/>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>Ghi chú</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="27" customHeight="1">
+      <c r="A20" s="6" t="n"/>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>uq_vehicle_models_live_make_model</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>make, model_name</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
         <is>
           <t>có</t>
         </is>
       </c>
-      <c r="E18" s="6" t="n"/>
-      <c r="F18" s="6" t="n"/>
-      <c r="G18" s="6" t="inlineStr">
-        <is>
-          <t>Thời điểm xóa mềm, chỉ dùng cho dòng xe nhập nhầm; NULL khi bản ghi còn hiệu lực.</t>
-        </is>
-      </c>
-      <c r="H18" s="6" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="I18" s="6" t="inlineStr">
-        <is>
-          <t>🔍</t>
-        </is>
-      </c>
-    </row>
-    <row r="19"/>
-    <row r="20">
-      <c r="A20" s="4" t="n"/>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>Chỉ mục (index)</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>Các cột</t>
-        </is>
-      </c>
-      <c r="D20" s="4" t="inlineStr">
-        <is>
-          <t>Duy nhất</t>
-        </is>
-      </c>
-      <c r="E20" s="4" t="n"/>
-      <c r="F20" s="4" t="inlineStr">
-        <is>
-          <t>Ghi chú</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="27" customHeight="1">
-      <c r="A21" s="6" t="n"/>
-      <c r="B21" s="6" t="inlineStr">
-        <is>
-          <t>uq_vehicle_models_live_make_model</t>
-        </is>
-      </c>
-      <c r="C21" s="6" t="inlineStr">
-        <is>
-          <t>make, model_name</t>
-        </is>
-      </c>
-      <c r="D21" s="6" t="inlineStr">
-        <is>
-          <t>có</t>
-        </is>
-      </c>
-      <c r="E21" s="6" t="n"/>
-      <c r="F21" s="6" t="inlineStr">
+      <c r="E20" s="6" t="n"/>
+      <c r="F20" s="6" t="inlineStr">
         <is>
           <t>WHERE deleted_at IS NULL</t>
         </is>
       </c>
     </row>
-    <row r="22"/>
+    <row r="21"/>
+    <row r="22">
+      <c r="A22" s="4" t="n"/>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>Được tham chiếu bởi bảng</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>Cột</t>
+        </is>
+      </c>
+    </row>
     <row r="23">
-      <c r="A23" s="4" t="n"/>
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>Được tham chiếu bởi bảng</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>Cột</t>
+      <c r="A23" s="6" t="n"/>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>vehicles</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>vehicle_model_id</t>
         </is>
       </c>
     </row>
@@ -11233,7 +11209,7 @@
       <c r="A24" s="6" t="n"/>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>vehicles</t>
+          <t>vehicle_model_history</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
@@ -11242,26 +11218,13 @@
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="6" t="n"/>
-      <c r="B25" s="7" t="inlineStr">
-        <is>
-          <t>vehicle_model_history</t>
-        </is>
-      </c>
-      <c r="C25" s="6" t="inlineStr">
-        <is>
-          <t>vehicle_model_id</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A7:I18"/>
+  <autoFilter ref="A7:I17"/>
   <hyperlinks>
     <hyperlink ref="A2" location="'Tổng quan'!A1"/>
     <hyperlink ref="A5" location="'vehicle_model_history'!A1"/>
-    <hyperlink ref="B24" location="'vehicles'!A1"/>
-    <hyperlink ref="B25" location="'vehicle_model_history'!A1"/>
+    <hyperlink ref="B23" location="'vehicles'!A1"/>
+    <hyperlink ref="B24" location="'vehicle_model_history'!A1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -11273,7 +11236,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I25"/>
+  <dimension ref="A1:I24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -11646,13 +11609,13 @@
       </c>
       <c r="I15" s="6" t="n"/>
     </row>
-    <row r="16" ht="27" customHeight="1">
+    <row r="16">
       <c r="A16" s="6" t="n">
         <v>9</v>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>spec_confirmed_at</t>
+          <t>created_at</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
@@ -11669,12 +11632,12 @@
       <c r="F16" s="6" t="n"/>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>Giá trị trước khi thay đổi (vehicle_models.spec_confirmed_at).</t>
+          <t>Giá trị trước khi thay đổi (vehicle_models.created_at).</t>
         </is>
       </c>
       <c r="H16" s="6" t="inlineStr">
         <is>
-          <t>2026-08-15T00:00:00Z</t>
+          <t>2026-09-01T02:00:00Z</t>
         </is>
       </c>
       <c r="I16" s="6" t="n"/>
@@ -11685,7 +11648,7 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>updated_at</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
@@ -11702,12 +11665,12 @@
       <c r="F17" s="6" t="n"/>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>Giá trị trước khi thay đổi (vehicle_models.created_at).</t>
+          <t>Giá trị trước khi thay đổi (vehicle_models.updated_at).</t>
         </is>
       </c>
       <c r="H17" s="6" t="inlineStr">
         <is>
-          <t>2026-09-01T02:00:00Z</t>
+          <t>2026-09-10T07:15:00Z</t>
         </is>
       </c>
       <c r="I17" s="6" t="n"/>
@@ -11718,7 +11681,7 @@
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>updated_at</t>
+          <t>deleted_at</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
@@ -11735,12 +11698,12 @@
       <c r="F18" s="6" t="n"/>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>Giá trị trước khi thay đổi (vehicle_models.updated_at).</t>
+          <t>Giá trị trước khi thay đổi (vehicle_models.deleted_at).</t>
         </is>
       </c>
       <c r="H18" s="6" t="inlineStr">
         <is>
-          <t>2026-09-10T07:15:00Z</t>
+          <t>NULL</t>
         </is>
       </c>
       <c r="I18" s="6" t="n"/>
@@ -11751,7 +11714,7 @@
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>deleted_at</t>
+          <t>changed_at</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
@@ -11761,182 +11724,149 @@
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>có</t>
+          <t>không</t>
         </is>
       </c>
       <c r="E19" s="6" t="n"/>
       <c r="F19" s="6" t="n"/>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>Giá trị trước khi thay đổi (vehicle_models.deleted_at).</t>
+          <t>Thời điểm phiên bản này của dòng bị thay thế.</t>
         </is>
       </c>
       <c r="H19" s="6" t="inlineStr">
         <is>
-          <t>NULL</t>
+          <t>2026-09-10T07:15:00Z</t>
         </is>
       </c>
       <c r="I19" s="6" t="n"/>
     </row>
-    <row r="20">
+    <row r="20" ht="27" customHeight="1">
       <c r="A20" s="6" t="n">
         <v>13</v>
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>changed_at</t>
+          <t>changed_by</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>timestamptz</t>
+          <t>uuid</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E20" s="6" t="n"/>
-      <c r="F20" s="6" t="n"/>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="F20" s="7" t="inlineStr">
+        <is>
+          <t>users.user_id (khi xóa: chặn xóa)</t>
+        </is>
+      </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>Thời điểm phiên bản này của dòng bị thay thế.</t>
+          <t>Người dùng đã thực hiện thay đổi; NULL nếu do hệ thống thực hiện.</t>
         </is>
       </c>
       <c r="H20" s="6" t="inlineStr">
         <is>
-          <t>2026-09-10T07:15:00Z</t>
+          <t>9b2e7d4a-1c3f-4a8e-b6d2-5e0f1a9c3d22</t>
         </is>
       </c>
       <c r="I20" s="6" t="n"/>
     </row>
-    <row r="21" ht="27" customHeight="1">
+    <row r="21" ht="40.5" customHeight="1">
       <c r="A21" s="6" t="n">
         <v>14</v>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>changed_by</t>
+          <t>change_reason</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>uuid</t>
+          <t>varchar(200)</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>có</t>
-        </is>
-      </c>
-      <c r="E21" s="6" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="F21" s="7" t="inlineStr">
-        <is>
-          <t>users.user_id (khi xóa: chặn xóa)</t>
-        </is>
-      </c>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="n"/>
+      <c r="F21" s="6" t="n"/>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>Người dùng đã thực hiện thay đổi; NULL nếu do hệ thống thực hiện.</t>
+          <t>Lý do thay đổi dòng, do ứng dụng đặt cho giao dịch: người dùng nhập với quyết định quản trị, văn bản cố định với thao tác thường lệ. Thay đổi không có lý do sẽ bị từ chối.</t>
         </is>
       </c>
       <c r="H21" s="6" t="inlineStr">
         <is>
-          <t>9b2e7d4a-1c3f-4a8e-b6d2-5e0f1a9c3d22</t>
+          <t>Customer moved to a new office</t>
         </is>
       </c>
       <c r="I21" s="6" t="n"/>
     </row>
-    <row r="22" ht="40.5" customHeight="1">
-      <c r="A22" s="6" t="n">
-        <v>15</v>
-      </c>
-      <c r="B22" s="6" t="inlineStr">
-        <is>
-          <t>change_reason</t>
-        </is>
-      </c>
-      <c r="C22" s="6" t="inlineStr">
-        <is>
-          <t>varchar(200)</t>
-        </is>
-      </c>
-      <c r="D22" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E22" s="6" t="n"/>
-      <c r="F22" s="6" t="n"/>
-      <c r="G22" s="6" t="inlineStr">
-        <is>
-          <t>Lý do thay đổi dòng, do ứng dụng đặt cho giao dịch: người dùng nhập với quyết định quản trị, văn bản cố định với thao tác thường lệ. Thay đổi không có lý do sẽ bị từ chối.</t>
-        </is>
-      </c>
-      <c r="H22" s="6" t="inlineStr">
-        <is>
-          <t>Customer moved to a new office</t>
-        </is>
-      </c>
-      <c r="I22" s="6" t="n"/>
-    </row>
-    <row r="23"/>
-    <row r="24">
-      <c r="A24" s="4" t="n"/>
-      <c r="B24" s="4" t="inlineStr">
+    <row r="22"/>
+    <row r="23">
+      <c r="A23" s="4" t="n"/>
+      <c r="B23" s="4" t="inlineStr">
         <is>
           <t>Chỉ mục (index)</t>
         </is>
       </c>
-      <c r="C24" s="4" t="inlineStr">
+      <c r="C23" s="4" t="inlineStr">
         <is>
           <t>Các cột</t>
         </is>
       </c>
-      <c r="D24" s="4" t="inlineStr">
+      <c r="D23" s="4" t="inlineStr">
         <is>
           <t>Duy nhất</t>
         </is>
       </c>
-      <c r="E24" s="4" t="n"/>
-      <c r="F24" s="4" t="inlineStr">
+      <c r="E23" s="4" t="n"/>
+      <c r="F23" s="4" t="inlineStr">
         <is>
           <t>Ghi chú</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="27" customHeight="1">
-      <c r="A25" s="6" t="n"/>
-      <c r="B25" s="6" t="inlineStr">
+    <row r="24" ht="27" customHeight="1">
+      <c r="A24" s="6" t="n"/>
+      <c r="B24" s="6" t="inlineStr">
         <is>
           <t>ix_vehicle_model_history_vehicle_model_id_time</t>
         </is>
       </c>
-      <c r="C25" s="6" t="inlineStr">
+      <c r="C24" s="6" t="inlineStr">
         <is>
           <t>vehicle_model_id, changed_at</t>
         </is>
       </c>
-      <c r="D25" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E25" s="6" t="n"/>
-      <c r="F25" s="6" t="n"/>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E24" s="6" t="n"/>
+      <c r="F24" s="6" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A7:I22"/>
+  <autoFilter ref="A7:I21"/>
   <hyperlinks>
     <hyperlink ref="A2" location="'Tổng quan'!A1"/>
     <hyperlink ref="A5" location="'vehicle_models'!A1"/>
     <hyperlink ref="F9" location="'vehicle_models'!A1"/>
-    <hyperlink ref="F21" location="'users'!A1"/>
+    <hyperlink ref="F20" location="'users'!A1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/design/domain-model/domain-model.xlsx
+++ b/docs/design/domain-model/domain-model.xlsx
@@ -1471,7 +1471,7 @@
       <c r="G23" s="5" t="inlineStr">
         <is>
           <t>Bản thân chiếc xe tải: định danh (VIN, biển số), thông số và trạng thái kích hoạt.
-• Tại mỗi thời điểm, một xe thuộc một tổ chức (organization_id, owned_since); các chủ trước nằm trong lịch sử thay đổi của xe, và view vehicle_ownership_periods liệt kê mọi giai đoạn sở hữu (VH-10).
+• Tại mỗi thời điểm, một xe thuộc một tổ chức (organization_id, acquired_at); các chủ trước nằm trong lịch sử thay đổi của xe, và view vehicle_ownership_periods liệt kê mọi giai đoạn sở hữu (VH-10).
 • Sau khi bán xe (VH-11): dữ liệu ghi nhận dưới chủ cũ (dữ liệu vận hành và những gì tính từ đó) vẫn thuộc chủ cũ; tình trạng xe (sức khỏe, lỗi, bảo dưỡng, bảo hành) và các tổng tích lũy (quãng đường, năng lượng, chu kỳ sạc) đi theo xe.
 • Chỉ một chủ sở hữu (quyết định ngày 03/10/2026): mỗi xe (và mỗi hồ sơ tài xế) thuộc đúng một tổ chức trong hệ thống. Khi các bên hợp tác (ví dụ chủ xe tự lái hoạt động dưới giấy phép kinh doanh vận tải của một công ty), các bên tự thỏa thuận và khai báo chủ sở hữu cho chúng ta; điều khoản hợp tác của họ nằm ngoài trách nhiệm của chúng ta và không được mô hình hóa.</t>
         </is>
@@ -8106,7 +8106,7 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>owned_since</t>
+          <t>acquired_at</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
@@ -8123,7 +8123,7 @@
       <c r="F10" s="6" t="n"/>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>Thời điểm chủ hiện tại nhận xe (ngày bàn giao, ngày hiệu lực của lần chuyển quyền). Một giai đoạn kết thúc tại owned_since của chủ kế tiếp. Giá trị của chủ đầu tiên là ngày bàn giao xe.</t>
+          <t>Thời điểm chủ hiện tại nhận xe (ngày bàn giao, ngày hiệu lực của lần chuyển quyền). Một giai đoạn kết thúc tại acquired_at của chủ kế tiếp. Giá trị của chủ đầu tiên là ngày bàn giao xe.</t>
         </is>
       </c>
       <c r="H10" s="6" t="inlineStr">
@@ -9199,7 +9199,7 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>owned_since</t>
+          <t>acquired_at</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
@@ -9216,7 +9216,7 @@
       <c r="F11" s="6" t="n"/>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>Giá trị trước khi thay đổi (vehicles.owned_since).</t>
+          <t>Giá trị trước khi thay đổi (vehicles.acquired_at).</t>
         </is>
       </c>
       <c r="H11" s="6" t="inlineStr">
@@ -13505,7 +13505,7 @@
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>owned_since</t>
+          <t>acquired_at</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
@@ -13587,7 +13587,7 @@
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>installed_since</t>
+          <t>installed_at</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
@@ -14240,7 +14240,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>owned_since</t>
+          <t>acquired_at</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
@@ -14257,7 +14257,7 @@
       <c r="F13" s="6" t="n"/>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>Giá trị trước khi thay đổi (batteries.owned_since).</t>
+          <t>Giá trị trước khi thay đổi (batteries.acquired_at).</t>
         </is>
       </c>
       <c r="H13" s="6" t="inlineStr">
@@ -14306,7 +14306,7 @@
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>installed_since</t>
+          <t>installed_at</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
@@ -14323,7 +14323,7 @@
       <c r="F15" s="6" t="n"/>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>Giá trị trước khi thay đổi (batteries.installed_since).</t>
+          <t>Giá trị trước khi thay đổi (batteries.installed_at).</t>
         </is>
       </c>
       <c r="H15" s="6" t="inlineStr">

--- a/docs/design/domain-model/domain-model.xlsx
+++ b/docs/design/domain-model/domain-model.xlsx
@@ -8359,7 +8359,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="94.5" customHeight="1">
+    <row r="17" ht="108" customHeight="1">
       <c r="A17" s="6" t="n">
         <v>10</v>
       </c>
@@ -8382,7 +8382,7 @@
       <c r="F17" s="6" t="n"/>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>Trạng thái phục vụ, luôn do con người đặt (VH-05). ACTIVE: đang phục vụ. MAINTENANCE: đang bảo dưỡng hoặc sửa chữa. DECOMMISSIONED: đã rời hệ thống (thanh lý, bán ra ngoài dịch vụ, hoặc ngừng sử dụng vĩnh viễn); giữ lại cho lịch sử và báo cáo, không nhận dữ liệu mới. Xe đang nhàn rỗi hay không gửi dữ liệu thì không lưu: được tính từ dữ liệu vận hành và T-Box.</t>
+          <t>Trạng thái phục vụ, do con người đặt hoặc do quy tắc nghiệp vụ thay mặt công ty, ví dụ trở lại ACTIVE khi hồ sơ sửa chữa được đóng (VH-05, VH-17). ACTIVE: đang phục vụ. MAINTENANCE: đang bảo dưỡng hoặc sửa chữa. DECOMMISSIONED: đã rời hệ thống (thanh lý, bán ra ngoài dịch vụ, hoặc ngừng sử dụng vĩnh viễn); giữ lại cho lịch sử và báo cáo, không nhận dữ liệu mới. Xe đang nhàn rỗi hay không gửi dữ liệu thì không lưu: được tính từ dữ liệu vận hành và T-Box.</t>
         </is>
       </c>
       <c r="H17" s="6" t="inlineStr">

--- a/docs/design/domain-model/domain-model.xlsx
+++ b/docs/design/domain-model/domain-model.xlsx
@@ -101,7 +101,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="24" hidden="1">'battery_history'!$A$7:$I$24</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="25" hidden="1">'warranties'!$A$7:$I$21</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="26" hidden="1">'warranty_history'!$A$7:$I$25</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="27" hidden="1">'telematics'!$A$6:$I$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="27" hidden="1">'telematics'!$A$6:$I$18</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="28" hidden="1">'vehicle_telemetry'!$A$6:$I$29</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="29" hidden="1">'drivers'!$A$6:$I$16</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="30" hidden="1">'driver_vehicle_assignments'!$A$6:$I$14</definedName>
@@ -628,7 +628,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I104"/>
+  <dimension ref="A1:I103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1999,7 +1999,7 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="27" customHeight="1">
+    <row r="37" ht="40.5" customHeight="1">
       <c r="A37" s="6" t="inlineStr">
         <is>
           <t>18</t>
@@ -2022,7 +2022,7 @@
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
-          <t>Chưa quyết định</t>
+          <t>Khách hàng</t>
         </is>
       </c>
       <c r="F37" s="6" t="inlineStr">
@@ -2032,11 +2032,11 @@
       </c>
       <c r="G37" s="6" t="inlineStr">
         <is>
-          <t>Một thiết bị telematics và chiếc xe nó đang gắn. Thiết bị thuộc khách hàng hay G3 là quyết định D6.</t>
+          <t>Một thiết bị telematics (T-Box) và chiếc xe nó đang gắn. Thiết bị là một tài sản có chủ riêng, là chủ xe hoặc G3 (TX-07); thiết bị thuộc bên bán đi theo xe khi bán xe.</t>
         </is>
       </c>
       <c r="H37" s="6" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I37" s="7" t="inlineStr">
         <is>
@@ -4199,23 +4199,6 @@
       <c r="C103" s="6" t="inlineStr">
         <is>
           <t>wallets, payments</t>
-        </is>
-      </c>
-    </row>
-    <row r="104" ht="40.5" customHeight="1">
-      <c r="A104" s="6" t="inlineStr">
-        <is>
-          <t>D6</t>
-        </is>
-      </c>
-      <c r="B104" s="6" t="inlineStr">
-        <is>
-          <t>Ai sở hữu thiết bị telematics: khách hàng, hay G3 (nằm trong gói thuê bao)?</t>
-        </is>
-      </c>
-      <c r="C104" s="6" t="inlineStr">
-        <is>
-          <t>chủ sở hữu telematics</t>
         </is>
       </c>
     </row>
@@ -9856,7 +9839,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I60"/>
+  <dimension ref="A1:I61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -10626,7 +10609,7 @@
       <c r="A35" s="6" t="n"/>
       <c r="B35" s="7" t="inlineStr">
         <is>
-          <t>vehicle_telemetry</t>
+          <t>telematics</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
@@ -10639,7 +10622,7 @@
       <c r="A36" s="6" t="n"/>
       <c r="B36" s="7" t="inlineStr">
         <is>
-          <t>drivers</t>
+          <t>vehicle_telemetry</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
@@ -10648,11 +10631,11 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="27" customHeight="1">
+    <row r="37">
       <c r="A37" s="6" t="n"/>
       <c r="B37" s="7" t="inlineStr">
         <is>
-          <t>driver_vehicle_assignments</t>
+          <t>drivers</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
@@ -10661,11 +10644,11 @@
         </is>
       </c>
     </row>
-    <row r="38">
+    <row r="38" ht="27" customHeight="1">
       <c r="A38" s="6" t="n"/>
       <c r="B38" s="7" t="inlineStr">
         <is>
-          <t>driving_sessions</t>
+          <t>driver_vehicle_assignments</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
@@ -10678,7 +10661,7 @@
       <c r="A39" s="6" t="n"/>
       <c r="B39" s="7" t="inlineStr">
         <is>
-          <t>charging_credentials</t>
+          <t>driving_sessions</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
@@ -10691,7 +10674,7 @@
       <c r="A40" s="6" t="n"/>
       <c r="B40" s="7" t="inlineStr">
         <is>
-          <t>fleets</t>
+          <t>charging_credentials</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
@@ -10700,11 +10683,11 @@
         </is>
       </c>
     </row>
-    <row r="41" ht="27" customHeight="1">
+    <row r="41">
       <c r="A41" s="6" t="n"/>
       <c r="B41" s="7" t="inlineStr">
         <is>
-          <t>fleet_vehicle_memberships</t>
+          <t>fleets</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
@@ -10713,11 +10696,11 @@
         </is>
       </c>
     </row>
-    <row r="42">
+    <row r="42" ht="27" customHeight="1">
       <c r="A42" s="6" t="n"/>
       <c r="B42" s="7" t="inlineStr">
         <is>
-          <t>fleet_user_assignments</t>
+          <t>fleet_vehicle_memberships</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
@@ -10730,7 +10713,7 @@
       <c r="A43" s="6" t="n"/>
       <c r="B43" s="7" t="inlineStr">
         <is>
-          <t>geofences</t>
+          <t>fleet_user_assignments</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
@@ -10743,7 +10726,7 @@
       <c r="A44" s="6" t="n"/>
       <c r="B44" s="7" t="inlineStr">
         <is>
-          <t>charging_reservations</t>
+          <t>geofences</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
@@ -10756,7 +10739,7 @@
       <c r="A45" s="6" t="n"/>
       <c r="B45" s="7" t="inlineStr">
         <is>
-          <t>charging_sessions</t>
+          <t>charging_reservations</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
@@ -10769,7 +10752,7 @@
       <c r="A46" s="6" t="n"/>
       <c r="B46" s="7" t="inlineStr">
         <is>
-          <t>notifications</t>
+          <t>charging_sessions</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
@@ -10782,7 +10765,7 @@
       <c r="A47" s="6" t="n"/>
       <c r="B47" s="7" t="inlineStr">
         <is>
-          <t>support_cases</t>
+          <t>notifications</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
@@ -10795,7 +10778,7 @@
       <c r="A48" s="6" t="n"/>
       <c r="B48" s="7" t="inlineStr">
         <is>
-          <t>repair_partners</t>
+          <t>support_cases</t>
         </is>
       </c>
       <c r="C48" s="6" t="inlineStr">
@@ -10808,7 +10791,7 @@
       <c r="A49" s="6" t="n"/>
       <c r="B49" s="7" t="inlineStr">
         <is>
-          <t>maintenance_bookings</t>
+          <t>repair_partners</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
@@ -10817,11 +10800,11 @@
         </is>
       </c>
     </row>
-    <row r="50" ht="27" customHeight="1">
+    <row r="50">
       <c r="A50" s="6" t="n"/>
       <c r="B50" s="7" t="inlineStr">
         <is>
-          <t>charging_policy_assignments</t>
+          <t>maintenance_bookings</t>
         </is>
       </c>
       <c r="C50" s="6" t="inlineStr">
@@ -10830,11 +10813,11 @@
         </is>
       </c>
     </row>
-    <row r="51">
+    <row r="51" ht="27" customHeight="1">
       <c r="A51" s="6" t="n"/>
       <c r="B51" s="7" t="inlineStr">
         <is>
-          <t>policy_violations</t>
+          <t>charging_policy_assignments</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
@@ -10847,7 +10830,7 @@
       <c r="A52" s="6" t="n"/>
       <c r="B52" s="7" t="inlineStr">
         <is>
-          <t>payments</t>
+          <t>policy_violations</t>
         </is>
       </c>
       <c r="C52" s="6" t="inlineStr">
@@ -10860,7 +10843,7 @@
       <c r="A53" s="6" t="n"/>
       <c r="B53" s="7" t="inlineStr">
         <is>
-          <t>wallets</t>
+          <t>payments</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
@@ -10873,7 +10856,7 @@
       <c r="A54" s="6" t="n"/>
       <c r="B54" s="7" t="inlineStr">
         <is>
-          <t>wallet_transactions</t>
+          <t>wallets</t>
         </is>
       </c>
       <c r="C54" s="6" t="inlineStr">
@@ -10886,7 +10869,7 @@
       <c r="A55" s="6" t="n"/>
       <c r="B55" s="7" t="inlineStr">
         <is>
-          <t>invoices</t>
+          <t>wallet_transactions</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
@@ -10899,7 +10882,7 @@
       <c r="A56" s="6" t="n"/>
       <c r="B56" s="7" t="inlineStr">
         <is>
-          <t>invoice_lines</t>
+          <t>invoices</t>
         </is>
       </c>
       <c r="C56" s="6" t="inlineStr">
@@ -10912,7 +10895,7 @@
       <c r="A57" s="6" t="n"/>
       <c r="B57" s="7" t="inlineStr">
         <is>
-          <t>subscriptions</t>
+          <t>invoice_lines</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
@@ -10925,7 +10908,7 @@
       <c r="A58" s="6" t="n"/>
       <c r="B58" s="7" t="inlineStr">
         <is>
-          <t>driver_scores</t>
+          <t>subscriptions</t>
         </is>
       </c>
       <c r="C58" s="6" t="inlineStr">
@@ -10938,7 +10921,7 @@
       <c r="A59" s="6" t="n"/>
       <c r="B59" s="7" t="inlineStr">
         <is>
-          <t>trips</t>
+          <t>driver_scores</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
@@ -10951,10 +10934,23 @@
       <c r="A60" s="6" t="n"/>
       <c r="B60" s="7" t="inlineStr">
         <is>
+          <t>trips</t>
+        </is>
+      </c>
+      <c r="C60" s="6" t="inlineStr">
+        <is>
+          <t>organization_id</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="6" t="n"/>
+      <c r="B61" s="7" t="inlineStr">
+        <is>
           <t>organization_history</t>
         </is>
       </c>
-      <c r="C60" s="6" t="inlineStr">
+      <c r="C61" s="6" t="inlineStr">
         <is>
           <t>organization_id</t>
         </is>
@@ -10975,32 +10971,33 @@
     <hyperlink ref="B32" location="'organization_settings'!A1"/>
     <hyperlink ref="B33" location="'vehicles'!A1"/>
     <hyperlink ref="B34" location="'batteries'!A1"/>
-    <hyperlink ref="B35" location="'vehicle_telemetry'!A1"/>
-    <hyperlink ref="B36" location="'drivers'!A1"/>
-    <hyperlink ref="B37" location="'driver_vehicle_assignments'!A1"/>
-    <hyperlink ref="B38" location="'driving_sessions'!A1"/>
-    <hyperlink ref="B39" location="'charging_credentials'!A1"/>
-    <hyperlink ref="B40" location="'fleets'!A1"/>
-    <hyperlink ref="B41" location="'fleet_vehicle_memberships'!A1"/>
-    <hyperlink ref="B42" location="'fleet_user_assignments'!A1"/>
-    <hyperlink ref="B43" location="'geofences'!A1"/>
-    <hyperlink ref="B44" location="'charging_reservations'!A1"/>
-    <hyperlink ref="B45" location="'charging_sessions'!A1"/>
-    <hyperlink ref="B46" location="'notifications'!A1"/>
-    <hyperlink ref="B47" location="'support_cases'!A1"/>
-    <hyperlink ref="B48" location="'repair_partners'!A1"/>
-    <hyperlink ref="B49" location="'maintenance_bookings'!A1"/>
-    <hyperlink ref="B50" location="'charging_policy_assignments'!A1"/>
-    <hyperlink ref="B51" location="'policy_violations'!A1"/>
-    <hyperlink ref="B52" location="'payments'!A1"/>
-    <hyperlink ref="B53" location="'wallets'!A1"/>
-    <hyperlink ref="B54" location="'wallet_transactions'!A1"/>
-    <hyperlink ref="B55" location="'invoices'!A1"/>
-    <hyperlink ref="B56" location="'invoice_lines'!A1"/>
-    <hyperlink ref="B57" location="'subscriptions'!A1"/>
-    <hyperlink ref="B58" location="'driver_scores'!A1"/>
-    <hyperlink ref="B59" location="'trips'!A1"/>
-    <hyperlink ref="B60" location="'organization_history'!A1"/>
+    <hyperlink ref="B35" location="'telematics'!A1"/>
+    <hyperlink ref="B36" location="'vehicle_telemetry'!A1"/>
+    <hyperlink ref="B37" location="'drivers'!A1"/>
+    <hyperlink ref="B38" location="'driver_vehicle_assignments'!A1"/>
+    <hyperlink ref="B39" location="'driving_sessions'!A1"/>
+    <hyperlink ref="B40" location="'charging_credentials'!A1"/>
+    <hyperlink ref="B41" location="'fleets'!A1"/>
+    <hyperlink ref="B42" location="'fleet_vehicle_memberships'!A1"/>
+    <hyperlink ref="B43" location="'fleet_user_assignments'!A1"/>
+    <hyperlink ref="B44" location="'geofences'!A1"/>
+    <hyperlink ref="B45" location="'charging_reservations'!A1"/>
+    <hyperlink ref="B46" location="'charging_sessions'!A1"/>
+    <hyperlink ref="B47" location="'notifications'!A1"/>
+    <hyperlink ref="B48" location="'support_cases'!A1"/>
+    <hyperlink ref="B49" location="'repair_partners'!A1"/>
+    <hyperlink ref="B50" location="'maintenance_bookings'!A1"/>
+    <hyperlink ref="B51" location="'charging_policy_assignments'!A1"/>
+    <hyperlink ref="B52" location="'policy_violations'!A1"/>
+    <hyperlink ref="B53" location="'payments'!A1"/>
+    <hyperlink ref="B54" location="'wallets'!A1"/>
+    <hyperlink ref="B55" location="'wallet_transactions'!A1"/>
+    <hyperlink ref="B56" location="'invoices'!A1"/>
+    <hyperlink ref="B57" location="'invoice_lines'!A1"/>
+    <hyperlink ref="B58" location="'subscriptions'!A1"/>
+    <hyperlink ref="B59" location="'driver_scores'!A1"/>
+    <hyperlink ref="B60" location="'trips'!A1"/>
+    <hyperlink ref="B61" location="'organization_history'!A1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -16420,7 +16417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I29"/>
+  <dimension ref="A1:I31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -16451,14 +16448,14 @@
     <row r="3">
       <c r="A3" s="11" t="inlineStr">
         <is>
-          <t>Miền nghiệp vụ: Thiết bị telematics (telematics)   ·   Chủ sở hữu dữ liệu: Chưa quyết định   ·   Tính năng: F-G1, F-J1, F-J2, F-J3</t>
+          <t>Miền nghiệp vụ: Thiết bị telematics (telematics)   ·   Chủ sở hữu dữ liệu: Khách hàng   ·   Tính năng: F-G1, F-J1, F-J2, F-J3</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="11" t="inlineStr">
         <is>
-          <t>Một thiết bị telematics và chiếc xe nó đang gắn. Thiết bị thuộc khách hàng hay G3 là quyết định D6.</t>
+          <t>Một thiết bị telematics (T-Box) và chiếc xe nó đang gắn. Thiết bị là một tài sản có chủ riêng, là chủ xe hoặc G3 (TX-07); thiết bị thuộc bên bán đi theo xe khi bán xe.</t>
         </is>
       </c>
     </row>
@@ -16590,7 +16587,7 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>vehicle_id</t>
+          <t>organization_id</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
@@ -16600,7 +16597,7 @@
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>có</t>
+          <t>không</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
@@ -16610,17 +16607,17 @@
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>vehicles.vehicle_id (khi xóa: đặt về NULL)</t>
+          <t>organizations.organization_id (khi xóa: chặn xóa)</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>Xe mà thiết bị đang gắn; NULL khi đã tháo. Mỗi xe có tối đa một thiết bị còn hiệu lực (chưa xóa mềm).</t>
+          <t>Tổ chức đang sở hữu thiết bị: chủ xe, hoặc G3 khi G3 cung cấp thiết bị (ví dụ kèm gói thuê bao).</t>
         </is>
       </c>
       <c r="H9" s="6" t="inlineStr">
         <is>
-          <t>7a4c1e9b-3d2f-4b8a-a6c5-1e0d9f8b7a44</t>
+          <t>3f6c2a1e-8b4d-4e2a-9c1f-0a7d5b2e4c11</t>
         </is>
       </c>
       <c r="I9" s="6" t="n"/>
@@ -16631,12 +16628,12 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>acquired_at</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>telematicstatus</t>
+          <t>timestamptz</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
@@ -16648,28 +16645,28 @@
       <c r="F10" s="6" t="n"/>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>Trạng thái vận hành của thiết bị.</t>
+          <t>Thời điểm chủ hiện tại nhận thiết bị (DM-22).</t>
         </is>
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>ACTIVE</t>
+          <t>2026-06-01T00:00:00Z</t>
         </is>
       </c>
       <c r="I10" s="6" t="n"/>
     </row>
-    <row r="11">
+    <row r="11" ht="27" customHeight="1">
       <c r="A11" s="6" t="n">
         <v>5</v>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>firmware_version</t>
+          <t>vehicle_id</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>varchar(50)</t>
+          <t>uuid</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
@@ -16677,65 +16674,73 @@
           <t>có</t>
         </is>
       </c>
-      <c r="E11" s="6" t="n"/>
-      <c r="F11" s="6" t="n"/>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>vehicles.vehicle_id (khi xóa: đặt về NULL)</t>
+        </is>
+      </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>Phiên bản firmware đang chạy trên thiết bị.</t>
+          <t>Xe mà thiết bị đang gắn; NULL khi đã tháo. Mỗi xe có tối đa một thiết bị còn hiệu lực (chưa xóa mềm).</t>
         </is>
       </c>
       <c r="H11" s="6" t="inlineStr">
         <is>
-          <t>1.4.2</t>
+          <t>7a4c1e9b-3d2f-4b8a-a6c5-1e0d9f8b7a44</t>
         </is>
       </c>
       <c r="I11" s="6" t="n"/>
     </row>
-    <row r="12" ht="27" customHeight="1">
+    <row r="12">
       <c r="A12" s="6" t="n">
         <v>6</v>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>telemetry_interval_seconds</t>
+          <t>status</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>telematicstatus</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>có</t>
+          <t>không</t>
         </is>
       </c>
       <c r="E12" s="6" t="n"/>
       <c r="F12" s="6" t="n"/>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>Chu kỳ gửi dữ liệu (giây) đã đẩy xuống thiết bị qua MQTT lần gần nhất (F-J2); NULL trước lần đẩy đầu tiên.</t>
+          <t>Trạng thái vận hành của thiết bị.</t>
         </is>
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="I12" s="6" t="n"/>
     </row>
-    <row r="13" ht="27" customHeight="1">
+    <row r="13">
       <c r="A13" s="6" t="n">
         <v>7</v>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>config_pushed_at</t>
+          <t>firmware_version</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>timestamptz</t>
+          <t>varchar(50)</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
@@ -16747,56 +16752,56 @@
       <c r="F13" s="6" t="n"/>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>Thời điểm đẩy chu kỳ đó lần gần nhất; NULL trước lần đẩy đầu tiên.</t>
+          <t>Phiên bản firmware đang chạy trên thiết bị.</t>
         </is>
       </c>
       <c r="H13" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12T03:00:00Z</t>
+          <t>1.4.2</t>
         </is>
       </c>
       <c r="I13" s="6" t="n"/>
     </row>
-    <row r="14">
+    <row r="14" ht="27" customHeight="1">
       <c r="A14" s="6" t="n">
         <v>8</v>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>telemetry_interval_seconds</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>timestamptz</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>không</t>
+          <t>có</t>
         </is>
       </c>
       <c r="E14" s="6" t="n"/>
       <c r="F14" s="6" t="n"/>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>Thời điểm tạo bản ghi (UTC).</t>
+          <t>Chu kỳ gửi dữ liệu (giây) đã đẩy xuống thiết bị qua MQTT lần gần nhất (F-J2); NULL trước lần đẩy đầu tiên.</t>
         </is>
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
-          <t>2026-09-01T02:00:00Z</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I14" s="6" t="n"/>
     </row>
-    <row r="15">
+    <row r="15" ht="27" customHeight="1">
       <c r="A15" s="6" t="n">
         <v>9</v>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>updated_at</t>
+          <t>config_pushed_at</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
@@ -16806,30 +16811,30 @@
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>không</t>
+          <t>có</t>
         </is>
       </c>
       <c r="E15" s="6" t="n"/>
       <c r="F15" s="6" t="n"/>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>Thời điểm bản ghi được sửa gần nhất (UTC).</t>
+          <t>Thời điểm đẩy chu kỳ đó lần gần nhất; NULL trước lần đẩy đầu tiên.</t>
         </is>
       </c>
       <c r="H15" s="6" t="inlineStr">
         <is>
-          <t>2026-09-10T07:15:00Z</t>
+          <t>2026-09-12T03:00:00Z</t>
         </is>
       </c>
       <c r="I15" s="6" t="n"/>
     </row>
-    <row r="16" ht="27" customHeight="1">
+    <row r="16">
       <c r="A16" s="6" t="n">
         <v>10</v>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>deleted_at</t>
+          <t>created_at</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
@@ -16839,125 +16844,151 @@
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>có</t>
+          <t>không</t>
         </is>
       </c>
       <c r="E16" s="6" t="n"/>
       <c r="F16" s="6" t="n"/>
       <c r="G16" s="6" t="inlineStr">
         <is>
+          <t>Thời điểm tạo bản ghi (UTC).</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-01T02:00:00Z</t>
+        </is>
+      </c>
+      <c r="I16" s="6" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>updated_at</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>timestamptz</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="n"/>
+      <c r="F17" s="6" t="n"/>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>Thời điểm bản ghi được sửa gần nhất (UTC).</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-10T07:15:00Z</t>
+        </is>
+      </c>
+      <c r="I17" s="6" t="n"/>
+    </row>
+    <row r="18" ht="27" customHeight="1">
+      <c r="A18" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>deleted_at</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>timestamptz</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="n"/>
+      <c r="F18" s="6" t="n"/>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
           <t>Thời điểm xóa mềm; NULL khi bản ghi còn hiệu lực. Không bao giờ xóa hẳn.</t>
         </is>
       </c>
-      <c r="H16" s="6" t="inlineStr">
+      <c r="H18" s="6" t="inlineStr">
         <is>
           <t>NULL</t>
         </is>
       </c>
-      <c r="I16" s="6" t="n"/>
-    </row>
-    <row r="17"/>
-    <row r="18">
-      <c r="A18" s="4" t="n"/>
-      <c r="B18" s="4" t="inlineStr">
+      <c r="I18" s="6" t="n"/>
+    </row>
+    <row r="19"/>
+    <row r="20">
+      <c r="A20" s="4" t="n"/>
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <t>Kiểu enum</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="C20" s="4" t="inlineStr">
         <is>
           <t>Giá trị cho phép</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="27" customHeight="1">
-      <c r="A19" s="6" t="n"/>
-      <c r="B19" s="6" t="inlineStr">
+    <row r="21" ht="27" customHeight="1">
+      <c r="A21" s="6" t="n"/>
+      <c r="B21" s="6" t="inlineStr">
         <is>
           <t>telematicstatus</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr">
+      <c r="C21" s="6" t="inlineStr">
         <is>
           <t>ACTIVE, INACTIVE, MAINTENANCE</t>
         </is>
       </c>
     </row>
-    <row r="20"/>
-    <row r="21">
-      <c r="A21" s="4" t="n"/>
-      <c r="B21" s="4" t="inlineStr">
+    <row r="22"/>
+    <row r="23">
+      <c r="A23" s="4" t="n"/>
+      <c r="B23" s="4" t="inlineStr">
         <is>
           <t>Chỉ mục (index)</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="C23" s="4" t="inlineStr">
         <is>
           <t>Các cột</t>
         </is>
       </c>
-      <c r="D21" s="4" t="inlineStr">
+      <c r="D23" s="4" t="inlineStr">
         <is>
           <t>Duy nhất</t>
         </is>
       </c>
-      <c r="E21" s="4" t="n"/>
-      <c r="F21" s="4" t="inlineStr">
+      <c r="E23" s="4" t="n"/>
+      <c r="F23" s="4" t="inlineStr">
         <is>
           <t>Ghi chú</t>
         </is>
       </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="6" t="n"/>
-      <c r="B22" s="6" t="inlineStr">
-        <is>
-          <t>ix_telematics_status</t>
-        </is>
-      </c>
-      <c r="C22" s="6" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="D22" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E22" s="6" t="n"/>
-      <c r="F22" s="6" t="n"/>
-    </row>
-    <row r="23" ht="27" customHeight="1">
-      <c r="A23" s="6" t="n"/>
-      <c r="B23" s="6" t="inlineStr">
-        <is>
-          <t>ix_telematics_telematic_serial</t>
-        </is>
-      </c>
-      <c r="C23" s="6" t="inlineStr">
-        <is>
-          <t>telematic_serial</t>
-        </is>
-      </c>
-      <c r="D23" s="6" t="inlineStr">
-        <is>
-          <t>có</t>
-        </is>
-      </c>
-      <c r="E23" s="6" t="n"/>
-      <c r="F23" s="6" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="6" t="n"/>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>ix_telematics_vehicle_id</t>
+          <t>ix_telematics_status</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>vehicle_id</t>
+          <t>status</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
@@ -16972,73 +17003,114 @@
       <c r="A25" s="6" t="n"/>
       <c r="B25" s="6" t="inlineStr">
         <is>
+          <t>ix_telematics_telematic_serial</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>telematic_serial</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E25" s="6" t="n"/>
+      <c r="F25" s="6" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="n"/>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>ix_telematics_vehicle_id</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>vehicle_id</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E26" s="6" t="n"/>
+      <c r="F26" s="6" t="n"/>
+    </row>
+    <row r="27" ht="27" customHeight="1">
+      <c r="A27" s="6" t="n"/>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
           <t>uq_telematics_active_vehicle</t>
         </is>
       </c>
-      <c r="C25" s="6" t="inlineStr">
+      <c r="C27" s="6" t="inlineStr">
         <is>
           <t>vehicle_id</t>
         </is>
       </c>
-      <c r="D25" s="6" t="inlineStr">
+      <c r="D27" s="6" t="inlineStr">
         <is>
           <t>có</t>
         </is>
       </c>
-      <c r="E25" s="6" t="n"/>
-      <c r="F25" s="6" t="inlineStr">
+      <c r="E27" s="6" t="n"/>
+      <c r="F27" s="6" t="inlineStr">
         <is>
           <t>WHERE deleted_at IS NULL</t>
         </is>
       </c>
     </row>
-    <row r="26"/>
-    <row r="27">
-      <c r="A27" s="4" t="n"/>
-      <c r="B27" s="4" t="inlineStr">
+    <row r="28"/>
+    <row r="29">
+      <c r="A29" s="4" t="n"/>
+      <c r="B29" s="4" t="inlineStr">
         <is>
           <t>Được tham chiếu bởi bảng</t>
         </is>
       </c>
-      <c r="C27" s="4" t="inlineStr">
+      <c r="C29" s="4" t="inlineStr">
         <is>
           <t>Cột</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="6" t="n"/>
-      <c r="B28" s="7" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="6" t="n"/>
+      <c r="B30" s="7" t="inlineStr">
         <is>
           <t>warranties</t>
         </is>
       </c>
-      <c r="C28" s="6" t="inlineStr">
+      <c r="C30" s="6" t="inlineStr">
         <is>
           <t>telematic_id</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="6" t="n"/>
-      <c r="B29" s="7" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="6" t="n"/>
+      <c r="B31" s="7" t="inlineStr">
         <is>
           <t>vehicle_telemetry</t>
         </is>
       </c>
-      <c r="C29" s="6" t="inlineStr">
+      <c r="C31" s="6" t="inlineStr">
         <is>
           <t>telematic_id</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A6:I16"/>
+  <autoFilter ref="A6:I18"/>
   <hyperlinks>
     <hyperlink ref="A2" location="'Tổng quan'!A1"/>
-    <hyperlink ref="F9" location="'vehicles'!A1"/>
-    <hyperlink ref="B28" location="'warranties'!A1"/>
-    <hyperlink ref="B29" location="'vehicle_telemetry'!A1"/>
+    <hyperlink ref="F9" location="'organizations'!A1"/>
+    <hyperlink ref="F11" location="'vehicles'!A1"/>
+    <hyperlink ref="B30" location="'warranties'!A1"/>
+    <hyperlink ref="B31" location="'vehicle_telemetry'!A1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/design/domain-model/domain-model.xlsx
+++ b/docs/design/domain-model/domain-model.xlsx
@@ -91,8 +91,8 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'legal_documents'!$A$6:$I$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'user_role_assignments'!$A$6:$I$14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'access_audit_logs'!$A$6:$I$16</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'organization_settings'!$A$7:$I$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="16" hidden="1">'organization_setting_history'!$A$7:$I$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'organization_settings'!$A$7:$I$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="16" hidden="1">'organization_setting_history'!$A$7:$I$16</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'vehicles'!$A$7:$I$23</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="18" hidden="1">'vehicle_history'!$A$7:$I$23</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'vehicle_models'!$A$7:$I$17</definedName>
@@ -103,9 +103,9 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="24" hidden="1">'battery_history'!$A$7:$I$24</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="25" hidden="1">'warranties'!$A$7:$I$21</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="26" hidden="1">'warranty_history'!$A$7:$I$25</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="27" hidden="1">'telematics'!$A$8:$I$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="27" hidden="1">'telematics'!$A$8:$I$23</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="28" hidden="1">'telematic_history'!$A$7:$I$23</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="29" hidden="1">'telematic_state'!$A$7:$I$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="29" hidden="1">'telematic_state'!$A$7:$I$18</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="30" hidden="1">'vehicle_telemetry'!$A$6:$I$29</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="31" hidden="1">'drivers'!$A$6:$I$16</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="32" hidden="1">'driver_vehicle_assignments'!$A$6:$I$14</definedName>
@@ -1408,7 +1408,7 @@
         </is>
       </c>
       <c r="H21" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I21" s="7" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
         </is>
       </c>
       <c r="H22" s="6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I22" s="7" t="inlineStr">
         <is>
@@ -2040,7 +2040,7 @@
         </is>
       </c>
       <c r="H37" s="6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I37" s="7" t="inlineStr">
         <is>
@@ -2093,7 +2093,7 @@
         </is>
       </c>
     </row>
-    <row r="39" ht="67.5" customHeight="1">
+    <row r="39" ht="94.5" customHeight="1">
       <c r="A39" s="6" t="inlineStr">
         <is>
           <t>19</t>
@@ -2126,11 +2126,11 @@
       </c>
       <c r="G39" s="6" t="inlineStr">
         <is>
-          <t>Những gì thiết bị tự báo về mình trên topic trạng thái MQTT (quan sát, không phải quyết định): chỉ giá trị mới nhất, không lưu lịch sử thay đổi (TX-08). Được tạo cùng lúc với thiết bị nên mỗi thiết bị luôn có đúng một dòng trạng thái. Thiết bị có trực tuyến hay không được tính từ dữ liệu vận hành (TX-06), không lưu.</t>
+          <t>Những gì thiết bị tự báo về mình trên topic trạng thái MQTT, khoảng mỗi ngày một lần (quan sát, không phải quyết định): firmware, chu kỳ đang dùng, SIM, nguồn điện, sóng, bộ nhớ, GNSS (TX-08, TX-09; các trường của bản tin là tạm thời cho tới khi nhà cung cấp xác nhận). Chỉ giá trị mới nhất, không lưu lịch sử thay đổi. Được tạo cùng lúc với thiết bị nên mỗi thiết bị luôn có đúng một dòng trạng thái. Thiết bị có trực tuyến hay không được tính từ dữ liệu vận hành (TX-06), không lưu.</t>
         </is>
       </c>
       <c r="H39" s="6" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="I39" s="7" t="inlineStr">
         <is>
@@ -7388,7 +7388,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -7526,13 +7526,13 @@
       </c>
       <c r="I8" s="6" t="n"/>
     </row>
-    <row r="9" ht="27" customHeight="1">
+    <row r="9" ht="54" customHeight="1">
       <c r="A9" s="6" t="n">
         <v>2</v>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>driving_session_auto_end_minutes</t>
+          <t>telemetry_interval_seconds</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
@@ -7549,12 +7549,12 @@
       <c r="F9" s="6" t="n"/>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>Phiên lái tự kết thúc khi xe không di chuyển trong khoảng thời gian này (DR-07); mặc định 120.</t>
+          <t>Chu kỳ T-Box trên các xe của tổ chức gửi dữ liệu (giây) (TX-09); mặc định 10, trong giới hạn backend cho phép. Được đẩy xuống mọi thiết bị trên xe của tổ chức khi thay đổi, và xuống thiết bị khi được gắn lên xe.</t>
         </is>
       </c>
       <c r="H9" s="6" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I9" s="6" t="inlineStr">
@@ -7563,18 +7563,18 @@
         </is>
       </c>
     </row>
-    <row r="10">
+    <row r="10" ht="27" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>3</v>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>driving_session_auto_end_minutes</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>timestamptz</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
@@ -7586,12 +7586,12 @@
       <c r="F10" s="6" t="n"/>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>Thời điểm tạo bản ghi (UTC).</t>
+          <t>Phiên lái tự kết thúc khi xe không di chuyển trong khoảng thời gian này (DR-07); mặc định 120.</t>
         </is>
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>2026-09-01T02:00:00Z</t>
+          <t>120</t>
         </is>
       </c>
       <c r="I10" s="6" t="inlineStr">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>updated_at</t>
+          <t>created_at</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
@@ -7623,54 +7623,91 @@
       <c r="F11" s="6" t="n"/>
       <c r="G11" s="6" t="inlineStr">
         <is>
+          <t>Thời điểm tạo bản ghi (UTC).</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-01T02:00:00Z</t>
+        </is>
+      </c>
+      <c r="I11" s="6" t="inlineStr">
+        <is>
+          <t>🔍</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>updated_at</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>timestamptz</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="n"/>
+      <c r="F12" s="6" t="n"/>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
           <t>Thời điểm thiết lập được sửa gần nhất (UTC).</t>
         </is>
       </c>
-      <c r="H11" s="6" t="inlineStr">
+      <c r="H12" s="6" t="inlineStr">
         <is>
           <t>2026-09-10T07:15:00Z</t>
         </is>
       </c>
-      <c r="I11" s="6" t="inlineStr">
+      <c r="I12" s="6" t="inlineStr">
         <is>
           <t>🔍</t>
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" s="4" t="n"/>
-      <c r="B13" s="4" t="inlineStr">
+    <row r="13"/>
+    <row r="14">
+      <c r="A14" s="4" t="n"/>
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>Được tham chiếu bởi bảng</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>Cột</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="27" customHeight="1">
-      <c r="A14" s="6" t="n"/>
-      <c r="B14" s="7" t="inlineStr">
+    <row r="15" ht="27" customHeight="1">
+      <c r="A15" s="6" t="n"/>
+      <c r="B15" s="7" t="inlineStr">
         <is>
           <t>organization_setting_history</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr">
+      <c r="C15" s="6" t="inlineStr">
         <is>
           <t>organization_id</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A7:I11"/>
+  <autoFilter ref="A7:I12"/>
   <hyperlinks>
     <hyperlink ref="A2" location="'Tổng quan'!A1"/>
     <hyperlink ref="A5" location="'organization_setting_history'!A1"/>
     <hyperlink ref="F8" location="'organizations'!A1"/>
-    <hyperlink ref="B14" location="'organization_setting_history'!A1"/>
+    <hyperlink ref="B15" location="'organization_setting_history'!A1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7682,7 +7719,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -7863,7 +7900,7 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>driving_session_auto_end_minutes</t>
+          <t>telemetry_interval_seconds</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
@@ -7880,12 +7917,12 @@
       <c r="F10" s="6" t="n"/>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>Giá trị trước khi thay đổi (organization_settings.driving_session_auto_end_minutes).</t>
+          <t>Giá trị trước khi thay đổi (organization_settings.telemetry_interval_seconds).</t>
         </is>
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I10" s="6" t="n"/>
@@ -7896,12 +7933,12 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>driving_session_auto_end_minutes</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>timestamptz</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
@@ -7913,12 +7950,12 @@
       <c r="F11" s="6" t="n"/>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>Giá trị trước khi thay đổi (organization_settings.created_at).</t>
+          <t>Giá trị trước khi thay đổi (organization_settings.driving_session_auto_end_minutes).</t>
         </is>
       </c>
       <c r="H11" s="6" t="inlineStr">
         <is>
-          <t>2026-09-01T02:00:00Z</t>
+          <t>120</t>
         </is>
       </c>
       <c r="I11" s="6" t="n"/>
@@ -7929,7 +7966,7 @@
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>updated_at</t>
+          <t>created_at</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
@@ -7946,23 +7983,23 @@
       <c r="F12" s="6" t="n"/>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>Giá trị trước khi thay đổi (organization_settings.updated_at).</t>
+          <t>Giá trị trước khi thay đổi (organization_settings.created_at).</t>
         </is>
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>2026-09-10T07:15:00Z</t>
+          <t>2026-09-01T02:00:00Z</t>
         </is>
       </c>
       <c r="I12" s="6" t="n"/>
     </row>
-    <row r="13">
+    <row r="13" ht="27" customHeight="1">
       <c r="A13" s="6" t="n">
         <v>6</v>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>changed_at</t>
+          <t>updated_at</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
@@ -7972,14 +8009,14 @@
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>không</t>
+          <t>có</t>
         </is>
       </c>
       <c r="E13" s="6" t="n"/>
       <c r="F13" s="6" t="n"/>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>Thời điểm phiên bản này của dòng bị thay thế.</t>
+          <t>Giá trị trước khi thay đổi (organization_settings.updated_at).</t>
         </is>
       </c>
       <c r="H13" s="6" t="inlineStr">
@@ -7989,132 +8026,165 @@
       </c>
       <c r="I13" s="6" t="n"/>
     </row>
-    <row r="14" ht="27" customHeight="1">
+    <row r="14">
       <c r="A14" s="6" t="n">
         <v>7</v>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>changed_by</t>
+          <t>changed_at</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>uuid</t>
+          <t>timestamptz</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>có</t>
-        </is>
-      </c>
-      <c r="E14" s="6" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="F14" s="7" t="inlineStr">
-        <is>
-          <t>users.user_id (khi xóa: chặn xóa)</t>
-        </is>
-      </c>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="n"/>
+      <c r="F14" s="6" t="n"/>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>Người dùng đã thực hiện thay đổi; NULL nếu do hệ thống thực hiện.</t>
+          <t>Thời điểm phiên bản này của dòng bị thay thế.</t>
         </is>
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
-          <t>9b2e7d4a-1c3f-4a8e-b6d2-5e0f1a9c3d22</t>
+          <t>2026-09-10T07:15:00Z</t>
         </is>
       </c>
       <c r="I14" s="6" t="n"/>
     </row>
-    <row r="15" ht="40.5" customHeight="1">
+    <row r="15" ht="27" customHeight="1">
       <c r="A15" s="6" t="n">
         <v>8</v>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
+          <t>changed_by</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>uuid</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>users.user_id (khi xóa: chặn xóa)</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>Người dùng đã thực hiện thay đổi; NULL nếu do hệ thống thực hiện.</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>9b2e7d4a-1c3f-4a8e-b6d2-5e0f1a9c3d22</t>
+        </is>
+      </c>
+      <c r="I15" s="6" t="n"/>
+    </row>
+    <row r="16" ht="40.5" customHeight="1">
+      <c r="A16" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
           <t>change_reason</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr">
+      <c r="C16" s="6" t="inlineStr">
         <is>
           <t>varchar(200)</t>
         </is>
       </c>
-      <c r="D15" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E15" s="6" t="n"/>
-      <c r="F15" s="6" t="n"/>
-      <c r="G15" s="6" t="inlineStr">
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="n"/>
+      <c r="F16" s="6" t="n"/>
+      <c r="G16" s="6" t="inlineStr">
         <is>
           <t>Lý do thay đổi dòng, do ứng dụng đặt cho giao dịch: người dùng nhập với quyết định quản trị, văn bản cố định với thao tác thường lệ. Thay đổi không có lý do sẽ bị từ chối.</t>
         </is>
       </c>
-      <c r="H15" s="6" t="inlineStr">
+      <c r="H16" s="6" t="inlineStr">
         <is>
           <t>Customer moved to a new office</t>
         </is>
       </c>
-      <c r="I15" s="6" t="n"/>
-    </row>
-    <row r="16"/>
-    <row r="17">
-      <c r="A17" s="4" t="n"/>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="I16" s="6" t="n"/>
+    </row>
+    <row r="17"/>
+    <row r="18">
+      <c r="A18" s="4" t="n"/>
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t>Chỉ mục (index)</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C18" s="4" t="inlineStr">
         <is>
           <t>Các cột</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="D18" s="4" t="inlineStr">
         <is>
           <t>Duy nhất</t>
         </is>
       </c>
-      <c r="E17" s="4" t="n"/>
-      <c r="F17" s="4" t="inlineStr">
+      <c r="E18" s="4" t="n"/>
+      <c r="F18" s="4" t="inlineStr">
         <is>
           <t>Ghi chú</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="40.5" customHeight="1">
-      <c r="A18" s="6" t="n"/>
-      <c r="B18" s="6" t="inlineStr">
+    <row r="19" ht="40.5" customHeight="1">
+      <c r="A19" s="6" t="n"/>
+      <c r="B19" s="6" t="inlineStr">
         <is>
           <t>ix_organization_setting_history_organization_id_time</t>
         </is>
       </c>
-      <c r="C18" s="6" t="inlineStr">
+      <c r="C19" s="6" t="inlineStr">
         <is>
           <t>organization_id, changed_at</t>
         </is>
       </c>
-      <c r="D18" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E18" s="6" t="n"/>
-      <c r="F18" s="6" t="n"/>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="n"/>
+      <c r="F19" s="6" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A7:I15"/>
+  <autoFilter ref="A7:I16"/>
   <hyperlinks>
     <hyperlink ref="A2" location="'Tổng quan'!A1"/>
     <hyperlink ref="A5" location="'organization_settings'!A1"/>
     <hyperlink ref="F9" location="'organization_settings'!A1"/>
-    <hyperlink ref="F14" location="'users'!A1"/>
+    <hyperlink ref="F15" location="'users'!A1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -16517,7 +16587,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I37"/>
+  <dimension ref="A1:I38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -16658,35 +16728,35 @@
       </c>
       <c r="I9" s="6" t="n"/>
     </row>
-    <row r="10" ht="27" customHeight="1">
+    <row r="10" ht="40.5" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>2</v>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>telematic_serial</t>
+          <t>imei</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>varchar(50)</t>
+          <t>varchar(15)</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>không</t>
+          <t>có</t>
         </is>
       </c>
       <c r="E10" s="6" t="n"/>
       <c r="F10" s="6" t="n"/>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>Số serial in trên thiết bị; cũng là định danh MQTT. Duy nhất trong các thiết bị chưa xóa.</t>
+          <t>Số IMEI của modem thiết bị, nhập khi cấp phát; định danh phần cứng cố định, duy nhất trong các thiết bị chưa xóa. NULL khi chưa nhập.</t>
         </is>
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>TBX-2409-000123</t>
+          <t>356938035643809</t>
         </is>
       </c>
       <c r="I10" s="6" t="inlineStr">
@@ -16701,12 +16771,12 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>organization_id</t>
+          <t>telematic_serial</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>uuid</t>
+          <t>varchar(50)</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
@@ -16714,24 +16784,16 @@
           <t>không</t>
         </is>
       </c>
-      <c r="E11" s="6" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="F11" s="7" t="inlineStr">
-        <is>
-          <t>organizations.organization_id (khi xóa: chặn xóa)</t>
-        </is>
-      </c>
+      <c r="E11" s="6" t="n"/>
+      <c r="F11" s="6" t="n"/>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>Tổ chức đang sở hữu thiết bị: chủ xe, hoặc G3 khi G3 cung cấp thiết bị (ví dụ kèm gói thuê bao).</t>
+          <t>Số serial in trên thiết bị; cũng là định danh MQTT. Duy nhất trong các thiết bị chưa xóa.</t>
         </is>
       </c>
       <c r="H11" s="6" t="inlineStr">
         <is>
-          <t>3f6c2a1e-8b4d-4e2a-9c1f-0a7d5b2e4c11</t>
+          <t>TBX-2409-000123</t>
         </is>
       </c>
       <c r="I11" s="6" t="inlineStr">
@@ -16740,18 +16802,18 @@
         </is>
       </c>
     </row>
-    <row r="12">
+    <row r="12" ht="27" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>4</v>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>acquired_at</t>
+          <t>organization_id</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>timestamptz</t>
+          <t>uuid</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
@@ -16759,16 +16821,24 @@
           <t>không</t>
         </is>
       </c>
-      <c r="E12" s="6" t="n"/>
-      <c r="F12" s="6" t="n"/>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>organizations.organization_id (khi xóa: chặn xóa)</t>
+        </is>
+      </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>Thời điểm chủ hiện tại nhận thiết bị (DM-22).</t>
+          <t>Tổ chức đang sở hữu thiết bị: chủ xe, hoặc G3 khi G3 cung cấp thiết bị (ví dụ kèm gói thuê bao).</t>
         </is>
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>2026-06-01T00:00:00Z</t>
+          <t>3f6c2a1e-8b4d-4e2a-9c1f-0a7d5b2e4c11</t>
         </is>
       </c>
       <c r="I12" s="6" t="inlineStr">
@@ -16777,43 +16847,35 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="40.5" customHeight="1">
+    <row r="13">
       <c r="A13" s="6" t="n">
         <v>5</v>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>vehicle_id</t>
+          <t>acquired_at</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>uuid</t>
+          <t>timestamptz</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>có</t>
-        </is>
-      </c>
-      <c r="E13" s="6" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="F13" s="7" t="inlineStr">
-        <is>
-          <t>vehicles.vehicle_id (khi xóa: đặt về NULL)</t>
-        </is>
-      </c>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="n"/>
+      <c r="F13" s="6" t="n"/>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>Xe mà thiết bị đang gắn; NULL khi trong kho hoặc đã tháo. Mỗi xe gắn tối đa một thiết bị. Các xe trước lấy từ view telematic_installation_periods (DM-22).</t>
+          <t>Thời điểm chủ hiện tại nhận thiết bị (DM-22).</t>
         </is>
       </c>
       <c r="H13" s="6" t="inlineStr">
         <is>
-          <t>7a4c1e9b-3d2f-4b8a-a6c5-1e0d9f8b7a44</t>
+          <t>2026-06-01T00:00:00Z</t>
         </is>
       </c>
       <c r="I13" s="6" t="inlineStr">
@@ -16822,18 +16884,18 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="27" customHeight="1">
+    <row r="14" ht="40.5" customHeight="1">
       <c r="A14" s="6" t="n">
         <v>6</v>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>installed_at</t>
+          <t>vehicle_id</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>timestamptz</t>
+          <t>uuid</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
@@ -16841,16 +16903,24 @@
           <t>có</t>
         </is>
       </c>
-      <c r="E14" s="6" t="n"/>
-      <c r="F14" s="6" t="n"/>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="F14" s="7" t="inlineStr">
+        <is>
+          <t>vehicles.vehicle_id (khi xóa: đặt về NULL)</t>
+        </is>
+      </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>Thời điểm thiết bị được gắn lên xe hiện tại; NULL khi chưa gắn (DM-22).</t>
+          <t>Xe mà thiết bị đang gắn; NULL khi trong kho hoặc đã tháo. Mỗi xe gắn tối đa một thiết bị. Các xe trước lấy từ view telematic_installation_periods (DM-22).</t>
         </is>
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
-          <t>2026-06-01T00:00:00Z</t>
+          <t>7a4c1e9b-3d2f-4b8a-a6c5-1e0d9f8b7a44</t>
         </is>
       </c>
       <c r="I14" s="6" t="inlineStr">
@@ -16859,35 +16929,35 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="81" customHeight="1">
+    <row r="15" ht="27" customHeight="1">
       <c r="A15" s="6" t="n">
         <v>7</v>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>installed_at</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>telematicstatus</t>
+          <t>timestamptz</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>không</t>
+          <t>có</t>
         </is>
       </c>
       <c r="E15" s="6" t="n"/>
       <c r="F15" s="6" t="n"/>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>Trạng thái do con người đặt (TX-08). ACTIVE: dùng được. MAINTENANCE: đang sửa chữa hoặc kiểm tra. DECOMMISSIONED: đã rời hệ thống (thanh lý, trả lại). Đang gắn hay trong kho đọc từ vehicle_id; có gửi dữ liệu hay im lặng được tính từ dữ liệu vận hành (TX-06). Chỉ thiết bị đang gắn và ACTIVE mới nhận cấu hình.</t>
+          <t>Thời điểm thiết bị được gắn lên xe hiện tại; NULL khi chưa gắn (DM-22).</t>
         </is>
       </c>
       <c r="H15" s="6" t="inlineStr">
         <is>
-          <t>ACTIVE</t>
+          <t>2026-06-01T00:00:00Z</t>
         </is>
       </c>
       <c r="I15" s="6" t="inlineStr">
@@ -16896,35 +16966,35 @@
         </is>
       </c>
     </row>
-    <row r="16">
+    <row r="16" ht="81" customHeight="1">
       <c r="A16" s="6" t="n">
         <v>8</v>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>status_reason</t>
+          <t>status</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>varchar(200)</t>
+          <t>telematicstatus</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>có</t>
+          <t>không</t>
         </is>
       </c>
       <c r="E16" s="6" t="n"/>
       <c r="F16" s="6" t="n"/>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>Lý do của trạng thái hiện tại; NULL khi ACTIVE.</t>
+          <t>Trạng thái do con người đặt (TX-08). ACTIVE: dùng được. MAINTENANCE: đang sửa chữa hoặc kiểm tra. DECOMMISSIONED: đã rời hệ thống (thanh lý, trả lại). Đang gắn hay trong kho đọc từ vehicle_id; có gửi dữ liệu hay im lặng được tính từ dữ liệu vận hành (TX-06). Chỉ thiết bị đang gắn và ACTIVE mới nhận cấu hình.</t>
         </is>
       </c>
       <c r="H16" s="6" t="inlineStr">
         <is>
-          <t>Antenna replaced at the Hanoi workshop</t>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="I16" s="6" t="inlineStr">
@@ -16933,18 +17003,18 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="27" customHeight="1">
+    <row r="17">
       <c r="A17" s="6" t="n">
         <v>9</v>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>firmware_version</t>
+          <t>status_reason</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>varchar(50)</t>
+          <t>varchar(200)</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
@@ -16956,28 +17026,32 @@
       <c r="F17" s="6" t="n"/>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>[Sẽ bỏ: TX-08] Firmware nhập qua API; thiết bị tự báo nên chuyển sang telematic_state.</t>
+          <t>Lý do của trạng thái hiện tại; NULL khi ACTIVE.</t>
         </is>
       </c>
       <c r="H17" s="6" t="inlineStr">
         <is>
-          <t>1.4.2</t>
-        </is>
-      </c>
-      <c r="I17" s="6" t="n"/>
-    </row>
-    <row r="18" ht="54" customHeight="1">
+          <t>Antenna replaced at the Hanoi workshop</t>
+        </is>
+      </c>
+      <c r="I17" s="6" t="inlineStr">
+        <is>
+          <t>🔍</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="27" customHeight="1">
       <c r="A18" s="6" t="n">
         <v>10</v>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>telemetry_interval_seconds</t>
+          <t>firmware_version</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>varchar(50)</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
@@ -16989,32 +17063,28 @@
       <c r="F18" s="6" t="n"/>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>Chu kỳ gửi dữ liệu (giây) đã đẩy xuống thiết bị qua MQTT lần gần nhất (F-J2), do con người chọn; NULL trước lần đẩy đầu tiên. Là một quyết định, nên lịch sử thay đổi ghi lại ai đổi, khi nào và vì sao.</t>
+          <t>[Sẽ bỏ: TX-08] Firmware nhập qua API; thiết bị tự báo nên chuyển sang telematic_state.</t>
         </is>
       </c>
       <c r="H18" s="6" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="I18" s="6" t="inlineStr">
-        <is>
-          <t>🔍</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="40.5" customHeight="1">
+          <t>1.4.2</t>
+        </is>
+      </c>
+      <c r="I18" s="6" t="n"/>
+    </row>
+    <row r="19" ht="54" customHeight="1">
       <c r="A19" s="6" t="n">
         <v>11</v>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>config_pushed_at</t>
+          <t>telemetry_interval_seconds</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>timestamptz</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
@@ -17026,23 +17096,23 @@
       <c r="F19" s="6" t="n"/>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>[Sẽ bỏ: TX-08] Thời điểm đẩy chu kỳ lần gần nhất; việc đẩy xảy ra khi lưu thay đổi nên lấy từ changed_at của lịch sử (DM-23).</t>
+          <t>[Sẽ bỏ: TX-09] Chu kỳ gửi đã đẩy xuống thiết bị này; chu kỳ nay là thiết lập của tổ chức (organization_settings), còn chu kỳ thiết bị thực sự dùng được báo trong telematic_state.</t>
         </is>
       </c>
       <c r="H19" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12T03:00:00Z</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I19" s="6" t="n"/>
     </row>
-    <row r="20">
+    <row r="20" ht="40.5" customHeight="1">
       <c r="A20" s="6" t="n">
         <v>12</v>
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>config_pushed_at</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
@@ -17052,26 +17122,22 @@
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>không</t>
+          <t>có</t>
         </is>
       </c>
       <c r="E20" s="6" t="n"/>
       <c r="F20" s="6" t="n"/>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>Thời điểm tạo bản ghi (UTC).</t>
+          <t>[Sẽ bỏ: TX-08] Thời điểm đẩy chu kỳ lần gần nhất; việc đẩy xảy ra khi lưu thay đổi nên lấy từ changed_at của lịch sử (DM-23).</t>
         </is>
       </c>
       <c r="H20" s="6" t="inlineStr">
         <is>
-          <t>2026-09-01T02:00:00Z</t>
-        </is>
-      </c>
-      <c r="I20" s="6" t="inlineStr">
-        <is>
-          <t>🔍</t>
-        </is>
-      </c>
+          <t>2026-09-12T03:00:00Z</t>
+        </is>
+      </c>
+      <c r="I20" s="6" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="6" t="n">
@@ -17079,7 +17145,7 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>updated_at</t>
+          <t>created_at</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
@@ -17096,12 +17162,12 @@
       <c r="F21" s="6" t="n"/>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>Thời điểm bản ghi được sửa gần nhất (UTC).</t>
+          <t>Thời điểm tạo bản ghi (UTC).</t>
         </is>
       </c>
       <c r="H21" s="6" t="inlineStr">
         <is>
-          <t>2026-09-10T07:15:00Z</t>
+          <t>2026-09-01T02:00:00Z</t>
         </is>
       </c>
       <c r="I21" s="6" t="inlineStr">
@@ -17110,13 +17176,13 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="54" customHeight="1">
+    <row r="22">
       <c r="A22" s="6" t="n">
         <v>14</v>
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>deleted_at</t>
+          <t>updated_at</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
@@ -17126,152 +17192,165 @@
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>có</t>
+          <t>không</t>
         </is>
       </c>
       <c r="E22" s="6" t="n"/>
       <c r="F22" s="6" t="n"/>
       <c r="G22" s="6" t="inlineStr">
         <is>
+          <t>Thời điểm bản ghi được sửa gần nhất (UTC).</t>
+        </is>
+      </c>
+      <c r="H22" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-10T07:15:00Z</t>
+        </is>
+      </c>
+      <c r="I22" s="6" t="inlineStr">
+        <is>
+          <t>🔍</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="54" customHeight="1">
+      <c r="A23" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>deleted_at</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>timestamptz</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="n"/>
+      <c r="F23" s="6" t="n"/>
+      <c r="G23" s="6" t="inlineStr">
+        <is>
           <t>Thời điểm xóa mềm, chỉ dùng cho thiết bị nhập nhầm; thiết bị thật rời hệ thống được chuyển sang DECOMMISSIONED và tháo khỏi xe, các xe trước được giữ trong lịch sử (TX-08). NULL khi bản ghi còn hiệu lực.</t>
         </is>
       </c>
-      <c r="H22" s="6" t="inlineStr">
+      <c r="H23" s="6" t="inlineStr">
         <is>
           <t>NULL</t>
         </is>
       </c>
-      <c r="I22" s="6" t="inlineStr">
+      <c r="I23" s="6" t="inlineStr">
         <is>
           <t>🔍</t>
         </is>
       </c>
     </row>
-    <row r="23"/>
-    <row r="24">
-      <c r="A24" s="4" t="n"/>
-      <c r="B24" s="4" t="inlineStr">
+    <row r="24"/>
+    <row r="25">
+      <c r="A25" s="4" t="n"/>
+      <c r="B25" s="4" t="inlineStr">
         <is>
           <t>Kiểu enum</t>
         </is>
       </c>
-      <c r="C24" s="4" t="inlineStr">
+      <c r="C25" s="4" t="inlineStr">
         <is>
           <t>Giá trị cho phép</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="54" customHeight="1">
-      <c r="A25" s="6" t="n"/>
-      <c r="B25" s="6" t="inlineStr">
+    <row r="26" ht="54" customHeight="1">
+      <c r="A26" s="6" t="n"/>
+      <c r="B26" s="6" t="inlineStr">
         <is>
           <t>telematicstatus</t>
         </is>
       </c>
-      <c r="C25" s="6" t="inlineStr">
+      <c r="C26" s="6" t="inlineStr">
         <is>
           <t>ACTIVE, INACTIVE (sẽ bỏ), MAINTENANCE, DECOMMISSIONED (dự kiến)</t>
         </is>
       </c>
     </row>
-    <row r="26"/>
-    <row r="27">
-      <c r="A27" s="4" t="n"/>
-      <c r="B27" s="4" t="inlineStr">
+    <row r="27"/>
+    <row r="28">
+      <c r="A28" s="4" t="n"/>
+      <c r="B28" s="4" t="inlineStr">
         <is>
           <t>Chỉ mục (index)</t>
         </is>
       </c>
-      <c r="C27" s="4" t="inlineStr">
+      <c r="C28" s="4" t="inlineStr">
         <is>
           <t>Các cột</t>
         </is>
       </c>
-      <c r="D27" s="4" t="inlineStr">
+      <c r="D28" s="4" t="inlineStr">
         <is>
           <t>Duy nhất</t>
         </is>
       </c>
-      <c r="E27" s="4" t="n"/>
-      <c r="F27" s="4" t="inlineStr">
+      <c r="E28" s="4" t="n"/>
+      <c r="F28" s="4" t="inlineStr">
         <is>
           <t>Ghi chú</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="6" t="n"/>
-      <c r="B28" s="6" t="inlineStr">
-        <is>
-          <t>ix_telematics_status</t>
-        </is>
-      </c>
-      <c r="C28" s="6" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="D28" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E28" s="6" t="n"/>
-      <c r="F28" s="6" t="n"/>
-    </row>
-    <row r="29" ht="40.5" customHeight="1">
+    <row r="29">
       <c r="A29" s="6" t="n"/>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>ix_telematics_telematic_serial</t>
+          <t>ix_telematics_status</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>telematic_serial</t>
+          <t>status</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>có</t>
+          <t>không</t>
         </is>
       </c>
       <c r="E29" s="6" t="n"/>
-      <c r="F29" s="6" t="inlineStr">
-        <is>
-          <t>Planned (TX-08): unique only among devices not deleted (WHERE deleted_at IS NULL)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="27" customHeight="1">
+      <c r="F29" s="6" t="n"/>
+    </row>
+    <row r="30" ht="40.5" customHeight="1">
       <c r="A30" s="6" t="n"/>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>ix_telematics_vehicle_id</t>
+          <t>ix_telematics_telematic_serial</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>vehicle_id</t>
+          <t>telematic_serial</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>không</t>
+          <t>có</t>
         </is>
       </c>
       <c r="E30" s="6" t="n"/>
       <c r="F30" s="6" t="inlineStr">
         <is>
-          <t>To be removed (TX-08): the unique index below serves it</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="54" customHeight="1">
+          <t>Planned (TX-08): unique only among devices not deleted (WHERE deleted_at IS NULL)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="27" customHeight="1">
       <c r="A31" s="6" t="n"/>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>uq_telematics_active_vehicle</t>
+          <t>ix_telematics_vehicle_id</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
@@ -17281,40 +17360,51 @@
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>có</t>
+          <t>không</t>
         </is>
       </c>
       <c r="E31" s="6" t="n"/>
       <c r="F31" s="6" t="inlineStr">
         <is>
+          <t>To be removed (TX-08): the unique index below serves it</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="54" customHeight="1">
+      <c r="A32" s="6" t="n"/>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>uq_telematics_active_vehicle</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t>vehicle_id</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E32" s="6" t="n"/>
+      <c r="F32" s="6" t="inlineStr">
+        <is>
           <t>WHERE deleted_at IS NULL; planned (TX-08): WHERE vehicle_id IS NOT NULL AND deleted_at IS NULL, one device per truck</t>
         </is>
       </c>
     </row>
-    <row r="32"/>
-    <row r="33">
-      <c r="A33" s="4" t="n"/>
-      <c r="B33" s="4" t="inlineStr">
+    <row r="33"/>
+    <row r="34">
+      <c r="A34" s="4" t="n"/>
+      <c r="B34" s="4" t="inlineStr">
         <is>
           <t>Được tham chiếu bởi bảng</t>
         </is>
       </c>
-      <c r="C33" s="4" t="inlineStr">
+      <c r="C34" s="4" t="inlineStr">
         <is>
           <t>Cột</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="6" t="n"/>
-      <c r="B34" s="7" t="inlineStr">
-        <is>
-          <t>warranties</t>
-        </is>
-      </c>
-      <c r="C34" s="6" t="inlineStr">
-        <is>
-          <t>telematic_id</t>
         </is>
       </c>
     </row>
@@ -17322,7 +17412,7 @@
       <c r="A35" s="6" t="n"/>
       <c r="B35" s="7" t="inlineStr">
         <is>
-          <t>telematic_state</t>
+          <t>warranties</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
@@ -17335,7 +17425,7 @@
       <c r="A36" s="6" t="n"/>
       <c r="B36" s="7" t="inlineStr">
         <is>
-          <t>vehicle_telemetry</t>
+          <t>telematic_state</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
@@ -17348,27 +17438,40 @@
       <c r="A37" s="6" t="n"/>
       <c r="B37" s="7" t="inlineStr">
         <is>
+          <t>vehicle_telemetry</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="inlineStr">
+        <is>
+          <t>telematic_id</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="6" t="n"/>
+      <c r="B38" s="7" t="inlineStr">
+        <is>
           <t>telematic_history</t>
         </is>
       </c>
-      <c r="C37" s="6" t="inlineStr">
+      <c r="C38" s="6" t="inlineStr">
         <is>
           <t>telematic_id</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A8:I22"/>
+  <autoFilter ref="A8:I23"/>
   <hyperlinks>
     <hyperlink ref="A2" location="'Tổng quan'!A1"/>
     <hyperlink ref="A5" location="'telematic_history'!A1"/>
     <hyperlink ref="A6" location="'telematic_state'!A1"/>
-    <hyperlink ref="F11" location="'organizations'!A1"/>
-    <hyperlink ref="F13" location="'vehicles'!A1"/>
-    <hyperlink ref="B34" location="'warranties'!A1"/>
-    <hyperlink ref="B35" location="'telematic_state'!A1"/>
-    <hyperlink ref="B36" location="'vehicle_telemetry'!A1"/>
-    <hyperlink ref="B37" location="'telematic_history'!A1"/>
+    <hyperlink ref="F12" location="'organizations'!A1"/>
+    <hyperlink ref="F14" location="'vehicles'!A1"/>
+    <hyperlink ref="B35" location="'warranties'!A1"/>
+    <hyperlink ref="B36" location="'telematic_state'!A1"/>
+    <hyperlink ref="B37" location="'vehicle_telemetry'!A1"/>
+    <hyperlink ref="B38" location="'telematic_history'!A1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -17561,12 +17664,12 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>telematic_serial</t>
+          <t>imei</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>varchar(50)</t>
+          <t>varchar(15)</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
@@ -17578,12 +17681,12 @@
       <c r="F10" s="6" t="n"/>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>Giá trị trước khi thay đổi (telematics.telematic_serial).</t>
+          <t>Giá trị trước khi thay đổi (telematics.imei).</t>
         </is>
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>TBX-2409-000123</t>
+          <t>356938035643809</t>
         </is>
       </c>
       <c r="I10" s="6" t="n"/>
@@ -17594,12 +17697,12 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>organization_id</t>
+          <t>telematic_serial</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>uuid</t>
+          <t>varchar(50)</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
@@ -17611,12 +17714,12 @@
       <c r="F11" s="6" t="n"/>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>Giá trị trước khi thay đổi (telematics.organization_id).</t>
+          <t>Giá trị trước khi thay đổi (telematics.telematic_serial).</t>
         </is>
       </c>
       <c r="H11" s="6" t="inlineStr">
         <is>
-          <t>3f6c2a1e-8b4d-4e2a-9c1f-0a7d5b2e4c11</t>
+          <t>TBX-2409-000123</t>
         </is>
       </c>
       <c r="I11" s="6" t="n"/>
@@ -17627,12 +17730,12 @@
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>acquired_at</t>
+          <t>organization_id</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>timestamptz</t>
+          <t>uuid</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
@@ -17644,12 +17747,12 @@
       <c r="F12" s="6" t="n"/>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>Giá trị trước khi thay đổi (telematics.acquired_at).</t>
+          <t>Giá trị trước khi thay đổi (telematics.organization_id).</t>
         </is>
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>2026-06-01T00:00:00Z</t>
+          <t>3f6c2a1e-8b4d-4e2a-9c1f-0a7d5b2e4c11</t>
         </is>
       </c>
       <c r="I12" s="6" t="n"/>
@@ -17660,12 +17763,12 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>vehicle_id</t>
+          <t>acquired_at</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>uuid</t>
+          <t>timestamptz</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
@@ -17677,12 +17780,12 @@
       <c r="F13" s="6" t="n"/>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>Giá trị trước khi thay đổi (telematics.vehicle_id).</t>
+          <t>Giá trị trước khi thay đổi (telematics.acquired_at).</t>
         </is>
       </c>
       <c r="H13" s="6" t="inlineStr">
         <is>
-          <t>7a4c1e9b-3d2f-4b8a-a6c5-1e0d9f8b7a44</t>
+          <t>2026-06-01T00:00:00Z</t>
         </is>
       </c>
       <c r="I13" s="6" t="n"/>
@@ -17693,12 +17796,12 @@
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>installed_at</t>
+          <t>vehicle_id</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>timestamptz</t>
+          <t>uuid</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
@@ -17710,12 +17813,12 @@
       <c r="F14" s="6" t="n"/>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>Giá trị trước khi thay đổi (telematics.installed_at).</t>
+          <t>Giá trị trước khi thay đổi (telematics.vehicle_id).</t>
         </is>
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
-          <t>2026-06-01T00:00:00Z</t>
+          <t>7a4c1e9b-3d2f-4b8a-a6c5-1e0d9f8b7a44</t>
         </is>
       </c>
       <c r="I14" s="6" t="n"/>
@@ -17726,12 +17829,12 @@
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>installed_at</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>telematicstatus</t>
+          <t>timestamptz</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
@@ -17743,12 +17846,12 @@
       <c r="F15" s="6" t="n"/>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>Giá trị trước khi thay đổi (telematics.status).</t>
+          <t>Giá trị trước khi thay đổi (telematics.installed_at).</t>
         </is>
       </c>
       <c r="H15" s="6" t="inlineStr">
         <is>
-          <t>ACTIVE</t>
+          <t>2026-06-01T00:00:00Z</t>
         </is>
       </c>
       <c r="I15" s="6" t="n"/>
@@ -17759,12 +17862,12 @@
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>status_reason</t>
+          <t>status</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>varchar(200)</t>
+          <t>telematicstatus</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
@@ -17776,28 +17879,28 @@
       <c r="F16" s="6" t="n"/>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>Giá trị trước khi thay đổi (telematics.status_reason).</t>
+          <t>Giá trị trước khi thay đổi (telematics.status).</t>
         </is>
       </c>
       <c r="H16" s="6" t="inlineStr">
         <is>
-          <t>Antenna replaced at the Hanoi workshop</t>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="I16" s="6" t="n"/>
     </row>
-    <row r="17" ht="27" customHeight="1">
+    <row r="17">
       <c r="A17" s="6" t="n">
         <v>10</v>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>telemetry_interval_seconds</t>
+          <t>status_reason</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>varchar(200)</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
@@ -17809,12 +17912,12 @@
       <c r="F17" s="6" t="n"/>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>Giá trị trước khi thay đổi (telematics.telemetry_interval_seconds).</t>
+          <t>Giá trị trước khi thay đổi (telematics.status_reason).</t>
         </is>
       </c>
       <c r="H17" s="6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>Antenna replaced at the Hanoi workshop</t>
         </is>
       </c>
       <c r="I17" s="6" t="n"/>
@@ -18856,7 +18959,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -18894,7 +18997,7 @@
     <row r="4">
       <c r="A4" s="11" t="inlineStr">
         <is>
-          <t>Những gì thiết bị tự báo về mình trên topic trạng thái MQTT (quan sát, không phải quyết định): chỉ giá trị mới nhất, không lưu lịch sử thay đổi (TX-08). Được tạo cùng lúc với thiết bị nên mỗi thiết bị luôn có đúng một dòng trạng thái. Thiết bị có trực tuyến hay không được tính từ dữ liệu vận hành (TX-06), không lưu.</t>
+          <t>Những gì thiết bị tự báo về mình trên topic trạng thái MQTT, khoảng mỗi ngày một lần (quan sát, không phải quyết định): firmware, chu kỳ đang dùng, SIM, nguồn điện, sóng, bộ nhớ, GNSS (TX-08, TX-09; các trường của bản tin là tạm thời cho tới khi nhà cung cấp xác nhận). Chỉ giá trị mới nhất, không lưu lịch sử thay đổi. Được tạo cùng lúc với thiết bị nên mỗi thiết bị luôn có đúng một dòng trạng thái. Thiết bị có trực tuyến hay không được tính từ dữ liệu vận hành (TX-06), không lưu.</t>
         </is>
       </c>
     </row>
@@ -18994,7 +19097,7 @@
       </c>
       <c r="I8" s="6" t="n"/>
     </row>
-    <row r="9" ht="27" customHeight="1">
+    <row r="9">
       <c r="A9" s="6" t="n">
         <v>2</v>
       </c>
@@ -19017,7 +19120,7 @@
       <c r="F9" s="6" t="n"/>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>Phiên bản firmware thiết bị báo gần nhất trên topic trạng thái; NULL trước lần báo đầu tiên.</t>
+          <t>Phiên bản firmware thiết bị báo gần nhất.</t>
         </is>
       </c>
       <c r="H9" s="6" t="inlineStr">
@@ -19027,18 +19130,18 @@
       </c>
       <c r="I9" s="6" t="n"/>
     </row>
-    <row r="10" ht="27" customHeight="1">
+    <row r="10" ht="40.5" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>3</v>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>firmware_reported_at</t>
+          <t>reported_telemetry_interval_seconds</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>timestamptz</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
@@ -19050,18 +19153,282 @@
       <c r="F10" s="6" t="n"/>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>Thời điểm thiết bị báo phiên bản đó; NULL trước lần báo đầu tiên.</t>
+          <t>Chu kỳ gửi mà thiết bị báo đang dùng; khác với thiết lập của chủ xe nghĩa là lần đẩy gần nhất chưa được áp dụng (TX-09).</t>
         </is>
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I10" s="6" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>sim_iccid</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>varchar(22)</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="n"/>
+      <c r="F11" s="6" t="n"/>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>Số ICCID của SIM trong thiết bị; đổi khi thay SIM.</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>8984049000001234567</t>
+        </is>
+      </c>
+      <c r="I11" s="6" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>is_esim</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>boolean</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="n"/>
+      <c r="F12" s="6" t="n"/>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>TRUE khi SIM là eSIM.</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="I12" s="6" t="n"/>
+    </row>
+    <row r="13" ht="27" customHeight="1">
+      <c r="A13" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>sim_data_status</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>varchar(20)</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="n"/>
+      <c r="F13" s="6" t="n"/>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>Trạng thái dữ liệu di động của SIM theo báo cáo (giá trị tạm: ACTIVE | NO_DATA | SUSPENDED | NO_SIM).</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="I13" s="6" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>supply_voltage_v</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>numeric(5,2)</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="n"/>
+      <c r="F14" s="6" t="n"/>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>Điện áp nguồn cấp tại thiết bị (V).</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>24.30</t>
+        </is>
+      </c>
+      <c r="I14" s="6" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>signal_dbm</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>smallint</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="n"/>
+      <c r="F15" s="6" t="n"/>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>Cường độ sóng di động (dBm, càng gần 0 càng mạnh).</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>-78</t>
+        </is>
+      </c>
+      <c r="I15" s="6" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>storage_used_percent</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>numeric(5,2)</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="n"/>
+      <c r="F16" s="6" t="n"/>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>Tỷ lệ bộ nhớ thiết bị đã dùng, 0-100.</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>41.50</t>
+        </is>
+      </c>
+      <c r="I16" s="6" t="n"/>
+    </row>
+    <row r="17" ht="27" customHeight="1">
+      <c r="A17" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>gnss_status</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>varchar(20)</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="n"/>
+      <c r="F17" s="6" t="n"/>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>Trạng thái định vị vệ tinh theo báo cáo (giá trị tạm: FIX | NO_FIX | ANTENNA_FAULT).</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>FIX</t>
+        </is>
+      </c>
+      <c r="I17" s="6" t="n"/>
+    </row>
+    <row r="18" ht="27" customHeight="1">
+      <c r="A18" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>reported_at</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>timestamptz</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="n"/>
+      <c r="F18" s="6" t="n"/>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>Thời điểm nhận báo cáo trạng thái gần nhất; mọi cột phía trên lấy từ báo cáo đó. NULL trước lần báo đầu tiên.</t>
+        </is>
+      </c>
+      <c r="H18" s="6" t="inlineStr">
+        <is>
           <t>2026-09-14T00:30:00Z</t>
         </is>
       </c>
-      <c r="I10" s="6" t="n"/>
+      <c r="I18" s="6" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A7:I10"/>
+  <autoFilter ref="A7:I18"/>
   <hyperlinks>
     <hyperlink ref="A2" location="'Tổng quan'!A1"/>
     <hyperlink ref="A5" location="'telematics'!A1"/>

--- a/docs/design/domain-model/domain-model.xlsx
+++ b/docs/design/domain-model/domain-model.xlsx
@@ -37,44 +37,45 @@
     <sheet name="telematics" sheetId="28" state="visible" r:id="rId28"/>
     <sheet name="telematic_history" sheetId="29" state="visible" r:id="rId29"/>
     <sheet name="telematic_state" sheetId="30" state="visible" r:id="rId30"/>
-    <sheet name="vehicle_telemetry" sheetId="31" state="visible" r:id="rId31"/>
-    <sheet name="drivers" sheetId="32" state="visible" r:id="rId32"/>
-    <sheet name="driver_vehicle_assignments" sheetId="33" state="visible" r:id="rId33"/>
-    <sheet name="driving_sessions" sheetId="34" state="visible" r:id="rId34"/>
-    <sheet name="charging_credentials" sheetId="35" state="visible" r:id="rId35"/>
-    <sheet name="fleets" sheetId="36" state="visible" r:id="rId36"/>
-    <sheet name="fleet_vehicle_memberships" sheetId="37" state="visible" r:id="rId37"/>
-    <sheet name="geofences" sheetId="38" state="visible" r:id="rId38"/>
-    <sheet name="fleet_user_assignments" sheetId="39" state="visible" r:id="rId39"/>
-    <sheet name="charging_stations" sheetId="40" state="visible" r:id="rId40"/>
-    <sheet name="charging_evses" sheetId="41" state="visible" r:id="rId41"/>
-    <sheet name="charging_connectors" sheetId="42" state="visible" r:id="rId42"/>
-    <sheet name="charging_ocpp_messages" sheetId="43" state="visible" r:id="rId43"/>
-    <sheet name="charging_station_config_entries" sheetId="44" state="visible" r:id="rId44"/>
-    <sheet name="charging_reservations" sheetId="45" state="visible" r:id="rId45"/>
-    <sheet name="charging_sessions" sheetId="46" state="visible" r:id="rId46"/>
-    <sheet name="charging_session_events" sheetId="47" state="visible" r:id="rId47"/>
-    <sheet name="charging_session_measurements" sheetId="48" state="visible" r:id="rId48"/>
-    <sheet name="notifications" sheetId="49" state="visible" r:id="rId49"/>
-    <sheet name="support_cases" sheetId="50" state="visible" r:id="rId50"/>
-    <sheet name="repair_partners" sheetId="51" state="visible" r:id="rId51"/>
-    <sheet name="maintenance_bookings" sheetId="52" state="visible" r:id="rId52"/>
-    <sheet name="charging_policies" sheetId="53" state="visible" r:id="rId53"/>
-    <sheet name="charging_policy_versions" sheetId="54" state="visible" r:id="rId54"/>
-    <sheet name="charging_policy_assignments" sheetId="55" state="visible" r:id="rId55"/>
-    <sheet name="policy_violations" sheetId="56" state="visible" r:id="rId56"/>
-    <sheet name="tariffs" sheetId="57" state="visible" r:id="rId57"/>
-    <sheet name="payments" sheetId="58" state="visible" r:id="rId58"/>
-    <sheet name="wallets" sheetId="59" state="visible" r:id="rId59"/>
-    <sheet name="wallet_transactions" sheetId="60" state="visible" r:id="rId60"/>
-    <sheet name="invoices" sheetId="61" state="visible" r:id="rId61"/>
-    <sheet name="invoice_lines" sheetId="62" state="visible" r:id="rId62"/>
-    <sheet name="subscription_plans" sheetId="63" state="visible" r:id="rId63"/>
-    <sheet name="plan_features" sheetId="64" state="visible" r:id="rId64"/>
-    <sheet name="subscriptions" sheetId="65" state="visible" r:id="rId65"/>
-    <sheet name="driver_scores" sheetId="66" state="visible" r:id="rId66"/>
-    <sheet name="promotion_campaigns" sheetId="67" state="visible" r:id="rId67"/>
-    <sheet name="trips" sheetId="68" state="visible" r:id="rId68"/>
+    <sheet name="telematic_status_reports" sheetId="31" state="visible" r:id="rId31"/>
+    <sheet name="vehicle_telemetry" sheetId="32" state="visible" r:id="rId32"/>
+    <sheet name="drivers" sheetId="33" state="visible" r:id="rId33"/>
+    <sheet name="driver_vehicle_assignments" sheetId="34" state="visible" r:id="rId34"/>
+    <sheet name="driving_sessions" sheetId="35" state="visible" r:id="rId35"/>
+    <sheet name="charging_credentials" sheetId="36" state="visible" r:id="rId36"/>
+    <sheet name="fleets" sheetId="37" state="visible" r:id="rId37"/>
+    <sheet name="fleet_vehicle_memberships" sheetId="38" state="visible" r:id="rId38"/>
+    <sheet name="geofences" sheetId="39" state="visible" r:id="rId39"/>
+    <sheet name="fleet_user_assignments" sheetId="40" state="visible" r:id="rId40"/>
+    <sheet name="charging_stations" sheetId="41" state="visible" r:id="rId41"/>
+    <sheet name="charging_evses" sheetId="42" state="visible" r:id="rId42"/>
+    <sheet name="charging_connectors" sheetId="43" state="visible" r:id="rId43"/>
+    <sheet name="charging_ocpp_messages" sheetId="44" state="visible" r:id="rId44"/>
+    <sheet name="charging_station_config_entries" sheetId="45" state="visible" r:id="rId45"/>
+    <sheet name="charging_reservations" sheetId="46" state="visible" r:id="rId46"/>
+    <sheet name="charging_sessions" sheetId="47" state="visible" r:id="rId47"/>
+    <sheet name="charging_session_events" sheetId="48" state="visible" r:id="rId48"/>
+    <sheet name="charging_session_measurements" sheetId="49" state="visible" r:id="rId49"/>
+    <sheet name="notifications" sheetId="50" state="visible" r:id="rId50"/>
+    <sheet name="support_cases" sheetId="51" state="visible" r:id="rId51"/>
+    <sheet name="repair_partners" sheetId="52" state="visible" r:id="rId52"/>
+    <sheet name="maintenance_bookings" sheetId="53" state="visible" r:id="rId53"/>
+    <sheet name="charging_policies" sheetId="54" state="visible" r:id="rId54"/>
+    <sheet name="charging_policy_versions" sheetId="55" state="visible" r:id="rId55"/>
+    <sheet name="charging_policy_assignments" sheetId="56" state="visible" r:id="rId56"/>
+    <sheet name="policy_violations" sheetId="57" state="visible" r:id="rId57"/>
+    <sheet name="tariffs" sheetId="58" state="visible" r:id="rId58"/>
+    <sheet name="payments" sheetId="59" state="visible" r:id="rId59"/>
+    <sheet name="wallets" sheetId="60" state="visible" r:id="rId60"/>
+    <sheet name="wallet_transactions" sheetId="61" state="visible" r:id="rId61"/>
+    <sheet name="invoices" sheetId="62" state="visible" r:id="rId62"/>
+    <sheet name="invoice_lines" sheetId="63" state="visible" r:id="rId63"/>
+    <sheet name="subscription_plans" sheetId="64" state="visible" r:id="rId64"/>
+    <sheet name="plan_features" sheetId="65" state="visible" r:id="rId65"/>
+    <sheet name="subscriptions" sheetId="66" state="visible" r:id="rId66"/>
+    <sheet name="driver_scores" sheetId="67" state="visible" r:id="rId67"/>
+    <sheet name="promotion_campaigns" sheetId="68" state="visible" r:id="rId68"/>
+    <sheet name="trips" sheetId="69" state="visible" r:id="rId69"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'organizations'!$A$7:$I$20</definedName>
@@ -106,44 +107,45 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="27" hidden="1">'telematics'!$A$8:$I$23</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="28" hidden="1">'telematic_history'!$A$7:$I$23</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="29" hidden="1">'telematic_state'!$A$7:$I$18</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="30" hidden="1">'vehicle_telemetry'!$A$6:$I$29</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="31" hidden="1">'drivers'!$A$6:$I$16</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="32" hidden="1">'driver_vehicle_assignments'!$A$6:$I$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="33" hidden="1">'driving_sessions'!$A$6:$I$17</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="34" hidden="1">'charging_credentials'!$A$6:$I$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="35" hidden="1">'fleets'!$A$6:$I$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="36" hidden="1">'fleet_vehicle_memberships'!$A$6:$I$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="37" hidden="1">'geofences'!$A$6:$I$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="38" hidden="1">'fleet_user_assignments'!$A$6:$I$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="39" hidden="1">'charging_stations'!$A$6:$I$28</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="40" hidden="1">'charging_evses'!$A$6:$I$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="41" hidden="1">'charging_connectors'!$A$6:$I$17</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="42" hidden="1">'charging_ocpp_messages'!$A$6:$I$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="43" hidden="1">'charging_station_config_entries'!$A$6:$I$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="44" hidden="1">'charging_reservations'!$A$6:$I$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="45" hidden="1">'charging_sessions'!$A$6:$I$26</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="46" hidden="1">'charging_session_events'!$A$6:$I$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="47" hidden="1">'charging_session_measurements'!$A$6:$I$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="48" hidden="1">'notifications'!$A$6:$I$16</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="49" hidden="1">'support_cases'!$A$6:$I$28</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="50" hidden="1">'repair_partners'!$A$6:$I$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="51" hidden="1">'maintenance_bookings'!$A$6:$I$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="52" hidden="1">'charging_policies'!$A$6:$I$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="53" hidden="1">'charging_policy_versions'!$A$6:$I$16</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="54" hidden="1">'charging_policy_assignments'!$A$6:$I$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="55" hidden="1">'policy_violations'!$A$6:$I$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="56" hidden="1">'tariffs'!$A$6:$I$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="57" hidden="1">'payments'!$A$6:$I$16</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="58" hidden="1">'wallets'!$A$6:$I$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="59" hidden="1">'wallet_transactions'!$A$6:$I$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="60" hidden="1">'invoices'!$A$6:$I$16</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="61" hidden="1">'invoice_lines'!$A$6:$I$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="62" hidden="1">'subscription_plans'!$A$6:$I$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="63" hidden="1">'plan_features'!$A$6:$I$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="64" hidden="1">'subscriptions'!$A$6:$I$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="65" hidden="1">'driver_scores'!$A$6:$I$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="66" hidden="1">'promotion_campaigns'!$A$6:$I$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="67" hidden="1">'trips'!$A$6:$I$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="30" hidden="1">'telematic_status_reports'!$A$6:$I$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="31" hidden="1">'vehicle_telemetry'!$A$6:$I$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="32" hidden="1">'drivers'!$A$6:$I$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="33" hidden="1">'driver_vehicle_assignments'!$A$6:$I$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="34" hidden="1">'driving_sessions'!$A$6:$I$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="35" hidden="1">'charging_credentials'!$A$6:$I$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="36" hidden="1">'fleets'!$A$6:$I$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="37" hidden="1">'fleet_vehicle_memberships'!$A$6:$I$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="38" hidden="1">'geofences'!$A$6:$I$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="39" hidden="1">'fleet_user_assignments'!$A$6:$I$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="40" hidden="1">'charging_stations'!$A$6:$I$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="41" hidden="1">'charging_evses'!$A$6:$I$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="42" hidden="1">'charging_connectors'!$A$6:$I$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="43" hidden="1">'charging_ocpp_messages'!$A$6:$I$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="44" hidden="1">'charging_station_config_entries'!$A$6:$I$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="45" hidden="1">'charging_reservations'!$A$6:$I$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="46" hidden="1">'charging_sessions'!$A$6:$I$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="47" hidden="1">'charging_session_events'!$A$6:$I$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="48" hidden="1">'charging_session_measurements'!$A$6:$I$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="49" hidden="1">'notifications'!$A$6:$I$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="50" hidden="1">'support_cases'!$A$6:$I$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="51" hidden="1">'repair_partners'!$A$6:$I$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="52" hidden="1">'maintenance_bookings'!$A$6:$I$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="53" hidden="1">'charging_policies'!$A$6:$I$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="54" hidden="1">'charging_policy_versions'!$A$6:$I$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="55" hidden="1">'charging_policy_assignments'!$A$6:$I$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="56" hidden="1">'policy_violations'!$A$6:$I$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="57" hidden="1">'tariffs'!$A$6:$I$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="58" hidden="1">'payments'!$A$6:$I$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="59" hidden="1">'wallets'!$A$6:$I$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="60" hidden="1">'wallet_transactions'!$A$6:$I$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="61" hidden="1">'invoices'!$A$6:$I$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="62" hidden="1">'invoice_lines'!$A$6:$I$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="63" hidden="1">'subscription_plans'!$A$6:$I$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="64" hidden="1">'plan_features'!$A$6:$I$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="65" hidden="1">'subscriptions'!$A$6:$I$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="66" hidden="1">'driver_scores'!$A$6:$I$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="67" hidden="1">'promotion_campaigns'!$A$6:$I$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="68" hidden="1">'trips'!$A$6:$I$14</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -632,7 +634,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I105"/>
+  <dimension ref="A1:I106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -663,7 +665,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>67 bảng trong 16 miền nghiệp vụ: 55 bảng chính, 10 bảng lịch sử (N.h), 2 bảng trạng thái. Bấm vào tên bảng hoặc «→ Mở» để mở sheet chi tiết của bảng; chú giải và các quyết định còn mở nằm ở cuối trang.</t>
+          <t>68 bảng trong 16 miền nghiệp vụ: 56 bảng chính, 10 bảng lịch sử (N.h), 2 bảng trạng thái. Bấm vào tên bảng hoặc «→ Mở» để mở sheet chi tiết của bảng; chú giải và các quyết định còn mở nằm ở cuối trang.</t>
         </is>
       </c>
     </row>
@@ -1980,7 +1982,7 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="67.5" customHeight="1">
+    <row r="36" ht="81" customHeight="1">
       <c r="A36" s="5" t="n"/>
       <c r="B36" s="5" t="inlineStr">
         <is>
@@ -1989,7 +1991,7 @@
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>3 bảng</t>
+          <t>4 bảng</t>
         </is>
       </c>
       <c r="D36" s="5" t="n"/>
@@ -1999,7 +2001,7 @@
         <is>
           <t>Các thiết bị telematics (T-box) gửi dữ liệu xe qua MQTT.
 • Một thiết bị là tài sản có chủ riêng; gắn trên tối đa một xe, và một xe có tối đa một thiết bị.
-• Trạng thái của thiết bị lưu những gì thiết bị tự báo (firmware); cấu hình đẩy xuống (F-J2) là quyết định nằm trên hồ sơ thiết bị.</t>
+• Những gì thiết bị tự báo về mình (firmware, SIM, nguồn điện, sóng) được lưu thành báo cáo trạng thái, mỗi báo cáo một dòng; trạng thái hiển thị báo cáo mới nhất. Chu kỳ gửi là thiết lập của tổ chức (TX-09).</t>
         </is>
       </c>
     </row>
@@ -2138,22 +2140,67 @@
         </is>
       </c>
     </row>
-    <row r="40" ht="67.5" customHeight="1">
-      <c r="A40" s="5" t="n"/>
-      <c r="B40" s="5" t="inlineStr">
+    <row r="40" ht="94.5" customHeight="1">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B40" s="6" t="inlineStr">
+        <is>
+          <t>Thiết bị telematics (telematics)</t>
+        </is>
+      </c>
+      <c r="C40" s="7" t="inlineStr">
+        <is>
+          <t>telematic_status_reports</t>
+        </is>
+      </c>
+      <c r="D40" s="7" t="inlineStr">
+        <is>
+          <t>Báo cáo trạng thái thiết bị telematics</t>
+        </is>
+      </c>
+      <c r="E40" s="6" t="inlineStr">
+        <is>
+          <t>Khách hàng</t>
+        </is>
+      </c>
+      <c r="F40" s="6" t="inlineStr">
+        <is>
+          <t>F-J1, F-J3</t>
+        </is>
+      </c>
+      <c r="G40" s="6" t="inlineStr">
+        <is>
+          <t>Mọi báo cáo sức khỏe mà T-Box gửi về chính nó, khoảng mỗi ngày một lần (TX-10), để xem được xu hướng (sóng yếu dần, điện áp tụt trước khi mất tín hiệu). Chỉ ghi thêm: không bao giờ sửa dòng nên không cần lịch sử thay đổi. Là bảng thường, không phải hypertable: khoảng 365 dòng mỗi thiết bị mỗi năm. Không có organization_id (DM-24): như các dữ liệu tình trạng khác, đi theo thiết bị sang chủ kế tiếp (VH-11). Các trường là tạm thời cho tới khi nhà cung cấp xác nhận bản tin (mqtt-spec.md mục 2.2).</t>
+        </is>
+      </c>
+      <c r="H40" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="I40" s="7" t="inlineStr">
+        <is>
+          <t>→ Mở</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="67.5" customHeight="1">
+      <c r="A41" s="5" t="n"/>
+      <c r="B41" s="5" t="inlineStr">
         <is>
           <t>Dữ liệu vận hành xe (telemetry)</t>
         </is>
       </c>
-      <c r="C40" s="5" t="inlineStr">
+      <c r="C41" s="5" t="inlineStr">
         <is>
           <t>1 bảng</t>
         </is>
       </c>
-      <c r="D40" s="5" t="n"/>
-      <c r="E40" s="5" t="n"/>
-      <c r="F40" s="5" t="n"/>
-      <c r="G40" s="5" t="inlineStr">
+      <c r="D41" s="5" t="n"/>
+      <c r="E41" s="5" t="n"/>
+      <c r="F41" s="5" t="n"/>
+      <c r="G41" s="5" t="inlineStr">
         <is>
           <t>Mọi thứ xe gửi về: vị trí, pin, động cơ, mã lỗi. Cảnh báo và báo cáo năng lượng được tính từ dữ liệu này.
 • Mỗi bản ghi đến từ một thiết bị và được lưu theo một xe.
@@ -2161,67 +2208,67 @@
         </is>
       </c>
     </row>
-    <row r="41" ht="40.5" customHeight="1">
-      <c r="A41" s="6" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="B41" s="6" t="inlineStr">
+    <row r="42" ht="40.5" customHeight="1">
+      <c r="A42" s="6" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B42" s="6" t="inlineStr">
         <is>
           <t>Dữ liệu vận hành xe (telemetry)</t>
         </is>
       </c>
-      <c r="C41" s="7" t="inlineStr">
+      <c r="C42" s="7" t="inlineStr">
         <is>
           <t>vehicle_telemetry</t>
         </is>
       </c>
-      <c r="D41" s="7" t="inlineStr">
+      <c r="D42" s="7" t="inlineStr">
         <is>
           <t>Dữ liệu vận hành xe</t>
         </is>
       </c>
-      <c r="E41" s="6" t="inlineStr">
+      <c r="E42" s="6" t="inlineStr">
         <is>
           <t>Khách hàng</t>
         </is>
       </c>
-      <c r="F41" s="6" t="inlineStr">
+      <c r="F42" s="6" t="inlineStr">
         <is>
           <t>F-A1, F-A2, F-A3, F-A4, F-A6, F-C6</t>
         </is>
       </c>
-      <c r="G41" s="6" t="inlineStr">
+      <c r="G42" s="6" t="inlineStr">
         <is>
           <t>Một bản ghi dữ liệu xe gửi về, mỗi 5-10 giây một bản ghi cho mỗi xe: bảng lớn nhất hệ thống.</t>
         </is>
       </c>
-      <c r="H41" s="6" t="n">
+      <c r="H42" s="6" t="n">
         <v>23</v>
       </c>
-      <c r="I41" s="7" t="inlineStr">
+      <c r="I42" s="7" t="inlineStr">
         <is>
           <t>→ Mở</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="121.5" customHeight="1">
-      <c r="A42" s="5" t="n"/>
-      <c r="B42" s="5" t="inlineStr">
+    <row r="43" ht="121.5" customHeight="1">
+      <c r="A43" s="5" t="n"/>
+      <c r="B43" s="5" t="inlineStr">
         <is>
           <t>Tài xế (drivers)</t>
         </is>
       </c>
-      <c r="C42" s="5" t="inlineStr">
+      <c r="C43" s="5" t="inlineStr">
         <is>
           <t>4 bảng</t>
         </is>
       </c>
-      <c r="D42" s="5" t="n"/>
-      <c r="E42" s="5" t="n"/>
-      <c r="F42" s="5" t="n"/>
-      <c r="G42" s="5" t="inlineStr">
+      <c r="D43" s="5" t="n"/>
+      <c r="E43" s="5" t="n"/>
+      <c r="F43" s="5" t="n"/>
+      <c r="G43" s="5" t="inlineStr">
         <is>
           <t>Những người lái xe và cách họ xác thực tại trụ sạc.
 • Một tài xế thuộc một tổ chức khách hàng.
@@ -2230,202 +2277,202 @@
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="6" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="B43" s="6" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B44" s="6" t="inlineStr">
         <is>
           <t>Tài xế (drivers)</t>
         </is>
       </c>
-      <c r="C43" s="7" t="inlineStr">
+      <c r="C44" s="7" t="inlineStr">
         <is>
           <t>drivers</t>
         </is>
       </c>
-      <c r="D43" s="7" t="inlineStr">
+      <c r="D44" s="7" t="inlineStr">
         <is>
           <t>Tài xế</t>
         </is>
       </c>
-      <c r="E43" s="6" t="inlineStr">
+      <c r="E44" s="6" t="inlineStr">
         <is>
           <t>Khách hàng</t>
         </is>
       </c>
-      <c r="F43" s="6" t="inlineStr">
+      <c r="F44" s="6" t="inlineStr">
         <is>
           <t>F-E4</t>
         </is>
       </c>
-      <c r="G43" s="6" t="inlineStr">
+      <c r="G44" s="6" t="inlineStr">
         <is>
           <t>Một tài xế do khách hàng tuyển dụng (hoặc chính là khách hàng).</t>
         </is>
       </c>
-      <c r="H43" s="6" t="n">
+      <c r="H44" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="I43" s="7" t="inlineStr">
+      <c r="I44" s="7" t="inlineStr">
         <is>
           <t>→ Mở</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="40.5" customHeight="1">
-      <c r="A44" s="6" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="B44" s="6" t="inlineStr">
+    <row r="45" ht="40.5" customHeight="1">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B45" s="6" t="inlineStr">
         <is>
           <t>Tài xế (drivers)</t>
         </is>
       </c>
-      <c r="C44" s="7" t="inlineStr">
+      <c r="C45" s="7" t="inlineStr">
         <is>
           <t>driver_vehicle_assignments</t>
         </is>
       </c>
-      <c r="D44" s="7" t="inlineStr">
+      <c r="D45" s="7" t="inlineStr">
         <is>
           <t>Phân công tài xế - xe</t>
         </is>
       </c>
-      <c r="E44" s="6" t="inlineStr">
+      <c r="E45" s="6" t="inlineStr">
         <is>
           <t>Khách hàng</t>
         </is>
       </c>
-      <c r="F44" s="6" t="inlineStr">
+      <c r="F45" s="6" t="inlineStr">
         <is>
           <t>F-E4</t>
         </is>
       </c>
-      <c r="G44" s="6" t="inlineStr">
+      <c r="G45" s="6" t="inlineStr">
         <is>
           <t>Tài xế nào lái xe nào, trong khoảng thời gian nào (lịch sử mở/đóng). Sẽ bị bỏ: được thay bằng driving_sessions (DR-07) và xóa khi tái cấu trúc; không có dữ liệu thật cần chuyển.</t>
         </is>
       </c>
-      <c r="H44" s="6" t="n">
+      <c r="H45" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="I44" s="7" t="inlineStr">
+      <c r="I45" s="7" t="inlineStr">
         <is>
           <t>→ Mở</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="135" customHeight="1">
-      <c r="A45" s="6" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="B45" s="6" t="inlineStr">
+    <row r="46" ht="135" customHeight="1">
+      <c r="A46" s="6" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="B46" s="6" t="inlineStr">
         <is>
           <t>Tài xế (drivers)</t>
         </is>
       </c>
-      <c r="C45" s="7" t="inlineStr">
+      <c r="C46" s="7" t="inlineStr">
         <is>
           <t>driving_sessions</t>
         </is>
       </c>
-      <c r="D45" s="7" t="inlineStr">
+      <c r="D46" s="7" t="inlineStr">
         <is>
           <t>Phiên lái xe</t>
         </is>
       </c>
-      <c r="E45" s="6" t="inlineStr">
+      <c r="E46" s="6" t="inlineStr">
         <is>
           <t>Khách hàng</t>
         </is>
       </c>
-      <c r="F45" s="6" t="inlineStr">
+      <c r="F46" s="6" t="inlineStr">
         <is>
           <t>F-E4</t>
         </is>
       </c>
-      <c r="G45" s="6" t="inlineStr">
+      <c r="G46" s="6" t="inlineStr">
         <is>
           <t>Ai cầm lái xe nào, trong khoảng thời gian nào (DR-07): tài xế nhận xe bằng cách quét mã QR trên xe hoặc chọn xe ở gần trên ứng dụng, hoặc quản lý nhận xe giúp trên portal. Thay thế driver_vehicle_assignments. Phiên kết thúc khi tài xế trả xe, tài xế khác nhận xe, tài xế nhận xe khác, hoặc xe không di chuyển quá thời gian tự kết thúc của tổ chức (organization_settings). Các sự kiện cần biết tài xế (điểm, chuyến, phiên sạc) lấy tài xế từ đây. Cảnh báo cho tài xế gửi tới tài xế đang nhận xe và portal; xe chạy mà không ai nhận xe sẽ cảnh báo lên portal. Tổ chức sở hữu xe và chính tài xế (trên ứng dụng) xem được phiên lái; tổ chức tuyển dụng tài xế không xem được phiên lái trên xe của tổ chức khác (DR-08). Dòng đã đóng không bao giờ bị sửa nên không cần lịch sử thay đổi.</t>
         </is>
       </c>
-      <c r="H45" s="6" t="n">
+      <c r="H46" s="6" t="n">
         <v>11</v>
       </c>
-      <c r="I45" s="7" t="inlineStr">
+      <c r="I46" s="7" t="inlineStr">
         <is>
           <t>→ Mở</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="27" customHeight="1">
-      <c r="A46" s="6" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="B46" s="6" t="inlineStr">
+    <row r="47" ht="27" customHeight="1">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B47" s="6" t="inlineStr">
         <is>
           <t>Tài xế (drivers)</t>
         </is>
       </c>
-      <c r="C46" s="7" t="inlineStr">
+      <c r="C47" s="7" t="inlineStr">
         <is>
           <t>charging_credentials</t>
         </is>
       </c>
-      <c r="D46" s="7" t="inlineStr">
+      <c r="D47" s="7" t="inlineStr">
         <is>
           <t>Phương thức xác thực sạc</t>
         </is>
       </c>
-      <c r="E46" s="6" t="inlineStr">
+      <c r="E47" s="6" t="inlineStr">
         <is>
           <t>Khách hàng</t>
         </is>
       </c>
-      <c r="F46" s="6" t="inlineStr">
+      <c r="F47" s="6" t="inlineStr">
         <is>
           <t>F-B2, F-C6, F-H1</t>
         </is>
       </c>
-      <c r="G46" s="6" t="inlineStr">
+      <c r="G47" s="6" t="inlineStr">
         <is>
           <t>Cách trụ sạc nhận biết ai đang sạc. Nối mã idTag thô của phiên sạc với tài xế và tổ chức. Việc đặt ở miền Tài xế là tạm thời.</t>
         </is>
       </c>
-      <c r="H46" s="6" t="n">
+      <c r="H47" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="I46" s="7" t="inlineStr">
+      <c r="I47" s="7" t="inlineStr">
         <is>
           <t>→ Mở</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="148.5" customHeight="1">
-      <c r="A47" s="5" t="n"/>
-      <c r="B47" s="5" t="inlineStr">
+    <row r="48" ht="148.5" customHeight="1">
+      <c r="A48" s="5" t="n"/>
+      <c r="B48" s="5" t="inlineStr">
         <is>
           <t>Đội xe (fleet)</t>
         </is>
       </c>
-      <c r="C47" s="5" t="inlineStr">
+      <c r="C48" s="5" t="inlineStr">
         <is>
           <t>4 bảng</t>
         </is>
       </c>
-      <c r="D47" s="5" t="n"/>
-      <c r="E47" s="5" t="n"/>
-      <c r="F47" s="5" t="n"/>
-      <c r="G47" s="5" t="inlineStr">
+      <c r="D48" s="5" t="n"/>
+      <c r="E48" s="5" t="n"/>
+      <c r="F48" s="5" t="n"/>
+      <c r="G48" s="5" t="inlineStr">
         <is>
           <t>Nhóm xe do một quản lý đội xe điều hành.
 • Một đội xe là một nhóm bên trong một tổ chức và có thể nằm dưới một đội xe khác, nên mỗi khách hàng tự mô tả cơ cấu của mình (miền &gt; chi nhánh &gt; bãi xe...) bằng dữ liệu.
@@ -2435,130 +2482,85 @@
         </is>
       </c>
     </row>
-    <row r="48" ht="54" customHeight="1">
-      <c r="A48" s="6" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="B48" s="6" t="inlineStr">
+    <row r="49" ht="54" customHeight="1">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B49" s="6" t="inlineStr">
         <is>
           <t>Đội xe (fleet)</t>
         </is>
       </c>
-      <c r="C48" s="7" t="inlineStr">
+      <c r="C49" s="7" t="inlineStr">
         <is>
           <t>fleets</t>
         </is>
       </c>
-      <c r="D48" s="7" t="inlineStr">
+      <c r="D49" s="7" t="inlineStr">
         <is>
           <t>Đội xe</t>
         </is>
       </c>
-      <c r="E48" s="6" t="inlineStr">
+      <c r="E49" s="6" t="inlineStr">
         <is>
           <t>Khách hàng</t>
         </is>
       </c>
-      <c r="F48" s="6" t="inlineStr">
+      <c r="F49" s="6" t="inlineStr">
         <is>
           <t>F-E1</t>
         </is>
       </c>
-      <c r="G48" s="6" t="inlineStr">
+      <c r="G49" s="6" t="inlineStr">
         <is>
           <t>Một nhóm xe có tên bên trong một tổ chức: một nút trong cơ cấu riêng của khách hàng (miền, chi nhánh, bãi xe, nhóm - tên tùy ý, không giới hạn số cấp, qua parent_fleet_id). Tái cơ cấu chỉ là sửa dữ liệu, không bao giờ phải đổi thiết kế.</t>
         </is>
       </c>
-      <c r="H48" s="6" t="n">
+      <c r="H49" s="6" t="n">
         <v>9</v>
       </c>
-      <c r="I48" s="7" t="inlineStr">
+      <c r="I49" s="7" t="inlineStr">
         <is>
           <t>→ Mở</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="6" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="B49" s="6" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="6" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B50" s="6" t="inlineStr">
         <is>
           <t>Đội xe (fleet)</t>
         </is>
       </c>
-      <c r="C49" s="7" t="inlineStr">
+      <c r="C50" s="7" t="inlineStr">
         <is>
           <t>fleet_vehicle_memberships</t>
         </is>
       </c>
-      <c r="D49" s="7" t="inlineStr">
+      <c r="D50" s="7" t="inlineStr">
         <is>
           <t>Thành viên đội xe</t>
         </is>
       </c>
-      <c r="E49" s="6" t="inlineStr">
+      <c r="E50" s="6" t="inlineStr">
         <is>
           <t>Khách hàng</t>
         </is>
       </c>
-      <c r="F49" s="6" t="inlineStr">
+      <c r="F50" s="6" t="inlineStr">
         <is>
           <t>F-E1</t>
         </is>
       </c>
-      <c r="G49" s="6" t="inlineStr">
+      <c r="G50" s="6" t="inlineStr">
         <is>
           <t>Xe nào thuộc đội nào, trong khoảng thời gian nào (lịch sử mở/đóng).</t>
-        </is>
-      </c>
-      <c r="H49" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="I49" s="7" t="inlineStr">
-        <is>
-          <t>→ Mở</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="27" customHeight="1">
-      <c r="A50" s="6" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="B50" s="6" t="inlineStr">
-        <is>
-          <t>Đội xe (fleet)</t>
-        </is>
-      </c>
-      <c r="C50" s="7" t="inlineStr">
-        <is>
-          <t>geofences</t>
-        </is>
-      </c>
-      <c r="D50" s="7" t="inlineStr">
-        <is>
-          <t>Vùng địa lý (geofence)</t>
-        </is>
-      </c>
-      <c r="E50" s="6" t="inlineStr">
-        <is>
-          <t>Khách hàng</t>
-        </is>
-      </c>
-      <c r="F50" s="6" t="inlineStr">
-        <is>
-          <t>F-A5</t>
-        </is>
-      </c>
-      <c r="G50" s="6" t="inlineStr">
-        <is>
-          <t>Một khu vực mà khi xe thuộc đội xe đi vào hoặc ra sẽ phát cảnh báo. Gắn với đội xe cho đến khi có tổ chức khách hàng (sau đó chuyển sang tổ chức).</t>
         </is>
       </c>
       <c r="H50" s="6" t="n">
@@ -2570,7 +2572,7 @@
         </is>
       </c>
     </row>
-    <row r="51" ht="67.5" customHeight="1">
+    <row r="51" ht="27" customHeight="1">
       <c r="A51" s="6" t="inlineStr">
         <is>
           <t>28</t>
@@ -2583,54 +2585,99 @@
       </c>
       <c r="C51" s="7" t="inlineStr">
         <is>
+          <t>geofences</t>
+        </is>
+      </c>
+      <c r="D51" s="7" t="inlineStr">
+        <is>
+          <t>Vùng địa lý (geofence)</t>
+        </is>
+      </c>
+      <c r="E51" s="6" t="inlineStr">
+        <is>
+          <t>Khách hàng</t>
+        </is>
+      </c>
+      <c r="F51" s="6" t="inlineStr">
+        <is>
+          <t>F-A5</t>
+        </is>
+      </c>
+      <c r="G51" s="6" t="inlineStr">
+        <is>
+          <t>Một khu vực mà khi xe thuộc đội xe đi vào hoặc ra sẽ phát cảnh báo. Gắn với đội xe cho đến khi có tổ chức khách hàng (sau đó chuyển sang tổ chức).</t>
+        </is>
+      </c>
+      <c r="H51" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="I51" s="7" t="inlineStr">
+        <is>
+          <t>→ Mở</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="67.5" customHeight="1">
+      <c r="A52" s="6" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B52" s="6" t="inlineStr">
+        <is>
+          <t>Đội xe (fleet)</t>
+        </is>
+      </c>
+      <c r="C52" s="7" t="inlineStr">
+        <is>
           <t>fleet_user_assignments</t>
         </is>
       </c>
-      <c r="D51" s="7" t="inlineStr">
+      <c r="D52" s="7" t="inlineStr">
         <is>
           <t>Phân công người dùng - đội xe</t>
         </is>
       </c>
-      <c r="E51" s="6" t="inlineStr">
+      <c r="E52" s="6" t="inlineStr">
         <is>
           <t>Khách hàng</t>
         </is>
       </c>
-      <c r="F51" s="6" t="inlineStr">
+      <c r="F52" s="6" t="inlineStr">
         <is>
           <t>F-F1, F-E1</t>
         </is>
       </c>
-      <c r="G51" s="6" t="inlineStr">
+      <c r="G52" s="6" t="inlineStr">
         <is>
           <t>Giới hạn vai trò cấp đội xe của một người dùng trong một số đội xe của tổ chức lớn (ví dụ một quản lý cho đội Hà Nội, một quản lý khác cho đội TP.HCM). Người dùng không có dòng nào đang hiệu lực ở đây thì quản lý mọi đội xe của tổ chức. Nằm ở miền Đội xe, không ở miền Danh tính, để miền Danh tính không phụ thuộc miền nào.</t>
         </is>
       </c>
-      <c r="H51" s="6" t="n">
+      <c r="H52" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="I51" s="7" t="inlineStr">
+      <c r="I52" s="7" t="inlineStr">
         <is>
           <t>→ Mở</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="67.5" customHeight="1">
-      <c r="A52" s="5" t="n"/>
-      <c r="B52" s="5" t="inlineStr">
+    <row r="53" ht="67.5" customHeight="1">
+      <c r="A53" s="5" t="n"/>
+      <c r="B53" s="5" t="inlineStr">
         <is>
           <t>Trạm sạc (charging_stations)</t>
         </is>
       </c>
-      <c r="C52" s="5" t="inlineStr">
+      <c r="C53" s="5" t="inlineStr">
         <is>
           <t>6 bảng</t>
         </is>
       </c>
-      <c r="D52" s="5" t="n"/>
-      <c r="E52" s="5" t="n"/>
-      <c r="F52" s="5" t="n"/>
-      <c r="G52" s="5" t="inlineStr">
+      <c r="D53" s="5" t="n"/>
+      <c r="E53" s="5" t="n"/>
+      <c r="F53" s="5" t="n"/>
+      <c r="G53" s="5" t="inlineStr">
         <is>
           <t>Mạng lưới trạm sạc của G3 và kết nối OCPP tới từng trụ sạc.
 • Một trạm có một hoặc nhiều EVSE; mỗi EVSE có một hoặc nhiều súng sạc (connector).
@@ -2639,89 +2686,44 @@
         </is>
       </c>
     </row>
-    <row r="53" ht="27" customHeight="1">
-      <c r="A53" s="6" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="B53" s="6" t="inlineStr">
+    <row r="54" ht="27" customHeight="1">
+      <c r="A54" s="6" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B54" s="6" t="inlineStr">
         <is>
           <t>Trạm sạc (charging_stations)</t>
         </is>
       </c>
-      <c r="C53" s="7" t="inlineStr">
+      <c r="C54" s="7" t="inlineStr">
         <is>
           <t>charging_stations</t>
         </is>
       </c>
-      <c r="D53" s="7" t="inlineStr">
+      <c r="D54" s="7" t="inlineStr">
         <is>
           <t>Trạm sạc</t>
         </is>
       </c>
-      <c r="E53" s="6" t="inlineStr">
+      <c r="E54" s="6" t="inlineStr">
         <is>
           <t>Nội bộ</t>
         </is>
       </c>
-      <c r="F53" s="6" t="inlineStr">
+      <c r="F54" s="6" t="inlineStr">
         <is>
           <t>F-C1, F-C2, F-D1, F-G2</t>
         </is>
       </c>
-      <c r="G53" s="6" t="inlineStr">
+      <c r="G54" s="6" t="inlineStr">
         <is>
           <t>Một trạm sạc trong mạng lưới của G3.</t>
         </is>
       </c>
-      <c r="H53" s="6" t="n">
+      <c r="H54" s="6" t="n">
         <v>22</v>
-      </c>
-      <c r="I53" s="7" t="inlineStr">
-        <is>
-          <t>→ Mở</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="6" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="B54" s="6" t="inlineStr">
-        <is>
-          <t>Trạm sạc (charging_stations)</t>
-        </is>
-      </c>
-      <c r="C54" s="7" t="inlineStr">
-        <is>
-          <t>charging_evses</t>
-        </is>
-      </c>
-      <c r="D54" s="7" t="inlineStr">
-        <is>
-          <t>EVSE (cụm cấp điện)</t>
-        </is>
-      </c>
-      <c r="E54" s="6" t="inlineStr">
-        <is>
-          <t>Nội bộ</t>
-        </is>
-      </c>
-      <c r="F54" s="6" t="inlineStr">
-        <is>
-          <t>F-C1, F-G2</t>
-        </is>
-      </c>
-      <c r="G54" s="6" t="inlineStr">
-        <is>
-          <t>Một EVSE (bộ cấp điện) của trạm.</t>
-        </is>
-      </c>
-      <c r="H54" s="6" t="n">
-        <v>6</v>
       </c>
       <c r="I54" s="7" t="inlineStr">
         <is>
@@ -2742,12 +2744,12 @@
       </c>
       <c r="C55" s="7" t="inlineStr">
         <is>
-          <t>charging_connectors</t>
+          <t>charging_evses</t>
         </is>
       </c>
       <c r="D55" s="7" t="inlineStr">
         <is>
-          <t>Súng sạc</t>
+          <t>EVSE (cụm cấp điện)</t>
         </is>
       </c>
       <c r="E55" s="6" t="inlineStr">
@@ -2757,16 +2759,16 @@
       </c>
       <c r="F55" s="6" t="inlineStr">
         <is>
-          <t>F-C1, F-C2</t>
+          <t>F-C1, F-G2</t>
         </is>
       </c>
       <c r="G55" s="6" t="inlineStr">
         <is>
-          <t>Một súng/đầu sạc vật lý, kèm trạng thái trực tiếp.</t>
+          <t>Một EVSE (bộ cấp điện) của trạm.</t>
         </is>
       </c>
       <c r="H55" s="6" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="I55" s="7" t="inlineStr">
         <is>
@@ -2787,117 +2789,117 @@
       </c>
       <c r="C56" s="7" t="inlineStr">
         <is>
+          <t>charging_connectors</t>
+        </is>
+      </c>
+      <c r="D56" s="7" t="inlineStr">
+        <is>
+          <t>Súng sạc</t>
+        </is>
+      </c>
+      <c r="E56" s="6" t="inlineStr">
+        <is>
+          <t>Nội bộ</t>
+        </is>
+      </c>
+      <c r="F56" s="6" t="inlineStr">
+        <is>
+          <t>F-C1, F-C2</t>
+        </is>
+      </c>
+      <c r="G56" s="6" t="inlineStr">
+        <is>
+          <t>Một súng/đầu sạc vật lý, kèm trạng thái trực tiếp.</t>
+        </is>
+      </c>
+      <c r="H56" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="I56" s="7" t="inlineStr">
+        <is>
+          <t>→ Mở</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="6" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B57" s="6" t="inlineStr">
+        <is>
+          <t>Trạm sạc (charging_stations)</t>
+        </is>
+      </c>
+      <c r="C57" s="7" t="inlineStr">
+        <is>
           <t>charging_ocpp_messages</t>
         </is>
       </c>
-      <c r="D56" s="7" t="inlineStr">
+      <c r="D57" s="7" t="inlineStr">
         <is>
           <t>Nhật ký bản tin OCPP</t>
         </is>
       </c>
-      <c r="E56" s="6" t="inlineStr">
+      <c r="E57" s="6" t="inlineStr">
         <is>
           <t>Nội bộ</t>
         </is>
       </c>
-      <c r="F56" s="6" t="inlineStr">
+      <c r="F57" s="6" t="inlineStr">
         <is>
           <t>F-G2</t>
         </is>
       </c>
-      <c r="G56" s="6" t="inlineStr">
+      <c r="G57" s="6" t="inlineStr">
         <is>
           <t>Mọi bản tin OCPP theo cả hai chiều, lưu nguyên văn, chỉ ghi thêm.</t>
         </is>
       </c>
-      <c r="H56" s="6" t="n">
+      <c r="H57" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="I56" s="7" t="inlineStr">
+      <c r="I57" s="7" t="inlineStr">
         <is>
           <t>→ Mở</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="27" customHeight="1">
-      <c r="A57" s="6" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="B57" s="6" t="inlineStr">
+    <row r="58" ht="27" customHeight="1">
+      <c r="A58" s="6" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="B58" s="6" t="inlineStr">
         <is>
           <t>Trạm sạc (charging_stations)</t>
         </is>
       </c>
-      <c r="C57" s="7" t="inlineStr">
+      <c r="C58" s="7" t="inlineStr">
         <is>
           <t>charging_station_configuration_entries</t>
         </is>
       </c>
-      <c r="D57" s="7" t="inlineStr">
+      <c r="D58" s="7" t="inlineStr">
         <is>
           <t>Cấu hình trụ sạc</t>
         </is>
       </c>
-      <c r="E57" s="6" t="inlineStr">
+      <c r="E58" s="6" t="inlineStr">
         <is>
           <t>Nội bộ</t>
         </is>
       </c>
-      <c r="F57" s="6" t="inlineStr">
+      <c r="F58" s="6" t="inlineStr">
         <is>
           <t>F-G2</t>
         </is>
       </c>
-      <c r="G57" s="6" t="inlineStr">
+      <c r="G58" s="6" t="inlineStr">
         <is>
           <t>Một khóa cấu hình trong câu trả lời GetConfiguration của trụ sạc (các bản chụp chỉ ghi thêm).</t>
-        </is>
-      </c>
-      <c r="H57" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="I57" s="7" t="inlineStr">
-        <is>
-          <t>→ Mở</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="6" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="B58" s="6" t="inlineStr">
-        <is>
-          <t>Trạm sạc (charging_stations)</t>
-        </is>
-      </c>
-      <c r="C58" s="7" t="inlineStr">
-        <is>
-          <t>charging_reservations</t>
-        </is>
-      </c>
-      <c r="D58" s="7" t="inlineStr">
-        <is>
-          <t>Đặt chỗ súng sạc</t>
-        </is>
-      </c>
-      <c r="E58" s="6" t="inlineStr">
-        <is>
-          <t>Hai bên</t>
-        </is>
-      </c>
-      <c r="F58" s="6" t="inlineStr">
-        <is>
-          <t>F-C4</t>
-        </is>
-      </c>
-      <c r="G58" s="6" t="inlineStr">
-        <is>
-          <t>Khách hàng giữ chỗ một súng sạc của G3 trong một khung giờ.</t>
         </is>
       </c>
       <c r="H58" s="6" t="n">
@@ -2909,22 +2911,67 @@
         </is>
       </c>
     </row>
-    <row r="59" ht="94.5" customHeight="1">
-      <c r="A59" s="5" t="n"/>
-      <c r="B59" s="5" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="6" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B59" s="6" t="inlineStr">
+        <is>
+          <t>Trạm sạc (charging_stations)</t>
+        </is>
+      </c>
+      <c r="C59" s="7" t="inlineStr">
+        <is>
+          <t>charging_reservations</t>
+        </is>
+      </c>
+      <c r="D59" s="7" t="inlineStr">
+        <is>
+          <t>Đặt chỗ súng sạc</t>
+        </is>
+      </c>
+      <c r="E59" s="6" t="inlineStr">
+        <is>
+          <t>Hai bên</t>
+        </is>
+      </c>
+      <c r="F59" s="6" t="inlineStr">
+        <is>
+          <t>F-C4</t>
+        </is>
+      </c>
+      <c r="G59" s="6" t="inlineStr">
+        <is>
+          <t>Khách hàng giữ chỗ một súng sạc của G3 trong một khung giờ.</t>
+        </is>
+      </c>
+      <c r="H59" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="I59" s="7" t="inlineStr">
+        <is>
+          <t>→ Mở</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="94.5" customHeight="1">
+      <c r="A60" s="5" t="n"/>
+      <c r="B60" s="5" t="inlineStr">
         <is>
           <t>Phiên sạc (charging_sessions)</t>
         </is>
       </c>
-      <c r="C59" s="5" t="inlineStr">
+      <c r="C60" s="5" t="inlineStr">
         <is>
           <t>3 bảng</t>
         </is>
       </c>
-      <c r="D59" s="5" t="n"/>
-      <c r="E59" s="5" t="n"/>
-      <c r="F59" s="5" t="n"/>
-      <c r="G59" s="5" t="inlineStr">
+      <c r="D60" s="5" t="n"/>
+      <c r="E60" s="5" t="n"/>
+      <c r="F60" s="5" t="n"/>
+      <c r="G60" s="5" t="inlineStr">
         <is>
           <t>Những gì diễn ra trong mỗi lần sạc: sự kiện, chỉ số công tơ, điện năng đã cấp.
 • Một phiên sạc diễn ra trên một súng sạc của một trạm G3.
@@ -2933,51 +2980,6 @@
         </is>
       </c>
     </row>
-    <row r="60" ht="27" customHeight="1">
-      <c r="A60" s="6" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="B60" s="6" t="inlineStr">
-        <is>
-          <t>Phiên sạc (charging_sessions)</t>
-        </is>
-      </c>
-      <c r="C60" s="7" t="inlineStr">
-        <is>
-          <t>charging_sessions</t>
-        </is>
-      </c>
-      <c r="D60" s="7" t="inlineStr">
-        <is>
-          <t>Phiên sạc</t>
-        </is>
-      </c>
-      <c r="E60" s="6" t="inlineStr">
-        <is>
-          <t>Hai bên</t>
-        </is>
-      </c>
-      <c r="F60" s="6" t="inlineStr">
-        <is>
-          <t>F-B2, F-C5</t>
-        </is>
-      </c>
-      <c r="G60" s="6" t="inlineStr">
-        <is>
-          <t>Một lần sạc trên một súng sạc, từ lúc bắt đầu đến lúc kết thúc.</t>
-        </is>
-      </c>
-      <c r="H60" s="6" t="n">
-        <v>20</v>
-      </c>
-      <c r="I60" s="7" t="inlineStr">
-        <is>
-          <t>→ Mở</t>
-        </is>
-      </c>
-    </row>
     <row r="61" ht="27" customHeight="1">
       <c r="A61" s="6" t="inlineStr">
         <is>
@@ -2991,12 +2993,12 @@
       </c>
       <c r="C61" s="7" t="inlineStr">
         <is>
-          <t>charging_session_events</t>
+          <t>charging_sessions</t>
         </is>
       </c>
       <c r="D61" s="7" t="inlineStr">
         <is>
-          <t>Sự kiện phiên sạc</t>
+          <t>Phiên sạc</t>
         </is>
       </c>
       <c r="E61" s="6" t="inlineStr">
@@ -3006,16 +3008,16 @@
       </c>
       <c r="F61" s="6" t="inlineStr">
         <is>
-          <t>F-B2</t>
+          <t>F-B2, F-C5</t>
         </is>
       </c>
       <c r="G61" s="6" t="inlineStr">
         <is>
-          <t>Từng sự kiện Bắt đầu / Cập nhật / Kết thúc của một phiên sạc.</t>
+          <t>Một lần sạc trên một súng sạc, từ lúc bắt đầu đến lúc kết thúc.</t>
         </is>
       </c>
       <c r="H61" s="6" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="I61" s="7" t="inlineStr">
         <is>
@@ -3036,54 +3038,99 @@
       </c>
       <c r="C62" s="7" t="inlineStr">
         <is>
+          <t>charging_session_events</t>
+        </is>
+      </c>
+      <c r="D62" s="7" t="inlineStr">
+        <is>
+          <t>Sự kiện phiên sạc</t>
+        </is>
+      </c>
+      <c r="E62" s="6" t="inlineStr">
+        <is>
+          <t>Hai bên</t>
+        </is>
+      </c>
+      <c r="F62" s="6" t="inlineStr">
+        <is>
+          <t>F-B2</t>
+        </is>
+      </c>
+      <c r="G62" s="6" t="inlineStr">
+        <is>
+          <t>Từng sự kiện Bắt đầu / Cập nhật / Kết thúc của một phiên sạc.</t>
+        </is>
+      </c>
+      <c r="H62" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="I62" s="7" t="inlineStr">
+        <is>
+          <t>→ Mở</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="27" customHeight="1">
+      <c r="A63" s="6" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B63" s="6" t="inlineStr">
+        <is>
+          <t>Phiên sạc (charging_sessions)</t>
+        </is>
+      </c>
+      <c r="C63" s="7" t="inlineStr">
+        <is>
           <t>charging_session_measurements</t>
         </is>
       </c>
-      <c r="D62" s="7" t="inlineStr">
+      <c r="D63" s="7" t="inlineStr">
         <is>
           <t>Số đo phiên sạc</t>
         </is>
       </c>
-      <c r="E62" s="6" t="inlineStr">
+      <c r="E63" s="6" t="inlineStr">
         <is>
           <t>Hai bên</t>
         </is>
       </c>
-      <c r="F62" s="6" t="inlineStr">
+      <c r="F63" s="6" t="inlineStr">
         <is>
           <t>F-B2</t>
         </is>
       </c>
-      <c r="G62" s="6" t="inlineStr">
+      <c r="G63" s="6" t="inlineStr">
         <is>
           <t>Mọi giá trị đo trụ sạc gửi trong phiên (điện năng, công suất, SOC...).</t>
         </is>
       </c>
-      <c r="H62" s="6" t="n">
+      <c r="H63" s="6" t="n">
         <v>9</v>
       </c>
-      <c r="I62" s="7" t="inlineStr">
+      <c r="I63" s="7" t="inlineStr">
         <is>
           <t>→ Mở</t>
         </is>
       </c>
     </row>
-    <row r="63" ht="54" customHeight="1">
-      <c r="A63" s="5" t="n"/>
-      <c r="B63" s="5" t="inlineStr">
+    <row r="64" ht="54" customHeight="1">
+      <c r="A64" s="5" t="n"/>
+      <c r="B64" s="5" t="inlineStr">
         <is>
           <t>Thông báo &amp; cảnh báo (notifications)</t>
         </is>
       </c>
-      <c r="C63" s="5" t="inlineStr">
+      <c r="C64" s="5" t="inlineStr">
         <is>
           <t>1 bảng</t>
         </is>
       </c>
-      <c r="D63" s="5" t="n"/>
-      <c r="E63" s="5" t="n"/>
-      <c r="F63" s="5" t="n"/>
-      <c r="G63" s="5" t="inlineStr">
+      <c r="D64" s="5" t="n"/>
+      <c r="E64" s="5" t="n"/>
+      <c r="F64" s="5" t="n"/>
+      <c r="G64" s="5" t="inlineStr">
         <is>
           <t>Cảnh báo do các miền khác phát sinh, được lưu để người vận hành truy vấn.
 • Một thông báo thường nói về một xe.
@@ -3091,67 +3138,67 @@
         </is>
       </c>
     </row>
-    <row r="64" ht="27" customHeight="1">
-      <c r="A64" s="6" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="B64" s="6" t="inlineStr">
+    <row r="65" ht="27" customHeight="1">
+      <c r="A65" s="6" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B65" s="6" t="inlineStr">
         <is>
           <t>Thông báo &amp; cảnh báo (notifications)</t>
         </is>
       </c>
-      <c r="C64" s="7" t="inlineStr">
+      <c r="C65" s="7" t="inlineStr">
         <is>
           <t>notifications</t>
         </is>
       </c>
-      <c r="D64" s="7" t="inlineStr">
+      <c r="D65" s="7" t="inlineStr">
         <is>
           <t>Thông báo</t>
         </is>
       </c>
-      <c r="E64" s="6" t="inlineStr">
+      <c r="E65" s="6" t="inlineStr">
         <is>
           <t>Khách hàng</t>
         </is>
       </c>
-      <c r="F64" s="6" t="inlineStr">
+      <c r="F65" s="6" t="inlineStr">
         <is>
           <t>F-A2, F-A3, F-A4, F-J1, F-J3</t>
         </is>
       </c>
-      <c r="G64" s="6" t="inlineStr">
+      <c r="G65" s="6" t="inlineStr">
         <is>
           <t>Một cảnh báo (pin, bất thường, SOH, thiết bị mất kết nối...). Một bảng chung; mỗi loại cảnh báo là một giá trị enum và một cấu trúc payload.</t>
         </is>
       </c>
-      <c r="H64" s="6" t="n">
+      <c r="H65" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="I64" s="7" t="inlineStr">
+      <c r="I65" s="7" t="inlineStr">
         <is>
           <t>→ Mở</t>
         </is>
       </c>
     </row>
-    <row r="65" ht="81" customHeight="1">
-      <c r="A65" s="5" t="n"/>
-      <c r="B65" s="5" t="inlineStr">
+    <row r="66" ht="81" customHeight="1">
+      <c r="A66" s="5" t="n"/>
+      <c r="B66" s="5" t="inlineStr">
         <is>
           <t>CSKH &amp; cứu hộ (support)</t>
         </is>
       </c>
-      <c r="C65" s="5" t="inlineStr">
+      <c r="C66" s="5" t="inlineStr">
         <is>
           <t>3 bảng</t>
         </is>
       </c>
-      <c r="D65" s="5" t="n"/>
-      <c r="E65" s="5" t="n"/>
-      <c r="F65" s="5" t="n"/>
-      <c r="G65" s="5" t="inlineStr">
+      <c r="D66" s="5" t="n"/>
+      <c r="E66" s="5" t="n"/>
+      <c r="F66" s="5" t="n"/>
+      <c r="G66" s="5" t="inlineStr">
         <is>
           <t>Chăm sóc khách hàng: yêu cầu hỗ trợ, SOS, điều phối cứu hộ và đặt lịch bảo dưỡng.
 • Một ca hỗ trợ (yêu cầu thường hoặc SOS) liên quan đến một xe và/hoặc một tài xế của một tổ chức.
@@ -3160,51 +3207,6 @@
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="6" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="B66" s="6" t="inlineStr">
-        <is>
-          <t>CSKH &amp; cứu hộ (support)</t>
-        </is>
-      </c>
-      <c r="C66" s="7" t="inlineStr">
-        <is>
-          <t>support_cases</t>
-        </is>
-      </c>
-      <c r="D66" s="7" t="inlineStr">
-        <is>
-          <t>Ca hỗ trợ</t>
-        </is>
-      </c>
-      <c r="E66" s="6" t="inlineStr">
-        <is>
-          <t>Khách hàng</t>
-        </is>
-      </c>
-      <c r="F66" s="6" t="inlineStr">
-        <is>
-          <t>F-I1, F-I2</t>
-        </is>
-      </c>
-      <c r="G66" s="6" t="inlineStr">
-        <is>
-          <t>Một yêu cầu hỗ trợ: yêu cầu thường hoặc SOS, kèm mốc thời gian SLA.</t>
-        </is>
-      </c>
-      <c r="H66" s="6" t="n">
-        <v>22</v>
-      </c>
-      <c r="I66" s="7" t="inlineStr">
-        <is>
-          <t>→ Mở</t>
-        </is>
-      </c>
-    </row>
     <row r="67">
       <c r="A67" s="6" t="inlineStr">
         <is>
@@ -3218,31 +3220,31 @@
       </c>
       <c r="C67" s="7" t="inlineStr">
         <is>
-          <t>repair_partners</t>
+          <t>support_cases</t>
         </is>
       </c>
       <c r="D67" s="7" t="inlineStr">
         <is>
-          <t>Đối tác sửa chữa &amp; cứu hộ</t>
+          <t>Ca hỗ trợ</t>
         </is>
       </c>
       <c r="E67" s="6" t="inlineStr">
         <is>
-          <t>Nội bộ</t>
+          <t>Khách hàng</t>
         </is>
       </c>
       <c r="F67" s="6" t="inlineStr">
         <is>
-          <t>F-I4, F-I3</t>
+          <t>F-I1, F-I2</t>
         </is>
       </c>
       <c r="G67" s="6" t="inlineStr">
         <is>
-          <t>Một xưởng hoặc đơn vị cứu hộ mà CSKH có thể điều phối tới.</t>
+          <t>Một yêu cầu hỗ trợ: yêu cầu thường hoặc SOS, kèm mốc thời gian SLA.</t>
         </is>
       </c>
       <c r="H67" s="6" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="I67" s="7" t="inlineStr">
         <is>
@@ -3263,27 +3265,27 @@
       </c>
       <c r="C68" s="7" t="inlineStr">
         <is>
-          <t>maintenance_bookings</t>
+          <t>repair_partners</t>
         </is>
       </c>
       <c r="D68" s="7" t="inlineStr">
         <is>
-          <t>Lịch bảo dưỡng</t>
+          <t>Đối tác sửa chữa &amp; cứu hộ</t>
         </is>
       </c>
       <c r="E68" s="6" t="inlineStr">
         <is>
-          <t>Khách hàng</t>
+          <t>Nội bộ</t>
         </is>
       </c>
       <c r="F68" s="6" t="inlineStr">
         <is>
-          <t>F-I3</t>
+          <t>F-I4, F-I3</t>
         </is>
       </c>
       <c r="G68" s="6" t="inlineStr">
         <is>
-          <t>Một lịch hẹn bảo dưỡng xe tại xưởng đối tác.</t>
+          <t>Một xưởng hoặc đơn vị cứu hộ mà CSKH có thể điều phối tới.</t>
         </is>
       </c>
       <c r="H68" s="6" t="n">
@@ -3295,22 +3297,67 @@
         </is>
       </c>
     </row>
-    <row r="69" ht="81" customHeight="1">
-      <c r="A69" s="5" t="n"/>
-      <c r="B69" s="5" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="6" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B69" s="6" t="inlineStr">
+        <is>
+          <t>CSKH &amp; cứu hộ (support)</t>
+        </is>
+      </c>
+      <c r="C69" s="7" t="inlineStr">
+        <is>
+          <t>maintenance_bookings</t>
+        </is>
+      </c>
+      <c r="D69" s="7" t="inlineStr">
+        <is>
+          <t>Lịch bảo dưỡng</t>
+        </is>
+      </c>
+      <c r="E69" s="6" t="inlineStr">
+        <is>
+          <t>Khách hàng</t>
+        </is>
+      </c>
+      <c r="F69" s="6" t="inlineStr">
+        <is>
+          <t>F-I3</t>
+        </is>
+      </c>
+      <c r="G69" s="6" t="inlineStr">
+        <is>
+          <t>Một lịch hẹn bảo dưỡng xe tại xưởng đối tác.</t>
+        </is>
+      </c>
+      <c r="H69" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="I69" s="7" t="inlineStr">
+        <is>
+          <t>→ Mở</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="81" customHeight="1">
+      <c r="A70" s="5" t="n"/>
+      <c r="B70" s="5" t="inlineStr">
         <is>
           <t>Chính sách sạc (bảo hành) (policy)</t>
         </is>
       </c>
-      <c r="C69" s="5" t="inlineStr">
+      <c r="C70" s="5" t="inlineStr">
         <is>
           <t>4 bảng</t>
         </is>
       </c>
-      <c r="D69" s="5" t="n"/>
-      <c r="E69" s="5" t="n"/>
-      <c r="F69" s="5" t="n"/>
-      <c r="G69" s="5" t="inlineStr">
+      <c r="D70" s="5" t="n"/>
+      <c r="E70" s="5" t="n"/>
+      <c r="F70" s="5" t="n"/>
+      <c r="G70" s="5" t="inlineStr">
         <is>
           <t>Quy tắc sạc gắn với bảo hành và các vi phạm được phát hiện.
 • Một chính sách có nhiều phiên bản không sửa được; giá trị cụ thể do G3 Mobility quyết định.
@@ -3319,51 +3366,6 @@
         </is>
       </c>
     </row>
-    <row r="70" ht="27" customHeight="1">
-      <c r="A70" s="6" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="B70" s="6" t="inlineStr">
-        <is>
-          <t>Chính sách sạc (bảo hành) (policy)</t>
-        </is>
-      </c>
-      <c r="C70" s="7" t="inlineStr">
-        <is>
-          <t>charging_policies</t>
-        </is>
-      </c>
-      <c r="D70" s="7" t="inlineStr">
-        <is>
-          <t>Chính sách sạc</t>
-        </is>
-      </c>
-      <c r="E70" s="6" t="inlineStr">
-        <is>
-          <t>Nội bộ</t>
-        </is>
-      </c>
-      <c r="F70" s="6" t="inlineStr">
-        <is>
-          <t>F-B1</t>
-        </is>
-      </c>
-      <c r="G70" s="6" t="inlineStr">
-        <is>
-          <t>Một chính sách sạc bảo hành có tên do G3 Mobility định nghĩa.</t>
-        </is>
-      </c>
-      <c r="H70" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="I70" s="7" t="inlineStr">
-        <is>
-          <t>→ Mở</t>
-        </is>
-      </c>
-    </row>
     <row r="71" ht="27" customHeight="1">
       <c r="A71" s="6" t="inlineStr">
         <is>
@@ -3377,12 +3379,12 @@
       </c>
       <c r="C71" s="7" t="inlineStr">
         <is>
-          <t>charging_policy_versions</t>
+          <t>charging_policies</t>
         </is>
       </c>
       <c r="D71" s="7" t="inlineStr">
         <is>
-          <t>Phiên bản chính sách sạc</t>
+          <t>Chính sách sạc</t>
         </is>
       </c>
       <c r="E71" s="6" t="inlineStr">
@@ -3397,11 +3399,11 @@
       </c>
       <c r="G71" s="6" t="inlineStr">
         <is>
-          <t>Một phiên bản quy tắc không sửa được của chính sách. Mọi phiên bản đều được giữ để kiểm toán.</t>
+          <t>Một chính sách sạc bảo hành có tên do G3 Mobility định nghĩa.</t>
         </is>
       </c>
       <c r="H71" s="6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I71" s="7" t="inlineStr">
         <is>
@@ -3422,17 +3424,17 @@
       </c>
       <c r="C72" s="7" t="inlineStr">
         <is>
-          <t>charging_policy_assignments</t>
+          <t>charging_policy_versions</t>
         </is>
       </c>
       <c r="D72" s="7" t="inlineStr">
         <is>
-          <t>Áp dụng chính sách sạc</t>
+          <t>Phiên bản chính sách sạc</t>
         </is>
       </c>
       <c r="E72" s="6" t="inlineStr">
         <is>
-          <t>Khách hàng</t>
+          <t>Nội bộ</t>
         </is>
       </c>
       <c r="F72" s="6" t="inlineStr">
@@ -3442,11 +3444,11 @@
       </c>
       <c r="G72" s="6" t="inlineStr">
         <is>
-          <t>Chính sách nào áp dụng cho một xe, một đội xe hay một dòng xe.</t>
+          <t>Một phiên bản quy tắc không sửa được của chính sách. Mọi phiên bản đều được giữ để kiểm toán.</t>
         </is>
       </c>
       <c r="H72" s="6" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I72" s="7" t="inlineStr">
         <is>
@@ -3467,12 +3469,12 @@
       </c>
       <c r="C73" s="7" t="inlineStr">
         <is>
-          <t>policy_violations</t>
+          <t>charging_policy_assignments</t>
         </is>
       </c>
       <c r="D73" s="7" t="inlineStr">
         <is>
-          <t>Vi phạm chính sách sạc</t>
+          <t>Áp dụng chính sách sạc</t>
         </is>
       </c>
       <c r="E73" s="6" t="inlineStr">
@@ -3482,12 +3484,12 @@
       </c>
       <c r="F73" s="6" t="inlineStr">
         <is>
-          <t>F-B3, F-B6</t>
+          <t>F-B1</t>
         </is>
       </c>
       <c r="G73" s="6" t="inlineStr">
         <is>
-          <t>Một phiên sạc vi phạm chính sách, kèm bằng chứng. Hệ quả của vi phạm vẫn là câu hỏi kinh doanh còn mở (mục 3 của feature-list).</t>
+          <t>Chính sách nào áp dụng cho một xe, một đội xe hay một dòng xe.</t>
         </is>
       </c>
       <c r="H73" s="6" t="n">
@@ -3499,22 +3501,67 @@
         </is>
       </c>
     </row>
-    <row r="74" ht="283.5" customHeight="1">
-      <c r="A74" s="5" t="n"/>
-      <c r="B74" s="5" t="inlineStr">
+    <row r="74" ht="27" customHeight="1">
+      <c r="A74" s="6" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="B74" s="6" t="inlineStr">
+        <is>
+          <t>Chính sách sạc (bảo hành) (policy)</t>
+        </is>
+      </c>
+      <c r="C74" s="7" t="inlineStr">
+        <is>
+          <t>policy_violations</t>
+        </is>
+      </c>
+      <c r="D74" s="7" t="inlineStr">
+        <is>
+          <t>Vi phạm chính sách sạc</t>
+        </is>
+      </c>
+      <c r="E74" s="6" t="inlineStr">
+        <is>
+          <t>Khách hàng</t>
+        </is>
+      </c>
+      <c r="F74" s="6" t="inlineStr">
+        <is>
+          <t>F-B3, F-B6</t>
+        </is>
+      </c>
+      <c r="G74" s="6" t="inlineStr">
+        <is>
+          <t>Một phiên sạc vi phạm chính sách, kèm bằng chứng. Hệ quả của vi phạm vẫn là câu hỏi kinh doanh còn mở (mục 3 của feature-list).</t>
+        </is>
+      </c>
+      <c r="H74" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="I74" s="7" t="inlineStr">
+        <is>
+          <t>→ Mở</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="283.5" customHeight="1">
+      <c r="A75" s="5" t="n"/>
+      <c r="B75" s="5" t="inlineStr">
         <is>
           <t>Thanh toán &amp; hóa đơn (billing)</t>
         </is>
       </c>
-      <c r="C74" s="5" t="inlineStr">
+      <c r="C75" s="5" t="inlineStr">
         <is>
           <t>9 bảng</t>
         </is>
       </c>
-      <c r="D74" s="5" t="n"/>
-      <c r="E74" s="5" t="n"/>
-      <c r="F74" s="5" t="n"/>
-      <c r="G74" s="5" t="inlineStr">
+      <c r="D75" s="5" t="n"/>
+      <c r="E75" s="5" t="n"/>
+      <c r="F75" s="5" t="n"/>
+      <c r="G75" s="5" t="inlineStr">
         <is>
           <t>Tiền: giá điện, thanh toán, ví trả trước, hóa đơn điện tử và thuê bao SaaS.
 • Biểu giá định giá điện cho toàn mạng hoặc từng trạm, theo khung giờ.
@@ -3526,51 +3573,6 @@
         </is>
       </c>
     </row>
-    <row r="75" ht="27" customHeight="1">
-      <c r="A75" s="6" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="B75" s="6" t="inlineStr">
-        <is>
-          <t>Thanh toán &amp; hóa đơn (billing)</t>
-        </is>
-      </c>
-      <c r="C75" s="7" t="inlineStr">
-        <is>
-          <t>tariffs</t>
-        </is>
-      </c>
-      <c r="D75" s="7" t="inlineStr">
-        <is>
-          <t>Biểu giá điện</t>
-        </is>
-      </c>
-      <c r="E75" s="6" t="inlineStr">
-        <is>
-          <t>Nội bộ</t>
-        </is>
-      </c>
-      <c r="F75" s="6" t="inlineStr">
-        <is>
-          <t>F-C8, F-H1</t>
-        </is>
-      </c>
-      <c r="G75" s="6" t="inlineStr">
-        <is>
-          <t>Giá điện. Ai sở hữu biểu giá (G3 Energy hay G3 Network) là mục 5 của feature-list.</t>
-        </is>
-      </c>
-      <c r="H75" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="I75" s="7" t="inlineStr">
-        <is>
-          <t>→ Mở</t>
-        </is>
-      </c>
-    </row>
     <row r="76" ht="27" customHeight="1">
       <c r="A76" s="6" t="inlineStr">
         <is>
@@ -3584,31 +3586,31 @@
       </c>
       <c r="C76" s="7" t="inlineStr">
         <is>
-          <t>payments</t>
+          <t>tariffs</t>
         </is>
       </c>
       <c r="D76" s="7" t="inlineStr">
         <is>
-          <t>Thanh toán</t>
+          <t>Biểu giá điện</t>
         </is>
       </c>
       <c r="E76" s="6" t="inlineStr">
         <is>
-          <t>Khách hàng</t>
+          <t>Nội bộ</t>
         </is>
       </c>
       <c r="F76" s="6" t="inlineStr">
         <is>
-          <t>F-H1</t>
+          <t>F-C8, F-H1</t>
         </is>
       </c>
       <c r="G76" s="6" t="inlineStr">
         <is>
-          <t>Một lần thanh toán qua cổng thanh toán hoặc ví, thường cho một phiên sạc.</t>
+          <t>Giá điện. Ai sở hữu biểu giá (G3 Energy hay G3 Network) là mục 5 của feature-list.</t>
         </is>
       </c>
       <c r="H76" s="6" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I76" s="7" t="inlineStr">
         <is>
@@ -3629,12 +3631,12 @@
       </c>
       <c r="C77" s="7" t="inlineStr">
         <is>
-          <t>wallets</t>
+          <t>payments</t>
         </is>
       </c>
       <c r="D77" s="7" t="inlineStr">
         <is>
-          <t>Ví</t>
+          <t>Thanh toán</t>
         </is>
       </c>
       <c r="E77" s="6" t="inlineStr">
@@ -3644,16 +3646,16 @@
       </c>
       <c r="F77" s="6" t="inlineStr">
         <is>
-          <t>F-H2</t>
+          <t>F-H1</t>
         </is>
       </c>
       <c r="G77" s="6" t="inlineStr">
         <is>
-          <t>Số dư trả trước của một tài xế hoặc của cả tổ chức.</t>
+          <t>Một lần thanh toán qua cổng thanh toán hoặc ví, thường cho một phiên sạc.</t>
         </is>
       </c>
       <c r="H77" s="6" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I77" s="7" t="inlineStr">
         <is>
@@ -3674,12 +3676,12 @@
       </c>
       <c r="C78" s="7" t="inlineStr">
         <is>
-          <t>wallet_transactions</t>
+          <t>wallets</t>
         </is>
       </c>
       <c r="D78" s="7" t="inlineStr">
         <is>
-          <t>Giao dịch ví</t>
+          <t>Ví</t>
         </is>
       </c>
       <c r="E78" s="6" t="inlineStr">
@@ -3694,11 +3696,11 @@
       </c>
       <c r="G78" s="6" t="inlineStr">
         <is>
-          <t>Biến động tiền vào/ra khỏi ví, chỉ ghi thêm.</t>
+          <t>Số dư trả trước của một tài xế hoặc của cả tổ chức.</t>
         </is>
       </c>
       <c r="H78" s="6" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I78" s="7" t="inlineStr">
         <is>
@@ -3719,12 +3721,12 @@
       </c>
       <c r="C79" s="7" t="inlineStr">
         <is>
-          <t>invoices</t>
+          <t>wallet_transactions</t>
         </is>
       </c>
       <c r="D79" s="7" t="inlineStr">
         <is>
-          <t>Hóa đơn</t>
+          <t>Giao dịch ví</t>
         </is>
       </c>
       <c r="E79" s="6" t="inlineStr">
@@ -3734,16 +3736,16 @@
       </c>
       <c r="F79" s="6" t="inlineStr">
         <is>
-          <t>F-H3, F-H4</t>
+          <t>F-H2</t>
         </is>
       </c>
       <c r="G79" s="6" t="inlineStr">
         <is>
-          <t>Một hóa đơn điện tử hợp lệ. Khi đã PHÁT HÀNH thì không sửa, chỉ điều chỉnh hoặc hủy bằng hóa đơn mới.</t>
+          <t>Biến động tiền vào/ra khỏi ví, chỉ ghi thêm.</t>
         </is>
       </c>
       <c r="H79" s="6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I79" s="7" t="inlineStr">
         <is>
@@ -3764,303 +3766,303 @@
       </c>
       <c r="C80" s="7" t="inlineStr">
         <is>
+          <t>invoices</t>
+        </is>
+      </c>
+      <c r="D80" s="7" t="inlineStr">
+        <is>
+          <t>Hóa đơn</t>
+        </is>
+      </c>
+      <c r="E80" s="6" t="inlineStr">
+        <is>
+          <t>Khách hàng</t>
+        </is>
+      </c>
+      <c r="F80" s="6" t="inlineStr">
+        <is>
+          <t>F-H3, F-H4</t>
+        </is>
+      </c>
+      <c r="G80" s="6" t="inlineStr">
+        <is>
+          <t>Một hóa đơn điện tử hợp lệ. Khi đã PHÁT HÀNH thì không sửa, chỉ điều chỉnh hoặc hủy bằng hóa đơn mới.</t>
+        </is>
+      </c>
+      <c r="H80" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="I80" s="7" t="inlineStr">
+        <is>
+          <t>→ Mở</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="27" customHeight="1">
+      <c r="A81" s="6" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="B81" s="6" t="inlineStr">
+        <is>
+          <t>Thanh toán &amp; hóa đơn (billing)</t>
+        </is>
+      </c>
+      <c r="C81" s="7" t="inlineStr">
+        <is>
           <t>invoice_lines</t>
         </is>
       </c>
-      <c r="D80" s="7" t="inlineStr">
+      <c r="D81" s="7" t="inlineStr">
         <is>
           <t>Dòng hóa đơn</t>
         </is>
       </c>
-      <c r="E80" s="6" t="inlineStr">
+      <c r="E81" s="6" t="inlineStr">
         <is>
           <t>Khách hàng</t>
         </is>
       </c>
-      <c r="F80" s="6" t="inlineStr">
+      <c r="F81" s="6" t="inlineStr">
         <is>
           <t>F-H3, F-H4</t>
         </is>
       </c>
-      <c r="G80" s="6" t="inlineStr">
+      <c r="G81" s="6" t="inlineStr">
         <is>
           <t>Một dòng của hóa đơn: một phiên sạc hoặc một kỳ thuê bao.</t>
         </is>
       </c>
-      <c r="H80" s="6" t="n">
+      <c r="H81" s="6" t="n">
         <v>9</v>
       </c>
-      <c r="I80" s="7" t="inlineStr">
+      <c r="I81" s="7" t="inlineStr">
         <is>
           <t>→ Mở</t>
         </is>
       </c>
     </row>
-    <row r="81" ht="54" customHeight="1">
-      <c r="A81" s="6" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="B81" s="6" t="inlineStr">
+    <row r="82" ht="54" customHeight="1">
+      <c r="A82" s="6" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="B82" s="6" t="inlineStr">
         <is>
           <t>Thanh toán &amp; hóa đơn (billing)</t>
         </is>
       </c>
-      <c r="C81" s="7" t="inlineStr">
+      <c r="C82" s="7" t="inlineStr">
         <is>
           <t>subscription_plans</t>
         </is>
       </c>
-      <c r="D81" s="7" t="inlineStr">
+      <c r="D82" s="7" t="inlineStr">
         <is>
           <t>Gói dịch vụ</t>
         </is>
       </c>
-      <c r="E81" s="6" t="inlineStr">
+      <c r="E82" s="6" t="inlineStr">
         <is>
           <t>Nội bộ</t>
         </is>
       </c>
-      <c r="F81" s="6" t="inlineStr">
+      <c r="F82" s="6" t="inlineStr">
         <is>
           <t>F-H4</t>
         </is>
       </c>
-      <c r="G81" s="6" t="inlineStr">
+      <c r="G82" s="6" t="inlineStr">
         <is>
           <t>Một gói dịch vụ: mỗi gói là một dòng (GUEST là gói mặc định miễn phí, STANDARD, ADVANCED, PRO, ..., hoặc gói riêng cho một khách hàng); tính năng của gói nằm ở plan_features. Giá được tính theo từng tính năng (xem ghi chú của miền thanh toán).</t>
         </is>
       </c>
-      <c r="H81" s="6" t="n">
+      <c r="H82" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="I81" s="7" t="inlineStr">
+      <c r="I82" s="7" t="inlineStr">
         <is>
           <t>→ Mở</t>
         </is>
       </c>
     </row>
-    <row r="82" ht="40.5" customHeight="1">
-      <c r="A82" s="6" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="B82" s="6" t="inlineStr">
+    <row r="83" ht="40.5" customHeight="1">
+      <c r="A83" s="6" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="B83" s="6" t="inlineStr">
         <is>
           <t>Thanh toán &amp; hóa đơn (billing)</t>
         </is>
       </c>
-      <c r="C82" s="7" t="inlineStr">
+      <c r="C83" s="7" t="inlineStr">
         <is>
           <t>plan_features</t>
         </is>
       </c>
-      <c r="D82" s="7" t="inlineStr">
+      <c r="D83" s="7" t="inlineStr">
         <is>
           <t>Tính năng của gói dịch vụ</t>
         </is>
       </c>
-      <c r="E82" s="6" t="inlineStr">
+      <c r="E83" s="6" t="inlineStr">
         <is>
           <t>Nội bộ</t>
         </is>
       </c>
-      <c r="F82" s="6" t="inlineStr">
+      <c r="F83" s="6" t="inlineStr">
         <is>
           <t>F-H4</t>
         </is>
       </c>
-      <c r="G82" s="6" t="inlineStr">
+      <c r="G83" s="6" t="inlineStr">
         <is>
           <t>Mỗi gói dịch vụ gồm những tính năng nào. Gói dịch vụ là dữ liệu, nên G3 có thể tạo gói mới (Pro, Max, gói riêng cho một khách hàng) trên portal mà không cần lập trình viên; chỉ tính năng hoàn toàn mới mới cần viết mã.</t>
         </is>
       </c>
-      <c r="H82" s="6" t="n">
+      <c r="H83" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="I82" s="7" t="inlineStr">
+      <c r="I83" s="7" t="inlineStr">
         <is>
           <t>→ Mở</t>
         </is>
       </c>
     </row>
-    <row r="83" ht="27" customHeight="1">
-      <c r="A83" s="6" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="B83" s="6" t="inlineStr">
+    <row r="84" ht="27" customHeight="1">
+      <c r="A84" s="6" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="B84" s="6" t="inlineStr">
         <is>
           <t>Thanh toán &amp; hóa đơn (billing)</t>
         </is>
       </c>
-      <c r="C83" s="7" t="inlineStr">
+      <c r="C84" s="7" t="inlineStr">
         <is>
           <t>subscriptions</t>
         </is>
       </c>
-      <c r="D83" s="7" t="inlineStr">
+      <c r="D84" s="7" t="inlineStr">
         <is>
           <t>Thuê bao</t>
         </is>
       </c>
-      <c r="E83" s="6" t="inlineStr">
+      <c r="E84" s="6" t="inlineStr">
         <is>
           <t>Khách hàng</t>
         </is>
       </c>
-      <c r="F83" s="6" t="inlineStr">
+      <c r="F84" s="6" t="inlineStr">
         <is>
           <t>F-H4</t>
         </is>
       </c>
-      <c r="G83" s="6" t="inlineStr">
+      <c r="G84" s="6" t="inlineStr">
         <is>
           <t>Một xe đăng ký một gói; quá hạn thanh toán sẽ khóa tính năng.</t>
         </is>
       </c>
-      <c r="H83" s="6" t="n">
+      <c r="H84" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="I83" s="7" t="inlineStr">
+      <c r="I84" s="7" t="inlineStr">
         <is>
           <t>→ Mở</t>
         </is>
       </c>
     </row>
-    <row r="84" ht="27" customHeight="1">
-      <c r="A84" s="5" t="n"/>
-      <c r="B84" s="5" t="inlineStr">
+    <row r="85" ht="27" customHeight="1">
+      <c r="A85" s="5" t="n"/>
+      <c r="B85" s="5" t="inlineStr">
         <is>
           <t>Chấm điểm tài xế (scoring)</t>
         </is>
       </c>
-      <c r="C84" s="5" t="inlineStr">
+      <c r="C85" s="5" t="inlineStr">
         <is>
           <t>1 bảng</t>
         </is>
       </c>
-      <c r="D84" s="5" t="n"/>
-      <c r="E84" s="5" t="n"/>
-      <c r="F84" s="5" t="n"/>
-      <c r="G84" s="5" t="inlineStr">
+      <c r="D85" s="5" t="n"/>
+      <c r="E85" s="5" t="n"/>
+      <c r="F85" s="5" t="n"/>
+      <c r="G85" s="5" t="inlineStr">
         <is>
           <t>Chấm điểm an toàn cho tài xế từ hành vi lái xe.
 • Mỗi tuần, mỗi tài xế có một điểm, tính từ dữ liệu vận hành của xe họ lái.</t>
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="6" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="B85" s="6" t="inlineStr">
+    <row r="86">
+      <c r="A86" s="6" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="B86" s="6" t="inlineStr">
         <is>
           <t>Chấm điểm tài xế (scoring)</t>
         </is>
       </c>
-      <c r="C85" s="7" t="inlineStr">
+      <c r="C86" s="7" t="inlineStr">
         <is>
           <t>driver_scores</t>
         </is>
       </c>
-      <c r="D85" s="7" t="inlineStr">
+      <c r="D86" s="7" t="inlineStr">
         <is>
           <t>Điểm tài xế</t>
         </is>
       </c>
-      <c r="E85" s="6" t="inlineStr">
+      <c r="E86" s="6" t="inlineStr">
         <is>
           <t>Khách hàng</t>
         </is>
       </c>
-      <c r="F85" s="6" t="inlineStr">
+      <c r="F86" s="6" t="inlineStr">
         <is>
           <t>F-K1</t>
         </is>
       </c>
-      <c r="G85" s="6" t="inlineStr">
+      <c r="G86" s="6" t="inlineStr">
         <is>
           <t>Điểm an toàn hằng tuần của tài xế, tính từ dữ liệu vận hành xe.</t>
         </is>
       </c>
-      <c r="H85" s="6" t="n">
+      <c r="H86" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="I85" s="7" t="inlineStr">
+      <c r="I86" s="7" t="inlineStr">
         <is>
           <t>→ Mở</t>
         </is>
       </c>
     </row>
-    <row r="86" ht="27" customHeight="1">
-      <c r="A86" s="5" t="n"/>
-      <c r="B86" s="5" t="inlineStr">
+    <row r="87" ht="27" customHeight="1">
+      <c r="A87" s="5" t="n"/>
+      <c r="B87" s="5" t="inlineStr">
         <is>
           <t>Chưa phân miền (unassigned)</t>
         </is>
       </c>
-      <c r="C86" s="5" t="inlineStr">
+      <c r="C87" s="5" t="inlineStr">
         <is>
           <t>2 bảng</t>
         </is>
       </c>
-      <c r="D86" s="5" t="n"/>
-      <c r="E86" s="5" t="n"/>
-      <c r="F86" s="5" t="n"/>
-      <c r="G86" s="5" t="inlineStr">
+      <c r="D87" s="5" t="n"/>
+      <c r="E87" s="5" t="n"/>
+      <c r="F87" s="5" t="n"/>
+      <c r="G87" s="5" t="inlineStr">
         <is>
           <t>Các tính năng chưa được quyết định thuộc miền nghiệp vụ nào (xem feature-list.md).</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="6" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="B87" s="6" t="inlineStr">
-        <is>
-          <t>Chưa phân miền (unassigned)</t>
-        </is>
-      </c>
-      <c r="C87" s="7" t="inlineStr">
-        <is>
-          <t>promotion_campaigns</t>
-        </is>
-      </c>
-      <c r="D87" s="7" t="inlineStr">
-        <is>
-          <t>Chiến dịch khuyến mãi</t>
-        </is>
-      </c>
-      <c r="E87" s="6" t="inlineStr">
-        <is>
-          <t>Nội bộ</t>
-        </is>
-      </c>
-      <c r="F87" s="6" t="inlineStr">
-        <is>
-          <t>F-F4</t>
-        </is>
-      </c>
-      <c r="G87" s="6" t="inlineStr">
-        <is>
-          <t>Một chiến dịch nhắc bảo dưỡng hoặc khuyến mãi.</t>
-        </is>
-      </c>
-      <c r="H87" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="I87" s="7" t="inlineStr">
-        <is>
-          <t>→ Mở</t>
         </is>
       </c>
     </row>
@@ -4077,220 +4079,265 @@
       </c>
       <c r="C88" s="7" t="inlineStr">
         <is>
+          <t>promotion_campaigns</t>
+        </is>
+      </c>
+      <c r="D88" s="7" t="inlineStr">
+        <is>
+          <t>Chiến dịch khuyến mãi</t>
+        </is>
+      </c>
+      <c r="E88" s="6" t="inlineStr">
+        <is>
+          <t>Nội bộ</t>
+        </is>
+      </c>
+      <c r="F88" s="6" t="inlineStr">
+        <is>
+          <t>F-F4</t>
+        </is>
+      </c>
+      <c r="G88" s="6" t="inlineStr">
+        <is>
+          <t>Một chiến dịch nhắc bảo dưỡng hoặc khuyến mãi.</t>
+        </is>
+      </c>
+      <c r="H88" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="I88" s="7" t="inlineStr">
+        <is>
+          <t>→ Mở</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="6" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="B89" s="6" t="inlineStr">
+        <is>
+          <t>Chưa phân miền (unassigned)</t>
+        </is>
+      </c>
+      <c r="C89" s="7" t="inlineStr">
+        <is>
           <t>trips</t>
         </is>
       </c>
-      <c r="D88" s="7" t="inlineStr">
+      <c r="D89" s="7" t="inlineStr">
         <is>
           <t>Chuyến đi</t>
         </is>
       </c>
-      <c r="E88" s="6" t="inlineStr">
+      <c r="E89" s="6" t="inlineStr">
         <is>
           <t>Khách hàng</t>
         </is>
       </c>
-      <c r="F88" s="6" t="inlineStr">
+      <c r="F89" s="6" t="inlineStr">
         <is>
           <t>F-A9</t>
         </is>
       </c>
-      <c r="G88" s="6" t="inlineStr">
+      <c r="G89" s="6" t="inlineStr">
         <is>
           <t>Một chuyến đi của xe. F-A9 đang tạm dừng: chưa có khái niệm chuyến đi.</t>
         </is>
       </c>
-      <c r="H88" s="6" t="n">
+      <c r="H89" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="I88" s="7" t="inlineStr">
+      <c r="I89" s="7" t="inlineStr">
         <is>
           <t>→ Mở</t>
         </is>
       </c>
     </row>
-    <row r="89"/>
-    <row r="90" ht="27" customHeight="1">
-      <c r="A90" s="4" t="inlineStr">
+    <row r="90"/>
+    <row r="91" ht="27" customHeight="1">
+      <c r="A91" s="4" t="inlineStr">
         <is>
           <t>Chú giải</t>
         </is>
       </c>
-      <c r="B90" s="4" t="inlineStr">
+      <c r="B91" s="4" t="inlineStr">
         <is>
           <t>Ý nghĩa</t>
         </is>
       </c>
     </row>
-    <row r="91" ht="108" customHeight="1">
-      <c r="A91" s="6" t="inlineStr">
+    <row r="92" ht="108" customHeight="1">
+      <c r="A92" s="6" t="inlineStr">
         <is>
           <t>Chủ sở hữu dữ liệu: Khách hàng</t>
         </is>
       </c>
-      <c r="B91" s="6" t="inlineStr">
+      <c r="B92" s="6" t="inlineStr">
         <is>
           <t>Thuộc về một tổ chức (thường là khách hàng; công ty G3 cũng có thể sở hữu); có cột organization_id hoặc lấy qua bảng cha (DM-24).</t>
-        </is>
-      </c>
-    </row>
-    <row r="92" ht="94.5" customHeight="1">
-      <c r="A92" s="6" t="inlineStr">
-        <is>
-          <t>Chủ sở hữu dữ liệu: Nội bộ</t>
-        </is>
-      </c>
-      <c r="B92" s="6" t="inlineStr">
-        <is>
-          <t>Dữ liệu của chính chúng ta (đơn vị vận hành nền tảng), dùng chung cho mọi tổ chức.</t>
         </is>
       </c>
     </row>
     <row r="93" ht="94.5" customHeight="1">
       <c r="A93" s="6" t="inlineStr">
         <is>
+          <t>Chủ sở hữu dữ liệu: Nội bộ</t>
+        </is>
+      </c>
+      <c r="B93" s="6" t="inlineStr">
+        <is>
+          <t>Dữ liệu của chính chúng ta (đơn vị vận hành nền tảng), dùng chung cho mọi tổ chức.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="94.5" customHeight="1">
+      <c r="A94" s="6" t="inlineStr">
+        <is>
           <t>Chủ sở hữu dữ liệu: Hai bên</t>
         </is>
       </c>
-      <c r="B93" s="6" t="inlineStr">
+      <c r="B94" s="6" t="inlineStr">
         <is>
           <t>Tài sản của G3 được khách hàng sử dụng; cả hai bên cùng liên quan.</t>
         </is>
       </c>
     </row>
-    <row r="94" ht="121.5" customHeight="1">
-      <c r="A94" s="6" t="inlineStr">
+    <row r="95" ht="121.5" customHeight="1">
+      <c r="A95" s="6" t="inlineStr">
         <is>
           <t>Chủ sở hữu dữ liệu: Chưa quyết định</t>
         </is>
       </c>
-      <c r="B94" s="6" t="inlineStr">
+      <c r="B95" s="6" t="inlineStr">
         <is>
           <t>Đang chờ một quyết định còn mở (xem cuối trang).</t>
         </is>
       </c>
     </row>
-    <row r="95" ht="81" customHeight="1">
-      <c r="A95" s="6" t="inlineStr">
+    <row r="96" ht="81" customHeight="1">
+      <c r="A96" s="6" t="inlineStr">
         <is>
           <t>Miền nghiệp vụ (domain)</t>
         </is>
       </c>
-      <c r="B95" s="6" t="inlineStr">
+      <c r="B96" s="6" t="inlineStr">
         <is>
           <t>Một phần của hệ thống sở hữu dữ liệu riêng, ví dụ Xe, Trạm sạc, Thanh toán. Mỗi miền gồm một hoặc nhiều bảng.</t>
         </is>
       </c>
     </row>
-    <row r="96" ht="54" customHeight="1">
-      <c r="A96" s="6" t="inlineStr">
+    <row r="97" ht="54" customHeight="1">
+      <c r="A97" s="6" t="inlineStr">
         <is>
           <t>Bảng</t>
         </is>
       </c>
-      <c r="B96" s="6" t="inlineStr">
+      <c r="B97" s="6" t="inlineStr">
         <is>
           <t>Một loại dữ liệu được lưu, ví dụ Xe hoặc Phiên sạc. Mỗi bảng có một sheet riêng liệt kê từng cột.</t>
         </is>
       </c>
     </row>
-    <row r="97" ht="40.5" customHeight="1">
-      <c r="A97" s="6" t="inlineStr">
+    <row r="98" ht="40.5" customHeight="1">
+      <c r="A98" s="6" t="inlineStr">
         <is>
           <t>Tính năng</t>
         </is>
       </c>
-      <c r="B97" s="6" t="inlineStr">
+      <c r="B98" s="6" t="inlineStr">
         <is>
           <t>Mã tính năng trong danh sách tính năng (feature-list.md), ví dụ F-B2.</t>
         </is>
       </c>
     </row>
-    <row r="98" ht="67.5" customHeight="1">
-      <c r="A98" s="6" t="inlineStr">
+    <row r="99" ht="67.5" customHeight="1">
+      <c r="A99" s="6" t="inlineStr">
         <is>
           <t>PK / FK / UQ</t>
         </is>
       </c>
-      <c r="B98" s="6" t="inlineStr">
+      <c r="B99" s="6" t="inlineStr">
         <is>
           <t>PK: khóa chính (định danh duy nhất của dòng). FK: khóa ngoại (trỏ tới dòng của bảng khác). UQ: giá trị không được trùng.</t>
         </is>
       </c>
     </row>
-    <row r="99" ht="54" customHeight="1">
-      <c r="A99" s="6" t="inlineStr">
+    <row r="100" ht="54" customHeight="1">
+      <c r="A100" s="6" t="inlineStr">
         <is>
           <t>Ví dụ</t>
         </is>
       </c>
-      <c r="B99" s="6" t="inlineStr">
+      <c r="B100" s="6" t="inlineStr">
         <is>
           <t>Giá trị mẫu. Các mã ví dụ khớp nhau giữa các bảng, nên có thể lần theo một bản ghi mẫu qua nhiều sheet.</t>
         </is>
       </c>
     </row>
-    <row r="100" ht="40.5" customHeight="1">
-      <c r="A100" s="6" t="inlineStr">
+    <row r="101" ht="40.5" customHeight="1">
+      <c r="A101" s="6" t="inlineStr">
         <is>
           <t>NULL</t>
         </is>
       </c>
-      <c r="B100" s="6" t="inlineStr">
+      <c r="B101" s="6" t="inlineStr">
         <is>
           <t>Ô không có giá trị. Ý nghĩa của NULL được giải thích trong cột Ý nghĩa.</t>
         </is>
       </c>
     </row>
-    <row r="101" ht="81" customHeight="1">
-      <c r="A101" s="6" t="inlineStr">
+    <row r="102" ht="81" customHeight="1">
+      <c r="A102" s="6" t="inlineStr">
         <is>
           <t>🔍 Lưu lịch sử</t>
         </is>
       </c>
-      <c r="B101" s="6" t="inlineStr">
+      <c r="B102" s="6" t="inlineStr">
         <is>
           <t>Cột được theo dõi: khi cột này thay đổi, toàn bộ dòng cũ được chép sang bảng lịch sử (tên kết thúc bằng _history) kèm thời điểm và người thay đổi.</t>
         </is>
       </c>
     </row>
-    <row r="102"/>
-    <row r="103">
-      <c r="A103" s="8" t="inlineStr">
+    <row r="103"/>
+    <row r="104">
+      <c r="A104" s="8" t="inlineStr">
         <is>
           <t>Các quyết định còn mở</t>
         </is>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" s="4" t="inlineStr">
+    <row r="105">
+      <c r="A105" s="4" t="inlineStr">
         <is>
           <t>Mã</t>
         </is>
       </c>
-      <c r="B104" s="4" t="inlineStr">
+      <c r="B105" s="4" t="inlineStr">
         <is>
           <t>Câu hỏi</t>
         </is>
       </c>
-      <c r="C104" s="4" t="inlineStr">
+      <c r="C105" s="4" t="inlineStr">
         <is>
           <t>Ảnh hưởng tới</t>
         </is>
       </c>
     </row>
-    <row r="105" ht="54" customHeight="1">
-      <c r="A105" s="6" t="inlineStr">
+    <row r="106" ht="54" customHeight="1">
+      <c r="A106" s="6" t="inlineStr">
         <is>
           <t>D5</t>
         </is>
       </c>
-      <c r="B105" s="6" t="inlineStr">
+      <c r="B106" s="6" t="inlineStr">
         <is>
           <t>Ai trả tiền khi tài xế của đội xe sạc: ví của tài xế, ví của đội xe, hay tùy trường hợp?</t>
         </is>
       </c>
-      <c r="C105" s="6" t="inlineStr">
+      <c r="C106" s="6" t="inlineStr">
         <is>
           <t>wallets, payments</t>
         </is>
@@ -4385,120 +4432,123 @@
     <hyperlink ref="C39" location="'telematic_state'!A1"/>
     <hyperlink ref="D39" location="'telematic_state'!A1"/>
     <hyperlink ref="I39" location="'telematic_state'!A1"/>
-    <hyperlink ref="C41" location="'vehicle_telemetry'!A1"/>
-    <hyperlink ref="D41" location="'vehicle_telemetry'!A1"/>
-    <hyperlink ref="I41" location="'vehicle_telemetry'!A1"/>
-    <hyperlink ref="C43" location="'drivers'!A1"/>
-    <hyperlink ref="D43" location="'drivers'!A1"/>
-    <hyperlink ref="I43" location="'drivers'!A1"/>
-    <hyperlink ref="C44" location="'driver_vehicle_assignments'!A1"/>
-    <hyperlink ref="D44" location="'driver_vehicle_assignments'!A1"/>
-    <hyperlink ref="I44" location="'driver_vehicle_assignments'!A1"/>
-    <hyperlink ref="C45" location="'driving_sessions'!A1"/>
-    <hyperlink ref="D45" location="'driving_sessions'!A1"/>
-    <hyperlink ref="I45" location="'driving_sessions'!A1"/>
-    <hyperlink ref="C46" location="'charging_credentials'!A1"/>
-    <hyperlink ref="D46" location="'charging_credentials'!A1"/>
-    <hyperlink ref="I46" location="'charging_credentials'!A1"/>
-    <hyperlink ref="C48" location="'fleets'!A1"/>
-    <hyperlink ref="D48" location="'fleets'!A1"/>
-    <hyperlink ref="I48" location="'fleets'!A1"/>
-    <hyperlink ref="C49" location="'fleet_vehicle_memberships'!A1"/>
-    <hyperlink ref="D49" location="'fleet_vehicle_memberships'!A1"/>
-    <hyperlink ref="I49" location="'fleet_vehicle_memberships'!A1"/>
-    <hyperlink ref="C50" location="'geofences'!A1"/>
-    <hyperlink ref="D50" location="'geofences'!A1"/>
-    <hyperlink ref="I50" location="'geofences'!A1"/>
-    <hyperlink ref="C51" location="'fleet_user_assignments'!A1"/>
-    <hyperlink ref="D51" location="'fleet_user_assignments'!A1"/>
-    <hyperlink ref="I51" location="'fleet_user_assignments'!A1"/>
-    <hyperlink ref="C53" location="'charging_stations'!A1"/>
-    <hyperlink ref="D53" location="'charging_stations'!A1"/>
-    <hyperlink ref="I53" location="'charging_stations'!A1"/>
-    <hyperlink ref="C54" location="'charging_evses'!A1"/>
-    <hyperlink ref="D54" location="'charging_evses'!A1"/>
-    <hyperlink ref="I54" location="'charging_evses'!A1"/>
-    <hyperlink ref="C55" location="'charging_connectors'!A1"/>
-    <hyperlink ref="D55" location="'charging_connectors'!A1"/>
-    <hyperlink ref="I55" location="'charging_connectors'!A1"/>
-    <hyperlink ref="C56" location="'charging_ocpp_messages'!A1"/>
-    <hyperlink ref="D56" location="'charging_ocpp_messages'!A1"/>
-    <hyperlink ref="I56" location="'charging_ocpp_messages'!A1"/>
-    <hyperlink ref="C57" location="'charging_station_config_entries'!A1"/>
-    <hyperlink ref="D57" location="'charging_station_config_entries'!A1"/>
-    <hyperlink ref="I57" location="'charging_station_config_entries'!A1"/>
-    <hyperlink ref="C58" location="'charging_reservations'!A1"/>
-    <hyperlink ref="D58" location="'charging_reservations'!A1"/>
-    <hyperlink ref="I58" location="'charging_reservations'!A1"/>
-    <hyperlink ref="C60" location="'charging_sessions'!A1"/>
-    <hyperlink ref="D60" location="'charging_sessions'!A1"/>
-    <hyperlink ref="I60" location="'charging_sessions'!A1"/>
-    <hyperlink ref="C61" location="'charging_session_events'!A1"/>
-    <hyperlink ref="D61" location="'charging_session_events'!A1"/>
-    <hyperlink ref="I61" location="'charging_session_events'!A1"/>
-    <hyperlink ref="C62" location="'charging_session_measurements'!A1"/>
-    <hyperlink ref="D62" location="'charging_session_measurements'!A1"/>
-    <hyperlink ref="I62" location="'charging_session_measurements'!A1"/>
-    <hyperlink ref="C64" location="'notifications'!A1"/>
-    <hyperlink ref="D64" location="'notifications'!A1"/>
-    <hyperlink ref="I64" location="'notifications'!A1"/>
-    <hyperlink ref="C66" location="'support_cases'!A1"/>
-    <hyperlink ref="D66" location="'support_cases'!A1"/>
-    <hyperlink ref="I66" location="'support_cases'!A1"/>
-    <hyperlink ref="C67" location="'repair_partners'!A1"/>
-    <hyperlink ref="D67" location="'repair_partners'!A1"/>
-    <hyperlink ref="I67" location="'repair_partners'!A1"/>
-    <hyperlink ref="C68" location="'maintenance_bookings'!A1"/>
-    <hyperlink ref="D68" location="'maintenance_bookings'!A1"/>
-    <hyperlink ref="I68" location="'maintenance_bookings'!A1"/>
-    <hyperlink ref="C70" location="'charging_policies'!A1"/>
-    <hyperlink ref="D70" location="'charging_policies'!A1"/>
-    <hyperlink ref="I70" location="'charging_policies'!A1"/>
-    <hyperlink ref="C71" location="'charging_policy_versions'!A1"/>
-    <hyperlink ref="D71" location="'charging_policy_versions'!A1"/>
-    <hyperlink ref="I71" location="'charging_policy_versions'!A1"/>
-    <hyperlink ref="C72" location="'charging_policy_assignments'!A1"/>
-    <hyperlink ref="D72" location="'charging_policy_assignments'!A1"/>
-    <hyperlink ref="I72" location="'charging_policy_assignments'!A1"/>
-    <hyperlink ref="C73" location="'policy_violations'!A1"/>
-    <hyperlink ref="D73" location="'policy_violations'!A1"/>
-    <hyperlink ref="I73" location="'policy_violations'!A1"/>
-    <hyperlink ref="C75" location="'tariffs'!A1"/>
-    <hyperlink ref="D75" location="'tariffs'!A1"/>
-    <hyperlink ref="I75" location="'tariffs'!A1"/>
-    <hyperlink ref="C76" location="'payments'!A1"/>
-    <hyperlink ref="D76" location="'payments'!A1"/>
-    <hyperlink ref="I76" location="'payments'!A1"/>
-    <hyperlink ref="C77" location="'wallets'!A1"/>
-    <hyperlink ref="D77" location="'wallets'!A1"/>
-    <hyperlink ref="I77" location="'wallets'!A1"/>
-    <hyperlink ref="C78" location="'wallet_transactions'!A1"/>
-    <hyperlink ref="D78" location="'wallet_transactions'!A1"/>
-    <hyperlink ref="I78" location="'wallet_transactions'!A1"/>
-    <hyperlink ref="C79" location="'invoices'!A1"/>
-    <hyperlink ref="D79" location="'invoices'!A1"/>
-    <hyperlink ref="I79" location="'invoices'!A1"/>
-    <hyperlink ref="C80" location="'invoice_lines'!A1"/>
-    <hyperlink ref="D80" location="'invoice_lines'!A1"/>
-    <hyperlink ref="I80" location="'invoice_lines'!A1"/>
-    <hyperlink ref="C81" location="'subscription_plans'!A1"/>
-    <hyperlink ref="D81" location="'subscription_plans'!A1"/>
-    <hyperlink ref="I81" location="'subscription_plans'!A1"/>
-    <hyperlink ref="C82" location="'plan_features'!A1"/>
-    <hyperlink ref="D82" location="'plan_features'!A1"/>
-    <hyperlink ref="I82" location="'plan_features'!A1"/>
-    <hyperlink ref="C83" location="'subscriptions'!A1"/>
-    <hyperlink ref="D83" location="'subscriptions'!A1"/>
-    <hyperlink ref="I83" location="'subscriptions'!A1"/>
-    <hyperlink ref="C85" location="'driver_scores'!A1"/>
-    <hyperlink ref="D85" location="'driver_scores'!A1"/>
-    <hyperlink ref="I85" location="'driver_scores'!A1"/>
-    <hyperlink ref="C87" location="'promotion_campaigns'!A1"/>
-    <hyperlink ref="D87" location="'promotion_campaigns'!A1"/>
-    <hyperlink ref="I87" location="'promotion_campaigns'!A1"/>
-    <hyperlink ref="C88" location="'trips'!A1"/>
-    <hyperlink ref="D88" location="'trips'!A1"/>
-    <hyperlink ref="I88" location="'trips'!A1"/>
+    <hyperlink ref="C40" location="'telematic_status_reports'!A1"/>
+    <hyperlink ref="D40" location="'telematic_status_reports'!A1"/>
+    <hyperlink ref="I40" location="'telematic_status_reports'!A1"/>
+    <hyperlink ref="C42" location="'vehicle_telemetry'!A1"/>
+    <hyperlink ref="D42" location="'vehicle_telemetry'!A1"/>
+    <hyperlink ref="I42" location="'vehicle_telemetry'!A1"/>
+    <hyperlink ref="C44" location="'drivers'!A1"/>
+    <hyperlink ref="D44" location="'drivers'!A1"/>
+    <hyperlink ref="I44" location="'drivers'!A1"/>
+    <hyperlink ref="C45" location="'driver_vehicle_assignments'!A1"/>
+    <hyperlink ref="D45" location="'driver_vehicle_assignments'!A1"/>
+    <hyperlink ref="I45" location="'driver_vehicle_assignments'!A1"/>
+    <hyperlink ref="C46" location="'driving_sessions'!A1"/>
+    <hyperlink ref="D46" location="'driving_sessions'!A1"/>
+    <hyperlink ref="I46" location="'driving_sessions'!A1"/>
+    <hyperlink ref="C47" location="'charging_credentials'!A1"/>
+    <hyperlink ref="D47" location="'charging_credentials'!A1"/>
+    <hyperlink ref="I47" location="'charging_credentials'!A1"/>
+    <hyperlink ref="C49" location="'fleets'!A1"/>
+    <hyperlink ref="D49" location="'fleets'!A1"/>
+    <hyperlink ref="I49" location="'fleets'!A1"/>
+    <hyperlink ref="C50" location="'fleet_vehicle_memberships'!A1"/>
+    <hyperlink ref="D50" location="'fleet_vehicle_memberships'!A1"/>
+    <hyperlink ref="I50" location="'fleet_vehicle_memberships'!A1"/>
+    <hyperlink ref="C51" location="'geofences'!A1"/>
+    <hyperlink ref="D51" location="'geofences'!A1"/>
+    <hyperlink ref="I51" location="'geofences'!A1"/>
+    <hyperlink ref="C52" location="'fleet_user_assignments'!A1"/>
+    <hyperlink ref="D52" location="'fleet_user_assignments'!A1"/>
+    <hyperlink ref="I52" location="'fleet_user_assignments'!A1"/>
+    <hyperlink ref="C54" location="'charging_stations'!A1"/>
+    <hyperlink ref="D54" location="'charging_stations'!A1"/>
+    <hyperlink ref="I54" location="'charging_stations'!A1"/>
+    <hyperlink ref="C55" location="'charging_evses'!A1"/>
+    <hyperlink ref="D55" location="'charging_evses'!A1"/>
+    <hyperlink ref="I55" location="'charging_evses'!A1"/>
+    <hyperlink ref="C56" location="'charging_connectors'!A1"/>
+    <hyperlink ref="D56" location="'charging_connectors'!A1"/>
+    <hyperlink ref="I56" location="'charging_connectors'!A1"/>
+    <hyperlink ref="C57" location="'charging_ocpp_messages'!A1"/>
+    <hyperlink ref="D57" location="'charging_ocpp_messages'!A1"/>
+    <hyperlink ref="I57" location="'charging_ocpp_messages'!A1"/>
+    <hyperlink ref="C58" location="'charging_station_config_entries'!A1"/>
+    <hyperlink ref="D58" location="'charging_station_config_entries'!A1"/>
+    <hyperlink ref="I58" location="'charging_station_config_entries'!A1"/>
+    <hyperlink ref="C59" location="'charging_reservations'!A1"/>
+    <hyperlink ref="D59" location="'charging_reservations'!A1"/>
+    <hyperlink ref="I59" location="'charging_reservations'!A1"/>
+    <hyperlink ref="C61" location="'charging_sessions'!A1"/>
+    <hyperlink ref="D61" location="'charging_sessions'!A1"/>
+    <hyperlink ref="I61" location="'charging_sessions'!A1"/>
+    <hyperlink ref="C62" location="'charging_session_events'!A1"/>
+    <hyperlink ref="D62" location="'charging_session_events'!A1"/>
+    <hyperlink ref="I62" location="'charging_session_events'!A1"/>
+    <hyperlink ref="C63" location="'charging_session_measurements'!A1"/>
+    <hyperlink ref="D63" location="'charging_session_measurements'!A1"/>
+    <hyperlink ref="I63" location="'charging_session_measurements'!A1"/>
+    <hyperlink ref="C65" location="'notifications'!A1"/>
+    <hyperlink ref="D65" location="'notifications'!A1"/>
+    <hyperlink ref="I65" location="'notifications'!A1"/>
+    <hyperlink ref="C67" location="'support_cases'!A1"/>
+    <hyperlink ref="D67" location="'support_cases'!A1"/>
+    <hyperlink ref="I67" location="'support_cases'!A1"/>
+    <hyperlink ref="C68" location="'repair_partners'!A1"/>
+    <hyperlink ref="D68" location="'repair_partners'!A1"/>
+    <hyperlink ref="I68" location="'repair_partners'!A1"/>
+    <hyperlink ref="C69" location="'maintenance_bookings'!A1"/>
+    <hyperlink ref="D69" location="'maintenance_bookings'!A1"/>
+    <hyperlink ref="I69" location="'maintenance_bookings'!A1"/>
+    <hyperlink ref="C71" location="'charging_policies'!A1"/>
+    <hyperlink ref="D71" location="'charging_policies'!A1"/>
+    <hyperlink ref="I71" location="'charging_policies'!A1"/>
+    <hyperlink ref="C72" location="'charging_policy_versions'!A1"/>
+    <hyperlink ref="D72" location="'charging_policy_versions'!A1"/>
+    <hyperlink ref="I72" location="'charging_policy_versions'!A1"/>
+    <hyperlink ref="C73" location="'charging_policy_assignments'!A1"/>
+    <hyperlink ref="D73" location="'charging_policy_assignments'!A1"/>
+    <hyperlink ref="I73" location="'charging_policy_assignments'!A1"/>
+    <hyperlink ref="C74" location="'policy_violations'!A1"/>
+    <hyperlink ref="D74" location="'policy_violations'!A1"/>
+    <hyperlink ref="I74" location="'policy_violations'!A1"/>
+    <hyperlink ref="C76" location="'tariffs'!A1"/>
+    <hyperlink ref="D76" location="'tariffs'!A1"/>
+    <hyperlink ref="I76" location="'tariffs'!A1"/>
+    <hyperlink ref="C77" location="'payments'!A1"/>
+    <hyperlink ref="D77" location="'payments'!A1"/>
+    <hyperlink ref="I77" location="'payments'!A1"/>
+    <hyperlink ref="C78" location="'wallets'!A1"/>
+    <hyperlink ref="D78" location="'wallets'!A1"/>
+    <hyperlink ref="I78" location="'wallets'!A1"/>
+    <hyperlink ref="C79" location="'wallet_transactions'!A1"/>
+    <hyperlink ref="D79" location="'wallet_transactions'!A1"/>
+    <hyperlink ref="I79" location="'wallet_transactions'!A1"/>
+    <hyperlink ref="C80" location="'invoices'!A1"/>
+    <hyperlink ref="D80" location="'invoices'!A1"/>
+    <hyperlink ref="I80" location="'invoices'!A1"/>
+    <hyperlink ref="C81" location="'invoice_lines'!A1"/>
+    <hyperlink ref="D81" location="'invoice_lines'!A1"/>
+    <hyperlink ref="I81" location="'invoice_lines'!A1"/>
+    <hyperlink ref="C82" location="'subscription_plans'!A1"/>
+    <hyperlink ref="D82" location="'subscription_plans'!A1"/>
+    <hyperlink ref="I82" location="'subscription_plans'!A1"/>
+    <hyperlink ref="C83" location="'plan_features'!A1"/>
+    <hyperlink ref="D83" location="'plan_features'!A1"/>
+    <hyperlink ref="I83" location="'plan_features'!A1"/>
+    <hyperlink ref="C84" location="'subscriptions'!A1"/>
+    <hyperlink ref="D84" location="'subscriptions'!A1"/>
+    <hyperlink ref="I84" location="'subscriptions'!A1"/>
+    <hyperlink ref="C86" location="'driver_scores'!A1"/>
+    <hyperlink ref="D86" location="'driver_scores'!A1"/>
+    <hyperlink ref="I86" location="'driver_scores'!A1"/>
+    <hyperlink ref="C88" location="'promotion_campaigns'!A1"/>
+    <hyperlink ref="D88" location="'promotion_campaigns'!A1"/>
+    <hyperlink ref="I88" location="'promotion_campaigns'!A1"/>
+    <hyperlink ref="C89" location="'trips'!A1"/>
+    <hyperlink ref="D89" location="'trips'!A1"/>
+    <hyperlink ref="I89" location="'trips'!A1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -16587,7 +16637,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I38"/>
+  <dimension ref="A1:I39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -17438,7 +17488,7 @@
       <c r="A37" s="6" t="n"/>
       <c r="B37" s="7" t="inlineStr">
         <is>
-          <t>vehicle_telemetry</t>
+          <t>telematic_status_reports</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
@@ -17451,10 +17501,23 @@
       <c r="A38" s="6" t="n"/>
       <c r="B38" s="7" t="inlineStr">
         <is>
+          <t>vehicle_telemetry</t>
+        </is>
+      </c>
+      <c r="C38" s="6" t="inlineStr">
+        <is>
+          <t>telematic_id</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="6" t="n"/>
+      <c r="B39" s="7" t="inlineStr">
+        <is>
           <t>telematic_history</t>
         </is>
       </c>
-      <c r="C38" s="6" t="inlineStr">
+      <c r="C39" s="6" t="inlineStr">
         <is>
           <t>telematic_id</t>
         </is>
@@ -17470,8 +17533,9 @@
     <hyperlink ref="F14" location="'vehicles'!A1"/>
     <hyperlink ref="B35" location="'warranties'!A1"/>
     <hyperlink ref="B36" location="'telematic_state'!A1"/>
-    <hyperlink ref="B37" location="'vehicle_telemetry'!A1"/>
-    <hyperlink ref="B38" location="'telematic_history'!A1"/>
+    <hyperlink ref="B37" location="'telematic_status_reports'!A1"/>
+    <hyperlink ref="B38" location="'vehicle_telemetry'!A1"/>
+    <hyperlink ref="B39" location="'telematic_history'!A1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -19444,6 +19508,602 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:I22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="7" max="7"/>
+    <col width="42" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>20. telematic_status_reports: Báo cáo trạng thái thiết bị telematics</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t>← Tổng quan</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>Miền nghiệp vụ: Thiết bị telematics (telematics)   ·   Chủ sở hữu dữ liệu: Khách hàng   ·   Tính năng: F-J1, F-J3</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>Mọi báo cáo sức khỏe mà T-Box gửi về chính nó, khoảng mỗi ngày một lần (TX-10), để xem được xu hướng (sóng yếu dần, điện áp tụt trước khi mất tín hiệu). Chỉ ghi thêm: không bao giờ sửa dòng nên không cần lịch sử thay đổi. Là bảng thường, không phải hypertable: khoảng 365 dòng mỗi thiết bị mỗi năm. Không có organization_id (DM-24): như các dữ liệu tình trạng khác, đi theo thiết bị sang chủ kế tiếp (VH-11). Các trường là tạm thời cho tới khi nhà cung cấp xác nhận bản tin (mqtt-spec.md mục 2.2).</t>
+        </is>
+      </c>
+    </row>
+    <row r="5"/>
+    <row r="6" ht="27" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Cột</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Kiểu dữ liệu</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Cho phép rỗng</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>Khóa</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>Tham chiếu tới</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>Ý nghĩa</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>Ví dụ</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>Lưu lịch sử</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>status_report_id</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>bigint</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="n"/>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>Mã tự tăng của báo cáo.</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>51234</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="n"/>
+    </row>
+    <row r="8" ht="27" customHeight="1">
+      <c r="A8" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>telematic_id</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>uuid</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>telematics.telematic_id (khi xóa: chặn xóa)</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>Thiết bị gửi báo cáo.</t>
+        </is>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>2c8e5a1d-9f3b-4d7c-b2e6-8a1f0c5d9e55</t>
+        </is>
+      </c>
+      <c r="I8" s="6" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>firmware_version</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>varchar(50)</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="n"/>
+      <c r="F9" s="6" t="n"/>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>Phiên bản firmware được báo.</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>1.4.2</t>
+        </is>
+      </c>
+      <c r="I9" s="6" t="n"/>
+    </row>
+    <row r="10" ht="27" customHeight="1">
+      <c r="A10" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>telemetry_interval_seconds</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="n"/>
+      <c r="F10" s="6" t="n"/>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>Chu kỳ gửi thiết bị báo đang dùng.</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I10" s="6" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>sim_iccid</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>varchar(22)</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="n"/>
+      <c r="F11" s="6" t="n"/>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>Số ICCID của SIM trong thiết bị.</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>8984049000001234567</t>
+        </is>
+      </c>
+      <c r="I11" s="6" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>is_esim</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>boolean</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="n"/>
+      <c r="F12" s="6" t="n"/>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>TRUE khi SIM là eSIM.</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="I12" s="6" t="n"/>
+    </row>
+    <row r="13" ht="27" customHeight="1">
+      <c r="A13" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>sim_data_status</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>varchar(20)</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="n"/>
+      <c r="F13" s="6" t="n"/>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>Trạng thái dữ liệu di động (giá trị tạm: ACTIVE | NO_DATA | SUSPENDED | NO_SIM).</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="I13" s="6" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>supply_voltage_v</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>numeric(5,2)</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="n"/>
+      <c r="F14" s="6" t="n"/>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>Điện áp nguồn cấp tại thiết bị (V).</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>24.30</t>
+        </is>
+      </c>
+      <c r="I14" s="6" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>signal_dbm</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>smallint</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="n"/>
+      <c r="F15" s="6" t="n"/>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>Cường độ sóng di động (dBm).</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>-78</t>
+        </is>
+      </c>
+      <c r="I15" s="6" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>storage_used_percent</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>numeric(5,2)</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="n"/>
+      <c r="F16" s="6" t="n"/>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>Tỷ lệ bộ nhớ thiết bị đã dùng, 0-100.</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>41.50</t>
+        </is>
+      </c>
+      <c r="I16" s="6" t="n"/>
+    </row>
+    <row r="17" ht="27" customHeight="1">
+      <c r="A17" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>gnss_status</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>varchar(20)</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="n"/>
+      <c r="F17" s="6" t="n"/>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>Trạng thái định vị vệ tinh (giá trị tạm: FIX | NO_FIX | ANTENNA_FAULT).</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>FIX</t>
+        </is>
+      </c>
+      <c r="I17" s="6" t="n"/>
+    </row>
+    <row r="18" ht="27" customHeight="1">
+      <c r="A18" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>reported_at</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>timestamptz</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="n"/>
+      <c r="F18" s="6" t="n"/>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>Thời điểm thiết bị tạo báo cáo (theo đồng hồ thiết bị, chuẩn hóa về UTC).</t>
+        </is>
+      </c>
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-14T00:30:00Z</t>
+        </is>
+      </c>
+      <c r="I18" s="6" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>received_at</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>timestamptz</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="n"/>
+      <c r="F19" s="6" t="n"/>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>Thời điểm backend nhận được.</t>
+        </is>
+      </c>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-14T00:30:02Z</t>
+        </is>
+      </c>
+      <c r="I19" s="6" t="n"/>
+    </row>
+    <row r="20"/>
+    <row r="21">
+      <c r="A21" s="4" t="n"/>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>Chỉ mục (index)</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>Các cột</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>Duy nhất</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="n"/>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>Ghi chú</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="27" customHeight="1">
+      <c r="A22" s="6" t="n"/>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>ix_telematic_status_reports_device_time</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>telematic_id, reported_at</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="n"/>
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t>A device's reports over time, newest first</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A6:I19"/>
+  <hyperlinks>
+    <hyperlink ref="A2" location="'Tổng quan'!A1"/>
+    <hyperlink ref="F8" location="'telematics'!A1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:I35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -19461,7 +20121,7 @@
     <row r="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>20. vehicle_telemetry: Dữ liệu vận hành xe</t>
+          <t>21. vehicle_telemetry: Dữ liệu vận hành xe</t>
         </is>
       </c>
     </row>
@@ -20446,7 +21106,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -20469,7 +21129,7 @@
     <row r="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>21. drivers: Tài xế</t>
+          <t>22. drivers: Tài xế</t>
         </is>
       </c>
     </row>
@@ -21149,7 +21809,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -21172,7 +21832,7 @@
     <row r="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>22. driver_vehicle_assignments: Phân công tài xế - xe</t>
+          <t>23. driver_vehicle_assignments: Phân công tài xế - xe</t>
         </is>
       </c>
     </row>
@@ -21682,7 +22342,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -21705,7 +22365,7 @@
     <row r="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>23. driving_sessions: Phiên lái xe</t>
+          <t>24. driving_sessions: Phiên lái xe</t>
         </is>
       </c>
     </row>
@@ -22294,7 +22954,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -22317,7 +22977,7 @@
     <row r="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>24. charging_credentials: Phương thức xác thực sạc</t>
+          <t>25. charging_credentials: Phương thức xác thực sạc</t>
         </is>
       </c>
     </row>
@@ -22717,7 +23377,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -22740,7 +23400,7 @@
     <row r="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>25. fleets: Đội xe</t>
+          <t>26. fleets: Đội xe</t>
         </is>
       </c>
     </row>
@@ -23321,7 +23981,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -23344,7 +24004,7 @@
     <row r="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>26. fleet_vehicle_memberships: Thành viên đội xe</t>
+          <t>27. fleet_vehicle_memberships: Thành viên đội xe</t>
         </is>
       </c>
     </row>
@@ -23830,7 +24490,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -23853,7 +24513,7 @@
     <row r="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>27. geofences: Vùng địa lý (geofence)</t>
+          <t>28. geofences: Vùng địa lý (geofence)</t>
         </is>
       </c>
     </row>
@@ -24261,389 +24921,6 @@
     <hyperlink ref="A2" location="'Tổng quan'!A1"/>
     <hyperlink ref="F8" location="'fleets'!A1"/>
     <hyperlink ref="F9" location="'organizations'!A1"/>
-  </hyperlinks>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I15"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="40" customWidth="1" min="6" max="6"/>
-    <col width="60" customWidth="1" min="7" max="7"/>
-    <col width="42" customWidth="1" min="8" max="8"/>
-    <col width="11" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="9" t="inlineStr">
-        <is>
-          <t>28. fleet_user_assignments: Phân công người dùng - đội xe</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="10" t="inlineStr">
-        <is>
-          <t>← Tổng quan</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>Miền nghiệp vụ: Đội xe (fleet)   ·   Chủ sở hữu dữ liệu: Khách hàng   ·   Tính năng: F-F1, F-E1</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="11" t="inlineStr">
-        <is>
-          <t>Giới hạn vai trò cấp đội xe của một người dùng trong một số đội xe của tổ chức lớn (ví dụ một quản lý cho đội Hà Nội, một quản lý khác cho đội TP.HCM). Người dùng không có dòng nào đang hiệu lực ở đây thì quản lý mọi đội xe của tổ chức. Nằm ở miền Đội xe, không ở miền Danh tính, để miền Danh tính không phụ thuộc miền nào.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5"/>
-    <row r="6" ht="27" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>Cột</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>Kiểu dữ liệu</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>Cho phép rỗng</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>Khóa</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>Tham chiếu tới</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>Ý nghĩa</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>Ví dụ</t>
-        </is>
-      </c>
-      <c r="I6" s="4" t="inlineStr">
-        <is>
-          <t>Lưu lịch sử</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>assignment_id</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>uuid</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
-      <c r="F7" s="6" t="n"/>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>Mã nội bộ của lần phân công.</t>
-        </is>
-      </c>
-      <c r="H7" s="6" t="inlineStr">
-        <is>
-          <t>0000001c-5a6b-4c7d-8e9f-0a1b2c3d4e5f</t>
-        </is>
-      </c>
-      <c r="I7" s="6" t="n"/>
-    </row>
-    <row r="8" ht="27" customHeight="1">
-      <c r="A8" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>organization_id</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>uuid</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E8" s="6" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="F8" s="7" t="inlineStr">
-        <is>
-          <t>organizations.organization_id (khi xóa: chặn xóa)</t>
-        </is>
-      </c>
-      <c r="G8" s="6" t="inlineStr">
-        <is>
-          <t>Tổ chức của đội xe và người dùng.</t>
-        </is>
-      </c>
-      <c r="H8" s="6" t="inlineStr">
-        <is>
-          <t>3f6c2a1e-8b4d-4e2a-9c1f-0a7d5b2e4c11</t>
-        </is>
-      </c>
-      <c r="I8" s="6" t="n"/>
-    </row>
-    <row r="9" ht="27" customHeight="1">
-      <c r="A9" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>fleet_id</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>uuid</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E9" s="6" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="F9" s="7" t="inlineStr">
-        <is>
-          <t>fleets.fleet_id (khi xóa: chặn xóa)</t>
-        </is>
-      </c>
-      <c r="G9" s="6" t="inlineStr">
-        <is>
-          <t>Đội xe mà người dùng được giới hạn trong đó, cùng mọi đội xe nằm dưới.</t>
-        </is>
-      </c>
-      <c r="H9" s="6" t="inlineStr">
-        <is>
-          <t>8d5f2b7e-1a9c-4f3d-b8e2-6c0a4d9f1e77</t>
-        </is>
-      </c>
-      <c r="I9" s="6" t="n"/>
-    </row>
-    <row r="10" ht="40.5" customHeight="1">
-      <c r="A10" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>membership_id</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>uuid</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E10" s="6" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="F10" s="7" t="inlineStr">
-        <is>
-          <t>memberships.membership_id (khi xóa: chặn xóa)</t>
-        </is>
-      </c>
-      <c r="G10" s="6" t="inlineStr">
-        <is>
-          <t>Thành viên (người trong tổ chức này) có các vai trò cấp đội xe (FLEET_MANAGER, DISPATCHER) chỉ áp dụng cho các đội xe được liệt kê.</t>
-        </is>
-      </c>
-      <c r="H10" s="6" t="inlineStr">
-        <is>
-          <t>00000022-5a6b-4c7d-8e9f-0a1b2c3d4e5f</t>
-        </is>
-      </c>
-      <c r="I10" s="6" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>assigned_at</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>timestamptz</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E11" s="6" t="n"/>
-      <c r="F11" s="6" t="n"/>
-      <c r="G11" s="6" t="inlineStr">
-        <is>
-          <t>Thời điểm người dùng được giao đội xe này.</t>
-        </is>
-      </c>
-      <c r="H11" s="6" t="inlineStr">
-        <is>
-          <t>2026-09-01T02:00:00Z</t>
-        </is>
-      </c>
-      <c r="I11" s="6" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>unassigned_at</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>timestamptz</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>có</t>
-        </is>
-      </c>
-      <c r="E12" s="6" t="n"/>
-      <c r="F12" s="6" t="n"/>
-      <c r="G12" s="6" t="inlineStr">
-        <is>
-          <t>Thời điểm bị thu lại; NULL khi còn hiệu lực.</t>
-        </is>
-      </c>
-      <c r="H12" s="6" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="I12" s="6" t="n"/>
-    </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" s="4" t="n"/>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>Chỉ mục (index)</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>Các cột</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="inlineStr">
-        <is>
-          <t>Duy nhất</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="n"/>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>Ghi chú</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="27" customHeight="1">
-      <c r="A15" s="6" t="n"/>
-      <c r="B15" s="6" t="inlineStr">
-        <is>
-          <t>uq_fleet_user_assignments_active</t>
-        </is>
-      </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>fleet_id, membership_id</t>
-        </is>
-      </c>
-      <c r="D15" s="6" t="inlineStr">
-        <is>
-          <t>có</t>
-        </is>
-      </c>
-      <c r="E15" s="6" t="n"/>
-      <c r="F15" s="6" t="inlineStr">
-        <is>
-          <t>WHERE unassigned_at IS NULL</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A6:I12"/>
-  <hyperlinks>
-    <hyperlink ref="A2" location="'Tổng quan'!A1"/>
-    <hyperlink ref="F8" location="'organizations'!A1"/>
-    <hyperlink ref="F9" location="'fleets'!A1"/>
-    <hyperlink ref="F10" location="'memberships'!A1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -25606,6 +25883,389 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:I15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="7" max="7"/>
+    <col width="42" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>29. fleet_user_assignments: Phân công người dùng - đội xe</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t>← Tổng quan</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>Miền nghiệp vụ: Đội xe (fleet)   ·   Chủ sở hữu dữ liệu: Khách hàng   ·   Tính năng: F-F1, F-E1</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>Giới hạn vai trò cấp đội xe của một người dùng trong một số đội xe của tổ chức lớn (ví dụ một quản lý cho đội Hà Nội, một quản lý khác cho đội TP.HCM). Người dùng không có dòng nào đang hiệu lực ở đây thì quản lý mọi đội xe của tổ chức. Nằm ở miền Đội xe, không ở miền Danh tính, để miền Danh tính không phụ thuộc miền nào.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5"/>
+    <row r="6" ht="27" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Cột</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Kiểu dữ liệu</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Cho phép rỗng</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>Khóa</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>Tham chiếu tới</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>Ý nghĩa</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>Ví dụ</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>Lưu lịch sử</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>assignment_id</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>uuid</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="n"/>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>Mã nội bộ của lần phân công.</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>0000001c-5a6b-4c7d-8e9f-0a1b2c3d4e5f</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="n"/>
+    </row>
+    <row r="8" ht="27" customHeight="1">
+      <c r="A8" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>organization_id</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>uuid</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>organizations.organization_id (khi xóa: chặn xóa)</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>Tổ chức của đội xe và người dùng.</t>
+        </is>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>3f6c2a1e-8b4d-4e2a-9c1f-0a7d5b2e4c11</t>
+        </is>
+      </c>
+      <c r="I8" s="6" t="n"/>
+    </row>
+    <row r="9" ht="27" customHeight="1">
+      <c r="A9" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>fleet_id</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>uuid</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>fleets.fleet_id (khi xóa: chặn xóa)</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>Đội xe mà người dùng được giới hạn trong đó, cùng mọi đội xe nằm dưới.</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>8d5f2b7e-1a9c-4f3d-b8e2-6c0a4d9f1e77</t>
+        </is>
+      </c>
+      <c r="I9" s="6" t="n"/>
+    </row>
+    <row r="10" ht="40.5" customHeight="1">
+      <c r="A10" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>membership_id</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>uuid</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>memberships.membership_id (khi xóa: chặn xóa)</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>Thành viên (người trong tổ chức này) có các vai trò cấp đội xe (FLEET_MANAGER, DISPATCHER) chỉ áp dụng cho các đội xe được liệt kê.</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>00000022-5a6b-4c7d-8e9f-0a1b2c3d4e5f</t>
+        </is>
+      </c>
+      <c r="I10" s="6" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>assigned_at</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>timestamptz</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="n"/>
+      <c r="F11" s="6" t="n"/>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>Thời điểm người dùng được giao đội xe này.</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-01T02:00:00Z</t>
+        </is>
+      </c>
+      <c r="I11" s="6" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>unassigned_at</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>timestamptz</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="n"/>
+      <c r="F12" s="6" t="n"/>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>Thời điểm bị thu lại; NULL khi còn hiệu lực.</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="I12" s="6" t="n"/>
+    </row>
+    <row r="13"/>
+    <row r="14">
+      <c r="A14" s="4" t="n"/>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>Chỉ mục (index)</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>Các cột</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>Duy nhất</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="n"/>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>Ghi chú</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="27" customHeight="1">
+      <c r="A15" s="6" t="n"/>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>uq_fleet_user_assignments_active</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>fleet_id, membership_id</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="n"/>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>WHERE unassigned_at IS NULL</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A6:I12"/>
+  <hyperlinks>
+    <hyperlink ref="A2" location="'Tổng quan'!A1"/>
+    <hyperlink ref="F8" location="'organizations'!A1"/>
+    <hyperlink ref="F9" location="'fleets'!A1"/>
+    <hyperlink ref="F10" location="'memberships'!A1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:I43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -25623,7 +26283,7 @@
     <row r="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>29. charging_stations: Trạm sạc</t>
+          <t>30. charging_stations: Trạm sạc</t>
         </is>
       </c>
     </row>
@@ -26632,7 +27292,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -26655,7 +27315,7 @@
     <row r="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>30. charging_evses: EVSE (cụm cấp điện)</t>
+          <t>31. charging_evses: EVSE (cụm cấp điện)</t>
         </is>
       </c>
     </row>
@@ -27055,7 +27715,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -27078,7 +27738,7 @@
     <row r="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>31. charging_connectors: Súng sạc</t>
+          <t>32. charging_connectors: Súng sạc</t>
         </is>
       </c>
     </row>
@@ -27670,7 +28330,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -27693,7 +28353,7 @@
     <row r="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>32. charging_ocpp_messages: Nhật ký bản tin OCPP</t>
+          <t>33. charging_ocpp_messages: Nhật ký bản tin OCPP</t>
         </is>
       </c>
     </row>
@@ -28062,7 +28722,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -28085,7 +28745,7 @@
     <row r="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>33. charging_station_configuration_entries: Cấu hình trụ sạc</t>
+          <t>34. charging_station_configuration_entries: Cấu hình trụ sạc</t>
         </is>
       </c>
     </row>
@@ -28456,7 +29116,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -28479,7 +29139,7 @@
     <row r="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>34. charging_reservations: Đặt chỗ súng sạc</t>
+          <t>35. charging_reservations: Đặt chỗ súng sạc</t>
         </is>
       </c>
     </row>
@@ -28823,7 +29483,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -28846,7 +29506,7 @@
     <row r="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>35. charging_sessions: Phiên sạc</t>
+          <t>36. charging_sessions: Phiên sạc</t>
         </is>
       </c>
     </row>
@@ -29936,7 +30596,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -29959,7 +30619,7 @@
     <row r="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>36. charging_session_events: Sự kiện phiên sạc</t>
+          <t>37. charging_session_events: Sự kiện phiên sạc</t>
         </is>
       </c>
     </row>
@@ -30295,7 +30955,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -30318,7 +30978,7 @@
     <row r="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>37. charging_session_measurements: Số đo phiên sạc</t>
+          <t>38. charging_session_measurements: Số đo phiên sạc</t>
         </is>
       </c>
     </row>
@@ -30754,548 +31414,6 @@
   <hyperlinks>
     <hyperlink ref="A2" location="'Tổng quan'!A1"/>
     <hyperlink ref="F9" location="'charging_sessions'!A1"/>
-  </hyperlinks>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I23"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="40" customWidth="1" min="6" max="6"/>
-    <col width="60" customWidth="1" min="7" max="7"/>
-    <col width="42" customWidth="1" min="8" max="8"/>
-    <col width="11" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="9" t="inlineStr">
-        <is>
-          <t>38. notifications: Thông báo</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="10" t="inlineStr">
-        <is>
-          <t>← Tổng quan</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>Miền nghiệp vụ: Thông báo &amp; cảnh báo (notifications)   ·   Chủ sở hữu dữ liệu: Khách hàng   ·   Tính năng: F-A2, F-A3, F-A4, F-J1, F-J3</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="11" t="inlineStr">
-        <is>
-          <t>Một cảnh báo (pin, bất thường, SOH, thiết bị mất kết nối...). Một bảng chung; mỗi loại cảnh báo là một giá trị enum và một cấu trúc payload.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5"/>
-    <row r="6" ht="27" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>Cột</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>Kiểu dữ liệu</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>Cho phép rỗng</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>Khóa</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>Tham chiếu tới</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>Ý nghĩa</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>Ví dụ</t>
-        </is>
-      </c>
-      <c r="I6" s="4" t="inlineStr">
-        <is>
-          <t>Lưu lịch sử</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="27" customHeight="1">
-      <c r="A7" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>notification_id</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>bigint</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
-      <c r="F7" s="6" t="n"/>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>Mã tự tăng; cũng là con trỏ khi truy vấn thông báo mới (after_id).</t>
-        </is>
-      </c>
-      <c r="H7" s="6" t="inlineStr">
-        <is>
-          <t>5821</t>
-        </is>
-      </c>
-      <c r="I7" s="6" t="n"/>
-    </row>
-    <row r="8" ht="27" customHeight="1">
-      <c r="A8" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>organization_id</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>uuid</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>có</t>
-        </is>
-      </c>
-      <c r="E8" s="6" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="F8" s="7" t="inlineStr">
-        <is>
-          <t>organizations.organization_id (khi xóa: chặn xóa)</t>
-        </is>
-      </c>
-      <c r="G8" s="6" t="inlineStr">
-        <is>
-          <t>Tổ chức khách hàng được xem thông báo.</t>
-        </is>
-      </c>
-      <c r="H8" s="6" t="inlineStr">
-        <is>
-          <t>3f6c2a1e-8b4d-4e2a-9c1f-0a7d5b2e4c11</t>
-        </is>
-      </c>
-      <c r="I8" s="6" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>notification_type</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>notificationtype</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E9" s="6" t="n"/>
-      <c r="F9" s="6" t="n"/>
-      <c r="G9" s="6" t="inlineStr">
-        <is>
-          <t>Loại sự kiện đã phát sinh thông báo.</t>
-        </is>
-      </c>
-      <c r="H9" s="6" t="inlineStr">
-        <is>
-          <t>BATTERY_ALERT</t>
-        </is>
-      </c>
-      <c r="I9" s="6" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>severity</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>notificationseverity</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E10" s="6" t="n"/>
-      <c r="F10" s="6" t="n"/>
-      <c r="G10" s="6" t="inlineStr">
-        <is>
-          <t>Mức độ khẩn cấp, độc lập với loại thông báo.</t>
-        </is>
-      </c>
-      <c r="H10" s="6" t="inlineStr">
-        <is>
-          <t>WARNING</t>
-        </is>
-      </c>
-      <c r="I10" s="6" t="n"/>
-    </row>
-    <row r="11" ht="27" customHeight="1">
-      <c r="A11" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>vehicle_id</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>uuid</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>có</t>
-        </is>
-      </c>
-      <c r="E11" s="6" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="F11" s="7" t="inlineStr">
-        <is>
-          <t>vehicles.vehicle_id (khi xóa: xóa theo)</t>
-        </is>
-      </c>
-      <c r="G11" s="6" t="inlineStr">
-        <is>
-          <t>Xe mà thông báo nói tới; NULL với thông báo không liên quan xe.</t>
-        </is>
-      </c>
-      <c r="H11" s="6" t="inlineStr">
-        <is>
-          <t>7a4c1e9b-3d2f-4b8a-a6c5-1e0d9f8b7a44</t>
-        </is>
-      </c>
-      <c r="I11" s="6" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>varchar(200)</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E12" s="6" t="n"/>
-      <c r="F12" s="6" t="n"/>
-      <c r="G12" s="6" t="inlineStr">
-        <is>
-          <t>Tóm tắt ngắn.</t>
-        </is>
-      </c>
-      <c r="H12" s="6" t="inlineStr">
-        <is>
-          <t>Pin còn 20%</t>
-        </is>
-      </c>
-      <c r="I12" s="6" t="n"/>
-    </row>
-    <row r="13" ht="27" customHeight="1">
-      <c r="A13" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>body</t>
-        </is>
-      </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>varchar(500)</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E13" s="6" t="n"/>
-      <c r="F13" s="6" t="n"/>
-      <c r="G13" s="6" t="inlineStr">
-        <is>
-          <t>Mô tả chi tiết.</t>
-        </is>
-      </c>
-      <c r="H13" s="6" t="inlineStr">
-        <is>
-          <t>Xe 51D-123.45 còn 20% pin. Trạm gần nhất: Trạm sạc G3 Bình Dương (8.4 km).</t>
-        </is>
-      </c>
-      <c r="I13" s="6" t="n"/>
-    </row>
-    <row r="14" ht="40.5" customHeight="1">
-      <c r="A14" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="B14" s="6" t="inlineStr">
-        <is>
-          <t>payload</t>
-        </is>
-      </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>jsonb</t>
-        </is>
-      </c>
-      <c r="D14" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E14" s="6" t="n"/>
-      <c r="F14" s="6" t="n"/>
-      <c r="G14" s="6" t="inlineStr">
-        <is>
-          <t>Chi tiết riêng theo loại thông báo, dạng JSON.</t>
-        </is>
-      </c>
-      <c r="H14" s="6" t="inlineStr">
-        <is>
-          <t>{"threshold": 20, "soc": 19.8, "nearest_station_id": "4b9d6f3a-2e8c-4a1b-9d5e-7f0c3a8b2d88", "distance_m": 8400}</t>
-        </is>
-      </c>
-      <c r="I14" s="6" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="B15" s="6" t="inlineStr">
-        <is>
-          <t>created_at</t>
-        </is>
-      </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>timestamptz</t>
-        </is>
-      </c>
-      <c r="D15" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E15" s="6" t="n"/>
-      <c r="F15" s="6" t="n"/>
-      <c r="G15" s="6" t="inlineStr">
-        <is>
-          <t>Thời điểm phát sinh thông báo.</t>
-        </is>
-      </c>
-      <c r="H15" s="6" t="inlineStr">
-        <is>
-          <t>2026-09-15T08:30:00Z</t>
-        </is>
-      </c>
-      <c r="I15" s="6" t="n"/>
-    </row>
-    <row r="16" ht="27" customHeight="1">
-      <c r="A16" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="B16" s="6" t="inlineStr">
-        <is>
-          <t>read_at</t>
-        </is>
-      </c>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>timestamptz</t>
-        </is>
-      </c>
-      <c r="D16" s="6" t="inlineStr">
-        <is>
-          <t>có</t>
-        </is>
-      </c>
-      <c r="E16" s="6" t="n"/>
-      <c r="F16" s="6" t="n"/>
-      <c r="G16" s="6" t="inlineStr">
-        <is>
-          <t>Thời điểm người vận hành đánh dấu đã đọc; NULL nếu chưa đọc.</t>
-        </is>
-      </c>
-      <c r="H16" s="6" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="I16" s="6" t="n"/>
-    </row>
-    <row r="17"/>
-    <row r="18">
-      <c r="A18" s="4" t="n"/>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>Kiểu enum</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>Giá trị cho phép</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="108" customHeight="1">
-      <c r="A19" s="6" t="n"/>
-      <c r="B19" s="6" t="inlineStr">
-        <is>
-          <t>notificationtype</t>
-        </is>
-      </c>
-      <c r="C19" s="6" t="inlineStr">
-        <is>
-          <t>BATTERY_ALERT, ANOMALY_ALERT, SOH_ALERT, DEVICE_OFFLINE_ALERT, SOS_ALERT, GEOFENCE_ALERT, NO_DRIVER_CHECK_IN_ALERT (dự kiến), OUTSIDE_DRIVER_CHECK_IN (dự kiến)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="27" customHeight="1">
-      <c r="A20" s="6" t="n"/>
-      <c r="B20" s="6" t="inlineStr">
-        <is>
-          <t>notificationseverity</t>
-        </is>
-      </c>
-      <c r="C20" s="6" t="inlineStr">
-        <is>
-          <t>INFO, WARNING, CRITICAL</t>
-        </is>
-      </c>
-    </row>
-    <row r="21"/>
-    <row r="22">
-      <c r="A22" s="4" t="n"/>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>Chỉ mục (index)</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="inlineStr">
-        <is>
-          <t>Các cột</t>
-        </is>
-      </c>
-      <c r="D22" s="4" t="inlineStr">
-        <is>
-          <t>Duy nhất</t>
-        </is>
-      </c>
-      <c r="E22" s="4" t="n"/>
-      <c r="F22" s="4" t="inlineStr">
-        <is>
-          <t>Ghi chú</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="27" customHeight="1">
-      <c r="A23" s="6" t="n"/>
-      <c r="B23" s="6" t="inlineStr">
-        <is>
-          <t>ix_notifications_vehicle_id</t>
-        </is>
-      </c>
-      <c r="C23" s="6" t="inlineStr">
-        <is>
-          <t>vehicle_id</t>
-        </is>
-      </c>
-      <c r="D23" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E23" s="6" t="n"/>
-      <c r="F23" s="6" t="n"/>
-    </row>
-  </sheetData>
-  <autoFilter ref="A6:I16"/>
-  <hyperlinks>
-    <hyperlink ref="A2" location="'Tổng quan'!A1"/>
-    <hyperlink ref="F8" location="'organizations'!A1"/>
-    <hyperlink ref="F11" location="'vehicles'!A1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -31949,6 +32067,548 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:I23"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="7" max="7"/>
+    <col width="42" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>39. notifications: Thông báo</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t>← Tổng quan</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>Miền nghiệp vụ: Thông báo &amp; cảnh báo (notifications)   ·   Chủ sở hữu dữ liệu: Khách hàng   ·   Tính năng: F-A2, F-A3, F-A4, F-J1, F-J3</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>Một cảnh báo (pin, bất thường, SOH, thiết bị mất kết nối...). Một bảng chung; mỗi loại cảnh báo là một giá trị enum và một cấu trúc payload.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5"/>
+    <row r="6" ht="27" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Cột</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Kiểu dữ liệu</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Cho phép rỗng</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>Khóa</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>Tham chiếu tới</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>Ý nghĩa</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>Ví dụ</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>Lưu lịch sử</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="27" customHeight="1">
+      <c r="A7" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>notification_id</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>bigint</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="n"/>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>Mã tự tăng; cũng là con trỏ khi truy vấn thông báo mới (after_id).</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>5821</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="n"/>
+    </row>
+    <row r="8" ht="27" customHeight="1">
+      <c r="A8" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>organization_id</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>uuid</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>organizations.organization_id (khi xóa: chặn xóa)</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>Tổ chức khách hàng được xem thông báo.</t>
+        </is>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>3f6c2a1e-8b4d-4e2a-9c1f-0a7d5b2e4c11</t>
+        </is>
+      </c>
+      <c r="I8" s="6" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>notification_type</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>notificationtype</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="n"/>
+      <c r="F9" s="6" t="n"/>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>Loại sự kiện đã phát sinh thông báo.</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>BATTERY_ALERT</t>
+        </is>
+      </c>
+      <c r="I9" s="6" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>severity</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>notificationseverity</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="n"/>
+      <c r="F10" s="6" t="n"/>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>Mức độ khẩn cấp, độc lập với loại thông báo.</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="I10" s="6" t="n"/>
+    </row>
+    <row r="11" ht="27" customHeight="1">
+      <c r="A11" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>vehicle_id</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>uuid</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>vehicles.vehicle_id (khi xóa: xóa theo)</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>Xe mà thông báo nói tới; NULL với thông báo không liên quan xe.</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>7a4c1e9b-3d2f-4b8a-a6c5-1e0d9f8b7a44</t>
+        </is>
+      </c>
+      <c r="I11" s="6" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>varchar(200)</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="n"/>
+      <c r="F12" s="6" t="n"/>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>Tóm tắt ngắn.</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>Pin còn 20%</t>
+        </is>
+      </c>
+      <c r="I12" s="6" t="n"/>
+    </row>
+    <row r="13" ht="27" customHeight="1">
+      <c r="A13" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>body</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>varchar(500)</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="n"/>
+      <c r="F13" s="6" t="n"/>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>Mô tả chi tiết.</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>Xe 51D-123.45 còn 20% pin. Trạm gần nhất: Trạm sạc G3 Bình Dương (8.4 km).</t>
+        </is>
+      </c>
+      <c r="I13" s="6" t="n"/>
+    </row>
+    <row r="14" ht="40.5" customHeight="1">
+      <c r="A14" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>payload</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>jsonb</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="n"/>
+      <c r="F14" s="6" t="n"/>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>Chi tiết riêng theo loại thông báo, dạng JSON.</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>{"threshold": 20, "soc": 19.8, "nearest_station_id": "4b9d6f3a-2e8c-4a1b-9d5e-7f0c3a8b2d88", "distance_m": 8400}</t>
+        </is>
+      </c>
+      <c r="I14" s="6" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>created_at</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>timestamptz</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="n"/>
+      <c r="F15" s="6" t="n"/>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>Thời điểm phát sinh thông báo.</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-15T08:30:00Z</t>
+        </is>
+      </c>
+      <c r="I15" s="6" t="n"/>
+    </row>
+    <row r="16" ht="27" customHeight="1">
+      <c r="A16" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>read_at</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>timestamptz</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="n"/>
+      <c r="F16" s="6" t="n"/>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>Thời điểm người vận hành đánh dấu đã đọc; NULL nếu chưa đọc.</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="I16" s="6" t="n"/>
+    </row>
+    <row r="17"/>
+    <row r="18">
+      <c r="A18" s="4" t="n"/>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>Kiểu enum</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>Giá trị cho phép</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="108" customHeight="1">
+      <c r="A19" s="6" t="n"/>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>notificationtype</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>BATTERY_ALERT, ANOMALY_ALERT, SOH_ALERT, DEVICE_OFFLINE_ALERT, SOS_ALERT, GEOFENCE_ALERT, NO_DRIVER_CHECK_IN_ALERT (dự kiến), OUTSIDE_DRIVER_CHECK_IN (dự kiến)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="27" customHeight="1">
+      <c r="A20" s="6" t="n"/>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>notificationseverity</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>INFO, WARNING, CRITICAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="21"/>
+    <row r="22">
+      <c r="A22" s="4" t="n"/>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>Chỉ mục (index)</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>Các cột</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>Duy nhất</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="n"/>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>Ghi chú</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="27" customHeight="1">
+      <c r="A23" s="6" t="n"/>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>ix_notifications_vehicle_id</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>vehicle_id</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="n"/>
+      <c r="F23" s="6" t="n"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A6:I16"/>
+  <hyperlinks>
+    <hyperlink ref="A2" location="'Tổng quan'!A1"/>
+    <hyperlink ref="F8" location="'organizations'!A1"/>
+    <hyperlink ref="F11" location="'vehicles'!A1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet51.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:I43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -31966,7 +32626,7 @@
     <row r="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>39. support_cases: Ca hỗ trợ</t>
+          <t>40. support_cases: Ca hỗ trợ</t>
         </is>
       </c>
     </row>
@@ -33049,7 +33709,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet51.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet52.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -33072,7 +33732,7 @@
     <row r="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>40. repair_partners: Đối tác sửa chữa &amp; cứu hộ</t>
+          <t>41. repair_partners: Đối tác sửa chữa &amp; cứu hộ</t>
         </is>
       </c>
     </row>
@@ -33440,7 +34100,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet52.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet53.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -33463,7 +34123,7 @@
     <row r="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>41. maintenance_bookings: Lịch bảo dưỡng</t>
+          <t>42. maintenance_bookings: Lịch bảo dưỡng</t>
         </is>
       </c>
     </row>
@@ -33807,7 +34467,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet53.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet54.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -33830,7 +34490,7 @@
     <row r="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>42. charging_policies: Chính sách sạc</t>
+          <t>43. charging_policies: Chính sách sạc</t>
         </is>
       </c>
     </row>
@@ -34127,7 +34787,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet54.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet55.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -34150,7 +34810,7 @@
     <row r="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>43. charging_policy_versions: Phiên bản chính sách sạc</t>
+          <t>44. charging_policy_versions: Phiên bản chính sách sạc</t>
         </is>
       </c>
     </row>
@@ -34652,415 +35312,6 @@
     <hyperlink ref="F8" location="'charging_policies'!A1"/>
     <hyperlink ref="F16" location="'users'!A1"/>
     <hyperlink ref="B22" location="'policy_violations'!A1"/>
-  </hyperlinks>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet55.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="40" customWidth="1" min="6" max="6"/>
-    <col width="60" customWidth="1" min="7" max="7"/>
-    <col width="42" customWidth="1" min="8" max="8"/>
-    <col width="11" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="9" t="inlineStr">
-        <is>
-          <t>44. charging_policy_assignments: Áp dụng chính sách sạc</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="10" t="inlineStr">
-        <is>
-          <t>← Tổng quan</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>Miền nghiệp vụ: Chính sách sạc (bảo hành) (policy)   ·   Chủ sở hữu dữ liệu: Khách hàng   ·   Tính năng: F-B1</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="11" t="inlineStr">
-        <is>
-          <t>Chính sách nào áp dụng cho một xe, một đội xe hay một dòng xe.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5"/>
-    <row r="6" ht="27" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>Cột</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>Kiểu dữ liệu</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>Cho phép rỗng</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>Khóa</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>Tham chiếu tới</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>Ý nghĩa</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>Ví dụ</t>
-        </is>
-      </c>
-      <c r="I6" s="4" t="inlineStr">
-        <is>
-          <t>Lưu lịch sử</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>assignment_id</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>uuid</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
-      <c r="F7" s="6" t="n"/>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>Mã nội bộ của lần áp dụng.</t>
-        </is>
-      </c>
-      <c r="H7" s="6" t="inlineStr">
-        <is>
-          <t>0000000e-5a6b-4c7d-8e9f-0a1b2c3d4e5f</t>
-        </is>
-      </c>
-      <c r="I7" s="6" t="n"/>
-    </row>
-    <row r="8" ht="27" customHeight="1">
-      <c r="A8" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>organization_id</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>uuid</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E8" s="6" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="F8" s="7" t="inlineStr">
-        <is>
-          <t>organizations.organization_id (khi xóa: chặn xóa)</t>
-        </is>
-      </c>
-      <c r="G8" s="6" t="inlineStr">
-        <is>
-          <t>Tổ chức khách hàng của lần áp dụng.</t>
-        </is>
-      </c>
-      <c r="H8" s="6" t="inlineStr">
-        <is>
-          <t>3f6c2a1e-8b4d-4e2a-9c1f-0a7d5b2e4c11</t>
-        </is>
-      </c>
-      <c r="I8" s="6" t="n"/>
-    </row>
-    <row r="9" ht="27" customHeight="1">
-      <c r="A9" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>policy_id</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>uuid</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E9" s="6" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="F9" s="7" t="inlineStr">
-        <is>
-          <t>charging_policies.policy_id (khi xóa: chặn xóa)</t>
-        </is>
-      </c>
-      <c r="G9" s="6" t="inlineStr">
-        <is>
-          <t>Chính sách được áp dụng.</t>
-        </is>
-      </c>
-      <c r="H9" s="6" t="inlineStr">
-        <is>
-          <t>b8e5a2d9-3c6f-4b1e-a9d7-5f2c0e8b1aee</t>
-        </is>
-      </c>
-      <c r="I9" s="6" t="n"/>
-    </row>
-    <row r="10" ht="27" customHeight="1">
-      <c r="A10" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>vehicle_id</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>uuid</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>có</t>
-        </is>
-      </c>
-      <c r="E10" s="6" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="F10" s="7" t="inlineStr">
-        <is>
-          <t>vehicles.vehicle_id (khi xóa: chặn xóa)</t>
-        </is>
-      </c>
-      <c r="G10" s="6" t="inlineStr">
-        <is>
-          <t>Xe được áp dụng, nếu phạm vi là một xe. Chỉ đúng một trong vehicle_id / fleet_id / vehicle_model có giá trị.</t>
-        </is>
-      </c>
-      <c r="H10" s="6" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="I10" s="6" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>fleet_id</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>uuid</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>có</t>
-        </is>
-      </c>
-      <c r="E11" s="6" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="F11" s="7" t="inlineStr">
-        <is>
-          <t>fleets.fleet_id (khi xóa: chặn xóa)</t>
-        </is>
-      </c>
-      <c r="G11" s="6" t="inlineStr">
-        <is>
-          <t>Đội xe được áp dụng, nếu phạm vi là một đội.</t>
-        </is>
-      </c>
-      <c r="H11" s="6" t="inlineStr">
-        <is>
-          <t>8d5f2b7e-1a9c-4f3d-b8e2-6c0a4d9f1e77</t>
-        </is>
-      </c>
-      <c r="I11" s="6" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>vehicle_model</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>varchar(50)</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>có</t>
-        </is>
-      </c>
-      <c r="E12" s="6" t="n"/>
-      <c r="F12" s="6" t="n"/>
-      <c r="G12" s="6" t="inlineStr">
-        <is>
-          <t>Dòng xe được áp dụng, nếu phạm vi là một dòng xe.</t>
-        </is>
-      </c>
-      <c r="H12" s="6" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="I12" s="6" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>assigned_at</t>
-        </is>
-      </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>timestamptz</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E13" s="6" t="n"/>
-      <c r="F13" s="6" t="n"/>
-      <c r="G13" s="6" t="inlineStr">
-        <is>
-          <t>Thời điểm bắt đầu áp dụng.</t>
-        </is>
-      </c>
-      <c r="H13" s="6" t="inlineStr">
-        <is>
-          <t>2026-10-01T00:00:00Z</t>
-        </is>
-      </c>
-      <c r="I13" s="6" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="B14" s="6" t="inlineStr">
-        <is>
-          <t>unassigned_at</t>
-        </is>
-      </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>timestamptz</t>
-        </is>
-      </c>
-      <c r="D14" s="6" t="inlineStr">
-        <is>
-          <t>có</t>
-        </is>
-      </c>
-      <c r="E14" s="6" t="n"/>
-      <c r="F14" s="6" t="n"/>
-      <c r="G14" s="6" t="inlineStr">
-        <is>
-          <t>Thời điểm kết thúc; NULL khi còn hiệu lực.</t>
-        </is>
-      </c>
-      <c r="H14" s="6" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="I14" s="6" t="n"/>
-    </row>
-  </sheetData>
-  <autoFilter ref="A6:I14"/>
-  <hyperlinks>
-    <hyperlink ref="A2" location="'Tổng quan'!A1"/>
-    <hyperlink ref="F8" location="'organizations'!A1"/>
-    <hyperlink ref="F9" location="'charging_policies'!A1"/>
-    <hyperlink ref="F10" location="'vehicles'!A1"/>
-    <hyperlink ref="F11" location="'fleets'!A1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -35089,7 +35340,7 @@
     <row r="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>45. policy_violations: Vi phạm chính sách sạc</t>
+          <t>45. charging_policy_assignments: Áp dụng chính sách sạc</t>
         </is>
       </c>
     </row>
@@ -35103,14 +35354,14 @@
     <row r="3">
       <c r="A3" s="11" t="inlineStr">
         <is>
-          <t>Miền nghiệp vụ: Chính sách sạc (bảo hành) (policy)   ·   Chủ sở hữu dữ liệu: Khách hàng   ·   Tính năng: F-B3, F-B6</t>
+          <t>Miền nghiệp vụ: Chính sách sạc (bảo hành) (policy)   ·   Chủ sở hữu dữ liệu: Khách hàng   ·   Tính năng: F-B1</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="11" t="inlineStr">
         <is>
-          <t>Một phiên sạc vi phạm chính sách, kèm bằng chứng. Hệ quả của vi phạm vẫn là câu hỏi kinh doanh còn mở (mục 3 của feature-list).</t>
+          <t>Chính sách nào áp dụng cho một xe, một đội xe hay một dòng xe.</t>
         </is>
       </c>
     </row>
@@ -35168,7 +35419,7 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>violation_id</t>
+          <t>assignment_id</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
@@ -35189,12 +35440,12 @@
       <c r="F7" s="6" t="n"/>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>Mã nội bộ của vi phạm.</t>
+          <t>Mã nội bộ của lần áp dụng.</t>
         </is>
       </c>
       <c r="H7" s="6" t="inlineStr">
         <is>
-          <t>0000000f-5a6b-4c7d-8e9f-0a1b2c3d4e5f</t>
+          <t>0000000e-5a6b-4c7d-8e9f-0a1b2c3d4e5f</t>
         </is>
       </c>
       <c r="I7" s="6" t="n"/>
@@ -35230,7 +35481,7 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>Tổ chức khách hàng sở hữu xe.</t>
+          <t>Tổ chức khách hàng của lần áp dụng.</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr">
@@ -35246,7 +35497,7 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>session_id</t>
+          <t>policy_id</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
@@ -35266,17 +35517,17 @@
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>charging_sessions.session_id (khi xóa: chặn xóa)</t>
+          <t>charging_policies.policy_id (khi xóa: chặn xóa)</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>Phiên sạc đã vi phạm chính sách.</t>
+          <t>Chính sách được áp dụng.</t>
         </is>
       </c>
       <c r="H9" s="6" t="inlineStr">
         <is>
-          <t>e5a2d8f1-4b7c-4e9a-b3d6-2c1f0e9a8dbb</t>
+          <t>b8e5a2d9-3c6f-4b1e-a9d7-5f2c0e8b1aee</t>
         </is>
       </c>
       <c r="I9" s="6" t="n"/>
@@ -35297,7 +35548,7 @@
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>không</t>
+          <t>có</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
@@ -35312,23 +35563,23 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>Xe liên quan.</t>
+          <t>Xe được áp dụng, nếu phạm vi là một xe. Chỉ đúng một trong vehicle_id / fleet_id / vehicle_model có giá trị.</t>
         </is>
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>7a4c1e9b-3d2f-4b8a-a6c5-1e0d9f8b7a44</t>
+          <t>NULL</t>
         </is>
       </c>
       <c r="I10" s="6" t="n"/>
     </row>
-    <row r="11" ht="27" customHeight="1">
+    <row r="11">
       <c r="A11" s="6" t="n">
         <v>5</v>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>policy_version_id</t>
+          <t>fleet_id</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
@@ -35338,7 +35589,7 @@
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>không</t>
+          <t>có</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
@@ -35348,17 +35599,17 @@
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>charging_policy_versions.version_id (khi xóa: chặn xóa)</t>
+          <t>fleets.fleet_id (khi xóa: chặn xóa)</t>
         </is>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>Đúng phiên bản chính sách bị vi phạm.</t>
+          <t>Đội xe được áp dụng, nếu phạm vi là một đội.</t>
         </is>
       </c>
       <c r="H11" s="6" t="inlineStr">
         <is>
-          <t>c7d4f1a8-2b5e-4c9d-8f6a-1e3b0d7c4aff</t>
+          <t>8d5f2b7e-1a9c-4f3d-b8e2-6c0a4d9f1e77</t>
         </is>
       </c>
       <c r="I11" s="6" t="n"/>
@@ -35369,29 +35620,29 @@
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>violation_type</t>
+          <t>vehicle_model</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>varchar(30)</t>
+          <t>varchar(50)</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>không</t>
+          <t>có</t>
         </is>
       </c>
       <c r="E12" s="6" t="n"/>
       <c r="F12" s="6" t="n"/>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>Quy tắc nào bị vi phạm.</t>
+          <t>Dòng xe được áp dụng, nếu phạm vi là một dòng xe.</t>
         </is>
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>SOC_ABOVE_MAX</t>
+          <t>NULL</t>
         </is>
       </c>
       <c r="I12" s="6" t="n"/>
@@ -35402,7 +35653,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>detected_at</t>
+          <t>assigned_at</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
@@ -35419,45 +35670,45 @@
       <c r="F13" s="6" t="n"/>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>Thời điểm phát hiện vi phạm.</t>
+          <t>Thời điểm bắt đầu áp dụng.</t>
         </is>
       </c>
       <c r="H13" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15T09:45:00Z</t>
+          <t>2026-10-01T00:00:00Z</t>
         </is>
       </c>
       <c r="I13" s="6" t="n"/>
     </row>
-    <row r="14" ht="27" customHeight="1">
+    <row r="14">
       <c r="A14" s="6" t="n">
         <v>8</v>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>evidence</t>
+          <t>unassigned_at</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>jsonb</t>
+          <t>timestamptz</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>không</t>
+          <t>có</t>
         </is>
       </c>
       <c r="E14" s="6" t="n"/>
       <c r="F14" s="6" t="n"/>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>Ảnh chụp dữ liệu chứng minh vi phạm, dạng JSON.</t>
+          <t>Thời điểm kết thúc; NULL khi còn hiệu lực.</t>
         </is>
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
-          <t>{"soc_end": 98.5, "soc_max": 90, "meter_stop_wh": 1712860}</t>
+          <t>NULL</t>
         </is>
       </c>
       <c r="I14" s="6" t="n"/>
@@ -35467,9 +35718,9 @@
   <hyperlinks>
     <hyperlink ref="A2" location="'Tổng quan'!A1"/>
     <hyperlink ref="F8" location="'organizations'!A1"/>
-    <hyperlink ref="F9" location="'charging_sessions'!A1"/>
+    <hyperlink ref="F9" location="'charging_policies'!A1"/>
     <hyperlink ref="F10" location="'vehicles'!A1"/>
-    <hyperlink ref="F11" location="'charging_policy_versions'!A1"/>
+    <hyperlink ref="F11" location="'fleets'!A1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -35498,7 +35749,416 @@
     <row r="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>46. tariffs: Biểu giá điện</t>
+          <t>46. policy_violations: Vi phạm chính sách sạc</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t>← Tổng quan</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>Miền nghiệp vụ: Chính sách sạc (bảo hành) (policy)   ·   Chủ sở hữu dữ liệu: Khách hàng   ·   Tính năng: F-B3, F-B6</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>Một phiên sạc vi phạm chính sách, kèm bằng chứng. Hệ quả của vi phạm vẫn là câu hỏi kinh doanh còn mở (mục 3 của feature-list).</t>
+        </is>
+      </c>
+    </row>
+    <row r="5"/>
+    <row r="6" ht="27" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Cột</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Kiểu dữ liệu</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Cho phép rỗng</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>Khóa</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>Tham chiếu tới</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>Ý nghĩa</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>Ví dụ</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>Lưu lịch sử</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>violation_id</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>uuid</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="n"/>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>Mã nội bộ của vi phạm.</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>0000000f-5a6b-4c7d-8e9f-0a1b2c3d4e5f</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="n"/>
+    </row>
+    <row r="8" ht="27" customHeight="1">
+      <c r="A8" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>organization_id</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>uuid</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>organizations.organization_id (khi xóa: chặn xóa)</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>Tổ chức khách hàng sở hữu xe.</t>
+        </is>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>3f6c2a1e-8b4d-4e2a-9c1f-0a7d5b2e4c11</t>
+        </is>
+      </c>
+      <c r="I8" s="6" t="n"/>
+    </row>
+    <row r="9" ht="27" customHeight="1">
+      <c r="A9" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>session_id</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>uuid</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>charging_sessions.session_id (khi xóa: chặn xóa)</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>Phiên sạc đã vi phạm chính sách.</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>e5a2d8f1-4b7c-4e9a-b3d6-2c1f0e9a8dbb</t>
+        </is>
+      </c>
+      <c r="I9" s="6" t="n"/>
+    </row>
+    <row r="10" ht="27" customHeight="1">
+      <c r="A10" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>vehicle_id</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>uuid</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>vehicles.vehicle_id (khi xóa: chặn xóa)</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>Xe liên quan.</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>7a4c1e9b-3d2f-4b8a-a6c5-1e0d9f8b7a44</t>
+        </is>
+      </c>
+      <c r="I10" s="6" t="n"/>
+    </row>
+    <row r="11" ht="27" customHeight="1">
+      <c r="A11" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>policy_version_id</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>uuid</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>charging_policy_versions.version_id (khi xóa: chặn xóa)</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>Đúng phiên bản chính sách bị vi phạm.</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>c7d4f1a8-2b5e-4c9d-8f6a-1e3b0d7c4aff</t>
+        </is>
+      </c>
+      <c r="I11" s="6" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>violation_type</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>varchar(30)</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="n"/>
+      <c r="F12" s="6" t="n"/>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>Quy tắc nào bị vi phạm.</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>SOC_ABOVE_MAX</t>
+        </is>
+      </c>
+      <c r="I12" s="6" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>detected_at</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>timestamptz</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="n"/>
+      <c r="F13" s="6" t="n"/>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>Thời điểm phát hiện vi phạm.</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-15T09:45:00Z</t>
+        </is>
+      </c>
+      <c r="I13" s="6" t="n"/>
+    </row>
+    <row r="14" ht="27" customHeight="1">
+      <c r="A14" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>jsonb</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="n"/>
+      <c r="F14" s="6" t="n"/>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>Ảnh chụp dữ liệu chứng minh vi phạm, dạng JSON.</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>{"soc_end": 98.5, "soc_max": 90, "meter_stop_wh": 1712860}</t>
+        </is>
+      </c>
+      <c r="I14" s="6" t="n"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A6:I14"/>
+  <hyperlinks>
+    <hyperlink ref="A2" location="'Tổng quan'!A1"/>
+    <hyperlink ref="F8" location="'organizations'!A1"/>
+    <hyperlink ref="F9" location="'charging_sessions'!A1"/>
+    <hyperlink ref="F10" location="'vehicles'!A1"/>
+    <hyperlink ref="F11" location="'charging_policy_versions'!A1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet58.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="7" max="7"/>
+    <col width="42" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>47. tariffs: Biểu giá điện</t>
         </is>
       </c>
     </row>
@@ -35857,7 +36517,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet58.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet59.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -35880,7 +36540,7 @@
     <row r="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>47. payments: Thanh toán</t>
+          <t>48. payments: Thanh toán</t>
         </is>
       </c>
     </row>
@@ -36337,359 +36997,6 @@
     <hyperlink ref="F8" location="'organizations'!A1"/>
     <hyperlink ref="F9" location="'charging_sessions'!A1"/>
     <hyperlink ref="B19" location="'wallet_transactions'!A1"/>
-  </hyperlinks>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet59.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I15"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="40" customWidth="1" min="6" max="6"/>
-    <col width="60" customWidth="1" min="7" max="7"/>
-    <col width="42" customWidth="1" min="8" max="8"/>
-    <col width="11" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="9" t="inlineStr">
-        <is>
-          <t>48. wallets: Ví</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="10" t="inlineStr">
-        <is>
-          <t>← Tổng quan</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>Miền nghiệp vụ: Thanh toán &amp; hóa đơn (billing)   ·   Chủ sở hữu dữ liệu: Khách hàng   ·   Tính năng: F-H2</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="11" t="inlineStr">
-        <is>
-          <t>Số dư trả trước của một tài xế hoặc của cả tổ chức.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5"/>
-    <row r="6" ht="27" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>Cột</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>Kiểu dữ liệu</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>Cho phép rỗng</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>Khóa</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>Tham chiếu tới</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>Ý nghĩa</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>Ví dụ</t>
-        </is>
-      </c>
-      <c r="I6" s="4" t="inlineStr">
-        <is>
-          <t>Lưu lịch sử</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>wallet_id</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>uuid</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
-      <c r="F7" s="6" t="n"/>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>Mã nội bộ của ví.</t>
-        </is>
-      </c>
-      <c r="H7" s="6" t="inlineStr">
-        <is>
-          <t>5c3a0e7d-2f9b-4c1e-a8d3-7b6f0c2e9a32</t>
-        </is>
-      </c>
-      <c r="I7" s="6" t="n"/>
-    </row>
-    <row r="8" ht="27" customHeight="1">
-      <c r="A8" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>organization_id</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>uuid</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E8" s="6" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="F8" s="7" t="inlineStr">
-        <is>
-          <t>organizations.organization_id (khi xóa: chặn xóa)</t>
-        </is>
-      </c>
-      <c r="G8" s="6" t="inlineStr">
-        <is>
-          <t>Tổ chức khách hàng sở hữu ví.</t>
-        </is>
-      </c>
-      <c r="H8" s="6" t="inlineStr">
-        <is>
-          <t>3f6c2a1e-8b4d-4e2a-9c1f-0a7d5b2e4c11</t>
-        </is>
-      </c>
-      <c r="I8" s="6" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>driver_id</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>uuid</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>có</t>
-        </is>
-      </c>
-      <c r="E9" s="6" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="F9" s="7" t="inlineStr">
-        <is>
-          <t>drivers.driver_id (khi xóa: chặn xóa)</t>
-        </is>
-      </c>
-      <c r="G9" s="6" t="inlineStr">
-        <is>
-          <t>Tài xế sở hữu ví; NULL với ví cấp tổ chức (quyết định D5).</t>
-        </is>
-      </c>
-      <c r="H9" s="6" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="I9" s="6" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>balance</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>numeric(14,2)</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E10" s="6" t="n"/>
-      <c r="F10" s="6" t="n"/>
-      <c r="G10" s="6" t="inlineStr">
-        <is>
-          <t>Số dư hiện tại; phải bằng tổng các giao dịch của ví.</t>
-        </is>
-      </c>
-      <c r="H10" s="6" t="inlineStr">
-        <is>
-          <t>12500000.00</t>
-        </is>
-      </c>
-      <c r="I10" s="6" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>currency</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>char(3)</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E11" s="6" t="n"/>
-      <c r="F11" s="6" t="n"/>
-      <c r="G11" s="6" t="inlineStr">
-        <is>
-          <t>Mã tiền tệ ISO 4217.</t>
-        </is>
-      </c>
-      <c r="H11" s="6" t="inlineStr">
-        <is>
-          <t>VND</t>
-        </is>
-      </c>
-      <c r="I11" s="6" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>varchar(20)</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E12" s="6" t="n"/>
-      <c r="F12" s="6" t="n"/>
-      <c r="G12" s="6" t="inlineStr">
-        <is>
-          <t>Ví có dùng được không.</t>
-        </is>
-      </c>
-      <c r="H12" s="6" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="I12" s="6" t="n"/>
-    </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" s="4" t="n"/>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>Được tham chiếu bởi bảng</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>Cột</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="6" t="n"/>
-      <c r="B15" s="7" t="inlineStr">
-        <is>
-          <t>wallet_transactions</t>
-        </is>
-      </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>wallet_id</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A6:I12"/>
-  <hyperlinks>
-    <hyperlink ref="A2" location="'Tổng quan'!A1"/>
-    <hyperlink ref="F8" location="'organizations'!A1"/>
-    <hyperlink ref="F9" location="'drivers'!A1"/>
-    <hyperlink ref="B15" location="'wallet_transactions'!A1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -37047,7 +37354,360 @@
     <row r="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>49. wallet_transactions: Giao dịch ví</t>
+          <t>49. wallets: Ví</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t>← Tổng quan</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>Miền nghiệp vụ: Thanh toán &amp; hóa đơn (billing)   ·   Chủ sở hữu dữ liệu: Khách hàng   ·   Tính năng: F-H2</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>Số dư trả trước của một tài xế hoặc của cả tổ chức.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5"/>
+    <row r="6" ht="27" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Cột</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Kiểu dữ liệu</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Cho phép rỗng</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>Khóa</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>Tham chiếu tới</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>Ý nghĩa</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>Ví dụ</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>Lưu lịch sử</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>wallet_id</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>uuid</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="n"/>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>Mã nội bộ của ví.</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>5c3a0e7d-2f9b-4c1e-a8d3-7b6f0c2e9a32</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="n"/>
+    </row>
+    <row r="8" ht="27" customHeight="1">
+      <c r="A8" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>organization_id</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>uuid</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>organizations.organization_id (khi xóa: chặn xóa)</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>Tổ chức khách hàng sở hữu ví.</t>
+        </is>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>3f6c2a1e-8b4d-4e2a-9c1f-0a7d5b2e4c11</t>
+        </is>
+      </c>
+      <c r="I8" s="6" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>driver_id</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>uuid</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>drivers.driver_id (khi xóa: chặn xóa)</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>Tài xế sở hữu ví; NULL với ví cấp tổ chức (quyết định D5).</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="I9" s="6" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>balance</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>numeric(14,2)</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="n"/>
+      <c r="F10" s="6" t="n"/>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>Số dư hiện tại; phải bằng tổng các giao dịch của ví.</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>12500000.00</t>
+        </is>
+      </c>
+      <c r="I10" s="6" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>currency</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>char(3)</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="n"/>
+      <c r="F11" s="6" t="n"/>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>Mã tiền tệ ISO 4217.</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="I11" s="6" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>varchar(20)</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="n"/>
+      <c r="F12" s="6" t="n"/>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>Ví có dùng được không.</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="I12" s="6" t="n"/>
+    </row>
+    <row r="13"/>
+    <row r="14">
+      <c r="A14" s="4" t="n"/>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>Được tham chiếu bởi bảng</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>Cột</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="n"/>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>wallet_transactions</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>wallet_id</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A6:I12"/>
+  <hyperlinks>
+    <hyperlink ref="A2" location="'Tổng quan'!A1"/>
+    <hyperlink ref="F8" location="'organizations'!A1"/>
+    <hyperlink ref="F9" location="'drivers'!A1"/>
+    <hyperlink ref="B15" location="'wallet_transactions'!A1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet61.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="7" max="7"/>
+    <col width="42" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>50. wallet_transactions: Giao dịch ví</t>
         </is>
       </c>
     </row>
@@ -37466,7 +38126,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet61.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet62.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -37489,7 +38149,7 @@
     <row r="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>50. invoices: Hóa đơn</t>
+          <t>51. invoices: Hóa đơn</t>
         </is>
       </c>
     </row>
@@ -37942,7 +38602,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet62.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet63.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -37965,7 +38625,7 @@
     <row r="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>51. invoice_lines: Dòng hóa đơn</t>
+          <t>52. invoice_lines: Dòng hóa đơn</t>
         </is>
       </c>
     </row>
@@ -38384,7 +39044,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet63.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet64.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -38407,7 +39067,7 @@
     <row r="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>52. subscription_plans: Gói dịch vụ</t>
+          <t>53. subscription_plans: Gói dịch vụ</t>
         </is>
       </c>
     </row>
@@ -38770,7 +39430,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet64.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet65.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -38793,7 +39453,7 @@
     <row r="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>53. plan_features: Tính năng của gói dịch vụ</t>
+          <t>54. plan_features: Tính năng của gói dịch vụ</t>
         </is>
       </c>
     </row>
@@ -39060,401 +39720,6 @@
   <hyperlinks>
     <hyperlink ref="A2" location="'Tổng quan'!A1"/>
     <hyperlink ref="F8" location="'subscription_plans'!A1"/>
-  </hyperlinks>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet65.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I16"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="40" customWidth="1" min="6" max="6"/>
-    <col width="60" customWidth="1" min="7" max="7"/>
-    <col width="42" customWidth="1" min="8" max="8"/>
-    <col width="11" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="9" t="inlineStr">
-        <is>
-          <t>54. subscriptions: Thuê bao</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="10" t="inlineStr">
-        <is>
-          <t>← Tổng quan</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>Miền nghiệp vụ: Thanh toán &amp; hóa đơn (billing)   ·   Chủ sở hữu dữ liệu: Khách hàng   ·   Tính năng: F-H4</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="11" t="inlineStr">
-        <is>
-          <t>Một xe đăng ký một gói; quá hạn thanh toán sẽ khóa tính năng.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5"/>
-    <row r="6" ht="27" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>Cột</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>Kiểu dữ liệu</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>Cho phép rỗng</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>Khóa</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>Tham chiếu tới</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>Ý nghĩa</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>Ví dụ</t>
-        </is>
-      </c>
-      <c r="I6" s="4" t="inlineStr">
-        <is>
-          <t>Lưu lịch sử</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>subscription_id</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>uuid</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
-      <c r="F7" s="6" t="n"/>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>Mã nội bộ của thuê bao.</t>
-        </is>
-      </c>
-      <c r="H7" s="6" t="inlineStr">
-        <is>
-          <t>9a7e4c1b-6d3f-4a5c-b0e8-2f1d7c9b3e54</t>
-        </is>
-      </c>
-      <c r="I7" s="6" t="n"/>
-    </row>
-    <row r="8" ht="27" customHeight="1">
-      <c r="A8" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>organization_id</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>uuid</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E8" s="6" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="F8" s="7" t="inlineStr">
-        <is>
-          <t>organizations.organization_id (khi xóa: chặn xóa)</t>
-        </is>
-      </c>
-      <c r="G8" s="6" t="inlineStr">
-        <is>
-          <t>Tổ chức khách hàng đăng ký.</t>
-        </is>
-      </c>
-      <c r="H8" s="6" t="inlineStr">
-        <is>
-          <t>3f6c2a1e-8b4d-4e2a-9c1f-0a7d5b2e4c11</t>
-        </is>
-      </c>
-      <c r="I8" s="6" t="n"/>
-    </row>
-    <row r="9" ht="27" customHeight="1">
-      <c r="A9" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>plan_id</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>uuid</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E9" s="6" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="F9" s="7" t="inlineStr">
-        <is>
-          <t>subscription_plans.plan_id (khi xóa: chặn xóa)</t>
-        </is>
-      </c>
-      <c r="G9" s="6" t="inlineStr">
-        <is>
-          <t>Gói được đăng ký.</t>
-        </is>
-      </c>
-      <c r="H9" s="6" t="inlineStr">
-        <is>
-          <t>0c9a6e3d-8f5b-4c7e-a2d1-4b3f9e6c0a65</t>
-        </is>
-      </c>
-      <c r="I9" s="6" t="n"/>
-    </row>
-    <row r="10" ht="27" customHeight="1">
-      <c r="A10" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>vehicle_id</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>uuid</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E10" s="6" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="F10" s="7" t="inlineStr">
-        <is>
-          <t>vehicles.vehicle_id (khi xóa: chặn xóa)</t>
-        </is>
-      </c>
-      <c r="G10" s="6" t="inlineStr">
-        <is>
-          <t>Xe được áp dụng.</t>
-        </is>
-      </c>
-      <c r="H10" s="6" t="inlineStr">
-        <is>
-          <t>7a4c1e9b-3d2f-4b8a-a6c5-1e0d9f8b7a44</t>
-        </is>
-      </c>
-      <c r="I10" s="6" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>started_at</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>timestamptz</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E11" s="6" t="n"/>
-      <c r="F11" s="6" t="n"/>
-      <c r="G11" s="6" t="inlineStr">
-        <is>
-          <t>Thời điểm bắt đầu thuê bao.</t>
-        </is>
-      </c>
-      <c r="H11" s="6" t="inlineStr">
-        <is>
-          <t>2026-09-01T00:00:00Z</t>
-        </is>
-      </c>
-      <c r="I11" s="6" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>ends_at</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>timestamptz</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>có</t>
-        </is>
-      </c>
-      <c r="E12" s="6" t="n"/>
-      <c r="F12" s="6" t="n"/>
-      <c r="G12" s="6" t="inlineStr">
-        <is>
-          <t>Thời điểm kết thúc; NULL nếu tự gia hạn cho tới khi hủy.</t>
-        </is>
-      </c>
-      <c r="H12" s="6" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="I12" s="6" t="n"/>
-    </row>
-    <row r="13" ht="27" customHeight="1">
-      <c r="A13" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>varchar(20)</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E13" s="6" t="n"/>
-      <c r="F13" s="6" t="n"/>
-      <c r="G13" s="6" t="inlineStr">
-        <is>
-          <t>Trạng thái thuê bao; OVERDUE sẽ khóa các tính năng trả phí. Giá trị: ACTIVE | OVERDUE | EXPIRED | CANCELLED.</t>
-        </is>
-      </c>
-      <c r="H13" s="6" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="I13" s="6" t="n"/>
-    </row>
-    <row r="14"/>
-    <row r="15">
-      <c r="A15" s="4" t="n"/>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>Được tham chiếu bởi bảng</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>Cột</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="6" t="n"/>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>invoice_lines</t>
-        </is>
-      </c>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>subscription_id</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A6:I13"/>
-  <hyperlinks>
-    <hyperlink ref="A2" location="'Tổng quan'!A1"/>
-    <hyperlink ref="F8" location="'organizations'!A1"/>
-    <hyperlink ref="F9" location="'subscription_plans'!A1"/>
-    <hyperlink ref="F10" location="'vehicles'!A1"/>
-    <hyperlink ref="B16" location="'invoice_lines'!A1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -39483,7 +39748,402 @@
     <row r="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>55. driver_scores: Điểm tài xế</t>
+          <t>55. subscriptions: Thuê bao</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t>← Tổng quan</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>Miền nghiệp vụ: Thanh toán &amp; hóa đơn (billing)   ·   Chủ sở hữu dữ liệu: Khách hàng   ·   Tính năng: F-H4</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>Một xe đăng ký một gói; quá hạn thanh toán sẽ khóa tính năng.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5"/>
+    <row r="6" ht="27" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Cột</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Kiểu dữ liệu</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Cho phép rỗng</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>Khóa</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>Tham chiếu tới</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>Ý nghĩa</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>Ví dụ</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>Lưu lịch sử</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>subscription_id</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>uuid</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="n"/>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>Mã nội bộ của thuê bao.</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>9a7e4c1b-6d3f-4a5c-b0e8-2f1d7c9b3e54</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="n"/>
+    </row>
+    <row r="8" ht="27" customHeight="1">
+      <c r="A8" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>organization_id</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>uuid</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>organizations.organization_id (khi xóa: chặn xóa)</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>Tổ chức khách hàng đăng ký.</t>
+        </is>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>3f6c2a1e-8b4d-4e2a-9c1f-0a7d5b2e4c11</t>
+        </is>
+      </c>
+      <c r="I8" s="6" t="n"/>
+    </row>
+    <row r="9" ht="27" customHeight="1">
+      <c r="A9" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>plan_id</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>uuid</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>subscription_plans.plan_id (khi xóa: chặn xóa)</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>Gói được đăng ký.</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>0c9a6e3d-8f5b-4c7e-a2d1-4b3f9e6c0a65</t>
+        </is>
+      </c>
+      <c r="I9" s="6" t="n"/>
+    </row>
+    <row r="10" ht="27" customHeight="1">
+      <c r="A10" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>vehicle_id</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>uuid</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>vehicles.vehicle_id (khi xóa: chặn xóa)</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>Xe được áp dụng.</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>7a4c1e9b-3d2f-4b8a-a6c5-1e0d9f8b7a44</t>
+        </is>
+      </c>
+      <c r="I10" s="6" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>started_at</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>timestamptz</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="n"/>
+      <c r="F11" s="6" t="n"/>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>Thời điểm bắt đầu thuê bao.</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="I11" s="6" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>ends_at</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>timestamptz</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="n"/>
+      <c r="F12" s="6" t="n"/>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>Thời điểm kết thúc; NULL nếu tự gia hạn cho tới khi hủy.</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="I12" s="6" t="n"/>
+    </row>
+    <row r="13" ht="27" customHeight="1">
+      <c r="A13" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>varchar(20)</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="n"/>
+      <c r="F13" s="6" t="n"/>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>Trạng thái thuê bao; OVERDUE sẽ khóa các tính năng trả phí. Giá trị: ACTIVE | OVERDUE | EXPIRED | CANCELLED.</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="I13" s="6" t="n"/>
+    </row>
+    <row r="14"/>
+    <row r="15">
+      <c r="A15" s="4" t="n"/>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>Được tham chiếu bởi bảng</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>Cột</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="n"/>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>invoice_lines</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>subscription_id</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A6:I13"/>
+  <hyperlinks>
+    <hyperlink ref="A2" location="'Tổng quan'!A1"/>
+    <hyperlink ref="F8" location="'organizations'!A1"/>
+    <hyperlink ref="F9" location="'subscription_plans'!A1"/>
+    <hyperlink ref="F10" location="'vehicles'!A1"/>
+    <hyperlink ref="B16" location="'invoice_lines'!A1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet67.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="7" max="7"/>
+    <col width="42" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>56. driver_scores: Điểm tài xế</t>
         </is>
       </c>
     </row>
@@ -39863,7 +40523,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet67.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet68.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -39886,7 +40546,7 @@
     <row r="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>56. promotion_campaigns: Chiến dịch khuyến mãi</t>
+          <t>57. promotion_campaigns: Chiến dịch khuyến mãi</t>
         </is>
       </c>
     </row>
@@ -40170,7 +40830,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet68.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet69.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -40193,7 +40853,7 @@
     <row r="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>57. trips: Chuyến đi</t>
+          <t>58. trips: Chuyến đi</t>
         </is>
       </c>
     </row>

--- a/docs/design/domain-model/domain-model.xlsx
+++ b/docs/design/domain-model/domain-model.xlsx
@@ -8435,7 +8435,7 @@
       <c r="F11" s="6" t="n"/>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>Biển số đăng ký. Xe chỉ được đăng ký vào hệ thống khi đã có biển số. Sửa được: biển số định danh theo chủ xe (Thông tư 24/2023/TT-BCA), nên xe sang tên sẽ có biển mới và biển cũ có thể xuất hiện lại trên xe khác; lịch sử thay đổi lưu các biển trước đó. Duy nhất trong các xe chưa xóa và chưa DECOMMISSIONED.</t>
+          <t>Biển số đăng ký. Xe chỉ được đăng ký vào hệ thống khi đã có biển số. Sửa được: biển số định danh theo chủ xe (Thông tư 24/2023/TT-BCA), nên xe sang tên sẽ có biển mới và biển cũ có thể xuất hiện lại trên xe khác; lịch sử thay đổi lưu các biển trước đó. Duy nhất trong các xe chưa xóa, nên biển số của xe đã rời hệ thống có thể chuyển sang xe khác.</t>
         </is>
       </c>
       <c r="H11" s="6" t="inlineStr">
@@ -8657,7 +8657,7 @@
       <c r="F17" s="6" t="n"/>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>Trạng thái phục vụ, do con người đặt hoặc do quy tắc nghiệp vụ thay mặt công ty, ví dụ trở lại ACTIVE khi hồ sơ sửa chữa được đóng (VH-05, VH-17). ACTIVE: đang phục vụ. MAINTENANCE: đang bảo dưỡng hoặc sửa chữa. DECOMMISSIONED: đã rời hệ thống (thanh lý, bán ra ngoài dịch vụ, hoặc ngừng sử dụng vĩnh viễn); giữ lại cho lịch sử và báo cáo, không nhận dữ liệu mới. Xe đang nhàn rỗi hay không gửi dữ liệu thì không lưu: được tính từ dữ liệu vận hành và T-Box.</t>
+          <t>Trạng thái phục vụ, do con người hoặc quy tắc nghiệp vụ thay mặt công ty đặt (DM-25). ACTIVE: đang phục vụ. INACTIVE: không phục vụ, ví dụ đang ở xưởng hoặc chủ xe không dùng; lý do cho biết trường hợp nào (khi có hồ sơ sửa chữa, việc đang bảo dưỡng được đọc từ hồ sơ sửa chữa đang mở). Xe rời hệ thống được chuyển sang INACTIVE và xóa mềm. Xe đang chạy hay gửi dữ liệu được tính từ dữ liệu vận hành, không lưu.</t>
         </is>
       </c>
       <c r="H17" s="6" t="inlineStr">
@@ -8694,7 +8694,7 @@
       <c r="F18" s="6" t="n"/>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>Lý do của trạng thái hiện tại; NULL khi ACTIVE.</t>
+          <t>Lý do của trạng thái hiện tại, hoặc lý do xe rời hệ thống; NULL khi ACTIVE.</t>
         </is>
       </c>
       <c r="H18" s="6" t="inlineStr">
@@ -8848,7 +8848,7 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="40.5" customHeight="1">
+    <row r="23" ht="54" customHeight="1">
       <c r="A23" s="6" t="n">
         <v>16</v>
       </c>
@@ -8871,7 +8871,7 @@
       <c r="F23" s="6" t="n"/>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>Thời điểm xóa mềm, chỉ dùng cho xe đăng ký nhầm; xe thật rời hệ thống được chuyển sang DECOMMISSIONED, không bao giờ bị xóa. NULL khi bản ghi còn hiệu lực.</t>
+          <t>Thời điểm xóa mềm: bản ghi không còn thuộc hệ thống, do đã rời đi hoặc nhập nhầm (DM-25); mọi dữ liệu vẫn được giữ, lý do nằm trong status_reason. NULL khi còn thuộc hệ thống.</t>
         </is>
       </c>
       <c r="H23" s="6" t="inlineStr">
@@ -8899,7 +8899,7 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="40.5" customHeight="1">
+    <row r="26" ht="54" customHeight="1">
       <c r="A26" s="6" t="n"/>
       <c r="B26" s="6" t="inlineStr">
         <is>
@@ -8908,7 +8908,7 @@
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>ACTIVE, INACTIVE (sẽ bỏ), MAINTENANCE, DECOMMISSIONED</t>
+          <t>ACTIVE, INACTIVE, MAINTENANCE (sẽ bỏ), DECOMMISSIONED (sẽ bỏ)</t>
         </is>
       </c>
     </row>
@@ -8994,7 +8994,7 @@
       <c r="E31" s="6" t="n"/>
       <c r="F31" s="6" t="inlineStr">
         <is>
-          <t>Planned (VH-07), replaces the full unique constraint: WHERE deleted_at IS NULL AND status &lt;&gt; 'DECOMMISSIONED'</t>
+          <t>Planned (VH-07), replaces the full unique constraint: WHERE deleted_at IS NULL</t>
         </is>
       </c>
     </row>
@@ -9933,7 +9933,7 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="27" customHeight="1">
+    <row r="26">
       <c r="A26" s="6" t="n"/>
       <c r="B26" s="6" t="inlineStr">
         <is>
@@ -9942,7 +9942,7 @@
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>ACTIVE, MAINTENANCE, DECOMMISSIONED</t>
+          <t>ACTIVE, INACTIVE</t>
         </is>
       </c>
     </row>
@@ -10365,7 +10365,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="81" customHeight="1">
+    <row r="15" ht="94.5" customHeight="1">
       <c r="A15" s="6" t="n">
         <v>8</v>
       </c>
@@ -10388,7 +10388,7 @@
       <c r="F15" s="6" t="n"/>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>Vòng đời tổ chức. ACTIVE: đang sử dụng. SUSPENDED: tạm ngừng (ví dụ nợ cước), chặn đăng nhập nhưng vẫn thu dữ liệu xe, có thể mở lại. CLOSED: không còn hợp đồng, chặn đăng nhập, không nhận dữ liệu mới, dữ liệu được giữ theo thời hạn luật định; chỉ mở lại khi ký hợp đồng mới. Giá trị: ACTIVE | SUSPENDED | CLOSED.</t>
+          <t>Vòng đời tổ chức. ACTIVE: đang sử dụng. SUSPENDED: tạm ngừng (ví dụ nợ cước), chặn đăng nhập nhưng vẫn thu dữ liệu xe, có thể mở lại. CLOSED: đã rời đi (không còn hợp đồng), chặn đăng nhập, không nhận dữ liệu mới, dữ liệu được giữ theo thời hạn luật định; luôn đi cùng deleted_at (DM-25); chỉ mở lại khi ký hợp đồng mới. Giá trị: ACTIVE | SUSPENDED | CLOSED.</t>
         </is>
       </c>
       <c r="H15" s="6" t="inlineStr">
@@ -10558,7 +10558,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="40.5" customHeight="1">
+    <row r="20" ht="67.5" customHeight="1">
       <c r="A20" s="6" t="n">
         <v>13</v>
       </c>
@@ -10581,7 +10581,7 @@
       <c r="F20" s="6" t="n"/>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>Thời điểm xóa mềm, chỉ dùng cho tổ chức tạo nhầm; khách hàng hay đối tác thật được chuyển sang CLOSED, không bao giờ bị xóa. NULL khi bản ghi còn hiệu lực.</t>
+          <t>Thời điểm xóa mềm: bản ghi không còn thuộc hệ thống, do đã rời đi hoặc nhập nhầm (DM-25); mọi dữ liệu vẫn được giữ, lý do nằm trong status_reason. NULL khi còn thuộc hệ thống. Tổ chức rời đi được chuyển sang CLOSED và xóa mềm; ký hợp đồng mới thì trở lại ACTIVE và xóa giá trị này.</t>
         </is>
       </c>
       <c r="H20" s="6" t="inlineStr">
@@ -11609,7 +11609,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="27" customHeight="1">
+    <row r="17" ht="40.5" customHeight="1">
       <c r="A17" s="6" t="n">
         <v>10</v>
       </c>
@@ -11632,7 +11632,7 @@
       <c r="F17" s="6" t="n"/>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>Thời điểm xóa mềm, chỉ dùng cho dòng xe nhập nhầm; NULL khi bản ghi còn hiệu lực.</t>
+          <t>Thời điểm xóa mềm: dòng này không còn được cung cấp, hoặc nhập nhầm (DM-25); các bản ghi đã trỏ tới vẫn giữ. NULL khi còn cung cấp.</t>
         </is>
       </c>
       <c r="H17" s="6" t="inlineStr">
@@ -12788,7 +12788,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="27" customHeight="1">
+    <row r="16" ht="40.5" customHeight="1">
       <c r="A16" s="6" t="n">
         <v>9</v>
       </c>
@@ -12811,7 +12811,7 @@
       <c r="F16" s="6" t="n"/>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>Thời điểm xóa mềm, chỉ dùng cho dòng pin nhập nhầm; NULL khi bản ghi còn hiệu lực.</t>
+          <t>Thời điểm xóa mềm: dòng này không còn được cung cấp, hoặc nhập nhầm (DM-25); các bản ghi đã trỏ tới vẫn giữ. NULL khi còn cung cấp.</t>
         </is>
       </c>
       <c r="H16" s="6" t="inlineStr">
@@ -13958,7 +13958,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="67.5" customHeight="1">
+    <row r="16" ht="81" customHeight="1">
       <c r="A16" s="6" t="n">
         <v>9</v>
       </c>
@@ -13981,7 +13981,7 @@
       <c r="F16" s="6" t="n"/>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>Trạng thái do con người đặt (VH-16). ACTIVE: dùng được. MAINTENANCE: đang sửa chữa hoặc kiểm tra. DECOMMISSIONED: đã rời hệ thống (tái chế, bán cho mục đích tái sử dụng). Đang lắp hay trong kho không phải trạng thái: đọc từ vehicle_id.</t>
+          <t>Trạng thái do con người đặt (DM-25). ACTIVE: dùng được. INACTIVE: hiện không dùng được, ví dụ đang sửa chữa hoặc kiểm tra; lý do cho biết vì sao. Pin rời hệ thống (tái chế, bán cho mục đích tái sử dụng) được chuyển sang INACTIVE và xóa mềm. Đang lắp hay trong kho không phải trạng thái: đọc từ vehicle_id.</t>
         </is>
       </c>
       <c r="H16" s="6" t="inlineStr">
@@ -14106,7 +14106,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="40.5" customHeight="1">
+    <row r="20" ht="54" customHeight="1">
       <c r="A20" s="6" t="n">
         <v>13</v>
       </c>
@@ -14129,7 +14129,7 @@
       <c r="F20" s="6" t="n"/>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>Thời điểm xóa mềm, chỉ dùng cho pin nhập nhầm; pin thật rời hệ thống được chuyển sang DECOMMISSIONED. NULL khi bản ghi còn hiệu lực.</t>
+          <t>Thời điểm xóa mềm: bản ghi không còn thuộc hệ thống, do đã rời đi hoặc nhập nhầm (DM-25); mọi dữ liệu vẫn được giữ, lý do nằm trong status_reason. NULL khi còn thuộc hệ thống.</t>
         </is>
       </c>
       <c r="H20" s="6" t="inlineStr">
@@ -15620,7 +15620,7 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="27" customHeight="1">
+    <row r="21" ht="40.5" customHeight="1">
       <c r="A21" s="6" t="n">
         <v>14</v>
       </c>
@@ -15643,7 +15643,7 @@
       <c r="F21" s="6" t="n"/>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>Thời điểm xóa mềm, chỉ dùng cho bảo hành nhập nhầm; NULL khi bản ghi còn hiệu lực.</t>
+          <t>Thời điểm xóa mềm: bảo hành nhập nhầm và không còn thuộc hệ thống (DM-25); đồng thời bị VOIDED, kèm lý do. NULL khi còn thuộc hệ thống.</t>
         </is>
       </c>
       <c r="H21" s="6" t="inlineStr">
@@ -16959,7 +16959,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="81" customHeight="1">
+    <row r="15" ht="94.5" customHeight="1">
       <c r="A15" s="6" t="n">
         <v>8</v>
       </c>
@@ -16982,7 +16982,7 @@
       <c r="F15" s="6" t="n"/>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>Trạng thái do con người đặt (TX-08). ACTIVE: dùng được. MAINTENANCE: đang sửa chữa hoặc kiểm tra. DECOMMISSIONED: đã rời hệ thống (thanh lý, trả lại). Đang gắn hay trong kho đọc từ vehicle_id; có gửi dữ liệu hay im lặng được tính từ dữ liệu vận hành (TX-06). Chỉ thiết bị đang gắn và ACTIVE mới nhận cấu hình.</t>
+          <t>Trạng thái do con người đặt (DM-25). ACTIVE: dùng được. INACTIVE: hiện không dùng được, ví dụ đang sửa chữa; lý do cho biết vì sao. Thiết bị rời hệ thống (thanh lý, trả lại) được chuyển sang INACTIVE, tháo khỏi xe và xóa mềm. Đang gắn hay trong kho đọc từ vehicle_id; có gửi dữ liệu hay im lặng được tính từ dữ liệu vận hành (TX-06). Chỉ thiết bị đang gắn và ACTIVE mới nhận cấu hình.</t>
         </is>
       </c>
       <c r="H15" s="6" t="inlineStr">
@@ -17229,7 +17229,7 @@
       <c r="F22" s="6" t="n"/>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>Thời điểm xóa mềm, chỉ dùng cho thiết bị nhập nhầm; thiết bị thật rời hệ thống được chuyển sang DECOMMISSIONED và tháo khỏi xe, các xe trước được giữ trong lịch sử (TX-08). NULL khi bản ghi còn hiệu lực.</t>
+          <t>Thời điểm xóa mềm: bản ghi không còn thuộc hệ thống, do đã rời đi hoặc nhập nhầm (DM-25); mọi dữ liệu vẫn được giữ, lý do nằm trong status_reason. NULL khi còn thuộc hệ thống. Các xe trước vẫn nằm trong lịch sử.</t>
         </is>
       </c>
       <c r="H22" s="6" t="inlineStr">
@@ -17257,7 +17257,7 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="54" customHeight="1">
+    <row r="25" ht="27" customHeight="1">
       <c r="A25" s="6" t="n"/>
       <c r="B25" s="6" t="inlineStr">
         <is>
@@ -17266,7 +17266,7 @@
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>ACTIVE, INACTIVE (sẽ bỏ), MAINTENANCE, DECOMMISSIONED (dự kiến)</t>
+          <t>ACTIVE, INACTIVE, MAINTENANCE (sẽ bỏ)</t>
         </is>
       </c>
     </row>
@@ -18134,7 +18134,7 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="27" customHeight="1">
+    <row r="26">
       <c r="A26" s="6" t="n"/>
       <c r="B26" s="6" t="inlineStr">
         <is>
@@ -18143,7 +18143,7 @@
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>ACTIVE, MAINTENANCE, DECOMMISSIONED</t>
+          <t>ACTIVE, INACTIVE</t>
         </is>
       </c>
     </row>
@@ -25203,7 +25203,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="27" customHeight="1">
+    <row r="18" ht="67.5" customHeight="1">
       <c r="A18" s="6" t="n">
         <v>10</v>
       </c>
@@ -25226,7 +25226,7 @@
       <c r="F18" s="6" t="n"/>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>Thời điểm xóa mềm; NULL khi bản ghi còn hiệu lực. Không bao giờ xóa hẳn.</t>
+          <t>Thời điểm xóa mềm: bản ghi không còn thuộc hệ thống, do đã rời đi hoặc nhập nhầm (DM-25); mọi dữ liệu vẫn được giữ, lý do nằm trong status_reason. NULL khi còn thuộc hệ thống. Tài khoản bị xóa cũng bị LOCKED, và số điện thoại, e-mail của nó được dùng lại cho tài khoản mới (ID-28).</t>
         </is>
       </c>
       <c r="H18" s="6" t="inlineStr">

--- a/docs/design/domain-model/domain-model.xlsx
+++ b/docs/design/domain-model/domain-model.xlsx
@@ -4606,7 +4606,7 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>session_id</t>
+          <t>user_session_id</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
@@ -5173,7 +5173,7 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>code_id</t>
+          <t>one_time_code_id</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
@@ -5679,7 +5679,7 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>consent_id</t>
+          <t>user_consent_id</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
@@ -5798,7 +5798,7 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>document_id</t>
+          <t>legal_document_id</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
@@ -5818,7 +5818,7 @@
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>legal_documents.document_id (khi xóa: chặn xóa)</t>
+          <t>legal_documents.legal_document_id (khi xóa: chặn xóa)</t>
         </is>
       </c>
       <c r="G10" s="6" t="inlineStr">
@@ -5961,12 +5961,12 @@
       <c r="A16" s="6" t="n"/>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>uq_user_consents_person_document</t>
+          <t>uq_user_consents_person_legal_document</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>user_id, document_id</t>
+          <t>user_id, legal_document_id</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
@@ -5985,12 +5985,12 @@
       <c r="A17" s="6" t="n"/>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>uq_user_consents_organization_document</t>
+          <t>uq_user_consents_organization_legal_document</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>organization_id, document_id</t>
+          <t>organization_id, legal_document_id</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
@@ -6119,7 +6119,7 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>document_id</t>
+          <t>legal_document_id</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
@@ -6424,7 +6424,7 @@
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>document_id</t>
+          <t>legal_document_id</t>
         </is>
       </c>
     </row>
@@ -6541,7 +6541,7 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>assignment_id</t>
+          <t>user_role_assignment_id</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
@@ -7023,7 +7023,7 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>audit_id</t>
+          <t>access_audit_log_id</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
@@ -19041,13 +19041,13 @@
         </is>
       </c>
     </row>
-    <row r="7">
+    <row r="7" ht="27" customHeight="1">
       <c r="A7" s="6" t="n">
         <v>1</v>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>status_report_id</t>
+          <t>telematic_status_report_id</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
@@ -42090,7 +42090,7 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>credential_id</t>
+          <t>user_credential_id</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">

--- a/docs/design/domain-model/domain-model.xlsx
+++ b/docs/design/domain-model/domain-model.xlsx
@@ -741,7 +741,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="121.5" customHeight="1">
+    <row r="7" ht="135" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
           <t>1</t>
@@ -774,7 +774,7 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>Mọi bên mà người dùng đại diện: khách hàng (doanh nghiệp vận tải và chủ xe cá nhân tự lái), (các) tổ chức nội bộ của chính chúng ta, và đối tác sửa chữa/cứu hộ - tất cả được lưu như nhau. Mọi dữ liệu thuộc một tổ chức đều trỏ về đây qua organization_id; xe của chính chúng ta được sở hữu giống hệt xe của khách hàng. Chỉ is_internal phân biệt các tổ chức về quyền truy cập: người dùng nội bộ xem được dữ liệu của mọi tổ chức, còn lại chỉ xem dữ liệu của chính mình. Không có danh sách người liên hệ riêng: ai cần nhận thông tin (hóa đơn, nhắc nhở, cảnh báo) đều là người dùng giữ vai trò tương ứng. Hợp đồng và gói dịch vụ nằm ở bảng riêng.</t>
+          <t>Mọi bên mà người dùng đại diện: khách hàng (doanh nghiệp vận tải và chủ xe cá nhân tự lái), (các) tổ chức nội bộ của chính chúng ta, và đối tác sửa chữa/cứu hộ - tất cả được lưu như nhau. Mọi dữ liệu thuộc một tổ chức đều trỏ về đây qua organization_id; xe của chính chúng ta được sở hữu giống hệt xe của khách hàng. Chỉ is_internal phân biệt các tổ chức về quyền truy cập: người dùng nội bộ xem được dữ liệu của mọi tổ chức, còn lại chỉ xem dữ liệu của chính mình. Không có danh sách người liên hệ riêng: ai cần nhận thông tin (hóa đơn, nhắc nhở, cảnh báo) đều là người dùng giữ vai trò tương ứng. Hợp đồng và gói dịch vụ nằm ở bảng riêng. Ràng buộc kiểm tra: (status = 'CLOSED') = (deleted_at IS NOT NULL) (DM-25).</t>
         </is>
       </c>
       <c r="H7" s="6" t="n">
@@ -831,7 +831,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="67.5" customHeight="1">
+    <row r="9" ht="81" customHeight="1">
       <c r="A9" s="6" t="inlineStr">
         <is>
           <t>2</t>
@@ -864,7 +864,7 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>Một con người - mỗi người một tài khoản, dùng cho mọi tổ chức mà họ làm việc (một người có thể thuộc nhiều tổ chức, qua bảng memberships): nhân viên khách hàng, tài xế, nhân viên nội bộ hoặc kỹ thuật viên đối tác. Quyền của họ đến từ vai trò (chức danh); thông tin riêng của một công việc (ví dụ bằng lái của tài xế) nằm ở hồ sơ, và vai trò DRIVER cần một hồ sơ tài xế còn hiệu lực.</t>
+          <t>Một con người - mỗi người một tài khoản, dùng cho mọi tổ chức mà họ làm việc (một người có thể thuộc nhiều tổ chức, qua bảng memberships): nhân viên khách hàng, tài xế, nhân viên nội bộ hoặc kỹ thuật viên đối tác. Quyền của họ đến từ vai trò (chức danh); thông tin riêng của một công việc (ví dụ bằng lái của tài xế) nằm ở hồ sơ, và vai trò DRIVER cần một hồ sơ tài xế còn hiệu lực. Ràng buộc kiểm tra: deleted_at IS NULL OR status = 'LOCKED' (DM-25).</t>
         </is>
       </c>
       <c r="H9" s="6" t="n">
@@ -1485,7 +1485,7 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="40.5" customHeight="1">
+    <row r="24" ht="54" customHeight="1">
       <c r="A24" s="6" t="inlineStr">
         <is>
           <t>13</t>
@@ -1518,7 +1518,7 @@
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>Hồ sơ của một xe tải điện: xe là gì và các quyết định về xe. Không có bảng trạng thái: mọi thứ xe báo về đi qua T-Box và được lưu từng bản tin trong vehicle_telemetry.</t>
+          <t>Hồ sơ của một xe tải điện: xe là gì và các quyết định về xe. Không có bảng trạng thái: mọi thứ xe báo về đi qua T-Box và được lưu từng bản tin trong vehicle_telemetry. Ràng buộc kiểm tra: deleted_at IS NULL OR status = 'INACTIVE' (DM-25).</t>
         </is>
       </c>
       <c r="H24" s="6" t="n">
@@ -1811,7 +1811,7 @@
       </c>
       <c r="G31" s="6" t="inlineStr">
         <is>
-          <t>Một viên pin vật lý, được quản lý như một tài sản (BAT-01, VH-16). Xe đang lắp pin và chủ sở hữu pin là các cột kèm thời điểm bắt đầu (DM-22); các giai đoạn lấy từ view battery_installation_periods và battery_ownership_periods trên battery_history, mã nguồn không bao giờ đọc trực tiếp bảng lịch sử. Lịch sử sức khỏe của pin qua các xe được ghép từ dữ liệu vận hành với các giai đoạn lắp. Khi bán xe mà bên bán sở hữu pin, pin chuyển sang bên mua trong cùng thao tác chuyển quyền (VH-12); pin thuộc bên khác (ví dụ thuê của G3) vẫn thuộc chủ của nó.</t>
+          <t>Một viên pin vật lý, được quản lý như một tài sản (BAT-01, VH-16). Xe đang lắp pin và chủ sở hữu pin là các cột kèm thời điểm bắt đầu (DM-22); các giai đoạn lấy từ view battery_installation_periods và battery_ownership_periods trên battery_history, mã nguồn không bao giờ đọc trực tiếp bảng lịch sử. Lịch sử sức khỏe của pin qua các xe được ghép từ dữ liệu vận hành với các giai đoạn lắp. Khi bán xe mà bên bán sở hữu pin, pin chuyển sang bên mua trong cùng thao tác chuyển quyền (VH-12); pin thuộc bên khác (ví dụ thuê của G3) vẫn thuộc chủ của nó. Ràng buộc kiểm tra: deleted_at IS NULL OR status = 'INACTIVE' (DM-25).</t>
         </is>
       </c>
       <c r="H31" s="6" t="n">
@@ -1890,7 +1890,7 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="81" customHeight="1">
+    <row r="34" ht="148.5" customHeight="1">
       <c r="A34" s="6" t="inlineStr">
         <is>
           <t>17</t>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="G34" s="6" t="inlineStr">
         <is>
-          <t>Một bảo hành của một xe, pin hoặc T-Box (WAR-01, VH-18), đặt riêng cho từng xe. Đối tượng được bảo hành là liên kết duy nhất có giá trị (đúng một, ràng buộc kiểm tra); liên kết đó cũng quyết định các khóa giới hạn áp dụng. Không có organization_id (DM-24): bảo hành đi theo đối tượng, ai đang sở hữu đối tượng thì xem được. Một xe thường có nhiều bảo hành (xe, pin, gia hạn). Có lưu lịch sử thay đổi: việc hủy bảo hành phải cho biết ai và vì sao.</t>
+          <t>Một bảo hành của một xe, pin hoặc T-Box (WAR-01, VH-18), đặt riêng cho từng xe. Đối tượng được bảo hành là liên kết duy nhất có giá trị (đúng một, ràng buộc kiểm tra); liên kết đó cũng quyết định các khóa giới hạn áp dụng. Không có organization_id (DM-24): bảo hành đi theo đối tượng, ai đang sở hữu đối tượng thì xem được. Một xe thường có nhiều bảo hành (xe, pin, gia hạn). Có lưu lịch sử thay đổi: việc hủy bảo hành phải cho biết ai và vì sao. Ràng buộc kiểm tra: num_nonnulls(vehicle_id, battery_id, telematic_id) = 1 (VH-18); deleted_at IS NULL OR status = 'VOIDED' (DM-25). Các khóa limits hợp lệ theo liên kết được đặt do ứng dụng kiểm tra. Có thể sau này: mỗi loại đối tượng một bảng bảo hành, nằm trong miền của đối tượng đó (bảo hành xe, pin, T-Box), nếu quy định của chúng khác nhau nhiều.</t>
         </is>
       </c>
       <c r="H34" s="6" t="n">
@@ -2003,7 +2003,7 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="94.5" customHeight="1">
+    <row r="37" ht="108" customHeight="1">
       <c r="A37" s="6" t="inlineStr">
         <is>
           <t>18</t>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G37" s="6" t="inlineStr">
         <is>
-          <t>Hồ sơ của một thiết bị telematics (T-Box): thiết bị là gì và các quyết định về nó (TX-08). Thiết bị là một tài sản có chủ riêng, là chủ xe hoặc G3 (TX-07); thiết bị thuộc bên bán đi theo xe khi bán xe. Chủ sở hữu và xe đang gắn là các cột kèm thời điểm bắt đầu (DM-22), các giai đoạn đọc qua view telematic_ownership_periods và telematic_installation_periods. Những gì thiết bị tự báo về mình được lưu trong telematic_status_reports; sức khỏe hiện tại là báo cáo mới nhất (TX-11).</t>
+          <t>Hồ sơ của một thiết bị telematics (T-Box): thiết bị là gì và các quyết định về nó (TX-08). Thiết bị là một tài sản có chủ riêng, là chủ xe hoặc G3 (TX-07); thiết bị thuộc bên bán đi theo xe khi bán xe. Chủ sở hữu và xe đang gắn là các cột kèm thời điểm bắt đầu (DM-22), các giai đoạn đọc qua view telematic_ownership_periods và telematic_installation_periods. Những gì thiết bị tự báo về mình được lưu trong telematic_status_reports; sức khỏe hiện tại là báo cáo mới nhất (TX-11). Ràng buộc kiểm tra: deleted_at IS NULL OR (status = 'INACTIVE' AND vehicle_id IS NULL) (DM-25).</t>
         </is>
       </c>
       <c r="H37" s="6" t="n">
@@ -8234,7 +8234,7 @@
     <row r="4">
       <c r="A4" s="11" t="inlineStr">
         <is>
-          <t>Hồ sơ của một xe tải điện: xe là gì và các quyết định về xe. Không có bảng trạng thái: mọi thứ xe báo về đi qua T-Box và được lưu từng bản tin trong vehicle_telemetry.</t>
+          <t>Hồ sơ của một xe tải điện: xe là gì và các quyết định về xe. Không có bảng trạng thái: mọi thứ xe báo về đi qua T-Box và được lưu từng bản tin trong vehicle_telemetry. Ràng buộc kiểm tra: deleted_at IS NULL OR status = 'INACTIVE' (DM-25).</t>
         </is>
       </c>
     </row>
@@ -10047,7 +10047,7 @@
     <row r="4">
       <c r="A4" s="11" t="inlineStr">
         <is>
-          <t>Mọi bên mà người dùng đại diện: khách hàng (doanh nghiệp vận tải và chủ xe cá nhân tự lái), (các) tổ chức nội bộ của chính chúng ta, và đối tác sửa chữa/cứu hộ - tất cả được lưu như nhau. Mọi dữ liệu thuộc một tổ chức đều trỏ về đây qua organization_id; xe của chính chúng ta được sở hữu giống hệt xe của khách hàng. Chỉ is_internal phân biệt các tổ chức về quyền truy cập: người dùng nội bộ xem được dữ liệu của mọi tổ chức, còn lại chỉ xem dữ liệu của chính mình. Không có danh sách người liên hệ riêng: ai cần nhận thông tin (hóa đơn, nhắc nhở, cảnh báo) đều là người dùng giữ vai trò tương ứng. Hợp đồng và gói dịch vụ nằm ở bảng riêng.</t>
+          <t>Mọi bên mà người dùng đại diện: khách hàng (doanh nghiệp vận tải và chủ xe cá nhân tự lái), (các) tổ chức nội bộ của chính chúng ta, và đối tác sửa chữa/cứu hộ - tất cả được lưu như nhau. Mọi dữ liệu thuộc một tổ chức đều trỏ về đây qua organization_id; xe của chính chúng ta được sở hữu giống hệt xe của khách hàng. Chỉ is_internal phân biệt các tổ chức về quyền truy cập: người dùng nội bộ xem được dữ liệu của mọi tổ chức, còn lại chỉ xem dữ liệu của chính mình. Không có danh sách người liên hệ riêng: ai cần nhận thông tin (hóa đơn, nhắc nhở, cảnh báo) đều là người dùng giữ vai trò tương ứng. Hợp đồng và gói dịch vụ nằm ở bảng riêng. Ràng buộc kiểm tra: (status = 'CLOSED') = (deleted_at IS NOT NULL) (DM-25).</t>
         </is>
       </c>
     </row>
@@ -13579,7 +13579,7 @@
     <row r="4">
       <c r="A4" s="11" t="inlineStr">
         <is>
-          <t>Một viên pin vật lý, được quản lý như một tài sản (BAT-01, VH-16). Xe đang lắp pin và chủ sở hữu pin là các cột kèm thời điểm bắt đầu (DM-22); các giai đoạn lấy từ view battery_installation_periods và battery_ownership_periods trên battery_history, mã nguồn không bao giờ đọc trực tiếp bảng lịch sử. Lịch sử sức khỏe của pin qua các xe được ghép từ dữ liệu vận hành với các giai đoạn lắp. Khi bán xe mà bên bán sở hữu pin, pin chuyển sang bên mua trong cùng thao tác chuyển quyền (VH-12); pin thuộc bên khác (ví dụ thuê của G3) vẫn thuộc chủ của nó.</t>
+          <t>Một viên pin vật lý, được quản lý như một tài sản (BAT-01, VH-16). Xe đang lắp pin và chủ sở hữu pin là các cột kèm thời điểm bắt đầu (DM-22); các giai đoạn lấy từ view battery_installation_periods và battery_ownership_periods trên battery_history, mã nguồn không bao giờ đọc trực tiếp bảng lịch sử. Lịch sử sức khỏe của pin qua các xe được ghép từ dữ liệu vận hành với các giai đoạn lắp. Khi bán xe mà bên bán sở hữu pin, pin chuyển sang bên mua trong cùng thao tác chuyển quyền (VH-12); pin thuộc bên khác (ví dụ thuê của G3) vẫn thuộc chủ của nó. Ràng buộc kiểm tra: deleted_at IS NULL OR status = 'INACTIVE' (DM-25).</t>
         </is>
       </c>
     </row>
@@ -15056,7 +15056,7 @@
     <row r="4">
       <c r="A4" s="11" t="inlineStr">
         <is>
-          <t>Một bảo hành của một xe, pin hoặc T-Box (WAR-01, VH-18), đặt riêng cho từng xe. Đối tượng được bảo hành là liên kết duy nhất có giá trị (đúng một, ràng buộc kiểm tra); liên kết đó cũng quyết định các khóa giới hạn áp dụng. Không có organization_id (DM-24): bảo hành đi theo đối tượng, ai đang sở hữu đối tượng thì xem được. Một xe thường có nhiều bảo hành (xe, pin, gia hạn). Có lưu lịch sử thay đổi: việc hủy bảo hành phải cho biết ai và vì sao.</t>
+          <t>Một bảo hành của một xe, pin hoặc T-Box (WAR-01, VH-18), đặt riêng cho từng xe. Đối tượng được bảo hành là liên kết duy nhất có giá trị (đúng một, ràng buộc kiểm tra); liên kết đó cũng quyết định các khóa giới hạn áp dụng. Không có organization_id (DM-24): bảo hành đi theo đối tượng, ai đang sở hữu đối tượng thì xem được. Một xe thường có nhiều bảo hành (xe, pin, gia hạn). Có lưu lịch sử thay đổi: việc hủy bảo hành phải cho biết ai và vì sao. Ràng buộc kiểm tra: num_nonnulls(vehicle_id, battery_id, telematic_id) = 1 (VH-18); deleted_at IS NULL OR status = 'VOIDED' (DM-25). Các khóa limits hợp lệ theo liên kết được đặt do ứng dụng kiểm tra. Có thể sau này: mỗi loại đối tượng một bảng bảo hành, nằm trong miền của đối tượng đó (bảo hành xe, pin, T-Box), nếu quy định của chúng khác nhau nhiều.</t>
         </is>
       </c>
     </row>
@@ -16625,7 +16625,7 @@
     <row r="4">
       <c r="A4" s="11" t="inlineStr">
         <is>
-          <t>Hồ sơ của một thiết bị telematics (T-Box): thiết bị là gì và các quyết định về nó (TX-08). Thiết bị là một tài sản có chủ riêng, là chủ xe hoặc G3 (TX-07); thiết bị thuộc bên bán đi theo xe khi bán xe. Chủ sở hữu và xe đang gắn là các cột kèm thời điểm bắt đầu (DM-22), các giai đoạn đọc qua view telematic_ownership_periods và telematic_installation_periods. Những gì thiết bị tự báo về mình được lưu trong telematic_status_reports; sức khỏe hiện tại là báo cáo mới nhất (TX-11).</t>
+          <t>Hồ sơ của một thiết bị telematics (T-Box): thiết bị là gì và các quyết định về nó (TX-08). Thiết bị là một tài sản có chủ riêng, là chủ xe hoặc G3 (TX-07); thiết bị thuộc bên bán đi theo xe khi bán xe. Chủ sở hữu và xe đang gắn là các cột kèm thời điểm bắt đầu (DM-22), các giai đoạn đọc qua view telematic_ownership_periods và telematic_installation_periods. Những gì thiết bị tự báo về mình được lưu trong telematic_status_reports; sức khỏe hiện tại là báo cáo mới nhất (TX-11). Ràng buộc kiểm tra: deleted_at IS NULL OR (status = 'INACTIVE' AND vehicle_id IS NULL) (DM-25).</t>
         </is>
       </c>
     </row>
@@ -16877,7 +16877,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="40.5" customHeight="1">
+    <row r="13" ht="67.5" customHeight="1">
       <c r="A13" s="6" t="n">
         <v>6</v>
       </c>
@@ -16908,7 +16908,7 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>Xe mà thiết bị đang gắn; NULL khi trong kho hoặc đã tháo. Mỗi xe gắn tối đa một thiết bị. Các xe trước lấy từ view telematic_installation_periods (DM-22).</t>
+          <t>Xe mà thiết bị đang gắn; NULL khi trong kho hoặc đã tháo. Mỗi xe gắn tối đa một thiết bị. Các xe trước lấy từ view telematic_installation_periods (DM-22). Dự kiến: khóa ngoại chuyển sang ON DELETE RESTRICT như mọi liên kết khác (hiện là SET NULL).</t>
         </is>
       </c>
       <c r="H13" s="6" t="inlineStr">
@@ -24796,7 +24796,7 @@
     <row r="4">
       <c r="A4" s="11" t="inlineStr">
         <is>
-          <t>Một con người - mỗi người một tài khoản, dùng cho mọi tổ chức mà họ làm việc (một người có thể thuộc nhiều tổ chức, qua bảng memberships): nhân viên khách hàng, tài xế, nhân viên nội bộ hoặc kỹ thuật viên đối tác. Quyền của họ đến từ vai trò (chức danh); thông tin riêng của một công việc (ví dụ bằng lái của tài xế) nằm ở hồ sơ, và vai trò DRIVER cần một hồ sơ tài xế còn hiệu lực.</t>
+          <t>Một con người - mỗi người một tài khoản, dùng cho mọi tổ chức mà họ làm việc (một người có thể thuộc nhiều tổ chức, qua bảng memberships): nhân viên khách hàng, tài xế, nhân viên nội bộ hoặc kỹ thuật viên đối tác. Quyền của họ đến từ vai trò (chức danh); thông tin riêng của một công việc (ví dụ bằng lái của tài xế) nằm ở hồ sơ, và vai trò DRIVER cần một hồ sơ tài xế còn hiệu lực. Ràng buộc kiểm tra: deleted_at IS NULL OR status = 'LOCKED' (DM-25).</t>
         </is>
       </c>
     </row>

--- a/docs/design/domain-model/domain-model.xlsx
+++ b/docs/design/domain-model/domain-model.xlsx
@@ -632,7 +632,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I105"/>
+  <dimension ref="A1:I110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1778,7 +1778,7 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="108" customHeight="1">
+    <row r="31" ht="121.5" customHeight="1">
       <c r="A31" s="6" t="inlineStr">
         <is>
           <t>16</t>
@@ -1811,7 +1811,7 @@
       </c>
       <c r="G31" s="6" t="inlineStr">
         <is>
-          <t>Một viên pin vật lý, được quản lý như một tài sản (BAT-01, VH-16). Xe đang lắp pin và chủ sở hữu pin là các cột kèm thời điểm bắt đầu (DM-22); các giai đoạn lấy từ view battery_installation_periods và battery_ownership_periods trên battery_history, mã nguồn không bao giờ đọc trực tiếp bảng lịch sử. Lịch sử sức khỏe của pin qua các xe được ghép từ dữ liệu vận hành với các giai đoạn lắp. Khi bán xe mà bên bán sở hữu pin, pin chuyển sang bên mua trong cùng thao tác chuyển quyền (VH-12); pin thuộc bên khác (ví dụ thuê của G3) vẫn thuộc chủ của nó. Ràng buộc kiểm tra: deleted_at IS NULL OR status = 'INACTIVE' (DM-25).</t>
+          <t>Một viên pin vật lý, được quản lý như một tài sản (BAT-01, VH-16). Xe đang lắp pin và chủ sở hữu pin là các cột kèm thời điểm bắt đầu (DM-22); các giai đoạn lắp lấy từ view battery_installation_periods (xem ghi chú views); giai đoạn sở hữu có view khi cần lần đầu (DM-27); mã nguồn không bao giờ đọc trực tiếp bảng lịch sử. Lịch sử sức khỏe của pin qua các xe được ghép từ dữ liệu vận hành với các giai đoạn lắp. Khi bán xe mà bên bán sở hữu pin, pin chuyển sang bên mua trong cùng thao tác chuyển quyền (VH-12); pin thuộc bên khác (ví dụ thuê của G3) vẫn thuộc chủ của nó. Ràng buộc kiểm tra: deleted_at IS NULL OR status = 'INACTIVE' (DM-25).</t>
         </is>
       </c>
       <c r="H31" s="6" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G37" s="6" t="inlineStr">
         <is>
-          <t>Hồ sơ của một thiết bị telematics (T-Box): thiết bị là gì và các quyết định về nó (TX-08). Thiết bị là một tài sản có chủ riêng, là chủ xe hoặc G3 (TX-07); thiết bị thuộc bên bán đi theo xe khi bán xe. Chủ sở hữu và xe đang gắn là các cột kèm thời điểm bắt đầu (DM-22), các giai đoạn đọc qua view telematic_ownership_periods và telematic_installation_periods. Những gì thiết bị tự báo về mình được lưu trong telematic_status_reports; sức khỏe hiện tại là báo cáo mới nhất (TX-11). Ràng buộc kiểm tra: deleted_at IS NULL OR (status = 'INACTIVE' AND vehicle_id IS NULL) (DM-25).</t>
+          <t>Hồ sơ của một thiết bị telematics (T-Box): thiết bị là gì và các quyết định về nó (TX-08). Thiết bị là một tài sản có chủ riêng, là chủ xe hoặc G3 (TX-07); thiết bị thuộc bên bán đi theo xe khi bán xe. Chủ sở hữu và xe đang gắn là các cột kèm thời điểm bắt đầu (DM-22), các giai đoạn có view khi có tính năng đầu tiên cần (DM-27). Những gì thiết bị tự báo về mình được lưu trong telematic_status_reports; sức khỏe hiện tại là báo cáo mới nhất (TX-11). Ràng buộc kiểm tra: deleted_at IS NULL OR (status = 'INACTIVE' AND vehicle_id IS NULL) (DM-25).</t>
         </is>
       </c>
       <c r="H37" s="6" t="n">
@@ -4258,39 +4258,113 @@
     <row r="103">
       <c r="A103" s="8" t="inlineStr">
         <is>
-          <t>Các quyết định còn mở</t>
+          <t>Các view (giai đoạn đọc từ lịch sử)</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="4" t="inlineStr">
         <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="B104" s="4" t="inlineStr">
+        <is>
+          <t>Mỗi dòng là</t>
+        </is>
+      </c>
+      <c r="C104" s="4" t="inlineStr">
+        <is>
+          <t>Các cột</t>
+        </is>
+      </c>
+      <c r="D104" s="4" t="inlineStr">
+        <is>
+          <t>Được dùng bởi</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="94.5" customHeight="1">
+      <c r="A105" s="6" t="inlineStr">
+        <is>
+          <t>vehicle_ownership_periods</t>
+        </is>
+      </c>
+      <c r="B105" s="6" t="inlineStr">
+        <is>
+          <t>một giai đoạn xe thuộc một chủ</t>
+        </is>
+      </c>
+      <c r="C105" s="6" t="inlineStr">
+        <is>
+          <t>vehicle_id, organization_id, owned_from, owned_until (NULL với chủ hiện tại)</t>
+        </is>
+      </c>
+      <c r="D105" s="6" t="inlineStr">
+        <is>
+          <t>lịch sử sở hữu và ngày bàn giao đầu tiên (VEH-02), "ngày đó xe của ai"</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="94.5" customHeight="1">
+      <c r="A106" s="6" t="inlineStr">
+        <is>
+          <t>battery_installation_periods</t>
+        </is>
+      </c>
+      <c r="B106" s="6" t="inlineStr">
+        <is>
+          <t>một lần pin nằm trên một xe</t>
+        </is>
+      </c>
+      <c r="C106" s="6" t="inlineStr">
+        <is>
+          <t>battery_id, vehicle_id, installed_from, installed_until (NULL khi đang lắp)</t>
+        </is>
+      </c>
+      <c r="D106" s="6" t="inlineStr">
+        <is>
+          <t>lịch sử sức khỏe pin qua các xe (MON-07), bộ đếm bảo hành pin (WAR-01)</t>
+        </is>
+      </c>
+    </row>
+    <row r="107"/>
+    <row r="108">
+      <c r="A108" s="8" t="inlineStr">
+        <is>
+          <t>Các quyết định còn mở</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="4" t="inlineStr">
+        <is>
           <t>Mã</t>
         </is>
       </c>
-      <c r="B104" s="4" t="inlineStr">
+      <c r="B109" s="4" t="inlineStr">
         <is>
           <t>Câu hỏi</t>
         </is>
       </c>
-      <c r="C104" s="4" t="inlineStr">
+      <c r="C109" s="4" t="inlineStr">
         <is>
           <t>Ảnh hưởng tới</t>
         </is>
       </c>
     </row>
-    <row r="105" ht="54" customHeight="1">
-      <c r="A105" s="6" t="inlineStr">
+    <row r="110" ht="54" customHeight="1">
+      <c r="A110" s="6" t="inlineStr">
         <is>
           <t>D5</t>
         </is>
       </c>
-      <c r="B105" s="6" t="inlineStr">
+      <c r="B110" s="6" t="inlineStr">
         <is>
           <t>Ai trả tiền khi tài xế của đội xe sạc: ví của tài xế, ví của đội xe, hay tùy trường hợp?</t>
         </is>
       </c>
-      <c r="C105" s="6" t="inlineStr">
+      <c r="C110" s="6" t="inlineStr">
         <is>
           <t>wallets, payments</t>
         </is>
@@ -13579,7 +13653,7 @@
     <row r="4">
       <c r="A4" s="11" t="inlineStr">
         <is>
-          <t>Một viên pin vật lý, được quản lý như một tài sản (BAT-01, VH-16). Xe đang lắp pin và chủ sở hữu pin là các cột kèm thời điểm bắt đầu (DM-22); các giai đoạn lấy từ view battery_installation_periods và battery_ownership_periods trên battery_history, mã nguồn không bao giờ đọc trực tiếp bảng lịch sử. Lịch sử sức khỏe của pin qua các xe được ghép từ dữ liệu vận hành với các giai đoạn lắp. Khi bán xe mà bên bán sở hữu pin, pin chuyển sang bên mua trong cùng thao tác chuyển quyền (VH-12); pin thuộc bên khác (ví dụ thuê của G3) vẫn thuộc chủ của nó. Ràng buộc kiểm tra: deleted_at IS NULL OR status = 'INACTIVE' (DM-25).</t>
+          <t>Một viên pin vật lý, được quản lý như một tài sản (BAT-01, VH-16). Xe đang lắp pin và chủ sở hữu pin là các cột kèm thời điểm bắt đầu (DM-22); các giai đoạn lắp lấy từ view battery_installation_periods (xem ghi chú views); giai đoạn sở hữu có view khi cần lần đầu (DM-27); mã nguồn không bao giờ đọc trực tiếp bảng lịch sử. Lịch sử sức khỏe của pin qua các xe được ghép từ dữ liệu vận hành với các giai đoạn lắp. Khi bán xe mà bên bán sở hữu pin, pin chuyển sang bên mua trong cùng thao tác chuyển quyền (VH-12); pin thuộc bên khác (ví dụ thuê của G3) vẫn thuộc chủ của nó. Ràng buộc kiểm tra: deleted_at IS NULL OR status = 'INACTIVE' (DM-25).</t>
         </is>
       </c>
     </row>
@@ -13757,7 +13831,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="40.5" customHeight="1">
+    <row r="11" ht="54" customHeight="1">
       <c r="A11" s="6" t="n">
         <v>4</v>
       </c>
@@ -13788,7 +13862,7 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>Tổ chức đang sở hữu pin; có thể khác chủ xe (ví dụ G3 cho thuê pin, deferred.md 88). Các chủ trước lấy từ view battery_ownership_periods.</t>
+          <t>Tổ chức đang sở hữu pin; có thể khác chủ xe (ví dụ G3 cho thuê pin, deferred.md 88). Các chủ trước nằm trong battery_history; view được thêm khi có tính năng đầu tiên cần (DM-27).</t>
         </is>
       </c>
       <c r="H11" s="6" t="inlineStr">
@@ -16625,7 +16699,7 @@
     <row r="4">
       <c r="A4" s="11" t="inlineStr">
         <is>
-          <t>Hồ sơ của một thiết bị telematics (T-Box): thiết bị là gì và các quyết định về nó (TX-08). Thiết bị là một tài sản có chủ riêng, là chủ xe hoặc G3 (TX-07); thiết bị thuộc bên bán đi theo xe khi bán xe. Chủ sở hữu và xe đang gắn là các cột kèm thời điểm bắt đầu (DM-22), các giai đoạn đọc qua view telematic_ownership_periods và telematic_installation_periods. Những gì thiết bị tự báo về mình được lưu trong telematic_status_reports; sức khỏe hiện tại là báo cáo mới nhất (TX-11). Ràng buộc kiểm tra: deleted_at IS NULL OR (status = 'INACTIVE' AND vehicle_id IS NULL) (DM-25).</t>
+          <t>Hồ sơ của một thiết bị telematics (T-Box): thiết bị là gì và các quyết định về nó (TX-08). Thiết bị là một tài sản có chủ riêng, là chủ xe hoặc G3 (TX-07); thiết bị thuộc bên bán đi theo xe khi bán xe. Chủ sở hữu và xe đang gắn là các cột kèm thời điểm bắt đầu (DM-22), các giai đoạn có view khi có tính năng đầu tiên cần (DM-27). Những gì thiết bị tự báo về mình được lưu trong telematic_status_reports; sức khỏe hiện tại là báo cáo mới nhất (TX-11). Ràng buộc kiểm tra: deleted_at IS NULL OR (status = 'INACTIVE' AND vehicle_id IS NULL) (DM-25).</t>
         </is>
       </c>
     </row>
@@ -16908,7 +16982,7 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>Xe mà thiết bị đang gắn; NULL khi trong kho hoặc đã tháo. Mỗi xe gắn tối đa một thiết bị. Các xe trước lấy từ view telematic_installation_periods (DM-22). Dự kiến: khóa ngoại chuyển sang ON DELETE RESTRICT như mọi liên kết khác (hiện là SET NULL).</t>
+          <t>Xe mà thiết bị đang gắn; NULL khi trong kho hoặc đã tháo. Mỗi xe gắn tối đa một thiết bị. Các xe trước nằm trong telematic_history; view được thêm khi có tính năng đầu tiên cần (DM-27). Dự kiến: khóa ngoại chuyển sang ON DELETE RESTRICT như mọi liên kết khác (hiện là SET NULL).</t>
         </is>
       </c>
       <c r="H13" s="6" t="inlineStr">

--- a/docs/design/domain-model/domain-model.xlsx
+++ b/docs/design/domain-model/domain-model.xlsx
@@ -37,7 +37,7 @@
     <sheet name="telematics" sheetId="28" state="visible" r:id="rId28"/>
     <sheet name="telematic_history" sheetId="29" state="visible" r:id="rId29"/>
     <sheet name="telematic_status_reports" sheetId="30" state="visible" r:id="rId30"/>
-    <sheet name="vehicle_telemetry" sheetId="31" state="visible" r:id="rId31"/>
+    <sheet name="telemetry" sheetId="31" state="visible" r:id="rId31"/>
     <sheet name="drivers" sheetId="32" state="visible" r:id="rId32"/>
     <sheet name="driver_vehicle_assignments" sheetId="33" state="visible" r:id="rId33"/>
     <sheet name="driving_sessions" sheetId="34" state="visible" r:id="rId34"/>
@@ -106,7 +106,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="27" hidden="1">'telematics'!$A$7:$I$22</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="28" hidden="1">'telematic_history'!$A$7:$I$23</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="29" hidden="1">'telematic_status_reports'!$A$6:$I$19</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="30" hidden="1">'vehicle_telemetry'!$A$6:$I$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="30" hidden="1">'telemetry'!$A$6:$I$29</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="31" hidden="1">'drivers'!$A$6:$I$16</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="32" hidden="1">'driver_vehicle_assignments'!$A$6:$I$14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="33" hidden="1">'driving_sessions'!$A$6:$I$17</definedName>
@@ -1485,7 +1485,7 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="54" customHeight="1">
+    <row r="24" ht="40.5" customHeight="1">
       <c r="A24" s="6" t="inlineStr">
         <is>
           <t>13</t>
@@ -1518,7 +1518,7 @@
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>Hồ sơ của một xe tải điện: xe là gì và các quyết định về xe. Không có bảng trạng thái: mọi thứ xe báo về đi qua T-Box và được lưu từng bản tin trong vehicle_telemetry. Ràng buộc kiểm tra: deleted_at IS NULL OR status = 'INACTIVE' (DM-25).</t>
+          <t>Hồ sơ của một xe tải điện: xe là gì và các quyết định về xe. Không có bảng trạng thái: mọi thứ xe báo về đi qua T-Box và được lưu từng bản tin trong telemetry. Ràng buộc kiểm tra: deleted_at IS NULL OR status = 'INACTIVE' (DM-25).</t>
         </is>
       </c>
       <c r="H24" s="6" t="n">
@@ -2174,7 +2174,7 @@
       </c>
       <c r="C41" s="7" t="inlineStr">
         <is>
-          <t>vehicle_telemetry</t>
+          <t>telemetry</t>
         </is>
       </c>
       <c r="D41" s="7" t="inlineStr">
@@ -4459,9 +4459,9 @@
     <hyperlink ref="C39" location="'telematic_status_reports'!A1"/>
     <hyperlink ref="D39" location="'telematic_status_reports'!A1"/>
     <hyperlink ref="I39" location="'telematic_status_reports'!A1"/>
-    <hyperlink ref="C41" location="'vehicle_telemetry'!A1"/>
-    <hyperlink ref="D41" location="'vehicle_telemetry'!A1"/>
-    <hyperlink ref="I41" location="'vehicle_telemetry'!A1"/>
+    <hyperlink ref="C41" location="'telemetry'!A1"/>
+    <hyperlink ref="D41" location="'telemetry'!A1"/>
+    <hyperlink ref="I41" location="'telemetry'!A1"/>
     <hyperlink ref="C43" location="'drivers'!A1"/>
     <hyperlink ref="D43" location="'drivers'!A1"/>
     <hyperlink ref="I43" location="'drivers'!A1"/>
@@ -8308,7 +8308,7 @@
     <row r="4">
       <c r="A4" s="11" t="inlineStr">
         <is>
-          <t>Hồ sơ của một xe tải điện: xe là gì và các quyết định về xe. Không có bảng trạng thái: mọi thứ xe báo về đi qua T-Box và được lưu từng bản tin trong vehicle_telemetry. Ràng buộc kiểm tra: deleted_at IS NULL OR status = 'INACTIVE' (DM-25).</t>
+          <t>Hồ sơ của một xe tải điện: xe là gì và các quyết định về xe. Không có bảng trạng thái: mọi thứ xe báo về đi qua T-Box và được lưu từng bản tin trong telemetry. Ràng buộc kiểm tra: deleted_at IS NULL OR status = 'INACTIVE' (DM-25).</t>
         </is>
       </c>
     </row>
@@ -8805,7 +8805,7 @@
       <c r="F19" s="6" t="n"/>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>[Sẽ bỏ: VH-06] Tiến độ kích hoạt thiết bị, thang một chiều không phản ánh việc T-Box bị tháo. Thay bằng tính toán: có thiết bị hiện tại từ telematics, đã nhận dữ liệu từ vehicle_telemetry.</t>
+          <t>[Sẽ bỏ: VH-06] Tiến độ kích hoạt thiết bị, thang một chiều không phản ánh việc T-Box bị tháo. Thay bằng tính toán: có thiết bị hiện tại từ telematics, đã nhận dữ liệu từ telemetry.</t>
         </is>
       </c>
       <c r="H19" s="6" t="inlineStr">
@@ -9149,7 +9149,7 @@
       <c r="A38" s="6" t="n"/>
       <c r="B38" s="7" t="inlineStr">
         <is>
-          <t>vehicle_telemetry</t>
+          <t>telemetry</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
@@ -9324,7 +9324,7 @@
     <hyperlink ref="B35" location="'batteries'!A1"/>
     <hyperlink ref="B36" location="'warranties'!A1"/>
     <hyperlink ref="B37" location="'telematics'!A1"/>
-    <hyperlink ref="B38" location="'vehicle_telemetry'!A1"/>
+    <hyperlink ref="B38" location="'telemetry'!A1"/>
     <hyperlink ref="B39" location="'driver_vehicle_assignments'!A1"/>
     <hyperlink ref="B40" location="'driving_sessions'!A1"/>
     <hyperlink ref="B41" location="'fleet_vehicle_memberships'!A1"/>
@@ -10866,7 +10866,7 @@
       <c r="A36" s="6" t="n"/>
       <c r="B36" s="7" t="inlineStr">
         <is>
-          <t>vehicle_telemetry</t>
+          <t>telemetry</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
@@ -11216,7 +11216,7 @@
     <hyperlink ref="B33" location="'vehicles'!A1"/>
     <hyperlink ref="B34" location="'batteries'!A1"/>
     <hyperlink ref="B35" location="'telematics'!A1"/>
-    <hyperlink ref="B36" location="'vehicle_telemetry'!A1"/>
+    <hyperlink ref="B36" location="'telemetry'!A1"/>
     <hyperlink ref="B37" location="'drivers'!A1"/>
     <hyperlink ref="B38" location="'driver_vehicle_assignments'!A1"/>
     <hyperlink ref="B39" location="'driving_sessions'!A1"/>
@@ -17505,7 +17505,7 @@
       <c r="A36" s="6" t="n"/>
       <c r="B36" s="7" t="inlineStr">
         <is>
-          <t>vehicle_telemetry</t>
+          <t>telemetry</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
@@ -17536,7 +17536,7 @@
     <hyperlink ref="F13" location="'vehicles'!A1"/>
     <hyperlink ref="B34" location="'warranties'!A1"/>
     <hyperlink ref="B35" location="'telematic_status_reports'!A1"/>
-    <hyperlink ref="B36" location="'vehicle_telemetry'!A1"/>
+    <hyperlink ref="B36" location="'telemetry'!A1"/>
     <hyperlink ref="B37" location="'telematic_history'!A1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -19638,7 +19638,7 @@
     <row r="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>20. vehicle_telemetry: Dữ liệu vận hành xe</t>
+          <t>20. telemetry: Dữ liệu vận hành xe</t>
         </is>
       </c>
     </row>
@@ -20531,7 +20531,7 @@
       <c r="A32" s="6" t="n"/>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>ix_vehicle_telemetry_vehicle_time</t>
+          <t>ix_telemetry_vehicle_time</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
@@ -20551,7 +20551,7 @@
       <c r="A33" s="6" t="n"/>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>ix_vehicle_telemetry_vehicle_received</t>
+          <t>ix_telemetry_vehicle_received</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
@@ -20575,7 +20575,7 @@
       <c r="A34" s="6" t="n"/>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>ix_vehicle_telemetry_message_uuid</t>
+          <t>ix_telemetry_message_uuid</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">

--- a/docs/design/domain-model/domain-model.xlsx
+++ b/docs/design/domain-model/domain-model.xlsx
@@ -2161,7 +2161,7 @@
         </is>
       </c>
     </row>
-    <row r="41" ht="40.5" customHeight="1">
+    <row r="41" ht="54" customHeight="1">
       <c r="A41" s="6" t="inlineStr">
         <is>
           <t>20</t>
@@ -2194,7 +2194,7 @@
       </c>
       <c r="G41" s="6" t="inlineStr">
         <is>
-          <t>Một bản ghi dữ liệu xe gửi về, mỗi 5-10 giây một bản ghi cho mỗi xe: bảng lớn nhất hệ thống.</t>
+          <t>Một bản ghi dữ liệu xe gửi về, mỗi 5-10 giây một bản ghi cho mỗi xe: bảng lớn nhất hệ thống. Một tín hiệu chỉ trở thành cột riêng khi có tính năng truy vấn nó; trước đó vẫn nằm trong raw_payload, nơi lưu nguyên vẹn mọi bản tin (TM-16). Mọi dòng đều được giữ; hiện chưa xóa hay nén dữ liệu cũ (TM-17).</t>
         </is>
       </c>
       <c r="H41" s="6" t="n">
@@ -19659,7 +19659,7 @@
     <row r="4">
       <c r="A4" s="11" t="inlineStr">
         <is>
-          <t>Một bản ghi dữ liệu xe gửi về, mỗi 5-10 giây một bản ghi cho mỗi xe: bảng lớn nhất hệ thống.</t>
+          <t>Một bản ghi dữ liệu xe gửi về, mỗi 5-10 giây một bản ghi cho mỗi xe: bảng lớn nhất hệ thống. Một tín hiệu chỉ trở thành cột riêng khi có tính năng truy vấn nó; trước đó vẫn nằm trong raw_payload, nơi lưu nguyên vẹn mọi bản tin (TM-16). Mọi dòng đều được giữ; hiện chưa xóa hay nén dữ liệu cũ (TM-17).</t>
         </is>
       </c>
     </row>
@@ -19801,7 +19801,7 @@
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>có</t>
+          <t>không</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
@@ -19923,7 +19923,7 @@
       <c r="F12" s="6" t="n"/>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>Serial thiết bị, chép vào dòng để phục vụ kiểm tra và gỡ lỗi.</t>
+          <t>[Sẽ bỏ: TM-16] Serial thiết bị, chép vào dòng để phục vụ kiểm tra và gỡ lỗi.</t>
         </is>
       </c>
       <c r="H12" s="6" t="inlineStr">
@@ -20046,7 +20046,7 @@
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>speed</t>
+          <t>speed_kmh</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
@@ -20063,7 +20063,7 @@
       <c r="F16" s="6" t="n"/>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>Tốc độ (km/h).</t>
+          <t>[Hiện tên là speed, sẽ đổi tên] Tốc độ (km/h).</t>
         </is>
       </c>
       <c r="H16" s="6" t="inlineStr">
@@ -20079,7 +20079,7 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>heading</t>
+          <t>heading_degrees</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
@@ -20096,7 +20096,7 @@
       <c r="F17" s="6" t="n"/>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>Hướng di chuyển (độ, 0-360, 0 = hướng bắc); NULL nếu không rõ.</t>
+          <t>[Hiện tên là heading, sẽ đổi tên] Hướng di chuyển (độ, 0-360, 0 = hướng bắc); NULL nếu không rõ.</t>
         </is>
       </c>
       <c r="H17" s="6" t="inlineStr">
@@ -20106,13 +20106,13 @@
       </c>
       <c r="I17" s="6" t="n"/>
     </row>
-    <row r="18">
+    <row r="18" ht="27" customHeight="1">
       <c r="A18" s="6" t="n">
         <v>12</v>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>soc</t>
+          <t>soc_percent</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
@@ -20129,7 +20129,7 @@
       <c r="F18" s="6" t="n"/>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>Mức pin còn lại (SOC), % (0-100).</t>
+          <t>[Hiện tên là soc, sẽ đổi tên] Mức pin còn lại (SOC), % (0-100).</t>
         </is>
       </c>
       <c r="H18" s="6" t="inlineStr">
@@ -20139,13 +20139,13 @@
       </c>
       <c r="I18" s="6" t="n"/>
     </row>
-    <row r="19">
+    <row r="19" ht="27" customHeight="1">
       <c r="A19" s="6" t="n">
         <v>13</v>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>battery_voltage</t>
+          <t>battery_voltage_v</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
@@ -20162,7 +20162,7 @@
       <c r="F19" s="6" t="n"/>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>Điện áp pack pin (V).</t>
+          <t>[Hiện tên là battery_voltage, sẽ đổi tên] Điện áp pack pin (V).</t>
         </is>
       </c>
       <c r="H19" s="6" t="inlineStr">
@@ -20172,13 +20172,13 @@
       </c>
       <c r="I19" s="6" t="n"/>
     </row>
-    <row r="20">
+    <row r="20" ht="27" customHeight="1">
       <c r="A20" s="6" t="n">
         <v>14</v>
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>battery_current</t>
+          <t>battery_current_a</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
@@ -20195,7 +20195,7 @@
       <c r="F20" s="6" t="n"/>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>Dòng điện pack pin (A).</t>
+          <t>[Hiện tên là battery_current, sẽ đổi tên] Dòng điện pack pin (A).</t>
         </is>
       </c>
       <c r="H20" s="6" t="inlineStr">
@@ -20205,13 +20205,13 @@
       </c>
       <c r="I20" s="6" t="n"/>
     </row>
-    <row r="21">
+    <row r="21" ht="27" customHeight="1">
       <c r="A21" s="6" t="n">
         <v>15</v>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>battery_temperature</t>
+          <t>battery_temperature_celsius</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
@@ -20228,7 +20228,7 @@
       <c r="F21" s="6" t="n"/>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>Nhiệt độ pin (°C).</t>
+          <t>[Hiện tên là battery_temperature, sẽ đổi tên] Nhiệt độ pin (°C).</t>
         </is>
       </c>
       <c r="H21" s="6" t="inlineStr">
@@ -20304,13 +20304,13 @@
       </c>
       <c r="I23" s="6" t="n"/>
     </row>
-    <row r="24">
+    <row r="24" ht="27" customHeight="1">
       <c r="A24" s="6" t="n">
         <v>18</v>
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>motor_temperature</t>
+          <t>motor_temperature_celsius</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
@@ -20327,7 +20327,7 @@
       <c r="F24" s="6" t="n"/>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>Nhiệt độ động cơ (°C).</t>
+          <t>[Hiện tên là motor_temperature, sẽ đổi tên] Nhiệt độ động cơ (°C).</t>
         </is>
       </c>
       <c r="H24" s="6" t="inlineStr">
@@ -20337,13 +20337,13 @@
       </c>
       <c r="I24" s="6" t="n"/>
     </row>
-    <row r="25">
+    <row r="25" ht="27" customHeight="1">
       <c r="A25" s="6" t="n">
         <v>19</v>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>odometer</t>
+          <t>odometer_km</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
@@ -20360,7 +20360,7 @@
       <c r="F25" s="6" t="n"/>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>Tổng quãng đường đã chạy (km).</t>
+          <t>[Hiện tên là odometer, sẽ đổi tên] Tổng quãng đường đã chạy (km).</t>
         </is>
       </c>
       <c r="H25" s="6" t="inlineStr">
@@ -20370,13 +20370,13 @@
       </c>
       <c r="I25" s="6" t="n"/>
     </row>
-    <row r="26">
+    <row r="26" ht="27" customHeight="1">
       <c r="A26" s="6" t="n">
         <v>20</v>
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>signal_strength</t>
+          <t>signal_dbm</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
@@ -20393,7 +20393,7 @@
       <c r="F26" s="6" t="n"/>
       <c r="G26" s="6" t="inlineStr">
         <is>
-          <t>Cường độ sóng di động (dBm).</t>
+          <t>[Hiện tên là signal_strength, sẽ đổi tên] Cường độ sóng di động (dBm).</t>
         </is>
       </c>
       <c r="H26" s="6" t="inlineStr">
@@ -20595,7 +20595,7 @@
       <c r="A35" s="6" t="n"/>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>uq_telematic_recorded_at</t>
+          <t>uq_telemetry_telematic_recorded_at</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">

--- a/docs/design/domain-model/domain-model.xlsx
+++ b/docs/design/domain-model/domain-model.xlsx
@@ -2308,7 +2308,7 @@
       </c>
       <c r="G44" s="6" t="inlineStr">
         <is>
-          <t>Tài xế nào lái xe nào, trong khoảng thời gian nào (lịch sử mở/đóng). Sẽ bị bỏ: được thay bằng driving_sessions (DR-07) và xóa khi tái cấu trúc; không có dữ liệu thật cần chuyển.</t>
+          <t>[Sẽ bỏ] Tài xế nào lái xe nào, trong khoảng thời gian nào (lịch sử mở/đóng). Sẽ bị bỏ: được thay bằng driving_sessions (DR-07) và xóa khi tái cấu trúc; không có dữ liệu thật cần chuyển.</t>
         </is>
       </c>
       <c r="H44" s="6" t="n">

--- a/docs/design/domain-model/domain-model.xlsx
+++ b/docs/design/domain-model/domain-model.xlsx
@@ -20547,7 +20547,7 @@
       <c r="E32" s="6" t="n"/>
       <c r="F32" s="6" t="n"/>
     </row>
-    <row r="33" ht="108" customHeight="1">
+    <row r="33" ht="54" customHeight="1">
       <c r="A33" s="6" t="n"/>
       <c r="B33" s="6" t="inlineStr">
         <is>
@@ -20567,7 +20567,7 @@
       <c r="E33" s="6" t="n"/>
       <c r="F33" s="6" t="inlineStr">
         <is>
-          <t>Last time the backend heard from a vehicle (F-J1/F-J3 device-health monitor); uses the receive clock, which a skewed device clock cannot move. @vi Lần cuối backend nhận dữ liệu từ xe (giám sát thiết bị F-J1/F-J3); dùng đồng hồ nhận của backend, không bị lệch giờ thiết bị làm sai.</t>
+          <t>Lần cuối backend nhận dữ liệu từ xe (giám sát thiết bị F-J1/F-J3); dùng đồng hồ nhận của backend, không bị lệch giờ thiết bị làm sai.</t>
         </is>
       </c>
     </row>

--- a/docs/design/domain-model/domain-model.xlsx
+++ b/docs/design/domain-model/domain-model.xlsx
@@ -19826,13 +19826,13 @@
       </c>
       <c r="I9" s="6" t="n"/>
     </row>
-    <row r="10">
+    <row r="10" ht="27" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>4</v>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>message_uuid</t>
+          <t>device_message_id</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
@@ -19849,7 +19849,7 @@
       <c r="F10" s="6" t="n"/>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>Mã thiết bị gán cho mỗi bản tin, dùng để phát hiện trùng.</t>
+          <t>[Hiện tên là message_uuid, sẽ đổi tên] Mã thiết bị gán cho mỗi bản tin, dùng để phát hiện trùng.</t>
         </is>
       </c>
       <c r="H10" s="6" t="inlineStr">
@@ -20575,12 +20575,12 @@
       <c r="A34" s="6" t="n"/>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>ix_telemetry_message_uuid</t>
+          <t>ix_telemetry_device_message_id</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>message_uuid</t>
+          <t>device_message_id</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">

--- a/docs/design/domain-model/domain-model.xlsx
+++ b/docs/design/domain-model/domain-model.xlsx
@@ -39,42 +39,43 @@
     <sheet name="telematic_status_reports" sheetId="30" state="visible" r:id="rId30"/>
     <sheet name="telemetry" sheetId="31" state="visible" r:id="rId31"/>
     <sheet name="drivers" sheetId="32" state="visible" r:id="rId32"/>
-    <sheet name="driver_vehicle_assignments" sheetId="33" state="visible" r:id="rId33"/>
-    <sheet name="driving_sessions" sheetId="34" state="visible" r:id="rId34"/>
-    <sheet name="charging_credentials" sheetId="35" state="visible" r:id="rId35"/>
-    <sheet name="fleets" sheetId="36" state="visible" r:id="rId36"/>
-    <sheet name="fleet_vehicle_memberships" sheetId="37" state="visible" r:id="rId37"/>
-    <sheet name="geofences" sheetId="38" state="visible" r:id="rId38"/>
-    <sheet name="fleet_user_assignments" sheetId="39" state="visible" r:id="rId39"/>
-    <sheet name="charging_stations" sheetId="40" state="visible" r:id="rId40"/>
-    <sheet name="charging_evses" sheetId="41" state="visible" r:id="rId41"/>
-    <sheet name="charging_connectors" sheetId="42" state="visible" r:id="rId42"/>
-    <sheet name="charging_ocpp_messages" sheetId="43" state="visible" r:id="rId43"/>
-    <sheet name="charging_station_config_entries" sheetId="44" state="visible" r:id="rId44"/>
-    <sheet name="charging_reservations" sheetId="45" state="visible" r:id="rId45"/>
-    <sheet name="charging_sessions" sheetId="46" state="visible" r:id="rId46"/>
-    <sheet name="charging_session_events" sheetId="47" state="visible" r:id="rId47"/>
-    <sheet name="charging_session_measurements" sheetId="48" state="visible" r:id="rId48"/>
-    <sheet name="notifications" sheetId="49" state="visible" r:id="rId49"/>
-    <sheet name="support_cases" sheetId="50" state="visible" r:id="rId50"/>
-    <sheet name="repair_partners" sheetId="51" state="visible" r:id="rId51"/>
-    <sheet name="maintenance_bookings" sheetId="52" state="visible" r:id="rId52"/>
-    <sheet name="charging_policies" sheetId="53" state="visible" r:id="rId53"/>
-    <sheet name="charging_policy_versions" sheetId="54" state="visible" r:id="rId54"/>
-    <sheet name="charging_policy_assignments" sheetId="55" state="visible" r:id="rId55"/>
-    <sheet name="policy_violations" sheetId="56" state="visible" r:id="rId56"/>
-    <sheet name="tariffs" sheetId="57" state="visible" r:id="rId57"/>
-    <sheet name="payments" sheetId="58" state="visible" r:id="rId58"/>
-    <sheet name="wallets" sheetId="59" state="visible" r:id="rId59"/>
-    <sheet name="wallet_transactions" sheetId="60" state="visible" r:id="rId60"/>
-    <sheet name="invoices" sheetId="61" state="visible" r:id="rId61"/>
-    <sheet name="invoice_lines" sheetId="62" state="visible" r:id="rId62"/>
-    <sheet name="subscription_plans" sheetId="63" state="visible" r:id="rId63"/>
-    <sheet name="plan_features" sheetId="64" state="visible" r:id="rId64"/>
-    <sheet name="subscriptions" sheetId="65" state="visible" r:id="rId65"/>
-    <sheet name="driver_scores" sheetId="66" state="visible" r:id="rId66"/>
-    <sheet name="promotion_campaigns" sheetId="67" state="visible" r:id="rId67"/>
-    <sheet name="trips" sheetId="68" state="visible" r:id="rId68"/>
+    <sheet name="driver_history" sheetId="33" state="visible" r:id="rId33"/>
+    <sheet name="driver_vehicle_assignments" sheetId="34" state="visible" r:id="rId34"/>
+    <sheet name="driving_sessions" sheetId="35" state="visible" r:id="rId35"/>
+    <sheet name="charging_credentials" sheetId="36" state="visible" r:id="rId36"/>
+    <sheet name="fleets" sheetId="37" state="visible" r:id="rId37"/>
+    <sheet name="fleet_vehicle_memberships" sheetId="38" state="visible" r:id="rId38"/>
+    <sheet name="geofences" sheetId="39" state="visible" r:id="rId39"/>
+    <sheet name="fleet_user_assignments" sheetId="40" state="visible" r:id="rId40"/>
+    <sheet name="charging_stations" sheetId="41" state="visible" r:id="rId41"/>
+    <sheet name="charging_evses" sheetId="42" state="visible" r:id="rId42"/>
+    <sheet name="charging_connectors" sheetId="43" state="visible" r:id="rId43"/>
+    <sheet name="charging_ocpp_messages" sheetId="44" state="visible" r:id="rId44"/>
+    <sheet name="charging_station_config_entries" sheetId="45" state="visible" r:id="rId45"/>
+    <sheet name="charging_reservations" sheetId="46" state="visible" r:id="rId46"/>
+    <sheet name="charging_sessions" sheetId="47" state="visible" r:id="rId47"/>
+    <sheet name="charging_session_events" sheetId="48" state="visible" r:id="rId48"/>
+    <sheet name="charging_session_measurements" sheetId="49" state="visible" r:id="rId49"/>
+    <sheet name="notifications" sheetId="50" state="visible" r:id="rId50"/>
+    <sheet name="support_cases" sheetId="51" state="visible" r:id="rId51"/>
+    <sheet name="repair_partners" sheetId="52" state="visible" r:id="rId52"/>
+    <sheet name="maintenance_bookings" sheetId="53" state="visible" r:id="rId53"/>
+    <sheet name="charging_policies" sheetId="54" state="visible" r:id="rId54"/>
+    <sheet name="charging_policy_versions" sheetId="55" state="visible" r:id="rId55"/>
+    <sheet name="charging_policy_assignments" sheetId="56" state="visible" r:id="rId56"/>
+    <sheet name="policy_violations" sheetId="57" state="visible" r:id="rId57"/>
+    <sheet name="tariffs" sheetId="58" state="visible" r:id="rId58"/>
+    <sheet name="payments" sheetId="59" state="visible" r:id="rId59"/>
+    <sheet name="wallets" sheetId="60" state="visible" r:id="rId60"/>
+    <sheet name="wallet_transactions" sheetId="61" state="visible" r:id="rId61"/>
+    <sheet name="invoices" sheetId="62" state="visible" r:id="rId62"/>
+    <sheet name="invoice_lines" sheetId="63" state="visible" r:id="rId63"/>
+    <sheet name="subscription_plans" sheetId="64" state="visible" r:id="rId64"/>
+    <sheet name="plan_features" sheetId="65" state="visible" r:id="rId65"/>
+    <sheet name="subscriptions" sheetId="66" state="visible" r:id="rId66"/>
+    <sheet name="driver_scores" sheetId="67" state="visible" r:id="rId67"/>
+    <sheet name="promotion_campaigns" sheetId="68" state="visible" r:id="rId68"/>
+    <sheet name="trips" sheetId="69" state="visible" r:id="rId69"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'organizations'!$A$7:$I$20</definedName>
@@ -107,43 +108,44 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="28" hidden="1">'telematic_history'!$A$7:$I$23</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="29" hidden="1">'telematic_status_reports'!$A$6:$I$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="30" hidden="1">'telemetry'!$A$6:$I$29</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="31" hidden="1">'drivers'!$A$6:$I$16</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="32" hidden="1">'driver_vehicle_assignments'!$A$6:$I$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="33" hidden="1">'driving_sessions'!$A$6:$I$17</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="34" hidden="1">'charging_credentials'!$A$6:$I$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="35" hidden="1">'fleets'!$A$6:$I$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="36" hidden="1">'fleet_vehicle_memberships'!$A$6:$I$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="37" hidden="1">'geofences'!$A$6:$I$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="38" hidden="1">'fleet_user_assignments'!$A$6:$I$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="39" hidden="1">'charging_stations'!$A$6:$I$28</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="40" hidden="1">'charging_evses'!$A$6:$I$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="41" hidden="1">'charging_connectors'!$A$6:$I$17</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="42" hidden="1">'charging_ocpp_messages'!$A$6:$I$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="43" hidden="1">'charging_station_config_entries'!$A$6:$I$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="44" hidden="1">'charging_reservations'!$A$6:$I$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="45" hidden="1">'charging_sessions'!$A$6:$I$26</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="46" hidden="1">'charging_session_events'!$A$6:$I$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="47" hidden="1">'charging_session_measurements'!$A$6:$I$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="48" hidden="1">'notifications'!$A$6:$I$16</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="49" hidden="1">'support_cases'!$A$6:$I$28</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="50" hidden="1">'repair_partners'!$A$6:$I$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="51" hidden="1">'maintenance_bookings'!$A$6:$I$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="52" hidden="1">'charging_policies'!$A$6:$I$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="53" hidden="1">'charging_policy_versions'!$A$6:$I$16</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="54" hidden="1">'charging_policy_assignments'!$A$6:$I$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="55" hidden="1">'policy_violations'!$A$6:$I$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="56" hidden="1">'tariffs'!$A$6:$I$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="57" hidden="1">'payments'!$A$6:$I$16</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="58" hidden="1">'wallets'!$A$6:$I$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="59" hidden="1">'wallet_transactions'!$A$6:$I$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="60" hidden="1">'invoices'!$A$6:$I$16</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="61" hidden="1">'invoice_lines'!$A$6:$I$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="62" hidden="1">'subscription_plans'!$A$6:$I$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="63" hidden="1">'plan_features'!$A$6:$I$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="64" hidden="1">'subscriptions'!$A$6:$I$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="65" hidden="1">'driver_scores'!$A$6:$I$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="66" hidden="1">'promotion_campaigns'!$A$6:$I$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="67" hidden="1">'trips'!$A$6:$I$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="31" hidden="1">'drivers'!$A$7:$I$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="32" hidden="1">'driver_history'!$A$7:$I$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="33" hidden="1">'driver_vehicle_assignments'!$A$6:$I$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="34" hidden="1">'driving_sessions'!$A$6:$I$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="35" hidden="1">'charging_credentials'!$A$6:$I$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="36" hidden="1">'fleets'!$A$6:$I$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="37" hidden="1">'fleet_vehicle_memberships'!$A$6:$I$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="38" hidden="1">'geofences'!$A$6:$I$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="39" hidden="1">'fleet_user_assignments'!$A$6:$I$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="40" hidden="1">'charging_stations'!$A$6:$I$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="41" hidden="1">'charging_evses'!$A$6:$I$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="42" hidden="1">'charging_connectors'!$A$6:$I$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="43" hidden="1">'charging_ocpp_messages'!$A$6:$I$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="44" hidden="1">'charging_station_config_entries'!$A$6:$I$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="45" hidden="1">'charging_reservations'!$A$6:$I$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="46" hidden="1">'charging_sessions'!$A$6:$I$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="47" hidden="1">'charging_session_events'!$A$6:$I$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="48" hidden="1">'charging_session_measurements'!$A$6:$I$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="49" hidden="1">'notifications'!$A$6:$I$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="50" hidden="1">'support_cases'!$A$6:$I$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="51" hidden="1">'repair_partners'!$A$6:$I$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="52" hidden="1">'maintenance_bookings'!$A$6:$I$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="53" hidden="1">'charging_policies'!$A$6:$I$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="54" hidden="1">'charging_policy_versions'!$A$6:$I$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="55" hidden="1">'charging_policy_assignments'!$A$6:$I$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="56" hidden="1">'policy_violations'!$A$6:$I$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="57" hidden="1">'tariffs'!$A$6:$I$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="58" hidden="1">'payments'!$A$6:$I$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="59" hidden="1">'wallets'!$A$6:$I$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="60" hidden="1">'wallet_transactions'!$A$6:$I$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="61" hidden="1">'invoices'!$A$6:$I$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="62" hidden="1">'invoice_lines'!$A$6:$I$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="63" hidden="1">'subscription_plans'!$A$6:$I$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="64" hidden="1">'plan_features'!$A$6:$I$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="65" hidden="1">'subscriptions'!$A$6:$I$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="66" hidden="1">'driver_scores'!$A$6:$I$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="67" hidden="1">'promotion_campaigns'!$A$6:$I$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="68" hidden="1">'trips'!$A$6:$I$14</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -632,7 +634,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I110"/>
+  <dimension ref="A1:I111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -663,7 +665,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>67 bảng trong 16 miền nghiệp vụ: 56 bảng chính, 10 bảng lịch sử (N.h), 1 bảng trạng thái. Bấm vào tên bảng hoặc «→ Mở» để mở sheet chi tiết của bảng; chú giải và các quyết định còn mở nằm ở cuối trang.</t>
+          <t>68 bảng trong 16 miền nghiệp vụ: 56 bảng chính, 11 bảng lịch sử (N.h), 1 bảng trạng thái. Bấm vào tên bảng hoặc «→ Mở» để mở sheet chi tiết của bảng; chú giải và các quyết định còn mở nằm ở cuối trang.</t>
         </is>
       </c>
     </row>
@@ -2215,7 +2217,7 @@
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>4 bảng</t>
+          <t>5 bảng</t>
         </is>
       </c>
       <c r="D42" s="5" t="n"/>
@@ -2230,7 +2232,7 @@
         </is>
       </c>
     </row>
-    <row r="43">
+    <row r="43" ht="94.5" customHeight="1">
       <c r="A43" s="6" t="inlineStr">
         <is>
           <t>21</t>
@@ -2263,11 +2265,11 @@
       </c>
       <c r="G43" s="6" t="inlineStr">
         <is>
-          <t>Một tài xế do khách hàng tuyển dụng (hoặc chính là khách hàng).</t>
+          <t>Hồ sơ tài xế: các thông tin mà hệ thống dùng về công việc lái xe của một người trong một tổ chức (ID-13). Người đó là ai (họ tên, số điện thoại) nằm ở users; tổ chức được đọc qua thành viên. Người lái xe cho hai tổ chức có hai hồ sơ, và mỗi tổ chức chịu trách nhiệm về hồ sơ của mình (DR-09). Tài xế được nhận xe khi hồ sơ ACTIVE và chưa bị xóa, giấy phép chưa hết hạn, thành viên và người dùng đều ACTIVE (DR-10). Ràng buộc kiểm tra: deleted_at IS NULL OR status = 'INACTIVE' (DM-25).</t>
         </is>
       </c>
       <c r="H43" s="6" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I43" s="7" t="inlineStr">
         <is>
@@ -2278,154 +2280,199 @@
     <row r="44" ht="40.5" customHeight="1">
       <c r="A44" s="6" t="inlineStr">
         <is>
+          <t>21.h</t>
+        </is>
+      </c>
+      <c r="B44" s="6" t="inlineStr">
+        <is>
+          <t>Tài xế (drivers)</t>
+        </is>
+      </c>
+      <c r="C44" s="7" t="inlineStr">
+        <is>
+          <t>driver_history</t>
+        </is>
+      </c>
+      <c r="D44" s="7" t="inlineStr">
+        <is>
+          <t>Lịch sử tài xế</t>
+        </is>
+      </c>
+      <c r="E44" s="6" t="inlineStr">
+        <is>
+          <t>Khách hàng</t>
+        </is>
+      </c>
+      <c r="F44" s="6" t="inlineStr">
+        <is>
+          <t>F-E4</t>
+        </is>
+      </c>
+      <c r="G44" s="6" t="inlineStr">
+        <is>
+          <t>Mọi phiên bản trước đây của một dòng trong bảng drivers: bản sao toàn bộ dòng, chụp ngay trước khi thay đổi và được trigger ghi trong cùng giao dịch. Do công cụ domain-model tự sinh từ @tracked *, không bao giờ viết tay.</t>
+        </is>
+      </c>
+      <c r="H44" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="I44" s="7" t="inlineStr">
+        <is>
+          <t>→ Mở</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="40.5" customHeight="1">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="B44" s="6" t="inlineStr">
+      <c r="B45" s="6" t="inlineStr">
         <is>
           <t>Tài xế (drivers)</t>
         </is>
       </c>
-      <c r="C44" s="7" t="inlineStr">
+      <c r="C45" s="7" t="inlineStr">
         <is>
           <t>driver_vehicle_assignments</t>
         </is>
       </c>
-      <c r="D44" s="7" t="inlineStr">
+      <c r="D45" s="7" t="inlineStr">
         <is>
           <t>Phân công tài xế - xe</t>
         </is>
       </c>
-      <c r="E44" s="6" t="inlineStr">
+      <c r="E45" s="6" t="inlineStr">
         <is>
           <t>Khách hàng</t>
         </is>
       </c>
-      <c r="F44" s="6" t="inlineStr">
+      <c r="F45" s="6" t="inlineStr">
         <is>
           <t>F-E4</t>
         </is>
       </c>
-      <c r="G44" s="6" t="inlineStr">
+      <c r="G45" s="6" t="inlineStr">
         <is>
           <t>[Sẽ bỏ] Tài xế nào lái xe nào, trong khoảng thời gian nào (lịch sử mở/đóng). Sẽ bị bỏ: được thay bằng driving_sessions (DR-07) và xóa khi tái cấu trúc; không có dữ liệu thật cần chuyển.</t>
         </is>
       </c>
-      <c r="H44" s="6" t="n">
+      <c r="H45" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="I44" s="7" t="inlineStr">
+      <c r="I45" s="7" t="inlineStr">
         <is>
           <t>→ Mở</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="135" customHeight="1">
-      <c r="A45" s="6" t="inlineStr">
+    <row r="46" ht="162" customHeight="1">
+      <c r="A46" s="6" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="B45" s="6" t="inlineStr">
+      <c r="B46" s="6" t="inlineStr">
         <is>
           <t>Tài xế (drivers)</t>
         </is>
       </c>
-      <c r="C45" s="7" t="inlineStr">
+      <c r="C46" s="7" t="inlineStr">
         <is>
           <t>driving_sessions</t>
         </is>
       </c>
-      <c r="D45" s="7" t="inlineStr">
+      <c r="D46" s="7" t="inlineStr">
         <is>
           <t>Phiên lái xe</t>
         </is>
       </c>
-      <c r="E45" s="6" t="inlineStr">
+      <c r="E46" s="6" t="inlineStr">
         <is>
           <t>Khách hàng</t>
         </is>
       </c>
-      <c r="F45" s="6" t="inlineStr">
+      <c r="F46" s="6" t="inlineStr">
         <is>
           <t>F-E4</t>
         </is>
       </c>
-      <c r="G45" s="6" t="inlineStr">
-        <is>
-          <t>Ai cầm lái xe nào, trong khoảng thời gian nào (DR-07): tài xế nhận xe bằng cách quét mã QR trên xe hoặc chọn xe ở gần trên ứng dụng, hoặc quản lý nhận xe giúp trên portal. Thay thế driver_vehicle_assignments. Phiên kết thúc khi tài xế trả xe, tài xế khác nhận xe, tài xế nhận xe khác, hoặc xe không di chuyển quá thời gian tự kết thúc của tổ chức (organization_settings). Các sự kiện cần biết tài xế (điểm, chuyến, phiên sạc) lấy tài xế từ đây. Cảnh báo cho tài xế gửi tới tài xế đang nhận xe và portal; xe chạy mà không ai nhận xe sẽ cảnh báo lên portal. Tổ chức sở hữu xe và chính tài xế (trên ứng dụng) xem được phiên lái; tổ chức tuyển dụng tài xế không xem được phiên lái trên xe của tổ chức khác (DR-08). Dòng đã đóng không bao giờ bị sửa nên không cần lịch sử thay đổi.</t>
-        </is>
-      </c>
-      <c r="H45" s="6" t="n">
+      <c r="G46" s="6" t="inlineStr">
+        <is>
+          <t>Ai cầm lái xe nào, trong khoảng thời gian nào (DR-07): tài xế nhận xe bằng cách quét mã QR trên xe hoặc chọn xe ở gần trên ứng dụng, hoặc quản lý nhận xe giúp trên portal. Thay thế driver_vehicle_assignments. Phiên kết thúc khi tài xế trả xe, tài xế khác nhận xe, tài xế nhận xe khác, hoặc xe không di chuyển quá thời gian tự kết thúc của tổ chức (organization_settings). Các sự kiện cần biết tài xế (điểm, chuyến, phiên sạc) lấy tài xế từ đây. Cảnh báo cho tài xế gửi tới tài xế đang nhận xe và portal; xe chạy mà không ai nhận xe sẽ cảnh báo lên portal. Tổ chức sở hữu xe xem đầy đủ phiên lái; tài xế chỉ xem bản tóm tắt các phiên của mình trên ứng dụng (thời gian, xe, thời lượng, quãng đường; không có lộ trình hay địa điểm, không xuất dữ liệu), và tổ chức tuyển dụng tài xế không xem được phiên lái trên xe của tổ chức khác (DR-08, DR-11). Dòng đã đóng không bao giờ bị sửa nên không cần lịch sử thay đổi.</t>
+        </is>
+      </c>
+      <c r="H46" s="6" t="n">
         <v>11</v>
       </c>
-      <c r="I45" s="7" t="inlineStr">
+      <c r="I46" s="7" t="inlineStr">
         <is>
           <t>→ Mở</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="27" customHeight="1">
-      <c r="A46" s="6" t="inlineStr">
+    <row r="47" ht="27" customHeight="1">
+      <c r="A47" s="6" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="B46" s="6" t="inlineStr">
+      <c r="B47" s="6" t="inlineStr">
         <is>
           <t>Tài xế (drivers)</t>
         </is>
       </c>
-      <c r="C46" s="7" t="inlineStr">
+      <c r="C47" s="7" t="inlineStr">
         <is>
           <t>charging_credentials</t>
         </is>
       </c>
-      <c r="D46" s="7" t="inlineStr">
+      <c r="D47" s="7" t="inlineStr">
         <is>
           <t>Phương thức xác thực sạc</t>
         </is>
       </c>
-      <c r="E46" s="6" t="inlineStr">
+      <c r="E47" s="6" t="inlineStr">
         <is>
           <t>Khách hàng</t>
         </is>
       </c>
-      <c r="F46" s="6" t="inlineStr">
+      <c r="F47" s="6" t="inlineStr">
         <is>
           <t>F-B2, F-C6, F-H1</t>
         </is>
       </c>
-      <c r="G46" s="6" t="inlineStr">
+      <c r="G47" s="6" t="inlineStr">
         <is>
           <t>Cách trụ sạc nhận biết ai đang sạc. Nối mã idTag thô của phiên sạc với tài xế và tổ chức. Việc đặt ở miền Tài xế là tạm thời.</t>
         </is>
       </c>
-      <c r="H46" s="6" t="n">
+      <c r="H47" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="I46" s="7" t="inlineStr">
+      <c r="I47" s="7" t="inlineStr">
         <is>
           <t>→ Mở</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="148.5" customHeight="1">
-      <c r="A47" s="5" t="n"/>
-      <c r="B47" s="5" t="inlineStr">
+    <row r="48" ht="148.5" customHeight="1">
+      <c r="A48" s="5" t="n"/>
+      <c r="B48" s="5" t="inlineStr">
         <is>
           <t>Đội xe (fleet)</t>
         </is>
       </c>
-      <c r="C47" s="5" t="inlineStr">
+      <c r="C48" s="5" t="inlineStr">
         <is>
           <t>4 bảng</t>
         </is>
       </c>
-      <c r="D47" s="5" t="n"/>
-      <c r="E47" s="5" t="n"/>
-      <c r="F47" s="5" t="n"/>
-      <c r="G47" s="5" t="inlineStr">
+      <c r="D48" s="5" t="n"/>
+      <c r="E48" s="5" t="n"/>
+      <c r="F48" s="5" t="n"/>
+      <c r="G48" s="5" t="inlineStr">
         <is>
           <t>Nhóm xe do một quản lý đội xe điều hành.
 • Một đội xe là một nhóm bên trong một tổ chức và có thể nằm dưới một đội xe khác, nên mỗi khách hàng tự mô tả cơ cấu của mình (miền &gt; chi nhánh &gt; bãi xe...) bằng dữ liệu.
@@ -2435,130 +2482,85 @@
         </is>
       </c>
     </row>
-    <row r="48" ht="54" customHeight="1">
-      <c r="A48" s="6" t="inlineStr">
+    <row r="49" ht="54" customHeight="1">
+      <c r="A49" s="6" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="B48" s="6" t="inlineStr">
+      <c r="B49" s="6" t="inlineStr">
         <is>
           <t>Đội xe (fleet)</t>
         </is>
       </c>
-      <c r="C48" s="7" t="inlineStr">
+      <c r="C49" s="7" t="inlineStr">
         <is>
           <t>fleets</t>
         </is>
       </c>
-      <c r="D48" s="7" t="inlineStr">
+      <c r="D49" s="7" t="inlineStr">
         <is>
           <t>Đội xe</t>
         </is>
       </c>
-      <c r="E48" s="6" t="inlineStr">
+      <c r="E49" s="6" t="inlineStr">
         <is>
           <t>Khách hàng</t>
         </is>
       </c>
-      <c r="F48" s="6" t="inlineStr">
+      <c r="F49" s="6" t="inlineStr">
         <is>
           <t>F-E1</t>
         </is>
       </c>
-      <c r="G48" s="6" t="inlineStr">
+      <c r="G49" s="6" t="inlineStr">
         <is>
           <t>Một nhóm xe có tên bên trong một tổ chức: một nút trong cơ cấu riêng của khách hàng (miền, chi nhánh, bãi xe, nhóm - tên tùy ý, không giới hạn số cấp, qua parent_fleet_id). Tái cơ cấu chỉ là sửa dữ liệu, không bao giờ phải đổi thiết kế.</t>
         </is>
       </c>
-      <c r="H48" s="6" t="n">
+      <c r="H49" s="6" t="n">
         <v>9</v>
       </c>
-      <c r="I48" s="7" t="inlineStr">
+      <c r="I49" s="7" t="inlineStr">
         <is>
           <t>→ Mở</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="6" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="6" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="B49" s="6" t="inlineStr">
+      <c r="B50" s="6" t="inlineStr">
         <is>
           <t>Đội xe (fleet)</t>
         </is>
       </c>
-      <c r="C49" s="7" t="inlineStr">
+      <c r="C50" s="7" t="inlineStr">
         <is>
           <t>fleet_vehicle_memberships</t>
         </is>
       </c>
-      <c r="D49" s="7" t="inlineStr">
+      <c r="D50" s="7" t="inlineStr">
         <is>
           <t>Thành viên đội xe</t>
         </is>
       </c>
-      <c r="E49" s="6" t="inlineStr">
+      <c r="E50" s="6" t="inlineStr">
         <is>
           <t>Khách hàng</t>
         </is>
       </c>
-      <c r="F49" s="6" t="inlineStr">
+      <c r="F50" s="6" t="inlineStr">
         <is>
           <t>F-E1</t>
         </is>
       </c>
-      <c r="G49" s="6" t="inlineStr">
+      <c r="G50" s="6" t="inlineStr">
         <is>
           <t>Xe nào thuộc đội nào, trong khoảng thời gian nào (lịch sử mở/đóng).</t>
-        </is>
-      </c>
-      <c r="H49" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="I49" s="7" t="inlineStr">
-        <is>
-          <t>→ Mở</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="27" customHeight="1">
-      <c r="A50" s="6" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="B50" s="6" t="inlineStr">
-        <is>
-          <t>Đội xe (fleet)</t>
-        </is>
-      </c>
-      <c r="C50" s="7" t="inlineStr">
-        <is>
-          <t>geofences</t>
-        </is>
-      </c>
-      <c r="D50" s="7" t="inlineStr">
-        <is>
-          <t>Vùng địa lý (geofence)</t>
-        </is>
-      </c>
-      <c r="E50" s="6" t="inlineStr">
-        <is>
-          <t>Khách hàng</t>
-        </is>
-      </c>
-      <c r="F50" s="6" t="inlineStr">
-        <is>
-          <t>F-A5</t>
-        </is>
-      </c>
-      <c r="G50" s="6" t="inlineStr">
-        <is>
-          <t>Một khu vực mà khi xe thuộc đội xe đi vào hoặc ra sẽ phát cảnh báo. Gắn với đội xe cho đến khi có tổ chức khách hàng (sau đó chuyển sang tổ chức).</t>
         </is>
       </c>
       <c r="H50" s="6" t="n">
@@ -2570,67 +2572,112 @@
         </is>
       </c>
     </row>
-    <row r="51" ht="67.5" customHeight="1">
+    <row r="51" ht="27" customHeight="1">
       <c r="A51" s="6" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B51" s="6" t="inlineStr">
+        <is>
+          <t>Đội xe (fleet)</t>
+        </is>
+      </c>
+      <c r="C51" s="7" t="inlineStr">
+        <is>
+          <t>geofences</t>
+        </is>
+      </c>
+      <c r="D51" s="7" t="inlineStr">
+        <is>
+          <t>Vùng địa lý (geofence)</t>
+        </is>
+      </c>
+      <c r="E51" s="6" t="inlineStr">
+        <is>
+          <t>Khách hàng</t>
+        </is>
+      </c>
+      <c r="F51" s="6" t="inlineStr">
+        <is>
+          <t>F-A5</t>
+        </is>
+      </c>
+      <c r="G51" s="6" t="inlineStr">
+        <is>
+          <t>Một khu vực mà khi xe thuộc đội xe đi vào hoặc ra sẽ phát cảnh báo. Gắn với đội xe cho đến khi có tổ chức khách hàng (sau đó chuyển sang tổ chức).</t>
+        </is>
+      </c>
+      <c r="H51" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="I51" s="7" t="inlineStr">
+        <is>
+          <t>→ Mở</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="67.5" customHeight="1">
+      <c r="A52" s="6" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="B51" s="6" t="inlineStr">
+      <c r="B52" s="6" t="inlineStr">
         <is>
           <t>Đội xe (fleet)</t>
         </is>
       </c>
-      <c r="C51" s="7" t="inlineStr">
+      <c r="C52" s="7" t="inlineStr">
         <is>
           <t>fleet_user_assignments</t>
         </is>
       </c>
-      <c r="D51" s="7" t="inlineStr">
+      <c r="D52" s="7" t="inlineStr">
         <is>
           <t>Phân công người dùng - đội xe</t>
         </is>
       </c>
-      <c r="E51" s="6" t="inlineStr">
+      <c r="E52" s="6" t="inlineStr">
         <is>
           <t>Khách hàng</t>
         </is>
       </c>
-      <c r="F51" s="6" t="inlineStr">
+      <c r="F52" s="6" t="inlineStr">
         <is>
           <t>F-F1, F-E1</t>
         </is>
       </c>
-      <c r="G51" s="6" t="inlineStr">
+      <c r="G52" s="6" t="inlineStr">
         <is>
           <t>Giới hạn vai trò cấp đội xe của một người dùng trong một số đội xe của tổ chức lớn (ví dụ một quản lý cho đội Hà Nội, một quản lý khác cho đội TP.HCM). Người dùng không có dòng nào đang hiệu lực ở đây thì quản lý mọi đội xe của tổ chức. Nằm ở miền Đội xe, không ở miền Danh tính, để miền Danh tính không phụ thuộc miền nào.</t>
         </is>
       </c>
-      <c r="H51" s="6" t="n">
+      <c r="H52" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="I51" s="7" t="inlineStr">
+      <c r="I52" s="7" t="inlineStr">
         <is>
           <t>→ Mở</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="67.5" customHeight="1">
-      <c r="A52" s="5" t="n"/>
-      <c r="B52" s="5" t="inlineStr">
+    <row r="53" ht="67.5" customHeight="1">
+      <c r="A53" s="5" t="n"/>
+      <c r="B53" s="5" t="inlineStr">
         <is>
           <t>Trạm sạc (charging_stations)</t>
         </is>
       </c>
-      <c r="C52" s="5" t="inlineStr">
+      <c r="C53" s="5" t="inlineStr">
         <is>
           <t>6 bảng</t>
         </is>
       </c>
-      <c r="D52" s="5" t="n"/>
-      <c r="E52" s="5" t="n"/>
-      <c r="F52" s="5" t="n"/>
-      <c r="G52" s="5" t="inlineStr">
+      <c r="D53" s="5" t="n"/>
+      <c r="E53" s="5" t="n"/>
+      <c r="F53" s="5" t="n"/>
+      <c r="G53" s="5" t="inlineStr">
         <is>
           <t>Mạng lưới trạm sạc của G3 và kết nối OCPP tới từng trụ sạc.
 • Một trạm có một hoặc nhiều EVSE; mỗi EVSE có một hoặc nhiều súng sạc (connector).
@@ -2639,89 +2686,44 @@
         </is>
       </c>
     </row>
-    <row r="53" ht="27" customHeight="1">
-      <c r="A53" s="6" t="inlineStr">
+    <row r="54" ht="27" customHeight="1">
+      <c r="A54" s="6" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="B53" s="6" t="inlineStr">
+      <c r="B54" s="6" t="inlineStr">
         <is>
           <t>Trạm sạc (charging_stations)</t>
         </is>
       </c>
-      <c r="C53" s="7" t="inlineStr">
+      <c r="C54" s="7" t="inlineStr">
         <is>
           <t>charging_stations</t>
         </is>
       </c>
-      <c r="D53" s="7" t="inlineStr">
+      <c r="D54" s="7" t="inlineStr">
         <is>
           <t>Trạm sạc</t>
         </is>
       </c>
-      <c r="E53" s="6" t="inlineStr">
+      <c r="E54" s="6" t="inlineStr">
         <is>
           <t>Nội bộ</t>
         </is>
       </c>
-      <c r="F53" s="6" t="inlineStr">
+      <c r="F54" s="6" t="inlineStr">
         <is>
           <t>F-C1, F-C2, F-D1, F-G2</t>
         </is>
       </c>
-      <c r="G53" s="6" t="inlineStr">
+      <c r="G54" s="6" t="inlineStr">
         <is>
           <t>Một trạm sạc trong mạng lưới của G3.</t>
         </is>
       </c>
-      <c r="H53" s="6" t="n">
+      <c r="H54" s="6" t="n">
         <v>22</v>
-      </c>
-      <c r="I53" s="7" t="inlineStr">
-        <is>
-          <t>→ Mở</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="6" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="B54" s="6" t="inlineStr">
-        <is>
-          <t>Trạm sạc (charging_stations)</t>
-        </is>
-      </c>
-      <c r="C54" s="7" t="inlineStr">
-        <is>
-          <t>charging_evses</t>
-        </is>
-      </c>
-      <c r="D54" s="7" t="inlineStr">
-        <is>
-          <t>EVSE (cụm cấp điện)</t>
-        </is>
-      </c>
-      <c r="E54" s="6" t="inlineStr">
-        <is>
-          <t>Nội bộ</t>
-        </is>
-      </c>
-      <c r="F54" s="6" t="inlineStr">
-        <is>
-          <t>F-C1, F-G2</t>
-        </is>
-      </c>
-      <c r="G54" s="6" t="inlineStr">
-        <is>
-          <t>Một EVSE (bộ cấp điện) của trạm.</t>
-        </is>
-      </c>
-      <c r="H54" s="6" t="n">
-        <v>6</v>
       </c>
       <c r="I54" s="7" t="inlineStr">
         <is>
@@ -2732,7 +2734,7 @@
     <row r="55">
       <c r="A55" s="6" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B55" s="6" t="inlineStr">
@@ -2742,12 +2744,12 @@
       </c>
       <c r="C55" s="7" t="inlineStr">
         <is>
-          <t>charging_connectors</t>
+          <t>charging_evses</t>
         </is>
       </c>
       <c r="D55" s="7" t="inlineStr">
         <is>
-          <t>Súng sạc</t>
+          <t>EVSE (cụm cấp điện)</t>
         </is>
       </c>
       <c r="E55" s="6" t="inlineStr">
@@ -2757,16 +2759,16 @@
       </c>
       <c r="F55" s="6" t="inlineStr">
         <is>
-          <t>F-C1, F-C2</t>
+          <t>F-C1, F-G2</t>
         </is>
       </c>
       <c r="G55" s="6" t="inlineStr">
         <is>
-          <t>Một súng/đầu sạc vật lý, kèm trạng thái trực tiếp.</t>
+          <t>Một EVSE (bộ cấp điện) của trạm.</t>
         </is>
       </c>
       <c r="H55" s="6" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="I55" s="7" t="inlineStr">
         <is>
@@ -2777,127 +2779,127 @@
     <row r="56">
       <c r="A56" s="6" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B56" s="6" t="inlineStr">
+        <is>
+          <t>Trạm sạc (charging_stations)</t>
+        </is>
+      </c>
+      <c r="C56" s="7" t="inlineStr">
+        <is>
+          <t>charging_connectors</t>
+        </is>
+      </c>
+      <c r="D56" s="7" t="inlineStr">
+        <is>
+          <t>Súng sạc</t>
+        </is>
+      </c>
+      <c r="E56" s="6" t="inlineStr">
+        <is>
+          <t>Nội bộ</t>
+        </is>
+      </c>
+      <c r="F56" s="6" t="inlineStr">
+        <is>
+          <t>F-C1, F-C2</t>
+        </is>
+      </c>
+      <c r="G56" s="6" t="inlineStr">
+        <is>
+          <t>Một súng/đầu sạc vật lý, kèm trạng thái trực tiếp.</t>
+        </is>
+      </c>
+      <c r="H56" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="I56" s="7" t="inlineStr">
+        <is>
+          <t>→ Mở</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="6" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="B56" s="6" t="inlineStr">
+      <c r="B57" s="6" t="inlineStr">
         <is>
           <t>Trạm sạc (charging_stations)</t>
         </is>
       </c>
-      <c r="C56" s="7" t="inlineStr">
+      <c r="C57" s="7" t="inlineStr">
         <is>
           <t>charging_ocpp_messages</t>
         </is>
       </c>
-      <c r="D56" s="7" t="inlineStr">
+      <c r="D57" s="7" t="inlineStr">
         <is>
           <t>Nhật ký bản tin OCPP</t>
         </is>
       </c>
-      <c r="E56" s="6" t="inlineStr">
+      <c r="E57" s="6" t="inlineStr">
         <is>
           <t>Nội bộ</t>
         </is>
       </c>
-      <c r="F56" s="6" t="inlineStr">
+      <c r="F57" s="6" t="inlineStr">
         <is>
           <t>F-G2</t>
         </is>
       </c>
-      <c r="G56" s="6" t="inlineStr">
+      <c r="G57" s="6" t="inlineStr">
         <is>
           <t>Mọi bản tin OCPP theo cả hai chiều, lưu nguyên văn, chỉ ghi thêm.</t>
         </is>
       </c>
-      <c r="H56" s="6" t="n">
+      <c r="H57" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="I56" s="7" t="inlineStr">
+      <c r="I57" s="7" t="inlineStr">
         <is>
           <t>→ Mở</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="27" customHeight="1">
-      <c r="A57" s="6" t="inlineStr">
+    <row r="58" ht="27" customHeight="1">
+      <c r="A58" s="6" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="B57" s="6" t="inlineStr">
+      <c r="B58" s="6" t="inlineStr">
         <is>
           <t>Trạm sạc (charging_stations)</t>
         </is>
       </c>
-      <c r="C57" s="7" t="inlineStr">
+      <c r="C58" s="7" t="inlineStr">
         <is>
           <t>charging_station_configuration_entries</t>
         </is>
       </c>
-      <c r="D57" s="7" t="inlineStr">
+      <c r="D58" s="7" t="inlineStr">
         <is>
           <t>Cấu hình trụ sạc</t>
         </is>
       </c>
-      <c r="E57" s="6" t="inlineStr">
+      <c r="E58" s="6" t="inlineStr">
         <is>
           <t>Nội bộ</t>
         </is>
       </c>
-      <c r="F57" s="6" t="inlineStr">
+      <c r="F58" s="6" t="inlineStr">
         <is>
           <t>F-G2</t>
         </is>
       </c>
-      <c r="G57" s="6" t="inlineStr">
+      <c r="G58" s="6" t="inlineStr">
         <is>
           <t>Một khóa cấu hình trong câu trả lời GetConfiguration của trụ sạc (các bản chụp chỉ ghi thêm).</t>
-        </is>
-      </c>
-      <c r="H57" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="I57" s="7" t="inlineStr">
-        <is>
-          <t>→ Mở</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="6" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="B58" s="6" t="inlineStr">
-        <is>
-          <t>Trạm sạc (charging_stations)</t>
-        </is>
-      </c>
-      <c r="C58" s="7" t="inlineStr">
-        <is>
-          <t>charging_reservations</t>
-        </is>
-      </c>
-      <c r="D58" s="7" t="inlineStr">
-        <is>
-          <t>Đặt chỗ súng sạc</t>
-        </is>
-      </c>
-      <c r="E58" s="6" t="inlineStr">
-        <is>
-          <t>Hai bên</t>
-        </is>
-      </c>
-      <c r="F58" s="6" t="inlineStr">
-        <is>
-          <t>F-C4</t>
-        </is>
-      </c>
-      <c r="G58" s="6" t="inlineStr">
-        <is>
-          <t>Khách hàng giữ chỗ một súng sạc của G3 trong một khung giờ.</t>
         </is>
       </c>
       <c r="H58" s="6" t="n">
@@ -2909,22 +2911,67 @@
         </is>
       </c>
     </row>
-    <row r="59" ht="94.5" customHeight="1">
-      <c r="A59" s="5" t="n"/>
-      <c r="B59" s="5" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="6" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="B59" s="6" t="inlineStr">
+        <is>
+          <t>Trạm sạc (charging_stations)</t>
+        </is>
+      </c>
+      <c r="C59" s="7" t="inlineStr">
+        <is>
+          <t>charging_reservations</t>
+        </is>
+      </c>
+      <c r="D59" s="7" t="inlineStr">
+        <is>
+          <t>Đặt chỗ súng sạc</t>
+        </is>
+      </c>
+      <c r="E59" s="6" t="inlineStr">
+        <is>
+          <t>Hai bên</t>
+        </is>
+      </c>
+      <c r="F59" s="6" t="inlineStr">
+        <is>
+          <t>F-C4</t>
+        </is>
+      </c>
+      <c r="G59" s="6" t="inlineStr">
+        <is>
+          <t>Khách hàng giữ chỗ một súng sạc của G3 trong một khung giờ.</t>
+        </is>
+      </c>
+      <c r="H59" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="I59" s="7" t="inlineStr">
+        <is>
+          <t>→ Mở</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="94.5" customHeight="1">
+      <c r="A60" s="5" t="n"/>
+      <c r="B60" s="5" t="inlineStr">
         <is>
           <t>Phiên sạc (charging_sessions)</t>
         </is>
       </c>
-      <c r="C59" s="5" t="inlineStr">
+      <c r="C60" s="5" t="inlineStr">
         <is>
           <t>3 bảng</t>
         </is>
       </c>
-      <c r="D59" s="5" t="n"/>
-      <c r="E59" s="5" t="n"/>
-      <c r="F59" s="5" t="n"/>
-      <c r="G59" s="5" t="inlineStr">
+      <c r="D60" s="5" t="n"/>
+      <c r="E60" s="5" t="n"/>
+      <c r="F60" s="5" t="n"/>
+      <c r="G60" s="5" t="inlineStr">
         <is>
           <t>Những gì diễn ra trong mỗi lần sạc: sự kiện, chỉ số công tơ, điện năng đã cấp.
 • Một phiên sạc diễn ra trên một súng sạc của một trạm G3.
@@ -2933,55 +2980,10 @@
         </is>
       </c>
     </row>
-    <row r="60" ht="27" customHeight="1">
-      <c r="A60" s="6" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="B60" s="6" t="inlineStr">
-        <is>
-          <t>Phiên sạc (charging_sessions)</t>
-        </is>
-      </c>
-      <c r="C60" s="7" t="inlineStr">
-        <is>
-          <t>charging_sessions</t>
-        </is>
-      </c>
-      <c r="D60" s="7" t="inlineStr">
-        <is>
-          <t>Phiên sạc</t>
-        </is>
-      </c>
-      <c r="E60" s="6" t="inlineStr">
-        <is>
-          <t>Hai bên</t>
-        </is>
-      </c>
-      <c r="F60" s="6" t="inlineStr">
-        <is>
-          <t>F-B2, F-C5</t>
-        </is>
-      </c>
-      <c r="G60" s="6" t="inlineStr">
-        <is>
-          <t>Một lần sạc trên một súng sạc, từ lúc bắt đầu đến lúc kết thúc.</t>
-        </is>
-      </c>
-      <c r="H60" s="6" t="n">
-        <v>20</v>
-      </c>
-      <c r="I60" s="7" t="inlineStr">
-        <is>
-          <t>→ Mở</t>
-        </is>
-      </c>
-    </row>
     <row r="61" ht="27" customHeight="1">
       <c r="A61" s="6" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B61" s="6" t="inlineStr">
@@ -2991,12 +2993,12 @@
       </c>
       <c r="C61" s="7" t="inlineStr">
         <is>
-          <t>charging_session_events</t>
+          <t>charging_sessions</t>
         </is>
       </c>
       <c r="D61" s="7" t="inlineStr">
         <is>
-          <t>Sự kiện phiên sạc</t>
+          <t>Phiên sạc</t>
         </is>
       </c>
       <c r="E61" s="6" t="inlineStr">
@@ -3006,16 +3008,16 @@
       </c>
       <c r="F61" s="6" t="inlineStr">
         <is>
-          <t>F-B2</t>
+          <t>F-B2, F-C5</t>
         </is>
       </c>
       <c r="G61" s="6" t="inlineStr">
         <is>
-          <t>Từng sự kiện Bắt đầu / Cập nhật / Kết thúc của một phiên sạc.</t>
+          <t>Một lần sạc trên một súng sạc, từ lúc bắt đầu đến lúc kết thúc.</t>
         </is>
       </c>
       <c r="H61" s="6" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="I61" s="7" t="inlineStr">
         <is>
@@ -3026,64 +3028,109 @@
     <row r="62" ht="27" customHeight="1">
       <c r="A62" s="6" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B62" s="6" t="inlineStr">
+        <is>
+          <t>Phiên sạc (charging_sessions)</t>
+        </is>
+      </c>
+      <c r="C62" s="7" t="inlineStr">
+        <is>
+          <t>charging_session_events</t>
+        </is>
+      </c>
+      <c r="D62" s="7" t="inlineStr">
+        <is>
+          <t>Sự kiện phiên sạc</t>
+        </is>
+      </c>
+      <c r="E62" s="6" t="inlineStr">
+        <is>
+          <t>Hai bên</t>
+        </is>
+      </c>
+      <c r="F62" s="6" t="inlineStr">
+        <is>
+          <t>F-B2</t>
+        </is>
+      </c>
+      <c r="G62" s="6" t="inlineStr">
+        <is>
+          <t>Từng sự kiện Bắt đầu / Cập nhật / Kết thúc của một phiên sạc.</t>
+        </is>
+      </c>
+      <c r="H62" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="I62" s="7" t="inlineStr">
+        <is>
+          <t>→ Mở</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="27" customHeight="1">
+      <c r="A63" s="6" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="B62" s="6" t="inlineStr">
+      <c r="B63" s="6" t="inlineStr">
         <is>
           <t>Phiên sạc (charging_sessions)</t>
         </is>
       </c>
-      <c r="C62" s="7" t="inlineStr">
+      <c r="C63" s="7" t="inlineStr">
         <is>
           <t>charging_session_measurements</t>
         </is>
       </c>
-      <c r="D62" s="7" t="inlineStr">
+      <c r="D63" s="7" t="inlineStr">
         <is>
           <t>Số đo phiên sạc</t>
         </is>
       </c>
-      <c r="E62" s="6" t="inlineStr">
+      <c r="E63" s="6" t="inlineStr">
         <is>
           <t>Hai bên</t>
         </is>
       </c>
-      <c r="F62" s="6" t="inlineStr">
+      <c r="F63" s="6" t="inlineStr">
         <is>
           <t>F-B2</t>
         </is>
       </c>
-      <c r="G62" s="6" t="inlineStr">
+      <c r="G63" s="6" t="inlineStr">
         <is>
           <t>Mọi giá trị đo trụ sạc gửi trong phiên (điện năng, công suất, SOC...).</t>
         </is>
       </c>
-      <c r="H62" s="6" t="n">
+      <c r="H63" s="6" t="n">
         <v>9</v>
       </c>
-      <c r="I62" s="7" t="inlineStr">
+      <c r="I63" s="7" t="inlineStr">
         <is>
           <t>→ Mở</t>
         </is>
       </c>
     </row>
-    <row r="63" ht="54" customHeight="1">
-      <c r="A63" s="5" t="n"/>
-      <c r="B63" s="5" t="inlineStr">
+    <row r="64" ht="54" customHeight="1">
+      <c r="A64" s="5" t="n"/>
+      <c r="B64" s="5" t="inlineStr">
         <is>
           <t>Thông báo &amp; cảnh báo (notifications)</t>
         </is>
       </c>
-      <c r="C63" s="5" t="inlineStr">
+      <c r="C64" s="5" t="inlineStr">
         <is>
           <t>1 bảng</t>
         </is>
       </c>
-      <c r="D63" s="5" t="n"/>
-      <c r="E63" s="5" t="n"/>
-      <c r="F63" s="5" t="n"/>
-      <c r="G63" s="5" t="inlineStr">
+      <c r="D64" s="5" t="n"/>
+      <c r="E64" s="5" t="n"/>
+      <c r="F64" s="5" t="n"/>
+      <c r="G64" s="5" t="inlineStr">
         <is>
           <t>Cảnh báo do các miền khác phát sinh, được lưu để người vận hành truy vấn.
 • Một thông báo thường nói về một xe.
@@ -3091,67 +3138,67 @@
         </is>
       </c>
     </row>
-    <row r="64" ht="27" customHeight="1">
-      <c r="A64" s="6" t="inlineStr">
+    <row r="65" ht="27" customHeight="1">
+      <c r="A65" s="6" t="inlineStr">
         <is>
           <t>38</t>
         </is>
       </c>
-      <c r="B64" s="6" t="inlineStr">
+      <c r="B65" s="6" t="inlineStr">
         <is>
           <t>Thông báo &amp; cảnh báo (notifications)</t>
         </is>
       </c>
-      <c r="C64" s="7" t="inlineStr">
+      <c r="C65" s="7" t="inlineStr">
         <is>
           <t>notifications</t>
         </is>
       </c>
-      <c r="D64" s="7" t="inlineStr">
+      <c r="D65" s="7" t="inlineStr">
         <is>
           <t>Thông báo</t>
         </is>
       </c>
-      <c r="E64" s="6" t="inlineStr">
+      <c r="E65" s="6" t="inlineStr">
         <is>
           <t>Khách hàng</t>
         </is>
       </c>
-      <c r="F64" s="6" t="inlineStr">
+      <c r="F65" s="6" t="inlineStr">
         <is>
           <t>F-A2, F-A3, F-A4, F-J1, F-J3</t>
         </is>
       </c>
-      <c r="G64" s="6" t="inlineStr">
+      <c r="G65" s="6" t="inlineStr">
         <is>
           <t>Một cảnh báo (pin, bất thường, SOH, thiết bị mất kết nối...). Một bảng chung; mỗi loại cảnh báo là một giá trị enum và một cấu trúc payload.</t>
         </is>
       </c>
-      <c r="H64" s="6" t="n">
+      <c r="H65" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="I64" s="7" t="inlineStr">
+      <c r="I65" s="7" t="inlineStr">
         <is>
           <t>→ Mở</t>
         </is>
       </c>
     </row>
-    <row r="65" ht="81" customHeight="1">
-      <c r="A65" s="5" t="n"/>
-      <c r="B65" s="5" t="inlineStr">
+    <row r="66" ht="81" customHeight="1">
+      <c r="A66" s="5" t="n"/>
+      <c r="B66" s="5" t="inlineStr">
         <is>
           <t>CSKH &amp; cứu hộ (support)</t>
         </is>
       </c>
-      <c r="C65" s="5" t="inlineStr">
+      <c r="C66" s="5" t="inlineStr">
         <is>
           <t>3 bảng</t>
         </is>
       </c>
-      <c r="D65" s="5" t="n"/>
-      <c r="E65" s="5" t="n"/>
-      <c r="F65" s="5" t="n"/>
-      <c r="G65" s="5" t="inlineStr">
+      <c r="D66" s="5" t="n"/>
+      <c r="E66" s="5" t="n"/>
+      <c r="F66" s="5" t="n"/>
+      <c r="G66" s="5" t="inlineStr">
         <is>
           <t>Chăm sóc khách hàng: yêu cầu hỗ trợ, SOS, điều phối cứu hộ và đặt lịch bảo dưỡng.
 • Một ca hỗ trợ (yêu cầu thường hoặc SOS) liên quan đến một xe và/hoặc một tài xế của một tổ chức.
@@ -3160,55 +3207,10 @@
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="6" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="B66" s="6" t="inlineStr">
-        <is>
-          <t>CSKH &amp; cứu hộ (support)</t>
-        </is>
-      </c>
-      <c r="C66" s="7" t="inlineStr">
-        <is>
-          <t>support_cases</t>
-        </is>
-      </c>
-      <c r="D66" s="7" t="inlineStr">
-        <is>
-          <t>Ca hỗ trợ</t>
-        </is>
-      </c>
-      <c r="E66" s="6" t="inlineStr">
-        <is>
-          <t>Khách hàng</t>
-        </is>
-      </c>
-      <c r="F66" s="6" t="inlineStr">
-        <is>
-          <t>F-I1, F-I2</t>
-        </is>
-      </c>
-      <c r="G66" s="6" t="inlineStr">
-        <is>
-          <t>Một yêu cầu hỗ trợ: yêu cầu thường hoặc SOS, kèm mốc thời gian SLA.</t>
-        </is>
-      </c>
-      <c r="H66" s="6" t="n">
-        <v>22</v>
-      </c>
-      <c r="I66" s="7" t="inlineStr">
-        <is>
-          <t>→ Mở</t>
-        </is>
-      </c>
-    </row>
     <row r="67">
       <c r="A67" s="6" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B67" s="6" t="inlineStr">
@@ -3218,31 +3220,31 @@
       </c>
       <c r="C67" s="7" t="inlineStr">
         <is>
-          <t>repair_partners</t>
+          <t>support_cases</t>
         </is>
       </c>
       <c r="D67" s="7" t="inlineStr">
         <is>
-          <t>Đối tác sửa chữa &amp; cứu hộ</t>
+          <t>Ca hỗ trợ</t>
         </is>
       </c>
       <c r="E67" s="6" t="inlineStr">
         <is>
-          <t>Nội bộ</t>
+          <t>Khách hàng</t>
         </is>
       </c>
       <c r="F67" s="6" t="inlineStr">
         <is>
-          <t>F-I4, F-I3</t>
+          <t>F-I1, F-I2</t>
         </is>
       </c>
       <c r="G67" s="6" t="inlineStr">
         <is>
-          <t>Một xưởng hoặc đơn vị cứu hộ mà CSKH có thể điều phối tới.</t>
+          <t>Một yêu cầu hỗ trợ: yêu cầu thường hoặc SOS, kèm mốc thời gian SLA.</t>
         </is>
       </c>
       <c r="H67" s="6" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="I67" s="7" t="inlineStr">
         <is>
@@ -3253,7 +3255,7 @@
     <row r="68">
       <c r="A68" s="6" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B68" s="6" t="inlineStr">
@@ -3263,27 +3265,27 @@
       </c>
       <c r="C68" s="7" t="inlineStr">
         <is>
-          <t>maintenance_bookings</t>
+          <t>repair_partners</t>
         </is>
       </c>
       <c r="D68" s="7" t="inlineStr">
         <is>
-          <t>Lịch bảo dưỡng</t>
+          <t>Đối tác sửa chữa &amp; cứu hộ</t>
         </is>
       </c>
       <c r="E68" s="6" t="inlineStr">
         <is>
-          <t>Khách hàng</t>
+          <t>Nội bộ</t>
         </is>
       </c>
       <c r="F68" s="6" t="inlineStr">
         <is>
-          <t>F-I3</t>
+          <t>F-I4, F-I3</t>
         </is>
       </c>
       <c r="G68" s="6" t="inlineStr">
         <is>
-          <t>Một lịch hẹn bảo dưỡng xe tại xưởng đối tác.</t>
+          <t>Một xưởng hoặc đơn vị cứu hộ mà CSKH có thể điều phối tới.</t>
         </is>
       </c>
       <c r="H68" s="6" t="n">
@@ -3295,22 +3297,67 @@
         </is>
       </c>
     </row>
-    <row r="69" ht="81" customHeight="1">
-      <c r="A69" s="5" t="n"/>
-      <c r="B69" s="5" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="6" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B69" s="6" t="inlineStr">
+        <is>
+          <t>CSKH &amp; cứu hộ (support)</t>
+        </is>
+      </c>
+      <c r="C69" s="7" t="inlineStr">
+        <is>
+          <t>maintenance_bookings</t>
+        </is>
+      </c>
+      <c r="D69" s="7" t="inlineStr">
+        <is>
+          <t>Lịch bảo dưỡng</t>
+        </is>
+      </c>
+      <c r="E69" s="6" t="inlineStr">
+        <is>
+          <t>Khách hàng</t>
+        </is>
+      </c>
+      <c r="F69" s="6" t="inlineStr">
+        <is>
+          <t>F-I3</t>
+        </is>
+      </c>
+      <c r="G69" s="6" t="inlineStr">
+        <is>
+          <t>Một lịch hẹn bảo dưỡng xe tại xưởng đối tác.</t>
+        </is>
+      </c>
+      <c r="H69" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="I69" s="7" t="inlineStr">
+        <is>
+          <t>→ Mở</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="81" customHeight="1">
+      <c r="A70" s="5" t="n"/>
+      <c r="B70" s="5" t="inlineStr">
         <is>
           <t>Chính sách sạc (bảo hành) (policy)</t>
         </is>
       </c>
-      <c r="C69" s="5" t="inlineStr">
+      <c r="C70" s="5" t="inlineStr">
         <is>
           <t>4 bảng</t>
         </is>
       </c>
-      <c r="D69" s="5" t="n"/>
-      <c r="E69" s="5" t="n"/>
-      <c r="F69" s="5" t="n"/>
-      <c r="G69" s="5" t="inlineStr">
+      <c r="D70" s="5" t="n"/>
+      <c r="E70" s="5" t="n"/>
+      <c r="F70" s="5" t="n"/>
+      <c r="G70" s="5" t="inlineStr">
         <is>
           <t>Quy tắc sạc gắn với bảo hành và các vi phạm được phát hiện.
 • Một chính sách có nhiều phiên bản không sửa được; giá trị cụ thể do G3 Mobility quyết định.
@@ -3319,55 +3366,10 @@
         </is>
       </c>
     </row>
-    <row r="70" ht="27" customHeight="1">
-      <c r="A70" s="6" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="B70" s="6" t="inlineStr">
-        <is>
-          <t>Chính sách sạc (bảo hành) (policy)</t>
-        </is>
-      </c>
-      <c r="C70" s="7" t="inlineStr">
-        <is>
-          <t>charging_policies</t>
-        </is>
-      </c>
-      <c r="D70" s="7" t="inlineStr">
-        <is>
-          <t>Chính sách sạc</t>
-        </is>
-      </c>
-      <c r="E70" s="6" t="inlineStr">
-        <is>
-          <t>Nội bộ</t>
-        </is>
-      </c>
-      <c r="F70" s="6" t="inlineStr">
-        <is>
-          <t>F-B1</t>
-        </is>
-      </c>
-      <c r="G70" s="6" t="inlineStr">
-        <is>
-          <t>Một chính sách sạc bảo hành có tên do G3 Mobility định nghĩa.</t>
-        </is>
-      </c>
-      <c r="H70" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="I70" s="7" t="inlineStr">
-        <is>
-          <t>→ Mở</t>
-        </is>
-      </c>
-    </row>
     <row r="71" ht="27" customHeight="1">
       <c r="A71" s="6" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B71" s="6" t="inlineStr">
@@ -3377,12 +3379,12 @@
       </c>
       <c r="C71" s="7" t="inlineStr">
         <is>
-          <t>charging_policy_versions</t>
+          <t>charging_policies</t>
         </is>
       </c>
       <c r="D71" s="7" t="inlineStr">
         <is>
-          <t>Phiên bản chính sách sạc</t>
+          <t>Chính sách sạc</t>
         </is>
       </c>
       <c r="E71" s="6" t="inlineStr">
@@ -3397,11 +3399,11 @@
       </c>
       <c r="G71" s="6" t="inlineStr">
         <is>
-          <t>Một phiên bản quy tắc không sửa được của chính sách. Mọi phiên bản đều được giữ để kiểm toán.</t>
+          <t>Một chính sách sạc bảo hành có tên do G3 Mobility định nghĩa.</t>
         </is>
       </c>
       <c r="H71" s="6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I71" s="7" t="inlineStr">
         <is>
@@ -3412,7 +3414,7 @@
     <row r="72" ht="27" customHeight="1">
       <c r="A72" s="6" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B72" s="6" t="inlineStr">
@@ -3422,17 +3424,17 @@
       </c>
       <c r="C72" s="7" t="inlineStr">
         <is>
-          <t>charging_policy_assignments</t>
+          <t>charging_policy_versions</t>
         </is>
       </c>
       <c r="D72" s="7" t="inlineStr">
         <is>
-          <t>Áp dụng chính sách sạc</t>
+          <t>Phiên bản chính sách sạc</t>
         </is>
       </c>
       <c r="E72" s="6" t="inlineStr">
         <is>
-          <t>Khách hàng</t>
+          <t>Nội bộ</t>
         </is>
       </c>
       <c r="F72" s="6" t="inlineStr">
@@ -3442,11 +3444,11 @@
       </c>
       <c r="G72" s="6" t="inlineStr">
         <is>
-          <t>Chính sách nào áp dụng cho một xe, một đội xe hay một dòng xe.</t>
+          <t>Một phiên bản quy tắc không sửa được của chính sách. Mọi phiên bản đều được giữ để kiểm toán.</t>
         </is>
       </c>
       <c r="H72" s="6" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I72" s="7" t="inlineStr">
         <is>
@@ -3457,7 +3459,7 @@
     <row r="73" ht="27" customHeight="1">
       <c r="A73" s="6" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B73" s="6" t="inlineStr">
@@ -3467,12 +3469,12 @@
       </c>
       <c r="C73" s="7" t="inlineStr">
         <is>
-          <t>policy_violations</t>
+          <t>charging_policy_assignments</t>
         </is>
       </c>
       <c r="D73" s="7" t="inlineStr">
         <is>
-          <t>Vi phạm chính sách sạc</t>
+          <t>Áp dụng chính sách sạc</t>
         </is>
       </c>
       <c r="E73" s="6" t="inlineStr">
@@ -3482,12 +3484,12 @@
       </c>
       <c r="F73" s="6" t="inlineStr">
         <is>
-          <t>F-B3, F-B6</t>
+          <t>F-B1</t>
         </is>
       </c>
       <c r="G73" s="6" t="inlineStr">
         <is>
-          <t>Một phiên sạc vi phạm chính sách, kèm bằng chứng. Hệ quả của vi phạm vẫn là câu hỏi kinh doanh còn mở (mục 3 của feature-list).</t>
+          <t>Chính sách nào áp dụng cho một xe, một đội xe hay một dòng xe.</t>
         </is>
       </c>
       <c r="H73" s="6" t="n">
@@ -3499,22 +3501,67 @@
         </is>
       </c>
     </row>
-    <row r="74" ht="283.5" customHeight="1">
-      <c r="A74" s="5" t="n"/>
-      <c r="B74" s="5" t="inlineStr">
+    <row r="74" ht="27" customHeight="1">
+      <c r="A74" s="6" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="B74" s="6" t="inlineStr">
+        <is>
+          <t>Chính sách sạc (bảo hành) (policy)</t>
+        </is>
+      </c>
+      <c r="C74" s="7" t="inlineStr">
+        <is>
+          <t>policy_violations</t>
+        </is>
+      </c>
+      <c r="D74" s="7" t="inlineStr">
+        <is>
+          <t>Vi phạm chính sách sạc</t>
+        </is>
+      </c>
+      <c r="E74" s="6" t="inlineStr">
+        <is>
+          <t>Khách hàng</t>
+        </is>
+      </c>
+      <c r="F74" s="6" t="inlineStr">
+        <is>
+          <t>F-B3, F-B6</t>
+        </is>
+      </c>
+      <c r="G74" s="6" t="inlineStr">
+        <is>
+          <t>Một phiên sạc vi phạm chính sách, kèm bằng chứng. Hệ quả của vi phạm vẫn là câu hỏi kinh doanh còn mở (mục 3 của feature-list).</t>
+        </is>
+      </c>
+      <c r="H74" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="I74" s="7" t="inlineStr">
+        <is>
+          <t>→ Mở</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="283.5" customHeight="1">
+      <c r="A75" s="5" t="n"/>
+      <c r="B75" s="5" t="inlineStr">
         <is>
           <t>Thanh toán &amp; hóa đơn (billing)</t>
         </is>
       </c>
-      <c r="C74" s="5" t="inlineStr">
+      <c r="C75" s="5" t="inlineStr">
         <is>
           <t>9 bảng</t>
         </is>
       </c>
-      <c r="D74" s="5" t="n"/>
-      <c r="E74" s="5" t="n"/>
-      <c r="F74" s="5" t="n"/>
-      <c r="G74" s="5" t="inlineStr">
+      <c r="D75" s="5" t="n"/>
+      <c r="E75" s="5" t="n"/>
+      <c r="F75" s="5" t="n"/>
+      <c r="G75" s="5" t="inlineStr">
         <is>
           <t>Tiền: giá điện, thanh toán, ví trả trước, hóa đơn điện tử và thuê bao SaaS.
 • Biểu giá định giá điện cho toàn mạng hoặc từng trạm, theo khung giờ.
@@ -3526,55 +3573,10 @@
         </is>
       </c>
     </row>
-    <row r="75" ht="27" customHeight="1">
-      <c r="A75" s="6" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="B75" s="6" t="inlineStr">
-        <is>
-          <t>Thanh toán &amp; hóa đơn (billing)</t>
-        </is>
-      </c>
-      <c r="C75" s="7" t="inlineStr">
-        <is>
-          <t>tariffs</t>
-        </is>
-      </c>
-      <c r="D75" s="7" t="inlineStr">
-        <is>
-          <t>Biểu giá điện</t>
-        </is>
-      </c>
-      <c r="E75" s="6" t="inlineStr">
-        <is>
-          <t>Nội bộ</t>
-        </is>
-      </c>
-      <c r="F75" s="6" t="inlineStr">
-        <is>
-          <t>F-C8, F-H1</t>
-        </is>
-      </c>
-      <c r="G75" s="6" t="inlineStr">
-        <is>
-          <t>Giá điện. Ai sở hữu biểu giá (G3 Energy hay G3 Network) là mục 5 của feature-list.</t>
-        </is>
-      </c>
-      <c r="H75" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="I75" s="7" t="inlineStr">
-        <is>
-          <t>→ Mở</t>
-        </is>
-      </c>
-    </row>
     <row r="76" ht="27" customHeight="1">
       <c r="A76" s="6" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>46</t>
         </is>
       </c>
       <c r="B76" s="6" t="inlineStr">
@@ -3584,31 +3586,31 @@
       </c>
       <c r="C76" s="7" t="inlineStr">
         <is>
-          <t>payments</t>
+          <t>tariffs</t>
         </is>
       </c>
       <c r="D76" s="7" t="inlineStr">
         <is>
-          <t>Thanh toán</t>
+          <t>Biểu giá điện</t>
         </is>
       </c>
       <c r="E76" s="6" t="inlineStr">
         <is>
-          <t>Khách hàng</t>
+          <t>Nội bộ</t>
         </is>
       </c>
       <c r="F76" s="6" t="inlineStr">
         <is>
-          <t>F-H1</t>
+          <t>F-C8, F-H1</t>
         </is>
       </c>
       <c r="G76" s="6" t="inlineStr">
         <is>
-          <t>Một lần thanh toán qua cổng thanh toán hoặc ví, thường cho một phiên sạc.</t>
+          <t>Giá điện. Ai sở hữu biểu giá (G3 Energy hay G3 Network) là mục 5 của feature-list.</t>
         </is>
       </c>
       <c r="H76" s="6" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I76" s="7" t="inlineStr">
         <is>
@@ -3619,7 +3621,7 @@
     <row r="77" ht="27" customHeight="1">
       <c r="A77" s="6" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>47</t>
         </is>
       </c>
       <c r="B77" s="6" t="inlineStr">
@@ -3629,12 +3631,12 @@
       </c>
       <c r="C77" s="7" t="inlineStr">
         <is>
-          <t>wallets</t>
+          <t>payments</t>
         </is>
       </c>
       <c r="D77" s="7" t="inlineStr">
         <is>
-          <t>Ví</t>
+          <t>Thanh toán</t>
         </is>
       </c>
       <c r="E77" s="6" t="inlineStr">
@@ -3644,16 +3646,16 @@
       </c>
       <c r="F77" s="6" t="inlineStr">
         <is>
-          <t>F-H2</t>
+          <t>F-H1</t>
         </is>
       </c>
       <c r="G77" s="6" t="inlineStr">
         <is>
-          <t>Số dư trả trước của một tài xế hoặc của cả tổ chức.</t>
+          <t>Một lần thanh toán qua cổng thanh toán hoặc ví, thường cho một phiên sạc.</t>
         </is>
       </c>
       <c r="H77" s="6" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I77" s="7" t="inlineStr">
         <is>
@@ -3664,7 +3666,7 @@
     <row r="78" ht="27" customHeight="1">
       <c r="A78" s="6" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>48</t>
         </is>
       </c>
       <c r="B78" s="6" t="inlineStr">
@@ -3674,12 +3676,12 @@
       </c>
       <c r="C78" s="7" t="inlineStr">
         <is>
-          <t>wallet_transactions</t>
+          <t>wallets</t>
         </is>
       </c>
       <c r="D78" s="7" t="inlineStr">
         <is>
-          <t>Giao dịch ví</t>
+          <t>Ví</t>
         </is>
       </c>
       <c r="E78" s="6" t="inlineStr">
@@ -3694,11 +3696,11 @@
       </c>
       <c r="G78" s="6" t="inlineStr">
         <is>
-          <t>Biến động tiền vào/ra khỏi ví, chỉ ghi thêm.</t>
+          <t>Số dư trả trước của một tài xế hoặc của cả tổ chức.</t>
         </is>
       </c>
       <c r="H78" s="6" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I78" s="7" t="inlineStr">
         <is>
@@ -3709,7 +3711,7 @@
     <row r="79" ht="27" customHeight="1">
       <c r="A79" s="6" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>49</t>
         </is>
       </c>
       <c r="B79" s="6" t="inlineStr">
@@ -3719,12 +3721,12 @@
       </c>
       <c r="C79" s="7" t="inlineStr">
         <is>
-          <t>invoices</t>
+          <t>wallet_transactions</t>
         </is>
       </c>
       <c r="D79" s="7" t="inlineStr">
         <is>
-          <t>Hóa đơn</t>
+          <t>Giao dịch ví</t>
         </is>
       </c>
       <c r="E79" s="6" t="inlineStr">
@@ -3734,16 +3736,16 @@
       </c>
       <c r="F79" s="6" t="inlineStr">
         <is>
-          <t>F-H3, F-H4</t>
+          <t>F-H2</t>
         </is>
       </c>
       <c r="G79" s="6" t="inlineStr">
         <is>
-          <t>Một hóa đơn điện tử hợp lệ. Khi đã PHÁT HÀNH thì không sửa, chỉ điều chỉnh hoặc hủy bằng hóa đơn mới.</t>
+          <t>Biến động tiền vào/ra khỏi ví, chỉ ghi thêm.</t>
         </is>
       </c>
       <c r="H79" s="6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I79" s="7" t="inlineStr">
         <is>
@@ -3754,617 +3756,662 @@
     <row r="80" ht="27" customHeight="1">
       <c r="A80" s="6" t="inlineStr">
         <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="B80" s="6" t="inlineStr">
+        <is>
+          <t>Thanh toán &amp; hóa đơn (billing)</t>
+        </is>
+      </c>
+      <c r="C80" s="7" t="inlineStr">
+        <is>
+          <t>invoices</t>
+        </is>
+      </c>
+      <c r="D80" s="7" t="inlineStr">
+        <is>
+          <t>Hóa đơn</t>
+        </is>
+      </c>
+      <c r="E80" s="6" t="inlineStr">
+        <is>
+          <t>Khách hàng</t>
+        </is>
+      </c>
+      <c r="F80" s="6" t="inlineStr">
+        <is>
+          <t>F-H3, F-H4</t>
+        </is>
+      </c>
+      <c r="G80" s="6" t="inlineStr">
+        <is>
+          <t>Một hóa đơn điện tử hợp lệ. Khi đã PHÁT HÀNH thì không sửa, chỉ điều chỉnh hoặc hủy bằng hóa đơn mới.</t>
+        </is>
+      </c>
+      <c r="H80" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="I80" s="7" t="inlineStr">
+        <is>
+          <t>→ Mở</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="27" customHeight="1">
+      <c r="A81" s="6" t="inlineStr">
+        <is>
           <t>51</t>
         </is>
       </c>
-      <c r="B80" s="6" t="inlineStr">
+      <c r="B81" s="6" t="inlineStr">
         <is>
           <t>Thanh toán &amp; hóa đơn (billing)</t>
         </is>
       </c>
-      <c r="C80" s="7" t="inlineStr">
+      <c r="C81" s="7" t="inlineStr">
         <is>
           <t>invoice_lines</t>
         </is>
       </c>
-      <c r="D80" s="7" t="inlineStr">
+      <c r="D81" s="7" t="inlineStr">
         <is>
           <t>Dòng hóa đơn</t>
         </is>
       </c>
-      <c r="E80" s="6" t="inlineStr">
+      <c r="E81" s="6" t="inlineStr">
         <is>
           <t>Khách hàng</t>
         </is>
       </c>
-      <c r="F80" s="6" t="inlineStr">
+      <c r="F81" s="6" t="inlineStr">
         <is>
           <t>F-H3, F-H4</t>
         </is>
       </c>
-      <c r="G80" s="6" t="inlineStr">
+      <c r="G81" s="6" t="inlineStr">
         <is>
           <t>Một dòng của hóa đơn: một phiên sạc hoặc một kỳ thuê bao.</t>
         </is>
       </c>
-      <c r="H80" s="6" t="n">
+      <c r="H81" s="6" t="n">
         <v>9</v>
       </c>
-      <c r="I80" s="7" t="inlineStr">
+      <c r="I81" s="7" t="inlineStr">
         <is>
           <t>→ Mở</t>
         </is>
       </c>
     </row>
-    <row r="81" ht="54" customHeight="1">
-      <c r="A81" s="6" t="inlineStr">
+    <row r="82" ht="54" customHeight="1">
+      <c r="A82" s="6" t="inlineStr">
         <is>
           <t>52</t>
         </is>
       </c>
-      <c r="B81" s="6" t="inlineStr">
+      <c r="B82" s="6" t="inlineStr">
         <is>
           <t>Thanh toán &amp; hóa đơn (billing)</t>
         </is>
       </c>
-      <c r="C81" s="7" t="inlineStr">
+      <c r="C82" s="7" t="inlineStr">
         <is>
           <t>subscription_plans</t>
         </is>
       </c>
-      <c r="D81" s="7" t="inlineStr">
+      <c r="D82" s="7" t="inlineStr">
         <is>
           <t>Gói dịch vụ</t>
         </is>
       </c>
-      <c r="E81" s="6" t="inlineStr">
+      <c r="E82" s="6" t="inlineStr">
         <is>
           <t>Nội bộ</t>
         </is>
       </c>
-      <c r="F81" s="6" t="inlineStr">
+      <c r="F82" s="6" t="inlineStr">
         <is>
           <t>F-H4</t>
         </is>
       </c>
-      <c r="G81" s="6" t="inlineStr">
+      <c r="G82" s="6" t="inlineStr">
         <is>
           <t>Một gói dịch vụ: mỗi gói là một dòng (GUEST là gói mặc định miễn phí, STANDARD, ADVANCED, PRO, ..., hoặc gói riêng cho một khách hàng); tính năng của gói nằm ở plan_features. Giá được tính theo từng tính năng (xem ghi chú của miền thanh toán).</t>
         </is>
       </c>
-      <c r="H81" s="6" t="n">
+      <c r="H82" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="I81" s="7" t="inlineStr">
+      <c r="I82" s="7" t="inlineStr">
         <is>
           <t>→ Mở</t>
         </is>
       </c>
     </row>
-    <row r="82" ht="40.5" customHeight="1">
-      <c r="A82" s="6" t="inlineStr">
+    <row r="83" ht="40.5" customHeight="1">
+      <c r="A83" s="6" t="inlineStr">
         <is>
           <t>53</t>
         </is>
       </c>
-      <c r="B82" s="6" t="inlineStr">
+      <c r="B83" s="6" t="inlineStr">
         <is>
           <t>Thanh toán &amp; hóa đơn (billing)</t>
         </is>
       </c>
-      <c r="C82" s="7" t="inlineStr">
+      <c r="C83" s="7" t="inlineStr">
         <is>
           <t>plan_features</t>
         </is>
       </c>
-      <c r="D82" s="7" t="inlineStr">
+      <c r="D83" s="7" t="inlineStr">
         <is>
           <t>Tính năng của gói dịch vụ</t>
         </is>
       </c>
-      <c r="E82" s="6" t="inlineStr">
+      <c r="E83" s="6" t="inlineStr">
         <is>
           <t>Nội bộ</t>
         </is>
       </c>
-      <c r="F82" s="6" t="inlineStr">
+      <c r="F83" s="6" t="inlineStr">
         <is>
           <t>F-H4</t>
         </is>
       </c>
-      <c r="G82" s="6" t="inlineStr">
+      <c r="G83" s="6" t="inlineStr">
         <is>
           <t>Mỗi gói dịch vụ gồm những tính năng nào. Gói dịch vụ là dữ liệu, nên G3 có thể tạo gói mới (Pro, Max, gói riêng cho một khách hàng) trên portal mà không cần lập trình viên; chỉ tính năng hoàn toàn mới mới cần viết mã.</t>
         </is>
       </c>
-      <c r="H82" s="6" t="n">
+      <c r="H83" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="I82" s="7" t="inlineStr">
+      <c r="I83" s="7" t="inlineStr">
         <is>
           <t>→ Mở</t>
         </is>
       </c>
     </row>
-    <row r="83" ht="27" customHeight="1">
-      <c r="A83" s="6" t="inlineStr">
+    <row r="84" ht="27" customHeight="1">
+      <c r="A84" s="6" t="inlineStr">
         <is>
           <t>54</t>
         </is>
       </c>
-      <c r="B83" s="6" t="inlineStr">
+      <c r="B84" s="6" t="inlineStr">
         <is>
           <t>Thanh toán &amp; hóa đơn (billing)</t>
         </is>
       </c>
-      <c r="C83" s="7" t="inlineStr">
+      <c r="C84" s="7" t="inlineStr">
         <is>
           <t>subscriptions</t>
         </is>
       </c>
-      <c r="D83" s="7" t="inlineStr">
+      <c r="D84" s="7" t="inlineStr">
         <is>
           <t>Thuê bao</t>
         </is>
       </c>
-      <c r="E83" s="6" t="inlineStr">
+      <c r="E84" s="6" t="inlineStr">
         <is>
           <t>Khách hàng</t>
         </is>
       </c>
-      <c r="F83" s="6" t="inlineStr">
+      <c r="F84" s="6" t="inlineStr">
         <is>
           <t>F-H4</t>
         </is>
       </c>
-      <c r="G83" s="6" t="inlineStr">
+      <c r="G84" s="6" t="inlineStr">
         <is>
           <t>Một xe đăng ký một gói; quá hạn thanh toán sẽ khóa tính năng.</t>
         </is>
       </c>
-      <c r="H83" s="6" t="n">
+      <c r="H84" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="I83" s="7" t="inlineStr">
+      <c r="I84" s="7" t="inlineStr">
         <is>
           <t>→ Mở</t>
         </is>
       </c>
     </row>
-    <row r="84" ht="27" customHeight="1">
-      <c r="A84" s="5" t="n"/>
-      <c r="B84" s="5" t="inlineStr">
+    <row r="85" ht="27" customHeight="1">
+      <c r="A85" s="5" t="n"/>
+      <c r="B85" s="5" t="inlineStr">
         <is>
           <t>Chấm điểm tài xế (scoring)</t>
         </is>
       </c>
-      <c r="C84" s="5" t="inlineStr">
+      <c r="C85" s="5" t="inlineStr">
         <is>
           <t>1 bảng</t>
         </is>
       </c>
-      <c r="D84" s="5" t="n"/>
-      <c r="E84" s="5" t="n"/>
-      <c r="F84" s="5" t="n"/>
-      <c r="G84" s="5" t="inlineStr">
+      <c r="D85" s="5" t="n"/>
+      <c r="E85" s="5" t="n"/>
+      <c r="F85" s="5" t="n"/>
+      <c r="G85" s="5" t="inlineStr">
         <is>
           <t>Chấm điểm an toàn cho tài xế từ hành vi lái xe.
 • Mỗi tuần, mỗi tài xế có một điểm, tính từ dữ liệu vận hành của xe họ lái.</t>
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="6" t="inlineStr">
+    <row r="86">
+      <c r="A86" s="6" t="inlineStr">
         <is>
           <t>55</t>
         </is>
       </c>
-      <c r="B85" s="6" t="inlineStr">
+      <c r="B86" s="6" t="inlineStr">
         <is>
           <t>Chấm điểm tài xế (scoring)</t>
         </is>
       </c>
-      <c r="C85" s="7" t="inlineStr">
+      <c r="C86" s="7" t="inlineStr">
         <is>
           <t>driver_scores</t>
         </is>
       </c>
-      <c r="D85" s="7" t="inlineStr">
+      <c r="D86" s="7" t="inlineStr">
         <is>
           <t>Điểm tài xế</t>
         </is>
       </c>
-      <c r="E85" s="6" t="inlineStr">
+      <c r="E86" s="6" t="inlineStr">
         <is>
           <t>Khách hàng</t>
         </is>
       </c>
-      <c r="F85" s="6" t="inlineStr">
+      <c r="F86" s="6" t="inlineStr">
         <is>
           <t>F-K1</t>
         </is>
       </c>
-      <c r="G85" s="6" t="inlineStr">
+      <c r="G86" s="6" t="inlineStr">
         <is>
           <t>Điểm an toàn hằng tuần của tài xế, tính từ dữ liệu vận hành xe.</t>
         </is>
       </c>
-      <c r="H85" s="6" t="n">
+      <c r="H86" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="I85" s="7" t="inlineStr">
+      <c r="I86" s="7" t="inlineStr">
         <is>
           <t>→ Mở</t>
         </is>
       </c>
     </row>
-    <row r="86" ht="27" customHeight="1">
-      <c r="A86" s="5" t="n"/>
-      <c r="B86" s="5" t="inlineStr">
+    <row r="87" ht="27" customHeight="1">
+      <c r="A87" s="5" t="n"/>
+      <c r="B87" s="5" t="inlineStr">
         <is>
           <t>Chưa phân miền (unassigned)</t>
         </is>
       </c>
-      <c r="C86" s="5" t="inlineStr">
+      <c r="C87" s="5" t="inlineStr">
         <is>
           <t>2 bảng</t>
         </is>
       </c>
-      <c r="D86" s="5" t="n"/>
-      <c r="E86" s="5" t="n"/>
-      <c r="F86" s="5" t="n"/>
-      <c r="G86" s="5" t="inlineStr">
+      <c r="D87" s="5" t="n"/>
+      <c r="E87" s="5" t="n"/>
+      <c r="F87" s="5" t="n"/>
+      <c r="G87" s="5" t="inlineStr">
         <is>
           <t>Các tính năng chưa được quyết định thuộc miền nghiệp vụ nào (xem feature-list.md).</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="6" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="B87" s="6" t="inlineStr">
-        <is>
-          <t>Chưa phân miền (unassigned)</t>
-        </is>
-      </c>
-      <c r="C87" s="7" t="inlineStr">
-        <is>
-          <t>promotion_campaigns</t>
-        </is>
-      </c>
-      <c r="D87" s="7" t="inlineStr">
-        <is>
-          <t>Chiến dịch khuyến mãi</t>
-        </is>
-      </c>
-      <c r="E87" s="6" t="inlineStr">
-        <is>
-          <t>Nội bộ</t>
-        </is>
-      </c>
-      <c r="F87" s="6" t="inlineStr">
-        <is>
-          <t>F-F4</t>
-        </is>
-      </c>
-      <c r="G87" s="6" t="inlineStr">
-        <is>
-          <t>Một chiến dịch nhắc bảo dưỡng hoặc khuyến mãi.</t>
-        </is>
-      </c>
-      <c r="H87" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="I87" s="7" t="inlineStr">
-        <is>
-          <t>→ Mở</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="6" t="inlineStr">
         <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="B88" s="6" t="inlineStr">
+        <is>
+          <t>Chưa phân miền (unassigned)</t>
+        </is>
+      </c>
+      <c r="C88" s="7" t="inlineStr">
+        <is>
+          <t>promotion_campaigns</t>
+        </is>
+      </c>
+      <c r="D88" s="7" t="inlineStr">
+        <is>
+          <t>Chiến dịch khuyến mãi</t>
+        </is>
+      </c>
+      <c r="E88" s="6" t="inlineStr">
+        <is>
+          <t>Nội bộ</t>
+        </is>
+      </c>
+      <c r="F88" s="6" t="inlineStr">
+        <is>
+          <t>F-F4</t>
+        </is>
+      </c>
+      <c r="G88" s="6" t="inlineStr">
+        <is>
+          <t>Một chiến dịch nhắc bảo dưỡng hoặc khuyến mãi.</t>
+        </is>
+      </c>
+      <c r="H88" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="I88" s="7" t="inlineStr">
+        <is>
+          <t>→ Mở</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="6" t="inlineStr">
+        <is>
           <t>57</t>
         </is>
       </c>
-      <c r="B88" s="6" t="inlineStr">
+      <c r="B89" s="6" t="inlineStr">
         <is>
           <t>Chưa phân miền (unassigned)</t>
         </is>
       </c>
-      <c r="C88" s="7" t="inlineStr">
+      <c r="C89" s="7" t="inlineStr">
         <is>
           <t>trips</t>
         </is>
       </c>
-      <c r="D88" s="7" t="inlineStr">
+      <c r="D89" s="7" t="inlineStr">
         <is>
           <t>Chuyến đi</t>
         </is>
       </c>
-      <c r="E88" s="6" t="inlineStr">
+      <c r="E89" s="6" t="inlineStr">
         <is>
           <t>Khách hàng</t>
         </is>
       </c>
-      <c r="F88" s="6" t="inlineStr">
+      <c r="F89" s="6" t="inlineStr">
         <is>
           <t>F-A9</t>
         </is>
       </c>
-      <c r="G88" s="6" t="inlineStr">
+      <c r="G89" s="6" t="inlineStr">
         <is>
           <t>Một chuyến đi của xe. F-A9 đang tạm dừng: chưa có khái niệm chuyến đi.</t>
         </is>
       </c>
-      <c r="H88" s="6" t="n">
+      <c r="H89" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="I88" s="7" t="inlineStr">
+      <c r="I89" s="7" t="inlineStr">
         <is>
           <t>→ Mở</t>
         </is>
       </c>
     </row>
-    <row r="89"/>
-    <row r="90" ht="27" customHeight="1">
-      <c r="A90" s="4" t="inlineStr">
+    <row r="90"/>
+    <row r="91" ht="27" customHeight="1">
+      <c r="A91" s="4" t="inlineStr">
         <is>
           <t>Chú giải</t>
         </is>
       </c>
-      <c r="B90" s="4" t="inlineStr">
+      <c r="B91" s="4" t="inlineStr">
         <is>
           <t>Ý nghĩa</t>
         </is>
       </c>
     </row>
-    <row r="91" ht="108" customHeight="1">
-      <c r="A91" s="6" t="inlineStr">
+    <row r="92" ht="108" customHeight="1">
+      <c r="A92" s="6" t="inlineStr">
         <is>
           <t>Chủ sở hữu dữ liệu: Khách hàng</t>
         </is>
       </c>
-      <c r="B91" s="6" t="inlineStr">
+      <c r="B92" s="6" t="inlineStr">
         <is>
           <t>Thuộc về một tổ chức (thường là khách hàng; công ty G3 cũng có thể sở hữu); có cột organization_id hoặc lấy qua bảng cha (DM-24).</t>
-        </is>
-      </c>
-    </row>
-    <row r="92" ht="94.5" customHeight="1">
-      <c r="A92" s="6" t="inlineStr">
-        <is>
-          <t>Chủ sở hữu dữ liệu: Nội bộ</t>
-        </is>
-      </c>
-      <c r="B92" s="6" t="inlineStr">
-        <is>
-          <t>Dữ liệu của chính chúng ta (đơn vị vận hành nền tảng), dùng chung cho mọi tổ chức.</t>
         </is>
       </c>
     </row>
     <row r="93" ht="94.5" customHeight="1">
       <c r="A93" s="6" t="inlineStr">
         <is>
+          <t>Chủ sở hữu dữ liệu: Nội bộ</t>
+        </is>
+      </c>
+      <c r="B93" s="6" t="inlineStr">
+        <is>
+          <t>Dữ liệu của chính chúng ta (đơn vị vận hành nền tảng), dùng chung cho mọi tổ chức.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="94.5" customHeight="1">
+      <c r="A94" s="6" t="inlineStr">
+        <is>
           <t>Chủ sở hữu dữ liệu: Hai bên</t>
         </is>
       </c>
-      <c r="B93" s="6" t="inlineStr">
+      <c r="B94" s="6" t="inlineStr">
         <is>
           <t>Tài sản của G3 được khách hàng sử dụng; cả hai bên cùng liên quan.</t>
         </is>
       </c>
     </row>
-    <row r="94" ht="121.5" customHeight="1">
-      <c r="A94" s="6" t="inlineStr">
+    <row r="95" ht="121.5" customHeight="1">
+      <c r="A95" s="6" t="inlineStr">
         <is>
           <t>Chủ sở hữu dữ liệu: Chưa quyết định</t>
         </is>
       </c>
-      <c r="B94" s="6" t="inlineStr">
+      <c r="B95" s="6" t="inlineStr">
         <is>
           <t>Đang chờ một quyết định còn mở (xem cuối trang).</t>
         </is>
       </c>
     </row>
-    <row r="95" ht="81" customHeight="1">
-      <c r="A95" s="6" t="inlineStr">
+    <row r="96" ht="81" customHeight="1">
+      <c r="A96" s="6" t="inlineStr">
         <is>
           <t>Miền nghiệp vụ (domain)</t>
         </is>
       </c>
-      <c r="B95" s="6" t="inlineStr">
+      <c r="B96" s="6" t="inlineStr">
         <is>
           <t>Một phần của hệ thống sở hữu dữ liệu riêng, ví dụ Xe, Trạm sạc, Thanh toán. Mỗi miền gồm một hoặc nhiều bảng.</t>
         </is>
       </c>
     </row>
-    <row r="96" ht="54" customHeight="1">
-      <c r="A96" s="6" t="inlineStr">
+    <row r="97" ht="54" customHeight="1">
+      <c r="A97" s="6" t="inlineStr">
         <is>
           <t>Bảng</t>
         </is>
       </c>
-      <c r="B96" s="6" t="inlineStr">
+      <c r="B97" s="6" t="inlineStr">
         <is>
           <t>Một loại dữ liệu được lưu, ví dụ Xe hoặc Phiên sạc. Mỗi bảng có một sheet riêng liệt kê từng cột.</t>
         </is>
       </c>
     </row>
-    <row r="97" ht="40.5" customHeight="1">
-      <c r="A97" s="6" t="inlineStr">
+    <row r="98" ht="40.5" customHeight="1">
+      <c r="A98" s="6" t="inlineStr">
         <is>
           <t>Tính năng</t>
         </is>
       </c>
-      <c r="B97" s="6" t="inlineStr">
+      <c r="B98" s="6" t="inlineStr">
         <is>
           <t>Mã tính năng trong danh sách tính năng (feature-list.md), ví dụ F-B2.</t>
         </is>
       </c>
     </row>
-    <row r="98" ht="67.5" customHeight="1">
-      <c r="A98" s="6" t="inlineStr">
+    <row r="99" ht="67.5" customHeight="1">
+      <c r="A99" s="6" t="inlineStr">
         <is>
           <t>PK / FK / UQ</t>
         </is>
       </c>
-      <c r="B98" s="6" t="inlineStr">
+      <c r="B99" s="6" t="inlineStr">
         <is>
           <t>PK: khóa chính (định danh duy nhất của dòng). FK: khóa ngoại (trỏ tới dòng của bảng khác). UQ: giá trị không được trùng.</t>
         </is>
       </c>
     </row>
-    <row r="99" ht="54" customHeight="1">
-      <c r="A99" s="6" t="inlineStr">
+    <row r="100" ht="54" customHeight="1">
+      <c r="A100" s="6" t="inlineStr">
         <is>
           <t>Ví dụ</t>
         </is>
       </c>
-      <c r="B99" s="6" t="inlineStr">
+      <c r="B100" s="6" t="inlineStr">
         <is>
           <t>Giá trị mẫu. Các mã ví dụ khớp nhau giữa các bảng, nên có thể lần theo một bản ghi mẫu qua nhiều sheet.</t>
         </is>
       </c>
     </row>
-    <row r="100" ht="40.5" customHeight="1">
-      <c r="A100" s="6" t="inlineStr">
+    <row r="101" ht="40.5" customHeight="1">
+      <c r="A101" s="6" t="inlineStr">
         <is>
           <t>NULL</t>
         </is>
       </c>
-      <c r="B100" s="6" t="inlineStr">
+      <c r="B101" s="6" t="inlineStr">
         <is>
           <t>Ô không có giá trị. Ý nghĩa của NULL được giải thích trong cột Ý nghĩa.</t>
         </is>
       </c>
     </row>
-    <row r="101" ht="81" customHeight="1">
-      <c r="A101" s="6" t="inlineStr">
+    <row r="102" ht="81" customHeight="1">
+      <c r="A102" s="6" t="inlineStr">
         <is>
           <t>🔍 Lưu lịch sử</t>
         </is>
       </c>
-      <c r="B101" s="6" t="inlineStr">
+      <c r="B102" s="6" t="inlineStr">
         <is>
           <t>Cột được theo dõi: khi cột này thay đổi, toàn bộ dòng cũ được chép sang bảng lịch sử (tên kết thúc bằng _history) kèm thời điểm và người thay đổi.</t>
         </is>
       </c>
     </row>
-    <row r="102"/>
-    <row r="103">
-      <c r="A103" s="8" t="inlineStr">
+    <row r="103"/>
+    <row r="104">
+      <c r="A104" s="8" t="inlineStr">
         <is>
           <t>Các view (giai đoạn đọc từ lịch sử)</t>
         </is>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" s="4" t="inlineStr">
+    <row r="105">
+      <c r="A105" s="4" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="B104" s="4" t="inlineStr">
+      <c r="B105" s="4" t="inlineStr">
         <is>
           <t>Mỗi dòng là</t>
         </is>
       </c>
-      <c r="C104" s="4" t="inlineStr">
+      <c r="C105" s="4" t="inlineStr">
         <is>
           <t>Các cột</t>
         </is>
       </c>
-      <c r="D104" s="4" t="inlineStr">
+      <c r="D105" s="4" t="inlineStr">
         <is>
           <t>Được dùng bởi</t>
-        </is>
-      </c>
-    </row>
-    <row r="105" ht="94.5" customHeight="1">
-      <c r="A105" s="6" t="inlineStr">
-        <is>
-          <t>vehicle_ownership_periods</t>
-        </is>
-      </c>
-      <c r="B105" s="6" t="inlineStr">
-        <is>
-          <t>một giai đoạn xe thuộc một chủ</t>
-        </is>
-      </c>
-      <c r="C105" s="6" t="inlineStr">
-        <is>
-          <t>vehicle_id, organization_id, owned_from, owned_until (NULL với chủ hiện tại)</t>
-        </is>
-      </c>
-      <c r="D105" s="6" t="inlineStr">
-        <is>
-          <t>lịch sử sở hữu và ngày bàn giao đầu tiên (VEH-02), "ngày đó xe của ai"</t>
         </is>
       </c>
     </row>
     <row r="106" ht="94.5" customHeight="1">
       <c r="A106" s="6" t="inlineStr">
         <is>
+          <t>vehicle_ownership_periods</t>
+        </is>
+      </c>
+      <c r="B106" s="6" t="inlineStr">
+        <is>
+          <t>một giai đoạn xe thuộc một chủ</t>
+        </is>
+      </c>
+      <c r="C106" s="6" t="inlineStr">
+        <is>
+          <t>vehicle_id, organization_id, owned_from, owned_until (NULL với chủ hiện tại)</t>
+        </is>
+      </c>
+      <c r="D106" s="6" t="inlineStr">
+        <is>
+          <t>lịch sử sở hữu và ngày bàn giao đầu tiên (VEH-02), "ngày đó xe của ai"</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="94.5" customHeight="1">
+      <c r="A107" s="6" t="inlineStr">
+        <is>
           <t>battery_installation_periods</t>
         </is>
       </c>
-      <c r="B106" s="6" t="inlineStr">
+      <c r="B107" s="6" t="inlineStr">
         <is>
           <t>một lần pin nằm trên một xe</t>
         </is>
       </c>
-      <c r="C106" s="6" t="inlineStr">
+      <c r="C107" s="6" t="inlineStr">
         <is>
           <t>battery_id, vehicle_id, installed_from, installed_until (NULL khi đang lắp)</t>
         </is>
       </c>
-      <c r="D106" s="6" t="inlineStr">
+      <c r="D107" s="6" t="inlineStr">
         <is>
           <t>lịch sử sức khỏe pin qua các xe (MON-07), bộ đếm bảo hành pin (WAR-01)</t>
         </is>
       </c>
     </row>
-    <row r="107"/>
-    <row r="108">
-      <c r="A108" s="8" t="inlineStr">
+    <row r="108"/>
+    <row r="109">
+      <c r="A109" s="8" t="inlineStr">
         <is>
           <t>Các quyết định còn mở</t>
         </is>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" s="4" t="inlineStr">
+    <row r="110">
+      <c r="A110" s="4" t="inlineStr">
         <is>
           <t>Mã</t>
         </is>
       </c>
-      <c r="B109" s="4" t="inlineStr">
+      <c r="B110" s="4" t="inlineStr">
         <is>
           <t>Câu hỏi</t>
         </is>
       </c>
-      <c r="C109" s="4" t="inlineStr">
+      <c r="C110" s="4" t="inlineStr">
         <is>
           <t>Ảnh hưởng tới</t>
         </is>
       </c>
     </row>
-    <row r="110" ht="54" customHeight="1">
-      <c r="A110" s="6" t="inlineStr">
+    <row r="111" ht="54" customHeight="1">
+      <c r="A111" s="6" t="inlineStr">
         <is>
           <t>D5</t>
         </is>
       </c>
-      <c r="B110" s="6" t="inlineStr">
+      <c r="B111" s="6" t="inlineStr">
         <is>
           <t>Ai trả tiền khi tài xế của đội xe sạc: ví của tài xế, ví của đội xe, hay tùy trường hợp?</t>
         </is>
       </c>
-      <c r="C110" s="6" t="inlineStr">
+      <c r="C111" s="6" t="inlineStr">
         <is>
           <t>wallets, payments</t>
         </is>
@@ -4465,114 +4512,117 @@
     <hyperlink ref="C43" location="'drivers'!A1"/>
     <hyperlink ref="D43" location="'drivers'!A1"/>
     <hyperlink ref="I43" location="'drivers'!A1"/>
-    <hyperlink ref="C44" location="'driver_vehicle_assignments'!A1"/>
-    <hyperlink ref="D44" location="'driver_vehicle_assignments'!A1"/>
-    <hyperlink ref="I44" location="'driver_vehicle_assignments'!A1"/>
-    <hyperlink ref="C45" location="'driving_sessions'!A1"/>
-    <hyperlink ref="D45" location="'driving_sessions'!A1"/>
-    <hyperlink ref="I45" location="'driving_sessions'!A1"/>
-    <hyperlink ref="C46" location="'charging_credentials'!A1"/>
-    <hyperlink ref="D46" location="'charging_credentials'!A1"/>
-    <hyperlink ref="I46" location="'charging_credentials'!A1"/>
-    <hyperlink ref="C48" location="'fleets'!A1"/>
-    <hyperlink ref="D48" location="'fleets'!A1"/>
-    <hyperlink ref="I48" location="'fleets'!A1"/>
-    <hyperlink ref="C49" location="'fleet_vehicle_memberships'!A1"/>
-    <hyperlink ref="D49" location="'fleet_vehicle_memberships'!A1"/>
-    <hyperlink ref="I49" location="'fleet_vehicle_memberships'!A1"/>
-    <hyperlink ref="C50" location="'geofences'!A1"/>
-    <hyperlink ref="D50" location="'geofences'!A1"/>
-    <hyperlink ref="I50" location="'geofences'!A1"/>
-    <hyperlink ref="C51" location="'fleet_user_assignments'!A1"/>
-    <hyperlink ref="D51" location="'fleet_user_assignments'!A1"/>
-    <hyperlink ref="I51" location="'fleet_user_assignments'!A1"/>
-    <hyperlink ref="C53" location="'charging_stations'!A1"/>
-    <hyperlink ref="D53" location="'charging_stations'!A1"/>
-    <hyperlink ref="I53" location="'charging_stations'!A1"/>
-    <hyperlink ref="C54" location="'charging_evses'!A1"/>
-    <hyperlink ref="D54" location="'charging_evses'!A1"/>
-    <hyperlink ref="I54" location="'charging_evses'!A1"/>
-    <hyperlink ref="C55" location="'charging_connectors'!A1"/>
-    <hyperlink ref="D55" location="'charging_connectors'!A1"/>
-    <hyperlink ref="I55" location="'charging_connectors'!A1"/>
-    <hyperlink ref="C56" location="'charging_ocpp_messages'!A1"/>
-    <hyperlink ref="D56" location="'charging_ocpp_messages'!A1"/>
-    <hyperlink ref="I56" location="'charging_ocpp_messages'!A1"/>
-    <hyperlink ref="C57" location="'charging_station_config_entries'!A1"/>
-    <hyperlink ref="D57" location="'charging_station_config_entries'!A1"/>
-    <hyperlink ref="I57" location="'charging_station_config_entries'!A1"/>
-    <hyperlink ref="C58" location="'charging_reservations'!A1"/>
-    <hyperlink ref="D58" location="'charging_reservations'!A1"/>
-    <hyperlink ref="I58" location="'charging_reservations'!A1"/>
-    <hyperlink ref="C60" location="'charging_sessions'!A1"/>
-    <hyperlink ref="D60" location="'charging_sessions'!A1"/>
-    <hyperlink ref="I60" location="'charging_sessions'!A1"/>
-    <hyperlink ref="C61" location="'charging_session_events'!A1"/>
-    <hyperlink ref="D61" location="'charging_session_events'!A1"/>
-    <hyperlink ref="I61" location="'charging_session_events'!A1"/>
-    <hyperlink ref="C62" location="'charging_session_measurements'!A1"/>
-    <hyperlink ref="D62" location="'charging_session_measurements'!A1"/>
-    <hyperlink ref="I62" location="'charging_session_measurements'!A1"/>
-    <hyperlink ref="C64" location="'notifications'!A1"/>
-    <hyperlink ref="D64" location="'notifications'!A1"/>
-    <hyperlink ref="I64" location="'notifications'!A1"/>
-    <hyperlink ref="C66" location="'support_cases'!A1"/>
-    <hyperlink ref="D66" location="'support_cases'!A1"/>
-    <hyperlink ref="I66" location="'support_cases'!A1"/>
-    <hyperlink ref="C67" location="'repair_partners'!A1"/>
-    <hyperlink ref="D67" location="'repair_partners'!A1"/>
-    <hyperlink ref="I67" location="'repair_partners'!A1"/>
-    <hyperlink ref="C68" location="'maintenance_bookings'!A1"/>
-    <hyperlink ref="D68" location="'maintenance_bookings'!A1"/>
-    <hyperlink ref="I68" location="'maintenance_bookings'!A1"/>
-    <hyperlink ref="C70" location="'charging_policies'!A1"/>
-    <hyperlink ref="D70" location="'charging_policies'!A1"/>
-    <hyperlink ref="I70" location="'charging_policies'!A1"/>
-    <hyperlink ref="C71" location="'charging_policy_versions'!A1"/>
-    <hyperlink ref="D71" location="'charging_policy_versions'!A1"/>
-    <hyperlink ref="I71" location="'charging_policy_versions'!A1"/>
-    <hyperlink ref="C72" location="'charging_policy_assignments'!A1"/>
-    <hyperlink ref="D72" location="'charging_policy_assignments'!A1"/>
-    <hyperlink ref="I72" location="'charging_policy_assignments'!A1"/>
-    <hyperlink ref="C73" location="'policy_violations'!A1"/>
-    <hyperlink ref="D73" location="'policy_violations'!A1"/>
-    <hyperlink ref="I73" location="'policy_violations'!A1"/>
-    <hyperlink ref="C75" location="'tariffs'!A1"/>
-    <hyperlink ref="D75" location="'tariffs'!A1"/>
-    <hyperlink ref="I75" location="'tariffs'!A1"/>
-    <hyperlink ref="C76" location="'payments'!A1"/>
-    <hyperlink ref="D76" location="'payments'!A1"/>
-    <hyperlink ref="I76" location="'payments'!A1"/>
-    <hyperlink ref="C77" location="'wallets'!A1"/>
-    <hyperlink ref="D77" location="'wallets'!A1"/>
-    <hyperlink ref="I77" location="'wallets'!A1"/>
-    <hyperlink ref="C78" location="'wallet_transactions'!A1"/>
-    <hyperlink ref="D78" location="'wallet_transactions'!A1"/>
-    <hyperlink ref="I78" location="'wallet_transactions'!A1"/>
-    <hyperlink ref="C79" location="'invoices'!A1"/>
-    <hyperlink ref="D79" location="'invoices'!A1"/>
-    <hyperlink ref="I79" location="'invoices'!A1"/>
-    <hyperlink ref="C80" location="'invoice_lines'!A1"/>
-    <hyperlink ref="D80" location="'invoice_lines'!A1"/>
-    <hyperlink ref="I80" location="'invoice_lines'!A1"/>
-    <hyperlink ref="C81" location="'subscription_plans'!A1"/>
-    <hyperlink ref="D81" location="'subscription_plans'!A1"/>
-    <hyperlink ref="I81" location="'subscription_plans'!A1"/>
-    <hyperlink ref="C82" location="'plan_features'!A1"/>
-    <hyperlink ref="D82" location="'plan_features'!A1"/>
-    <hyperlink ref="I82" location="'plan_features'!A1"/>
-    <hyperlink ref="C83" location="'subscriptions'!A1"/>
-    <hyperlink ref="D83" location="'subscriptions'!A1"/>
-    <hyperlink ref="I83" location="'subscriptions'!A1"/>
-    <hyperlink ref="C85" location="'driver_scores'!A1"/>
-    <hyperlink ref="D85" location="'driver_scores'!A1"/>
-    <hyperlink ref="I85" location="'driver_scores'!A1"/>
-    <hyperlink ref="C87" location="'promotion_campaigns'!A1"/>
-    <hyperlink ref="D87" location="'promotion_campaigns'!A1"/>
-    <hyperlink ref="I87" location="'promotion_campaigns'!A1"/>
-    <hyperlink ref="C88" location="'trips'!A1"/>
-    <hyperlink ref="D88" location="'trips'!A1"/>
-    <hyperlink ref="I88" location="'trips'!A1"/>
+    <hyperlink ref="C44" location="'driver_history'!A1"/>
+    <hyperlink ref="D44" location="'driver_history'!A1"/>
+    <hyperlink ref="I44" location="'driver_history'!A1"/>
+    <hyperlink ref="C45" location="'driver_vehicle_assignments'!A1"/>
+    <hyperlink ref="D45" location="'driver_vehicle_assignments'!A1"/>
+    <hyperlink ref="I45" location="'driver_vehicle_assignments'!A1"/>
+    <hyperlink ref="C46" location="'driving_sessions'!A1"/>
+    <hyperlink ref="D46" location="'driving_sessions'!A1"/>
+    <hyperlink ref="I46" location="'driving_sessions'!A1"/>
+    <hyperlink ref="C47" location="'charging_credentials'!A1"/>
+    <hyperlink ref="D47" location="'charging_credentials'!A1"/>
+    <hyperlink ref="I47" location="'charging_credentials'!A1"/>
+    <hyperlink ref="C49" location="'fleets'!A1"/>
+    <hyperlink ref="D49" location="'fleets'!A1"/>
+    <hyperlink ref="I49" location="'fleets'!A1"/>
+    <hyperlink ref="C50" location="'fleet_vehicle_memberships'!A1"/>
+    <hyperlink ref="D50" location="'fleet_vehicle_memberships'!A1"/>
+    <hyperlink ref="I50" location="'fleet_vehicle_memberships'!A1"/>
+    <hyperlink ref="C51" location="'geofences'!A1"/>
+    <hyperlink ref="D51" location="'geofences'!A1"/>
+    <hyperlink ref="I51" location="'geofences'!A1"/>
+    <hyperlink ref="C52" location="'fleet_user_assignments'!A1"/>
+    <hyperlink ref="D52" location="'fleet_user_assignments'!A1"/>
+    <hyperlink ref="I52" location="'fleet_user_assignments'!A1"/>
+    <hyperlink ref="C54" location="'charging_stations'!A1"/>
+    <hyperlink ref="D54" location="'charging_stations'!A1"/>
+    <hyperlink ref="I54" location="'charging_stations'!A1"/>
+    <hyperlink ref="C55" location="'charging_evses'!A1"/>
+    <hyperlink ref="D55" location="'charging_evses'!A1"/>
+    <hyperlink ref="I55" location="'charging_evses'!A1"/>
+    <hyperlink ref="C56" location="'charging_connectors'!A1"/>
+    <hyperlink ref="D56" location="'charging_connectors'!A1"/>
+    <hyperlink ref="I56" location="'charging_connectors'!A1"/>
+    <hyperlink ref="C57" location="'charging_ocpp_messages'!A1"/>
+    <hyperlink ref="D57" location="'charging_ocpp_messages'!A1"/>
+    <hyperlink ref="I57" location="'charging_ocpp_messages'!A1"/>
+    <hyperlink ref="C58" location="'charging_station_config_entries'!A1"/>
+    <hyperlink ref="D58" location="'charging_station_config_entries'!A1"/>
+    <hyperlink ref="I58" location="'charging_station_config_entries'!A1"/>
+    <hyperlink ref="C59" location="'charging_reservations'!A1"/>
+    <hyperlink ref="D59" location="'charging_reservations'!A1"/>
+    <hyperlink ref="I59" location="'charging_reservations'!A1"/>
+    <hyperlink ref="C61" location="'charging_sessions'!A1"/>
+    <hyperlink ref="D61" location="'charging_sessions'!A1"/>
+    <hyperlink ref="I61" location="'charging_sessions'!A1"/>
+    <hyperlink ref="C62" location="'charging_session_events'!A1"/>
+    <hyperlink ref="D62" location="'charging_session_events'!A1"/>
+    <hyperlink ref="I62" location="'charging_session_events'!A1"/>
+    <hyperlink ref="C63" location="'charging_session_measurements'!A1"/>
+    <hyperlink ref="D63" location="'charging_session_measurements'!A1"/>
+    <hyperlink ref="I63" location="'charging_session_measurements'!A1"/>
+    <hyperlink ref="C65" location="'notifications'!A1"/>
+    <hyperlink ref="D65" location="'notifications'!A1"/>
+    <hyperlink ref="I65" location="'notifications'!A1"/>
+    <hyperlink ref="C67" location="'support_cases'!A1"/>
+    <hyperlink ref="D67" location="'support_cases'!A1"/>
+    <hyperlink ref="I67" location="'support_cases'!A1"/>
+    <hyperlink ref="C68" location="'repair_partners'!A1"/>
+    <hyperlink ref="D68" location="'repair_partners'!A1"/>
+    <hyperlink ref="I68" location="'repair_partners'!A1"/>
+    <hyperlink ref="C69" location="'maintenance_bookings'!A1"/>
+    <hyperlink ref="D69" location="'maintenance_bookings'!A1"/>
+    <hyperlink ref="I69" location="'maintenance_bookings'!A1"/>
+    <hyperlink ref="C71" location="'charging_policies'!A1"/>
+    <hyperlink ref="D71" location="'charging_policies'!A1"/>
+    <hyperlink ref="I71" location="'charging_policies'!A1"/>
+    <hyperlink ref="C72" location="'charging_policy_versions'!A1"/>
+    <hyperlink ref="D72" location="'charging_policy_versions'!A1"/>
+    <hyperlink ref="I72" location="'charging_policy_versions'!A1"/>
+    <hyperlink ref="C73" location="'charging_policy_assignments'!A1"/>
+    <hyperlink ref="D73" location="'charging_policy_assignments'!A1"/>
+    <hyperlink ref="I73" location="'charging_policy_assignments'!A1"/>
+    <hyperlink ref="C74" location="'policy_violations'!A1"/>
+    <hyperlink ref="D74" location="'policy_violations'!A1"/>
+    <hyperlink ref="I74" location="'policy_violations'!A1"/>
+    <hyperlink ref="C76" location="'tariffs'!A1"/>
+    <hyperlink ref="D76" location="'tariffs'!A1"/>
+    <hyperlink ref="I76" location="'tariffs'!A1"/>
+    <hyperlink ref="C77" location="'payments'!A1"/>
+    <hyperlink ref="D77" location="'payments'!A1"/>
+    <hyperlink ref="I77" location="'payments'!A1"/>
+    <hyperlink ref="C78" location="'wallets'!A1"/>
+    <hyperlink ref="D78" location="'wallets'!A1"/>
+    <hyperlink ref="I78" location="'wallets'!A1"/>
+    <hyperlink ref="C79" location="'wallet_transactions'!A1"/>
+    <hyperlink ref="D79" location="'wallet_transactions'!A1"/>
+    <hyperlink ref="I79" location="'wallet_transactions'!A1"/>
+    <hyperlink ref="C80" location="'invoices'!A1"/>
+    <hyperlink ref="D80" location="'invoices'!A1"/>
+    <hyperlink ref="I80" location="'invoices'!A1"/>
+    <hyperlink ref="C81" location="'invoice_lines'!A1"/>
+    <hyperlink ref="D81" location="'invoice_lines'!A1"/>
+    <hyperlink ref="I81" location="'invoice_lines'!A1"/>
+    <hyperlink ref="C82" location="'subscription_plans'!A1"/>
+    <hyperlink ref="D82" location="'subscription_plans'!A1"/>
+    <hyperlink ref="I82" location="'subscription_plans'!A1"/>
+    <hyperlink ref="C83" location="'plan_features'!A1"/>
+    <hyperlink ref="D83" location="'plan_features'!A1"/>
+    <hyperlink ref="I83" location="'plan_features'!A1"/>
+    <hyperlink ref="C84" location="'subscriptions'!A1"/>
+    <hyperlink ref="D84" location="'subscriptions'!A1"/>
+    <hyperlink ref="I84" location="'subscriptions'!A1"/>
+    <hyperlink ref="C86" location="'driver_scores'!A1"/>
+    <hyperlink ref="D86" location="'driver_scores'!A1"/>
+    <hyperlink ref="I86" location="'driver_scores'!A1"/>
+    <hyperlink ref="C88" location="'promotion_campaigns'!A1"/>
+    <hyperlink ref="D88" location="'promotion_campaigns'!A1"/>
+    <hyperlink ref="I88" location="'promotion_campaigns'!A1"/>
+    <hyperlink ref="C89" location="'trips'!A1"/>
+    <hyperlink ref="D89" location="'trips'!A1"/>
+    <hyperlink ref="I89" location="'trips'!A1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10083,7 +10133,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I61"/>
+  <dimension ref="A1:I60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -10875,11 +10925,11 @@
         </is>
       </c>
     </row>
-    <row r="37">
+    <row r="37" ht="27" customHeight="1">
       <c r="A37" s="6" t="n"/>
       <c r="B37" s="7" t="inlineStr">
         <is>
-          <t>drivers</t>
+          <t>driver_vehicle_assignments</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
@@ -10888,11 +10938,11 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="27" customHeight="1">
+    <row r="38">
       <c r="A38" s="6" t="n"/>
       <c r="B38" s="7" t="inlineStr">
         <is>
-          <t>driver_vehicle_assignments</t>
+          <t>driving_sessions</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
@@ -10905,7 +10955,7 @@
       <c r="A39" s="6" t="n"/>
       <c r="B39" s="7" t="inlineStr">
         <is>
-          <t>driving_sessions</t>
+          <t>charging_credentials</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
@@ -10918,7 +10968,7 @@
       <c r="A40" s="6" t="n"/>
       <c r="B40" s="7" t="inlineStr">
         <is>
-          <t>charging_credentials</t>
+          <t>fleets</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
@@ -10927,11 +10977,11 @@
         </is>
       </c>
     </row>
-    <row r="41">
+    <row r="41" ht="27" customHeight="1">
       <c r="A41" s="6" t="n"/>
       <c r="B41" s="7" t="inlineStr">
         <is>
-          <t>fleets</t>
+          <t>fleet_vehicle_memberships</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
@@ -10940,11 +10990,11 @@
         </is>
       </c>
     </row>
-    <row r="42" ht="27" customHeight="1">
+    <row r="42">
       <c r="A42" s="6" t="n"/>
       <c r="B42" s="7" t="inlineStr">
         <is>
-          <t>fleet_vehicle_memberships</t>
+          <t>fleet_user_assignments</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
@@ -10957,7 +11007,7 @@
       <c r="A43" s="6" t="n"/>
       <c r="B43" s="7" t="inlineStr">
         <is>
-          <t>fleet_user_assignments</t>
+          <t>geofences</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
@@ -10970,7 +11020,7 @@
       <c r="A44" s="6" t="n"/>
       <c r="B44" s="7" t="inlineStr">
         <is>
-          <t>geofences</t>
+          <t>charging_reservations</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
@@ -10983,7 +11033,7 @@
       <c r="A45" s="6" t="n"/>
       <c r="B45" s="7" t="inlineStr">
         <is>
-          <t>charging_reservations</t>
+          <t>charging_sessions</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
@@ -10996,7 +11046,7 @@
       <c r="A46" s="6" t="n"/>
       <c r="B46" s="7" t="inlineStr">
         <is>
-          <t>charging_sessions</t>
+          <t>notifications</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
@@ -11009,7 +11059,7 @@
       <c r="A47" s="6" t="n"/>
       <c r="B47" s="7" t="inlineStr">
         <is>
-          <t>notifications</t>
+          <t>support_cases</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
@@ -11022,7 +11072,7 @@
       <c r="A48" s="6" t="n"/>
       <c r="B48" s="7" t="inlineStr">
         <is>
-          <t>support_cases</t>
+          <t>repair_partners</t>
         </is>
       </c>
       <c r="C48" s="6" t="inlineStr">
@@ -11035,7 +11085,7 @@
       <c r="A49" s="6" t="n"/>
       <c r="B49" s="7" t="inlineStr">
         <is>
-          <t>repair_partners</t>
+          <t>maintenance_bookings</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
@@ -11044,11 +11094,11 @@
         </is>
       </c>
     </row>
-    <row r="50">
+    <row r="50" ht="27" customHeight="1">
       <c r="A50" s="6" t="n"/>
       <c r="B50" s="7" t="inlineStr">
         <is>
-          <t>maintenance_bookings</t>
+          <t>charging_policy_assignments</t>
         </is>
       </c>
       <c r="C50" s="6" t="inlineStr">
@@ -11057,11 +11107,11 @@
         </is>
       </c>
     </row>
-    <row r="51" ht="27" customHeight="1">
+    <row r="51">
       <c r="A51" s="6" t="n"/>
       <c r="B51" s="7" t="inlineStr">
         <is>
-          <t>charging_policy_assignments</t>
+          <t>policy_violations</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
@@ -11074,7 +11124,7 @@
       <c r="A52" s="6" t="n"/>
       <c r="B52" s="7" t="inlineStr">
         <is>
-          <t>policy_violations</t>
+          <t>payments</t>
         </is>
       </c>
       <c r="C52" s="6" t="inlineStr">
@@ -11087,7 +11137,7 @@
       <c r="A53" s="6" t="n"/>
       <c r="B53" s="7" t="inlineStr">
         <is>
-          <t>payments</t>
+          <t>wallets</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
@@ -11100,7 +11150,7 @@
       <c r="A54" s="6" t="n"/>
       <c r="B54" s="7" t="inlineStr">
         <is>
-          <t>wallets</t>
+          <t>wallet_transactions</t>
         </is>
       </c>
       <c r="C54" s="6" t="inlineStr">
@@ -11113,7 +11163,7 @@
       <c r="A55" s="6" t="n"/>
       <c r="B55" s="7" t="inlineStr">
         <is>
-          <t>wallet_transactions</t>
+          <t>invoices</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
@@ -11126,7 +11176,7 @@
       <c r="A56" s="6" t="n"/>
       <c r="B56" s="7" t="inlineStr">
         <is>
-          <t>invoices</t>
+          <t>invoice_lines</t>
         </is>
       </c>
       <c r="C56" s="6" t="inlineStr">
@@ -11139,7 +11189,7 @@
       <c r="A57" s="6" t="n"/>
       <c r="B57" s="7" t="inlineStr">
         <is>
-          <t>invoice_lines</t>
+          <t>subscriptions</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
@@ -11152,7 +11202,7 @@
       <c r="A58" s="6" t="n"/>
       <c r="B58" s="7" t="inlineStr">
         <is>
-          <t>subscriptions</t>
+          <t>driver_scores</t>
         </is>
       </c>
       <c r="C58" s="6" t="inlineStr">
@@ -11165,7 +11215,7 @@
       <c r="A59" s="6" t="n"/>
       <c r="B59" s="7" t="inlineStr">
         <is>
-          <t>driver_scores</t>
+          <t>trips</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
@@ -11178,23 +11228,10 @@
       <c r="A60" s="6" t="n"/>
       <c r="B60" s="7" t="inlineStr">
         <is>
-          <t>trips</t>
+          <t>organization_history</t>
         </is>
       </c>
       <c r="C60" s="6" t="inlineStr">
-        <is>
-          <t>organization_id</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="6" t="n"/>
-      <c r="B61" s="7" t="inlineStr">
-        <is>
-          <t>organization_history</t>
-        </is>
-      </c>
-      <c r="C61" s="6" t="inlineStr">
         <is>
           <t>organization_id</t>
         </is>
@@ -11217,31 +11254,30 @@
     <hyperlink ref="B34" location="'batteries'!A1"/>
     <hyperlink ref="B35" location="'telematics'!A1"/>
     <hyperlink ref="B36" location="'telemetry'!A1"/>
-    <hyperlink ref="B37" location="'drivers'!A1"/>
-    <hyperlink ref="B38" location="'driver_vehicle_assignments'!A1"/>
-    <hyperlink ref="B39" location="'driving_sessions'!A1"/>
-    <hyperlink ref="B40" location="'charging_credentials'!A1"/>
-    <hyperlink ref="B41" location="'fleets'!A1"/>
-    <hyperlink ref="B42" location="'fleet_vehicle_memberships'!A1"/>
-    <hyperlink ref="B43" location="'fleet_user_assignments'!A1"/>
-    <hyperlink ref="B44" location="'geofences'!A1"/>
-    <hyperlink ref="B45" location="'charging_reservations'!A1"/>
-    <hyperlink ref="B46" location="'charging_sessions'!A1"/>
-    <hyperlink ref="B47" location="'notifications'!A1"/>
-    <hyperlink ref="B48" location="'support_cases'!A1"/>
-    <hyperlink ref="B49" location="'repair_partners'!A1"/>
-    <hyperlink ref="B50" location="'maintenance_bookings'!A1"/>
-    <hyperlink ref="B51" location="'charging_policy_assignments'!A1"/>
-    <hyperlink ref="B52" location="'policy_violations'!A1"/>
-    <hyperlink ref="B53" location="'payments'!A1"/>
-    <hyperlink ref="B54" location="'wallets'!A1"/>
-    <hyperlink ref="B55" location="'wallet_transactions'!A1"/>
-    <hyperlink ref="B56" location="'invoices'!A1"/>
-    <hyperlink ref="B57" location="'invoice_lines'!A1"/>
-    <hyperlink ref="B58" location="'subscriptions'!A1"/>
-    <hyperlink ref="B59" location="'driver_scores'!A1"/>
-    <hyperlink ref="B60" location="'trips'!A1"/>
-    <hyperlink ref="B61" location="'organization_history'!A1"/>
+    <hyperlink ref="B37" location="'driver_vehicle_assignments'!A1"/>
+    <hyperlink ref="B38" location="'driving_sessions'!A1"/>
+    <hyperlink ref="B39" location="'charging_credentials'!A1"/>
+    <hyperlink ref="B40" location="'fleets'!A1"/>
+    <hyperlink ref="B41" location="'fleet_vehicle_memberships'!A1"/>
+    <hyperlink ref="B42" location="'fleet_user_assignments'!A1"/>
+    <hyperlink ref="B43" location="'geofences'!A1"/>
+    <hyperlink ref="B44" location="'charging_reservations'!A1"/>
+    <hyperlink ref="B45" location="'charging_sessions'!A1"/>
+    <hyperlink ref="B46" location="'notifications'!A1"/>
+    <hyperlink ref="B47" location="'support_cases'!A1"/>
+    <hyperlink ref="B48" location="'repair_partners'!A1"/>
+    <hyperlink ref="B49" location="'maintenance_bookings'!A1"/>
+    <hyperlink ref="B50" location="'charging_policy_assignments'!A1"/>
+    <hyperlink ref="B51" location="'policy_violations'!A1"/>
+    <hyperlink ref="B52" location="'payments'!A1"/>
+    <hyperlink ref="B53" location="'wallets'!A1"/>
+    <hyperlink ref="B54" location="'wallet_transactions'!A1"/>
+    <hyperlink ref="B55" location="'invoices'!A1"/>
+    <hyperlink ref="B56" location="'invoice_lines'!A1"/>
+    <hyperlink ref="B57" location="'subscriptions'!A1"/>
+    <hyperlink ref="B58" location="'driver_scores'!A1"/>
+    <hyperlink ref="B59" location="'trips'!A1"/>
+    <hyperlink ref="B60" location="'organization_history'!A1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -20629,7 +20665,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I34"/>
+  <dimension ref="A1:I36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -20667,180 +20703,150 @@
     <row r="4">
       <c r="A4" s="11" t="inlineStr">
         <is>
-          <t>Một tài xế do khách hàng tuyển dụng (hoặc chính là khách hàng).</t>
-        </is>
-      </c>
-    </row>
-    <row r="5"/>
-    <row r="6" ht="27" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
+          <t>Hồ sơ tài xế: các thông tin mà hệ thống dùng về công việc lái xe của một người trong một tổ chức (ID-13). Người đó là ai (họ tên, số điện thoại) nằm ở users; tổ chức được đọc qua thành viên. Người lái xe cho hai tổ chức có hai hồ sơ, và mỗi tổ chức chịu trách nhiệm về hồ sơ của mình (DR-09). Tài xế được nhận xe khi hồ sơ ACTIVE và chưa bị xóa, giấy phép chưa hết hạn, thành viên và người dùng đều ACTIVE (DR-10). Ràng buộc kiểm tra: deleted_at IS NULL OR status = 'INACTIVE' (DM-25).</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>🔍 Lưu lịch sử: khi một cột có dấu 🔍 thay đổi, toàn bộ dòng cũ được chép sang bảng driver_history.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6"/>
+    <row r="7" ht="27" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>Cột</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>Kiểu dữ liệu</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>Cho phép rỗng</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>Khóa</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>Tham chiếu tới</t>
         </is>
       </c>
-      <c r="G6" s="4" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>Ý nghĩa</t>
         </is>
       </c>
-      <c r="H6" s="4" t="inlineStr">
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>Ví dụ</t>
         </is>
       </c>
-      <c r="I6" s="4" t="inlineStr">
+      <c r="I7" s="4" t="inlineStr">
         <is>
           <t>Lưu lịch sử</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="6" t="n">
+    <row r="8">
+      <c r="A8" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>driver_id</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="C8" s="6" t="inlineStr">
         <is>
           <t>uuid</t>
         </is>
       </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="inlineStr">
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="F7" s="6" t="n"/>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>Mã nội bộ của tài xế.</t>
-        </is>
-      </c>
-      <c r="H7" s="6" t="inlineStr">
+      <c r="F8" s="6" t="n"/>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>Mã nội bộ của hồ sơ tài xế.</t>
+        </is>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
         <is>
           <t>6e3b9d2a-4c1f-4e8b-9a7d-0c2e5f1b8d66</t>
         </is>
       </c>
-      <c r="I7" s="6" t="n"/>
-    </row>
-    <row r="8" ht="27" customHeight="1">
-      <c r="A8" s="6" t="n">
+      <c r="I8" s="6" t="n"/>
+    </row>
+    <row r="9" ht="67.5" customHeight="1">
+      <c r="A9" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>organization_id</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>membership_id</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
         <is>
           <t>uuid</t>
         </is>
       </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>có</t>
-        </is>
-      </c>
-      <c r="E8" s="6" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="F8" s="7" t="inlineStr">
-        <is>
-          <t>organizations.organization_id (khi xóa: chặn xóa)</t>
-        </is>
-      </c>
-      <c r="G8" s="6" t="inlineStr">
-        <is>
-          <t>Tổ chức khách hàng tuyển dụng tài xế.</t>
-        </is>
-      </c>
-      <c r="H8" s="6" t="inlineStr">
-        <is>
-          <t>3f6c2a1e-8b4d-4e2a-9c1f-0a7d5b2e4c11</t>
-        </is>
-      </c>
-      <c r="I8" s="6" t="n"/>
-    </row>
-    <row r="9" ht="40.5" customHeight="1">
-      <c r="A9" s="6" t="n">
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>FK UQ</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>memberships.membership_id (khi xóa: chặn xóa)</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>Thành viên (một người trong một tổ chức) sở hữu hồ sơ này; tổ chức được đọc qua thành viên (DM-24). Người lái xe cho hai tổ chức có một hồ sơ ở mỗi tổ chức, và mỗi tổ chức tự giữ bản thông tin của mình. Thành viên mới sau khi đã rời đi có hồ sơ mới.</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>00000022-5a6b-4c7d-8e9f-0a1b2c3d4e5f</t>
+        </is>
+      </c>
+      <c r="I9" s="6" t="inlineStr">
+        <is>
+          <t>🔍</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="27" customHeight="1">
+      <c r="A10" s="6" t="n">
         <v>3</v>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>membership_id</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>uuid</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>có</t>
-        </is>
-      </c>
-      <c r="E9" s="6" t="inlineStr">
-        <is>
-          <t>FK UQ</t>
-        </is>
-      </c>
-      <c r="F9" s="7" t="inlineStr">
-        <is>
-          <t>memberships.membership_id (khi xóa: chặn xóa)</t>
-        </is>
-      </c>
-      <c r="G9" s="6" t="inlineStr">
-        <is>
-          <t>Thành viên (người trong tổ chức này) sở hữu hồ sơ tài xế; người lái xe cho hai công ty có một hồ sơ tài xế ở mỗi công ty. Vai trò DRIVER cần một hồ sơ còn hiệu lực.</t>
-        </is>
-      </c>
-      <c r="H9" s="6" t="inlineStr">
-        <is>
-          <t>00000022-5a6b-4c7d-8e9f-0a1b2c3d4e5f</t>
-        </is>
-      </c>
-      <c r="I9" s="6" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="6" t="n">
-        <v>4</v>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
@@ -20861,7 +20867,7 @@
       <c r="F10" s="6" t="n"/>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>Họ tên tài xế.</t>
+          <t>[Sẽ bỏ: DR-09] Họ tên tài xế; là thông tin của con người, đã có ở users.full_name.</t>
         </is>
       </c>
       <c r="H10" s="6" t="inlineStr">
@@ -20871,9 +20877,9 @@
       </c>
       <c r="I10" s="6" t="n"/>
     </row>
-    <row r="11">
+    <row r="11" ht="27" customHeight="1">
       <c r="A11" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
@@ -20898,7 +20904,7 @@
       <c r="F11" s="6" t="n"/>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>Số điện thoại liên hệ, duy nhất.</t>
+          <t>[Sẽ bỏ: DR-09] Số điện thoại liên hệ; là thông tin của con người, đã có ở users.phone_number.</t>
         </is>
       </c>
       <c r="H11" s="6" t="inlineStr">
@@ -20908,9 +20914,9 @@
       </c>
       <c r="I11" s="6" t="n"/>
     </row>
-    <row r="12" ht="27" customHeight="1">
+    <row r="12" ht="67.5" customHeight="1">
       <c r="A12" s="6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
@@ -20927,15 +20933,11 @@
           <t>không</t>
         </is>
       </c>
-      <c r="E12" s="6" t="inlineStr">
-        <is>
-          <t>UQ</t>
-        </is>
-      </c>
+      <c r="E12" s="6" t="n"/>
       <c r="F12" s="6" t="n"/>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>Số giấy phép lái xe, duy nhất; là khóa nghiệp vụ của tài xế.</t>
+          <t>Số giấy phép lái xe do tổ chức này ghi nhận. Không duy nhất: người lái xe cho hai tổ chức có số này ở cả hai hồ sơ. Khi số đã có trên hồ sơ còn hiệu lực của người khác, ứng dụng chỉ cảnh báo chứ không từ chối, để một tổ chức không biết gì về tài xế của tổ chức khác (DR-09).</t>
         </is>
       </c>
       <c r="H12" s="6" t="inlineStr">
@@ -20943,20 +20945,24 @@
           <t>790123456789</t>
         </is>
       </c>
-      <c r="I12" s="6" t="n"/>
-    </row>
-    <row r="13">
+      <c r="I12" s="6" t="inlineStr">
+        <is>
+          <t>🔍</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="54" customHeight="1">
       <c r="A13" s="6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>license_class</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>driverstatus</t>
+          <t>varchar(5)</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
@@ -20968,28 +20974,32 @@
       <c r="F13" s="6" t="n"/>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>Trạng thái của tài xế.</t>
+          <t>Hạng giấy phép lái xe theo Luật 36/2024/QH15 (hạng cao nhất dùng cho xe tải). Đầu kéo cần hạng CE; hạng khác chỉ bị cảnh báo khi nhận xe cho tới khi dòng xe có loại thân xe (DR-10).</t>
         </is>
       </c>
       <c r="H13" s="6" t="inlineStr">
         <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="I13" s="6" t="n"/>
-    </row>
-    <row r="14">
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="I13" s="6" t="inlineStr">
+        <is>
+          <t>🔍</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="54" customHeight="1">
       <c r="A14" s="6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>license_expires_on</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>timestamptz</t>
+          <t>date</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
@@ -21001,28 +21011,32 @@
       <c r="F14" s="6" t="n"/>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>Thời điểm tạo bản ghi (UTC).</t>
+          <t>Ngày hết hạn ghi trên giấy phép (DM-26); mọi hạng xe tải đều có thời hạn. "Hết hạn" được tính từ cột này, không lưu thành trạng thái; giấy phép hết hạn chặn việc nhận xe và dùng để nhắc gia hạn (DRV-01).</t>
         </is>
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
-          <t>2026-09-01T02:00:00Z</t>
-        </is>
-      </c>
-      <c r="I14" s="6" t="n"/>
-    </row>
-    <row r="15">
+          <t>2029-03-01</t>
+        </is>
+      </c>
+      <c r="I14" s="6" t="inlineStr">
+        <is>
+          <t>🔍</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="54" customHeight="1">
       <c r="A15" s="6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>updated_at</t>
+          <t>status</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>timestamptz</t>
+          <t>driverstatus</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
@@ -21034,28 +21048,32 @@
       <c r="F15" s="6" t="n"/>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>Thời điểm bản ghi được sửa gần nhất (UTC).</t>
+          <t>Do tổ chức quyết định. ACTIVE: được nhận xe (cùng các điều kiện khác của DR-10). INACTIVE: không được, ví dụ bị tạm đình chỉ, hoặc người đó đã rời đi (khi đó cũng bị xóa mềm).</t>
         </is>
       </c>
       <c r="H15" s="6" t="inlineStr">
         <is>
-          <t>2026-09-10T07:15:00Z</t>
-        </is>
-      </c>
-      <c r="I15" s="6" t="n"/>
-    </row>
-    <row r="16" ht="27" customHeight="1">
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="I15" s="6" t="inlineStr">
+        <is>
+          <t>🔍</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="40.5" customHeight="1">
       <c r="A16" s="6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>deleted_at</t>
+          <t>status_reason</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>timestamptz</t>
+          <t>varchar(200)</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
@@ -21067,40 +21085,128 @@
       <c r="F16" s="6" t="n"/>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>Thời điểm xóa mềm; NULL khi bản ghi còn hiệu lực. Không bao giờ xóa hẳn.</t>
+          <t>Lý do của trạng thái hiện tại, hoặc lý do hồ sơ rời hệ thống; NULL khi không có gì cần giải thích. Các lý do trước đó nằm trong driver_history.</t>
         </is>
       </c>
       <c r="H16" s="6" t="inlineStr">
         <is>
+          <t>Tạm đình chỉ sau va chạm ngày 12/09</t>
+        </is>
+      </c>
+      <c r="I16" s="6" t="inlineStr">
+        <is>
+          <t>🔍</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>created_at</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>timestamptz</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="n"/>
+      <c r="F17" s="6" t="n"/>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>Thời điểm tạo bản ghi (UTC).</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-01T02:00:00Z</t>
+        </is>
+      </c>
+      <c r="I17" s="6" t="inlineStr">
+        <is>
+          <t>🔍</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>updated_at</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>timestamptz</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="n"/>
+      <c r="F18" s="6" t="n"/>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>Thời điểm bản ghi được sửa gần nhất (UTC).</t>
+        </is>
+      </c>
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-10T07:15:00Z</t>
+        </is>
+      </c>
+      <c r="I18" s="6" t="inlineStr">
+        <is>
+          <t>🔍</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="81" customHeight="1">
+      <c r="A19" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>deleted_at</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>timestamptz</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="n"/>
+      <c r="F19" s="6" t="n"/>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>Thời điểm xóa mềm: hồ sơ không còn thuộc hệ thống, do người đó rời tổ chức (thành viên kết thúc) hoặc nhập nhầm (DM-25); mọi dữ liệu vẫn được giữ, lý do nằm trong status_reason. Khi thành viên kết thúc, hồ sơ được chuyển sang INACTIVE và điền cột này trong cùng giao dịch (DR-10). NULL khi còn thuộc hệ thống.</t>
+        </is>
+      </c>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
           <t>NULL</t>
         </is>
       </c>
-      <c r="I16" s="6" t="n"/>
-    </row>
-    <row r="17"/>
-    <row r="18">
-      <c r="A18" s="4" t="n"/>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>Kiểu enum</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>Giá trị cho phép</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="6" t="n"/>
-      <c r="B19" s="6" t="inlineStr">
-        <is>
-          <t>driverstatus</t>
-        </is>
-      </c>
-      <c r="C19" s="6" t="inlineStr">
-        <is>
-          <t>ACTIVE, INACTIVE</t>
+      <c r="I19" s="6" t="inlineStr">
+        <is>
+          <t>🔍</t>
         </is>
       </c>
     </row>
@@ -21109,23 +21215,12 @@
       <c r="A21" s="4" t="n"/>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Chỉ mục (index)</t>
+          <t>Kiểu enum</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>Các cột</t>
-        </is>
-      </c>
-      <c r="D21" s="4" t="inlineStr">
-        <is>
-          <t>Duy nhất</t>
-        </is>
-      </c>
-      <c r="E21" s="4" t="n"/>
-      <c r="F21" s="4" t="inlineStr">
-        <is>
-          <t>Ghi chú</t>
+          <t>Giá trị cho phép</t>
         </is>
       </c>
     </row>
@@ -21133,94 +21228,83 @@
       <c r="A22" s="6" t="n"/>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>ix_drivers_status</t>
+          <t>driverstatus</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="D22" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E22" s="6" t="n"/>
-      <c r="F22" s="6" t="n"/>
-    </row>
-    <row r="23" ht="27" customHeight="1">
-      <c r="A23" s="6" t="n"/>
-      <c r="B23" s="6" t="inlineStr">
+          <t>ACTIVE, INACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="23"/>
+    <row r="24">
+      <c r="A24" s="4" t="n"/>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>Chỉ mục (index)</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>Các cột</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>Duy nhất</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="n"/>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>Ghi chú</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="40.5" customHeight="1">
+      <c r="A25" s="6" t="n"/>
+      <c r="B25" s="6" t="inlineStr">
         <is>
           <t>ix_drivers_license_number</t>
         </is>
       </c>
-      <c r="C23" s="6" t="inlineStr">
+      <c r="C25" s="6" t="inlineStr">
         <is>
           <t>license_number</t>
         </is>
       </c>
-      <c r="D23" s="6" t="inlineStr">
-        <is>
-          <t>có</t>
-        </is>
-      </c>
-      <c r="E23" s="6" t="n"/>
-      <c r="F23" s="6" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="6" t="n"/>
-      <c r="B24" s="6" t="inlineStr">
-        <is>
-          <t>ix_drivers_phone_number</t>
-        </is>
-      </c>
-      <c r="C24" s="6" t="inlineStr">
-        <is>
-          <t>phone_number</t>
-        </is>
-      </c>
-      <c r="D24" s="6" t="inlineStr">
-        <is>
-          <t>có</t>
-        </is>
-      </c>
-      <c r="E24" s="6" t="n"/>
-      <c r="F24" s="6" t="n"/>
-    </row>
-    <row r="25"/>
-    <row r="26">
-      <c r="A26" s="4" t="n"/>
-      <c r="B26" s="4" t="inlineStr">
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E25" s="6" t="n"/>
+      <c r="F25" s="6" t="inlineStr">
+        <is>
+          <t>Planned (DR-09): no longer unique; for search and the duplicate-number warning</t>
+        </is>
+      </c>
+    </row>
+    <row r="26"/>
+    <row r="27">
+      <c r="A27" s="4" t="n"/>
+      <c r="B27" s="4" t="inlineStr">
         <is>
           <t>Được tham chiếu bởi bảng</t>
         </is>
       </c>
-      <c r="C26" s="4" t="inlineStr">
+      <c r="C27" s="4" t="inlineStr">
         <is>
           <t>Cột</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="27" customHeight="1">
-      <c r="A27" s="6" t="n"/>
-      <c r="B27" s="7" t="inlineStr">
-        <is>
-          <t>driver_vehicle_assignments</t>
-        </is>
-      </c>
-      <c r="C27" s="6" t="inlineStr">
-        <is>
-          <t>driver_id</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
+    <row r="28" ht="27" customHeight="1">
       <c r="A28" s="6" t="n"/>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>driving_sessions</t>
+          <t>driver_vehicle_assignments</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
@@ -21233,7 +21317,7 @@
       <c r="A29" s="6" t="n"/>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>charging_credentials</t>
+          <t>driving_sessions</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
@@ -21246,7 +21330,7 @@
       <c r="A30" s="6" t="n"/>
       <c r="B30" s="7" t="inlineStr">
         <is>
-          <t>charging_reservations</t>
+          <t>charging_credentials</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
@@ -21259,7 +21343,7 @@
       <c r="A31" s="6" t="n"/>
       <c r="B31" s="7" t="inlineStr">
         <is>
-          <t>support_cases</t>
+          <t>charging_reservations</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
@@ -21272,7 +21356,7 @@
       <c r="A32" s="6" t="n"/>
       <c r="B32" s="7" t="inlineStr">
         <is>
-          <t>wallets</t>
+          <t>support_cases</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
@@ -21285,7 +21369,7 @@
       <c r="A33" s="6" t="n"/>
       <c r="B33" s="7" t="inlineStr">
         <is>
-          <t>driver_scores</t>
+          <t>wallets</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
@@ -21298,35 +21382,731 @@
       <c r="A34" s="6" t="n"/>
       <c r="B34" s="7" t="inlineStr">
         <is>
+          <t>driver_scores</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t>driver_id</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="n"/>
+      <c r="B35" s="7" t="inlineStr">
+        <is>
           <t>trips</t>
         </is>
       </c>
-      <c r="C34" s="6" t="inlineStr">
+      <c r="C35" s="6" t="inlineStr">
         <is>
           <t>driver_id</t>
         </is>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" s="6" t="n"/>
+      <c r="B36" s="7" t="inlineStr">
+        <is>
+          <t>driver_history</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="inlineStr">
+        <is>
+          <t>driver_id</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A6:I16"/>
+  <autoFilter ref="A7:I19"/>
   <hyperlinks>
     <hyperlink ref="A2" location="'Tổng quan'!A1"/>
-    <hyperlink ref="F8" location="'organizations'!A1"/>
+    <hyperlink ref="A5" location="'driver_history'!A1"/>
     <hyperlink ref="F9" location="'memberships'!A1"/>
-    <hyperlink ref="B27" location="'driver_vehicle_assignments'!A1"/>
-    <hyperlink ref="B28" location="'driving_sessions'!A1"/>
-    <hyperlink ref="B29" location="'charging_credentials'!A1"/>
-    <hyperlink ref="B30" location="'charging_reservations'!A1"/>
-    <hyperlink ref="B31" location="'support_cases'!A1"/>
-    <hyperlink ref="B32" location="'wallets'!A1"/>
-    <hyperlink ref="B33" location="'driver_scores'!A1"/>
-    <hyperlink ref="B34" location="'trips'!A1"/>
+    <hyperlink ref="B28" location="'driver_vehicle_assignments'!A1"/>
+    <hyperlink ref="B29" location="'driving_sessions'!A1"/>
+    <hyperlink ref="B30" location="'charging_credentials'!A1"/>
+    <hyperlink ref="B31" location="'charging_reservations'!A1"/>
+    <hyperlink ref="B32" location="'support_cases'!A1"/>
+    <hyperlink ref="B33" location="'wallets'!A1"/>
+    <hyperlink ref="B34" location="'driver_scores'!A1"/>
+    <hyperlink ref="B35" location="'trips'!A1"/>
+    <hyperlink ref="B36" location="'driver_history'!A1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I27"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="7" max="7"/>
+    <col width="42" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>21.h. driver_history: Lịch sử tài xế</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t>← Tổng quan</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>Miền nghiệp vụ: Tài xế (drivers)   ·   Chủ sở hữu dữ liệu: Khách hàng   ·   Tính năng: F-E4</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>Mọi phiên bản trước đây của một dòng trong bảng drivers: bản sao toàn bộ dòng, chụp ngay trước khi thay đổi và được trigger ghi trong cùng giao dịch. Do công cụ domain-model tự sinh từ @tracked *, không bao giờ viết tay.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>Bảng lịch sử của: drivers</t>
+        </is>
+      </c>
+    </row>
+    <row r="6"/>
+    <row r="7" ht="27" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Cột</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Kiểu dữ liệu</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Cho phép rỗng</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>Khóa</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>Tham chiếu tới</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>Ý nghĩa</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>Ví dụ</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>Lưu lịch sử</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>history_id</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>bigint</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="n"/>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>Mã tự tăng của dòng lịch sử.</t>
+        </is>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>1024</t>
+        </is>
+      </c>
+      <c r="I8" s="6" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>driver_id</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>uuid</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>drivers.driver_id (khi xóa: chặn xóa)</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>Giá trị trước khi thay đổi (drivers.driver_id).</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>6e3b9d2a-4c1f-4e8b-9a7d-0c2e5f1b8d66</t>
+        </is>
+      </c>
+      <c r="I9" s="6" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>membership_id</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>uuid</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="n"/>
+      <c r="F10" s="6" t="n"/>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>Giá trị trước khi thay đổi (drivers.membership_id).</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>00000022-5a6b-4c7d-8e9f-0a1b2c3d4e5f</t>
+        </is>
+      </c>
+      <c r="I10" s="6" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>license_number</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>varchar(50)</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="n"/>
+      <c r="F11" s="6" t="n"/>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>Giá trị trước khi thay đổi (drivers.license_number).</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>790123456789</t>
+        </is>
+      </c>
+      <c r="I11" s="6" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>license_class</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>varchar(5)</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="n"/>
+      <c r="F12" s="6" t="n"/>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>Giá trị trước khi thay đổi (drivers.license_class).</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="I12" s="6" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>license_expires_on</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="n"/>
+      <c r="F13" s="6" t="n"/>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>Giá trị trước khi thay đổi (drivers.license_expires_on).</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>2029-03-01</t>
+        </is>
+      </c>
+      <c r="I13" s="6" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>driverstatus</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="n"/>
+      <c r="F14" s="6" t="n"/>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>Giá trị trước khi thay đổi (drivers.status).</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="I14" s="6" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>status_reason</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>varchar(200)</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="n"/>
+      <c r="F15" s="6" t="n"/>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>Giá trị trước khi thay đổi (drivers.status_reason).</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>Tạm đình chỉ sau va chạm ngày 12/09</t>
+        </is>
+      </c>
+      <c r="I15" s="6" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>created_at</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>timestamptz</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="n"/>
+      <c r="F16" s="6" t="n"/>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>Giá trị trước khi thay đổi (drivers.created_at).</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-01T02:00:00Z</t>
+        </is>
+      </c>
+      <c r="I16" s="6" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>updated_at</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>timestamptz</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="n"/>
+      <c r="F17" s="6" t="n"/>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>Giá trị trước khi thay đổi (drivers.updated_at).</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-10T07:15:00Z</t>
+        </is>
+      </c>
+      <c r="I17" s="6" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>deleted_at</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>timestamptz</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="n"/>
+      <c r="F18" s="6" t="n"/>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>Giá trị trước khi thay đổi (drivers.deleted_at).</t>
+        </is>
+      </c>
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="I18" s="6" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>changed_at</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>timestamptz</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="n"/>
+      <c r="F19" s="6" t="n"/>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>Thời điểm phiên bản này của dòng bị thay thế.</t>
+        </is>
+      </c>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-10T07:15:00Z</t>
+        </is>
+      </c>
+      <c r="I19" s="6" t="n"/>
+    </row>
+    <row r="20" ht="27" customHeight="1">
+      <c r="A20" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>changed_by</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>uuid</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="F20" s="7" t="inlineStr">
+        <is>
+          <t>users.user_id (khi xóa: chặn xóa)</t>
+        </is>
+      </c>
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t>Người dùng đã thực hiện thay đổi; NULL nếu do hệ thống thực hiện.</t>
+        </is>
+      </c>
+      <c r="H20" s="6" t="inlineStr">
+        <is>
+          <t>9b2e7d4a-1c3f-4a8e-b6d2-5e0f1a9c3d22</t>
+        </is>
+      </c>
+      <c r="I20" s="6" t="n"/>
+    </row>
+    <row r="21" ht="40.5" customHeight="1">
+      <c r="A21" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>change_reason</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>varchar(200)</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="n"/>
+      <c r="F21" s="6" t="n"/>
+      <c r="G21" s="6" t="inlineStr">
+        <is>
+          <t>Lý do thay đổi dòng, do ứng dụng đặt cho giao dịch: người dùng nhập với quyết định quản trị, văn bản cố định với thao tác thường lệ. Thay đổi không có lý do sẽ bị từ chối.</t>
+        </is>
+      </c>
+      <c r="H21" s="6" t="inlineStr">
+        <is>
+          <t>Customer moved to a new office</t>
+        </is>
+      </c>
+      <c r="I21" s="6" t="n"/>
+    </row>
+    <row r="22"/>
+    <row r="23">
+      <c r="A23" s="4" t="n"/>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>Kiểu enum</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>Giá trị cho phép</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="n"/>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>driverstatus</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE, INACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="25"/>
+    <row r="26">
+      <c r="A26" s="4" t="n"/>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>Chỉ mục (index)</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>Các cột</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>Duy nhất</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="n"/>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>Ghi chú</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="27" customHeight="1">
+      <c r="A27" s="6" t="n"/>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>ix_driver_history_driver_id_time</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>driver_id, changed_at</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E27" s="6" t="n"/>
+      <c r="F27" s="6" t="n"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A7:I21"/>
+  <hyperlinks>
+    <hyperlink ref="A2" location="'Tổng quan'!A1"/>
+    <hyperlink ref="A5" location="'drivers'!A1"/>
+    <hyperlink ref="F9" location="'drivers'!A1"/>
+    <hyperlink ref="F20" location="'users'!A1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -21859,7 +22639,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -21903,7 +22683,7 @@
     <row r="4">
       <c r="A4" s="11" t="inlineStr">
         <is>
-          <t>Ai cầm lái xe nào, trong khoảng thời gian nào (DR-07): tài xế nhận xe bằng cách quét mã QR trên xe hoặc chọn xe ở gần trên ứng dụng, hoặc quản lý nhận xe giúp trên portal. Thay thế driver_vehicle_assignments. Phiên kết thúc khi tài xế trả xe, tài xế khác nhận xe, tài xế nhận xe khác, hoặc xe không di chuyển quá thời gian tự kết thúc của tổ chức (organization_settings). Các sự kiện cần biết tài xế (điểm, chuyến, phiên sạc) lấy tài xế từ đây. Cảnh báo cho tài xế gửi tới tài xế đang nhận xe và portal; xe chạy mà không ai nhận xe sẽ cảnh báo lên portal. Tổ chức sở hữu xe và chính tài xế (trên ứng dụng) xem được phiên lái; tổ chức tuyển dụng tài xế không xem được phiên lái trên xe của tổ chức khác (DR-08). Dòng đã đóng không bao giờ bị sửa nên không cần lịch sử thay đổi.</t>
+          <t>Ai cầm lái xe nào, trong khoảng thời gian nào (DR-07): tài xế nhận xe bằng cách quét mã QR trên xe hoặc chọn xe ở gần trên ứng dụng, hoặc quản lý nhận xe giúp trên portal. Thay thế driver_vehicle_assignments. Phiên kết thúc khi tài xế trả xe, tài xế khác nhận xe, tài xế nhận xe khác, hoặc xe không di chuyển quá thời gian tự kết thúc của tổ chức (organization_settings). Các sự kiện cần biết tài xế (điểm, chuyến, phiên sạc) lấy tài xế từ đây. Cảnh báo cho tài xế gửi tới tài xế đang nhận xe và portal; xe chạy mà không ai nhận xe sẽ cảnh báo lên portal. Tổ chức sở hữu xe xem đầy đủ phiên lái; tài xế chỉ xem bản tóm tắt các phiên của mình trên ứng dụng (thời gian, xe, thời lượng, quãng đường; không có lộ trình hay địa điểm, không xuất dữ liệu), và tổ chức tuyển dụng tài xế không xem được phiên lái trên xe của tổ chức khác (DR-08, DR-11). Dòng đã đóng không bao giờ bị sửa nên không cần lịch sử thay đổi.</t>
         </is>
       </c>
     </row>
@@ -22033,7 +22813,7 @@
       </c>
       <c r="I8" s="6" t="n"/>
     </row>
-    <row r="9" ht="27" customHeight="1">
+    <row r="9" ht="108" customHeight="1">
       <c r="A9" s="6" t="n">
         <v>3</v>
       </c>
@@ -22064,7 +22844,7 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>Tài xế đang cầm lái: bất kỳ tài xế đang hoạt động nào trong hệ thống, thuộc bất kỳ tổ chức nào.</t>
+          <t>Hồ sơ tài xế đang cầm lái: bất kỳ tài xế đang hoạt động nào trong hệ thống, thuộc bất kỳ tổ chức nào; tài xế của tổ chức khác là trường hợp bình thường (ví dụ chủ xe thuê tài xế của công ty khác) và chỉ có cảnh báo. Hồ sơ được dùng là hồ sơ của người đó trong tổ chức sở hữu xe nếu có, nếu không thì hồ sơ trong tổ chức họ đang làm việc trên ứng dụng; quản lý nhận xe giúp trên portal chọn một hồ sơ của chính tổ chức mình (DR-10).</t>
         </is>
       </c>
       <c r="H9" s="6" t="inlineStr">
@@ -22471,7 +23251,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -22894,7 +23674,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -23498,7 +24278,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -24007,7 +24787,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -24443,13 +25223,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:I51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -24466,389 +25246,6 @@
     <row r="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>28. fleet_user_assignments: Phân công người dùng - đội xe</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="10" t="inlineStr">
-        <is>
-          <t>← Tổng quan</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>Miền nghiệp vụ: Đội xe (fleet)   ·   Chủ sở hữu dữ liệu: Khách hàng   ·   Tính năng: F-F1, F-E1</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="11" t="inlineStr">
-        <is>
-          <t>Giới hạn vai trò cấp đội xe của một người dùng trong một số đội xe của tổ chức lớn (ví dụ một quản lý cho đội Hà Nội, một quản lý khác cho đội TP.HCM). Người dùng không có dòng nào đang hiệu lực ở đây thì quản lý mọi đội xe của tổ chức. Nằm ở miền Đội xe, không ở miền Danh tính, để miền Danh tính không phụ thuộc miền nào.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5"/>
-    <row r="6" ht="27" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>Cột</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>Kiểu dữ liệu</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>Cho phép rỗng</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>Khóa</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>Tham chiếu tới</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>Ý nghĩa</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>Ví dụ</t>
-        </is>
-      </c>
-      <c r="I6" s="4" t="inlineStr">
-        <is>
-          <t>Lưu lịch sử</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>assignment_id</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>uuid</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
-      <c r="F7" s="6" t="n"/>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>Mã nội bộ của lần phân công.</t>
-        </is>
-      </c>
-      <c r="H7" s="6" t="inlineStr">
-        <is>
-          <t>0000001c-5a6b-4c7d-8e9f-0a1b2c3d4e5f</t>
-        </is>
-      </c>
-      <c r="I7" s="6" t="n"/>
-    </row>
-    <row r="8" ht="27" customHeight="1">
-      <c r="A8" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>organization_id</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>uuid</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E8" s="6" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="F8" s="7" t="inlineStr">
-        <is>
-          <t>organizations.organization_id (khi xóa: chặn xóa)</t>
-        </is>
-      </c>
-      <c r="G8" s="6" t="inlineStr">
-        <is>
-          <t>Tổ chức của đội xe và người dùng.</t>
-        </is>
-      </c>
-      <c r="H8" s="6" t="inlineStr">
-        <is>
-          <t>3f6c2a1e-8b4d-4e2a-9c1f-0a7d5b2e4c11</t>
-        </is>
-      </c>
-      <c r="I8" s="6" t="n"/>
-    </row>
-    <row r="9" ht="27" customHeight="1">
-      <c r="A9" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>fleet_id</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>uuid</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E9" s="6" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="F9" s="7" t="inlineStr">
-        <is>
-          <t>fleets.fleet_id (khi xóa: chặn xóa)</t>
-        </is>
-      </c>
-      <c r="G9" s="6" t="inlineStr">
-        <is>
-          <t>Đội xe mà người dùng được giới hạn trong đó, cùng mọi đội xe nằm dưới.</t>
-        </is>
-      </c>
-      <c r="H9" s="6" t="inlineStr">
-        <is>
-          <t>8d5f2b7e-1a9c-4f3d-b8e2-6c0a4d9f1e77</t>
-        </is>
-      </c>
-      <c r="I9" s="6" t="n"/>
-    </row>
-    <row r="10" ht="40.5" customHeight="1">
-      <c r="A10" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>membership_id</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>uuid</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E10" s="6" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="F10" s="7" t="inlineStr">
-        <is>
-          <t>memberships.membership_id (khi xóa: chặn xóa)</t>
-        </is>
-      </c>
-      <c r="G10" s="6" t="inlineStr">
-        <is>
-          <t>Thành viên (người trong tổ chức này) có các vai trò cấp đội xe (FLEET_MANAGER, DISPATCHER) chỉ áp dụng cho các đội xe được liệt kê.</t>
-        </is>
-      </c>
-      <c r="H10" s="6" t="inlineStr">
-        <is>
-          <t>00000022-5a6b-4c7d-8e9f-0a1b2c3d4e5f</t>
-        </is>
-      </c>
-      <c r="I10" s="6" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>assigned_at</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>timestamptz</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E11" s="6" t="n"/>
-      <c r="F11" s="6" t="n"/>
-      <c r="G11" s="6" t="inlineStr">
-        <is>
-          <t>Thời điểm người dùng được giao đội xe này.</t>
-        </is>
-      </c>
-      <c r="H11" s="6" t="inlineStr">
-        <is>
-          <t>2026-09-01T02:00:00Z</t>
-        </is>
-      </c>
-      <c r="I11" s="6" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>unassigned_at</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>timestamptz</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>có</t>
-        </is>
-      </c>
-      <c r="E12" s="6" t="n"/>
-      <c r="F12" s="6" t="n"/>
-      <c r="G12" s="6" t="inlineStr">
-        <is>
-          <t>Thời điểm bị thu lại; NULL khi còn hiệu lực.</t>
-        </is>
-      </c>
-      <c r="H12" s="6" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="I12" s="6" t="n"/>
-    </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" s="4" t="n"/>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>Chỉ mục (index)</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>Các cột</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="inlineStr">
-        <is>
-          <t>Duy nhất</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="n"/>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>Ghi chú</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="27" customHeight="1">
-      <c r="A15" s="6" t="n"/>
-      <c r="B15" s="6" t="inlineStr">
-        <is>
-          <t>uq_fleet_user_assignments_active</t>
-        </is>
-      </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>fleet_id, membership_id</t>
-        </is>
-      </c>
-      <c r="D15" s="6" t="inlineStr">
-        <is>
-          <t>có</t>
-        </is>
-      </c>
-      <c r="E15" s="6" t="n"/>
-      <c r="F15" s="6" t="inlineStr">
-        <is>
-          <t>WHERE unassigned_at IS NULL</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A6:I12"/>
-  <hyperlinks>
-    <hyperlink ref="A2" location="'Tổng quan'!A1"/>
-    <hyperlink ref="F8" location="'organizations'!A1"/>
-    <hyperlink ref="F9" location="'fleets'!A1"/>
-    <hyperlink ref="F10" location="'memberships'!A1"/>
-  </hyperlinks>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I50"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="40" customWidth="1" min="6" max="6"/>
-    <col width="60" customWidth="1" min="7" max="7"/>
-    <col width="42" customWidth="1" min="8" max="8"/>
-    <col width="11" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="9" t="inlineStr">
-        <is>
           <t>2. users: Người dùng</t>
         </is>
       </c>
@@ -25734,6 +26131,19 @@
         </is>
       </c>
       <c r="C50" s="6" t="inlineStr">
+        <is>
+          <t>changed_by</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="6" t="n"/>
+      <c r="B51" s="7" t="inlineStr">
+        <is>
+          <t>driver_history</t>
+        </is>
+      </c>
+      <c r="C51" s="6" t="inlineStr">
         <is>
           <t>changed_by</t>
         </is>
@@ -25772,12 +26182,396 @@
     <hyperlink ref="B48" location="'battery_history'!A1"/>
     <hyperlink ref="B49" location="'warranty_history'!A1"/>
     <hyperlink ref="B50" location="'telematic_history'!A1"/>
+    <hyperlink ref="B51" location="'driver_history'!A1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="7" max="7"/>
+    <col width="42" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>28. fleet_user_assignments: Phân công người dùng - đội xe</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t>← Tổng quan</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>Miền nghiệp vụ: Đội xe (fleet)   ·   Chủ sở hữu dữ liệu: Khách hàng   ·   Tính năng: F-F1, F-E1</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>Giới hạn vai trò cấp đội xe của một người dùng trong một số đội xe của tổ chức lớn (ví dụ một quản lý cho đội Hà Nội, một quản lý khác cho đội TP.HCM). Người dùng không có dòng nào đang hiệu lực ở đây thì quản lý mọi đội xe của tổ chức. Nằm ở miền Đội xe, không ở miền Danh tính, để miền Danh tính không phụ thuộc miền nào.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5"/>
+    <row r="6" ht="27" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Cột</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Kiểu dữ liệu</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Cho phép rỗng</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>Khóa</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>Tham chiếu tới</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>Ý nghĩa</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>Ví dụ</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>Lưu lịch sử</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>assignment_id</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>uuid</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="n"/>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>Mã nội bộ của lần phân công.</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>0000001c-5a6b-4c7d-8e9f-0a1b2c3d4e5f</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="n"/>
+    </row>
+    <row r="8" ht="27" customHeight="1">
+      <c r="A8" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>organization_id</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>uuid</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>organizations.organization_id (khi xóa: chặn xóa)</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>Tổ chức của đội xe và người dùng.</t>
+        </is>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>3f6c2a1e-8b4d-4e2a-9c1f-0a7d5b2e4c11</t>
+        </is>
+      </c>
+      <c r="I8" s="6" t="n"/>
+    </row>
+    <row r="9" ht="27" customHeight="1">
+      <c r="A9" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>fleet_id</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>uuid</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>fleets.fleet_id (khi xóa: chặn xóa)</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>Đội xe mà người dùng được giới hạn trong đó, cùng mọi đội xe nằm dưới.</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>8d5f2b7e-1a9c-4f3d-b8e2-6c0a4d9f1e77</t>
+        </is>
+      </c>
+      <c r="I9" s="6" t="n"/>
+    </row>
+    <row r="10" ht="40.5" customHeight="1">
+      <c r="A10" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>membership_id</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>uuid</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>memberships.membership_id (khi xóa: chặn xóa)</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>Thành viên (người trong tổ chức này) có các vai trò cấp đội xe (FLEET_MANAGER, DISPATCHER) chỉ áp dụng cho các đội xe được liệt kê.</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>00000022-5a6b-4c7d-8e9f-0a1b2c3d4e5f</t>
+        </is>
+      </c>
+      <c r="I10" s="6" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>assigned_at</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>timestamptz</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="n"/>
+      <c r="F11" s="6" t="n"/>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>Thời điểm người dùng được giao đội xe này.</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-01T02:00:00Z</t>
+        </is>
+      </c>
+      <c r="I11" s="6" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>unassigned_at</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>timestamptz</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="n"/>
+      <c r="F12" s="6" t="n"/>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>Thời điểm bị thu lại; NULL khi còn hiệu lực.</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="I12" s="6" t="n"/>
+    </row>
+    <row r="13"/>
+    <row r="14">
+      <c r="A14" s="4" t="n"/>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>Chỉ mục (index)</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>Các cột</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>Duy nhất</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="n"/>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>Ghi chú</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="27" customHeight="1">
+      <c r="A15" s="6" t="n"/>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>uq_fleet_user_assignments_active</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>fleet_id, membership_id</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="n"/>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>WHERE unassigned_at IS NULL</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A6:I12"/>
+  <hyperlinks>
+    <hyperlink ref="A2" location="'Tổng quan'!A1"/>
+    <hyperlink ref="F8" location="'organizations'!A1"/>
+    <hyperlink ref="F9" location="'fleets'!A1"/>
+    <hyperlink ref="F10" location="'memberships'!A1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -26809,7 +27603,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -27232,7 +28026,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -27847,7 +28641,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -28239,7 +29033,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -28633,7 +29427,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -29000,7 +29794,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -30113,7 +30907,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -30472,7 +31266,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -30931,548 +31725,6 @@
   <hyperlinks>
     <hyperlink ref="A2" location="'Tổng quan'!A1"/>
     <hyperlink ref="F9" location="'charging_sessions'!A1"/>
-  </hyperlinks>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I23"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="40" customWidth="1" min="6" max="6"/>
-    <col width="60" customWidth="1" min="7" max="7"/>
-    <col width="42" customWidth="1" min="8" max="8"/>
-    <col width="11" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="9" t="inlineStr">
-        <is>
-          <t>38. notifications: Thông báo</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="10" t="inlineStr">
-        <is>
-          <t>← Tổng quan</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>Miền nghiệp vụ: Thông báo &amp; cảnh báo (notifications)   ·   Chủ sở hữu dữ liệu: Khách hàng   ·   Tính năng: F-A2, F-A3, F-A4, F-J1, F-J3</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="11" t="inlineStr">
-        <is>
-          <t>Một cảnh báo (pin, bất thường, SOH, thiết bị mất kết nối...). Một bảng chung; mỗi loại cảnh báo là một giá trị enum và một cấu trúc payload.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5"/>
-    <row r="6" ht="27" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>Cột</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>Kiểu dữ liệu</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>Cho phép rỗng</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>Khóa</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>Tham chiếu tới</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>Ý nghĩa</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>Ví dụ</t>
-        </is>
-      </c>
-      <c r="I6" s="4" t="inlineStr">
-        <is>
-          <t>Lưu lịch sử</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="27" customHeight="1">
-      <c r="A7" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>notification_id</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>bigint</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
-      <c r="F7" s="6" t="n"/>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>Mã tự tăng; cũng là con trỏ khi truy vấn thông báo mới (after_id).</t>
-        </is>
-      </c>
-      <c r="H7" s="6" t="inlineStr">
-        <is>
-          <t>5821</t>
-        </is>
-      </c>
-      <c r="I7" s="6" t="n"/>
-    </row>
-    <row r="8" ht="27" customHeight="1">
-      <c r="A8" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>organization_id</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>uuid</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>có</t>
-        </is>
-      </c>
-      <c r="E8" s="6" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="F8" s="7" t="inlineStr">
-        <is>
-          <t>organizations.organization_id (khi xóa: chặn xóa)</t>
-        </is>
-      </c>
-      <c r="G8" s="6" t="inlineStr">
-        <is>
-          <t>Tổ chức khách hàng được xem thông báo.</t>
-        </is>
-      </c>
-      <c r="H8" s="6" t="inlineStr">
-        <is>
-          <t>3f6c2a1e-8b4d-4e2a-9c1f-0a7d5b2e4c11</t>
-        </is>
-      </c>
-      <c r="I8" s="6" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>notification_type</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>notificationtype</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E9" s="6" t="n"/>
-      <c r="F9" s="6" t="n"/>
-      <c r="G9" s="6" t="inlineStr">
-        <is>
-          <t>Loại sự kiện đã phát sinh thông báo.</t>
-        </is>
-      </c>
-      <c r="H9" s="6" t="inlineStr">
-        <is>
-          <t>BATTERY_ALERT</t>
-        </is>
-      </c>
-      <c r="I9" s="6" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>severity</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>notificationseverity</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E10" s="6" t="n"/>
-      <c r="F10" s="6" t="n"/>
-      <c r="G10" s="6" t="inlineStr">
-        <is>
-          <t>Mức độ khẩn cấp, độc lập với loại thông báo.</t>
-        </is>
-      </c>
-      <c r="H10" s="6" t="inlineStr">
-        <is>
-          <t>WARNING</t>
-        </is>
-      </c>
-      <c r="I10" s="6" t="n"/>
-    </row>
-    <row r="11" ht="27" customHeight="1">
-      <c r="A11" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>vehicle_id</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>uuid</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>có</t>
-        </is>
-      </c>
-      <c r="E11" s="6" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="F11" s="7" t="inlineStr">
-        <is>
-          <t>vehicles.vehicle_id (khi xóa: xóa theo)</t>
-        </is>
-      </c>
-      <c r="G11" s="6" t="inlineStr">
-        <is>
-          <t>Xe mà thông báo nói tới; NULL với thông báo không liên quan xe.</t>
-        </is>
-      </c>
-      <c r="H11" s="6" t="inlineStr">
-        <is>
-          <t>7a4c1e9b-3d2f-4b8a-a6c5-1e0d9f8b7a44</t>
-        </is>
-      </c>
-      <c r="I11" s="6" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>varchar(200)</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E12" s="6" t="n"/>
-      <c r="F12" s="6" t="n"/>
-      <c r="G12" s="6" t="inlineStr">
-        <is>
-          <t>Tóm tắt ngắn.</t>
-        </is>
-      </c>
-      <c r="H12" s="6" t="inlineStr">
-        <is>
-          <t>Pin còn 20%</t>
-        </is>
-      </c>
-      <c r="I12" s="6" t="n"/>
-    </row>
-    <row r="13" ht="27" customHeight="1">
-      <c r="A13" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>body</t>
-        </is>
-      </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>varchar(500)</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E13" s="6" t="n"/>
-      <c r="F13" s="6" t="n"/>
-      <c r="G13" s="6" t="inlineStr">
-        <is>
-          <t>Mô tả chi tiết.</t>
-        </is>
-      </c>
-      <c r="H13" s="6" t="inlineStr">
-        <is>
-          <t>Xe 51D-123.45 còn 20% pin. Trạm gần nhất: Trạm sạc G3 Bình Dương (8.4 km).</t>
-        </is>
-      </c>
-      <c r="I13" s="6" t="n"/>
-    </row>
-    <row r="14" ht="40.5" customHeight="1">
-      <c r="A14" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="B14" s="6" t="inlineStr">
-        <is>
-          <t>payload</t>
-        </is>
-      </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>jsonb</t>
-        </is>
-      </c>
-      <c r="D14" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E14" s="6" t="n"/>
-      <c r="F14" s="6" t="n"/>
-      <c r="G14" s="6" t="inlineStr">
-        <is>
-          <t>Chi tiết riêng theo loại thông báo, dạng JSON.</t>
-        </is>
-      </c>
-      <c r="H14" s="6" t="inlineStr">
-        <is>
-          <t>{"threshold": 20, "soc": 19.8, "nearest_station_id": "4b9d6f3a-2e8c-4a1b-9d5e-7f0c3a8b2d88", "distance_m": 8400}</t>
-        </is>
-      </c>
-      <c r="I14" s="6" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="B15" s="6" t="inlineStr">
-        <is>
-          <t>created_at</t>
-        </is>
-      </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>timestamptz</t>
-        </is>
-      </c>
-      <c r="D15" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E15" s="6" t="n"/>
-      <c r="F15" s="6" t="n"/>
-      <c r="G15" s="6" t="inlineStr">
-        <is>
-          <t>Thời điểm phát sinh thông báo.</t>
-        </is>
-      </c>
-      <c r="H15" s="6" t="inlineStr">
-        <is>
-          <t>2026-09-15T08:30:00Z</t>
-        </is>
-      </c>
-      <c r="I15" s="6" t="n"/>
-    </row>
-    <row r="16" ht="27" customHeight="1">
-      <c r="A16" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="B16" s="6" t="inlineStr">
-        <is>
-          <t>read_at</t>
-        </is>
-      </c>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>timestamptz</t>
-        </is>
-      </c>
-      <c r="D16" s="6" t="inlineStr">
-        <is>
-          <t>có</t>
-        </is>
-      </c>
-      <c r="E16" s="6" t="n"/>
-      <c r="F16" s="6" t="n"/>
-      <c r="G16" s="6" t="inlineStr">
-        <is>
-          <t>Thời điểm người vận hành đánh dấu đã đọc; NULL nếu chưa đọc.</t>
-        </is>
-      </c>
-      <c r="H16" s="6" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="I16" s="6" t="n"/>
-    </row>
-    <row r="17"/>
-    <row r="18">
-      <c r="A18" s="4" t="n"/>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>Kiểu enum</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>Giá trị cho phép</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="108" customHeight="1">
-      <c r="A19" s="6" t="n"/>
-      <c r="B19" s="6" t="inlineStr">
-        <is>
-          <t>notificationtype</t>
-        </is>
-      </c>
-      <c r="C19" s="6" t="inlineStr">
-        <is>
-          <t>BATTERY_ALERT, ANOMALY_ALERT, SOH_ALERT, DEVICE_OFFLINE_ALERT, SOS_ALERT, GEOFENCE_ALERT, NO_DRIVER_CHECK_IN_ALERT (dự kiến), OUTSIDE_DRIVER_CHECK_IN (dự kiến)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="27" customHeight="1">
-      <c r="A20" s="6" t="n"/>
-      <c r="B20" s="6" t="inlineStr">
-        <is>
-          <t>notificationseverity</t>
-        </is>
-      </c>
-      <c r="C20" s="6" t="inlineStr">
-        <is>
-          <t>INFO, WARNING, CRITICAL</t>
-        </is>
-      </c>
-    </row>
-    <row r="21"/>
-    <row r="22">
-      <c r="A22" s="4" t="n"/>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>Chỉ mục (index)</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="inlineStr">
-        <is>
-          <t>Các cột</t>
-        </is>
-      </c>
-      <c r="D22" s="4" t="inlineStr">
-        <is>
-          <t>Duy nhất</t>
-        </is>
-      </c>
-      <c r="E22" s="4" t="n"/>
-      <c r="F22" s="4" t="inlineStr">
-        <is>
-          <t>Ghi chú</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="27" customHeight="1">
-      <c r="A23" s="6" t="n"/>
-      <c r="B23" s="6" t="inlineStr">
-        <is>
-          <t>ix_notifications_vehicle_id</t>
-        </is>
-      </c>
-      <c r="C23" s="6" t="inlineStr">
-        <is>
-          <t>vehicle_id</t>
-        </is>
-      </c>
-      <c r="D23" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E23" s="6" t="n"/>
-      <c r="F23" s="6" t="n"/>
-    </row>
-  </sheetData>
-  <autoFilter ref="A6:I16"/>
-  <hyperlinks>
-    <hyperlink ref="A2" location="'Tổng quan'!A1"/>
-    <hyperlink ref="F8" location="'organizations'!A1"/>
-    <hyperlink ref="F11" location="'vehicles'!A1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -32126,6 +32378,548 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:I23"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="7" max="7"/>
+    <col width="42" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>38. notifications: Thông báo</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t>← Tổng quan</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>Miền nghiệp vụ: Thông báo &amp; cảnh báo (notifications)   ·   Chủ sở hữu dữ liệu: Khách hàng   ·   Tính năng: F-A2, F-A3, F-A4, F-J1, F-J3</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>Một cảnh báo (pin, bất thường, SOH, thiết bị mất kết nối...). Một bảng chung; mỗi loại cảnh báo là một giá trị enum và một cấu trúc payload.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5"/>
+    <row r="6" ht="27" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Cột</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Kiểu dữ liệu</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Cho phép rỗng</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>Khóa</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>Tham chiếu tới</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>Ý nghĩa</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>Ví dụ</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>Lưu lịch sử</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="27" customHeight="1">
+      <c r="A7" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>notification_id</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>bigint</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="n"/>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>Mã tự tăng; cũng là con trỏ khi truy vấn thông báo mới (after_id).</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>5821</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="n"/>
+    </row>
+    <row r="8" ht="27" customHeight="1">
+      <c r="A8" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>organization_id</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>uuid</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>organizations.organization_id (khi xóa: chặn xóa)</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>Tổ chức khách hàng được xem thông báo.</t>
+        </is>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>3f6c2a1e-8b4d-4e2a-9c1f-0a7d5b2e4c11</t>
+        </is>
+      </c>
+      <c r="I8" s="6" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>notification_type</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>notificationtype</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="n"/>
+      <c r="F9" s="6" t="n"/>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>Loại sự kiện đã phát sinh thông báo.</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>BATTERY_ALERT</t>
+        </is>
+      </c>
+      <c r="I9" s="6" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>severity</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>notificationseverity</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="n"/>
+      <c r="F10" s="6" t="n"/>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>Mức độ khẩn cấp, độc lập với loại thông báo.</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="I10" s="6" t="n"/>
+    </row>
+    <row r="11" ht="27" customHeight="1">
+      <c r="A11" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>vehicle_id</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>uuid</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>vehicles.vehicle_id (khi xóa: xóa theo)</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>Xe mà thông báo nói tới; NULL với thông báo không liên quan xe.</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>7a4c1e9b-3d2f-4b8a-a6c5-1e0d9f8b7a44</t>
+        </is>
+      </c>
+      <c r="I11" s="6" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>varchar(200)</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="n"/>
+      <c r="F12" s="6" t="n"/>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>Tóm tắt ngắn.</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>Pin còn 20%</t>
+        </is>
+      </c>
+      <c r="I12" s="6" t="n"/>
+    </row>
+    <row r="13" ht="27" customHeight="1">
+      <c r="A13" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>body</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>varchar(500)</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="n"/>
+      <c r="F13" s="6" t="n"/>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>Mô tả chi tiết.</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>Xe 51D-123.45 còn 20% pin. Trạm gần nhất: Trạm sạc G3 Bình Dương (8.4 km).</t>
+        </is>
+      </c>
+      <c r="I13" s="6" t="n"/>
+    </row>
+    <row r="14" ht="40.5" customHeight="1">
+      <c r="A14" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>payload</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>jsonb</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="n"/>
+      <c r="F14" s="6" t="n"/>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>Chi tiết riêng theo loại thông báo, dạng JSON.</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>{"threshold": 20, "soc": 19.8, "nearest_station_id": "4b9d6f3a-2e8c-4a1b-9d5e-7f0c3a8b2d88", "distance_m": 8400}</t>
+        </is>
+      </c>
+      <c r="I14" s="6" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>created_at</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>timestamptz</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="n"/>
+      <c r="F15" s="6" t="n"/>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>Thời điểm phát sinh thông báo.</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-15T08:30:00Z</t>
+        </is>
+      </c>
+      <c r="I15" s="6" t="n"/>
+    </row>
+    <row r="16" ht="27" customHeight="1">
+      <c r="A16" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>read_at</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>timestamptz</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="n"/>
+      <c r="F16" s="6" t="n"/>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>Thời điểm người vận hành đánh dấu đã đọc; NULL nếu chưa đọc.</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="I16" s="6" t="n"/>
+    </row>
+    <row r="17"/>
+    <row r="18">
+      <c r="A18" s="4" t="n"/>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>Kiểu enum</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>Giá trị cho phép</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="108" customHeight="1">
+      <c r="A19" s="6" t="n"/>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>notificationtype</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>BATTERY_ALERT, ANOMALY_ALERT, SOH_ALERT, DEVICE_OFFLINE_ALERT, SOS_ALERT, GEOFENCE_ALERT, NO_DRIVER_CHECK_IN_ALERT (dự kiến), OUTSIDE_DRIVER_CHECK_IN (dự kiến)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="27" customHeight="1">
+      <c r="A20" s="6" t="n"/>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>notificationseverity</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>INFO, WARNING, CRITICAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="21"/>
+    <row r="22">
+      <c r="A22" s="4" t="n"/>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>Chỉ mục (index)</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>Các cột</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>Duy nhất</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="n"/>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>Ghi chú</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="27" customHeight="1">
+      <c r="A23" s="6" t="n"/>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>ix_notifications_vehicle_id</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>vehicle_id</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="n"/>
+      <c r="F23" s="6" t="n"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A6:I16"/>
+  <hyperlinks>
+    <hyperlink ref="A2" location="'Tổng quan'!A1"/>
+    <hyperlink ref="F8" location="'organizations'!A1"/>
+    <hyperlink ref="F11" location="'vehicles'!A1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet51.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:I43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -33226,7 +34020,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet51.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet52.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -33617,7 +34411,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet52.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet53.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -33984,7 +34778,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet53.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet54.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -34304,7 +35098,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet54.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet55.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -34829,415 +35623,6 @@
     <hyperlink ref="F8" location="'charging_policies'!A1"/>
     <hyperlink ref="F16" location="'users'!A1"/>
     <hyperlink ref="B22" location="'policy_violations'!A1"/>
-  </hyperlinks>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet55.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="40" customWidth="1" min="6" max="6"/>
-    <col width="60" customWidth="1" min="7" max="7"/>
-    <col width="42" customWidth="1" min="8" max="8"/>
-    <col width="11" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="9" t="inlineStr">
-        <is>
-          <t>44. charging_policy_assignments: Áp dụng chính sách sạc</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="10" t="inlineStr">
-        <is>
-          <t>← Tổng quan</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>Miền nghiệp vụ: Chính sách sạc (bảo hành) (policy)   ·   Chủ sở hữu dữ liệu: Khách hàng   ·   Tính năng: F-B1</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="11" t="inlineStr">
-        <is>
-          <t>Chính sách nào áp dụng cho một xe, một đội xe hay một dòng xe.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5"/>
-    <row r="6" ht="27" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>Cột</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>Kiểu dữ liệu</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>Cho phép rỗng</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>Khóa</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>Tham chiếu tới</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>Ý nghĩa</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>Ví dụ</t>
-        </is>
-      </c>
-      <c r="I6" s="4" t="inlineStr">
-        <is>
-          <t>Lưu lịch sử</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>assignment_id</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>uuid</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
-      <c r="F7" s="6" t="n"/>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>Mã nội bộ của lần áp dụng.</t>
-        </is>
-      </c>
-      <c r="H7" s="6" t="inlineStr">
-        <is>
-          <t>0000000e-5a6b-4c7d-8e9f-0a1b2c3d4e5f</t>
-        </is>
-      </c>
-      <c r="I7" s="6" t="n"/>
-    </row>
-    <row r="8" ht="27" customHeight="1">
-      <c r="A8" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>organization_id</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>uuid</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E8" s="6" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="F8" s="7" t="inlineStr">
-        <is>
-          <t>organizations.organization_id (khi xóa: chặn xóa)</t>
-        </is>
-      </c>
-      <c r="G8" s="6" t="inlineStr">
-        <is>
-          <t>Tổ chức khách hàng của lần áp dụng.</t>
-        </is>
-      </c>
-      <c r="H8" s="6" t="inlineStr">
-        <is>
-          <t>3f6c2a1e-8b4d-4e2a-9c1f-0a7d5b2e4c11</t>
-        </is>
-      </c>
-      <c r="I8" s="6" t="n"/>
-    </row>
-    <row r="9" ht="27" customHeight="1">
-      <c r="A9" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>policy_id</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>uuid</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E9" s="6" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="F9" s="7" t="inlineStr">
-        <is>
-          <t>charging_policies.policy_id (khi xóa: chặn xóa)</t>
-        </is>
-      </c>
-      <c r="G9" s="6" t="inlineStr">
-        <is>
-          <t>Chính sách được áp dụng.</t>
-        </is>
-      </c>
-      <c r="H9" s="6" t="inlineStr">
-        <is>
-          <t>b8e5a2d9-3c6f-4b1e-a9d7-5f2c0e8b1aee</t>
-        </is>
-      </c>
-      <c r="I9" s="6" t="n"/>
-    </row>
-    <row r="10" ht="27" customHeight="1">
-      <c r="A10" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>vehicle_id</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>uuid</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>có</t>
-        </is>
-      </c>
-      <c r="E10" s="6" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="F10" s="7" t="inlineStr">
-        <is>
-          <t>vehicles.vehicle_id (khi xóa: chặn xóa)</t>
-        </is>
-      </c>
-      <c r="G10" s="6" t="inlineStr">
-        <is>
-          <t>Xe được áp dụng, nếu phạm vi là một xe. Chỉ đúng một trong vehicle_id / fleet_id / vehicle_model có giá trị.</t>
-        </is>
-      </c>
-      <c r="H10" s="6" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="I10" s="6" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>fleet_id</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>uuid</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>có</t>
-        </is>
-      </c>
-      <c r="E11" s="6" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="F11" s="7" t="inlineStr">
-        <is>
-          <t>fleets.fleet_id (khi xóa: chặn xóa)</t>
-        </is>
-      </c>
-      <c r="G11" s="6" t="inlineStr">
-        <is>
-          <t>Đội xe được áp dụng, nếu phạm vi là một đội.</t>
-        </is>
-      </c>
-      <c r="H11" s="6" t="inlineStr">
-        <is>
-          <t>8d5f2b7e-1a9c-4f3d-b8e2-6c0a4d9f1e77</t>
-        </is>
-      </c>
-      <c r="I11" s="6" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>vehicle_model</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>varchar(50)</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>có</t>
-        </is>
-      </c>
-      <c r="E12" s="6" t="n"/>
-      <c r="F12" s="6" t="n"/>
-      <c r="G12" s="6" t="inlineStr">
-        <is>
-          <t>Dòng xe được áp dụng, nếu phạm vi là một dòng xe.</t>
-        </is>
-      </c>
-      <c r="H12" s="6" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="I12" s="6" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>assigned_at</t>
-        </is>
-      </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>timestamptz</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E13" s="6" t="n"/>
-      <c r="F13" s="6" t="n"/>
-      <c r="G13" s="6" t="inlineStr">
-        <is>
-          <t>Thời điểm bắt đầu áp dụng.</t>
-        </is>
-      </c>
-      <c r="H13" s="6" t="inlineStr">
-        <is>
-          <t>2026-10-01T00:00:00Z</t>
-        </is>
-      </c>
-      <c r="I13" s="6" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="B14" s="6" t="inlineStr">
-        <is>
-          <t>unassigned_at</t>
-        </is>
-      </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>timestamptz</t>
-        </is>
-      </c>
-      <c r="D14" s="6" t="inlineStr">
-        <is>
-          <t>có</t>
-        </is>
-      </c>
-      <c r="E14" s="6" t="n"/>
-      <c r="F14" s="6" t="n"/>
-      <c r="G14" s="6" t="inlineStr">
-        <is>
-          <t>Thời điểm kết thúc; NULL khi còn hiệu lực.</t>
-        </is>
-      </c>
-      <c r="H14" s="6" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="I14" s="6" t="n"/>
-    </row>
-  </sheetData>
-  <autoFilter ref="A6:I14"/>
-  <hyperlinks>
-    <hyperlink ref="A2" location="'Tổng quan'!A1"/>
-    <hyperlink ref="F8" location="'organizations'!A1"/>
-    <hyperlink ref="F9" location="'charging_policies'!A1"/>
-    <hyperlink ref="F10" location="'vehicles'!A1"/>
-    <hyperlink ref="F11" location="'fleets'!A1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -35266,7 +35651,7 @@
     <row r="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>45. policy_violations: Vi phạm chính sách sạc</t>
+          <t>44. charging_policy_assignments: Áp dụng chính sách sạc</t>
         </is>
       </c>
     </row>
@@ -35280,14 +35665,14 @@
     <row r="3">
       <c r="A3" s="11" t="inlineStr">
         <is>
-          <t>Miền nghiệp vụ: Chính sách sạc (bảo hành) (policy)   ·   Chủ sở hữu dữ liệu: Khách hàng   ·   Tính năng: F-B3, F-B6</t>
+          <t>Miền nghiệp vụ: Chính sách sạc (bảo hành) (policy)   ·   Chủ sở hữu dữ liệu: Khách hàng   ·   Tính năng: F-B1</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="11" t="inlineStr">
         <is>
-          <t>Một phiên sạc vi phạm chính sách, kèm bằng chứng. Hệ quả của vi phạm vẫn là câu hỏi kinh doanh còn mở (mục 3 của feature-list).</t>
+          <t>Chính sách nào áp dụng cho một xe, một đội xe hay một dòng xe.</t>
         </is>
       </c>
     </row>
@@ -35345,7 +35730,7 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>violation_id</t>
+          <t>assignment_id</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
@@ -35366,12 +35751,12 @@
       <c r="F7" s="6" t="n"/>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>Mã nội bộ của vi phạm.</t>
+          <t>Mã nội bộ của lần áp dụng.</t>
         </is>
       </c>
       <c r="H7" s="6" t="inlineStr">
         <is>
-          <t>0000000f-5a6b-4c7d-8e9f-0a1b2c3d4e5f</t>
+          <t>0000000e-5a6b-4c7d-8e9f-0a1b2c3d4e5f</t>
         </is>
       </c>
       <c r="I7" s="6" t="n"/>
@@ -35407,7 +35792,7 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>Tổ chức khách hàng sở hữu xe.</t>
+          <t>Tổ chức khách hàng của lần áp dụng.</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr">
@@ -35423,7 +35808,7 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>session_id</t>
+          <t>policy_id</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
@@ -35443,17 +35828,17 @@
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>charging_sessions.session_id (khi xóa: chặn xóa)</t>
+          <t>charging_policies.policy_id (khi xóa: chặn xóa)</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>Phiên sạc đã vi phạm chính sách.</t>
+          <t>Chính sách được áp dụng.</t>
         </is>
       </c>
       <c r="H9" s="6" t="inlineStr">
         <is>
-          <t>e5a2d8f1-4b7c-4e9a-b3d6-2c1f0e9a8dbb</t>
+          <t>b8e5a2d9-3c6f-4b1e-a9d7-5f2c0e8b1aee</t>
         </is>
       </c>
       <c r="I9" s="6" t="n"/>
@@ -35474,7 +35859,7 @@
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>không</t>
+          <t>có</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
@@ -35489,23 +35874,23 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>Xe liên quan.</t>
+          <t>Xe được áp dụng, nếu phạm vi là một xe. Chỉ đúng một trong vehicle_id / fleet_id / vehicle_model có giá trị.</t>
         </is>
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>7a4c1e9b-3d2f-4b8a-a6c5-1e0d9f8b7a44</t>
+          <t>NULL</t>
         </is>
       </c>
       <c r="I10" s="6" t="n"/>
     </row>
-    <row r="11" ht="27" customHeight="1">
+    <row r="11">
       <c r="A11" s="6" t="n">
         <v>5</v>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>policy_version_id</t>
+          <t>fleet_id</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
@@ -35515,7 +35900,7 @@
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>không</t>
+          <t>có</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
@@ -35525,17 +35910,17 @@
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>charging_policy_versions.version_id (khi xóa: chặn xóa)</t>
+          <t>fleets.fleet_id (khi xóa: chặn xóa)</t>
         </is>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>Đúng phiên bản chính sách bị vi phạm.</t>
+          <t>Đội xe được áp dụng, nếu phạm vi là một đội.</t>
         </is>
       </c>
       <c r="H11" s="6" t="inlineStr">
         <is>
-          <t>c7d4f1a8-2b5e-4c9d-8f6a-1e3b0d7c4aff</t>
+          <t>8d5f2b7e-1a9c-4f3d-b8e2-6c0a4d9f1e77</t>
         </is>
       </c>
       <c r="I11" s="6" t="n"/>
@@ -35546,29 +35931,29 @@
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>violation_type</t>
+          <t>vehicle_model</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>varchar(30)</t>
+          <t>varchar(50)</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>không</t>
+          <t>có</t>
         </is>
       </c>
       <c r="E12" s="6" t="n"/>
       <c r="F12" s="6" t="n"/>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>Quy tắc nào bị vi phạm.</t>
+          <t>Dòng xe được áp dụng, nếu phạm vi là một dòng xe.</t>
         </is>
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>SOC_ABOVE_MAX</t>
+          <t>NULL</t>
         </is>
       </c>
       <c r="I12" s="6" t="n"/>
@@ -35579,7 +35964,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>detected_at</t>
+          <t>assigned_at</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
@@ -35596,45 +35981,45 @@
       <c r="F13" s="6" t="n"/>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>Thời điểm phát hiện vi phạm.</t>
+          <t>Thời điểm bắt đầu áp dụng.</t>
         </is>
       </c>
       <c r="H13" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15T09:45:00Z</t>
+          <t>2026-10-01T00:00:00Z</t>
         </is>
       </c>
       <c r="I13" s="6" t="n"/>
     </row>
-    <row r="14" ht="27" customHeight="1">
+    <row r="14">
       <c r="A14" s="6" t="n">
         <v>8</v>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>evidence</t>
+          <t>unassigned_at</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>jsonb</t>
+          <t>timestamptz</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>không</t>
+          <t>có</t>
         </is>
       </c>
       <c r="E14" s="6" t="n"/>
       <c r="F14" s="6" t="n"/>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>Ảnh chụp dữ liệu chứng minh vi phạm, dạng JSON.</t>
+          <t>Thời điểm kết thúc; NULL khi còn hiệu lực.</t>
         </is>
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
-          <t>{"soc_end": 98.5, "soc_max": 90, "meter_stop_wh": 1712860}</t>
+          <t>NULL</t>
         </is>
       </c>
       <c r="I14" s="6" t="n"/>
@@ -35644,9 +36029,9 @@
   <hyperlinks>
     <hyperlink ref="A2" location="'Tổng quan'!A1"/>
     <hyperlink ref="F8" location="'organizations'!A1"/>
-    <hyperlink ref="F9" location="'charging_sessions'!A1"/>
+    <hyperlink ref="F9" location="'charging_policies'!A1"/>
     <hyperlink ref="F10" location="'vehicles'!A1"/>
-    <hyperlink ref="F11" location="'charging_policy_versions'!A1"/>
+    <hyperlink ref="F11" location="'fleets'!A1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -35675,6 +36060,415 @@
     <row r="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
+          <t>45. policy_violations: Vi phạm chính sách sạc</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t>← Tổng quan</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>Miền nghiệp vụ: Chính sách sạc (bảo hành) (policy)   ·   Chủ sở hữu dữ liệu: Khách hàng   ·   Tính năng: F-B3, F-B6</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>Một phiên sạc vi phạm chính sách, kèm bằng chứng. Hệ quả của vi phạm vẫn là câu hỏi kinh doanh còn mở (mục 3 của feature-list).</t>
+        </is>
+      </c>
+    </row>
+    <row r="5"/>
+    <row r="6" ht="27" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Cột</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Kiểu dữ liệu</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Cho phép rỗng</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>Khóa</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>Tham chiếu tới</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>Ý nghĩa</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>Ví dụ</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>Lưu lịch sử</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>violation_id</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>uuid</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="n"/>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>Mã nội bộ của vi phạm.</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>0000000f-5a6b-4c7d-8e9f-0a1b2c3d4e5f</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="n"/>
+    </row>
+    <row r="8" ht="27" customHeight="1">
+      <c r="A8" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>organization_id</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>uuid</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>organizations.organization_id (khi xóa: chặn xóa)</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>Tổ chức khách hàng sở hữu xe.</t>
+        </is>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>3f6c2a1e-8b4d-4e2a-9c1f-0a7d5b2e4c11</t>
+        </is>
+      </c>
+      <c r="I8" s="6" t="n"/>
+    </row>
+    <row r="9" ht="27" customHeight="1">
+      <c r="A9" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>session_id</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>uuid</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>charging_sessions.session_id (khi xóa: chặn xóa)</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>Phiên sạc đã vi phạm chính sách.</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>e5a2d8f1-4b7c-4e9a-b3d6-2c1f0e9a8dbb</t>
+        </is>
+      </c>
+      <c r="I9" s="6" t="n"/>
+    </row>
+    <row r="10" ht="27" customHeight="1">
+      <c r="A10" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>vehicle_id</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>uuid</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>vehicles.vehicle_id (khi xóa: chặn xóa)</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>Xe liên quan.</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>7a4c1e9b-3d2f-4b8a-a6c5-1e0d9f8b7a44</t>
+        </is>
+      </c>
+      <c r="I10" s="6" t="n"/>
+    </row>
+    <row r="11" ht="27" customHeight="1">
+      <c r="A11" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>policy_version_id</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>uuid</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>charging_policy_versions.version_id (khi xóa: chặn xóa)</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>Đúng phiên bản chính sách bị vi phạm.</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>c7d4f1a8-2b5e-4c9d-8f6a-1e3b0d7c4aff</t>
+        </is>
+      </c>
+      <c r="I11" s="6" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>violation_type</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>varchar(30)</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="n"/>
+      <c r="F12" s="6" t="n"/>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>Quy tắc nào bị vi phạm.</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>SOC_ABOVE_MAX</t>
+        </is>
+      </c>
+      <c r="I12" s="6" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>detected_at</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>timestamptz</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="n"/>
+      <c r="F13" s="6" t="n"/>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>Thời điểm phát hiện vi phạm.</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-15T09:45:00Z</t>
+        </is>
+      </c>
+      <c r="I13" s="6" t="n"/>
+    </row>
+    <row r="14" ht="27" customHeight="1">
+      <c r="A14" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>jsonb</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="n"/>
+      <c r="F14" s="6" t="n"/>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>Ảnh chụp dữ liệu chứng minh vi phạm, dạng JSON.</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>{"soc_end": 98.5, "soc_max": 90, "meter_stop_wh": 1712860}</t>
+        </is>
+      </c>
+      <c r="I14" s="6" t="n"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A6:I14"/>
+  <hyperlinks>
+    <hyperlink ref="A2" location="'Tổng quan'!A1"/>
+    <hyperlink ref="F8" location="'organizations'!A1"/>
+    <hyperlink ref="F9" location="'charging_sessions'!A1"/>
+    <hyperlink ref="F10" location="'vehicles'!A1"/>
+    <hyperlink ref="F11" location="'charging_policy_versions'!A1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet58.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="7" max="7"/>
+    <col width="42" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
           <t>46. tariffs: Biểu giá điện</t>
         </is>
       </c>
@@ -36034,7 +36828,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet58.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet59.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -36514,359 +37308,6 @@
     <hyperlink ref="F8" location="'organizations'!A1"/>
     <hyperlink ref="F9" location="'charging_sessions'!A1"/>
     <hyperlink ref="B19" location="'wallet_transactions'!A1"/>
-  </hyperlinks>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet59.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I15"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="40" customWidth="1" min="6" max="6"/>
-    <col width="60" customWidth="1" min="7" max="7"/>
-    <col width="42" customWidth="1" min="8" max="8"/>
-    <col width="11" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="9" t="inlineStr">
-        <is>
-          <t>48. wallets: Ví</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="10" t="inlineStr">
-        <is>
-          <t>← Tổng quan</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>Miền nghiệp vụ: Thanh toán &amp; hóa đơn (billing)   ·   Chủ sở hữu dữ liệu: Khách hàng   ·   Tính năng: F-H2</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="11" t="inlineStr">
-        <is>
-          <t>Số dư trả trước của một tài xế hoặc của cả tổ chức.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5"/>
-    <row r="6" ht="27" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>Cột</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>Kiểu dữ liệu</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>Cho phép rỗng</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>Khóa</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>Tham chiếu tới</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>Ý nghĩa</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>Ví dụ</t>
-        </is>
-      </c>
-      <c r="I6" s="4" t="inlineStr">
-        <is>
-          <t>Lưu lịch sử</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>wallet_id</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>uuid</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
-      <c r="F7" s="6" t="n"/>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>Mã nội bộ của ví.</t>
-        </is>
-      </c>
-      <c r="H7" s="6" t="inlineStr">
-        <is>
-          <t>5c3a0e7d-2f9b-4c1e-a8d3-7b6f0c2e9a32</t>
-        </is>
-      </c>
-      <c r="I7" s="6" t="n"/>
-    </row>
-    <row r="8" ht="27" customHeight="1">
-      <c r="A8" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>organization_id</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>uuid</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E8" s="6" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="F8" s="7" t="inlineStr">
-        <is>
-          <t>organizations.organization_id (khi xóa: chặn xóa)</t>
-        </is>
-      </c>
-      <c r="G8" s="6" t="inlineStr">
-        <is>
-          <t>Tổ chức khách hàng sở hữu ví.</t>
-        </is>
-      </c>
-      <c r="H8" s="6" t="inlineStr">
-        <is>
-          <t>3f6c2a1e-8b4d-4e2a-9c1f-0a7d5b2e4c11</t>
-        </is>
-      </c>
-      <c r="I8" s="6" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>driver_id</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>uuid</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>có</t>
-        </is>
-      </c>
-      <c r="E9" s="6" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="F9" s="7" t="inlineStr">
-        <is>
-          <t>drivers.driver_id (khi xóa: chặn xóa)</t>
-        </is>
-      </c>
-      <c r="G9" s="6" t="inlineStr">
-        <is>
-          <t>Tài xế sở hữu ví; NULL với ví cấp tổ chức (quyết định D5).</t>
-        </is>
-      </c>
-      <c r="H9" s="6" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="I9" s="6" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>balance</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>numeric(14,2)</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E10" s="6" t="n"/>
-      <c r="F10" s="6" t="n"/>
-      <c r="G10" s="6" t="inlineStr">
-        <is>
-          <t>Số dư hiện tại; phải bằng tổng các giao dịch của ví.</t>
-        </is>
-      </c>
-      <c r="H10" s="6" t="inlineStr">
-        <is>
-          <t>12500000.00</t>
-        </is>
-      </c>
-      <c r="I10" s="6" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>currency</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>char(3)</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E11" s="6" t="n"/>
-      <c r="F11" s="6" t="n"/>
-      <c r="G11" s="6" t="inlineStr">
-        <is>
-          <t>Mã tiền tệ ISO 4217.</t>
-        </is>
-      </c>
-      <c r="H11" s="6" t="inlineStr">
-        <is>
-          <t>VND</t>
-        </is>
-      </c>
-      <c r="I11" s="6" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>varchar(20)</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E12" s="6" t="n"/>
-      <c r="F12" s="6" t="n"/>
-      <c r="G12" s="6" t="inlineStr">
-        <is>
-          <t>Ví có dùng được không.</t>
-        </is>
-      </c>
-      <c r="H12" s="6" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="I12" s="6" t="n"/>
-    </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" s="4" t="n"/>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>Được tham chiếu bởi bảng</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>Cột</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="6" t="n"/>
-      <c r="B15" s="7" t="inlineStr">
-        <is>
-          <t>wallet_transactions</t>
-        </is>
-      </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>wallet_id</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A6:I12"/>
-  <hyperlinks>
-    <hyperlink ref="A2" location="'Tổng quan'!A1"/>
-    <hyperlink ref="F8" location="'organizations'!A1"/>
-    <hyperlink ref="F9" location="'drivers'!A1"/>
-    <hyperlink ref="B15" location="'wallet_transactions'!A1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -37224,6 +37665,359 @@
     <row r="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
+          <t>48. wallets: Ví</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t>← Tổng quan</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>Miền nghiệp vụ: Thanh toán &amp; hóa đơn (billing)   ·   Chủ sở hữu dữ liệu: Khách hàng   ·   Tính năng: F-H2</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>Số dư trả trước của một tài xế hoặc của cả tổ chức.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5"/>
+    <row r="6" ht="27" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Cột</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Kiểu dữ liệu</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Cho phép rỗng</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>Khóa</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>Tham chiếu tới</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>Ý nghĩa</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>Ví dụ</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>Lưu lịch sử</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>wallet_id</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>uuid</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="n"/>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>Mã nội bộ của ví.</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>5c3a0e7d-2f9b-4c1e-a8d3-7b6f0c2e9a32</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="n"/>
+    </row>
+    <row r="8" ht="27" customHeight="1">
+      <c r="A8" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>organization_id</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>uuid</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>organizations.organization_id (khi xóa: chặn xóa)</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>Tổ chức khách hàng sở hữu ví.</t>
+        </is>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>3f6c2a1e-8b4d-4e2a-9c1f-0a7d5b2e4c11</t>
+        </is>
+      </c>
+      <c r="I8" s="6" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>driver_id</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>uuid</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>drivers.driver_id (khi xóa: chặn xóa)</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>Tài xế sở hữu ví; NULL với ví cấp tổ chức (quyết định D5).</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="I9" s="6" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>balance</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>numeric(14,2)</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="n"/>
+      <c r="F10" s="6" t="n"/>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>Số dư hiện tại; phải bằng tổng các giao dịch của ví.</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>12500000.00</t>
+        </is>
+      </c>
+      <c r="I10" s="6" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>currency</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>char(3)</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="n"/>
+      <c r="F11" s="6" t="n"/>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>Mã tiền tệ ISO 4217.</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="I11" s="6" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>varchar(20)</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="n"/>
+      <c r="F12" s="6" t="n"/>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>Ví có dùng được không.</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="I12" s="6" t="n"/>
+    </row>
+    <row r="13"/>
+    <row r="14">
+      <c r="A14" s="4" t="n"/>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>Được tham chiếu bởi bảng</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>Cột</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="n"/>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>wallet_transactions</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>wallet_id</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A6:I12"/>
+  <hyperlinks>
+    <hyperlink ref="A2" location="'Tổng quan'!A1"/>
+    <hyperlink ref="F8" location="'organizations'!A1"/>
+    <hyperlink ref="F9" location="'drivers'!A1"/>
+    <hyperlink ref="B15" location="'wallet_transactions'!A1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet61.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="7" max="7"/>
+    <col width="42" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
           <t>49. wallet_transactions: Giao dịch ví</t>
         </is>
       </c>
@@ -37643,7 +38437,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet61.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet62.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -38119,7 +38913,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet62.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet63.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -38561,7 +39355,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet63.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet64.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -38947,7 +39741,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet64.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet65.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -39237,401 +40031,6 @@
   <hyperlinks>
     <hyperlink ref="A2" location="'Tổng quan'!A1"/>
     <hyperlink ref="F8" location="'subscription_plans'!A1"/>
-  </hyperlinks>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet65.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I16"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="40" customWidth="1" min="6" max="6"/>
-    <col width="60" customWidth="1" min="7" max="7"/>
-    <col width="42" customWidth="1" min="8" max="8"/>
-    <col width="11" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="9" t="inlineStr">
-        <is>
-          <t>54. subscriptions: Thuê bao</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="10" t="inlineStr">
-        <is>
-          <t>← Tổng quan</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>Miền nghiệp vụ: Thanh toán &amp; hóa đơn (billing)   ·   Chủ sở hữu dữ liệu: Khách hàng   ·   Tính năng: F-H4</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="11" t="inlineStr">
-        <is>
-          <t>Một xe đăng ký một gói; quá hạn thanh toán sẽ khóa tính năng.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5"/>
-    <row r="6" ht="27" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>Cột</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>Kiểu dữ liệu</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>Cho phép rỗng</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>Khóa</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>Tham chiếu tới</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>Ý nghĩa</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>Ví dụ</t>
-        </is>
-      </c>
-      <c r="I6" s="4" t="inlineStr">
-        <is>
-          <t>Lưu lịch sử</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>subscription_id</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>uuid</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
-      <c r="F7" s="6" t="n"/>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>Mã nội bộ của thuê bao.</t>
-        </is>
-      </c>
-      <c r="H7" s="6" t="inlineStr">
-        <is>
-          <t>9a7e4c1b-6d3f-4a5c-b0e8-2f1d7c9b3e54</t>
-        </is>
-      </c>
-      <c r="I7" s="6" t="n"/>
-    </row>
-    <row r="8" ht="27" customHeight="1">
-      <c r="A8" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>organization_id</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>uuid</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E8" s="6" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="F8" s="7" t="inlineStr">
-        <is>
-          <t>organizations.organization_id (khi xóa: chặn xóa)</t>
-        </is>
-      </c>
-      <c r="G8" s="6" t="inlineStr">
-        <is>
-          <t>Tổ chức khách hàng đăng ký.</t>
-        </is>
-      </c>
-      <c r="H8" s="6" t="inlineStr">
-        <is>
-          <t>3f6c2a1e-8b4d-4e2a-9c1f-0a7d5b2e4c11</t>
-        </is>
-      </c>
-      <c r="I8" s="6" t="n"/>
-    </row>
-    <row r="9" ht="27" customHeight="1">
-      <c r="A9" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>plan_id</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>uuid</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E9" s="6" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="F9" s="7" t="inlineStr">
-        <is>
-          <t>subscription_plans.plan_id (khi xóa: chặn xóa)</t>
-        </is>
-      </c>
-      <c r="G9" s="6" t="inlineStr">
-        <is>
-          <t>Gói được đăng ký.</t>
-        </is>
-      </c>
-      <c r="H9" s="6" t="inlineStr">
-        <is>
-          <t>0c9a6e3d-8f5b-4c7e-a2d1-4b3f9e6c0a65</t>
-        </is>
-      </c>
-      <c r="I9" s="6" t="n"/>
-    </row>
-    <row r="10" ht="27" customHeight="1">
-      <c r="A10" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>vehicle_id</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>uuid</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E10" s="6" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="F10" s="7" t="inlineStr">
-        <is>
-          <t>vehicles.vehicle_id (khi xóa: chặn xóa)</t>
-        </is>
-      </c>
-      <c r="G10" s="6" t="inlineStr">
-        <is>
-          <t>Xe được áp dụng.</t>
-        </is>
-      </c>
-      <c r="H10" s="6" t="inlineStr">
-        <is>
-          <t>7a4c1e9b-3d2f-4b8a-a6c5-1e0d9f8b7a44</t>
-        </is>
-      </c>
-      <c r="I10" s="6" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>started_at</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>timestamptz</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E11" s="6" t="n"/>
-      <c r="F11" s="6" t="n"/>
-      <c r="G11" s="6" t="inlineStr">
-        <is>
-          <t>Thời điểm bắt đầu thuê bao.</t>
-        </is>
-      </c>
-      <c r="H11" s="6" t="inlineStr">
-        <is>
-          <t>2026-09-01T00:00:00Z</t>
-        </is>
-      </c>
-      <c r="I11" s="6" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>ends_at</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>timestamptz</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>có</t>
-        </is>
-      </c>
-      <c r="E12" s="6" t="n"/>
-      <c r="F12" s="6" t="n"/>
-      <c r="G12" s="6" t="inlineStr">
-        <is>
-          <t>Thời điểm kết thúc; NULL nếu tự gia hạn cho tới khi hủy.</t>
-        </is>
-      </c>
-      <c r="H12" s="6" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="I12" s="6" t="n"/>
-    </row>
-    <row r="13" ht="27" customHeight="1">
-      <c r="A13" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>varchar(20)</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E13" s="6" t="n"/>
-      <c r="F13" s="6" t="n"/>
-      <c r="G13" s="6" t="inlineStr">
-        <is>
-          <t>Trạng thái thuê bao; OVERDUE sẽ khóa các tính năng trả phí. Giá trị: ACTIVE | OVERDUE | EXPIRED | CANCELLED.</t>
-        </is>
-      </c>
-      <c r="H13" s="6" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="I13" s="6" t="n"/>
-    </row>
-    <row r="14"/>
-    <row r="15">
-      <c r="A15" s="4" t="n"/>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>Được tham chiếu bởi bảng</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>Cột</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="6" t="n"/>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>invoice_lines</t>
-        </is>
-      </c>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>subscription_id</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A6:I13"/>
-  <hyperlinks>
-    <hyperlink ref="A2" location="'Tổng quan'!A1"/>
-    <hyperlink ref="F8" location="'organizations'!A1"/>
-    <hyperlink ref="F9" location="'subscription_plans'!A1"/>
-    <hyperlink ref="F10" location="'vehicles'!A1"/>
-    <hyperlink ref="B16" location="'invoice_lines'!A1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -39660,6 +40059,401 @@
     <row r="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
+          <t>54. subscriptions: Thuê bao</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t>← Tổng quan</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>Miền nghiệp vụ: Thanh toán &amp; hóa đơn (billing)   ·   Chủ sở hữu dữ liệu: Khách hàng   ·   Tính năng: F-H4</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>Một xe đăng ký một gói; quá hạn thanh toán sẽ khóa tính năng.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5"/>
+    <row r="6" ht="27" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Cột</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Kiểu dữ liệu</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Cho phép rỗng</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>Khóa</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>Tham chiếu tới</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>Ý nghĩa</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>Ví dụ</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>Lưu lịch sử</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>subscription_id</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>uuid</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="n"/>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>Mã nội bộ của thuê bao.</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>9a7e4c1b-6d3f-4a5c-b0e8-2f1d7c9b3e54</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="n"/>
+    </row>
+    <row r="8" ht="27" customHeight="1">
+      <c r="A8" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>organization_id</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>uuid</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>organizations.organization_id (khi xóa: chặn xóa)</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>Tổ chức khách hàng đăng ký.</t>
+        </is>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>3f6c2a1e-8b4d-4e2a-9c1f-0a7d5b2e4c11</t>
+        </is>
+      </c>
+      <c r="I8" s="6" t="n"/>
+    </row>
+    <row r="9" ht="27" customHeight="1">
+      <c r="A9" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>plan_id</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>uuid</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>subscription_plans.plan_id (khi xóa: chặn xóa)</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>Gói được đăng ký.</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>0c9a6e3d-8f5b-4c7e-a2d1-4b3f9e6c0a65</t>
+        </is>
+      </c>
+      <c r="I9" s="6" t="n"/>
+    </row>
+    <row r="10" ht="27" customHeight="1">
+      <c r="A10" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>vehicle_id</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>uuid</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>vehicles.vehicle_id (khi xóa: chặn xóa)</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>Xe được áp dụng.</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>7a4c1e9b-3d2f-4b8a-a6c5-1e0d9f8b7a44</t>
+        </is>
+      </c>
+      <c r="I10" s="6" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>started_at</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>timestamptz</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="n"/>
+      <c r="F11" s="6" t="n"/>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>Thời điểm bắt đầu thuê bao.</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="I11" s="6" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>ends_at</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>timestamptz</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="n"/>
+      <c r="F12" s="6" t="n"/>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>Thời điểm kết thúc; NULL nếu tự gia hạn cho tới khi hủy.</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="I12" s="6" t="n"/>
+    </row>
+    <row r="13" ht="27" customHeight="1">
+      <c r="A13" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>varchar(20)</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="n"/>
+      <c r="F13" s="6" t="n"/>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>Trạng thái thuê bao; OVERDUE sẽ khóa các tính năng trả phí. Giá trị: ACTIVE | OVERDUE | EXPIRED | CANCELLED.</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="I13" s="6" t="n"/>
+    </row>
+    <row r="14"/>
+    <row r="15">
+      <c r="A15" s="4" t="n"/>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>Được tham chiếu bởi bảng</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>Cột</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="n"/>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>invoice_lines</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>subscription_id</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A6:I13"/>
+  <hyperlinks>
+    <hyperlink ref="A2" location="'Tổng quan'!A1"/>
+    <hyperlink ref="F8" location="'organizations'!A1"/>
+    <hyperlink ref="F9" location="'subscription_plans'!A1"/>
+    <hyperlink ref="F10" location="'vehicles'!A1"/>
+    <hyperlink ref="B16" location="'invoice_lines'!A1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet67.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="7" max="7"/>
+    <col width="42" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
           <t>55. driver_scores: Điểm tài xế</t>
         </is>
       </c>
@@ -40040,7 +40834,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet67.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet68.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -40347,7 +41141,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet68.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet69.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/docs/design/domain-model/domain-model.xlsx
+++ b/docs/design/domain-model/domain-model.xlsx
@@ -58,30 +58,31 @@
     <sheet name="charging_connector_history" sheetId="49" state="visible" r:id="rId49"/>
     <sheet name="charging_connector_state" sheetId="50" state="visible" r:id="rId50"/>
     <sheet name="charging_ocpp_messages" sheetId="51" state="visible" r:id="rId51"/>
-    <sheet name="charging_station_config_entries" sheetId="52" state="visible" r:id="rId52"/>
-    <sheet name="charging_sessions" sheetId="53" state="visible" r:id="rId53"/>
-    <sheet name="charging_session_events" sheetId="54" state="visible" r:id="rId54"/>
-    <sheet name="charging_session_measurements" sheetId="55" state="visible" r:id="rId55"/>
-    <sheet name="notifications" sheetId="56" state="visible" r:id="rId56"/>
-    <sheet name="support_cases" sheetId="57" state="visible" r:id="rId57"/>
-    <sheet name="repair_partners" sheetId="58" state="visible" r:id="rId58"/>
-    <sheet name="maintenance_bookings" sheetId="59" state="visible" r:id="rId59"/>
-    <sheet name="charging_policies" sheetId="60" state="visible" r:id="rId60"/>
-    <sheet name="charging_policy_versions" sheetId="61" state="visible" r:id="rId61"/>
-    <sheet name="charging_policy_assignments" sheetId="62" state="visible" r:id="rId62"/>
-    <sheet name="policy_violations" sheetId="63" state="visible" r:id="rId63"/>
-    <sheet name="tariffs" sheetId="64" state="visible" r:id="rId64"/>
-    <sheet name="payments" sheetId="65" state="visible" r:id="rId65"/>
-    <sheet name="wallets" sheetId="66" state="visible" r:id="rId66"/>
-    <sheet name="wallet_transactions" sheetId="67" state="visible" r:id="rId67"/>
-    <sheet name="invoices" sheetId="68" state="visible" r:id="rId68"/>
-    <sheet name="invoice_lines" sheetId="69" state="visible" r:id="rId69"/>
-    <sheet name="subscription_plans" sheetId="70" state="visible" r:id="rId70"/>
-    <sheet name="plan_features" sheetId="71" state="visible" r:id="rId71"/>
-    <sheet name="subscriptions" sheetId="72" state="visible" r:id="rId72"/>
-    <sheet name="driver_scores" sheetId="73" state="visible" r:id="rId73"/>
-    <sheet name="promotion_campaigns" sheetId="74" state="visible" r:id="rId74"/>
-    <sheet name="trips" sheetId="75" state="visible" r:id="rId75"/>
+    <sheet name="charging_station_config_capture" sheetId="52" state="visible" r:id="rId52"/>
+    <sheet name="charging_station_config_entries" sheetId="53" state="visible" r:id="rId53"/>
+    <sheet name="charging_sessions" sheetId="54" state="visible" r:id="rId54"/>
+    <sheet name="charging_session_events" sheetId="55" state="visible" r:id="rId55"/>
+    <sheet name="charging_session_measurements" sheetId="56" state="visible" r:id="rId56"/>
+    <sheet name="notifications" sheetId="57" state="visible" r:id="rId57"/>
+    <sheet name="support_cases" sheetId="58" state="visible" r:id="rId58"/>
+    <sheet name="repair_partners" sheetId="59" state="visible" r:id="rId59"/>
+    <sheet name="maintenance_bookings" sheetId="60" state="visible" r:id="rId60"/>
+    <sheet name="charging_policies" sheetId="61" state="visible" r:id="rId61"/>
+    <sheet name="charging_policy_versions" sheetId="62" state="visible" r:id="rId62"/>
+    <sheet name="charging_policy_assignments" sheetId="63" state="visible" r:id="rId63"/>
+    <sheet name="policy_violations" sheetId="64" state="visible" r:id="rId64"/>
+    <sheet name="tariffs" sheetId="65" state="visible" r:id="rId65"/>
+    <sheet name="payments" sheetId="66" state="visible" r:id="rId66"/>
+    <sheet name="wallets" sheetId="67" state="visible" r:id="rId67"/>
+    <sheet name="wallet_transactions" sheetId="68" state="visible" r:id="rId68"/>
+    <sheet name="invoices" sheetId="69" state="visible" r:id="rId69"/>
+    <sheet name="invoice_lines" sheetId="70" state="visible" r:id="rId70"/>
+    <sheet name="subscription_plans" sheetId="71" state="visible" r:id="rId71"/>
+    <sheet name="plan_features" sheetId="72" state="visible" r:id="rId72"/>
+    <sheet name="subscriptions" sheetId="73" state="visible" r:id="rId73"/>
+    <sheet name="driver_scores" sheetId="74" state="visible" r:id="rId74"/>
+    <sheet name="promotion_campaigns" sheetId="75" state="visible" r:id="rId75"/>
+    <sheet name="trips" sheetId="76" state="visible" r:id="rId76"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'organizations'!$A$7:$I$20</definedName>
@@ -133,31 +134,32 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="47" hidden="1">'charging_connectors'!$A$8:$I$23</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="48" hidden="1">'charging_connector_history'!$A$7:$I$21</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="49" hidden="1">'charging_connector_state'!$A$7:$I$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="50" hidden="1">'charging_ocpp_messages'!$A$6:$I$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="51" hidden="1">'charging_station_config_entries'!$A$6:$I$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="52" hidden="1">'charging_sessions'!$A$6:$I$25</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="53" hidden="1">'charging_session_events'!$A$6:$I$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="54" hidden="1">'charging_session_measurements'!$A$6:$I$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="55" hidden="1">'notifications'!$A$6:$I$16</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="56" hidden="1">'support_cases'!$A$6:$I$28</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="57" hidden="1">'repair_partners'!$A$6:$I$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="58" hidden="1">'maintenance_bookings'!$A$6:$I$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="59" hidden="1">'charging_policies'!$A$6:$I$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="60" hidden="1">'charging_policy_versions'!$A$6:$I$16</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="61" hidden="1">'charging_policy_assignments'!$A$6:$I$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="62" hidden="1">'policy_violations'!$A$6:$I$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="63" hidden="1">'tariffs'!$A$6:$I$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="64" hidden="1">'payments'!$A$6:$I$16</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="65" hidden="1">'wallets'!$A$6:$I$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="66" hidden="1">'wallet_transactions'!$A$6:$I$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="67" hidden="1">'invoices'!$A$6:$I$16</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="68" hidden="1">'invoice_lines'!$A$6:$I$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="69" hidden="1">'subscription_plans'!$A$6:$I$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="70" hidden="1">'plan_features'!$A$6:$I$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="71" hidden="1">'subscriptions'!$A$6:$I$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="72" hidden="1">'driver_scores'!$A$6:$I$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="73" hidden="1">'promotion_campaigns'!$A$6:$I$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="74" hidden="1">'trips'!$A$6:$I$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="50" hidden="1">'charging_ocpp_messages'!$A$6:$I$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="51" hidden="1">'charging_station_config_capture'!$A$6:$I$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="52" hidden="1">'charging_station_config_entries'!$A$6:$I$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="53" hidden="1">'charging_sessions'!$A$6:$I$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="54" hidden="1">'charging_session_events'!$A$6:$I$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="55" hidden="1">'charging_session_measurements'!$A$6:$I$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="56" hidden="1">'notifications'!$A$6:$I$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="57" hidden="1">'support_cases'!$A$6:$I$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="58" hidden="1">'repair_partners'!$A$6:$I$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="59" hidden="1">'maintenance_bookings'!$A$6:$I$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="60" hidden="1">'charging_policies'!$A$6:$I$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="61" hidden="1">'charging_policy_versions'!$A$6:$I$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="62" hidden="1">'charging_policy_assignments'!$A$6:$I$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="63" hidden="1">'policy_violations'!$A$6:$I$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="64" hidden="1">'tariffs'!$A$6:$I$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="65" hidden="1">'payments'!$A$6:$I$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="66" hidden="1">'wallets'!$A$6:$I$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="67" hidden="1">'wallet_transactions'!$A$6:$I$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="68" hidden="1">'invoices'!$A$6:$I$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="69" hidden="1">'invoice_lines'!$A$6:$I$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="70" hidden="1">'subscription_plans'!$A$6:$I$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="71" hidden="1">'plan_features'!$A$6:$I$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="72" hidden="1">'subscriptions'!$A$6:$I$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="73" hidden="1">'driver_scores'!$A$6:$I$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="74" hidden="1">'promotion_campaigns'!$A$6:$I$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="75" hidden="1">'trips'!$A$6:$I$14</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -646,7 +648,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I117"/>
+  <dimension ref="A1:I118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -677,7 +679,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>74 bảng trong 16 miền nghiệp vụ: 56 bảng chính, 15 bảng lịch sử (N.h), 3 bảng trạng thái. Bấm vào tên bảng hoặc «→ Mở» để mở sheet chi tiết của bảng; chú giải và các quyết định còn mở nằm ở cuối trang.</t>
+          <t>75 bảng trong 16 miền nghiệp vụ: 57 bảng chính, 15 bảng lịch sử (N.h), 3 bảng trạng thái. Bấm vào tên bảng hoặc «→ Mở» để mở sheet chi tiết của bảng; chú giải và các quyết định còn mở nằm ở cuối trang.</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2640,7 @@
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>13 bảng</t>
+          <t>14 bảng</t>
         </is>
       </c>
       <c r="D52" s="5" t="n"/>
@@ -3185,7 +3187,7 @@
         </is>
       </c>
       <c r="H64" s="6" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I64" s="7" t="inlineStr">
         <is>
@@ -3193,7 +3195,7 @@
         </is>
       </c>
     </row>
-    <row r="65" ht="27" customHeight="1">
+    <row r="65" ht="67.5" customHeight="1">
       <c r="A65" s="6" t="inlineStr">
         <is>
           <t>36</t>
@@ -3206,54 +3208,99 @@
       </c>
       <c r="C65" s="7" t="inlineStr">
         <is>
+          <t>charging_station_configuration_captures</t>
+        </is>
+      </c>
+      <c r="D65" s="7" t="inlineStr">
+        <is>
+          <t>Lần chụp cấu hình trụ</t>
+        </is>
+      </c>
+      <c r="E65" s="6" t="inlineStr">
+        <is>
+          <t>Nội bộ</t>
+        </is>
+      </c>
+      <c r="F65" s="6" t="inlineStr">
+        <is>
+          <t>F-G2</t>
+        </is>
+      </c>
+      <c r="G65" s="6" t="inlineStr">
+        <is>
+          <t>Một lần chụp cấu hình của trụ sạc: một câu trả lời GetConfiguration (1.6J) hoặc một GetBaseReport được trả lời bằng nhiều phần NotifyReport (2.0.1). Các cấu hình nằm ở charging_station_configuration_entries. Chỉ ghi thêm: cấu hình hiện tại là lần chụp COMPLETE mới nhất, so hai lần chụp cho biết những gì đã đổi (CS-19). Đổi một cấu hình là lệnh gửi xuống trụ, không phải một lần chụp.</t>
+        </is>
+      </c>
+      <c r="H65" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="I65" s="7" t="inlineStr">
+        <is>
+          <t>→ Mở</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="67.5" customHeight="1">
+      <c r="A66" s="6" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B66" s="6" t="inlineStr">
+        <is>
+          <t>Trạm sạc (charging_stations)</t>
+        </is>
+      </c>
+      <c r="C66" s="7" t="inlineStr">
+        <is>
           <t>charging_station_configuration_entries</t>
         </is>
       </c>
-      <c r="D65" s="7" t="inlineStr">
+      <c r="D66" s="7" t="inlineStr">
         <is>
           <t>Cấu hình trụ sạc</t>
         </is>
       </c>
-      <c r="E65" s="6" t="inlineStr">
+      <c r="E66" s="6" t="inlineStr">
         <is>
           <t>Nội bộ</t>
         </is>
       </c>
-      <c r="F65" s="6" t="inlineStr">
+      <c r="F66" s="6" t="inlineStr">
         <is>
           <t>F-G2</t>
         </is>
       </c>
-      <c r="G65" s="6" t="inlineStr">
-        <is>
-          <t>Một khóa cấu hình trong câu trả lời GetConfiguration của trụ sạc (các bản chụp chỉ ghi thêm).</t>
-        </is>
-      </c>
-      <c r="H65" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="I65" s="7" t="inlineStr">
+      <c r="G66" s="6" t="inlineStr">
+        <is>
+          <t>Một giá trị của một cấu hình trong một lần chụp (CS-19). Đặt tên theo cách của OCPP 2.0.1 (thành phần + biến + loại thuộc tính), cách này cũng chứa được 1.6J: khóa 1.6J là một biến không có thành phần, thuộc tính Actual, và readonly được quy đổi sang mutability. Cấu hình được lưu đúng như trụ gửi; khóa 1.6J không bị dịch sang tên 2.0.1. Chỉ ghi thêm, theo lần chụp của nó.</t>
+        </is>
+      </c>
+      <c r="H66" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="I66" s="7" t="inlineStr">
         <is>
           <t>→ Mở</t>
         </is>
       </c>
     </row>
-    <row r="66" ht="108" customHeight="1">
-      <c r="A66" s="5" t="n"/>
-      <c r="B66" s="5" t="inlineStr">
+    <row r="67" ht="108" customHeight="1">
+      <c r="A67" s="5" t="n"/>
+      <c r="B67" s="5" t="inlineStr">
         <is>
           <t>Phiên sạc (charging_sessions)</t>
         </is>
       </c>
-      <c r="C66" s="5" t="inlineStr">
+      <c r="C67" s="5" t="inlineStr">
         <is>
           <t>3 bảng</t>
         </is>
       </c>
-      <c r="D66" s="5" t="n"/>
-      <c r="E66" s="5" t="n"/>
-      <c r="F66" s="5" t="n"/>
-      <c r="G66" s="5" t="inlineStr">
+      <c r="D67" s="5" t="n"/>
+      <c r="E67" s="5" t="n"/>
+      <c r="F67" s="5" t="n"/>
+      <c r="G67" s="5" t="inlineStr">
         <is>
           <t>Những gì diễn ra trong mỗi lần sạc: sự kiện, chỉ số công tơ, điện năng đã cấp.
 • Một phiên sạc diễn ra trên một súng sạc của một trạm G3.
@@ -3262,89 +3309,44 @@
         </is>
       </c>
     </row>
-    <row r="67" ht="27" customHeight="1">
-      <c r="A67" s="6" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="B67" s="6" t="inlineStr">
+    <row r="68" ht="67.5" customHeight="1">
+      <c r="A68" s="6" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B68" s="6" t="inlineStr">
         <is>
           <t>Phiên sạc (charging_sessions)</t>
         </is>
       </c>
-      <c r="C67" s="7" t="inlineStr">
+      <c r="C68" s="7" t="inlineStr">
         <is>
           <t>charging_sessions</t>
         </is>
       </c>
-      <c r="D67" s="7" t="inlineStr">
+      <c r="D68" s="7" t="inlineStr">
         <is>
           <t>Phiên sạc</t>
         </is>
       </c>
-      <c r="E67" s="6" t="inlineStr">
+      <c r="E68" s="6" t="inlineStr">
         <is>
           <t>Hai bên</t>
         </is>
       </c>
-      <c r="F67" s="6" t="inlineStr">
+      <c r="F68" s="6" t="inlineStr">
         <is>
           <t>F-B2, F-C5</t>
         </is>
       </c>
-      <c r="G67" s="6" t="inlineStr">
-        <is>
-          <t>Một lần sạc trên một súng sạc, từ lúc bắt đầu đến lúc kết thúc.</t>
-        </is>
-      </c>
-      <c r="H67" s="6" t="n">
+      <c r="G68" s="6" t="inlineStr">
+        <is>
+          <t>Một lần sạc trên một súng sạc, từ lúc bắt đầu đến lúc kết thúc. Cần quyết định khi rà soát bảng (CS-18): lần sạc bằng QR (CO-14) cần lưu ngữ cảnh nghiệp vụ ngay khi tài xế quét (ai quét, tổ chức nào trả tiền, mã gửi trong RemoteStartTransaction, câu trả lời của trụ) để ghép với StartTransaction mang mã đó: tạo dòng phiên PENDING khi quét, một bảng các lệnh gửi xuống trụ, hoặc cả hai.</t>
+        </is>
+      </c>
+      <c r="H68" s="6" t="n">
         <v>19</v>
-      </c>
-      <c r="I67" s="7" t="inlineStr">
-        <is>
-          <t>→ Mở</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="27" customHeight="1">
-      <c r="A68" s="6" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="B68" s="6" t="inlineStr">
-        <is>
-          <t>Phiên sạc (charging_sessions)</t>
-        </is>
-      </c>
-      <c r="C68" s="7" t="inlineStr">
-        <is>
-          <t>charging_session_events</t>
-        </is>
-      </c>
-      <c r="D68" s="7" t="inlineStr">
-        <is>
-          <t>Sự kiện phiên sạc</t>
-        </is>
-      </c>
-      <c r="E68" s="6" t="inlineStr">
-        <is>
-          <t>Hai bên</t>
-        </is>
-      </c>
-      <c r="F68" s="6" t="inlineStr">
-        <is>
-          <t>F-B2</t>
-        </is>
-      </c>
-      <c r="G68" s="6" t="inlineStr">
-        <is>
-          <t>Từng sự kiện Bắt đầu / Cập nhật / Kết thúc của một phiên sạc.</t>
-        </is>
-      </c>
-      <c r="H68" s="6" t="n">
-        <v>5</v>
       </c>
       <c r="I68" s="7" t="inlineStr">
         <is>
@@ -3365,54 +3367,99 @@
       </c>
       <c r="C69" s="7" t="inlineStr">
         <is>
+          <t>charging_session_events</t>
+        </is>
+      </c>
+      <c r="D69" s="7" t="inlineStr">
+        <is>
+          <t>Sự kiện phiên sạc</t>
+        </is>
+      </c>
+      <c r="E69" s="6" t="inlineStr">
+        <is>
+          <t>Hai bên</t>
+        </is>
+      </c>
+      <c r="F69" s="6" t="inlineStr">
+        <is>
+          <t>F-B2</t>
+        </is>
+      </c>
+      <c r="G69" s="6" t="inlineStr">
+        <is>
+          <t>Từng sự kiện Bắt đầu / Cập nhật / Kết thúc của một phiên sạc.</t>
+        </is>
+      </c>
+      <c r="H69" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="I69" s="7" t="inlineStr">
+        <is>
+          <t>→ Mở</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="27" customHeight="1">
+      <c r="A70" s="6" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B70" s="6" t="inlineStr">
+        <is>
+          <t>Phiên sạc (charging_sessions)</t>
+        </is>
+      </c>
+      <c r="C70" s="7" t="inlineStr">
+        <is>
           <t>charging_session_measurements</t>
         </is>
       </c>
-      <c r="D69" s="7" t="inlineStr">
+      <c r="D70" s="7" t="inlineStr">
         <is>
           <t>Số đo phiên sạc</t>
         </is>
       </c>
-      <c r="E69" s="6" t="inlineStr">
+      <c r="E70" s="6" t="inlineStr">
         <is>
           <t>Hai bên</t>
         </is>
       </c>
-      <c r="F69" s="6" t="inlineStr">
+      <c r="F70" s="6" t="inlineStr">
         <is>
           <t>F-B2</t>
         </is>
       </c>
-      <c r="G69" s="6" t="inlineStr">
+      <c r="G70" s="6" t="inlineStr">
         <is>
           <t>Mọi giá trị đo trụ sạc gửi trong phiên (điện năng, công suất, SOC...).</t>
         </is>
       </c>
-      <c r="H69" s="6" t="n">
+      <c r="H70" s="6" t="n">
         <v>9</v>
       </c>
-      <c r="I69" s="7" t="inlineStr">
+      <c r="I70" s="7" t="inlineStr">
         <is>
           <t>→ Mở</t>
         </is>
       </c>
     </row>
-    <row r="70" ht="54" customHeight="1">
-      <c r="A70" s="5" t="n"/>
-      <c r="B70" s="5" t="inlineStr">
+    <row r="71" ht="54" customHeight="1">
+      <c r="A71" s="5" t="n"/>
+      <c r="B71" s="5" t="inlineStr">
         <is>
           <t>Thông báo &amp; cảnh báo (notifications)</t>
         </is>
       </c>
-      <c r="C70" s="5" t="inlineStr">
+      <c r="C71" s="5" t="inlineStr">
         <is>
           <t>1 bảng</t>
         </is>
       </c>
-      <c r="D70" s="5" t="n"/>
-      <c r="E70" s="5" t="n"/>
-      <c r="F70" s="5" t="n"/>
-      <c r="G70" s="5" t="inlineStr">
+      <c r="D71" s="5" t="n"/>
+      <c r="E71" s="5" t="n"/>
+      <c r="F71" s="5" t="n"/>
+      <c r="G71" s="5" t="inlineStr">
         <is>
           <t>Cảnh báo do các miền khác phát sinh, được lưu để người vận hành truy vấn.
 • Một thông báo thường nói về một xe.
@@ -3420,67 +3467,67 @@
         </is>
       </c>
     </row>
-    <row r="71" ht="27" customHeight="1">
-      <c r="A71" s="6" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="B71" s="6" t="inlineStr">
+    <row r="72" ht="27" customHeight="1">
+      <c r="A72" s="6" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B72" s="6" t="inlineStr">
         <is>
           <t>Thông báo &amp; cảnh báo (notifications)</t>
         </is>
       </c>
-      <c r="C71" s="7" t="inlineStr">
+      <c r="C72" s="7" t="inlineStr">
         <is>
           <t>notifications</t>
         </is>
       </c>
-      <c r="D71" s="7" t="inlineStr">
+      <c r="D72" s="7" t="inlineStr">
         <is>
           <t>Thông báo</t>
         </is>
       </c>
-      <c r="E71" s="6" t="inlineStr">
+      <c r="E72" s="6" t="inlineStr">
         <is>
           <t>Khách hàng</t>
         </is>
       </c>
-      <c r="F71" s="6" t="inlineStr">
+      <c r="F72" s="6" t="inlineStr">
         <is>
           <t>F-A2, F-A3, F-A4, F-J1, F-J3</t>
         </is>
       </c>
-      <c r="G71" s="6" t="inlineStr">
+      <c r="G72" s="6" t="inlineStr">
         <is>
           <t>Một cảnh báo (pin, bất thường, SOH, thiết bị mất kết nối...). Một bảng chung; mỗi loại cảnh báo là một giá trị enum và một cấu trúc payload.</t>
         </is>
       </c>
-      <c r="H71" s="6" t="n">
+      <c r="H72" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="I71" s="7" t="inlineStr">
+      <c r="I72" s="7" t="inlineStr">
         <is>
           <t>→ Mở</t>
         </is>
       </c>
     </row>
-    <row r="72" ht="81" customHeight="1">
-      <c r="A72" s="5" t="n"/>
-      <c r="B72" s="5" t="inlineStr">
+    <row r="73" ht="81" customHeight="1">
+      <c r="A73" s="5" t="n"/>
+      <c r="B73" s="5" t="inlineStr">
         <is>
           <t>CSKH &amp; cứu hộ (support)</t>
         </is>
       </c>
-      <c r="C72" s="5" t="inlineStr">
+      <c r="C73" s="5" t="inlineStr">
         <is>
           <t>3 bảng</t>
         </is>
       </c>
-      <c r="D72" s="5" t="n"/>
-      <c r="E72" s="5" t="n"/>
-      <c r="F72" s="5" t="n"/>
-      <c r="G72" s="5" t="inlineStr">
+      <c r="D73" s="5" t="n"/>
+      <c r="E73" s="5" t="n"/>
+      <c r="F73" s="5" t="n"/>
+      <c r="G73" s="5" t="inlineStr">
         <is>
           <t>Chăm sóc khách hàng: yêu cầu hỗ trợ, SOS, điều phối cứu hộ và đặt lịch bảo dưỡng.
 • Một ca hỗ trợ (yêu cầu thường hoặc SOS) liên quan đến một xe và/hoặc một tài xế của một tổ chức.
@@ -3489,51 +3536,6 @@
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="6" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="B73" s="6" t="inlineStr">
-        <is>
-          <t>CSKH &amp; cứu hộ (support)</t>
-        </is>
-      </c>
-      <c r="C73" s="7" t="inlineStr">
-        <is>
-          <t>support_cases</t>
-        </is>
-      </c>
-      <c r="D73" s="7" t="inlineStr">
-        <is>
-          <t>Ca hỗ trợ</t>
-        </is>
-      </c>
-      <c r="E73" s="6" t="inlineStr">
-        <is>
-          <t>Khách hàng</t>
-        </is>
-      </c>
-      <c r="F73" s="6" t="inlineStr">
-        <is>
-          <t>F-I1, F-I2</t>
-        </is>
-      </c>
-      <c r="G73" s="6" t="inlineStr">
-        <is>
-          <t>Một yêu cầu hỗ trợ: yêu cầu thường hoặc SOS, kèm mốc thời gian SLA.</t>
-        </is>
-      </c>
-      <c r="H73" s="6" t="n">
-        <v>22</v>
-      </c>
-      <c r="I73" s="7" t="inlineStr">
-        <is>
-          <t>→ Mở</t>
-        </is>
-      </c>
-    </row>
     <row r="74">
       <c r="A74" s="6" t="inlineStr">
         <is>
@@ -3547,31 +3549,31 @@
       </c>
       <c r="C74" s="7" t="inlineStr">
         <is>
-          <t>repair_partners</t>
+          <t>support_cases</t>
         </is>
       </c>
       <c r="D74" s="7" t="inlineStr">
         <is>
-          <t>Đối tác sửa chữa &amp; cứu hộ</t>
+          <t>Ca hỗ trợ</t>
         </is>
       </c>
       <c r="E74" s="6" t="inlineStr">
         <is>
-          <t>Nội bộ</t>
+          <t>Khách hàng</t>
         </is>
       </c>
       <c r="F74" s="6" t="inlineStr">
         <is>
-          <t>F-I4, F-I3</t>
+          <t>F-I1, F-I2</t>
         </is>
       </c>
       <c r="G74" s="6" t="inlineStr">
         <is>
-          <t>Một xưởng hoặc đơn vị cứu hộ mà CSKH có thể điều phối tới.</t>
+          <t>Một yêu cầu hỗ trợ: yêu cầu thường hoặc SOS, kèm mốc thời gian SLA.</t>
         </is>
       </c>
       <c r="H74" s="6" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="I74" s="7" t="inlineStr">
         <is>
@@ -3592,27 +3594,27 @@
       </c>
       <c r="C75" s="7" t="inlineStr">
         <is>
-          <t>maintenance_bookings</t>
+          <t>repair_partners</t>
         </is>
       </c>
       <c r="D75" s="7" t="inlineStr">
         <is>
-          <t>Lịch bảo dưỡng</t>
+          <t>Đối tác sửa chữa &amp; cứu hộ</t>
         </is>
       </c>
       <c r="E75" s="6" t="inlineStr">
         <is>
-          <t>Khách hàng</t>
+          <t>Nội bộ</t>
         </is>
       </c>
       <c r="F75" s="6" t="inlineStr">
         <is>
-          <t>F-I3</t>
+          <t>F-I4, F-I3</t>
         </is>
       </c>
       <c r="G75" s="6" t="inlineStr">
         <is>
-          <t>Một lịch hẹn bảo dưỡng xe tại xưởng đối tác.</t>
+          <t>Một xưởng hoặc đơn vị cứu hộ mà CSKH có thể điều phối tới.</t>
         </is>
       </c>
       <c r="H75" s="6" t="n">
@@ -3624,22 +3626,67 @@
         </is>
       </c>
     </row>
-    <row r="76" ht="81" customHeight="1">
-      <c r="A76" s="5" t="n"/>
-      <c r="B76" s="5" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="6" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B76" s="6" t="inlineStr">
+        <is>
+          <t>CSKH &amp; cứu hộ (support)</t>
+        </is>
+      </c>
+      <c r="C76" s="7" t="inlineStr">
+        <is>
+          <t>maintenance_bookings</t>
+        </is>
+      </c>
+      <c r="D76" s="7" t="inlineStr">
+        <is>
+          <t>Lịch bảo dưỡng</t>
+        </is>
+      </c>
+      <c r="E76" s="6" t="inlineStr">
+        <is>
+          <t>Khách hàng</t>
+        </is>
+      </c>
+      <c r="F76" s="6" t="inlineStr">
+        <is>
+          <t>F-I3</t>
+        </is>
+      </c>
+      <c r="G76" s="6" t="inlineStr">
+        <is>
+          <t>Một lịch hẹn bảo dưỡng xe tại xưởng đối tác.</t>
+        </is>
+      </c>
+      <c r="H76" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="I76" s="7" t="inlineStr">
+        <is>
+          <t>→ Mở</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="81" customHeight="1">
+      <c r="A77" s="5" t="n"/>
+      <c r="B77" s="5" t="inlineStr">
         <is>
           <t>Chính sách sạc (bảo hành) (policy)</t>
         </is>
       </c>
-      <c r="C76" s="5" t="inlineStr">
+      <c r="C77" s="5" t="inlineStr">
         <is>
           <t>4 bảng</t>
         </is>
       </c>
-      <c r="D76" s="5" t="n"/>
-      <c r="E76" s="5" t="n"/>
-      <c r="F76" s="5" t="n"/>
-      <c r="G76" s="5" t="inlineStr">
+      <c r="D77" s="5" t="n"/>
+      <c r="E77" s="5" t="n"/>
+      <c r="F77" s="5" t="n"/>
+      <c r="G77" s="5" t="inlineStr">
         <is>
           <t>Quy tắc sạc gắn với bảo hành và các vi phạm được phát hiện.
 • Một chính sách có nhiều phiên bản không sửa được; giá trị cụ thể do G3 Mobility quyết định.
@@ -3648,51 +3695,6 @@
         </is>
       </c>
     </row>
-    <row r="77" ht="27" customHeight="1">
-      <c r="A77" s="6" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="B77" s="6" t="inlineStr">
-        <is>
-          <t>Chính sách sạc (bảo hành) (policy)</t>
-        </is>
-      </c>
-      <c r="C77" s="7" t="inlineStr">
-        <is>
-          <t>charging_policies</t>
-        </is>
-      </c>
-      <c r="D77" s="7" t="inlineStr">
-        <is>
-          <t>Chính sách sạc</t>
-        </is>
-      </c>
-      <c r="E77" s="6" t="inlineStr">
-        <is>
-          <t>Nội bộ</t>
-        </is>
-      </c>
-      <c r="F77" s="6" t="inlineStr">
-        <is>
-          <t>F-B1</t>
-        </is>
-      </c>
-      <c r="G77" s="6" t="inlineStr">
-        <is>
-          <t>Một chính sách sạc bảo hành có tên do G3 Mobility định nghĩa.</t>
-        </is>
-      </c>
-      <c r="H77" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="I77" s="7" t="inlineStr">
-        <is>
-          <t>→ Mở</t>
-        </is>
-      </c>
-    </row>
     <row r="78" ht="27" customHeight="1">
       <c r="A78" s="6" t="inlineStr">
         <is>
@@ -3706,12 +3708,12 @@
       </c>
       <c r="C78" s="7" t="inlineStr">
         <is>
-          <t>charging_policy_versions</t>
+          <t>charging_policies</t>
         </is>
       </c>
       <c r="D78" s="7" t="inlineStr">
         <is>
-          <t>Phiên bản chính sách sạc</t>
+          <t>Chính sách sạc</t>
         </is>
       </c>
       <c r="E78" s="6" t="inlineStr">
@@ -3726,11 +3728,11 @@
       </c>
       <c r="G78" s="6" t="inlineStr">
         <is>
-          <t>Một phiên bản quy tắc không sửa được của chính sách. Mọi phiên bản đều được giữ để kiểm toán.</t>
+          <t>Một chính sách sạc bảo hành có tên do G3 Mobility định nghĩa.</t>
         </is>
       </c>
       <c r="H78" s="6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I78" s="7" t="inlineStr">
         <is>
@@ -3751,17 +3753,17 @@
       </c>
       <c r="C79" s="7" t="inlineStr">
         <is>
-          <t>charging_policy_assignments</t>
+          <t>charging_policy_versions</t>
         </is>
       </c>
       <c r="D79" s="7" t="inlineStr">
         <is>
-          <t>Áp dụng chính sách sạc</t>
+          <t>Phiên bản chính sách sạc</t>
         </is>
       </c>
       <c r="E79" s="6" t="inlineStr">
         <is>
-          <t>Khách hàng</t>
+          <t>Nội bộ</t>
         </is>
       </c>
       <c r="F79" s="6" t="inlineStr">
@@ -3771,11 +3773,11 @@
       </c>
       <c r="G79" s="6" t="inlineStr">
         <is>
-          <t>Chính sách nào áp dụng cho một xe, một đội xe hay một dòng xe.</t>
+          <t>Một phiên bản quy tắc không sửa được của chính sách. Mọi phiên bản đều được giữ để kiểm toán.</t>
         </is>
       </c>
       <c r="H79" s="6" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I79" s="7" t="inlineStr">
         <is>
@@ -3796,12 +3798,12 @@
       </c>
       <c r="C80" s="7" t="inlineStr">
         <is>
-          <t>policy_violations</t>
+          <t>charging_policy_assignments</t>
         </is>
       </c>
       <c r="D80" s="7" t="inlineStr">
         <is>
-          <t>Vi phạm chính sách sạc</t>
+          <t>Áp dụng chính sách sạc</t>
         </is>
       </c>
       <c r="E80" s="6" t="inlineStr">
@@ -3811,12 +3813,12 @@
       </c>
       <c r="F80" s="6" t="inlineStr">
         <is>
-          <t>F-B3, F-B6</t>
+          <t>F-B1</t>
         </is>
       </c>
       <c r="G80" s="6" t="inlineStr">
         <is>
-          <t>Một phiên sạc vi phạm chính sách, kèm bằng chứng. Hệ quả của vi phạm vẫn là câu hỏi kinh doanh còn mở (mục 3 của feature-list).</t>
+          <t>Chính sách nào áp dụng cho một xe, một đội xe hay một dòng xe.</t>
         </is>
       </c>
       <c r="H80" s="6" t="n">
@@ -3828,22 +3830,67 @@
         </is>
       </c>
     </row>
-    <row r="81" ht="283.5" customHeight="1">
-      <c r="A81" s="5" t="n"/>
-      <c r="B81" s="5" t="inlineStr">
+    <row r="81" ht="27" customHeight="1">
+      <c r="A81" s="6" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="B81" s="6" t="inlineStr">
+        <is>
+          <t>Chính sách sạc (bảo hành) (policy)</t>
+        </is>
+      </c>
+      <c r="C81" s="7" t="inlineStr">
+        <is>
+          <t>policy_violations</t>
+        </is>
+      </c>
+      <c r="D81" s="7" t="inlineStr">
+        <is>
+          <t>Vi phạm chính sách sạc</t>
+        </is>
+      </c>
+      <c r="E81" s="6" t="inlineStr">
+        <is>
+          <t>Khách hàng</t>
+        </is>
+      </c>
+      <c r="F81" s="6" t="inlineStr">
+        <is>
+          <t>F-B3, F-B6</t>
+        </is>
+      </c>
+      <c r="G81" s="6" t="inlineStr">
+        <is>
+          <t>Một phiên sạc vi phạm chính sách, kèm bằng chứng. Hệ quả của vi phạm vẫn là câu hỏi kinh doanh còn mở (mục 3 của feature-list).</t>
+        </is>
+      </c>
+      <c r="H81" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="I81" s="7" t="inlineStr">
+        <is>
+          <t>→ Mở</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="283.5" customHeight="1">
+      <c r="A82" s="5" t="n"/>
+      <c r="B82" s="5" t="inlineStr">
         <is>
           <t>Thanh toán &amp; hóa đơn (billing)</t>
         </is>
       </c>
-      <c r="C81" s="5" t="inlineStr">
+      <c r="C82" s="5" t="inlineStr">
         <is>
           <t>9 bảng</t>
         </is>
       </c>
-      <c r="D81" s="5" t="n"/>
-      <c r="E81" s="5" t="n"/>
-      <c r="F81" s="5" t="n"/>
-      <c r="G81" s="5" t="inlineStr">
+      <c r="D82" s="5" t="n"/>
+      <c r="E82" s="5" t="n"/>
+      <c r="F82" s="5" t="n"/>
+      <c r="G82" s="5" t="inlineStr">
         <is>
           <t>Tiền: giá điện, thanh toán, ví trả trước, hóa đơn điện tử và thuê bao SaaS.
 • Biểu giá định giá điện cho toàn mạng hoặc từng trạm, theo khung giờ.
@@ -3855,51 +3902,6 @@
         </is>
       </c>
     </row>
-    <row r="82" ht="27" customHeight="1">
-      <c r="A82" s="6" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="B82" s="6" t="inlineStr">
-        <is>
-          <t>Thanh toán &amp; hóa đơn (billing)</t>
-        </is>
-      </c>
-      <c r="C82" s="7" t="inlineStr">
-        <is>
-          <t>tariffs</t>
-        </is>
-      </c>
-      <c r="D82" s="7" t="inlineStr">
-        <is>
-          <t>Biểu giá điện</t>
-        </is>
-      </c>
-      <c r="E82" s="6" t="inlineStr">
-        <is>
-          <t>Nội bộ</t>
-        </is>
-      </c>
-      <c r="F82" s="6" t="inlineStr">
-        <is>
-          <t>F-C8, F-H1</t>
-        </is>
-      </c>
-      <c r="G82" s="6" t="inlineStr">
-        <is>
-          <t>Giá điện. Ai sở hữu biểu giá (G3 Energy hay G3 Network) là mục 5 của feature-list.</t>
-        </is>
-      </c>
-      <c r="H82" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="I82" s="7" t="inlineStr">
-        <is>
-          <t>→ Mở</t>
-        </is>
-      </c>
-    </row>
     <row r="83" ht="27" customHeight="1">
       <c r="A83" s="6" t="inlineStr">
         <is>
@@ -3913,31 +3915,31 @@
       </c>
       <c r="C83" s="7" t="inlineStr">
         <is>
-          <t>payments</t>
+          <t>tariffs</t>
         </is>
       </c>
       <c r="D83" s="7" t="inlineStr">
         <is>
-          <t>Thanh toán</t>
+          <t>Biểu giá điện</t>
         </is>
       </c>
       <c r="E83" s="6" t="inlineStr">
         <is>
-          <t>Khách hàng</t>
+          <t>Nội bộ</t>
         </is>
       </c>
       <c r="F83" s="6" t="inlineStr">
         <is>
-          <t>F-H1</t>
+          <t>F-C8, F-H1</t>
         </is>
       </c>
       <c r="G83" s="6" t="inlineStr">
         <is>
-          <t>Một lần thanh toán qua cổng thanh toán hoặc ví, thường cho một phiên sạc.</t>
+          <t>Giá điện. Ai sở hữu biểu giá (G3 Energy hay G3 Network) là mục 5 của feature-list.</t>
         </is>
       </c>
       <c r="H83" s="6" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I83" s="7" t="inlineStr">
         <is>
@@ -3958,12 +3960,12 @@
       </c>
       <c r="C84" s="7" t="inlineStr">
         <is>
-          <t>wallets</t>
+          <t>payments</t>
         </is>
       </c>
       <c r="D84" s="7" t="inlineStr">
         <is>
-          <t>Ví</t>
+          <t>Thanh toán</t>
         </is>
       </c>
       <c r="E84" s="6" t="inlineStr">
@@ -3973,16 +3975,16 @@
       </c>
       <c r="F84" s="6" t="inlineStr">
         <is>
-          <t>F-H2</t>
+          <t>F-H1</t>
         </is>
       </c>
       <c r="G84" s="6" t="inlineStr">
         <is>
-          <t>Số dư trả trước của một tài xế hoặc của cả tổ chức.</t>
+          <t>Một lần thanh toán qua cổng thanh toán hoặc ví, thường cho một phiên sạc.</t>
         </is>
       </c>
       <c r="H84" s="6" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I84" s="7" t="inlineStr">
         <is>
@@ -4003,12 +4005,12 @@
       </c>
       <c r="C85" s="7" t="inlineStr">
         <is>
-          <t>wallet_transactions</t>
+          <t>wallets</t>
         </is>
       </c>
       <c r="D85" s="7" t="inlineStr">
         <is>
-          <t>Giao dịch ví</t>
+          <t>Ví</t>
         </is>
       </c>
       <c r="E85" s="6" t="inlineStr">
@@ -4023,11 +4025,11 @@
       </c>
       <c r="G85" s="6" t="inlineStr">
         <is>
-          <t>Biến động tiền vào/ra khỏi ví, chỉ ghi thêm.</t>
+          <t>Số dư trả trước của một tài xế hoặc của cả tổ chức.</t>
         </is>
       </c>
       <c r="H85" s="6" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I85" s="7" t="inlineStr">
         <is>
@@ -4048,12 +4050,12 @@
       </c>
       <c r="C86" s="7" t="inlineStr">
         <is>
-          <t>invoices</t>
+          <t>wallet_transactions</t>
         </is>
       </c>
       <c r="D86" s="7" t="inlineStr">
         <is>
-          <t>Hóa đơn</t>
+          <t>Giao dịch ví</t>
         </is>
       </c>
       <c r="E86" s="6" t="inlineStr">
@@ -4063,16 +4065,16 @@
       </c>
       <c r="F86" s="6" t="inlineStr">
         <is>
-          <t>F-H3, F-H4</t>
+          <t>F-H2</t>
         </is>
       </c>
       <c r="G86" s="6" t="inlineStr">
         <is>
-          <t>Một hóa đơn điện tử hợp lệ. Khi đã PHÁT HÀNH thì không sửa, chỉ điều chỉnh hoặc hủy bằng hóa đơn mới.</t>
+          <t>Biến động tiền vào/ra khỏi ví, chỉ ghi thêm.</t>
         </is>
       </c>
       <c r="H86" s="6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I86" s="7" t="inlineStr">
         <is>
@@ -4093,303 +4095,303 @@
       </c>
       <c r="C87" s="7" t="inlineStr">
         <is>
+          <t>invoices</t>
+        </is>
+      </c>
+      <c r="D87" s="7" t="inlineStr">
+        <is>
+          <t>Hóa đơn</t>
+        </is>
+      </c>
+      <c r="E87" s="6" t="inlineStr">
+        <is>
+          <t>Khách hàng</t>
+        </is>
+      </c>
+      <c r="F87" s="6" t="inlineStr">
+        <is>
+          <t>F-H3, F-H4</t>
+        </is>
+      </c>
+      <c r="G87" s="6" t="inlineStr">
+        <is>
+          <t>Một hóa đơn điện tử hợp lệ. Khi đã PHÁT HÀNH thì không sửa, chỉ điều chỉnh hoặc hủy bằng hóa đơn mới.</t>
+        </is>
+      </c>
+      <c r="H87" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="I87" s="7" t="inlineStr">
+        <is>
+          <t>→ Mở</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="27" customHeight="1">
+      <c r="A88" s="6" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="B88" s="6" t="inlineStr">
+        <is>
+          <t>Thanh toán &amp; hóa đơn (billing)</t>
+        </is>
+      </c>
+      <c r="C88" s="7" t="inlineStr">
+        <is>
           <t>invoice_lines</t>
         </is>
       </c>
-      <c r="D87" s="7" t="inlineStr">
+      <c r="D88" s="7" t="inlineStr">
         <is>
           <t>Dòng hóa đơn</t>
         </is>
       </c>
-      <c r="E87" s="6" t="inlineStr">
+      <c r="E88" s="6" t="inlineStr">
         <is>
           <t>Khách hàng</t>
         </is>
       </c>
-      <c r="F87" s="6" t="inlineStr">
+      <c r="F88" s="6" t="inlineStr">
         <is>
           <t>F-H3, F-H4</t>
         </is>
       </c>
-      <c r="G87" s="6" t="inlineStr">
+      <c r="G88" s="6" t="inlineStr">
         <is>
           <t>Một dòng của hóa đơn: một phiên sạc hoặc một kỳ thuê bao.</t>
         </is>
       </c>
-      <c r="H87" s="6" t="n">
+      <c r="H88" s="6" t="n">
         <v>9</v>
       </c>
-      <c r="I87" s="7" t="inlineStr">
+      <c r="I88" s="7" t="inlineStr">
         <is>
           <t>→ Mở</t>
         </is>
       </c>
     </row>
-    <row r="88" ht="54" customHeight="1">
-      <c r="A88" s="6" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="B88" s="6" t="inlineStr">
+    <row r="89" ht="54" customHeight="1">
+      <c r="A89" s="6" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="B89" s="6" t="inlineStr">
         <is>
           <t>Thanh toán &amp; hóa đơn (billing)</t>
         </is>
       </c>
-      <c r="C88" s="7" t="inlineStr">
+      <c r="C89" s="7" t="inlineStr">
         <is>
           <t>subscription_plans</t>
         </is>
       </c>
-      <c r="D88" s="7" t="inlineStr">
+      <c r="D89" s="7" t="inlineStr">
         <is>
           <t>Gói dịch vụ</t>
         </is>
       </c>
-      <c r="E88" s="6" t="inlineStr">
+      <c r="E89" s="6" t="inlineStr">
         <is>
           <t>Nội bộ</t>
         </is>
       </c>
-      <c r="F88" s="6" t="inlineStr">
+      <c r="F89" s="6" t="inlineStr">
         <is>
           <t>F-H4</t>
         </is>
       </c>
-      <c r="G88" s="6" t="inlineStr">
+      <c r="G89" s="6" t="inlineStr">
         <is>
           <t>Một gói dịch vụ: mỗi gói là một dòng (GUEST là gói mặc định miễn phí, STANDARD, ADVANCED, PRO, ..., hoặc gói riêng cho một khách hàng); tính năng của gói nằm ở plan_features. Giá được tính theo từng tính năng (xem ghi chú của miền thanh toán).</t>
         </is>
       </c>
-      <c r="H88" s="6" t="n">
+      <c r="H89" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="I88" s="7" t="inlineStr">
+      <c r="I89" s="7" t="inlineStr">
         <is>
           <t>→ Mở</t>
         </is>
       </c>
     </row>
-    <row r="89" ht="40.5" customHeight="1">
-      <c r="A89" s="6" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="B89" s="6" t="inlineStr">
+    <row r="90" ht="40.5" customHeight="1">
+      <c r="A90" s="6" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="B90" s="6" t="inlineStr">
         <is>
           <t>Thanh toán &amp; hóa đơn (billing)</t>
         </is>
       </c>
-      <c r="C89" s="7" t="inlineStr">
+      <c r="C90" s="7" t="inlineStr">
         <is>
           <t>plan_features</t>
         </is>
       </c>
-      <c r="D89" s="7" t="inlineStr">
+      <c r="D90" s="7" t="inlineStr">
         <is>
           <t>Tính năng của gói dịch vụ</t>
         </is>
       </c>
-      <c r="E89" s="6" t="inlineStr">
+      <c r="E90" s="6" t="inlineStr">
         <is>
           <t>Nội bộ</t>
         </is>
       </c>
-      <c r="F89" s="6" t="inlineStr">
+      <c r="F90" s="6" t="inlineStr">
         <is>
           <t>F-H4</t>
         </is>
       </c>
-      <c r="G89" s="6" t="inlineStr">
+      <c r="G90" s="6" t="inlineStr">
         <is>
           <t>Mỗi gói dịch vụ gồm những tính năng nào. Gói dịch vụ là dữ liệu, nên G3 có thể tạo gói mới (Pro, Max, gói riêng cho một khách hàng) trên portal mà không cần lập trình viên; chỉ tính năng hoàn toàn mới mới cần viết mã.</t>
         </is>
       </c>
-      <c r="H89" s="6" t="n">
+      <c r="H90" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="I89" s="7" t="inlineStr">
+      <c r="I90" s="7" t="inlineStr">
         <is>
           <t>→ Mở</t>
         </is>
       </c>
     </row>
-    <row r="90" ht="27" customHeight="1">
-      <c r="A90" s="6" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="B90" s="6" t="inlineStr">
+    <row r="91" ht="27" customHeight="1">
+      <c r="A91" s="6" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="B91" s="6" t="inlineStr">
         <is>
           <t>Thanh toán &amp; hóa đơn (billing)</t>
         </is>
       </c>
-      <c r="C90" s="7" t="inlineStr">
+      <c r="C91" s="7" t="inlineStr">
         <is>
           <t>subscriptions</t>
         </is>
       </c>
-      <c r="D90" s="7" t="inlineStr">
+      <c r="D91" s="7" t="inlineStr">
         <is>
           <t>Thuê bao</t>
         </is>
       </c>
-      <c r="E90" s="6" t="inlineStr">
+      <c r="E91" s="6" t="inlineStr">
         <is>
           <t>Khách hàng</t>
         </is>
       </c>
-      <c r="F90" s="6" t="inlineStr">
+      <c r="F91" s="6" t="inlineStr">
         <is>
           <t>F-H4</t>
         </is>
       </c>
-      <c r="G90" s="6" t="inlineStr">
+      <c r="G91" s="6" t="inlineStr">
         <is>
           <t>Một xe đăng ký một gói; quá hạn thanh toán sẽ khóa tính năng.</t>
         </is>
       </c>
-      <c r="H90" s="6" t="n">
+      <c r="H91" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="I90" s="7" t="inlineStr">
+      <c r="I91" s="7" t="inlineStr">
         <is>
           <t>→ Mở</t>
         </is>
       </c>
     </row>
-    <row r="91" ht="27" customHeight="1">
-      <c r="A91" s="5" t="n"/>
-      <c r="B91" s="5" t="inlineStr">
+    <row r="92" ht="27" customHeight="1">
+      <c r="A92" s="5" t="n"/>
+      <c r="B92" s="5" t="inlineStr">
         <is>
           <t>Chấm điểm tài xế (scoring)</t>
         </is>
       </c>
-      <c r="C91" s="5" t="inlineStr">
+      <c r="C92" s="5" t="inlineStr">
         <is>
           <t>1 bảng</t>
         </is>
       </c>
-      <c r="D91" s="5" t="n"/>
-      <c r="E91" s="5" t="n"/>
-      <c r="F91" s="5" t="n"/>
-      <c r="G91" s="5" t="inlineStr">
+      <c r="D92" s="5" t="n"/>
+      <c r="E92" s="5" t="n"/>
+      <c r="F92" s="5" t="n"/>
+      <c r="G92" s="5" t="inlineStr">
         <is>
           <t>Chấm điểm an toàn cho tài xế từ hành vi lái xe.
 • Mỗi tuần, mỗi tài xế có một điểm, tính từ dữ liệu vận hành của xe họ lái.</t>
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" s="6" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="B92" s="6" t="inlineStr">
+    <row r="93">
+      <c r="A93" s="6" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="B93" s="6" t="inlineStr">
         <is>
           <t>Chấm điểm tài xế (scoring)</t>
         </is>
       </c>
-      <c r="C92" s="7" t="inlineStr">
+      <c r="C93" s="7" t="inlineStr">
         <is>
           <t>driver_scores</t>
         </is>
       </c>
-      <c r="D92" s="7" t="inlineStr">
+      <c r="D93" s="7" t="inlineStr">
         <is>
           <t>Điểm tài xế</t>
         </is>
       </c>
-      <c r="E92" s="6" t="inlineStr">
+      <c r="E93" s="6" t="inlineStr">
         <is>
           <t>Khách hàng</t>
         </is>
       </c>
-      <c r="F92" s="6" t="inlineStr">
+      <c r="F93" s="6" t="inlineStr">
         <is>
           <t>F-K1</t>
         </is>
       </c>
-      <c r="G92" s="6" t="inlineStr">
+      <c r="G93" s="6" t="inlineStr">
         <is>
           <t>Điểm an toàn hằng tuần của tài xế, tính từ dữ liệu vận hành xe.</t>
         </is>
       </c>
-      <c r="H92" s="6" t="n">
+      <c r="H93" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="I92" s="7" t="inlineStr">
+      <c r="I93" s="7" t="inlineStr">
         <is>
           <t>→ Mở</t>
         </is>
       </c>
     </row>
-    <row r="93" ht="27" customHeight="1">
-      <c r="A93" s="5" t="n"/>
-      <c r="B93" s="5" t="inlineStr">
+    <row r="94" ht="27" customHeight="1">
+      <c r="A94" s="5" t="n"/>
+      <c r="B94" s="5" t="inlineStr">
         <is>
           <t>Chưa phân miền (unassigned)</t>
         </is>
       </c>
-      <c r="C93" s="5" t="inlineStr">
+      <c r="C94" s="5" t="inlineStr">
         <is>
           <t>2 bảng</t>
         </is>
       </c>
-      <c r="D93" s="5" t="n"/>
-      <c r="E93" s="5" t="n"/>
-      <c r="F93" s="5" t="n"/>
-      <c r="G93" s="5" t="inlineStr">
+      <c r="D94" s="5" t="n"/>
+      <c r="E94" s="5" t="n"/>
+      <c r="F94" s="5" t="n"/>
+      <c r="G94" s="5" t="inlineStr">
         <is>
           <t>Các tính năng chưa được quyết định thuộc miền nghiệp vụ nào (xem feature-list.md).</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="6" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="B94" s="6" t="inlineStr">
-        <is>
-          <t>Chưa phân miền (unassigned)</t>
-        </is>
-      </c>
-      <c r="C94" s="7" t="inlineStr">
-        <is>
-          <t>promotion_campaigns</t>
-        </is>
-      </c>
-      <c r="D94" s="7" t="inlineStr">
-        <is>
-          <t>Chiến dịch khuyến mãi</t>
-        </is>
-      </c>
-      <c r="E94" s="6" t="inlineStr">
-        <is>
-          <t>Nội bộ</t>
-        </is>
-      </c>
-      <c r="F94" s="6" t="inlineStr">
-        <is>
-          <t>F-F4</t>
-        </is>
-      </c>
-      <c r="G94" s="6" t="inlineStr">
-        <is>
-          <t>Một chiến dịch nhắc bảo dưỡng hoặc khuyến mãi.</t>
-        </is>
-      </c>
-      <c r="H94" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="I94" s="7" t="inlineStr">
-        <is>
-          <t>→ Mở</t>
         </is>
       </c>
     </row>
@@ -4406,294 +4408,339 @@
       </c>
       <c r="C95" s="7" t="inlineStr">
         <is>
+          <t>promotion_campaigns</t>
+        </is>
+      </c>
+      <c r="D95" s="7" t="inlineStr">
+        <is>
+          <t>Chiến dịch khuyến mãi</t>
+        </is>
+      </c>
+      <c r="E95" s="6" t="inlineStr">
+        <is>
+          <t>Nội bộ</t>
+        </is>
+      </c>
+      <c r="F95" s="6" t="inlineStr">
+        <is>
+          <t>F-F4</t>
+        </is>
+      </c>
+      <c r="G95" s="6" t="inlineStr">
+        <is>
+          <t>Một chiến dịch nhắc bảo dưỡng hoặc khuyến mãi.</t>
+        </is>
+      </c>
+      <c r="H95" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="I95" s="7" t="inlineStr">
+        <is>
+          <t>→ Mở</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="6" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="B96" s="6" t="inlineStr">
+        <is>
+          <t>Chưa phân miền (unassigned)</t>
+        </is>
+      </c>
+      <c r="C96" s="7" t="inlineStr">
+        <is>
           <t>trips</t>
         </is>
       </c>
-      <c r="D95" s="7" t="inlineStr">
+      <c r="D96" s="7" t="inlineStr">
         <is>
           <t>Chuyến đi</t>
         </is>
       </c>
-      <c r="E95" s="6" t="inlineStr">
+      <c r="E96" s="6" t="inlineStr">
         <is>
           <t>Khách hàng</t>
         </is>
       </c>
-      <c r="F95" s="6" t="inlineStr">
+      <c r="F96" s="6" t="inlineStr">
         <is>
           <t>F-A9</t>
         </is>
       </c>
-      <c r="G95" s="6" t="inlineStr">
+      <c r="G96" s="6" t="inlineStr">
         <is>
           <t>Một chuyến đi của xe. F-A9 đang tạm dừng: chưa có khái niệm chuyến đi.</t>
         </is>
       </c>
-      <c r="H95" s="6" t="n">
+      <c r="H96" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="I95" s="7" t="inlineStr">
+      <c r="I96" s="7" t="inlineStr">
         <is>
           <t>→ Mở</t>
         </is>
       </c>
     </row>
-    <row r="96"/>
-    <row r="97" ht="27" customHeight="1">
-      <c r="A97" s="4" t="inlineStr">
+    <row r="97"/>
+    <row r="98" ht="27" customHeight="1">
+      <c r="A98" s="4" t="inlineStr">
         <is>
           <t>Chú giải</t>
         </is>
       </c>
-      <c r="B97" s="4" t="inlineStr">
+      <c r="B98" s="4" t="inlineStr">
         <is>
           <t>Ý nghĩa</t>
         </is>
       </c>
     </row>
-    <row r="98" ht="108" customHeight="1">
-      <c r="A98" s="6" t="inlineStr">
+    <row r="99" ht="108" customHeight="1">
+      <c r="A99" s="6" t="inlineStr">
         <is>
           <t>Chủ sở hữu dữ liệu: Khách hàng</t>
         </is>
       </c>
-      <c r="B98" s="6" t="inlineStr">
+      <c r="B99" s="6" t="inlineStr">
         <is>
           <t>Thuộc về một tổ chức (thường là khách hàng; công ty G3 cũng có thể sở hữu); có cột organization_id hoặc lấy qua bảng cha (DM-24).</t>
-        </is>
-      </c>
-    </row>
-    <row r="99" ht="94.5" customHeight="1">
-      <c r="A99" s="6" t="inlineStr">
-        <is>
-          <t>Chủ sở hữu dữ liệu: Nội bộ</t>
-        </is>
-      </c>
-      <c r="B99" s="6" t="inlineStr">
-        <is>
-          <t>Dữ liệu của chính chúng ta (đơn vị vận hành nền tảng), dùng chung cho mọi tổ chức.</t>
         </is>
       </c>
     </row>
     <row r="100" ht="94.5" customHeight="1">
       <c r="A100" s="6" t="inlineStr">
         <is>
+          <t>Chủ sở hữu dữ liệu: Nội bộ</t>
+        </is>
+      </c>
+      <c r="B100" s="6" t="inlineStr">
+        <is>
+          <t>Dữ liệu của chính chúng ta (đơn vị vận hành nền tảng), dùng chung cho mọi tổ chức.</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="94.5" customHeight="1">
+      <c r="A101" s="6" t="inlineStr">
+        <is>
           <t>Chủ sở hữu dữ liệu: Hai bên</t>
         </is>
       </c>
-      <c r="B100" s="6" t="inlineStr">
+      <c r="B101" s="6" t="inlineStr">
         <is>
           <t>Tài sản của G3 được khách hàng sử dụng; cả hai bên cùng liên quan.</t>
         </is>
       </c>
     </row>
-    <row r="101" ht="121.5" customHeight="1">
-      <c r="A101" s="6" t="inlineStr">
+    <row r="102" ht="121.5" customHeight="1">
+      <c r="A102" s="6" t="inlineStr">
         <is>
           <t>Chủ sở hữu dữ liệu: Chưa quyết định</t>
         </is>
       </c>
-      <c r="B101" s="6" t="inlineStr">
+      <c r="B102" s="6" t="inlineStr">
         <is>
           <t>Đang chờ một quyết định còn mở (xem cuối trang).</t>
         </is>
       </c>
     </row>
-    <row r="102" ht="81" customHeight="1">
-      <c r="A102" s="6" t="inlineStr">
+    <row r="103" ht="81" customHeight="1">
+      <c r="A103" s="6" t="inlineStr">
         <is>
           <t>Miền nghiệp vụ (domain)</t>
         </is>
       </c>
-      <c r="B102" s="6" t="inlineStr">
+      <c r="B103" s="6" t="inlineStr">
         <is>
           <t>Một phần của hệ thống sở hữu dữ liệu riêng, ví dụ Xe, Trạm sạc, Thanh toán. Mỗi miền gồm một hoặc nhiều bảng.</t>
         </is>
       </c>
     </row>
-    <row r="103" ht="54" customHeight="1">
-      <c r="A103" s="6" t="inlineStr">
+    <row r="104" ht="54" customHeight="1">
+      <c r="A104" s="6" t="inlineStr">
         <is>
           <t>Bảng</t>
         </is>
       </c>
-      <c r="B103" s="6" t="inlineStr">
+      <c r="B104" s="6" t="inlineStr">
         <is>
           <t>Một loại dữ liệu được lưu, ví dụ Xe hoặc Phiên sạc. Mỗi bảng có một sheet riêng liệt kê từng cột.</t>
         </is>
       </c>
     </row>
-    <row r="104" ht="40.5" customHeight="1">
-      <c r="A104" s="6" t="inlineStr">
+    <row r="105" ht="40.5" customHeight="1">
+      <c r="A105" s="6" t="inlineStr">
         <is>
           <t>Tính năng</t>
         </is>
       </c>
-      <c r="B104" s="6" t="inlineStr">
+      <c r="B105" s="6" t="inlineStr">
         <is>
           <t>Mã tính năng trong danh sách tính năng (feature-list.md), ví dụ F-B2.</t>
         </is>
       </c>
     </row>
-    <row r="105" ht="67.5" customHeight="1">
-      <c r="A105" s="6" t="inlineStr">
+    <row r="106" ht="67.5" customHeight="1">
+      <c r="A106" s="6" t="inlineStr">
         <is>
           <t>PK / FK / UQ</t>
         </is>
       </c>
-      <c r="B105" s="6" t="inlineStr">
+      <c r="B106" s="6" t="inlineStr">
         <is>
           <t>PK: khóa chính (định danh duy nhất của dòng). FK: khóa ngoại (trỏ tới dòng của bảng khác). UQ: giá trị không được trùng.</t>
         </is>
       </c>
     </row>
-    <row r="106" ht="54" customHeight="1">
-      <c r="A106" s="6" t="inlineStr">
+    <row r="107" ht="54" customHeight="1">
+      <c r="A107" s="6" t="inlineStr">
         <is>
           <t>Ví dụ</t>
         </is>
       </c>
-      <c r="B106" s="6" t="inlineStr">
+      <c r="B107" s="6" t="inlineStr">
         <is>
           <t>Giá trị mẫu. Các mã ví dụ khớp nhau giữa các bảng, nên có thể lần theo một bản ghi mẫu qua nhiều sheet.</t>
         </is>
       </c>
     </row>
-    <row r="107" ht="40.5" customHeight="1">
-      <c r="A107" s="6" t="inlineStr">
+    <row r="108" ht="40.5" customHeight="1">
+      <c r="A108" s="6" t="inlineStr">
         <is>
           <t>NULL</t>
         </is>
       </c>
-      <c r="B107" s="6" t="inlineStr">
+      <c r="B108" s="6" t="inlineStr">
         <is>
           <t>Ô không có giá trị. Ý nghĩa của NULL được giải thích trong cột Ý nghĩa.</t>
         </is>
       </c>
     </row>
-    <row r="108" ht="81" customHeight="1">
-      <c r="A108" s="6" t="inlineStr">
+    <row r="109" ht="81" customHeight="1">
+      <c r="A109" s="6" t="inlineStr">
         <is>
           <t>🔍 Lưu lịch sử</t>
         </is>
       </c>
-      <c r="B108" s="6" t="inlineStr">
+      <c r="B109" s="6" t="inlineStr">
         <is>
           <t>Cột được theo dõi: khi cột này thay đổi, toàn bộ dòng cũ được chép sang bảng lịch sử (tên kết thúc bằng _history) kèm thời điểm và người thay đổi.</t>
         </is>
       </c>
     </row>
-    <row r="109"/>
-    <row r="110">
-      <c r="A110" s="8" t="inlineStr">
+    <row r="110"/>
+    <row r="111">
+      <c r="A111" s="8" t="inlineStr">
         <is>
           <t>Các view (giai đoạn đọc từ lịch sử)</t>
         </is>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" s="4" t="inlineStr">
+    <row r="112">
+      <c r="A112" s="4" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="B111" s="4" t="inlineStr">
+      <c r="B112" s="4" t="inlineStr">
         <is>
           <t>Mỗi dòng là</t>
         </is>
       </c>
-      <c r="C111" s="4" t="inlineStr">
+      <c r="C112" s="4" t="inlineStr">
         <is>
           <t>Các cột</t>
         </is>
       </c>
-      <c r="D111" s="4" t="inlineStr">
+      <c r="D112" s="4" t="inlineStr">
         <is>
           <t>Được dùng bởi</t>
-        </is>
-      </c>
-    </row>
-    <row r="112" ht="94.5" customHeight="1">
-      <c r="A112" s="6" t="inlineStr">
-        <is>
-          <t>vehicle_ownership_periods</t>
-        </is>
-      </c>
-      <c r="B112" s="6" t="inlineStr">
-        <is>
-          <t>một giai đoạn xe thuộc một chủ</t>
-        </is>
-      </c>
-      <c r="C112" s="6" t="inlineStr">
-        <is>
-          <t>vehicle_id, organization_id, owned_from, owned_until (NULL với chủ hiện tại)</t>
-        </is>
-      </c>
-      <c r="D112" s="6" t="inlineStr">
-        <is>
-          <t>lịch sử sở hữu và ngày bàn giao đầu tiên (VEH-02), "ngày đó xe của ai"</t>
         </is>
       </c>
     </row>
     <row r="113" ht="94.5" customHeight="1">
       <c r="A113" s="6" t="inlineStr">
         <is>
+          <t>vehicle_ownership_periods</t>
+        </is>
+      </c>
+      <c r="B113" s="6" t="inlineStr">
+        <is>
+          <t>một giai đoạn xe thuộc một chủ</t>
+        </is>
+      </c>
+      <c r="C113" s="6" t="inlineStr">
+        <is>
+          <t>vehicle_id, organization_id, owned_from, owned_until (NULL với chủ hiện tại)</t>
+        </is>
+      </c>
+      <c r="D113" s="6" t="inlineStr">
+        <is>
+          <t>lịch sử sở hữu và ngày bàn giao đầu tiên (VEH-02), "ngày đó xe của ai"</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="94.5" customHeight="1">
+      <c r="A114" s="6" t="inlineStr">
+        <is>
           <t>battery_installation_periods</t>
         </is>
       </c>
-      <c r="B113" s="6" t="inlineStr">
+      <c r="B114" s="6" t="inlineStr">
         <is>
           <t>một lần pin nằm trên một xe</t>
         </is>
       </c>
-      <c r="C113" s="6" t="inlineStr">
+      <c r="C114" s="6" t="inlineStr">
         <is>
           <t>battery_id, vehicle_id, installed_from, installed_until (NULL khi đang lắp)</t>
         </is>
       </c>
-      <c r="D113" s="6" t="inlineStr">
+      <c r="D114" s="6" t="inlineStr">
         <is>
           <t>lịch sử sức khỏe pin qua các xe (MON-07), bộ đếm bảo hành pin (WAR-01)</t>
         </is>
       </c>
     </row>
-    <row r="114"/>
-    <row r="115">
-      <c r="A115" s="8" t="inlineStr">
+    <row r="115"/>
+    <row r="116">
+      <c r="A116" s="8" t="inlineStr">
         <is>
           <t>Các quyết định còn mở</t>
         </is>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" s="4" t="inlineStr">
+    <row r="117">
+      <c r="A117" s="4" t="inlineStr">
         <is>
           <t>Mã</t>
         </is>
       </c>
-      <c r="B116" s="4" t="inlineStr">
+      <c r="B117" s="4" t="inlineStr">
         <is>
           <t>Câu hỏi</t>
         </is>
       </c>
-      <c r="C116" s="4" t="inlineStr">
+      <c r="C117" s="4" t="inlineStr">
         <is>
           <t>Ảnh hưởng tới</t>
         </is>
       </c>
     </row>
-    <row r="117" ht="54" customHeight="1">
-      <c r="A117" s="6" t="inlineStr">
+    <row r="118" ht="54" customHeight="1">
+      <c r="A118" s="6" t="inlineStr">
         <is>
           <t>D5</t>
         </is>
       </c>
-      <c r="B117" s="6" t="inlineStr">
+      <c r="B118" s="6" t="inlineStr">
         <is>
           <t>Ai trả tiền khi tài xế của đội xe sạc: ví của tài xế, ví của đội xe, hay tùy trường hợp?</t>
         </is>
       </c>
-      <c r="C117" s="6" t="inlineStr">
+      <c r="C118" s="6" t="inlineStr">
         <is>
           <t>wallets, payments</t>
         </is>
@@ -4851,78 +4898,81 @@
     <hyperlink ref="C64" location="'charging_ocpp_messages'!A1"/>
     <hyperlink ref="D64" location="'charging_ocpp_messages'!A1"/>
     <hyperlink ref="I64" location="'charging_ocpp_messages'!A1"/>
-    <hyperlink ref="C65" location="'charging_station_config_entries'!A1"/>
-    <hyperlink ref="D65" location="'charging_station_config_entries'!A1"/>
-    <hyperlink ref="I65" location="'charging_station_config_entries'!A1"/>
-    <hyperlink ref="C67" location="'charging_sessions'!A1"/>
-    <hyperlink ref="D67" location="'charging_sessions'!A1"/>
-    <hyperlink ref="I67" location="'charging_sessions'!A1"/>
-    <hyperlink ref="C68" location="'charging_session_events'!A1"/>
-    <hyperlink ref="D68" location="'charging_session_events'!A1"/>
-    <hyperlink ref="I68" location="'charging_session_events'!A1"/>
-    <hyperlink ref="C69" location="'charging_session_measurements'!A1"/>
-    <hyperlink ref="D69" location="'charging_session_measurements'!A1"/>
-    <hyperlink ref="I69" location="'charging_session_measurements'!A1"/>
-    <hyperlink ref="C71" location="'notifications'!A1"/>
-    <hyperlink ref="D71" location="'notifications'!A1"/>
-    <hyperlink ref="I71" location="'notifications'!A1"/>
-    <hyperlink ref="C73" location="'support_cases'!A1"/>
-    <hyperlink ref="D73" location="'support_cases'!A1"/>
-    <hyperlink ref="I73" location="'support_cases'!A1"/>
-    <hyperlink ref="C74" location="'repair_partners'!A1"/>
-    <hyperlink ref="D74" location="'repair_partners'!A1"/>
-    <hyperlink ref="I74" location="'repair_partners'!A1"/>
-    <hyperlink ref="C75" location="'maintenance_bookings'!A1"/>
-    <hyperlink ref="D75" location="'maintenance_bookings'!A1"/>
-    <hyperlink ref="I75" location="'maintenance_bookings'!A1"/>
-    <hyperlink ref="C77" location="'charging_policies'!A1"/>
-    <hyperlink ref="D77" location="'charging_policies'!A1"/>
-    <hyperlink ref="I77" location="'charging_policies'!A1"/>
-    <hyperlink ref="C78" location="'charging_policy_versions'!A1"/>
-    <hyperlink ref="D78" location="'charging_policy_versions'!A1"/>
-    <hyperlink ref="I78" location="'charging_policy_versions'!A1"/>
-    <hyperlink ref="C79" location="'charging_policy_assignments'!A1"/>
-    <hyperlink ref="D79" location="'charging_policy_assignments'!A1"/>
-    <hyperlink ref="I79" location="'charging_policy_assignments'!A1"/>
-    <hyperlink ref="C80" location="'policy_violations'!A1"/>
-    <hyperlink ref="D80" location="'policy_violations'!A1"/>
-    <hyperlink ref="I80" location="'policy_violations'!A1"/>
-    <hyperlink ref="C82" location="'tariffs'!A1"/>
-    <hyperlink ref="D82" location="'tariffs'!A1"/>
-    <hyperlink ref="I82" location="'tariffs'!A1"/>
-    <hyperlink ref="C83" location="'payments'!A1"/>
-    <hyperlink ref="D83" location="'payments'!A1"/>
-    <hyperlink ref="I83" location="'payments'!A1"/>
-    <hyperlink ref="C84" location="'wallets'!A1"/>
-    <hyperlink ref="D84" location="'wallets'!A1"/>
-    <hyperlink ref="I84" location="'wallets'!A1"/>
-    <hyperlink ref="C85" location="'wallet_transactions'!A1"/>
-    <hyperlink ref="D85" location="'wallet_transactions'!A1"/>
-    <hyperlink ref="I85" location="'wallet_transactions'!A1"/>
-    <hyperlink ref="C86" location="'invoices'!A1"/>
-    <hyperlink ref="D86" location="'invoices'!A1"/>
-    <hyperlink ref="I86" location="'invoices'!A1"/>
-    <hyperlink ref="C87" location="'invoice_lines'!A1"/>
-    <hyperlink ref="D87" location="'invoice_lines'!A1"/>
-    <hyperlink ref="I87" location="'invoice_lines'!A1"/>
-    <hyperlink ref="C88" location="'subscription_plans'!A1"/>
-    <hyperlink ref="D88" location="'subscription_plans'!A1"/>
-    <hyperlink ref="I88" location="'subscription_plans'!A1"/>
-    <hyperlink ref="C89" location="'plan_features'!A1"/>
-    <hyperlink ref="D89" location="'plan_features'!A1"/>
-    <hyperlink ref="I89" location="'plan_features'!A1"/>
-    <hyperlink ref="C90" location="'subscriptions'!A1"/>
-    <hyperlink ref="D90" location="'subscriptions'!A1"/>
-    <hyperlink ref="I90" location="'subscriptions'!A1"/>
-    <hyperlink ref="C92" location="'driver_scores'!A1"/>
-    <hyperlink ref="D92" location="'driver_scores'!A1"/>
-    <hyperlink ref="I92" location="'driver_scores'!A1"/>
-    <hyperlink ref="C94" location="'promotion_campaigns'!A1"/>
-    <hyperlink ref="D94" location="'promotion_campaigns'!A1"/>
-    <hyperlink ref="I94" location="'promotion_campaigns'!A1"/>
-    <hyperlink ref="C95" location="'trips'!A1"/>
-    <hyperlink ref="D95" location="'trips'!A1"/>
-    <hyperlink ref="I95" location="'trips'!A1"/>
+    <hyperlink ref="C65" location="'charging_station_config_capture'!A1"/>
+    <hyperlink ref="D65" location="'charging_station_config_capture'!A1"/>
+    <hyperlink ref="I65" location="'charging_station_config_capture'!A1"/>
+    <hyperlink ref="C66" location="'charging_station_config_entries'!A1"/>
+    <hyperlink ref="D66" location="'charging_station_config_entries'!A1"/>
+    <hyperlink ref="I66" location="'charging_station_config_entries'!A1"/>
+    <hyperlink ref="C68" location="'charging_sessions'!A1"/>
+    <hyperlink ref="D68" location="'charging_sessions'!A1"/>
+    <hyperlink ref="I68" location="'charging_sessions'!A1"/>
+    <hyperlink ref="C69" location="'charging_session_events'!A1"/>
+    <hyperlink ref="D69" location="'charging_session_events'!A1"/>
+    <hyperlink ref="I69" location="'charging_session_events'!A1"/>
+    <hyperlink ref="C70" location="'charging_session_measurements'!A1"/>
+    <hyperlink ref="D70" location="'charging_session_measurements'!A1"/>
+    <hyperlink ref="I70" location="'charging_session_measurements'!A1"/>
+    <hyperlink ref="C72" location="'notifications'!A1"/>
+    <hyperlink ref="D72" location="'notifications'!A1"/>
+    <hyperlink ref="I72" location="'notifications'!A1"/>
+    <hyperlink ref="C74" location="'support_cases'!A1"/>
+    <hyperlink ref="D74" location="'support_cases'!A1"/>
+    <hyperlink ref="I74" location="'support_cases'!A1"/>
+    <hyperlink ref="C75" location="'repair_partners'!A1"/>
+    <hyperlink ref="D75" location="'repair_partners'!A1"/>
+    <hyperlink ref="I75" location="'repair_partners'!A1"/>
+    <hyperlink ref="C76" location="'maintenance_bookings'!A1"/>
+    <hyperlink ref="D76" location="'maintenance_bookings'!A1"/>
+    <hyperlink ref="I76" location="'maintenance_bookings'!A1"/>
+    <hyperlink ref="C78" location="'charging_policies'!A1"/>
+    <hyperlink ref="D78" location="'charging_policies'!A1"/>
+    <hyperlink ref="I78" location="'charging_policies'!A1"/>
+    <hyperlink ref="C79" location="'charging_policy_versions'!A1"/>
+    <hyperlink ref="D79" location="'charging_policy_versions'!A1"/>
+    <hyperlink ref="I79" location="'charging_policy_versions'!A1"/>
+    <hyperlink ref="C80" location="'charging_policy_assignments'!A1"/>
+    <hyperlink ref="D80" location="'charging_policy_assignments'!A1"/>
+    <hyperlink ref="I80" location="'charging_policy_assignments'!A1"/>
+    <hyperlink ref="C81" location="'policy_violations'!A1"/>
+    <hyperlink ref="D81" location="'policy_violations'!A1"/>
+    <hyperlink ref="I81" location="'policy_violations'!A1"/>
+    <hyperlink ref="C83" location="'tariffs'!A1"/>
+    <hyperlink ref="D83" location="'tariffs'!A1"/>
+    <hyperlink ref="I83" location="'tariffs'!A1"/>
+    <hyperlink ref="C84" location="'payments'!A1"/>
+    <hyperlink ref="D84" location="'payments'!A1"/>
+    <hyperlink ref="I84" location="'payments'!A1"/>
+    <hyperlink ref="C85" location="'wallets'!A1"/>
+    <hyperlink ref="D85" location="'wallets'!A1"/>
+    <hyperlink ref="I85" location="'wallets'!A1"/>
+    <hyperlink ref="C86" location="'wallet_transactions'!A1"/>
+    <hyperlink ref="D86" location="'wallet_transactions'!A1"/>
+    <hyperlink ref="I86" location="'wallet_transactions'!A1"/>
+    <hyperlink ref="C87" location="'invoices'!A1"/>
+    <hyperlink ref="D87" location="'invoices'!A1"/>
+    <hyperlink ref="I87" location="'invoices'!A1"/>
+    <hyperlink ref="C88" location="'invoice_lines'!A1"/>
+    <hyperlink ref="D88" location="'invoice_lines'!A1"/>
+    <hyperlink ref="I88" location="'invoice_lines'!A1"/>
+    <hyperlink ref="C89" location="'subscription_plans'!A1"/>
+    <hyperlink ref="D89" location="'subscription_plans'!A1"/>
+    <hyperlink ref="I89" location="'subscription_plans'!A1"/>
+    <hyperlink ref="C90" location="'plan_features'!A1"/>
+    <hyperlink ref="D90" location="'plan_features'!A1"/>
+    <hyperlink ref="I90" location="'plan_features'!A1"/>
+    <hyperlink ref="C91" location="'subscriptions'!A1"/>
+    <hyperlink ref="D91" location="'subscriptions'!A1"/>
+    <hyperlink ref="I91" location="'subscriptions'!A1"/>
+    <hyperlink ref="C93" location="'driver_scores'!A1"/>
+    <hyperlink ref="D93" location="'driver_scores'!A1"/>
+    <hyperlink ref="I93" location="'driver_scores'!A1"/>
+    <hyperlink ref="C95" location="'promotion_campaigns'!A1"/>
+    <hyperlink ref="D95" location="'promotion_campaigns'!A1"/>
+    <hyperlink ref="I95" location="'promotion_campaigns'!A1"/>
+    <hyperlink ref="C96" location="'trips'!A1"/>
+    <hyperlink ref="D96" location="'trips'!A1"/>
+    <hyperlink ref="I96" location="'trips'!A1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -28453,7 +28503,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I55"/>
+  <dimension ref="A1:I56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -29740,11 +29790,11 @@
         </is>
       </c>
     </row>
-    <row r="53">
+    <row r="53" ht="27" customHeight="1">
       <c r="A53" s="6" t="n"/>
       <c r="B53" s="7" t="inlineStr">
         <is>
-          <t>charging_sessions</t>
+          <t>charging_station_configuration_captures</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
@@ -29757,7 +29807,7 @@
       <c r="A54" s="6" t="n"/>
       <c r="B54" s="7" t="inlineStr">
         <is>
-          <t>tariffs</t>
+          <t>charging_sessions</t>
         </is>
       </c>
       <c r="C54" s="6" t="inlineStr">
@@ -29770,10 +29820,23 @@
       <c r="A55" s="6" t="n"/>
       <c r="B55" s="7" t="inlineStr">
         <is>
+          <t>tariffs</t>
+        </is>
+      </c>
+      <c r="C55" s="6" t="inlineStr">
+        <is>
+          <t>station_id</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="6" t="n"/>
+      <c r="B56" s="7" t="inlineStr">
+        <is>
           <t>charging_station_history</t>
         </is>
       </c>
-      <c r="C55" s="6" t="inlineStr">
+      <c r="C56" s="6" t="inlineStr">
         <is>
           <t>station_id</t>
         </is>
@@ -29791,9 +29854,10 @@
     <hyperlink ref="B50" location="'charging_evses'!A1"/>
     <hyperlink ref="B51" location="'charging_ocpp_messages'!A1"/>
     <hyperlink ref="B52" location="'charging_station_config_entries'!A1"/>
-    <hyperlink ref="B53" location="'charging_sessions'!A1"/>
-    <hyperlink ref="B54" location="'tariffs'!A1"/>
-    <hyperlink ref="B55" location="'charging_station_history'!A1"/>
+    <hyperlink ref="B53" location="'charging_station_config_capture'!A1"/>
+    <hyperlink ref="B54" location="'charging_sessions'!A1"/>
+    <hyperlink ref="B55" location="'tariffs'!A1"/>
+    <hyperlink ref="B56" location="'charging_station_history'!A1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -34624,7 +34688,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -34751,7 +34815,7 @@
       </c>
       <c r="I7" s="6" t="n"/>
     </row>
-    <row r="8" ht="27" customHeight="1">
+    <row r="8" ht="81" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>2</v>
       </c>
@@ -34778,7 +34842,7 @@
       <c r="F8" s="6" t="n"/>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>Thời điểm nhận hoặc gửi bản tin; cột thời gian của bảng chuỗi thời gian.</t>
+          <t>Đồng hồ của máy chủ: thời điểm cổng OCPP nhận bản tin (CP_TO_CSMS) hoặc gửi đi (CSMS_TO_CP); cột thời gian của bảng chuỗi thời gian. Thời gian riêng của trụ nằm trong nội dung một số bản tin và được ghi vào các bảng đã diễn giải, nên bản tin gửi lại sau khi mất kết nối có thời điểm đến ở đây và thời điểm thực ở đó (CS-18).</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr">
@@ -34928,80 +34992,194 @@
       </c>
       <c r="I12" s="6" t="n"/>
     </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" s="4" t="n"/>
-      <c r="B14" s="4" t="inlineStr">
+    <row r="13" ht="54" customHeight="1">
+      <c r="A13" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>action</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>varchar(50)</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="n"/>
+      <c r="F13" s="6" t="n"/>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>Loại bản tin chép từ phần bao của một yêu cầu, ví dụ StatusNotification, RemoteStartTransaction; NULL với bản tin trả lời và báo lỗi (không có action) và với bản tin không đọc được. raw_frame vẫn là bản gốc.</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>StatusNotification</t>
+        </is>
+      </c>
+      <c r="I13" s="6" t="n"/>
+    </row>
+    <row r="14" ht="81" customHeight="1">
+      <c r="A14" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>ocpp_message_id</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>varchar(36)</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="n"/>
+      <c r="F14" s="6" t="n"/>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>Mã bản tin riêng trong phần bao, có ở mọi bản tin; yêu cầu và câu trả lời dùng chung mã này, nên (station_id, ocpp_message_id) ghép được chúng, ví dụ lệnh RemoteStartTransaction của chúng ta với câu trả lời Accepted của trụ. NULL với bản tin không đọc được. Không duy nhất: trụ và cổng OCPP đánh số yêu cầu riêng.</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>19223201</t>
+        </is>
+      </c>
+      <c r="I14" s="6" t="n"/>
+    </row>
+    <row r="15"/>
+    <row r="16">
+      <c r="A16" s="4" t="n"/>
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>Kiểu enum</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C16" s="4" t="inlineStr">
         <is>
           <t>Giá trị cho phép</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="27" customHeight="1">
-      <c r="A15" s="6" t="n"/>
-      <c r="B15" s="6" t="inlineStr">
+    <row r="17" ht="27" customHeight="1">
+      <c r="A17" s="6" t="n"/>
+      <c r="B17" s="6" t="inlineStr">
         <is>
           <t>chargingocppmessagedirection</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr">
+      <c r="C17" s="6" t="inlineStr">
         <is>
           <t>CP_TO_CSMS, CSMS_TO_CP</t>
         </is>
       </c>
     </row>
-    <row r="16"/>
-    <row r="17">
-      <c r="A17" s="4" t="n"/>
-      <c r="B17" s="4" t="inlineStr">
+    <row r="18"/>
+    <row r="19">
+      <c r="A19" s="4" t="n"/>
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>Chỉ mục (index)</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C19" s="4" t="inlineStr">
         <is>
           <t>Các cột</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="D19" s="4" t="inlineStr">
         <is>
           <t>Duy nhất</t>
         </is>
       </c>
-      <c r="E17" s="4" t="n"/>
-      <c r="F17" s="4" t="inlineStr">
+      <c r="E19" s="4" t="n"/>
+      <c r="F19" s="4" t="inlineStr">
         <is>
           <t>Ghi chú</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="27" customHeight="1">
-      <c r="A18" s="6" t="n"/>
-      <c r="B18" s="6" t="inlineStr">
+    <row r="20" ht="27" customHeight="1">
+      <c r="A20" s="6" t="n"/>
+      <c r="B20" s="6" t="inlineStr">
         <is>
           <t>ix_charging_ocpp_messages_station_time</t>
         </is>
       </c>
-      <c r="C18" s="6" t="inlineStr">
+      <c r="C20" s="6" t="inlineStr">
         <is>
           <t>station_id, occurred_at</t>
         </is>
       </c>
-      <c r="D18" s="6" t="inlineStr">
+      <c r="D20" s="6" t="inlineStr">
         <is>
           <t>không</t>
         </is>
       </c>
-      <c r="E18" s="6" t="n"/>
-      <c r="F18" s="6" t="n"/>
+      <c r="E20" s="6" t="n"/>
+      <c r="F20" s="6" t="n"/>
+    </row>
+    <row r="21" ht="27" customHeight="1">
+      <c r="A21" s="6" t="n"/>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>ix_charging_ocpp_messages_station_action_time</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>station_id, action, occurred_at</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="n"/>
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t>Planned (CS-18): the message viewer filtering by type (STN-15)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="27" customHeight="1">
+      <c r="A22" s="6" t="n"/>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>ix_charging_ocpp_messages_station_message_id</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>station_id, ocpp_message_id</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="n"/>
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t>Planned (CS-18): pairing a request with its answer</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A6:I12"/>
+  <autoFilter ref="A6:I14"/>
   <hyperlinks>
     <hyperlink ref="A2" location="'Tổng quan'!A1"/>
     <hyperlink ref="F9" location="'charging_stations'!A1"/>
@@ -35016,7 +35194,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -35033,7 +35211,7 @@
     <row r="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>36. charging_station_configuration_entries: Cấu hình trụ sạc</t>
+          <t>36. charging_station_configuration_captures: Lần chụp cấu hình trụ</t>
         </is>
       </c>
     </row>
@@ -35054,7 +35232,7 @@
     <row r="4">
       <c r="A4" s="11" t="inlineStr">
         <is>
-          <t>Một khóa cấu hình trong câu trả lời GetConfiguration của trụ sạc (các bản chụp chỉ ghi thêm).</t>
+          <t>Một lần chụp cấu hình của trụ sạc: một câu trả lời GetConfiguration (1.6J) hoặc một GetBaseReport được trả lời bằng nhiều phần NotifyReport (2.0.1). Các cấu hình nằm ở charging_station_configuration_entries. Chỉ ghi thêm: cấu hình hiện tại là lần chụp COMPLETE mới nhất, so hai lần chụp cho biết những gì đã đổi (CS-19). Đổi một cấu hình là lệnh gửi xuống trụ, không phải một lần chụp.</t>
         </is>
       </c>
     </row>
@@ -35112,7 +35290,7 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>entry_id</t>
+          <t>capture_id</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
@@ -35133,12 +35311,12 @@
       <c r="F7" s="6" t="n"/>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>Mã nội bộ của dòng.</t>
+          <t>Mã nội bộ của một lần chụp cấu hình trụ sạc.</t>
         </is>
       </c>
       <c r="H7" s="6" t="inlineStr">
         <is>
-          <t>00000007-5a6b-4c7d-8e9f-0a1b2c3d4e5f</t>
+          <t>00000008-5a6b-4c7d-8e9f-0a1b2c3d4e5f</t>
         </is>
       </c>
       <c r="I7" s="6" t="n"/>
@@ -35174,7 +35352,7 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>Trạm sở hữu cấu hình.</t>
+          <t>Trụ sạc.</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr">
@@ -35184,18 +35362,18 @@
       </c>
       <c r="I8" s="6" t="n"/>
     </row>
-    <row r="9" ht="27" customHeight="1">
+    <row r="9" ht="54" customHeight="1">
       <c r="A9" s="6" t="n">
         <v>3</v>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>capture_id</t>
+          <t>reason</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>uuid</t>
+          <t>varchar(20)</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
@@ -35207,28 +35385,28 @@
       <c r="F9" s="6" t="n"/>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>Nhóm tất cả các khóa của cùng một lần trả lời GetConfiguration.</t>
+          <t>Lý do chụp. BOOT: tự động sau mỗi lần khởi động. ON_DEMAND: có người yêu cầu. AFTER_CHANGE: ngay sau khi đổi một cấu hình, để xác nhận trụ đã áp dụng (lệnh đổi chỉ trả về kết quả chấp nhận hay từ chối, không có giá trị).</t>
         </is>
       </c>
       <c r="H9" s="6" t="inlineStr">
         <is>
-          <t>00000008-5a6b-4c7d-8e9f-0a1b2c3d4e5f</t>
+          <t>BOOT</t>
         </is>
       </c>
       <c r="I9" s="6" t="n"/>
     </row>
-    <row r="10">
+    <row r="10" ht="40.5" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>4</v>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>captured_at</t>
+          <t>ocpp_protocol_version</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>timestamptz</t>
+          <t>varchar(20)</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
@@ -35240,45 +35418,45 @@
       <c r="F10" s="6" t="n"/>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>Thời điểm nhận câu trả lời từ trụ sạc.</t>
+          <t>Giao thức của kết nối mà lần chụp đến qua; cho biết các dòng cấu hình được đặt tên thế nào (1.6J: chỉ có khóa; 2.0.1: thành phần và biến).</t>
         </is>
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14T22:00:10Z</t>
+          <t>ocpp1.6</t>
         </is>
       </c>
       <c r="I10" s="6" t="n"/>
     </row>
-    <row r="11">
+    <row r="11" ht="40.5" customHeight="1">
       <c r="A11" s="6" t="n">
         <v>5</v>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>config_key</t>
+          <t>ocpp_request_id</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>varchar(100)</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>không</t>
+          <t>có</t>
         </is>
       </c>
       <c r="E11" s="6" t="n"/>
       <c r="F11" s="6" t="n"/>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>Tên khóa cấu hình.</t>
+          <t>requestId của GetBaseReport trong OCPP 2.0.1, dùng để ghép nhiều phần NotifyReport thành một lần chụp; NULL với 1.6J (một câu trả lời).</t>
         </is>
       </c>
       <c r="H11" s="6" t="inlineStr">
         <is>
-          <t>HeartbeatInterval</t>
+          <t>NULL</t>
         </is>
       </c>
       <c r="I11" s="6" t="n"/>
@@ -35289,113 +35467,150 @@
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>value</t>
+          <t>requested_at</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>timestamptz</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>có</t>
+          <t>không</t>
         </is>
       </c>
       <c r="E12" s="6" t="n"/>
       <c r="F12" s="6" t="n"/>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>Giá trị khóa dạng chuỗi; NULL nếu trụ không gửi.</t>
+          <t>Thời điểm cổng OCPP hỏi trụ.</t>
         </is>
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>2026-09-14T22:00:06Z</t>
         </is>
       </c>
       <c r="I12" s="6" t="n"/>
     </row>
-    <row r="13">
+    <row r="13" ht="27" customHeight="1">
       <c r="A13" s="6" t="n">
         <v>7</v>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>is_readonly</t>
+          <t>captured_at</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>timestamptz</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>không</t>
+          <t>có</t>
         </is>
       </c>
       <c r="E13" s="6" t="n"/>
       <c r="F13" s="6" t="n"/>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>Trụ sạc có báo khóa này là chỉ-đọc không.</t>
+          <t>Thời điểm nhận câu trả lời (2.0.1: phần cuối cùng); NULL khi đang chờ hoặc thất bại.</t>
         </is>
       </c>
       <c r="H13" s="6" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>2026-09-14T22:00:10Z</t>
         </is>
       </c>
       <c r="I13" s="6" t="n"/>
     </row>
-    <row r="14"/>
-    <row r="15">
-      <c r="A15" s="4" t="n"/>
-      <c r="B15" s="4" t="inlineStr">
+    <row r="14" ht="40.5" customHeight="1">
+      <c r="A14" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>outcome</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>varchar(20)</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="n"/>
+      <c r="F14" s="6" t="n"/>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>Kết quả quan sát được. PENDING: đã hỏi, chưa đủ. COMPLETE: đã nhận đủ. FAILED: không trả lời kịp, trả lời lỗi, hoặc thiếu phần.</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>COMPLETE</t>
+        </is>
+      </c>
+      <c r="I14" s="6" t="n"/>
+    </row>
+    <row r="15"/>
+    <row r="16">
+      <c r="A16" s="4" t="n"/>
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>Chỉ mục (index)</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C16" s="4" t="inlineStr">
         <is>
           <t>Các cột</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="D16" s="4" t="inlineStr">
         <is>
           <t>Duy nhất</t>
         </is>
       </c>
-      <c r="E15" s="4" t="n"/>
-      <c r="F15" s="4" t="inlineStr">
+      <c r="E16" s="4" t="n"/>
+      <c r="F16" s="4" t="inlineStr">
         <is>
           <t>Ghi chú</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="27" customHeight="1">
-      <c r="A16" s="6" t="n"/>
-      <c r="B16" s="6" t="inlineStr">
-        <is>
-          <t>ix_charging_config_entries_station_captured</t>
-        </is>
-      </c>
-      <c r="C16" s="6" t="inlineStr">
+    <row r="17" ht="27" customHeight="1">
+      <c r="A17" s="6" t="n"/>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>ix_charging_config_captures_station_captured</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
         <is>
           <t>station_id, captured_at</t>
         </is>
       </c>
-      <c r="D16" s="6" t="inlineStr">
+      <c r="D17" s="6" t="inlineStr">
         <is>
           <t>không</t>
         </is>
       </c>
-      <c r="E16" s="6" t="n"/>
-      <c r="F16" s="6" t="n"/>
+      <c r="E17" s="6" t="n"/>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>The latest complete snapshot of a charger</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A6:I13"/>
+  <autoFilter ref="A6:I14"/>
   <hyperlinks>
     <hyperlink ref="A2" location="'Tổng quan'!A1"/>
     <hyperlink ref="F8" location="'charging_stations'!A1"/>
@@ -35405,6 +35620,659 @@
 </file>
 
 <file path=xl/worksheets/sheet53.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="7" max="7"/>
+    <col width="42" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>37. charging_station_configuration_entries: Cấu hình trụ sạc</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t>← Tổng quan</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>Miền nghiệp vụ: Trạm sạc (charging_stations)   ·   Chủ sở hữu dữ liệu: Nội bộ   ·   Tính năng: F-G2</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>Một giá trị của một cấu hình trong một lần chụp (CS-19). Đặt tên theo cách của OCPP 2.0.1 (thành phần + biến + loại thuộc tính), cách này cũng chứa được 1.6J: khóa 1.6J là một biến không có thành phần, thuộc tính Actual, và readonly được quy đổi sang mutability. Cấu hình được lưu đúng như trụ gửi; khóa 1.6J không bị dịch sang tên 2.0.1. Chỉ ghi thêm, theo lần chụp của nó.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5"/>
+    <row r="6" ht="27" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Cột</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Kiểu dữ liệu</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Cho phép rỗng</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>Khóa</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>Tham chiếu tới</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>Ý nghĩa</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>Ví dụ</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>Lưu lịch sử</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="27" customHeight="1">
+      <c r="A7" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>entry_id</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>uuid</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="n"/>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>Mã nội bộ của dòng: một giá trị của một cấu hình trong một lần chụp.</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>00000007-5a6b-4c7d-8e9f-0a1b2c3d4e5f</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="n"/>
+    </row>
+    <row r="8" ht="27" customHeight="1">
+      <c r="A8" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>station_id</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>uuid</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>charging_stations.station_id (khi xóa: chặn xóa)</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>[Sẽ bỏ: CS-19] Trụ sạc; nay nằm ở lần chụp.</t>
+        </is>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>4b9d6f3a-2e8c-4a1b-9d5e-7f0c3a8b2d88</t>
+        </is>
+      </c>
+      <c r="I8" s="6" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>capture_id</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>uuid</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="n"/>
+      <c r="F9" s="6" t="n"/>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>Lần chụp chứa giá trị này.</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>00000008-5a6b-4c7d-8e9f-0a1b2c3d4e5f</t>
+        </is>
+      </c>
+      <c r="I9" s="6" t="n"/>
+    </row>
+    <row r="10" ht="27" customHeight="1">
+      <c r="A10" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>captured_at</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>timestamptz</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="n"/>
+      <c r="F10" s="6" t="n"/>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>[Sẽ bỏ: CS-19] Thời điểm nhận câu trả lời; nay nằm ở lần chụp.</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-14T22:00:10Z</t>
+        </is>
+      </c>
+      <c r="I10" s="6" t="n"/>
+    </row>
+    <row r="11" ht="27" customHeight="1">
+      <c r="A11" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>component_name</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>varchar(50)</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="n"/>
+      <c r="F11" s="6" t="n"/>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>Thành phần OCPP 2.0.1, ví dụ OCPPCommCtrlr, EVSE, Connector; NULL với 1.6J (chỉ có khóa).</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="I11" s="6" t="n"/>
+    </row>
+    <row r="12" ht="27" customHeight="1">
+      <c r="A12" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>component_instance</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>varchar(50)</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="n"/>
+      <c r="F12" s="6" t="n"/>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>Bản thể của thành phần khi có nhiều (2.0.1); NULL nếu không.</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="I12" s="6" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>ocpp_evse_id</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="n"/>
+      <c r="F13" s="6" t="n"/>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>EVSE chứa thành phần (2.0.1); NULL với cả trụ và với 1.6J.</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="I13" s="6" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>ocpp_connector_id</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="n"/>
+      <c r="F14" s="6" t="n"/>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>Súng chứa thành phần (2.0.1); NULL nếu không.</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="I14" s="6" t="n"/>
+    </row>
+    <row r="15" ht="40.5" customHeight="1">
+      <c r="A15" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>variable_name</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>varchar(100)</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="n"/>
+      <c r="F15" s="6" t="n"/>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>[Hiện tên là config_key, sẽ đổi tên] Cấu hình: khóa cấu hình của 1.6J (ví dụ HeartbeatInterval) hoặc biến của 2.0.1 trong thành phần của nó.</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>HeartbeatInterval</t>
+        </is>
+      </c>
+      <c r="I15" s="6" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>variable_instance</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>varchar(50)</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="n"/>
+      <c r="F16" s="6" t="n"/>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>Bản thể của biến (2.0.1); NULL nếu không.</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="I16" s="6" t="n"/>
+    </row>
+    <row r="17" ht="27" customHeight="1">
+      <c r="A17" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>attribute_type</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>varchar(10)</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="n"/>
+      <c r="F17" s="6" t="n"/>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>Giá trị nào của cấu hình: Actual (giá trị hiện tại; luôn là Actual với 1.6J), Target, MinSet hoặc MaxSet (2.0.1).</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>Actual</t>
+        </is>
+      </c>
+      <c r="I17" s="6" t="n"/>
+    </row>
+    <row r="18" ht="27" customHeight="1">
+      <c r="A18" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="n"/>
+      <c r="F18" s="6" t="n"/>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>Giá trị dạng chuỗi, đúng như trụ gửi; NULL nếu trụ không gửi (ví dụ cấu hình chỉ-ghi).</t>
+        </is>
+      </c>
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="I18" s="6" t="n"/>
+    </row>
+    <row r="19" ht="54" customHeight="1">
+      <c r="A19" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>mutability</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>varchar(10)</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="n"/>
+      <c r="F19" s="6" t="n"/>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>Cấu hình có đổi được không: READ_ONLY (lệnh đổi bị từ chối, ví dụ NumberOfConnectors), READ_WRITE, WRITE_ONLY (2.0.1, ví dụ mật khẩu: không hiện giá trị). Với 1.6J readonly=true là READ_ONLY, false là READ_WRITE.</t>
+        </is>
+      </c>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>READ_WRITE</t>
+        </is>
+      </c>
+      <c r="I19" s="6" t="n"/>
+    </row>
+    <row r="20" ht="27" customHeight="1">
+      <c r="A20" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>is_readonly</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>boolean</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="n"/>
+      <c r="F20" s="6" t="n"/>
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t>[Sẽ bỏ: CS-19] Trụ có báo khóa này là chỉ-đọc không; thay bằng mutability, bao cả 2.0.1.</t>
+        </is>
+      </c>
+      <c r="H20" s="6" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="I20" s="6" t="n"/>
+    </row>
+    <row r="21"/>
+    <row r="22">
+      <c r="A22" s="4" t="n"/>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>Chỉ mục (index)</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>Các cột</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>Duy nhất</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="n"/>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>Ghi chú</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="27" customHeight="1">
+      <c r="A23" s="6" t="n"/>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>ix_charging_config_entries_station_captured</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>station_id, captured_at</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="n"/>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>Replaced by ix_charging_config_captures_station_captured (CS-19)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="94.5" customHeight="1">
+      <c r="A24" s="6" t="n"/>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>uq_charging_config_entries_capture_setting</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>capture_id, component_name, component_instance, ocpp_evse_id, ocpp_connector_id, variable_name, variable_instance, attribute_type</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E24" s="6" t="n"/>
+      <c r="F24" s="6" t="inlineStr">
+        <is>
+          <t>Planned (CS-19): NULLS NOT DISTINCT; one value per setting and attribute in a snapshot</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A6:I20"/>
+  <hyperlinks>
+    <hyperlink ref="A2" location="'Tổng quan'!A1"/>
+    <hyperlink ref="F8" location="'charging_stations'!A1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet54.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -35427,7 +36295,7 @@
     <row r="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>37. charging_sessions: Phiên sạc</t>
+          <t>38. charging_sessions: Phiên sạc</t>
         </is>
       </c>
     </row>
@@ -35448,7 +36316,7 @@
     <row r="4">
       <c r="A4" s="11" t="inlineStr">
         <is>
-          <t>Một lần sạc trên một súng sạc, từ lúc bắt đầu đến lúc kết thúc.</t>
+          <t>Một lần sạc trên một súng sạc, từ lúc bắt đầu đến lúc kết thúc. Cần quyết định khi rà soát bảng (CS-18): lần sạc bằng QR (CO-14) cần lưu ngữ cảnh nghiệp vụ ngay khi tài xế quét (ai quét, tổ chức nào trả tiền, mã gửi trong RemoteStartTransaction, câu trả lời của trụ) để ghép với StartTransaction mang mã đó: tạo dòng phiên PENDING khi quét, một bảng các lệnh gửi xuống trụ, hoặc cả hai.</t>
         </is>
       </c>
     </row>
@@ -36475,7 +37343,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet54.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet55.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -36498,7 +37366,7 @@
     <row r="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>38. charging_session_events: Sự kiện phiên sạc</t>
+          <t>39. charging_session_events: Sự kiện phiên sạc</t>
         </is>
       </c>
     </row>
@@ -36834,7 +37702,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet55.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet56.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -36857,7 +37725,7 @@
     <row r="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>39. charging_session_measurements: Số đo phiên sạc</t>
+          <t>40. charging_session_measurements: Số đo phiên sạc</t>
         </is>
       </c>
     </row>
@@ -37298,7 +38166,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet56.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet57.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -37321,7 +38189,7 @@
     <row r="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>40. notifications: Thông báo</t>
+          <t>41. notifications: Thông báo</t>
         </is>
       </c>
     </row>
@@ -37840,7 +38708,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet57.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet58.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -37863,7 +38731,7 @@
     <row r="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>41. support_cases: Ca hỗ trợ</t>
+          <t>42. support_cases: Ca hỗ trợ</t>
         </is>
       </c>
     </row>
@@ -38946,7 +39814,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet58.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet59.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -38969,7 +39837,7 @@
     <row r="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>42. repair_partners: Đối tác sửa chữa &amp; cứu hộ</t>
+          <t>43. repair_partners: Đối tác sửa chữa &amp; cứu hộ</t>
         </is>
       </c>
     </row>
@@ -39332,373 +40200,6 @@
     <hyperlink ref="F8" location="'organizations'!A1"/>
     <hyperlink ref="B16" location="'support_cases'!A1"/>
     <hyperlink ref="B17" location="'maintenance_bookings'!A1"/>
-  </hyperlinks>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet59.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I13"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="40" customWidth="1" min="6" max="6"/>
-    <col width="60" customWidth="1" min="7" max="7"/>
-    <col width="42" customWidth="1" min="8" max="8"/>
-    <col width="11" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="9" t="inlineStr">
-        <is>
-          <t>43. maintenance_bookings: Lịch bảo dưỡng</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="10" t="inlineStr">
-        <is>
-          <t>← Tổng quan</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>Miền nghiệp vụ: CSKH &amp; cứu hộ (support)   ·   Chủ sở hữu dữ liệu: Khách hàng   ·   Tính năng: F-I3</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="11" t="inlineStr">
-        <is>
-          <t>Một lịch hẹn bảo dưỡng xe tại xưởng đối tác.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5"/>
-    <row r="6" ht="27" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>Cột</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>Kiểu dữ liệu</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>Cho phép rỗng</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>Khóa</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>Tham chiếu tới</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>Ý nghĩa</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>Ví dụ</t>
-        </is>
-      </c>
-      <c r="I6" s="4" t="inlineStr">
-        <is>
-          <t>Lưu lịch sử</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>booking_id</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>uuid</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
-      <c r="F7" s="6" t="n"/>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>Mã nội bộ của lịch hẹn.</t>
-        </is>
-      </c>
-      <c r="H7" s="6" t="inlineStr">
-        <is>
-          <t>0000000d-5a6b-4c7d-8e9f-0a1b2c3d4e5f</t>
-        </is>
-      </c>
-      <c r="I7" s="6" t="n"/>
-    </row>
-    <row r="8" ht="27" customHeight="1">
-      <c r="A8" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>organization_id</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>uuid</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E8" s="6" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="F8" s="7" t="inlineStr">
-        <is>
-          <t>organizations.organization_id (khi xóa: chặn xóa)</t>
-        </is>
-      </c>
-      <c r="G8" s="6" t="inlineStr">
-        <is>
-          <t>Tổ chức khách hàng đặt lịch.</t>
-        </is>
-      </c>
-      <c r="H8" s="6" t="inlineStr">
-        <is>
-          <t>3f6c2a1e-8b4d-4e2a-9c1f-0a7d5b2e4c11</t>
-        </is>
-      </c>
-      <c r="I8" s="6" t="n"/>
-    </row>
-    <row r="9" ht="27" customHeight="1">
-      <c r="A9" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>vehicle_id</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>uuid</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E9" s="6" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="F9" s="7" t="inlineStr">
-        <is>
-          <t>vehicles.vehicle_id (khi xóa: chặn xóa)</t>
-        </is>
-      </c>
-      <c r="G9" s="6" t="inlineStr">
-        <is>
-          <t>Xe cần bảo dưỡng.</t>
-        </is>
-      </c>
-      <c r="H9" s="6" t="inlineStr">
-        <is>
-          <t>7a4c1e9b-3d2f-4b8a-a6c5-1e0d9f8b7a44</t>
-        </is>
-      </c>
-      <c r="I9" s="6" t="n"/>
-    </row>
-    <row r="10" ht="27" customHeight="1">
-      <c r="A10" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>partner_id</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>uuid</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E10" s="6" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="F10" s="7" t="inlineStr">
-        <is>
-          <t>repair_partners.partner_id (khi xóa: chặn xóa)</t>
-        </is>
-      </c>
-      <c r="G10" s="6" t="inlineStr">
-        <is>
-          <t>Xưởng được đặt.</t>
-        </is>
-      </c>
-      <c r="H10" s="6" t="inlineStr">
-        <is>
-          <t>a9c6e3b1-5f2d-4a8c-b7e4-3d1f0a6c9bdd</t>
-        </is>
-      </c>
-      <c r="I10" s="6" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>scheduled_at</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>timestamptz</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E11" s="6" t="n"/>
-      <c r="F11" s="6" t="n"/>
-      <c r="G11" s="6" t="inlineStr">
-        <is>
-          <t>Thời gian hẹn.</t>
-        </is>
-      </c>
-      <c r="H11" s="6" t="inlineStr">
-        <is>
-          <t>2026-09-20T01:00:00Z</t>
-        </is>
-      </c>
-      <c r="I11" s="6" t="n"/>
-    </row>
-    <row r="12" ht="27" customHeight="1">
-      <c r="A12" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>varchar(20)</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E12" s="6" t="n"/>
-      <c r="F12" s="6" t="n"/>
-      <c r="G12" s="6" t="inlineStr">
-        <is>
-          <t>Trạng thái lịch hẹn. Giá trị: REQUESTED | CONFIRMED | DONE | CANCELLED.</t>
-        </is>
-      </c>
-      <c r="H12" s="6" t="inlineStr">
-        <is>
-          <t>CONFIRMED</t>
-        </is>
-      </c>
-      <c r="I12" s="6" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>created_at</t>
-        </is>
-      </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>timestamptz</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E13" s="6" t="n"/>
-      <c r="F13" s="6" t="n"/>
-      <c r="G13" s="6" t="inlineStr">
-        <is>
-          <t>Thời điểm tạo bản ghi (UTC).</t>
-        </is>
-      </c>
-      <c r="H13" s="6" t="inlineStr">
-        <is>
-          <t>2026-09-10T07:15:00Z</t>
-        </is>
-      </c>
-      <c r="I13" s="6" t="n"/>
-    </row>
-  </sheetData>
-  <autoFilter ref="A6:I13"/>
-  <hyperlinks>
-    <hyperlink ref="A2" location="'Tổng quan'!A1"/>
-    <hyperlink ref="F8" location="'organizations'!A1"/>
-    <hyperlink ref="F9" location="'vehicles'!A1"/>
-    <hyperlink ref="F10" location="'repair_partners'!A1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -40039,6 +40540,373 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:I13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="7" max="7"/>
+    <col width="42" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>44. maintenance_bookings: Lịch bảo dưỡng</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t>← Tổng quan</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>Miền nghiệp vụ: CSKH &amp; cứu hộ (support)   ·   Chủ sở hữu dữ liệu: Khách hàng   ·   Tính năng: F-I3</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>Một lịch hẹn bảo dưỡng xe tại xưởng đối tác.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5"/>
+    <row r="6" ht="27" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Cột</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Kiểu dữ liệu</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Cho phép rỗng</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>Khóa</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>Tham chiếu tới</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>Ý nghĩa</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>Ví dụ</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>Lưu lịch sử</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>booking_id</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>uuid</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="n"/>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>Mã nội bộ của lịch hẹn.</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>0000000d-5a6b-4c7d-8e9f-0a1b2c3d4e5f</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="n"/>
+    </row>
+    <row r="8" ht="27" customHeight="1">
+      <c r="A8" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>organization_id</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>uuid</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>organizations.organization_id (khi xóa: chặn xóa)</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>Tổ chức khách hàng đặt lịch.</t>
+        </is>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>3f6c2a1e-8b4d-4e2a-9c1f-0a7d5b2e4c11</t>
+        </is>
+      </c>
+      <c r="I8" s="6" t="n"/>
+    </row>
+    <row r="9" ht="27" customHeight="1">
+      <c r="A9" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>vehicle_id</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>uuid</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>vehicles.vehicle_id (khi xóa: chặn xóa)</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>Xe cần bảo dưỡng.</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>7a4c1e9b-3d2f-4b8a-a6c5-1e0d9f8b7a44</t>
+        </is>
+      </c>
+      <c r="I9" s="6" t="n"/>
+    </row>
+    <row r="10" ht="27" customHeight="1">
+      <c r="A10" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>partner_id</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>uuid</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>repair_partners.partner_id (khi xóa: chặn xóa)</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>Xưởng được đặt.</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>a9c6e3b1-5f2d-4a8c-b7e4-3d1f0a6c9bdd</t>
+        </is>
+      </c>
+      <c r="I10" s="6" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>scheduled_at</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>timestamptz</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="n"/>
+      <c r="F11" s="6" t="n"/>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>Thời gian hẹn.</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-20T01:00:00Z</t>
+        </is>
+      </c>
+      <c r="I11" s="6" t="n"/>
+    </row>
+    <row r="12" ht="27" customHeight="1">
+      <c r="A12" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>varchar(20)</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="n"/>
+      <c r="F12" s="6" t="n"/>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>Trạng thái lịch hẹn. Giá trị: REQUESTED | CONFIRMED | DONE | CANCELLED.</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I12" s="6" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>created_at</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>timestamptz</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="n"/>
+      <c r="F13" s="6" t="n"/>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>Thời điểm tạo bản ghi (UTC).</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-10T07:15:00Z</t>
+        </is>
+      </c>
+      <c r="I13" s="6" t="n"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A6:I13"/>
+  <hyperlinks>
+    <hyperlink ref="A2" location="'Tổng quan'!A1"/>
+    <hyperlink ref="F8" location="'organizations'!A1"/>
+    <hyperlink ref="F9" location="'vehicles'!A1"/>
+    <hyperlink ref="F10" location="'repair_partners'!A1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet61.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -40056,7 +40924,7 @@
     <row r="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>44. charging_policies: Chính sách sạc</t>
+          <t>45. charging_policies: Chính sách sạc</t>
         </is>
       </c>
     </row>
@@ -40353,7 +41221,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet61.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet62.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -40376,7 +41244,7 @@
     <row r="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>45. charging_policy_versions: Phiên bản chính sách sạc</t>
+          <t>46. charging_policy_versions: Phiên bản chính sách sạc</t>
         </is>
       </c>
     </row>
@@ -40878,415 +41746,6 @@
     <hyperlink ref="F8" location="'charging_policies'!A1"/>
     <hyperlink ref="F16" location="'users'!A1"/>
     <hyperlink ref="B22" location="'policy_violations'!A1"/>
-  </hyperlinks>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet62.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="40" customWidth="1" min="6" max="6"/>
-    <col width="60" customWidth="1" min="7" max="7"/>
-    <col width="42" customWidth="1" min="8" max="8"/>
-    <col width="11" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="9" t="inlineStr">
-        <is>
-          <t>46. charging_policy_assignments: Áp dụng chính sách sạc</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="10" t="inlineStr">
-        <is>
-          <t>← Tổng quan</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>Miền nghiệp vụ: Chính sách sạc (bảo hành) (policy)   ·   Chủ sở hữu dữ liệu: Khách hàng   ·   Tính năng: F-B1</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="11" t="inlineStr">
-        <is>
-          <t>Chính sách nào áp dụng cho một xe, một đội xe hay một dòng xe.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5"/>
-    <row r="6" ht="27" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>Cột</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>Kiểu dữ liệu</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>Cho phép rỗng</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>Khóa</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>Tham chiếu tới</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>Ý nghĩa</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>Ví dụ</t>
-        </is>
-      </c>
-      <c r="I6" s="4" t="inlineStr">
-        <is>
-          <t>Lưu lịch sử</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>assignment_id</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>uuid</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
-      <c r="F7" s="6" t="n"/>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>Mã nội bộ của lần áp dụng.</t>
-        </is>
-      </c>
-      <c r="H7" s="6" t="inlineStr">
-        <is>
-          <t>0000000e-5a6b-4c7d-8e9f-0a1b2c3d4e5f</t>
-        </is>
-      </c>
-      <c r="I7" s="6" t="n"/>
-    </row>
-    <row r="8" ht="27" customHeight="1">
-      <c r="A8" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>organization_id</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>uuid</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E8" s="6" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="F8" s="7" t="inlineStr">
-        <is>
-          <t>organizations.organization_id (khi xóa: chặn xóa)</t>
-        </is>
-      </c>
-      <c r="G8" s="6" t="inlineStr">
-        <is>
-          <t>Tổ chức khách hàng của lần áp dụng.</t>
-        </is>
-      </c>
-      <c r="H8" s="6" t="inlineStr">
-        <is>
-          <t>3f6c2a1e-8b4d-4e2a-9c1f-0a7d5b2e4c11</t>
-        </is>
-      </c>
-      <c r="I8" s="6" t="n"/>
-    </row>
-    <row r="9" ht="27" customHeight="1">
-      <c r="A9" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>policy_id</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>uuid</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E9" s="6" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="F9" s="7" t="inlineStr">
-        <is>
-          <t>charging_policies.policy_id (khi xóa: chặn xóa)</t>
-        </is>
-      </c>
-      <c r="G9" s="6" t="inlineStr">
-        <is>
-          <t>Chính sách được áp dụng.</t>
-        </is>
-      </c>
-      <c r="H9" s="6" t="inlineStr">
-        <is>
-          <t>b8e5a2d9-3c6f-4b1e-a9d7-5f2c0e8b1aee</t>
-        </is>
-      </c>
-      <c r="I9" s="6" t="n"/>
-    </row>
-    <row r="10" ht="27" customHeight="1">
-      <c r="A10" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>vehicle_id</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>uuid</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>có</t>
-        </is>
-      </c>
-      <c r="E10" s="6" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="F10" s="7" t="inlineStr">
-        <is>
-          <t>vehicles.vehicle_id (khi xóa: chặn xóa)</t>
-        </is>
-      </c>
-      <c r="G10" s="6" t="inlineStr">
-        <is>
-          <t>Xe được áp dụng, nếu phạm vi là một xe. Chỉ đúng một trong vehicle_id / fleet_id / vehicle_model có giá trị.</t>
-        </is>
-      </c>
-      <c r="H10" s="6" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="I10" s="6" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>fleet_id</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>uuid</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>có</t>
-        </is>
-      </c>
-      <c r="E11" s="6" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="F11" s="7" t="inlineStr">
-        <is>
-          <t>fleets.fleet_id (khi xóa: chặn xóa)</t>
-        </is>
-      </c>
-      <c r="G11" s="6" t="inlineStr">
-        <is>
-          <t>Đội xe được áp dụng, nếu phạm vi là một đội.</t>
-        </is>
-      </c>
-      <c r="H11" s="6" t="inlineStr">
-        <is>
-          <t>8d5f2b7e-1a9c-4f3d-b8e2-6c0a4d9f1e77</t>
-        </is>
-      </c>
-      <c r="I11" s="6" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>vehicle_model</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>varchar(50)</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>có</t>
-        </is>
-      </c>
-      <c r="E12" s="6" t="n"/>
-      <c r="F12" s="6" t="n"/>
-      <c r="G12" s="6" t="inlineStr">
-        <is>
-          <t>Dòng xe được áp dụng, nếu phạm vi là một dòng xe.</t>
-        </is>
-      </c>
-      <c r="H12" s="6" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="I12" s="6" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>assigned_at</t>
-        </is>
-      </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>timestamptz</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E13" s="6" t="n"/>
-      <c r="F13" s="6" t="n"/>
-      <c r="G13" s="6" t="inlineStr">
-        <is>
-          <t>Thời điểm bắt đầu áp dụng.</t>
-        </is>
-      </c>
-      <c r="H13" s="6" t="inlineStr">
-        <is>
-          <t>2026-10-01T00:00:00Z</t>
-        </is>
-      </c>
-      <c r="I13" s="6" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="B14" s="6" t="inlineStr">
-        <is>
-          <t>unassigned_at</t>
-        </is>
-      </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>timestamptz</t>
-        </is>
-      </c>
-      <c r="D14" s="6" t="inlineStr">
-        <is>
-          <t>có</t>
-        </is>
-      </c>
-      <c r="E14" s="6" t="n"/>
-      <c r="F14" s="6" t="n"/>
-      <c r="G14" s="6" t="inlineStr">
-        <is>
-          <t>Thời điểm kết thúc; NULL khi còn hiệu lực.</t>
-        </is>
-      </c>
-      <c r="H14" s="6" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="I14" s="6" t="n"/>
-    </row>
-  </sheetData>
-  <autoFilter ref="A6:I14"/>
-  <hyperlinks>
-    <hyperlink ref="A2" location="'Tổng quan'!A1"/>
-    <hyperlink ref="F8" location="'organizations'!A1"/>
-    <hyperlink ref="F9" location="'charging_policies'!A1"/>
-    <hyperlink ref="F10" location="'vehicles'!A1"/>
-    <hyperlink ref="F11" location="'fleets'!A1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -41315,7 +41774,7 @@
     <row r="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>47. policy_violations: Vi phạm chính sách sạc</t>
+          <t>47. charging_policy_assignments: Áp dụng chính sách sạc</t>
         </is>
       </c>
     </row>
@@ -41329,14 +41788,14 @@
     <row r="3">
       <c r="A3" s="11" t="inlineStr">
         <is>
-          <t>Miền nghiệp vụ: Chính sách sạc (bảo hành) (policy)   ·   Chủ sở hữu dữ liệu: Khách hàng   ·   Tính năng: F-B3, F-B6</t>
+          <t>Miền nghiệp vụ: Chính sách sạc (bảo hành) (policy)   ·   Chủ sở hữu dữ liệu: Khách hàng   ·   Tính năng: F-B1</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="11" t="inlineStr">
         <is>
-          <t>Một phiên sạc vi phạm chính sách, kèm bằng chứng. Hệ quả của vi phạm vẫn là câu hỏi kinh doanh còn mở (mục 3 của feature-list).</t>
+          <t>Chính sách nào áp dụng cho một xe, một đội xe hay một dòng xe.</t>
         </is>
       </c>
     </row>
@@ -41394,7 +41853,7 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>violation_id</t>
+          <t>assignment_id</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
@@ -41415,12 +41874,12 @@
       <c r="F7" s="6" t="n"/>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>Mã nội bộ của vi phạm.</t>
+          <t>Mã nội bộ của lần áp dụng.</t>
         </is>
       </c>
       <c r="H7" s="6" t="inlineStr">
         <is>
-          <t>0000000f-5a6b-4c7d-8e9f-0a1b2c3d4e5f</t>
+          <t>0000000e-5a6b-4c7d-8e9f-0a1b2c3d4e5f</t>
         </is>
       </c>
       <c r="I7" s="6" t="n"/>
@@ -41456,7 +41915,7 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>Tổ chức khách hàng sở hữu xe.</t>
+          <t>Tổ chức khách hàng của lần áp dụng.</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr">
@@ -41472,7 +41931,7 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>session_id</t>
+          <t>policy_id</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
@@ -41492,17 +41951,17 @@
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>charging_sessions.session_id (khi xóa: chặn xóa)</t>
+          <t>charging_policies.policy_id (khi xóa: chặn xóa)</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>Phiên sạc đã vi phạm chính sách.</t>
+          <t>Chính sách được áp dụng.</t>
         </is>
       </c>
       <c r="H9" s="6" t="inlineStr">
         <is>
-          <t>e5a2d8f1-4b7c-4e9a-b3d6-2c1f0e9a8dbb</t>
+          <t>b8e5a2d9-3c6f-4b1e-a9d7-5f2c0e8b1aee</t>
         </is>
       </c>
       <c r="I9" s="6" t="n"/>
@@ -41523,7 +41982,7 @@
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>không</t>
+          <t>có</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
@@ -41538,23 +41997,23 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>Xe liên quan.</t>
+          <t>Xe được áp dụng, nếu phạm vi là một xe. Chỉ đúng một trong vehicle_id / fleet_id / vehicle_model có giá trị.</t>
         </is>
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>7a4c1e9b-3d2f-4b8a-a6c5-1e0d9f8b7a44</t>
+          <t>NULL</t>
         </is>
       </c>
       <c r="I10" s="6" t="n"/>
     </row>
-    <row r="11" ht="27" customHeight="1">
+    <row r="11">
       <c r="A11" s="6" t="n">
         <v>5</v>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>policy_version_id</t>
+          <t>fleet_id</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
@@ -41564,7 +42023,7 @@
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>không</t>
+          <t>có</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
@@ -41574,17 +42033,17 @@
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>charging_policy_versions.version_id (khi xóa: chặn xóa)</t>
+          <t>fleets.fleet_id (khi xóa: chặn xóa)</t>
         </is>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>Đúng phiên bản chính sách bị vi phạm.</t>
+          <t>Đội xe được áp dụng, nếu phạm vi là một đội.</t>
         </is>
       </c>
       <c r="H11" s="6" t="inlineStr">
         <is>
-          <t>c7d4f1a8-2b5e-4c9d-8f6a-1e3b0d7c4aff</t>
+          <t>8d5f2b7e-1a9c-4f3d-b8e2-6c0a4d9f1e77</t>
         </is>
       </c>
       <c r="I11" s="6" t="n"/>
@@ -41595,29 +42054,29 @@
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>violation_type</t>
+          <t>vehicle_model</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>varchar(30)</t>
+          <t>varchar(50)</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>không</t>
+          <t>có</t>
         </is>
       </c>
       <c r="E12" s="6" t="n"/>
       <c r="F12" s="6" t="n"/>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>Quy tắc nào bị vi phạm.</t>
+          <t>Dòng xe được áp dụng, nếu phạm vi là một dòng xe.</t>
         </is>
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>SOC_ABOVE_MAX</t>
+          <t>NULL</t>
         </is>
       </c>
       <c r="I12" s="6" t="n"/>
@@ -41628,7 +42087,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>detected_at</t>
+          <t>assigned_at</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
@@ -41645,45 +42104,45 @@
       <c r="F13" s="6" t="n"/>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>Thời điểm phát hiện vi phạm.</t>
+          <t>Thời điểm bắt đầu áp dụng.</t>
         </is>
       </c>
       <c r="H13" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15T09:45:00Z</t>
+          <t>2026-10-01T00:00:00Z</t>
         </is>
       </c>
       <c r="I13" s="6" t="n"/>
     </row>
-    <row r="14" ht="27" customHeight="1">
+    <row r="14">
       <c r="A14" s="6" t="n">
         <v>8</v>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>evidence</t>
+          <t>unassigned_at</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>jsonb</t>
+          <t>timestamptz</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>không</t>
+          <t>có</t>
         </is>
       </c>
       <c r="E14" s="6" t="n"/>
       <c r="F14" s="6" t="n"/>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>Ảnh chụp dữ liệu chứng minh vi phạm, dạng JSON.</t>
+          <t>Thời điểm kết thúc; NULL khi còn hiệu lực.</t>
         </is>
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
-          <t>{"soc_end": 98.5, "soc_max": 90, "meter_stop_wh": 1712860}</t>
+          <t>NULL</t>
         </is>
       </c>
       <c r="I14" s="6" t="n"/>
@@ -41693,9 +42152,9 @@
   <hyperlinks>
     <hyperlink ref="A2" location="'Tổng quan'!A1"/>
     <hyperlink ref="F8" location="'organizations'!A1"/>
-    <hyperlink ref="F9" location="'charging_sessions'!A1"/>
+    <hyperlink ref="F9" location="'charging_policies'!A1"/>
     <hyperlink ref="F10" location="'vehicles'!A1"/>
-    <hyperlink ref="F11" location="'charging_policy_versions'!A1"/>
+    <hyperlink ref="F11" location="'fleets'!A1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -41724,7 +42183,416 @@
     <row r="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>48. tariffs: Biểu giá điện</t>
+          <t>48. policy_violations: Vi phạm chính sách sạc</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t>← Tổng quan</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>Miền nghiệp vụ: Chính sách sạc (bảo hành) (policy)   ·   Chủ sở hữu dữ liệu: Khách hàng   ·   Tính năng: F-B3, F-B6</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>Một phiên sạc vi phạm chính sách, kèm bằng chứng. Hệ quả của vi phạm vẫn là câu hỏi kinh doanh còn mở (mục 3 của feature-list).</t>
+        </is>
+      </c>
+    </row>
+    <row r="5"/>
+    <row r="6" ht="27" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Cột</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Kiểu dữ liệu</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Cho phép rỗng</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>Khóa</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>Tham chiếu tới</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>Ý nghĩa</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>Ví dụ</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>Lưu lịch sử</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>violation_id</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>uuid</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="n"/>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>Mã nội bộ của vi phạm.</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>0000000f-5a6b-4c7d-8e9f-0a1b2c3d4e5f</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="n"/>
+    </row>
+    <row r="8" ht="27" customHeight="1">
+      <c r="A8" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>organization_id</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>uuid</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>organizations.organization_id (khi xóa: chặn xóa)</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>Tổ chức khách hàng sở hữu xe.</t>
+        </is>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>3f6c2a1e-8b4d-4e2a-9c1f-0a7d5b2e4c11</t>
+        </is>
+      </c>
+      <c r="I8" s="6" t="n"/>
+    </row>
+    <row r="9" ht="27" customHeight="1">
+      <c r="A9" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>session_id</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>uuid</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>charging_sessions.session_id (khi xóa: chặn xóa)</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>Phiên sạc đã vi phạm chính sách.</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>e5a2d8f1-4b7c-4e9a-b3d6-2c1f0e9a8dbb</t>
+        </is>
+      </c>
+      <c r="I9" s="6" t="n"/>
+    </row>
+    <row r="10" ht="27" customHeight="1">
+      <c r="A10" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>vehicle_id</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>uuid</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>vehicles.vehicle_id (khi xóa: chặn xóa)</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>Xe liên quan.</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>7a4c1e9b-3d2f-4b8a-a6c5-1e0d9f8b7a44</t>
+        </is>
+      </c>
+      <c r="I10" s="6" t="n"/>
+    </row>
+    <row r="11" ht="27" customHeight="1">
+      <c r="A11" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>policy_version_id</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>uuid</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>charging_policy_versions.version_id (khi xóa: chặn xóa)</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>Đúng phiên bản chính sách bị vi phạm.</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>c7d4f1a8-2b5e-4c9d-8f6a-1e3b0d7c4aff</t>
+        </is>
+      </c>
+      <c r="I11" s="6" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>violation_type</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>varchar(30)</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="n"/>
+      <c r="F12" s="6" t="n"/>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>Quy tắc nào bị vi phạm.</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>SOC_ABOVE_MAX</t>
+        </is>
+      </c>
+      <c r="I12" s="6" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>detected_at</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>timestamptz</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="n"/>
+      <c r="F13" s="6" t="n"/>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>Thời điểm phát hiện vi phạm.</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-15T09:45:00Z</t>
+        </is>
+      </c>
+      <c r="I13" s="6" t="n"/>
+    </row>
+    <row r="14" ht="27" customHeight="1">
+      <c r="A14" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>jsonb</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="n"/>
+      <c r="F14" s="6" t="n"/>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>Ảnh chụp dữ liệu chứng minh vi phạm, dạng JSON.</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>{"soc_end": 98.5, "soc_max": 90, "meter_stop_wh": 1712860}</t>
+        </is>
+      </c>
+      <c r="I14" s="6" t="n"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A6:I14"/>
+  <hyperlinks>
+    <hyperlink ref="A2" location="'Tổng quan'!A1"/>
+    <hyperlink ref="F8" location="'organizations'!A1"/>
+    <hyperlink ref="F9" location="'charging_sessions'!A1"/>
+    <hyperlink ref="F10" location="'vehicles'!A1"/>
+    <hyperlink ref="F11" location="'charging_policy_versions'!A1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet65.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="7" max="7"/>
+    <col width="42" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>49. tariffs: Biểu giá điện</t>
         </is>
       </c>
     </row>
@@ -42083,7 +42951,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet65.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet66.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -42106,7 +42974,7 @@
     <row r="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>49. payments: Thanh toán</t>
+          <t>50. payments: Thanh toán</t>
         </is>
       </c>
     </row>
@@ -42563,359 +43431,6 @@
     <hyperlink ref="F8" location="'organizations'!A1"/>
     <hyperlink ref="F9" location="'charging_sessions'!A1"/>
     <hyperlink ref="B19" location="'wallet_transactions'!A1"/>
-  </hyperlinks>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet66.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I15"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="40" customWidth="1" min="6" max="6"/>
-    <col width="60" customWidth="1" min="7" max="7"/>
-    <col width="42" customWidth="1" min="8" max="8"/>
-    <col width="11" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="9" t="inlineStr">
-        <is>
-          <t>50. wallets: Ví</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="10" t="inlineStr">
-        <is>
-          <t>← Tổng quan</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>Miền nghiệp vụ: Thanh toán &amp; hóa đơn (billing)   ·   Chủ sở hữu dữ liệu: Khách hàng   ·   Tính năng: F-H2</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="11" t="inlineStr">
-        <is>
-          <t>Số dư trả trước của một tài xế hoặc của cả tổ chức.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5"/>
-    <row r="6" ht="27" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>Cột</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>Kiểu dữ liệu</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>Cho phép rỗng</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>Khóa</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>Tham chiếu tới</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>Ý nghĩa</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>Ví dụ</t>
-        </is>
-      </c>
-      <c r="I6" s="4" t="inlineStr">
-        <is>
-          <t>Lưu lịch sử</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>wallet_id</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>uuid</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
-      <c r="F7" s="6" t="n"/>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>Mã nội bộ của ví.</t>
-        </is>
-      </c>
-      <c r="H7" s="6" t="inlineStr">
-        <is>
-          <t>5c3a0e7d-2f9b-4c1e-a8d3-7b6f0c2e9a32</t>
-        </is>
-      </c>
-      <c r="I7" s="6" t="n"/>
-    </row>
-    <row r="8" ht="27" customHeight="1">
-      <c r="A8" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>organization_id</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>uuid</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E8" s="6" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="F8" s="7" t="inlineStr">
-        <is>
-          <t>organizations.organization_id (khi xóa: chặn xóa)</t>
-        </is>
-      </c>
-      <c r="G8" s="6" t="inlineStr">
-        <is>
-          <t>Tổ chức khách hàng sở hữu ví.</t>
-        </is>
-      </c>
-      <c r="H8" s="6" t="inlineStr">
-        <is>
-          <t>3f6c2a1e-8b4d-4e2a-9c1f-0a7d5b2e4c11</t>
-        </is>
-      </c>
-      <c r="I8" s="6" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>driver_id</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>uuid</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>có</t>
-        </is>
-      </c>
-      <c r="E9" s="6" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="F9" s="7" t="inlineStr">
-        <is>
-          <t>drivers.driver_id (khi xóa: chặn xóa)</t>
-        </is>
-      </c>
-      <c r="G9" s="6" t="inlineStr">
-        <is>
-          <t>Tài xế sở hữu ví; NULL với ví cấp tổ chức (quyết định D5).</t>
-        </is>
-      </c>
-      <c r="H9" s="6" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="I9" s="6" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>balance</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>numeric(14,2)</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E10" s="6" t="n"/>
-      <c r="F10" s="6" t="n"/>
-      <c r="G10" s="6" t="inlineStr">
-        <is>
-          <t>Số dư hiện tại; phải bằng tổng các giao dịch của ví.</t>
-        </is>
-      </c>
-      <c r="H10" s="6" t="inlineStr">
-        <is>
-          <t>12500000.00</t>
-        </is>
-      </c>
-      <c r="I10" s="6" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>currency</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>char(3)</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E11" s="6" t="n"/>
-      <c r="F11" s="6" t="n"/>
-      <c r="G11" s="6" t="inlineStr">
-        <is>
-          <t>Mã tiền tệ ISO 4217.</t>
-        </is>
-      </c>
-      <c r="H11" s="6" t="inlineStr">
-        <is>
-          <t>VND</t>
-        </is>
-      </c>
-      <c r="I11" s="6" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>varchar(20)</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E12" s="6" t="n"/>
-      <c r="F12" s="6" t="n"/>
-      <c r="G12" s="6" t="inlineStr">
-        <is>
-          <t>Ví có dùng được không.</t>
-        </is>
-      </c>
-      <c r="H12" s="6" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="I12" s="6" t="n"/>
-    </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" s="4" t="n"/>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>Được tham chiếu bởi bảng</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>Cột</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="6" t="n"/>
-      <c r="B15" s="7" t="inlineStr">
-        <is>
-          <t>wallet_transactions</t>
-        </is>
-      </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>wallet_id</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A6:I12"/>
-  <hyperlinks>
-    <hyperlink ref="A2" location="'Tổng quan'!A1"/>
-    <hyperlink ref="F8" location="'organizations'!A1"/>
-    <hyperlink ref="F9" location="'drivers'!A1"/>
-    <hyperlink ref="B15" location="'wallet_transactions'!A1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -42944,7 +43459,360 @@
     <row r="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>51. wallet_transactions: Giao dịch ví</t>
+          <t>51. wallets: Ví</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t>← Tổng quan</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>Miền nghiệp vụ: Thanh toán &amp; hóa đơn (billing)   ·   Chủ sở hữu dữ liệu: Khách hàng   ·   Tính năng: F-H2</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>Số dư trả trước của một tài xế hoặc của cả tổ chức.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5"/>
+    <row r="6" ht="27" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Cột</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Kiểu dữ liệu</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Cho phép rỗng</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>Khóa</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>Tham chiếu tới</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>Ý nghĩa</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>Ví dụ</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>Lưu lịch sử</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>wallet_id</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>uuid</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="n"/>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>Mã nội bộ của ví.</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>5c3a0e7d-2f9b-4c1e-a8d3-7b6f0c2e9a32</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="n"/>
+    </row>
+    <row r="8" ht="27" customHeight="1">
+      <c r="A8" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>organization_id</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>uuid</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>organizations.organization_id (khi xóa: chặn xóa)</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>Tổ chức khách hàng sở hữu ví.</t>
+        </is>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>3f6c2a1e-8b4d-4e2a-9c1f-0a7d5b2e4c11</t>
+        </is>
+      </c>
+      <c r="I8" s="6" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>driver_id</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>uuid</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>drivers.driver_id (khi xóa: chặn xóa)</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>Tài xế sở hữu ví; NULL với ví cấp tổ chức (quyết định D5).</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="I9" s="6" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>balance</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>numeric(14,2)</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="n"/>
+      <c r="F10" s="6" t="n"/>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>Số dư hiện tại; phải bằng tổng các giao dịch của ví.</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>12500000.00</t>
+        </is>
+      </c>
+      <c r="I10" s="6" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>currency</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>char(3)</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="n"/>
+      <c r="F11" s="6" t="n"/>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>Mã tiền tệ ISO 4217.</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="I11" s="6" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>varchar(20)</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="n"/>
+      <c r="F12" s="6" t="n"/>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>Ví có dùng được không.</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="I12" s="6" t="n"/>
+    </row>
+    <row r="13"/>
+    <row r="14">
+      <c r="A14" s="4" t="n"/>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>Được tham chiếu bởi bảng</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>Cột</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="n"/>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>wallet_transactions</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>wallet_id</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A6:I12"/>
+  <hyperlinks>
+    <hyperlink ref="A2" location="'Tổng quan'!A1"/>
+    <hyperlink ref="F8" location="'organizations'!A1"/>
+    <hyperlink ref="F9" location="'drivers'!A1"/>
+    <hyperlink ref="B15" location="'wallet_transactions'!A1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet68.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="7" max="7"/>
+    <col width="42" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>52. wallet_transactions: Giao dịch ví</t>
         </is>
       </c>
     </row>
@@ -43363,7 +44231,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet68.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet69.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -43386,7 +44254,7 @@
     <row r="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>52. invoices: Hóa đơn</t>
+          <t>53. invoices: Hóa đơn</t>
         </is>
       </c>
     </row>
@@ -43834,448 +44702,6 @@
     <hyperlink ref="A2" location="'Tổng quan'!A1"/>
     <hyperlink ref="F8" location="'organizations'!A1"/>
     <hyperlink ref="B19" location="'invoice_lines'!A1"/>
-  </hyperlinks>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet69.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I15"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="40" customWidth="1" min="6" max="6"/>
-    <col width="60" customWidth="1" min="7" max="7"/>
-    <col width="42" customWidth="1" min="8" max="8"/>
-    <col width="11" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="9" t="inlineStr">
-        <is>
-          <t>53. invoice_lines: Dòng hóa đơn</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="10" t="inlineStr">
-        <is>
-          <t>← Tổng quan</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>Miền nghiệp vụ: Thanh toán &amp; hóa đơn (billing)   ·   Chủ sở hữu dữ liệu: Khách hàng   ·   Tính năng: F-H3, F-H4</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="11" t="inlineStr">
-        <is>
-          <t>Một dòng của hóa đơn: một phiên sạc hoặc một kỳ thuê bao.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5"/>
-    <row r="6" ht="27" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>Cột</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>Kiểu dữ liệu</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>Cho phép rỗng</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>Khóa</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>Tham chiếu tới</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>Ý nghĩa</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>Ví dụ</t>
-        </is>
-      </c>
-      <c r="I6" s="4" t="inlineStr">
-        <is>
-          <t>Lưu lịch sử</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>line_id</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>uuid</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
-      <c r="F7" s="6" t="n"/>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>Mã nội bộ của dòng hóa đơn.</t>
-        </is>
-      </c>
-      <c r="H7" s="6" t="inlineStr">
-        <is>
-          <t>00000011-5a6b-4c7d-8e9f-0a1b2c3d4e5f</t>
-        </is>
-      </c>
-      <c r="I7" s="6" t="n"/>
-    </row>
-    <row r="8" ht="27" customHeight="1">
-      <c r="A8" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>invoice_id</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>uuid</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E8" s="6" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="F8" s="7" t="inlineStr">
-        <is>
-          <t>invoices.invoice_id (khi xóa: chặn xóa)</t>
-        </is>
-      </c>
-      <c r="G8" s="6" t="inlineStr">
-        <is>
-          <t>Hóa đơn chứa dòng.</t>
-        </is>
-      </c>
-      <c r="H8" s="6" t="inlineStr">
-        <is>
-          <t>7e5c2a9f-4b1d-4e3a-9c8f-0d6b1e4a7c43</t>
-        </is>
-      </c>
-      <c r="I8" s="6" t="n"/>
-    </row>
-    <row r="9" ht="27" customHeight="1">
-      <c r="A9" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>organization_id</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>uuid</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E9" s="6" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="F9" s="7" t="inlineStr">
-        <is>
-          <t>organizations.organization_id (khi xóa: chặn xóa)</t>
-        </is>
-      </c>
-      <c r="G9" s="6" t="inlineStr">
-        <is>
-          <t>Tổ chức khách hàng được xuất hóa đơn.</t>
-        </is>
-      </c>
-      <c r="H9" s="6" t="inlineStr">
-        <is>
-          <t>3f6c2a1e-8b4d-4e2a-9c1f-0a7d5b2e4c11</t>
-        </is>
-      </c>
-      <c r="I9" s="6" t="n"/>
-    </row>
-    <row r="10" ht="27" customHeight="1">
-      <c r="A10" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>session_id</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>uuid</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>có</t>
-        </is>
-      </c>
-      <c r="E10" s="6" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="F10" s="7" t="inlineStr">
-        <is>
-          <t>charging_sessions.session_id (khi xóa: chặn xóa)</t>
-        </is>
-      </c>
-      <c r="G10" s="6" t="inlineStr">
-        <is>
-          <t>Phiên sạc được tính tiền ở dòng này, nếu có.</t>
-        </is>
-      </c>
-      <c r="H10" s="6" t="inlineStr">
-        <is>
-          <t>e5a2d8f1-4b7c-4e9a-b3d6-2c1f0e9a8dbb</t>
-        </is>
-      </c>
-      <c r="I10" s="6" t="n"/>
-    </row>
-    <row r="11" ht="27" customHeight="1">
-      <c r="A11" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>subscription_id</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>uuid</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>có</t>
-        </is>
-      </c>
-      <c r="E11" s="6" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="F11" s="7" t="inlineStr">
-        <is>
-          <t>subscriptions.subscription_id (khi xóa: chặn xóa)</t>
-        </is>
-      </c>
-      <c r="G11" s="6" t="inlineStr">
-        <is>
-          <t>Kỳ thuê bao được tính tiền ở dòng này, nếu có.</t>
-        </is>
-      </c>
-      <c r="H11" s="6" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="I11" s="6" t="n"/>
-    </row>
-    <row r="12" ht="27" customHeight="1">
-      <c r="A12" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>varchar(200)</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E12" s="6" t="n"/>
-      <c r="F12" s="6" t="n"/>
-      <c r="G12" s="6" t="inlineStr">
-        <is>
-          <t>Nội dung dòng in trên hóa đơn.</t>
-        </is>
-      </c>
-      <c r="H12" s="6" t="inlineStr">
-        <is>
-          <t>Sạc điện 192.5 kWh - Trạm sạc G3 Bình Dương - 15/09/2026</t>
-        </is>
-      </c>
-      <c r="I12" s="6" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>quantity</t>
-        </is>
-      </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>numeric(14,3)</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E13" s="6" t="n"/>
-      <c r="F13" s="6" t="n"/>
-      <c r="G13" s="6" t="inlineStr">
-        <is>
-          <t>Số lượng tính tiền (kWh hoặc số tháng).</t>
-        </is>
-      </c>
-      <c r="H13" s="6" t="inlineStr">
-        <is>
-          <t>192.500</t>
-        </is>
-      </c>
-      <c r="I13" s="6" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="B14" s="6" t="inlineStr">
-        <is>
-          <t>unit_price</t>
-        </is>
-      </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>numeric(12,2)</t>
-        </is>
-      </c>
-      <c r="D14" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E14" s="6" t="n"/>
-      <c r="F14" s="6" t="n"/>
-      <c r="G14" s="6" t="inlineStr">
-        <is>
-          <t>Đơn giá.</t>
-        </is>
-      </c>
-      <c r="H14" s="6" t="inlineStr">
-        <is>
-          <t>4500.00</t>
-        </is>
-      </c>
-      <c r="I14" s="6" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="B15" s="6" t="inlineStr">
-        <is>
-          <t>amount</t>
-        </is>
-      </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>numeric(14,2)</t>
-        </is>
-      </c>
-      <c r="D15" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E15" s="6" t="n"/>
-      <c r="F15" s="6" t="n"/>
-      <c r="G15" s="6" t="inlineStr">
-        <is>
-          <t>Thành tiền: số lượng × đơn giá.</t>
-        </is>
-      </c>
-      <c r="H15" s="6" t="inlineStr">
-        <is>
-          <t>866250.00</t>
-        </is>
-      </c>
-      <c r="I15" s="6" t="n"/>
-    </row>
-  </sheetData>
-  <autoFilter ref="A6:I15"/>
-  <hyperlinks>
-    <hyperlink ref="A2" location="'Tổng quan'!A1"/>
-    <hyperlink ref="F8" location="'invoices'!A1"/>
-    <hyperlink ref="F9" location="'organizations'!A1"/>
-    <hyperlink ref="F10" location="'charging_sessions'!A1"/>
-    <hyperlink ref="F11" location="'subscriptions'!A1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -44960,6 +45386,448 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:I15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="7" max="7"/>
+    <col width="42" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>54. invoice_lines: Dòng hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t>← Tổng quan</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>Miền nghiệp vụ: Thanh toán &amp; hóa đơn (billing)   ·   Chủ sở hữu dữ liệu: Khách hàng   ·   Tính năng: F-H3, F-H4</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>Một dòng của hóa đơn: một phiên sạc hoặc một kỳ thuê bao.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5"/>
+    <row r="6" ht="27" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Cột</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Kiểu dữ liệu</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Cho phép rỗng</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>Khóa</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>Tham chiếu tới</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>Ý nghĩa</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>Ví dụ</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>Lưu lịch sử</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>line_id</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>uuid</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="n"/>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>Mã nội bộ của dòng hóa đơn.</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>00000011-5a6b-4c7d-8e9f-0a1b2c3d4e5f</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="n"/>
+    </row>
+    <row r="8" ht="27" customHeight="1">
+      <c r="A8" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>invoice_id</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>uuid</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>invoices.invoice_id (khi xóa: chặn xóa)</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn chứa dòng.</t>
+        </is>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>7e5c2a9f-4b1d-4e3a-9c8f-0d6b1e4a7c43</t>
+        </is>
+      </c>
+      <c r="I8" s="6" t="n"/>
+    </row>
+    <row r="9" ht="27" customHeight="1">
+      <c r="A9" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>organization_id</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>uuid</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>organizations.organization_id (khi xóa: chặn xóa)</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>Tổ chức khách hàng được xuất hóa đơn.</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>3f6c2a1e-8b4d-4e2a-9c1f-0a7d5b2e4c11</t>
+        </is>
+      </c>
+      <c r="I9" s="6" t="n"/>
+    </row>
+    <row r="10" ht="27" customHeight="1">
+      <c r="A10" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>session_id</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>uuid</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>charging_sessions.session_id (khi xóa: chặn xóa)</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>Phiên sạc được tính tiền ở dòng này, nếu có.</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>e5a2d8f1-4b7c-4e9a-b3d6-2c1f0e9a8dbb</t>
+        </is>
+      </c>
+      <c r="I10" s="6" t="n"/>
+    </row>
+    <row r="11" ht="27" customHeight="1">
+      <c r="A11" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>subscription_id</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>uuid</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>subscriptions.subscription_id (khi xóa: chặn xóa)</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>Kỳ thuê bao được tính tiền ở dòng này, nếu có.</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="I11" s="6" t="n"/>
+    </row>
+    <row r="12" ht="27" customHeight="1">
+      <c r="A12" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>varchar(200)</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="n"/>
+      <c r="F12" s="6" t="n"/>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>Nội dung dòng in trên hóa đơn.</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>Sạc điện 192.5 kWh - Trạm sạc G3 Bình Dương - 15/09/2026</t>
+        </is>
+      </c>
+      <c r="I12" s="6" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>quantity</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>numeric(14,3)</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="n"/>
+      <c r="F13" s="6" t="n"/>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>Số lượng tính tiền (kWh hoặc số tháng).</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>192.500</t>
+        </is>
+      </c>
+      <c r="I13" s="6" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>unit_price</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>numeric(12,2)</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="n"/>
+      <c r="F14" s="6" t="n"/>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>Đơn giá.</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>4500.00</t>
+        </is>
+      </c>
+      <c r="I14" s="6" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>numeric(14,2)</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="n"/>
+      <c r="F15" s="6" t="n"/>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>Thành tiền: số lượng × đơn giá.</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>866250.00</t>
+        </is>
+      </c>
+      <c r="I15" s="6" t="n"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A6:I15"/>
+  <hyperlinks>
+    <hyperlink ref="A2" location="'Tổng quan'!A1"/>
+    <hyperlink ref="F8" location="'invoices'!A1"/>
+    <hyperlink ref="F9" location="'organizations'!A1"/>
+    <hyperlink ref="F10" location="'charging_sessions'!A1"/>
+    <hyperlink ref="F11" location="'subscriptions'!A1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet71.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:I17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -44977,7 +45845,7 @@
     <row r="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>54. subscription_plans: Gói dịch vụ</t>
+          <t>55. subscription_plans: Gói dịch vụ</t>
         </is>
       </c>
     </row>
@@ -45340,7 +46208,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet71.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet72.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -45363,7 +46231,7 @@
     <row r="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>55. plan_features: Tính năng của gói dịch vụ</t>
+          <t>56. plan_features: Tính năng của gói dịch vụ</t>
         </is>
       </c>
     </row>
@@ -45630,401 +46498,6 @@
   <hyperlinks>
     <hyperlink ref="A2" location="'Tổng quan'!A1"/>
     <hyperlink ref="F8" location="'subscription_plans'!A1"/>
-  </hyperlinks>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet72.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I16"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="40" customWidth="1" min="6" max="6"/>
-    <col width="60" customWidth="1" min="7" max="7"/>
-    <col width="42" customWidth="1" min="8" max="8"/>
-    <col width="11" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="9" t="inlineStr">
-        <is>
-          <t>56. subscriptions: Thuê bao</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="10" t="inlineStr">
-        <is>
-          <t>← Tổng quan</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>Miền nghiệp vụ: Thanh toán &amp; hóa đơn (billing)   ·   Chủ sở hữu dữ liệu: Khách hàng   ·   Tính năng: F-H4</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="11" t="inlineStr">
-        <is>
-          <t>Một xe đăng ký một gói; quá hạn thanh toán sẽ khóa tính năng.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5"/>
-    <row r="6" ht="27" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>Cột</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>Kiểu dữ liệu</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>Cho phép rỗng</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>Khóa</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>Tham chiếu tới</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>Ý nghĩa</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>Ví dụ</t>
-        </is>
-      </c>
-      <c r="I6" s="4" t="inlineStr">
-        <is>
-          <t>Lưu lịch sử</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>subscription_id</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>uuid</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
-      <c r="F7" s="6" t="n"/>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>Mã nội bộ của thuê bao.</t>
-        </is>
-      </c>
-      <c r="H7" s="6" t="inlineStr">
-        <is>
-          <t>9a7e4c1b-6d3f-4a5c-b0e8-2f1d7c9b3e54</t>
-        </is>
-      </c>
-      <c r="I7" s="6" t="n"/>
-    </row>
-    <row r="8" ht="27" customHeight="1">
-      <c r="A8" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>organization_id</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>uuid</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E8" s="6" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="F8" s="7" t="inlineStr">
-        <is>
-          <t>organizations.organization_id (khi xóa: chặn xóa)</t>
-        </is>
-      </c>
-      <c r="G8" s="6" t="inlineStr">
-        <is>
-          <t>Tổ chức khách hàng đăng ký.</t>
-        </is>
-      </c>
-      <c r="H8" s="6" t="inlineStr">
-        <is>
-          <t>3f6c2a1e-8b4d-4e2a-9c1f-0a7d5b2e4c11</t>
-        </is>
-      </c>
-      <c r="I8" s="6" t="n"/>
-    </row>
-    <row r="9" ht="27" customHeight="1">
-      <c r="A9" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>plan_id</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>uuid</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E9" s="6" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="F9" s="7" t="inlineStr">
-        <is>
-          <t>subscription_plans.plan_id (khi xóa: chặn xóa)</t>
-        </is>
-      </c>
-      <c r="G9" s="6" t="inlineStr">
-        <is>
-          <t>Gói được đăng ký.</t>
-        </is>
-      </c>
-      <c r="H9" s="6" t="inlineStr">
-        <is>
-          <t>0c9a6e3d-8f5b-4c7e-a2d1-4b3f9e6c0a65</t>
-        </is>
-      </c>
-      <c r="I9" s="6" t="n"/>
-    </row>
-    <row r="10" ht="27" customHeight="1">
-      <c r="A10" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>vehicle_id</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>uuid</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E10" s="6" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="F10" s="7" t="inlineStr">
-        <is>
-          <t>vehicles.vehicle_id (khi xóa: chặn xóa)</t>
-        </is>
-      </c>
-      <c r="G10" s="6" t="inlineStr">
-        <is>
-          <t>Xe được áp dụng.</t>
-        </is>
-      </c>
-      <c r="H10" s="6" t="inlineStr">
-        <is>
-          <t>7a4c1e9b-3d2f-4b8a-a6c5-1e0d9f8b7a44</t>
-        </is>
-      </c>
-      <c r="I10" s="6" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>started_at</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>timestamptz</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E11" s="6" t="n"/>
-      <c r="F11" s="6" t="n"/>
-      <c r="G11" s="6" t="inlineStr">
-        <is>
-          <t>Thời điểm bắt đầu thuê bao.</t>
-        </is>
-      </c>
-      <c r="H11" s="6" t="inlineStr">
-        <is>
-          <t>2026-09-01T00:00:00Z</t>
-        </is>
-      </c>
-      <c r="I11" s="6" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>ends_at</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>timestamptz</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>có</t>
-        </is>
-      </c>
-      <c r="E12" s="6" t="n"/>
-      <c r="F12" s="6" t="n"/>
-      <c r="G12" s="6" t="inlineStr">
-        <is>
-          <t>Thời điểm kết thúc; NULL nếu tự gia hạn cho tới khi hủy.</t>
-        </is>
-      </c>
-      <c r="H12" s="6" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="I12" s="6" t="n"/>
-    </row>
-    <row r="13" ht="27" customHeight="1">
-      <c r="A13" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>varchar(20)</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E13" s="6" t="n"/>
-      <c r="F13" s="6" t="n"/>
-      <c r="G13" s="6" t="inlineStr">
-        <is>
-          <t>Trạng thái thuê bao; OVERDUE sẽ khóa các tính năng trả phí. Giá trị: ACTIVE | OVERDUE | EXPIRED | CANCELLED.</t>
-        </is>
-      </c>
-      <c r="H13" s="6" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="I13" s="6" t="n"/>
-    </row>
-    <row r="14"/>
-    <row r="15">
-      <c r="A15" s="4" t="n"/>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>Được tham chiếu bởi bảng</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>Cột</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="6" t="n"/>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>invoice_lines</t>
-        </is>
-      </c>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>subscription_id</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A6:I13"/>
-  <hyperlinks>
-    <hyperlink ref="A2" location="'Tổng quan'!A1"/>
-    <hyperlink ref="F8" location="'organizations'!A1"/>
-    <hyperlink ref="F9" location="'subscription_plans'!A1"/>
-    <hyperlink ref="F10" location="'vehicles'!A1"/>
-    <hyperlink ref="B16" location="'invoice_lines'!A1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -46053,7 +46526,402 @@
     <row r="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>57. driver_scores: Điểm tài xế</t>
+          <t>57. subscriptions: Thuê bao</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t>← Tổng quan</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>Miền nghiệp vụ: Thanh toán &amp; hóa đơn (billing)   ·   Chủ sở hữu dữ liệu: Khách hàng   ·   Tính năng: F-H4</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>Một xe đăng ký một gói; quá hạn thanh toán sẽ khóa tính năng.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5"/>
+    <row r="6" ht="27" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Cột</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Kiểu dữ liệu</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Cho phép rỗng</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>Khóa</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>Tham chiếu tới</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>Ý nghĩa</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>Ví dụ</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>Lưu lịch sử</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>subscription_id</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>uuid</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="n"/>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>Mã nội bộ của thuê bao.</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>9a7e4c1b-6d3f-4a5c-b0e8-2f1d7c9b3e54</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="n"/>
+    </row>
+    <row r="8" ht="27" customHeight="1">
+      <c r="A8" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>organization_id</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>uuid</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>organizations.organization_id (khi xóa: chặn xóa)</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>Tổ chức khách hàng đăng ký.</t>
+        </is>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>3f6c2a1e-8b4d-4e2a-9c1f-0a7d5b2e4c11</t>
+        </is>
+      </c>
+      <c r="I8" s="6" t="n"/>
+    </row>
+    <row r="9" ht="27" customHeight="1">
+      <c r="A9" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>plan_id</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>uuid</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>subscription_plans.plan_id (khi xóa: chặn xóa)</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>Gói được đăng ký.</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>0c9a6e3d-8f5b-4c7e-a2d1-4b3f9e6c0a65</t>
+        </is>
+      </c>
+      <c r="I9" s="6" t="n"/>
+    </row>
+    <row r="10" ht="27" customHeight="1">
+      <c r="A10" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>vehicle_id</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>uuid</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>vehicles.vehicle_id (khi xóa: chặn xóa)</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>Xe được áp dụng.</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>7a4c1e9b-3d2f-4b8a-a6c5-1e0d9f8b7a44</t>
+        </is>
+      </c>
+      <c r="I10" s="6" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>started_at</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>timestamptz</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="n"/>
+      <c r="F11" s="6" t="n"/>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>Thời điểm bắt đầu thuê bao.</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="I11" s="6" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>ends_at</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>timestamptz</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="n"/>
+      <c r="F12" s="6" t="n"/>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>Thời điểm kết thúc; NULL nếu tự gia hạn cho tới khi hủy.</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="I12" s="6" t="n"/>
+    </row>
+    <row r="13" ht="27" customHeight="1">
+      <c r="A13" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>varchar(20)</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="n"/>
+      <c r="F13" s="6" t="n"/>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>Trạng thái thuê bao; OVERDUE sẽ khóa các tính năng trả phí. Giá trị: ACTIVE | OVERDUE | EXPIRED | CANCELLED.</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="I13" s="6" t="n"/>
+    </row>
+    <row r="14"/>
+    <row r="15">
+      <c r="A15" s="4" t="n"/>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>Được tham chiếu bởi bảng</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>Cột</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="n"/>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>invoice_lines</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>subscription_id</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A6:I13"/>
+  <hyperlinks>
+    <hyperlink ref="A2" location="'Tổng quan'!A1"/>
+    <hyperlink ref="F8" location="'organizations'!A1"/>
+    <hyperlink ref="F9" location="'subscription_plans'!A1"/>
+    <hyperlink ref="F10" location="'vehicles'!A1"/>
+    <hyperlink ref="B16" location="'invoice_lines'!A1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet74.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="7" max="7"/>
+    <col width="42" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>58. driver_scores: Điểm tài xế</t>
         </is>
       </c>
     </row>
@@ -46433,7 +47301,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet74.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet75.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -46456,7 +47324,7 @@
     <row r="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>58. promotion_campaigns: Chiến dịch khuyến mãi</t>
+          <t>59. promotion_campaigns: Chiến dịch khuyến mãi</t>
         </is>
       </c>
     </row>
@@ -46740,7 +47608,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet75.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet76.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -46763,7 +47631,7 @@
     <row r="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>59. trips: Chuyến đi</t>
+          <t>60. trips: Chuyến đi</t>
         </is>
       </c>
     </row>

--- a/docs/design/domain-model/domain-model.xlsx
+++ b/docs/design/domain-model/domain-model.xlsx
@@ -137,7 +137,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="50" hidden="1">'charging_ocpp_messages'!$A$6:$I$14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="51" hidden="1">'charging_station_config_capture'!$A$6:$I$14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="52" hidden="1">'charging_station_config_entries'!$A$6:$I$20</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="53" hidden="1">'charging_sessions'!$A$6:$I$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="53" hidden="1">'charging_sessions'!$A$6:$I$26</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="54" hidden="1">'charging_session_events'!$A$6:$I$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="55" hidden="1">'charging_session_measurements'!$A$6:$I$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="56" hidden="1">'notifications'!$A$6:$I$16</definedName>
@@ -3303,13 +3303,13 @@
       <c r="G67" s="5" t="inlineStr">
         <is>
           <t>Những gì diễn ra trong mỗi lần sạc: sự kiện, chỉ số công tơ, điện năng đã cấp.
-• Một phiên sạc diễn ra trên một súng sạc của một trạm G3.
-• Khoảng trống hiện nay: phiên sạc chưa gắn với xe, tài xế hay khách hàng nào, chỉ có mã id_tag thô. Lúc ra mắt mọi lần sạc đều bắt đầu bằng quét mã QR (CO-13), nên phiên sạc sẽ ghi người khởi động và tổ chức thanh toán (thiết kế khi rà soát charging_sessions); thanh toán (F-H1/F-H3) và đối soát (NF-10) cần liên kết này.
+• Một phiên sạc diễn ra trên một súng sạc của một trụ. Phiên được tạo khi tài xế quét mã QR trên trụ bằng ứng dụng của chúng ta (CE-10) và ghi người quét, tổ chức trả tiền và, nếu tài xế đang nhận một xe, chiếc xe đó; sau đó bản tin bắt đầu của trụ điền súng sạc và giao dịch (CE-11).
+• Bản đang chạy chưa có liên kết này (chỉ có mã id_tag thô); sẽ có khi tái cấu trúc.
 • Một phiên sạc có nhiều sự kiện và nhiều số đo.</t>
         </is>
       </c>
     </row>
-    <row r="68" ht="67.5" customHeight="1">
+    <row r="68" ht="148.5" customHeight="1">
       <c r="A68" s="6" t="inlineStr">
         <is>
           <t>38</t>
@@ -3342,11 +3342,11 @@
       </c>
       <c r="G68" s="6" t="inlineStr">
         <is>
-          <t>Một lần sạc trên một súng sạc, từ lúc bắt đầu đến lúc kết thúc. Cần quyết định khi rà soát bảng (CS-18): lần sạc bằng QR (CO-14) cần lưu ngữ cảnh nghiệp vụ ngay khi tài xế quét (ai quét, tổ chức nào trả tiền, mã gửi trong RemoteStartTransaction, câu trả lời của trụ) để ghép với StartTransaction mang mã đó: tạo dòng phiên PENDING khi quét, một bảng các lệnh gửi xuống trụ, hoặc cả hai.</t>
+          <t>Một lần sạc trên một súng của một trụ, từ lúc quét mã QR đến lúc dừng (CE-10). Dòng được tạo ở trạng thái PENDING khi tài xế quét mã QR trong ứng dụng của chúng ta, cùng tổ chức trả tiền, người quét và mã dùng một lần gửi trong lệnh bắt đầu từ xa; bản tin bắt đầu của chính trụ đó mang mã này chuyển phiên sang ACTIVE (CE-11), bản tin dừng chuyển sang COMPLETED; ABANDONED khi lần bắt đầu không xảy ra. Số liệu trực tiếp (kWh đã sạc, % pin, công suất cao nhất) đọc từ charging_session_measurements; đơn giá và số tiền thuộc bản ghi thanh toán (PAY-10). Không có lịch sử thay đổi và không xóa mềm: không ai sửa một phiên sạc. Ràng buộc kiểm tra (CE-10): phiên ACTIVE hoặc COMPLETED phải có mã giao dịch, EVSE, súng, thời điểm bắt đầu và chỉ số công tơ đầu; phiên COMPLETED phải có thời điểm kết thúc; phiên PENDING hoặc ABANDONED không có mã giao dịch.</t>
         </is>
       </c>
       <c r="H68" s="6" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I68" s="7" t="inlineStr">
         <is>
@@ -25610,7 +25610,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I57"/>
+  <dimension ref="A1:I58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -26391,12 +26391,12 @@
       <c r="A41" s="6" t="n"/>
       <c r="B41" s="7" t="inlineStr">
         <is>
-          <t>charging_policy_versions</t>
+          <t>charging_sessions</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>created_by</t>
+          <t>started_by</t>
         </is>
       </c>
     </row>
@@ -26404,12 +26404,12 @@
       <c r="A42" s="6" t="n"/>
       <c r="B42" s="7" t="inlineStr">
         <is>
-          <t>organization_history</t>
+          <t>charging_policy_versions</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>changed_by</t>
+          <t>created_by</t>
         </is>
       </c>
     </row>
@@ -26417,12 +26417,12 @@
       <c r="A43" s="6" t="n"/>
       <c r="B43" s="7" t="inlineStr">
         <is>
-          <t>user_history</t>
+          <t>organization_history</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>user_id</t>
+          <t>changed_by</t>
         </is>
       </c>
     </row>
@@ -26435,7 +26435,7 @@
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>changed_by</t>
+          <t>user_id</t>
         </is>
       </c>
     </row>
@@ -26443,7 +26443,7 @@
       <c r="A45" s="6" t="n"/>
       <c r="B45" s="7" t="inlineStr">
         <is>
-          <t>membership_history</t>
+          <t>user_history</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
@@ -26452,11 +26452,11 @@
         </is>
       </c>
     </row>
-    <row r="46" ht="27" customHeight="1">
+    <row r="46">
       <c r="A46" s="6" t="n"/>
       <c r="B46" s="7" t="inlineStr">
         <is>
-          <t>organization_setting_history</t>
+          <t>membership_history</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
@@ -26465,11 +26465,11 @@
         </is>
       </c>
     </row>
-    <row r="47">
+    <row r="47" ht="27" customHeight="1">
       <c r="A47" s="6" t="n"/>
       <c r="B47" s="7" t="inlineStr">
         <is>
-          <t>vehicle_history</t>
+          <t>organization_setting_history</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
@@ -26482,7 +26482,7 @@
       <c r="A48" s="6" t="n"/>
       <c r="B48" s="7" t="inlineStr">
         <is>
-          <t>vehicle_model_history</t>
+          <t>vehicle_history</t>
         </is>
       </c>
       <c r="C48" s="6" t="inlineStr">
@@ -26495,7 +26495,7 @@
       <c r="A49" s="6" t="n"/>
       <c r="B49" s="7" t="inlineStr">
         <is>
-          <t>battery_model_history</t>
+          <t>vehicle_model_history</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
@@ -26508,7 +26508,7 @@
       <c r="A50" s="6" t="n"/>
       <c r="B50" s="7" t="inlineStr">
         <is>
-          <t>battery_history</t>
+          <t>battery_model_history</t>
         </is>
       </c>
       <c r="C50" s="6" t="inlineStr">
@@ -26521,7 +26521,7 @@
       <c r="A51" s="6" t="n"/>
       <c r="B51" s="7" t="inlineStr">
         <is>
-          <t>warranty_history</t>
+          <t>battery_history</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
@@ -26534,7 +26534,7 @@
       <c r="A52" s="6" t="n"/>
       <c r="B52" s="7" t="inlineStr">
         <is>
-          <t>telematic_history</t>
+          <t>warranty_history</t>
         </is>
       </c>
       <c r="C52" s="6" t="inlineStr">
@@ -26547,7 +26547,7 @@
       <c r="A53" s="6" t="n"/>
       <c r="B53" s="7" t="inlineStr">
         <is>
-          <t>driver_history</t>
+          <t>telematic_history</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
@@ -26556,11 +26556,11 @@
         </is>
       </c>
     </row>
-    <row r="54" ht="27" customHeight="1">
+    <row r="54">
       <c r="A54" s="6" t="n"/>
       <c r="B54" s="7" t="inlineStr">
         <is>
-          <t>charging_location_history</t>
+          <t>driver_history</t>
         </is>
       </c>
       <c r="C54" s="6" t="inlineStr">
@@ -26569,11 +26569,11 @@
         </is>
       </c>
     </row>
-    <row r="55">
+    <row r="55" ht="27" customHeight="1">
       <c r="A55" s="6" t="n"/>
       <c r="B55" s="7" t="inlineStr">
         <is>
-          <t>charging_station_history</t>
+          <t>charging_location_history</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
@@ -26586,7 +26586,7 @@
       <c r="A56" s="6" t="n"/>
       <c r="B56" s="7" t="inlineStr">
         <is>
-          <t>charging_evse_history</t>
+          <t>charging_station_history</t>
         </is>
       </c>
       <c r="C56" s="6" t="inlineStr">
@@ -26595,14 +26595,27 @@
         </is>
       </c>
     </row>
-    <row r="57" ht="27" customHeight="1">
+    <row r="57">
       <c r="A57" s="6" t="n"/>
       <c r="B57" s="7" t="inlineStr">
         <is>
+          <t>charging_evse_history</t>
+        </is>
+      </c>
+      <c r="C57" s="6" t="inlineStr">
+        <is>
+          <t>changed_by</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="27" customHeight="1">
+      <c r="A58" s="6" t="n"/>
+      <c r="B58" s="7" t="inlineStr">
+        <is>
           <t>charging_connector_history</t>
         </is>
       </c>
-      <c r="C57" s="6" t="inlineStr">
+      <c r="C58" s="6" t="inlineStr">
         <is>
           <t>changed_by</t>
         </is>
@@ -26631,23 +26644,24 @@
     <hyperlink ref="B38" location="'access_audit_logs'!A1"/>
     <hyperlink ref="B39" location="'charging_location_access'!A1"/>
     <hyperlink ref="B40" location="'charging_location_access'!A1"/>
-    <hyperlink ref="B41" location="'charging_policy_versions'!A1"/>
-    <hyperlink ref="B42" location="'organization_history'!A1"/>
-    <hyperlink ref="B43" location="'user_history'!A1"/>
+    <hyperlink ref="B41" location="'charging_sessions'!A1"/>
+    <hyperlink ref="B42" location="'charging_policy_versions'!A1"/>
+    <hyperlink ref="B43" location="'organization_history'!A1"/>
     <hyperlink ref="B44" location="'user_history'!A1"/>
-    <hyperlink ref="B45" location="'membership_history'!A1"/>
-    <hyperlink ref="B46" location="'organization_setting_history'!A1"/>
-    <hyperlink ref="B47" location="'vehicle_history'!A1"/>
-    <hyperlink ref="B48" location="'vehicle_model_history'!A1"/>
-    <hyperlink ref="B49" location="'battery_model_history'!A1"/>
-    <hyperlink ref="B50" location="'battery_history'!A1"/>
-    <hyperlink ref="B51" location="'warranty_history'!A1"/>
-    <hyperlink ref="B52" location="'telematic_history'!A1"/>
-    <hyperlink ref="B53" location="'driver_history'!A1"/>
-    <hyperlink ref="B54" location="'charging_location_history'!A1"/>
-    <hyperlink ref="B55" location="'charging_station_history'!A1"/>
-    <hyperlink ref="B56" location="'charging_evse_history'!A1"/>
-    <hyperlink ref="B57" location="'charging_connector_history'!A1"/>
+    <hyperlink ref="B45" location="'user_history'!A1"/>
+    <hyperlink ref="B46" location="'membership_history'!A1"/>
+    <hyperlink ref="B47" location="'organization_setting_history'!A1"/>
+    <hyperlink ref="B48" location="'vehicle_history'!A1"/>
+    <hyperlink ref="B49" location="'vehicle_model_history'!A1"/>
+    <hyperlink ref="B50" location="'battery_model_history'!A1"/>
+    <hyperlink ref="B51" location="'battery_history'!A1"/>
+    <hyperlink ref="B52" location="'warranty_history'!A1"/>
+    <hyperlink ref="B53" location="'telematic_history'!A1"/>
+    <hyperlink ref="B54" location="'driver_history'!A1"/>
+    <hyperlink ref="B55" location="'charging_location_history'!A1"/>
+    <hyperlink ref="B56" location="'charging_station_history'!A1"/>
+    <hyperlink ref="B57" location="'charging_evse_history'!A1"/>
+    <hyperlink ref="B58" location="'charging_connector_history'!A1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -36278,7 +36292,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I45"/>
+  <dimension ref="A1:I49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -36316,7 +36330,7 @@
     <row r="4">
       <c r="A4" s="11" t="inlineStr">
         <is>
-          <t>Một lần sạc trên một súng sạc, từ lúc bắt đầu đến lúc kết thúc. Cần quyết định khi rà soát bảng (CS-18): lần sạc bằng QR (CO-14) cần lưu ngữ cảnh nghiệp vụ ngay khi tài xế quét (ai quét, tổ chức nào trả tiền, mã gửi trong RemoteStartTransaction, câu trả lời của trụ) để ghép với StartTransaction mang mã đó: tạo dòng phiên PENDING khi quét, một bảng các lệnh gửi xuống trụ, hoặc cả hai.</t>
+          <t>Một lần sạc trên một súng của một trụ, từ lúc quét mã QR đến lúc dừng (CE-10). Dòng được tạo ở trạng thái PENDING khi tài xế quét mã QR trong ứng dụng của chúng ta, cùng tổ chức trả tiền, người quét và mã dùng một lần gửi trong lệnh bắt đầu từ xa; bản tin bắt đầu của chính trụ đó mang mã này chuyển phiên sang ACTIVE (CE-11), bản tin dừng chuyển sang COMPLETED; ABANDONED khi lần bắt đầu không xảy ra. Số liệu trực tiếp (kWh đã sạc, % pin, công suất cao nhất) đọc từ charging_session_measurements; đơn giá và số tiền thuộc bản ghi thanh toán (PAY-10). Không có lịch sử thay đổi và không xóa mềm: không ai sửa một phiên sạc. Ràng buộc kiểm tra (CE-10): phiên ACTIVE hoặc COMPLETED phải có mã giao dịch, EVSE, súng, thời điểm bắt đầu và chỉ số công tơ đầu; phiên COMPLETED phải có thời điểm kết thúc; phiên PENDING hoặc ABANDONED không có mã giao dịch.</t>
         </is>
       </c>
     </row>
@@ -36436,7 +36450,7 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>Trạm diễn ra phiên sạc.</t>
+          <t>Trụ sạc nơi diễn ra phiên sạc, biết được từ mã QR khi quét.</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr">
@@ -36446,7 +36460,7 @@
       </c>
       <c r="I8" s="6" t="n"/>
     </row>
-    <row r="9" ht="27" customHeight="1">
+    <row r="9" ht="54" customHeight="1">
       <c r="A9" s="6" t="n">
         <v>3</v>
       </c>
@@ -36477,7 +36491,7 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>EVSE được dùng.</t>
+          <t>EVSE được dùng, lấy từ bản tin bắt đầu của trụ. Dự kiến (CE-10): cho phép NULL, NULL khi PENDING và với phiên ABANDONED, vì tài xế chọn súng trên màn hình trụ sau khi quét (CO-14).</t>
         </is>
       </c>
       <c r="H9" s="6" t="inlineStr">
@@ -36487,7 +36501,7 @@
       </c>
       <c r="I9" s="6" t="n"/>
     </row>
-    <row r="10" ht="27" customHeight="1">
+    <row r="10" ht="40.5" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>4</v>
       </c>
@@ -36518,7 +36532,7 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>Súng sạc được dùng.</t>
+          <t>Súng sạc được dùng, lấy từ bản tin bắt đầu của trụ. Dự kiến (CE-10): cho phép NULL, NULL khi PENDING và với phiên ABANDONED.</t>
         </is>
       </c>
       <c r="H10" s="6" t="inlineStr">
@@ -36528,7 +36542,7 @@
       </c>
       <c r="I10" s="6" t="n"/>
     </row>
-    <row r="11" ht="27" customHeight="1">
+    <row r="11" ht="40.5" customHeight="1">
       <c r="A11" s="6" t="n">
         <v>5</v>
       </c>
@@ -36544,7 +36558,7 @@
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>có</t>
+          <t>không</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
@@ -36559,7 +36573,7 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>Tổ chức khách hàng bị tính tiền cho phiên sạc. (xem quyết định D5)</t>
+          <t>Tổ chức trả tiền: tổ chức mà người quét mã đại diện, ghi một lần khi quét và không đổi (DM-24 trường hợp C). Ví nào trong tổ chức trả tiền là câu hỏi mở D5.</t>
         </is>
       </c>
       <c r="H11" s="6" t="inlineStr">
@@ -36569,13 +36583,13 @@
       </c>
       <c r="I11" s="6" t="n"/>
     </row>
-    <row r="12" ht="27" customHeight="1">
+    <row r="12" ht="40.5" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>6</v>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>vehicle_id</t>
+          <t>started_by</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
@@ -36585,7 +36599,7 @@
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>có</t>
+          <t>không</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
@@ -36595,66 +36609,74 @@
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>vehicles.vehicle_id (khi xóa: chặn xóa)</t>
+          <t>users.user_id (khi xóa: chặn xóa)</t>
         </is>
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>Xe được sạc.</t>
+          <t>Người dùng đã quét mã QR trong ứng dụng của chúng ta; mọi lần sạc đều bắt đầu như vậy (CO-13). Lần bắt đầu mang mã không do chúng ta cấp bị từ chối và không tạo dòng (CE-11).</t>
         </is>
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>7a4c1e9b-3d2f-4b8a-a6c5-1e0d9f8b7a44</t>
+          <t>9b2e7d4a-1c3f-4a8e-b6d2-5e0f1a9c3d22</t>
         </is>
       </c>
       <c r="I12" s="6" t="n"/>
     </row>
-    <row r="13">
+    <row r="13" ht="54" customHeight="1">
       <c r="A13" s="6" t="n">
         <v>7</v>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>ocpp_transaction_id</t>
+          <t>vehicle_id</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>varchar(255)</t>
+          <t>uuid</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E13" s="6" t="n"/>
-      <c r="F13" s="6" t="n"/>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>vehicles.vehicle_id (khi xóa: chặn xóa)</t>
+        </is>
+      </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>Mã giao dịch dùng với trụ sạc, duy nhất trong trạm.</t>
+          <t>Xe được sạc, lấy khi quét mã từ phiên lái đang mở của tài xế quét mã (CHG-07); NULL nếu không có (xe khách vãng lai chưa có hồ sơ, hoặc tài xế chưa nhận xe). Sau này có thể lấy từ VIN hoặc địa chỉ MAC do trụ báo (deferred.md 90).</t>
         </is>
       </c>
       <c r="H13" s="6" t="inlineStr">
         <is>
-          <t>1042</t>
+          <t>7a4c1e9b-3d2f-4b8a-a6c5-1e0d9f8b7a44</t>
         </is>
       </c>
       <c r="I13" s="6" t="n"/>
     </row>
-    <row r="14" ht="27" customHeight="1">
+    <row r="14" ht="67.5" customHeight="1">
       <c r="A14" s="6" t="n">
         <v>8</v>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>ocpp_transaction_id</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>chargingsessionstatus</t>
+          <t>varchar(255)</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
@@ -36666,28 +36688,28 @@
       <c r="F14" s="6" t="n"/>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>Phiên sạc còn đang chạy hay đã xong.</t>
+          <t>Mã giao dịch của trụ, duy nhất trong mỗi trụ: trụ OCPP 2.0.1 tự chọn (chuỗi tối đa 36 ký tự); với 1.6J là số thứ tự của chúng ta dạng chữ (CE-03). Dự kiến (CE-10): varchar(36) và cho phép NULL, NULL khi PENDING và với phiên ABANDONED.</t>
         </is>
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>1042</t>
         </is>
       </c>
       <c r="I14" s="6" t="n"/>
     </row>
-    <row r="15">
+    <row r="15" ht="94.5" customHeight="1">
       <c r="A15" s="6" t="n">
         <v>9</v>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>started_at</t>
+          <t>status</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>timestamptz</t>
+          <t>chargingsessionstatus</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
@@ -36699,23 +36721,23 @@
       <c r="F15" s="6" t="n"/>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>Thời điểm bắt đầu sạc.</t>
+          <t>Vòng đời của phiên; là trạng thái quan sát được nên không có status_reason (DM-19). PENDING: đã nhận lượt quét, chờ trụ. ACTIVE: giao dịch đang chạy. COMPLETED: trụ đã dừng. ABANDONED: lệnh bắt đầu từ xa bị từ chối hoặc hết thời gian chờ, hoặc không có giao dịch nào trong khoảng thời gian cấu hình. Dự kiến (CE-10): giá trị viết hoa; PENDING và ABANDONED là giá trị mới.</t>
         </is>
       </c>
       <c r="H15" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15T08:30:00Z</t>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="I15" s="6" t="n"/>
     </row>
-    <row r="16">
+    <row r="16" ht="40.5" customHeight="1">
       <c r="A16" s="6" t="n">
         <v>10</v>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>ended_at</t>
+          <t>started_at</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
@@ -36725,35 +36747,35 @@
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>có</t>
+          <t>không</t>
         </is>
       </c>
       <c r="E16" s="6" t="n"/>
       <c r="F16" s="6" t="n"/>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>Thời điểm kết thúc sạc; NULL khi đang sạc.</t>
+          <t>Thời điểm bắt đầu theo đồng hồ của trụ. Dự kiến (CE-10): cho phép NULL, NULL khi PENDING và với phiên ABANDONED; thời điểm quét mã là created_at.</t>
         </is>
       </c>
       <c r="H16" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15T09:45:00Z</t>
+          <t>2026-09-15T08:30:00Z</t>
         </is>
       </c>
       <c r="I16" s="6" t="n"/>
     </row>
-    <row r="17">
+    <row r="17" ht="27" customHeight="1">
       <c r="A17" s="6" t="n">
         <v>11</v>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>meter_start_wh</t>
+          <t>ended_at</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>numeric(24,3)</t>
+          <t>timestamptz</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
@@ -36765,23 +36787,23 @@
       <c r="F17" s="6" t="n"/>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>Chỉ số công tơ của trụ lúc bắt đầu (Wh).</t>
+          <t>Thời điểm dừng theo đồng hồ của trụ; NULL cho đến khi COMPLETED.</t>
         </is>
       </c>
       <c r="H17" s="6" t="inlineStr">
         <is>
-          <t>1520340.000</t>
+          <t>2026-09-15T09:45:00Z</t>
         </is>
       </c>
       <c r="I17" s="6" t="n"/>
     </row>
-    <row r="18" ht="27" customHeight="1">
+    <row r="18">
       <c r="A18" s="6" t="n">
         <v>12</v>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>meter_end_wh</t>
+          <t>meter_start_wh</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
@@ -36798,28 +36820,28 @@
       <c r="F18" s="6" t="n"/>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>Chỉ số công tơ mới nhất được chấp nhận (Wh), không bao giờ lùi về thời gian trước.</t>
+          <t>Chỉ số công tơ trụ báo lúc bắt đầu (Wh); NULL khi PENDING.</t>
         </is>
       </c>
       <c r="H18" s="6" t="inlineStr">
         <is>
-          <t>1712840.000</t>
+          <t>1520340.000</t>
         </is>
       </c>
       <c r="I18" s="6" t="n"/>
     </row>
-    <row r="19">
+    <row r="19" ht="40.5" customHeight="1">
       <c r="A19" s="6" t="n">
         <v>13</v>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>meter_end_sampled_at</t>
+          <t>meter_end_wh</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>timestamptz</t>
+          <t>numeric(24,3)</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
@@ -36831,28 +36853,28 @@
       <c r="F19" s="6" t="n"/>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>Thời điểm đo meter_end_wh.</t>
+          <t>[Sẽ bỏ: CE-12] Chỉ số công tơ mới nhất được chấp nhận (Wh); là bản sao của số đo điện năng mới nhất trong charging_session_measurements, nay đọc ở đó.</t>
         </is>
       </c>
       <c r="H19" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15T09:44:30Z</t>
+          <t>1712840.000</t>
         </is>
       </c>
       <c r="I19" s="6" t="n"/>
     </row>
-    <row r="20">
+    <row r="20" ht="27" customHeight="1">
       <c r="A20" s="6" t="n">
         <v>14</v>
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>energy_delivered_wh</t>
+          <t>meter_end_sampled_at</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>numeric(24,3)</t>
+          <t>timestamptz</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
@@ -36864,28 +36886,28 @@
       <c r="F20" s="6" t="n"/>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>Điện năng đã cấp: chỉ số cuối trừ chỉ số đầu (Wh).</t>
+          <t>[Sẽ bỏ: CE-12] Thời điểm đo meter_end_wh; là sampled_at của số đo mới nhất.</t>
         </is>
       </c>
       <c r="H20" s="6" t="inlineStr">
         <is>
-          <t>192500.000</t>
+          <t>2026-09-15T09:44:30Z</t>
         </is>
       </c>
       <c r="I20" s="6" t="n"/>
     </row>
-    <row r="21" ht="27" customHeight="1">
+    <row r="21" ht="40.5" customHeight="1">
       <c r="A21" s="6" t="n">
         <v>15</v>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>id_tag</t>
+          <t>energy_delivered_wh</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>varchar(20)</t>
+          <t>numeric(24,3)</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
@@ -36897,28 +36919,28 @@
       <c r="F21" s="6" t="n"/>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>Mã định danh thô (RFID/token) đã bắt đầu phiên, đúng như trụ gửi; chưa được xác thực.</t>
+          <t>[Sẽ bỏ: CE-12] Giá trị suy ra: meter_stop_wh trừ meter_start_wh, tính khi đọc; số kWh tính tiền được chốt trên bản ghi thanh toán (PAY-10).</t>
         </is>
       </c>
       <c r="H21" s="6" t="inlineStr">
         <is>
-          <t>04A1B2C3D4E5F6</t>
+          <t>192500.000</t>
         </is>
       </c>
       <c r="I21" s="6" t="n"/>
     </row>
-    <row r="22">
+    <row r="22" ht="108" customHeight="1">
       <c r="A22" s="6" t="n">
         <v>16</v>
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>stop_reason</t>
+          <t>id_token</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>varchar(30)</t>
+          <t>varchar(20)</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
@@ -36930,28 +36952,28 @@
       <c r="F22" s="6" t="n"/>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>Lý do dừng sạc, theo trụ sạc báo.</t>
+          <t>[Hiện tên là id_tag, sẽ đổi tên] Mã định danh trụ báo cho giao dịch. Với lần sạc bằng QR, đó là mã dùng một lần chúng ta tạo khi quét và gửi trong lệnh bắt đầu từ xa (tối đa 20 ký tự, giới hạn idTag của OCPP 1.6J); trụ gửi lại mã này trong bản tin bắt đầu, nhờ đó bản tin tìm được dòng này (CE-11). Sau này còn là số thẻ hoặc mã Autocharge (CHG-08); không bao giờ chép vào log ứng dụng (IS-07). Dự kiến (CE-10): varchar(255) (độ dài của OCPP 2.1) và bắt buộc.</t>
         </is>
       </c>
       <c r="H22" s="6" t="inlineStr">
         <is>
-          <t>EVDisconnected</t>
+          <t>G3K7Q2M9X4T1</t>
         </is>
       </c>
       <c r="I22" s="6" t="n"/>
     </row>
-    <row r="23">
+    <row r="23" ht="54" customHeight="1">
       <c r="A23" s="6" t="n">
         <v>17</v>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>meter_stop_wh</t>
+          <t>stop_reason</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>numeric(24,3)</t>
+          <t>varchar(30)</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
@@ -36963,56 +36985,56 @@
       <c r="F23" s="6" t="n"/>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>Chỉ số công tơ lúc kết thúc do chính trụ sạc báo (Wh).</t>
+          <t>Lý do dừng theo trụ báo, giữ nguyên (reason của 1.6J, stoppedReason của 2.0.1); NULL nếu chưa COMPLETED. Lý do phiên bị ABANDONED không lưu ở đây mà thuộc về bản ghi lệnh bắt đầu từ xa chúng ta đã gửi (CS-18).</t>
         </is>
       </c>
       <c r="H23" s="6" t="inlineStr">
         <is>
-          <t>1712860.000</t>
+          <t>EVDisconnected</t>
         </is>
       </c>
       <c r="I23" s="6" t="n"/>
     </row>
-    <row r="24">
+    <row r="24" ht="54" customHeight="1">
       <c r="A24" s="6" t="n">
         <v>18</v>
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>meter_stop_wh</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>timestamptz</t>
+          <t>numeric(24,3)</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>không</t>
+          <t>có</t>
         </is>
       </c>
       <c r="E24" s="6" t="n"/>
       <c r="F24" s="6" t="n"/>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>Thời điểm tạo bản ghi (UTC).</t>
+          <t>Chỉ số công tơ trụ báo trong bản tin dừng (Wh): con số dùng để tính tiền (CE-12), luôn lưu đúng như trụ gửi (CE-03). NULL cho đến khi COMPLETED, hoặc khi bản tin dừng không có; khi đó tính tiền theo số đo mới nhất.</t>
         </is>
       </c>
       <c r="H24" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15T08:30:00Z</t>
+          <t>1712860.000</t>
         </is>
       </c>
       <c r="I24" s="6" t="n"/>
     </row>
-    <row r="25">
+    <row r="25" ht="27" customHeight="1">
       <c r="A25" s="6" t="n">
         <v>19</v>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>updated_at</t>
+          <t>created_at</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
@@ -37029,98 +37051,111 @@
       <c r="F25" s="6" t="n"/>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>Thời điểm bản ghi được sửa gần nhất (UTC).</t>
+          <t>Thời điểm tạo bản ghi (UTC): là thời điểm quét mã với lần sạc bằng QR.</t>
         </is>
       </c>
       <c r="H25" s="6" t="inlineStr">
         <is>
+          <t>2026-09-15T08:29:10Z</t>
+        </is>
+      </c>
+      <c r="I25" s="6" t="n"/>
+    </row>
+    <row r="26" ht="27" customHeight="1">
+      <c r="A26" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>updated_at</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>timestamptz</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E26" s="6" t="n"/>
+      <c r="F26" s="6" t="n"/>
+      <c r="G26" s="6" t="inlineStr">
+        <is>
+          <t>Thời điểm bản ghi được sửa gần nhất (UTC); thay đổi ở mỗi bước của phiên.</t>
+        </is>
+      </c>
+      <c r="H26" s="6" t="inlineStr">
+        <is>
           <t>2026-09-15T09:45:00Z</t>
         </is>
       </c>
-      <c r="I25" s="6" t="n"/>
-    </row>
-    <row r="26"/>
-    <row r="27">
-      <c r="A27" s="4" t="n"/>
-      <c r="B27" s="4" t="inlineStr">
+      <c r="I26" s="6" t="n"/>
+    </row>
+    <row r="27"/>
+    <row r="28">
+      <c r="A28" s="4" t="n"/>
+      <c r="B28" s="4" t="inlineStr">
         <is>
           <t>Kiểu enum</t>
         </is>
       </c>
-      <c r="C27" s="4" t="inlineStr">
+      <c r="C28" s="4" t="inlineStr">
         <is>
           <t>Giá trị cho phép</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="6" t="n"/>
-      <c r="B28" s="6" t="inlineStr">
+    <row r="29" ht="81" customHeight="1">
+      <c r="A29" s="6" t="n"/>
+      <c r="B29" s="6" t="inlineStr">
         <is>
           <t>chargingsessionstatus</t>
         </is>
       </c>
-      <c r="C28" s="6" t="inlineStr">
-        <is>
-          <t>active, completed</t>
-        </is>
-      </c>
-    </row>
-    <row r="29"/>
-    <row r="30">
-      <c r="A30" s="4" t="n"/>
-      <c r="B30" s="4" t="inlineStr">
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>active (sẽ bỏ), completed (sẽ bỏ), PENDING (dự kiến), ACTIVE (dự kiến), COMPLETED (dự kiến), ABANDONED (dự kiến)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30"/>
+    <row r="31">
+      <c r="A31" s="4" t="n"/>
+      <c r="B31" s="4" t="inlineStr">
         <is>
           <t>Chỉ mục (index)</t>
         </is>
       </c>
-      <c r="C30" s="4" t="inlineStr">
+      <c r="C31" s="4" t="inlineStr">
         <is>
           <t>Các cột</t>
         </is>
       </c>
-      <c r="D30" s="4" t="inlineStr">
+      <c r="D31" s="4" t="inlineStr">
         <is>
           <t>Duy nhất</t>
         </is>
       </c>
-      <c r="E30" s="4" t="n"/>
-      <c r="F30" s="4" t="inlineStr">
+      <c r="E31" s="4" t="n"/>
+      <c r="F31" s="4" t="inlineStr">
         <is>
           <t>Ghi chú</t>
         </is>
       </c>
-    </row>
-    <row r="31" ht="27" customHeight="1">
-      <c r="A31" s="6" t="n"/>
-      <c r="B31" s="6" t="inlineStr">
-        <is>
-          <t>ix_charging_sessions_ended_at</t>
-        </is>
-      </c>
-      <c r="C31" s="6" t="inlineStr">
-        <is>
-          <t>ended_at</t>
-        </is>
-      </c>
-      <c r="D31" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E31" s="6" t="n"/>
-      <c r="F31" s="6" t="n"/>
     </row>
     <row r="32" ht="27" customHeight="1">
       <c r="A32" s="6" t="n"/>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>ix_charging_sessions_status_updated</t>
+          <t>ix_charging_sessions_ended_at</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>status, updated_at</t>
+          <t>ended_at</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
@@ -37135,12 +37170,12 @@
       <c r="A33" s="6" t="n"/>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>ix_charging_sessions_station_status</t>
+          <t>ix_charging_sessions_status_updated</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>station_id, status</t>
+          <t>status, updated_at</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
@@ -37155,12 +37190,12 @@
       <c r="A34" s="6" t="n"/>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>ix_charging_sessions_evse_status</t>
+          <t>ix_charging_sessions_station_status</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>evse_id, status</t>
+          <t>station_id, status</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
@@ -37175,12 +37210,12 @@
       <c r="A35" s="6" t="n"/>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>ix_charging_sessions_connector_status</t>
+          <t>ix_charging_sessions_evse_status</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>connector_id, status</t>
+          <t>evse_id, status</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
@@ -37195,12 +37230,12 @@
       <c r="A36" s="6" t="n"/>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>ix_charging_sessions_started_at</t>
+          <t>ix_charging_sessions_connector_status</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>started_at</t>
+          <t>connector_id, status</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
@@ -37215,85 +37250,129 @@
       <c r="A37" s="6" t="n"/>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>uq_charging_sessions_station_transaction</t>
+          <t>ix_charging_sessions_started_at</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>station_id, ocpp_transaction_id</t>
+          <t>started_at</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>có</t>
+          <t>không</t>
         </is>
       </c>
       <c r="E37" s="6" t="n"/>
       <c r="F37" s="6" t="n"/>
     </row>
-    <row r="38"/>
-    <row r="39">
-      <c r="A39" s="4" t="n"/>
-      <c r="B39" s="4" t="inlineStr">
-        <is>
-          <t>Được tham chiếu bởi bảng</t>
-        </is>
-      </c>
-      <c r="C39" s="4" t="inlineStr">
-        <is>
-          <t>Cột</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
+    <row r="38" ht="27" customHeight="1">
+      <c r="A38" s="6" t="n"/>
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t>uq_charging_sessions_station_transaction</t>
+        </is>
+      </c>
+      <c r="C38" s="6" t="inlineStr">
+        <is>
+          <t>station_id, ocpp_transaction_id</t>
+        </is>
+      </c>
+      <c r="D38" s="6" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E38" s="6" t="n"/>
+      <c r="F38" s="6" t="inlineStr">
+        <is>
+          <t>Planned (CE-10): partial, WHERE ocpp_transaction_id IS NOT NULL</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="40.5" customHeight="1">
+      <c r="A39" s="6" t="n"/>
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>ix_charging_sessions_pending_token</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>station_id, id_token</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E39" s="6" t="n"/>
+      <c r="F39" s="6" t="inlineStr">
+        <is>
+          <t>Planned (CE-11): WHERE status = 'PENDING'; matches a start message to its scan</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="27" customHeight="1">
       <c r="A40" s="6" t="n"/>
-      <c r="B40" s="7" t="inlineStr">
-        <is>
-          <t>charging_session_events</t>
+      <c r="B40" s="6" t="inlineStr">
+        <is>
+          <t>ix_charging_sessions_organization_started</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>session_id</t>
+          <t>organization_id, started_at</t>
+        </is>
+      </c>
+      <c r="D40" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E40" s="6" t="n"/>
+      <c r="F40" s="6" t="inlineStr">
+        <is>
+          <t>Planned (CE-10): a customer's charging history (CHG-04)</t>
         </is>
       </c>
     </row>
     <row r="41" ht="27" customHeight="1">
       <c r="A41" s="6" t="n"/>
-      <c r="B41" s="7" t="inlineStr">
-        <is>
-          <t>charging_session_measurements</t>
+      <c r="B41" s="6" t="inlineStr">
+        <is>
+          <t>ix_charging_sessions_vehicle_id</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>session_id</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="6" t="n"/>
-      <c r="B42" s="7" t="inlineStr">
-        <is>
-          <t>policy_violations</t>
-        </is>
-      </c>
-      <c r="C42" s="6" t="inlineStr">
-        <is>
-          <t>session_id</t>
-        </is>
-      </c>
-    </row>
+          <t>vehicle_id</t>
+        </is>
+      </c>
+      <c r="D41" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E41" s="6" t="n"/>
+      <c r="F41" s="6" t="inlineStr">
+        <is>
+          <t>Planned (CE-13)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42"/>
     <row r="43">
-      <c r="A43" s="6" t="n"/>
-      <c r="B43" s="7" t="inlineStr">
-        <is>
-          <t>payments</t>
-        </is>
-      </c>
-      <c r="C43" s="6" t="inlineStr">
-        <is>
-          <t>session_id</t>
+      <c r="A43" s="4" t="n"/>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>Được tham chiếu bởi bảng</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>Cột</t>
         </is>
       </c>
     </row>
@@ -37301,7 +37380,7 @@
       <c r="A44" s="6" t="n"/>
       <c r="B44" s="7" t="inlineStr">
         <is>
-          <t>wallet_transactions</t>
+          <t>charging_session_events</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
@@ -37310,34 +37389,87 @@
         </is>
       </c>
     </row>
-    <row r="45">
+    <row r="45" ht="27" customHeight="1">
       <c r="A45" s="6" t="n"/>
       <c r="B45" s="7" t="inlineStr">
         <is>
+          <t>charging_session_measurements</t>
+        </is>
+      </c>
+      <c r="C45" s="6" t="inlineStr">
+        <is>
+          <t>session_id</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="6" t="n"/>
+      <c r="B46" s="7" t="inlineStr">
+        <is>
+          <t>policy_violations</t>
+        </is>
+      </c>
+      <c r="C46" s="6" t="inlineStr">
+        <is>
+          <t>session_id</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="6" t="n"/>
+      <c r="B47" s="7" t="inlineStr">
+        <is>
+          <t>payments</t>
+        </is>
+      </c>
+      <c r="C47" s="6" t="inlineStr">
+        <is>
+          <t>session_id</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="6" t="n"/>
+      <c r="B48" s="7" t="inlineStr">
+        <is>
+          <t>wallet_transactions</t>
+        </is>
+      </c>
+      <c r="C48" s="6" t="inlineStr">
+        <is>
+          <t>session_id</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="6" t="n"/>
+      <c r="B49" s="7" t="inlineStr">
+        <is>
           <t>invoice_lines</t>
         </is>
       </c>
-      <c r="C45" s="6" t="inlineStr">
+      <c r="C49" s="6" t="inlineStr">
         <is>
           <t>session_id</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A6:I25"/>
+  <autoFilter ref="A6:I26"/>
   <hyperlinks>
     <hyperlink ref="A2" location="'Tổng quan'!A1"/>
     <hyperlink ref="F8" location="'charging_stations'!A1"/>
     <hyperlink ref="F9" location="'charging_evses'!A1"/>
     <hyperlink ref="F10" location="'charging_connectors'!A1"/>
     <hyperlink ref="F11" location="'organizations'!A1"/>
-    <hyperlink ref="F12" location="'vehicles'!A1"/>
-    <hyperlink ref="B40" location="'charging_session_events'!A1"/>
-    <hyperlink ref="B41" location="'charging_session_measurements'!A1"/>
-    <hyperlink ref="B42" location="'policy_violations'!A1"/>
-    <hyperlink ref="B43" location="'payments'!A1"/>
-    <hyperlink ref="B44" location="'wallet_transactions'!A1"/>
-    <hyperlink ref="B45" location="'invoice_lines'!A1"/>
+    <hyperlink ref="F12" location="'users'!A1"/>
+    <hyperlink ref="F13" location="'vehicles'!A1"/>
+    <hyperlink ref="B44" location="'charging_session_events'!A1"/>
+    <hyperlink ref="B45" location="'charging_session_measurements'!A1"/>
+    <hyperlink ref="B46" location="'policy_violations'!A1"/>
+    <hyperlink ref="B47" location="'payments'!A1"/>
+    <hyperlink ref="B48" location="'wallet_transactions'!A1"/>
+    <hyperlink ref="B49" location="'invoice_lines'!A1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/design/domain-model/domain-model.xlsx
+++ b/docs/design/domain-model/domain-model.xlsx
@@ -3399,7 +3399,7 @@
         </is>
       </c>
     </row>
-    <row r="70" ht="27" customHeight="1">
+    <row r="70" ht="67.5" customHeight="1">
       <c r="A70" s="6" t="inlineStr">
         <is>
           <t>40</t>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="G70" s="6" t="inlineStr">
         <is>
-          <t>Mọi giá trị đo trụ sạc gửi trong phiên (điện năng, công suất, SOC...).</t>
+          <t>Mọi giá trị đo trụ sạc gửi trong phiên (điện năng, công suất, dòng điện, điện áp, SoC, nhiệt độ...), chỉ ghi thêm. Cổng OCPP lưu mỗi đại lượng đã biết theo một đơn vị cố định và điền giá trị mặc định của OCPP khi thiếu context hoặc điểm đo, nên nơi đọc không phải đổi đơn vị hay đoán giá trị mặc định (CE-14). Không có lịch sử thay đổi và không xóa mềm.</t>
         </is>
       </c>
       <c r="H70" s="6" t="n">
@@ -37878,7 +37878,7 @@
     <row r="4">
       <c r="A4" s="11" t="inlineStr">
         <is>
-          <t>Mọi giá trị đo trụ sạc gửi trong phiên (điện năng, công suất, SOC...).</t>
+          <t>Mọi giá trị đo trụ sạc gửi trong phiên (điện năng, công suất, dòng điện, điện áp, SoC, nhiệt độ...), chỉ ghi thêm. Cổng OCPP lưu mỗi đại lượng đã biết theo một đơn vị cố định và điền giá trị mặc định của OCPP khi thiếu context hoặc điểm đo, nên nơi đọc không phải đổi đơn vị hay đoán giá trị mặc định (CE-14). Không có lịch sử thay đổi và không xóa mềm.</t>
         </is>
       </c>
     </row>
@@ -37967,7 +37967,7 @@
       </c>
       <c r="I7" s="6" t="n"/>
     </row>
-    <row r="8">
+    <row r="8" ht="27" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>2</v>
       </c>
@@ -37994,7 +37994,7 @@
       <c r="F8" s="6" t="n"/>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>Thời điểm đo; cột thời gian của bảng chuỗi thời gian.</t>
+          <t>Thời điểm đo theo đồng hồ của trụ; cột thời gian của bảng chuỗi thời gian.</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr">
@@ -38004,7 +38004,7 @@
       </c>
       <c r="I8" s="6" t="n"/>
     </row>
-    <row r="9" ht="27" customHeight="1">
+    <row r="9" ht="40.5" customHeight="1">
       <c r="A9" s="6" t="n">
         <v>3</v>
       </c>
@@ -38035,7 +38035,7 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>Phiên sạc chứa số đo.</t>
+          <t>Phiên sạc chứa số đo. Số đo gửi ngoài phiên (lấy mẫu theo đồng hồ) chỉ được giữ trong nhật ký OCPP thô (CE-06, deferred.md 77).</t>
         </is>
       </c>
       <c r="H9" s="6" t="inlineStr">
@@ -38045,7 +38045,7 @@
       </c>
       <c r="I9" s="6" t="n"/>
     </row>
-    <row r="10">
+    <row r="10" ht="54" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>4</v>
       </c>
@@ -38068,7 +38068,7 @@
       <c r="F10" s="6" t="n"/>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>Đại lượng được đo, theo tên measurand của OCPP.</t>
+          <t>Đại lượng được đo, theo tên của OCPP (Energy.Active.Import.Register, Power.Active.Import, Current.Import, Voltage, SoC, Temperature); tên riêng của hãng được lưu đúng như gửi.</t>
         </is>
       </c>
       <c r="H10" s="6" t="inlineStr">
@@ -38078,7 +38078,7 @@
       </c>
       <c r="I10" s="6" t="n"/>
     </row>
-    <row r="11" ht="27" customHeight="1">
+    <row r="11" ht="94.5" customHeight="1">
       <c r="A11" s="6" t="n">
         <v>5</v>
       </c>
@@ -38101,7 +38101,7 @@
       <c r="F11" s="6" t="n"/>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>Giá trị đo; điện năng luôn lưu bằng Wh, các đại lượng khác theo đơn vị ở cột unit.</t>
+          <t>Giá trị đo. Hiện điện năng được lưu bằng Wh. Dự kiến (CE-14): cổng OCPP đổi mọi đại lượng đã biết sang một đơn vị cố định khi ghi: điện năng Wh (phản kháng varh), công suất W (phản kháng var, biểu kiến VA), dòng điện A, điện áp V, nhiệt độ Celsius, SoC và các tỷ lệ khác Percent; đơn vị kilo nhân 1000, Fahrenheit và K đổi sang Celsius. Đại lượng riêng của hãng được lưu đúng như gửi.</t>
         </is>
       </c>
       <c r="H11" s="6" t="inlineStr">
@@ -38111,7 +38111,7 @@
       </c>
       <c r="I11" s="6" t="n"/>
     </row>
-    <row r="12">
+    <row r="12" ht="40.5" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>6</v>
       </c>
@@ -38134,7 +38134,7 @@
       <c r="F12" s="6" t="n"/>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>Đơn vị của giá trị.</t>
+          <t>Đơn vị của giá trị, viết theo OCPP. Dự kiến (CE-14): luôn là đơn vị cố định của đại lượng đã biết; đúng như gửi, hoặc NULL, với đại lượng riêng của hãng.</t>
         </is>
       </c>
       <c r="H12" s="6" t="inlineStr">
@@ -38144,7 +38144,7 @@
       </c>
       <c r="I12" s="6" t="n"/>
     </row>
-    <row r="13">
+    <row r="13" ht="67.5" customHeight="1">
       <c r="A13" s="6" t="n">
         <v>7</v>
       </c>
@@ -38167,7 +38167,7 @@
       <c r="F13" s="6" t="n"/>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>Lý do trụ sạc gửi số đo.</t>
+          <t>Lý do trụ gửi số đo: Sample.Periodic, Transaction.Begin, Transaction.End, Sample.Clock, Trigger, Interruption.Begin, Interruption.End, Other. Dự kiến (CE-14): bắt buộc; lưu giá trị mặc định của OCPP là Sample.Periodic khi trụ không gửi.</t>
         </is>
       </c>
       <c r="H13" s="6" t="inlineStr">
@@ -38177,7 +38177,7 @@
       </c>
       <c r="I13" s="6" t="n"/>
     </row>
-    <row r="14">
+    <row r="14" ht="27" customHeight="1">
       <c r="A14" s="6" t="n">
         <v>8</v>
       </c>
@@ -38200,7 +38200,7 @@
       <c r="F14" s="6" t="n"/>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>Pha điện của giá trị; NULL với sạc DC.</t>
+          <t>Pha điện của giá trị (L1, L2, L3 ...); NULL với sạc DC, là mọi trụ chúng ta đang có.</t>
         </is>
       </c>
       <c r="H14" s="6" t="inlineStr">
@@ -38210,13 +38210,13 @@
       </c>
       <c r="I14" s="6" t="n"/>
     </row>
-    <row r="15">
+    <row r="15" ht="135" customHeight="1">
       <c r="A15" s="6" t="n">
         <v>9</v>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>location</t>
+          <t>measurement_location</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
@@ -38233,7 +38233,7 @@
       <c r="F15" s="6" t="n"/>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>Vị trí đo.</t>
+          <t>[Hiện tên là location, sẽ đổi tên] Điểm đo trên đường sạc (OCPP gọi là location): Outlet (đầu ra của trụ về phía xe: tiến trình trực tiếp và số dự phòng khi tính tiền), Inlet (đầu vào từ lưới: tổn thất và chi phí điện của chúng ta), Cable, EV (do xe báo, ví dụ SoC), Body (bên trong tủ trụ). Mọi điểm đo đều được lưu; hiện các tính năng chỉ đọc Outlet, và EV cho SoC (CE-14). Đổi tên vì location dễ hiểu nhầm là địa điểm (charging_locations). Dự kiến (CE-14): bắt buộc; lưu giá trị mặc định của OCPP là Outlet khi trụ không gửi.</t>
         </is>
       </c>
       <c r="H15" s="6" t="inlineStr">

--- a/docs/design/domain-model/domain-model.xlsx
+++ b/docs/design/domain-model/domain-model.xlsx
@@ -3285,7 +3285,7 @@
         </is>
       </c>
     </row>
-    <row r="67" ht="108" customHeight="1">
+    <row r="67" ht="121.5" customHeight="1">
       <c r="A67" s="5" t="n"/>
       <c r="B67" s="5" t="inlineStr">
         <is>
@@ -3305,7 +3305,7 @@
           <t>Những gì diễn ra trong mỗi lần sạc: sự kiện, chỉ số công tơ, điện năng đã cấp.
 • Một phiên sạc diễn ra trên một súng sạc của một trụ. Phiên được tạo khi tài xế quét mã QR trên trụ bằng ứng dụng của chúng ta (CE-10) và ghi người quét, tổ chức trả tiền và, nếu tài xế đang nhận một xe, chiếc xe đó; sau đó bản tin bắt đầu của trụ điền súng sạc và giao dịch (CE-11).
 • Bản đang chạy chưa có liên kết này (chỉ có mã id_tag thô); sẽ có khi tái cấu trúc.
-• Một phiên sạc có nhiều sự kiện và nhiều số đo.</t>
+• Một phiên sạc có nhiều số đo. Bảng sự kiện đã được xây dựng nhưng bị bỏ trong thiết kế đích (CE-15).</t>
         </is>
       </c>
     </row>
@@ -3354,7 +3354,7 @@
         </is>
       </c>
     </row>
-    <row r="69" ht="27" customHeight="1">
+    <row r="69" ht="81" customHeight="1">
       <c r="A69" s="6" t="inlineStr">
         <is>
           <t>39</t>
@@ -3387,7 +3387,7 @@
       </c>
       <c r="G69" s="6" t="inlineStr">
         <is>
-          <t>Từng sự kiện Bắt đầu / Cập nhật / Kết thúc của một phiên sạc.</t>
+          <t>[Sẽ bỏ] Từng sự kiện Bắt đầu / Cập nhật / Kết thúc của một phiên sạc. Bị bỏ trong thiết kế đích (CE-15): với OCPP 1.6J bảng chỉ chép lại thời điểm bắt đầu và kết thúc của phiên, nhật ký OCPP thô đã giữ mọi bản tin để kiểm tra, và chưa tính năng nào đọc dòng thời gian của phiên. Việc loại bản tin trùng của OCPP 2.0.1 (seqNo) và các khoảng trạng thái sạc được thiết kế khi xây dựng hỗ trợ 2.0.1 (deferred.md 78).</t>
         </is>
       </c>
       <c r="H69" s="6" t="n">
@@ -37519,7 +37519,7 @@
     <row r="4">
       <c r="A4" s="11" t="inlineStr">
         <is>
-          <t>Từng sự kiện Bắt đầu / Cập nhật / Kết thúc của một phiên sạc.</t>
+          <t>Từng sự kiện Bắt đầu / Cập nhật / Kết thúc của một phiên sạc. Bị bỏ trong thiết kế đích (CE-15): với OCPP 1.6J bảng chỉ chép lại thời điểm bắt đầu và kết thúc của phiên, nhật ký OCPP thô đã giữ mọi bản tin để kiểm tra, và chưa tính năng nào đọc dòng thời gian của phiên. Việc loại bản tin trùng của OCPP 2.0.1 (seqNo) và các khoảng trạng thái sạc được thiết kế khi xây dựng hỗ trợ 2.0.1 (deferred.md 78).</t>
         </is>
       </c>
     </row>

--- a/docs/design/domain-model/domain-model.xlsx
+++ b/docs/design/domain-model/domain-model.xlsx
@@ -60,29 +60,30 @@
     <sheet name="charging_ocpp_messages" sheetId="51" state="visible" r:id="rId51"/>
     <sheet name="charging_station_config_capture" sheetId="52" state="visible" r:id="rId52"/>
     <sheet name="charging_station_config_entries" sheetId="53" state="visible" r:id="rId53"/>
-    <sheet name="charging_sessions" sheetId="54" state="visible" r:id="rId54"/>
-    <sheet name="charging_session_events" sheetId="55" state="visible" r:id="rId55"/>
-    <sheet name="charging_session_measurements" sheetId="56" state="visible" r:id="rId56"/>
-    <sheet name="notifications" sheetId="57" state="visible" r:id="rId57"/>
-    <sheet name="support_cases" sheetId="58" state="visible" r:id="rId58"/>
-    <sheet name="repair_partners" sheetId="59" state="visible" r:id="rId59"/>
-    <sheet name="maintenance_bookings" sheetId="60" state="visible" r:id="rId60"/>
-    <sheet name="charging_policies" sheetId="61" state="visible" r:id="rId61"/>
-    <sheet name="charging_policy_versions" sheetId="62" state="visible" r:id="rId62"/>
-    <sheet name="charging_policy_assignments" sheetId="63" state="visible" r:id="rId63"/>
-    <sheet name="policy_violations" sheetId="64" state="visible" r:id="rId64"/>
-    <sheet name="tariffs" sheetId="65" state="visible" r:id="rId65"/>
-    <sheet name="payments" sheetId="66" state="visible" r:id="rId66"/>
-    <sheet name="wallets" sheetId="67" state="visible" r:id="rId67"/>
-    <sheet name="wallet_transactions" sheetId="68" state="visible" r:id="rId68"/>
-    <sheet name="invoices" sheetId="69" state="visible" r:id="rId69"/>
-    <sheet name="invoice_lines" sheetId="70" state="visible" r:id="rId70"/>
-    <sheet name="subscription_plans" sheetId="71" state="visible" r:id="rId71"/>
-    <sheet name="plan_features" sheetId="72" state="visible" r:id="rId72"/>
-    <sheet name="subscriptions" sheetId="73" state="visible" r:id="rId73"/>
-    <sheet name="driver_scores" sheetId="74" state="visible" r:id="rId74"/>
-    <sheet name="promotion_campaigns" sheetId="75" state="visible" r:id="rId75"/>
-    <sheet name="trips" sheetId="76" state="visible" r:id="rId76"/>
+    <sheet name="charging_station_commands" sheetId="54" state="visible" r:id="rId54"/>
+    <sheet name="charging_sessions" sheetId="55" state="visible" r:id="rId55"/>
+    <sheet name="charging_session_events" sheetId="56" state="visible" r:id="rId56"/>
+    <sheet name="charging_session_measurements" sheetId="57" state="visible" r:id="rId57"/>
+    <sheet name="notifications" sheetId="58" state="visible" r:id="rId58"/>
+    <sheet name="support_cases" sheetId="59" state="visible" r:id="rId59"/>
+    <sheet name="repair_partners" sheetId="60" state="visible" r:id="rId60"/>
+    <sheet name="maintenance_bookings" sheetId="61" state="visible" r:id="rId61"/>
+    <sheet name="charging_policies" sheetId="62" state="visible" r:id="rId62"/>
+    <sheet name="charging_policy_versions" sheetId="63" state="visible" r:id="rId63"/>
+    <sheet name="charging_policy_assignments" sheetId="64" state="visible" r:id="rId64"/>
+    <sheet name="policy_violations" sheetId="65" state="visible" r:id="rId65"/>
+    <sheet name="tariffs" sheetId="66" state="visible" r:id="rId66"/>
+    <sheet name="payments" sheetId="67" state="visible" r:id="rId67"/>
+    <sheet name="wallets" sheetId="68" state="visible" r:id="rId68"/>
+    <sheet name="wallet_transactions" sheetId="69" state="visible" r:id="rId69"/>
+    <sheet name="invoices" sheetId="70" state="visible" r:id="rId70"/>
+    <sheet name="invoice_lines" sheetId="71" state="visible" r:id="rId71"/>
+    <sheet name="subscription_plans" sheetId="72" state="visible" r:id="rId72"/>
+    <sheet name="plan_features" sheetId="73" state="visible" r:id="rId73"/>
+    <sheet name="subscriptions" sheetId="74" state="visible" r:id="rId74"/>
+    <sheet name="driver_scores" sheetId="75" state="visible" r:id="rId75"/>
+    <sheet name="promotion_campaigns" sheetId="76" state="visible" r:id="rId76"/>
+    <sheet name="trips" sheetId="77" state="visible" r:id="rId77"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'organizations'!$A$7:$I$20</definedName>
@@ -137,29 +138,30 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="50" hidden="1">'charging_ocpp_messages'!$A$6:$I$14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="51" hidden="1">'charging_station_config_capture'!$A$6:$I$14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="52" hidden="1">'charging_station_config_entries'!$A$6:$I$20</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="53" hidden="1">'charging_sessions'!$A$6:$I$26</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="54" hidden="1">'charging_session_events'!$A$6:$I$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="55" hidden="1">'charging_session_measurements'!$A$6:$I$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="56" hidden="1">'notifications'!$A$6:$I$16</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="57" hidden="1">'support_cases'!$A$6:$I$28</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="58" hidden="1">'repair_partners'!$A$6:$I$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="59" hidden="1">'maintenance_bookings'!$A$6:$I$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="60" hidden="1">'charging_policies'!$A$6:$I$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="61" hidden="1">'charging_policy_versions'!$A$6:$I$16</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="62" hidden="1">'charging_policy_assignments'!$A$6:$I$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="63" hidden="1">'policy_violations'!$A$6:$I$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="64" hidden="1">'tariffs'!$A$6:$I$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="65" hidden="1">'payments'!$A$6:$I$16</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="66" hidden="1">'wallets'!$A$6:$I$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="67" hidden="1">'wallet_transactions'!$A$6:$I$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="68" hidden="1">'invoices'!$A$6:$I$16</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="69" hidden="1">'invoice_lines'!$A$6:$I$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="70" hidden="1">'subscription_plans'!$A$6:$I$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="71" hidden="1">'plan_features'!$A$6:$I$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="72" hidden="1">'subscriptions'!$A$6:$I$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="73" hidden="1">'driver_scores'!$A$6:$I$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="74" hidden="1">'promotion_campaigns'!$A$6:$I$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="75" hidden="1">'trips'!$A$6:$I$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="53" hidden="1">'charging_station_commands'!$A$6:$I$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="54" hidden="1">'charging_sessions'!$A$6:$I$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="55" hidden="1">'charging_session_events'!$A$6:$I$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="56" hidden="1">'charging_session_measurements'!$A$6:$I$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="57" hidden="1">'notifications'!$A$6:$I$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="58" hidden="1">'support_cases'!$A$6:$I$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="59" hidden="1">'repair_partners'!$A$6:$I$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="60" hidden="1">'maintenance_bookings'!$A$6:$I$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="61" hidden="1">'charging_policies'!$A$6:$I$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="62" hidden="1">'charging_policy_versions'!$A$6:$I$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="63" hidden="1">'charging_policy_assignments'!$A$6:$I$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="64" hidden="1">'policy_violations'!$A$6:$I$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="65" hidden="1">'tariffs'!$A$6:$I$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="66" hidden="1">'payments'!$A$6:$I$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="67" hidden="1">'wallets'!$A$6:$I$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="68" hidden="1">'wallet_transactions'!$A$6:$I$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="69" hidden="1">'invoices'!$A$6:$I$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="70" hidden="1">'invoice_lines'!$A$6:$I$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="71" hidden="1">'subscription_plans'!$A$6:$I$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="72" hidden="1">'plan_features'!$A$6:$I$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="73" hidden="1">'subscriptions'!$A$6:$I$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="74" hidden="1">'driver_scores'!$A$6:$I$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="75" hidden="1">'promotion_campaigns'!$A$6:$I$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="76" hidden="1">'trips'!$A$6:$I$14</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -648,7 +650,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I118"/>
+  <dimension ref="A1:I119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -679,7 +681,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>75 bảng trong 16 miền nghiệp vụ: 57 bảng chính, 15 bảng lịch sử (N.h), 3 bảng trạng thái. Bấm vào tên bảng hoặc «→ Mở» để mở sheet chi tiết của bảng; chú giải và các quyết định còn mở nằm ở cuối trang.</t>
+          <t>76 bảng trong 16 miền nghiệp vụ: 58 bảng chính, 15 bảng lịch sử (N.h), 3 bảng trạng thái. Bấm vào tên bảng hoặc «→ Mở» để mở sheet chi tiết của bảng; chú giải và các quyết định còn mở nằm ở cuối trang.</t>
         </is>
       </c>
     </row>
@@ -2631,7 +2633,7 @@
         </is>
       </c>
     </row>
-    <row r="52" ht="81" customHeight="1">
+    <row r="52" ht="108" customHeight="1">
       <c r="A52" s="5" t="n"/>
       <c r="B52" s="5" t="inlineStr">
         <is>
@@ -2640,7 +2642,7 @@
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>14 bảng</t>
+          <t>15 bảng</t>
         </is>
       </c>
       <c r="D52" s="5" t="n"/>
@@ -2651,7 +2653,8 @@
           <t>Mạng lưới trạm sạc và kết nối OCPP tới từng trụ sạc (thuật ngữ: CS-09).
 • Một trạm là một nơi tài xế tới sạc, thuộc một tổ chức; trạm công cộng hoặc riêng, trạm riêng liệt kê các tổ chức khác được sạc tại đó (CS-10).
 • Một trạm có một hoặc nhiều trụ sạc (một kết nối OCPP); mỗi trụ có một hoặc nhiều EVSE, mỗi EVSE có một hoặc nhiều súng sạc.
-• Mọi bản tin OCPP và mọi bản chụp cấu hình đều được lưu theo trụ.</t>
+• Mọi bản tin OCPP và mọi bản chụp cấu hình đều được lưu theo trụ.
+• Mọi lệnh gửi tới trụ được lưu cùng câu trả lời; lệnh bắt đầu hoặc dừng từ xa trỏ tới phiên sạc của nó (CS-20).</t>
         </is>
       </c>
     </row>
@@ -3285,22 +3288,67 @@
         </is>
       </c>
     </row>
-    <row r="67" ht="121.5" customHeight="1">
-      <c r="A67" s="5" t="n"/>
-      <c r="B67" s="5" t="inlineStr">
+    <row r="67" ht="135" customHeight="1">
+      <c r="A67" s="6" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B67" s="6" t="inlineStr">
+        <is>
+          <t>Trạm sạc (charging_stations)</t>
+        </is>
+      </c>
+      <c r="C67" s="7" t="inlineStr">
+        <is>
+          <t>charging_station_commands</t>
+        </is>
+      </c>
+      <c r="D67" s="7" t="inlineStr">
+        <is>
+          <t>Lệnh gửi trụ sạc</t>
+        </is>
+      </c>
+      <c r="E67" s="6" t="inlineStr">
+        <is>
+          <t>Nội bộ</t>
+        </is>
+      </c>
+      <c r="F67" s="6" t="inlineStr">
+        <is>
+          <t>F-G2, F-H1</t>
+        </is>
+      </c>
+      <c r="G67" s="6" t="inlineStr">
+        <is>
+          <t>Mọi lệnh chúng ta gửi tới trụ sạc và câu trả lời (STN-10, CS-20): ai yêu cầu, vì sao, liên quan phiên sạc nào, và các kết quả không để lại bản tin trong nhật ký thô (chưa gửi, hết thời gian chờ). Gửi lệnh là khả năng của cổng OCPP nên bảng thuộc miền charging_stations, không thuộc charging_sessions. Ghi khi tạo lệnh và cập nhật một lần khi có trả lời; không có lịch sử thay đổi, không xóa mềm. Phần lớn câu trả lời chỉ là chấp nhận hay từ chối; kết quả thật đến sau bằng bản tin riêng. Bảng lệnh cho T-Box (telematic_commands, deferred.md 55) sẽ dùng cùng dạng. Ràng buộc kiểm tra (CS-20): lệnh NOT_SENT không có ocpp_message_id; lệnh đã có kết quả (không PENDING, không NOT_SENT) phải có answered_at.</t>
+        </is>
+      </c>
+      <c r="H67" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="I67" s="7" t="inlineStr">
+        <is>
+          <t>→ Mở</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="121.5" customHeight="1">
+      <c r="A68" s="5" t="n"/>
+      <c r="B68" s="5" t="inlineStr">
         <is>
           <t>Phiên sạc (charging_sessions)</t>
         </is>
       </c>
-      <c r="C67" s="5" t="inlineStr">
+      <c r="C68" s="5" t="inlineStr">
         <is>
           <t>3 bảng</t>
         </is>
       </c>
-      <c r="D67" s="5" t="n"/>
-      <c r="E67" s="5" t="n"/>
-      <c r="F67" s="5" t="n"/>
-      <c r="G67" s="5" t="inlineStr">
+      <c r="D68" s="5" t="n"/>
+      <c r="E68" s="5" t="n"/>
+      <c r="F68" s="5" t="n"/>
+      <c r="G68" s="5" t="inlineStr">
         <is>
           <t>Những gì diễn ra trong mỗi lần sạc: sự kiện, chỉ số công tơ, điện năng đã cấp.
 • Một phiên sạc diễn ra trên một súng sạc của một trụ. Phiên được tạo khi tài xế quét mã QR trên trụ bằng ứng dụng của chúng ta (CE-10) và ghi người quét, tổ chức trả tiền và, nếu tài xế đang nhận một xe, chiếc xe đó; sau đó bản tin bắt đầu của trụ điền súng sạc và giao dịch (CE-11).
@@ -3309,157 +3357,157 @@
         </is>
       </c>
     </row>
-    <row r="68" ht="148.5" customHeight="1">
-      <c r="A68" s="6" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="B68" s="6" t="inlineStr">
+    <row r="69" ht="148.5" customHeight="1">
+      <c r="A69" s="6" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B69" s="6" t="inlineStr">
         <is>
           <t>Phiên sạc (charging_sessions)</t>
         </is>
       </c>
-      <c r="C68" s="7" t="inlineStr">
+      <c r="C69" s="7" t="inlineStr">
         <is>
           <t>charging_sessions</t>
         </is>
       </c>
-      <c r="D68" s="7" t="inlineStr">
+      <c r="D69" s="7" t="inlineStr">
         <is>
           <t>Phiên sạc</t>
         </is>
       </c>
-      <c r="E68" s="6" t="inlineStr">
+      <c r="E69" s="6" t="inlineStr">
         <is>
           <t>Hai bên</t>
         </is>
       </c>
-      <c r="F68" s="6" t="inlineStr">
+      <c r="F69" s="6" t="inlineStr">
         <is>
           <t>F-B2, F-C5</t>
         </is>
       </c>
-      <c r="G68" s="6" t="inlineStr">
+      <c r="G69" s="6" t="inlineStr">
         <is>
           <t>Một lần sạc trên một súng của một trụ, từ lúc quét mã QR đến lúc dừng (CE-10). Dòng được tạo ở trạng thái PENDING khi tài xế quét mã QR trong ứng dụng của chúng ta, cùng tổ chức trả tiền, người quét và mã dùng một lần gửi trong lệnh bắt đầu từ xa; bản tin bắt đầu của chính trụ đó mang mã này chuyển phiên sang ACTIVE (CE-11), bản tin dừng chuyển sang COMPLETED; ABANDONED khi lần bắt đầu không xảy ra. Số liệu trực tiếp (kWh đã sạc, % pin, công suất cao nhất) đọc từ charging_session_measurements; đơn giá và số tiền thuộc bản ghi thanh toán (PAY-10). Không có lịch sử thay đổi và không xóa mềm: không ai sửa một phiên sạc. Ràng buộc kiểm tra (CE-10): phiên ACTIVE hoặc COMPLETED phải có mã giao dịch, EVSE, súng, thời điểm bắt đầu và chỉ số công tơ đầu; phiên COMPLETED phải có thời điểm kết thúc; phiên PENDING hoặc ABANDONED không có mã giao dịch.</t>
         </is>
       </c>
-      <c r="H68" s="6" t="n">
+      <c r="H69" s="6" t="n">
         <v>20</v>
       </c>
-      <c r="I68" s="7" t="inlineStr">
+      <c r="I69" s="7" t="inlineStr">
         <is>
           <t>→ Mở</t>
         </is>
       </c>
     </row>
-    <row r="69" ht="81" customHeight="1">
-      <c r="A69" s="6" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="B69" s="6" t="inlineStr">
+    <row r="70" ht="81" customHeight="1">
+      <c r="A70" s="6" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B70" s="6" t="inlineStr">
         <is>
           <t>Phiên sạc (charging_sessions)</t>
         </is>
       </c>
-      <c r="C69" s="7" t="inlineStr">
+      <c r="C70" s="7" t="inlineStr">
         <is>
           <t>charging_session_events</t>
         </is>
       </c>
-      <c r="D69" s="7" t="inlineStr">
+      <c r="D70" s="7" t="inlineStr">
         <is>
           <t>Sự kiện phiên sạc</t>
         </is>
       </c>
-      <c r="E69" s="6" t="inlineStr">
+      <c r="E70" s="6" t="inlineStr">
         <is>
           <t>Hai bên</t>
         </is>
       </c>
-      <c r="F69" s="6" t="inlineStr">
+      <c r="F70" s="6" t="inlineStr">
         <is>
           <t>F-B2</t>
         </is>
       </c>
-      <c r="G69" s="6" t="inlineStr">
+      <c r="G70" s="6" t="inlineStr">
         <is>
           <t>[Sẽ bỏ] Từng sự kiện Bắt đầu / Cập nhật / Kết thúc của một phiên sạc. Bị bỏ trong thiết kế đích (CE-15): với OCPP 1.6J bảng chỉ chép lại thời điểm bắt đầu và kết thúc của phiên, nhật ký OCPP thô đã giữ mọi bản tin để kiểm tra, và chưa tính năng nào đọc dòng thời gian của phiên. Việc loại bản tin trùng của OCPP 2.0.1 (seqNo) và các khoảng trạng thái sạc được thiết kế khi xây dựng hỗ trợ 2.0.1 (deferred.md 78).</t>
         </is>
       </c>
-      <c r="H69" s="6" t="n">
+      <c r="H70" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="I69" s="7" t="inlineStr">
+      <c r="I70" s="7" t="inlineStr">
         <is>
           <t>→ Mở</t>
         </is>
       </c>
     </row>
-    <row r="70" ht="67.5" customHeight="1">
-      <c r="A70" s="6" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="B70" s="6" t="inlineStr">
+    <row r="71" ht="67.5" customHeight="1">
+      <c r="A71" s="6" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B71" s="6" t="inlineStr">
         <is>
           <t>Phiên sạc (charging_sessions)</t>
         </is>
       </c>
-      <c r="C70" s="7" t="inlineStr">
+      <c r="C71" s="7" t="inlineStr">
         <is>
           <t>charging_session_measurements</t>
         </is>
       </c>
-      <c r="D70" s="7" t="inlineStr">
+      <c r="D71" s="7" t="inlineStr">
         <is>
           <t>Số đo phiên sạc</t>
         </is>
       </c>
-      <c r="E70" s="6" t="inlineStr">
+      <c r="E71" s="6" t="inlineStr">
         <is>
           <t>Hai bên</t>
         </is>
       </c>
-      <c r="F70" s="6" t="inlineStr">
+      <c r="F71" s="6" t="inlineStr">
         <is>
           <t>F-B2</t>
         </is>
       </c>
-      <c r="G70" s="6" t="inlineStr">
+      <c r="G71" s="6" t="inlineStr">
         <is>
           <t>Mọi giá trị đo trụ sạc gửi trong phiên (điện năng, công suất, dòng điện, điện áp, SoC, nhiệt độ...), chỉ ghi thêm. Cổng OCPP lưu mỗi đại lượng đã biết theo một đơn vị cố định và điền giá trị mặc định của OCPP khi thiếu context hoặc điểm đo, nên nơi đọc không phải đổi đơn vị hay đoán giá trị mặc định (CE-14). Không có lịch sử thay đổi và không xóa mềm.</t>
         </is>
       </c>
-      <c r="H70" s="6" t="n">
+      <c r="H71" s="6" t="n">
         <v>9</v>
       </c>
-      <c r="I70" s="7" t="inlineStr">
+      <c r="I71" s="7" t="inlineStr">
         <is>
           <t>→ Mở</t>
         </is>
       </c>
     </row>
-    <row r="71" ht="54" customHeight="1">
-      <c r="A71" s="5" t="n"/>
-      <c r="B71" s="5" t="inlineStr">
+    <row r="72" ht="54" customHeight="1">
+      <c r="A72" s="5" t="n"/>
+      <c r="B72" s="5" t="inlineStr">
         <is>
           <t>Thông báo &amp; cảnh báo (notifications)</t>
         </is>
       </c>
-      <c r="C71" s="5" t="inlineStr">
+      <c r="C72" s="5" t="inlineStr">
         <is>
           <t>1 bảng</t>
         </is>
       </c>
-      <c r="D71" s="5" t="n"/>
-      <c r="E71" s="5" t="n"/>
-      <c r="F71" s="5" t="n"/>
-      <c r="G71" s="5" t="inlineStr">
+      <c r="D72" s="5" t="n"/>
+      <c r="E72" s="5" t="n"/>
+      <c r="F72" s="5" t="n"/>
+      <c r="G72" s="5" t="inlineStr">
         <is>
           <t>Cảnh báo do các miền khác phát sinh, được lưu để người vận hành truy vấn.
 • Một thông báo thường nói về một xe.
@@ -3467,67 +3515,67 @@
         </is>
       </c>
     </row>
-    <row r="72" ht="27" customHeight="1">
-      <c r="A72" s="6" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="B72" s="6" t="inlineStr">
+    <row r="73" ht="27" customHeight="1">
+      <c r="A73" s="6" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B73" s="6" t="inlineStr">
         <is>
           <t>Thông báo &amp; cảnh báo (notifications)</t>
         </is>
       </c>
-      <c r="C72" s="7" t="inlineStr">
+      <c r="C73" s="7" t="inlineStr">
         <is>
           <t>notifications</t>
         </is>
       </c>
-      <c r="D72" s="7" t="inlineStr">
+      <c r="D73" s="7" t="inlineStr">
         <is>
           <t>Thông báo</t>
         </is>
       </c>
-      <c r="E72" s="6" t="inlineStr">
+      <c r="E73" s="6" t="inlineStr">
         <is>
           <t>Khách hàng</t>
         </is>
       </c>
-      <c r="F72" s="6" t="inlineStr">
+      <c r="F73" s="6" t="inlineStr">
         <is>
           <t>F-A2, F-A3, F-A4, F-J1, F-J3</t>
         </is>
       </c>
-      <c r="G72" s="6" t="inlineStr">
+      <c r="G73" s="6" t="inlineStr">
         <is>
           <t>Một cảnh báo (pin, bất thường, SOH, thiết bị mất kết nối...). Một bảng chung; mỗi loại cảnh báo là một giá trị enum và một cấu trúc payload.</t>
         </is>
       </c>
-      <c r="H72" s="6" t="n">
+      <c r="H73" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="I72" s="7" t="inlineStr">
+      <c r="I73" s="7" t="inlineStr">
         <is>
           <t>→ Mở</t>
         </is>
       </c>
     </row>
-    <row r="73" ht="81" customHeight="1">
-      <c r="A73" s="5" t="n"/>
-      <c r="B73" s="5" t="inlineStr">
+    <row r="74" ht="81" customHeight="1">
+      <c r="A74" s="5" t="n"/>
+      <c r="B74" s="5" t="inlineStr">
         <is>
           <t>CSKH &amp; cứu hộ (support)</t>
         </is>
       </c>
-      <c r="C73" s="5" t="inlineStr">
+      <c r="C74" s="5" t="inlineStr">
         <is>
           <t>3 bảng</t>
         </is>
       </c>
-      <c r="D73" s="5" t="n"/>
-      <c r="E73" s="5" t="n"/>
-      <c r="F73" s="5" t="n"/>
-      <c r="G73" s="5" t="inlineStr">
+      <c r="D74" s="5" t="n"/>
+      <c r="E74" s="5" t="n"/>
+      <c r="F74" s="5" t="n"/>
+      <c r="G74" s="5" t="inlineStr">
         <is>
           <t>Chăm sóc khách hàng: yêu cầu hỗ trợ, SOS, điều phối cứu hộ và đặt lịch bảo dưỡng.
 • Một ca hỗ trợ (yêu cầu thường hoặc SOS) liên quan đến một xe và/hoặc một tài xế của một tổ chức.
@@ -3536,51 +3584,6 @@
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="6" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="B74" s="6" t="inlineStr">
-        <is>
-          <t>CSKH &amp; cứu hộ (support)</t>
-        </is>
-      </c>
-      <c r="C74" s="7" t="inlineStr">
-        <is>
-          <t>support_cases</t>
-        </is>
-      </c>
-      <c r="D74" s="7" t="inlineStr">
-        <is>
-          <t>Ca hỗ trợ</t>
-        </is>
-      </c>
-      <c r="E74" s="6" t="inlineStr">
-        <is>
-          <t>Khách hàng</t>
-        </is>
-      </c>
-      <c r="F74" s="6" t="inlineStr">
-        <is>
-          <t>F-I1, F-I2</t>
-        </is>
-      </c>
-      <c r="G74" s="6" t="inlineStr">
-        <is>
-          <t>Một yêu cầu hỗ trợ: yêu cầu thường hoặc SOS, kèm mốc thời gian SLA.</t>
-        </is>
-      </c>
-      <c r="H74" s="6" t="n">
-        <v>22</v>
-      </c>
-      <c r="I74" s="7" t="inlineStr">
-        <is>
-          <t>→ Mở</t>
-        </is>
-      </c>
-    </row>
     <row r="75">
       <c r="A75" s="6" t="inlineStr">
         <is>
@@ -3594,31 +3597,31 @@
       </c>
       <c r="C75" s="7" t="inlineStr">
         <is>
-          <t>repair_partners</t>
+          <t>support_cases</t>
         </is>
       </c>
       <c r="D75" s="7" t="inlineStr">
         <is>
-          <t>Đối tác sửa chữa &amp; cứu hộ</t>
+          <t>Ca hỗ trợ</t>
         </is>
       </c>
       <c r="E75" s="6" t="inlineStr">
         <is>
-          <t>Nội bộ</t>
+          <t>Khách hàng</t>
         </is>
       </c>
       <c r="F75" s="6" t="inlineStr">
         <is>
-          <t>F-I4, F-I3</t>
+          <t>F-I1, F-I2</t>
         </is>
       </c>
       <c r="G75" s="6" t="inlineStr">
         <is>
-          <t>Một xưởng hoặc đơn vị cứu hộ mà CSKH có thể điều phối tới.</t>
+          <t>Một yêu cầu hỗ trợ: yêu cầu thường hoặc SOS, kèm mốc thời gian SLA.</t>
         </is>
       </c>
       <c r="H75" s="6" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="I75" s="7" t="inlineStr">
         <is>
@@ -3639,27 +3642,27 @@
       </c>
       <c r="C76" s="7" t="inlineStr">
         <is>
-          <t>maintenance_bookings</t>
+          <t>repair_partners</t>
         </is>
       </c>
       <c r="D76" s="7" t="inlineStr">
         <is>
-          <t>Lịch bảo dưỡng</t>
+          <t>Đối tác sửa chữa &amp; cứu hộ</t>
         </is>
       </c>
       <c r="E76" s="6" t="inlineStr">
         <is>
-          <t>Khách hàng</t>
+          <t>Nội bộ</t>
         </is>
       </c>
       <c r="F76" s="6" t="inlineStr">
         <is>
-          <t>F-I3</t>
+          <t>F-I4, F-I3</t>
         </is>
       </c>
       <c r="G76" s="6" t="inlineStr">
         <is>
-          <t>Một lịch hẹn bảo dưỡng xe tại xưởng đối tác.</t>
+          <t>Một xưởng hoặc đơn vị cứu hộ mà CSKH có thể điều phối tới.</t>
         </is>
       </c>
       <c r="H76" s="6" t="n">
@@ -3671,22 +3674,67 @@
         </is>
       </c>
     </row>
-    <row r="77" ht="81" customHeight="1">
-      <c r="A77" s="5" t="n"/>
-      <c r="B77" s="5" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="6" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="B77" s="6" t="inlineStr">
+        <is>
+          <t>CSKH &amp; cứu hộ (support)</t>
+        </is>
+      </c>
+      <c r="C77" s="7" t="inlineStr">
+        <is>
+          <t>maintenance_bookings</t>
+        </is>
+      </c>
+      <c r="D77" s="7" t="inlineStr">
+        <is>
+          <t>Lịch bảo dưỡng</t>
+        </is>
+      </c>
+      <c r="E77" s="6" t="inlineStr">
+        <is>
+          <t>Khách hàng</t>
+        </is>
+      </c>
+      <c r="F77" s="6" t="inlineStr">
+        <is>
+          <t>F-I3</t>
+        </is>
+      </c>
+      <c r="G77" s="6" t="inlineStr">
+        <is>
+          <t>Một lịch hẹn bảo dưỡng xe tại xưởng đối tác.</t>
+        </is>
+      </c>
+      <c r="H77" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="I77" s="7" t="inlineStr">
+        <is>
+          <t>→ Mở</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="81" customHeight="1">
+      <c r="A78" s="5" t="n"/>
+      <c r="B78" s="5" t="inlineStr">
         <is>
           <t>Chính sách sạc (bảo hành) (policy)</t>
         </is>
       </c>
-      <c r="C77" s="5" t="inlineStr">
+      <c r="C78" s="5" t="inlineStr">
         <is>
           <t>4 bảng</t>
         </is>
       </c>
-      <c r="D77" s="5" t="n"/>
-      <c r="E77" s="5" t="n"/>
-      <c r="F77" s="5" t="n"/>
-      <c r="G77" s="5" t="inlineStr">
+      <c r="D78" s="5" t="n"/>
+      <c r="E78" s="5" t="n"/>
+      <c r="F78" s="5" t="n"/>
+      <c r="G78" s="5" t="inlineStr">
         <is>
           <t>Quy tắc sạc gắn với bảo hành và các vi phạm được phát hiện.
 • Một chính sách có nhiều phiên bản không sửa được; giá trị cụ thể do G3 Mobility quyết định.
@@ -3695,51 +3743,6 @@
         </is>
       </c>
     </row>
-    <row r="78" ht="27" customHeight="1">
-      <c r="A78" s="6" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="B78" s="6" t="inlineStr">
-        <is>
-          <t>Chính sách sạc (bảo hành) (policy)</t>
-        </is>
-      </c>
-      <c r="C78" s="7" t="inlineStr">
-        <is>
-          <t>charging_policies</t>
-        </is>
-      </c>
-      <c r="D78" s="7" t="inlineStr">
-        <is>
-          <t>Chính sách sạc</t>
-        </is>
-      </c>
-      <c r="E78" s="6" t="inlineStr">
-        <is>
-          <t>Nội bộ</t>
-        </is>
-      </c>
-      <c r="F78" s="6" t="inlineStr">
-        <is>
-          <t>F-B1</t>
-        </is>
-      </c>
-      <c r="G78" s="6" t="inlineStr">
-        <is>
-          <t>Một chính sách sạc bảo hành có tên do G3 Mobility định nghĩa.</t>
-        </is>
-      </c>
-      <c r="H78" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="I78" s="7" t="inlineStr">
-        <is>
-          <t>→ Mở</t>
-        </is>
-      </c>
-    </row>
     <row r="79" ht="27" customHeight="1">
       <c r="A79" s="6" t="inlineStr">
         <is>
@@ -3753,12 +3756,12 @@
       </c>
       <c r="C79" s="7" t="inlineStr">
         <is>
-          <t>charging_policy_versions</t>
+          <t>charging_policies</t>
         </is>
       </c>
       <c r="D79" s="7" t="inlineStr">
         <is>
-          <t>Phiên bản chính sách sạc</t>
+          <t>Chính sách sạc</t>
         </is>
       </c>
       <c r="E79" s="6" t="inlineStr">
@@ -3773,11 +3776,11 @@
       </c>
       <c r="G79" s="6" t="inlineStr">
         <is>
-          <t>Một phiên bản quy tắc không sửa được của chính sách. Mọi phiên bản đều được giữ để kiểm toán.</t>
+          <t>Một chính sách sạc bảo hành có tên do G3 Mobility định nghĩa.</t>
         </is>
       </c>
       <c r="H79" s="6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I79" s="7" t="inlineStr">
         <is>
@@ -3798,17 +3801,17 @@
       </c>
       <c r="C80" s="7" t="inlineStr">
         <is>
-          <t>charging_policy_assignments</t>
+          <t>charging_policy_versions</t>
         </is>
       </c>
       <c r="D80" s="7" t="inlineStr">
         <is>
-          <t>Áp dụng chính sách sạc</t>
+          <t>Phiên bản chính sách sạc</t>
         </is>
       </c>
       <c r="E80" s="6" t="inlineStr">
         <is>
-          <t>Khách hàng</t>
+          <t>Nội bộ</t>
         </is>
       </c>
       <c r="F80" s="6" t="inlineStr">
@@ -3818,11 +3821,11 @@
       </c>
       <c r="G80" s="6" t="inlineStr">
         <is>
-          <t>Chính sách nào áp dụng cho một xe, một đội xe hay một dòng xe.</t>
+          <t>Một phiên bản quy tắc không sửa được của chính sách. Mọi phiên bản đều được giữ để kiểm toán.</t>
         </is>
       </c>
       <c r="H80" s="6" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I80" s="7" t="inlineStr">
         <is>
@@ -3843,12 +3846,12 @@
       </c>
       <c r="C81" s="7" t="inlineStr">
         <is>
-          <t>policy_violations</t>
+          <t>charging_policy_assignments</t>
         </is>
       </c>
       <c r="D81" s="7" t="inlineStr">
         <is>
-          <t>Vi phạm chính sách sạc</t>
+          <t>Áp dụng chính sách sạc</t>
         </is>
       </c>
       <c r="E81" s="6" t="inlineStr">
@@ -3858,12 +3861,12 @@
       </c>
       <c r="F81" s="6" t="inlineStr">
         <is>
-          <t>F-B3, F-B6</t>
+          <t>F-B1</t>
         </is>
       </c>
       <c r="G81" s="6" t="inlineStr">
         <is>
-          <t>Một phiên sạc vi phạm chính sách, kèm bằng chứng. Hệ quả của vi phạm vẫn là câu hỏi kinh doanh còn mở (mục 3 của feature-list).</t>
+          <t>Chính sách nào áp dụng cho một xe, một đội xe hay một dòng xe.</t>
         </is>
       </c>
       <c r="H81" s="6" t="n">
@@ -3875,22 +3878,67 @@
         </is>
       </c>
     </row>
-    <row r="82" ht="283.5" customHeight="1">
-      <c r="A82" s="5" t="n"/>
-      <c r="B82" s="5" t="inlineStr">
+    <row r="82" ht="27" customHeight="1">
+      <c r="A82" s="6" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="B82" s="6" t="inlineStr">
+        <is>
+          <t>Chính sách sạc (bảo hành) (policy)</t>
+        </is>
+      </c>
+      <c r="C82" s="7" t="inlineStr">
+        <is>
+          <t>policy_violations</t>
+        </is>
+      </c>
+      <c r="D82" s="7" t="inlineStr">
+        <is>
+          <t>Vi phạm chính sách sạc</t>
+        </is>
+      </c>
+      <c r="E82" s="6" t="inlineStr">
+        <is>
+          <t>Khách hàng</t>
+        </is>
+      </c>
+      <c r="F82" s="6" t="inlineStr">
+        <is>
+          <t>F-B3, F-B6</t>
+        </is>
+      </c>
+      <c r="G82" s="6" t="inlineStr">
+        <is>
+          <t>Một phiên sạc vi phạm chính sách, kèm bằng chứng. Hệ quả của vi phạm vẫn là câu hỏi kinh doanh còn mở (mục 3 của feature-list).</t>
+        </is>
+      </c>
+      <c r="H82" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="I82" s="7" t="inlineStr">
+        <is>
+          <t>→ Mở</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="283.5" customHeight="1">
+      <c r="A83" s="5" t="n"/>
+      <c r="B83" s="5" t="inlineStr">
         <is>
           <t>Thanh toán &amp; hóa đơn (billing)</t>
         </is>
       </c>
-      <c r="C82" s="5" t="inlineStr">
+      <c r="C83" s="5" t="inlineStr">
         <is>
           <t>9 bảng</t>
         </is>
       </c>
-      <c r="D82" s="5" t="n"/>
-      <c r="E82" s="5" t="n"/>
-      <c r="F82" s="5" t="n"/>
-      <c r="G82" s="5" t="inlineStr">
+      <c r="D83" s="5" t="n"/>
+      <c r="E83" s="5" t="n"/>
+      <c r="F83" s="5" t="n"/>
+      <c r="G83" s="5" t="inlineStr">
         <is>
           <t>Tiền: giá điện, thanh toán, ví trả trước, hóa đơn điện tử và thuê bao SaaS.
 • Biểu giá định giá điện cho toàn mạng hoặc từng trạm, theo khung giờ.
@@ -3902,51 +3950,6 @@
         </is>
       </c>
     </row>
-    <row r="83" ht="27" customHeight="1">
-      <c r="A83" s="6" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="B83" s="6" t="inlineStr">
-        <is>
-          <t>Thanh toán &amp; hóa đơn (billing)</t>
-        </is>
-      </c>
-      <c r="C83" s="7" t="inlineStr">
-        <is>
-          <t>tariffs</t>
-        </is>
-      </c>
-      <c r="D83" s="7" t="inlineStr">
-        <is>
-          <t>Biểu giá điện</t>
-        </is>
-      </c>
-      <c r="E83" s="6" t="inlineStr">
-        <is>
-          <t>Nội bộ</t>
-        </is>
-      </c>
-      <c r="F83" s="6" t="inlineStr">
-        <is>
-          <t>F-C8, F-H1</t>
-        </is>
-      </c>
-      <c r="G83" s="6" t="inlineStr">
-        <is>
-          <t>Giá điện. Ai sở hữu biểu giá (G3 Energy hay G3 Network) là mục 5 của feature-list.</t>
-        </is>
-      </c>
-      <c r="H83" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="I83" s="7" t="inlineStr">
-        <is>
-          <t>→ Mở</t>
-        </is>
-      </c>
-    </row>
     <row r="84" ht="27" customHeight="1">
       <c r="A84" s="6" t="inlineStr">
         <is>
@@ -3960,31 +3963,31 @@
       </c>
       <c r="C84" s="7" t="inlineStr">
         <is>
-          <t>payments</t>
+          <t>tariffs</t>
         </is>
       </c>
       <c r="D84" s="7" t="inlineStr">
         <is>
-          <t>Thanh toán</t>
+          <t>Biểu giá điện</t>
         </is>
       </c>
       <c r="E84" s="6" t="inlineStr">
         <is>
-          <t>Khách hàng</t>
+          <t>Nội bộ</t>
         </is>
       </c>
       <c r="F84" s="6" t="inlineStr">
         <is>
-          <t>F-H1</t>
+          <t>F-C8, F-H1</t>
         </is>
       </c>
       <c r="G84" s="6" t="inlineStr">
         <is>
-          <t>Một lần thanh toán qua cổng thanh toán hoặc ví, thường cho một phiên sạc.</t>
+          <t>Giá điện. Ai sở hữu biểu giá (G3 Energy hay G3 Network) là mục 5 của feature-list.</t>
         </is>
       </c>
       <c r="H84" s="6" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I84" s="7" t="inlineStr">
         <is>
@@ -4005,12 +4008,12 @@
       </c>
       <c r="C85" s="7" t="inlineStr">
         <is>
-          <t>wallets</t>
+          <t>payments</t>
         </is>
       </c>
       <c r="D85" s="7" t="inlineStr">
         <is>
-          <t>Ví</t>
+          <t>Thanh toán</t>
         </is>
       </c>
       <c r="E85" s="6" t="inlineStr">
@@ -4020,16 +4023,16 @@
       </c>
       <c r="F85" s="6" t="inlineStr">
         <is>
-          <t>F-H2</t>
+          <t>F-H1</t>
         </is>
       </c>
       <c r="G85" s="6" t="inlineStr">
         <is>
-          <t>Số dư trả trước của một tài xế hoặc của cả tổ chức.</t>
+          <t>Một lần thanh toán qua cổng thanh toán hoặc ví, thường cho một phiên sạc.</t>
         </is>
       </c>
       <c r="H85" s="6" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I85" s="7" t="inlineStr">
         <is>
@@ -4050,12 +4053,12 @@
       </c>
       <c r="C86" s="7" t="inlineStr">
         <is>
-          <t>wallet_transactions</t>
+          <t>wallets</t>
         </is>
       </c>
       <c r="D86" s="7" t="inlineStr">
         <is>
-          <t>Giao dịch ví</t>
+          <t>Ví</t>
         </is>
       </c>
       <c r="E86" s="6" t="inlineStr">
@@ -4070,11 +4073,11 @@
       </c>
       <c r="G86" s="6" t="inlineStr">
         <is>
-          <t>Biến động tiền vào/ra khỏi ví, chỉ ghi thêm.</t>
+          <t>Số dư trả trước của một tài xế hoặc của cả tổ chức.</t>
         </is>
       </c>
       <c r="H86" s="6" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I86" s="7" t="inlineStr">
         <is>
@@ -4095,12 +4098,12 @@
       </c>
       <c r="C87" s="7" t="inlineStr">
         <is>
-          <t>invoices</t>
+          <t>wallet_transactions</t>
         </is>
       </c>
       <c r="D87" s="7" t="inlineStr">
         <is>
-          <t>Hóa đơn</t>
+          <t>Giao dịch ví</t>
         </is>
       </c>
       <c r="E87" s="6" t="inlineStr">
@@ -4110,16 +4113,16 @@
       </c>
       <c r="F87" s="6" t="inlineStr">
         <is>
-          <t>F-H3, F-H4</t>
+          <t>F-H2</t>
         </is>
       </c>
       <c r="G87" s="6" t="inlineStr">
         <is>
-          <t>Một hóa đơn điện tử hợp lệ. Khi đã PHÁT HÀNH thì không sửa, chỉ điều chỉnh hoặc hủy bằng hóa đơn mới.</t>
+          <t>Biến động tiền vào/ra khỏi ví, chỉ ghi thêm.</t>
         </is>
       </c>
       <c r="H87" s="6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I87" s="7" t="inlineStr">
         <is>
@@ -4140,303 +4143,303 @@
       </c>
       <c r="C88" s="7" t="inlineStr">
         <is>
+          <t>invoices</t>
+        </is>
+      </c>
+      <c r="D88" s="7" t="inlineStr">
+        <is>
+          <t>Hóa đơn</t>
+        </is>
+      </c>
+      <c r="E88" s="6" t="inlineStr">
+        <is>
+          <t>Khách hàng</t>
+        </is>
+      </c>
+      <c r="F88" s="6" t="inlineStr">
+        <is>
+          <t>F-H3, F-H4</t>
+        </is>
+      </c>
+      <c r="G88" s="6" t="inlineStr">
+        <is>
+          <t>Một hóa đơn điện tử hợp lệ. Khi đã PHÁT HÀNH thì không sửa, chỉ điều chỉnh hoặc hủy bằng hóa đơn mới.</t>
+        </is>
+      </c>
+      <c r="H88" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="I88" s="7" t="inlineStr">
+        <is>
+          <t>→ Mở</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="27" customHeight="1">
+      <c r="A89" s="6" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="B89" s="6" t="inlineStr">
+        <is>
+          <t>Thanh toán &amp; hóa đơn (billing)</t>
+        </is>
+      </c>
+      <c r="C89" s="7" t="inlineStr">
+        <is>
           <t>invoice_lines</t>
         </is>
       </c>
-      <c r="D88" s="7" t="inlineStr">
+      <c r="D89" s="7" t="inlineStr">
         <is>
           <t>Dòng hóa đơn</t>
         </is>
       </c>
-      <c r="E88" s="6" t="inlineStr">
+      <c r="E89" s="6" t="inlineStr">
         <is>
           <t>Khách hàng</t>
         </is>
       </c>
-      <c r="F88" s="6" t="inlineStr">
+      <c r="F89" s="6" t="inlineStr">
         <is>
           <t>F-H3, F-H4</t>
         </is>
       </c>
-      <c r="G88" s="6" t="inlineStr">
+      <c r="G89" s="6" t="inlineStr">
         <is>
           <t>Một dòng của hóa đơn: một phiên sạc hoặc một kỳ thuê bao.</t>
         </is>
       </c>
-      <c r="H88" s="6" t="n">
+      <c r="H89" s="6" t="n">
         <v>9</v>
       </c>
-      <c r="I88" s="7" t="inlineStr">
+      <c r="I89" s="7" t="inlineStr">
         <is>
           <t>→ Mở</t>
         </is>
       </c>
     </row>
-    <row r="89" ht="54" customHeight="1">
-      <c r="A89" s="6" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="B89" s="6" t="inlineStr">
+    <row r="90" ht="54" customHeight="1">
+      <c r="A90" s="6" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="B90" s="6" t="inlineStr">
         <is>
           <t>Thanh toán &amp; hóa đơn (billing)</t>
         </is>
       </c>
-      <c r="C89" s="7" t="inlineStr">
+      <c r="C90" s="7" t="inlineStr">
         <is>
           <t>subscription_plans</t>
         </is>
       </c>
-      <c r="D89" s="7" t="inlineStr">
+      <c r="D90" s="7" t="inlineStr">
         <is>
           <t>Gói dịch vụ</t>
         </is>
       </c>
-      <c r="E89" s="6" t="inlineStr">
+      <c r="E90" s="6" t="inlineStr">
         <is>
           <t>Nội bộ</t>
         </is>
       </c>
-      <c r="F89" s="6" t="inlineStr">
+      <c r="F90" s="6" t="inlineStr">
         <is>
           <t>F-H4</t>
         </is>
       </c>
-      <c r="G89" s="6" t="inlineStr">
+      <c r="G90" s="6" t="inlineStr">
         <is>
           <t>Một gói dịch vụ: mỗi gói là một dòng (GUEST là gói mặc định miễn phí, STANDARD, ADVANCED, PRO, ..., hoặc gói riêng cho một khách hàng); tính năng của gói nằm ở plan_features. Giá được tính theo từng tính năng (xem ghi chú của miền thanh toán).</t>
         </is>
       </c>
-      <c r="H89" s="6" t="n">
+      <c r="H90" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="I89" s="7" t="inlineStr">
+      <c r="I90" s="7" t="inlineStr">
         <is>
           <t>→ Mở</t>
         </is>
       </c>
     </row>
-    <row r="90" ht="40.5" customHeight="1">
-      <c r="A90" s="6" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="B90" s="6" t="inlineStr">
+    <row r="91" ht="40.5" customHeight="1">
+      <c r="A91" s="6" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="B91" s="6" t="inlineStr">
         <is>
           <t>Thanh toán &amp; hóa đơn (billing)</t>
         </is>
       </c>
-      <c r="C90" s="7" t="inlineStr">
+      <c r="C91" s="7" t="inlineStr">
         <is>
           <t>plan_features</t>
         </is>
       </c>
-      <c r="D90" s="7" t="inlineStr">
+      <c r="D91" s="7" t="inlineStr">
         <is>
           <t>Tính năng của gói dịch vụ</t>
         </is>
       </c>
-      <c r="E90" s="6" t="inlineStr">
+      <c r="E91" s="6" t="inlineStr">
         <is>
           <t>Nội bộ</t>
         </is>
       </c>
-      <c r="F90" s="6" t="inlineStr">
+      <c r="F91" s="6" t="inlineStr">
         <is>
           <t>F-H4</t>
         </is>
       </c>
-      <c r="G90" s="6" t="inlineStr">
+      <c r="G91" s="6" t="inlineStr">
         <is>
           <t>Mỗi gói dịch vụ gồm những tính năng nào. Gói dịch vụ là dữ liệu, nên G3 có thể tạo gói mới (Pro, Max, gói riêng cho một khách hàng) trên portal mà không cần lập trình viên; chỉ tính năng hoàn toàn mới mới cần viết mã.</t>
         </is>
       </c>
-      <c r="H90" s="6" t="n">
+      <c r="H91" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="I90" s="7" t="inlineStr">
+      <c r="I91" s="7" t="inlineStr">
         <is>
           <t>→ Mở</t>
         </is>
       </c>
     </row>
-    <row r="91" ht="27" customHeight="1">
-      <c r="A91" s="6" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="B91" s="6" t="inlineStr">
+    <row r="92" ht="27" customHeight="1">
+      <c r="A92" s="6" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="B92" s="6" t="inlineStr">
         <is>
           <t>Thanh toán &amp; hóa đơn (billing)</t>
         </is>
       </c>
-      <c r="C91" s="7" t="inlineStr">
+      <c r="C92" s="7" t="inlineStr">
         <is>
           <t>subscriptions</t>
         </is>
       </c>
-      <c r="D91" s="7" t="inlineStr">
+      <c r="D92" s="7" t="inlineStr">
         <is>
           <t>Thuê bao</t>
         </is>
       </c>
-      <c r="E91" s="6" t="inlineStr">
+      <c r="E92" s="6" t="inlineStr">
         <is>
           <t>Khách hàng</t>
         </is>
       </c>
-      <c r="F91" s="6" t="inlineStr">
+      <c r="F92" s="6" t="inlineStr">
         <is>
           <t>F-H4</t>
         </is>
       </c>
-      <c r="G91" s="6" t="inlineStr">
+      <c r="G92" s="6" t="inlineStr">
         <is>
           <t>Một xe đăng ký một gói; quá hạn thanh toán sẽ khóa tính năng.</t>
         </is>
       </c>
-      <c r="H91" s="6" t="n">
+      <c r="H92" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="I91" s="7" t="inlineStr">
+      <c r="I92" s="7" t="inlineStr">
         <is>
           <t>→ Mở</t>
         </is>
       </c>
     </row>
-    <row r="92" ht="27" customHeight="1">
-      <c r="A92" s="5" t="n"/>
-      <c r="B92" s="5" t="inlineStr">
+    <row r="93" ht="27" customHeight="1">
+      <c r="A93" s="5" t="n"/>
+      <c r="B93" s="5" t="inlineStr">
         <is>
           <t>Chấm điểm tài xế (scoring)</t>
         </is>
       </c>
-      <c r="C92" s="5" t="inlineStr">
+      <c r="C93" s="5" t="inlineStr">
         <is>
           <t>1 bảng</t>
         </is>
       </c>
-      <c r="D92" s="5" t="n"/>
-      <c r="E92" s="5" t="n"/>
-      <c r="F92" s="5" t="n"/>
-      <c r="G92" s="5" t="inlineStr">
+      <c r="D93" s="5" t="n"/>
+      <c r="E93" s="5" t="n"/>
+      <c r="F93" s="5" t="n"/>
+      <c r="G93" s="5" t="inlineStr">
         <is>
           <t>Chấm điểm an toàn cho tài xế từ hành vi lái xe.
 • Mỗi tuần, mỗi tài xế có một điểm, tính từ dữ liệu vận hành của xe họ lái.</t>
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" s="6" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="B93" s="6" t="inlineStr">
+    <row r="94">
+      <c r="A94" s="6" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="B94" s="6" t="inlineStr">
         <is>
           <t>Chấm điểm tài xế (scoring)</t>
         </is>
       </c>
-      <c r="C93" s="7" t="inlineStr">
+      <c r="C94" s="7" t="inlineStr">
         <is>
           <t>driver_scores</t>
         </is>
       </c>
-      <c r="D93" s="7" t="inlineStr">
+      <c r="D94" s="7" t="inlineStr">
         <is>
           <t>Điểm tài xế</t>
         </is>
       </c>
-      <c r="E93" s="6" t="inlineStr">
+      <c r="E94" s="6" t="inlineStr">
         <is>
           <t>Khách hàng</t>
         </is>
       </c>
-      <c r="F93" s="6" t="inlineStr">
+      <c r="F94" s="6" t="inlineStr">
         <is>
           <t>F-K1</t>
         </is>
       </c>
-      <c r="G93" s="6" t="inlineStr">
+      <c r="G94" s="6" t="inlineStr">
         <is>
           <t>Điểm an toàn hằng tuần của tài xế, tính từ dữ liệu vận hành xe.</t>
         </is>
       </c>
-      <c r="H93" s="6" t="n">
+      <c r="H94" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="I93" s="7" t="inlineStr">
+      <c r="I94" s="7" t="inlineStr">
         <is>
           <t>→ Mở</t>
         </is>
       </c>
     </row>
-    <row r="94" ht="27" customHeight="1">
-      <c r="A94" s="5" t="n"/>
-      <c r="B94" s="5" t="inlineStr">
+    <row r="95" ht="27" customHeight="1">
+      <c r="A95" s="5" t="n"/>
+      <c r="B95" s="5" t="inlineStr">
         <is>
           <t>Chưa phân miền (unassigned)</t>
         </is>
       </c>
-      <c r="C94" s="5" t="inlineStr">
+      <c r="C95" s="5" t="inlineStr">
         <is>
           <t>2 bảng</t>
         </is>
       </c>
-      <c r="D94" s="5" t="n"/>
-      <c r="E94" s="5" t="n"/>
-      <c r="F94" s="5" t="n"/>
-      <c r="G94" s="5" t="inlineStr">
+      <c r="D95" s="5" t="n"/>
+      <c r="E95" s="5" t="n"/>
+      <c r="F95" s="5" t="n"/>
+      <c r="G95" s="5" t="inlineStr">
         <is>
           <t>Các tính năng chưa được quyết định thuộc miền nghiệp vụ nào (xem feature-list.md).</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="6" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="B95" s="6" t="inlineStr">
-        <is>
-          <t>Chưa phân miền (unassigned)</t>
-        </is>
-      </c>
-      <c r="C95" s="7" t="inlineStr">
-        <is>
-          <t>promotion_campaigns</t>
-        </is>
-      </c>
-      <c r="D95" s="7" t="inlineStr">
-        <is>
-          <t>Chiến dịch khuyến mãi</t>
-        </is>
-      </c>
-      <c r="E95" s="6" t="inlineStr">
-        <is>
-          <t>Nội bộ</t>
-        </is>
-      </c>
-      <c r="F95" s="6" t="inlineStr">
-        <is>
-          <t>F-F4</t>
-        </is>
-      </c>
-      <c r="G95" s="6" t="inlineStr">
-        <is>
-          <t>Một chiến dịch nhắc bảo dưỡng hoặc khuyến mãi.</t>
-        </is>
-      </c>
-      <c r="H95" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="I95" s="7" t="inlineStr">
-        <is>
-          <t>→ Mở</t>
         </is>
       </c>
     </row>
@@ -4453,294 +4456,339 @@
       </c>
       <c r="C96" s="7" t="inlineStr">
         <is>
+          <t>promotion_campaigns</t>
+        </is>
+      </c>
+      <c r="D96" s="7" t="inlineStr">
+        <is>
+          <t>Chiến dịch khuyến mãi</t>
+        </is>
+      </c>
+      <c r="E96" s="6" t="inlineStr">
+        <is>
+          <t>Nội bộ</t>
+        </is>
+      </c>
+      <c r="F96" s="6" t="inlineStr">
+        <is>
+          <t>F-F4</t>
+        </is>
+      </c>
+      <c r="G96" s="6" t="inlineStr">
+        <is>
+          <t>Một chiến dịch nhắc bảo dưỡng hoặc khuyến mãi.</t>
+        </is>
+      </c>
+      <c r="H96" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="I96" s="7" t="inlineStr">
+        <is>
+          <t>→ Mở</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="6" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="B97" s="6" t="inlineStr">
+        <is>
+          <t>Chưa phân miền (unassigned)</t>
+        </is>
+      </c>
+      <c r="C97" s="7" t="inlineStr">
+        <is>
           <t>trips</t>
         </is>
       </c>
-      <c r="D96" s="7" t="inlineStr">
+      <c r="D97" s="7" t="inlineStr">
         <is>
           <t>Chuyến đi</t>
         </is>
       </c>
-      <c r="E96" s="6" t="inlineStr">
+      <c r="E97" s="6" t="inlineStr">
         <is>
           <t>Khách hàng</t>
         </is>
       </c>
-      <c r="F96" s="6" t="inlineStr">
+      <c r="F97" s="6" t="inlineStr">
         <is>
           <t>F-A9</t>
         </is>
       </c>
-      <c r="G96" s="6" t="inlineStr">
+      <c r="G97" s="6" t="inlineStr">
         <is>
           <t>Một chuyến đi của xe. F-A9 đang tạm dừng: chưa có khái niệm chuyến đi.</t>
         </is>
       </c>
-      <c r="H96" s="6" t="n">
+      <c r="H97" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="I96" s="7" t="inlineStr">
+      <c r="I97" s="7" t="inlineStr">
         <is>
           <t>→ Mở</t>
         </is>
       </c>
     </row>
-    <row r="97"/>
-    <row r="98" ht="27" customHeight="1">
-      <c r="A98" s="4" t="inlineStr">
+    <row r="98"/>
+    <row r="99" ht="27" customHeight="1">
+      <c r="A99" s="4" t="inlineStr">
         <is>
           <t>Chú giải</t>
         </is>
       </c>
-      <c r="B98" s="4" t="inlineStr">
+      <c r="B99" s="4" t="inlineStr">
         <is>
           <t>Ý nghĩa</t>
         </is>
       </c>
     </row>
-    <row r="99" ht="108" customHeight="1">
-      <c r="A99" s="6" t="inlineStr">
+    <row r="100" ht="108" customHeight="1">
+      <c r="A100" s="6" t="inlineStr">
         <is>
           <t>Chủ sở hữu dữ liệu: Khách hàng</t>
         </is>
       </c>
-      <c r="B99" s="6" t="inlineStr">
+      <c r="B100" s="6" t="inlineStr">
         <is>
           <t>Thuộc về một tổ chức (thường là khách hàng; công ty G3 cũng có thể sở hữu); có cột organization_id hoặc lấy qua bảng cha (DM-24).</t>
-        </is>
-      </c>
-    </row>
-    <row r="100" ht="94.5" customHeight="1">
-      <c r="A100" s="6" t="inlineStr">
-        <is>
-          <t>Chủ sở hữu dữ liệu: Nội bộ</t>
-        </is>
-      </c>
-      <c r="B100" s="6" t="inlineStr">
-        <is>
-          <t>Dữ liệu của chính chúng ta (đơn vị vận hành nền tảng), dùng chung cho mọi tổ chức.</t>
         </is>
       </c>
     </row>
     <row r="101" ht="94.5" customHeight="1">
       <c r="A101" s="6" t="inlineStr">
         <is>
+          <t>Chủ sở hữu dữ liệu: Nội bộ</t>
+        </is>
+      </c>
+      <c r="B101" s="6" t="inlineStr">
+        <is>
+          <t>Dữ liệu của chính chúng ta (đơn vị vận hành nền tảng), dùng chung cho mọi tổ chức.</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="94.5" customHeight="1">
+      <c r="A102" s="6" t="inlineStr">
+        <is>
           <t>Chủ sở hữu dữ liệu: Hai bên</t>
         </is>
       </c>
-      <c r="B101" s="6" t="inlineStr">
+      <c r="B102" s="6" t="inlineStr">
         <is>
           <t>Tài sản của G3 được khách hàng sử dụng; cả hai bên cùng liên quan.</t>
         </is>
       </c>
     </row>
-    <row r="102" ht="121.5" customHeight="1">
-      <c r="A102" s="6" t="inlineStr">
+    <row r="103" ht="121.5" customHeight="1">
+      <c r="A103" s="6" t="inlineStr">
         <is>
           <t>Chủ sở hữu dữ liệu: Chưa quyết định</t>
         </is>
       </c>
-      <c r="B102" s="6" t="inlineStr">
+      <c r="B103" s="6" t="inlineStr">
         <is>
           <t>Đang chờ một quyết định còn mở (xem cuối trang).</t>
         </is>
       </c>
     </row>
-    <row r="103" ht="81" customHeight="1">
-      <c r="A103" s="6" t="inlineStr">
+    <row r="104" ht="81" customHeight="1">
+      <c r="A104" s="6" t="inlineStr">
         <is>
           <t>Miền nghiệp vụ (domain)</t>
         </is>
       </c>
-      <c r="B103" s="6" t="inlineStr">
+      <c r="B104" s="6" t="inlineStr">
         <is>
           <t>Một phần của hệ thống sở hữu dữ liệu riêng, ví dụ Xe, Trạm sạc, Thanh toán. Mỗi miền gồm một hoặc nhiều bảng.</t>
         </is>
       </c>
     </row>
-    <row r="104" ht="54" customHeight="1">
-      <c r="A104" s="6" t="inlineStr">
+    <row r="105" ht="54" customHeight="1">
+      <c r="A105" s="6" t="inlineStr">
         <is>
           <t>Bảng</t>
         </is>
       </c>
-      <c r="B104" s="6" t="inlineStr">
+      <c r="B105" s="6" t="inlineStr">
         <is>
           <t>Một loại dữ liệu được lưu, ví dụ Xe hoặc Phiên sạc. Mỗi bảng có một sheet riêng liệt kê từng cột.</t>
         </is>
       </c>
     </row>
-    <row r="105" ht="40.5" customHeight="1">
-      <c r="A105" s="6" t="inlineStr">
+    <row r="106" ht="40.5" customHeight="1">
+      <c r="A106" s="6" t="inlineStr">
         <is>
           <t>Tính năng</t>
         </is>
       </c>
-      <c r="B105" s="6" t="inlineStr">
+      <c r="B106" s="6" t="inlineStr">
         <is>
           <t>Mã tính năng trong danh sách tính năng (feature-list.md), ví dụ F-B2.</t>
         </is>
       </c>
     </row>
-    <row r="106" ht="67.5" customHeight="1">
-      <c r="A106" s="6" t="inlineStr">
+    <row r="107" ht="67.5" customHeight="1">
+      <c r="A107" s="6" t="inlineStr">
         <is>
           <t>PK / FK / UQ</t>
         </is>
       </c>
-      <c r="B106" s="6" t="inlineStr">
+      <c r="B107" s="6" t="inlineStr">
         <is>
           <t>PK: khóa chính (định danh duy nhất của dòng). FK: khóa ngoại (trỏ tới dòng của bảng khác). UQ: giá trị không được trùng.</t>
         </is>
       </c>
     </row>
-    <row r="107" ht="54" customHeight="1">
-      <c r="A107" s="6" t="inlineStr">
+    <row r="108" ht="54" customHeight="1">
+      <c r="A108" s="6" t="inlineStr">
         <is>
           <t>Ví dụ</t>
         </is>
       </c>
-      <c r="B107" s="6" t="inlineStr">
+      <c r="B108" s="6" t="inlineStr">
         <is>
           <t>Giá trị mẫu. Các mã ví dụ khớp nhau giữa các bảng, nên có thể lần theo một bản ghi mẫu qua nhiều sheet.</t>
         </is>
       </c>
     </row>
-    <row r="108" ht="40.5" customHeight="1">
-      <c r="A108" s="6" t="inlineStr">
+    <row r="109" ht="40.5" customHeight="1">
+      <c r="A109" s="6" t="inlineStr">
         <is>
           <t>NULL</t>
         </is>
       </c>
-      <c r="B108" s="6" t="inlineStr">
+      <c r="B109" s="6" t="inlineStr">
         <is>
           <t>Ô không có giá trị. Ý nghĩa của NULL được giải thích trong cột Ý nghĩa.</t>
         </is>
       </c>
     </row>
-    <row r="109" ht="81" customHeight="1">
-      <c r="A109" s="6" t="inlineStr">
+    <row r="110" ht="81" customHeight="1">
+      <c r="A110" s="6" t="inlineStr">
         <is>
           <t>🔍 Lưu lịch sử</t>
         </is>
       </c>
-      <c r="B109" s="6" t="inlineStr">
+      <c r="B110" s="6" t="inlineStr">
         <is>
           <t>Cột được theo dõi: khi cột này thay đổi, toàn bộ dòng cũ được chép sang bảng lịch sử (tên kết thúc bằng _history) kèm thời điểm và người thay đổi.</t>
         </is>
       </c>
     </row>
-    <row r="110"/>
-    <row r="111">
-      <c r="A111" s="8" t="inlineStr">
+    <row r="111"/>
+    <row r="112">
+      <c r="A112" s="8" t="inlineStr">
         <is>
           <t>Các view (giai đoạn đọc từ lịch sử)</t>
         </is>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" s="4" t="inlineStr">
+    <row r="113">
+      <c r="A113" s="4" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="B112" s="4" t="inlineStr">
+      <c r="B113" s="4" t="inlineStr">
         <is>
           <t>Mỗi dòng là</t>
         </is>
       </c>
-      <c r="C112" s="4" t="inlineStr">
+      <c r="C113" s="4" t="inlineStr">
         <is>
           <t>Các cột</t>
         </is>
       </c>
-      <c r="D112" s="4" t="inlineStr">
+      <c r="D113" s="4" t="inlineStr">
         <is>
           <t>Được dùng bởi</t>
-        </is>
-      </c>
-    </row>
-    <row r="113" ht="94.5" customHeight="1">
-      <c r="A113" s="6" t="inlineStr">
-        <is>
-          <t>vehicle_ownership_periods</t>
-        </is>
-      </c>
-      <c r="B113" s="6" t="inlineStr">
-        <is>
-          <t>một giai đoạn xe thuộc một chủ</t>
-        </is>
-      </c>
-      <c r="C113" s="6" t="inlineStr">
-        <is>
-          <t>vehicle_id, organization_id, owned_from, owned_until (NULL với chủ hiện tại)</t>
-        </is>
-      </c>
-      <c r="D113" s="6" t="inlineStr">
-        <is>
-          <t>lịch sử sở hữu và ngày bàn giao đầu tiên (VEH-02), "ngày đó xe của ai"</t>
         </is>
       </c>
     </row>
     <row r="114" ht="94.5" customHeight="1">
       <c r="A114" s="6" t="inlineStr">
         <is>
+          <t>vehicle_ownership_periods</t>
+        </is>
+      </c>
+      <c r="B114" s="6" t="inlineStr">
+        <is>
+          <t>một giai đoạn xe thuộc một chủ</t>
+        </is>
+      </c>
+      <c r="C114" s="6" t="inlineStr">
+        <is>
+          <t>vehicle_id, organization_id, owned_from, owned_until (NULL với chủ hiện tại)</t>
+        </is>
+      </c>
+      <c r="D114" s="6" t="inlineStr">
+        <is>
+          <t>lịch sử sở hữu và ngày bàn giao đầu tiên (VEH-02), "ngày đó xe của ai"</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="94.5" customHeight="1">
+      <c r="A115" s="6" t="inlineStr">
+        <is>
           <t>battery_installation_periods</t>
         </is>
       </c>
-      <c r="B114" s="6" t="inlineStr">
+      <c r="B115" s="6" t="inlineStr">
         <is>
           <t>một lần pin nằm trên một xe</t>
         </is>
       </c>
-      <c r="C114" s="6" t="inlineStr">
+      <c r="C115" s="6" t="inlineStr">
         <is>
           <t>battery_id, vehicle_id, installed_from, installed_until (NULL khi đang lắp)</t>
         </is>
       </c>
-      <c r="D114" s="6" t="inlineStr">
+      <c r="D115" s="6" t="inlineStr">
         <is>
           <t>lịch sử sức khỏe pin qua các xe (MON-07), bộ đếm bảo hành pin (WAR-01)</t>
         </is>
       </c>
     </row>
-    <row r="115"/>
-    <row r="116">
-      <c r="A116" s="8" t="inlineStr">
+    <row r="116"/>
+    <row r="117">
+      <c r="A117" s="8" t="inlineStr">
         <is>
           <t>Các quyết định còn mở</t>
         </is>
       </c>
     </row>
-    <row r="117">
-      <c r="A117" s="4" t="inlineStr">
+    <row r="118">
+      <c r="A118" s="4" t="inlineStr">
         <is>
           <t>Mã</t>
         </is>
       </c>
-      <c r="B117" s="4" t="inlineStr">
+      <c r="B118" s="4" t="inlineStr">
         <is>
           <t>Câu hỏi</t>
         </is>
       </c>
-      <c r="C117" s="4" t="inlineStr">
+      <c r="C118" s="4" t="inlineStr">
         <is>
           <t>Ảnh hưởng tới</t>
         </is>
       </c>
     </row>
-    <row r="118" ht="54" customHeight="1">
-      <c r="A118" s="6" t="inlineStr">
+    <row r="119" ht="54" customHeight="1">
+      <c r="A119" s="6" t="inlineStr">
         <is>
           <t>D5</t>
         </is>
       </c>
-      <c r="B118" s="6" t="inlineStr">
+      <c r="B119" s="6" t="inlineStr">
         <is>
           <t>Ai trả tiền khi tài xế của đội xe sạc: ví của tài xế, ví của đội xe, hay tùy trường hợp?</t>
         </is>
       </c>
-      <c r="C118" s="6" t="inlineStr">
+      <c r="C119" s="6" t="inlineStr">
         <is>
           <t>wallets, payments</t>
         </is>
@@ -4904,75 +4952,78 @@
     <hyperlink ref="C66" location="'charging_station_config_entries'!A1"/>
     <hyperlink ref="D66" location="'charging_station_config_entries'!A1"/>
     <hyperlink ref="I66" location="'charging_station_config_entries'!A1"/>
-    <hyperlink ref="C68" location="'charging_sessions'!A1"/>
-    <hyperlink ref="D68" location="'charging_sessions'!A1"/>
-    <hyperlink ref="I68" location="'charging_sessions'!A1"/>
-    <hyperlink ref="C69" location="'charging_session_events'!A1"/>
-    <hyperlink ref="D69" location="'charging_session_events'!A1"/>
-    <hyperlink ref="I69" location="'charging_session_events'!A1"/>
-    <hyperlink ref="C70" location="'charging_session_measurements'!A1"/>
-    <hyperlink ref="D70" location="'charging_session_measurements'!A1"/>
-    <hyperlink ref="I70" location="'charging_session_measurements'!A1"/>
-    <hyperlink ref="C72" location="'notifications'!A1"/>
-    <hyperlink ref="D72" location="'notifications'!A1"/>
-    <hyperlink ref="I72" location="'notifications'!A1"/>
-    <hyperlink ref="C74" location="'support_cases'!A1"/>
-    <hyperlink ref="D74" location="'support_cases'!A1"/>
-    <hyperlink ref="I74" location="'support_cases'!A1"/>
-    <hyperlink ref="C75" location="'repair_partners'!A1"/>
-    <hyperlink ref="D75" location="'repair_partners'!A1"/>
-    <hyperlink ref="I75" location="'repair_partners'!A1"/>
-    <hyperlink ref="C76" location="'maintenance_bookings'!A1"/>
-    <hyperlink ref="D76" location="'maintenance_bookings'!A1"/>
-    <hyperlink ref="I76" location="'maintenance_bookings'!A1"/>
-    <hyperlink ref="C78" location="'charging_policies'!A1"/>
-    <hyperlink ref="D78" location="'charging_policies'!A1"/>
-    <hyperlink ref="I78" location="'charging_policies'!A1"/>
-    <hyperlink ref="C79" location="'charging_policy_versions'!A1"/>
-    <hyperlink ref="D79" location="'charging_policy_versions'!A1"/>
-    <hyperlink ref="I79" location="'charging_policy_versions'!A1"/>
-    <hyperlink ref="C80" location="'charging_policy_assignments'!A1"/>
-    <hyperlink ref="D80" location="'charging_policy_assignments'!A1"/>
-    <hyperlink ref="I80" location="'charging_policy_assignments'!A1"/>
-    <hyperlink ref="C81" location="'policy_violations'!A1"/>
-    <hyperlink ref="D81" location="'policy_violations'!A1"/>
-    <hyperlink ref="I81" location="'policy_violations'!A1"/>
-    <hyperlink ref="C83" location="'tariffs'!A1"/>
-    <hyperlink ref="D83" location="'tariffs'!A1"/>
-    <hyperlink ref="I83" location="'tariffs'!A1"/>
-    <hyperlink ref="C84" location="'payments'!A1"/>
-    <hyperlink ref="D84" location="'payments'!A1"/>
-    <hyperlink ref="I84" location="'payments'!A1"/>
-    <hyperlink ref="C85" location="'wallets'!A1"/>
-    <hyperlink ref="D85" location="'wallets'!A1"/>
-    <hyperlink ref="I85" location="'wallets'!A1"/>
-    <hyperlink ref="C86" location="'wallet_transactions'!A1"/>
-    <hyperlink ref="D86" location="'wallet_transactions'!A1"/>
-    <hyperlink ref="I86" location="'wallet_transactions'!A1"/>
-    <hyperlink ref="C87" location="'invoices'!A1"/>
-    <hyperlink ref="D87" location="'invoices'!A1"/>
-    <hyperlink ref="I87" location="'invoices'!A1"/>
-    <hyperlink ref="C88" location="'invoice_lines'!A1"/>
-    <hyperlink ref="D88" location="'invoice_lines'!A1"/>
-    <hyperlink ref="I88" location="'invoice_lines'!A1"/>
-    <hyperlink ref="C89" location="'subscription_plans'!A1"/>
-    <hyperlink ref="D89" location="'subscription_plans'!A1"/>
-    <hyperlink ref="I89" location="'subscription_plans'!A1"/>
-    <hyperlink ref="C90" location="'plan_features'!A1"/>
-    <hyperlink ref="D90" location="'plan_features'!A1"/>
-    <hyperlink ref="I90" location="'plan_features'!A1"/>
-    <hyperlink ref="C91" location="'subscriptions'!A1"/>
-    <hyperlink ref="D91" location="'subscriptions'!A1"/>
-    <hyperlink ref="I91" location="'subscriptions'!A1"/>
-    <hyperlink ref="C93" location="'driver_scores'!A1"/>
-    <hyperlink ref="D93" location="'driver_scores'!A1"/>
-    <hyperlink ref="I93" location="'driver_scores'!A1"/>
-    <hyperlink ref="C95" location="'promotion_campaigns'!A1"/>
-    <hyperlink ref="D95" location="'promotion_campaigns'!A1"/>
-    <hyperlink ref="I95" location="'promotion_campaigns'!A1"/>
-    <hyperlink ref="C96" location="'trips'!A1"/>
-    <hyperlink ref="D96" location="'trips'!A1"/>
-    <hyperlink ref="I96" location="'trips'!A1"/>
+    <hyperlink ref="C67" location="'charging_station_commands'!A1"/>
+    <hyperlink ref="D67" location="'charging_station_commands'!A1"/>
+    <hyperlink ref="I67" location="'charging_station_commands'!A1"/>
+    <hyperlink ref="C69" location="'charging_sessions'!A1"/>
+    <hyperlink ref="D69" location="'charging_sessions'!A1"/>
+    <hyperlink ref="I69" location="'charging_sessions'!A1"/>
+    <hyperlink ref="C70" location="'charging_session_events'!A1"/>
+    <hyperlink ref="D70" location="'charging_session_events'!A1"/>
+    <hyperlink ref="I70" location="'charging_session_events'!A1"/>
+    <hyperlink ref="C71" location="'charging_session_measurements'!A1"/>
+    <hyperlink ref="D71" location="'charging_session_measurements'!A1"/>
+    <hyperlink ref="I71" location="'charging_session_measurements'!A1"/>
+    <hyperlink ref="C73" location="'notifications'!A1"/>
+    <hyperlink ref="D73" location="'notifications'!A1"/>
+    <hyperlink ref="I73" location="'notifications'!A1"/>
+    <hyperlink ref="C75" location="'support_cases'!A1"/>
+    <hyperlink ref="D75" location="'support_cases'!A1"/>
+    <hyperlink ref="I75" location="'support_cases'!A1"/>
+    <hyperlink ref="C76" location="'repair_partners'!A1"/>
+    <hyperlink ref="D76" location="'repair_partners'!A1"/>
+    <hyperlink ref="I76" location="'repair_partners'!A1"/>
+    <hyperlink ref="C77" location="'maintenance_bookings'!A1"/>
+    <hyperlink ref="D77" location="'maintenance_bookings'!A1"/>
+    <hyperlink ref="I77" location="'maintenance_bookings'!A1"/>
+    <hyperlink ref="C79" location="'charging_policies'!A1"/>
+    <hyperlink ref="D79" location="'charging_policies'!A1"/>
+    <hyperlink ref="I79" location="'charging_policies'!A1"/>
+    <hyperlink ref="C80" location="'charging_policy_versions'!A1"/>
+    <hyperlink ref="D80" location="'charging_policy_versions'!A1"/>
+    <hyperlink ref="I80" location="'charging_policy_versions'!A1"/>
+    <hyperlink ref="C81" location="'charging_policy_assignments'!A1"/>
+    <hyperlink ref="D81" location="'charging_policy_assignments'!A1"/>
+    <hyperlink ref="I81" location="'charging_policy_assignments'!A1"/>
+    <hyperlink ref="C82" location="'policy_violations'!A1"/>
+    <hyperlink ref="D82" location="'policy_violations'!A1"/>
+    <hyperlink ref="I82" location="'policy_violations'!A1"/>
+    <hyperlink ref="C84" location="'tariffs'!A1"/>
+    <hyperlink ref="D84" location="'tariffs'!A1"/>
+    <hyperlink ref="I84" location="'tariffs'!A1"/>
+    <hyperlink ref="C85" location="'payments'!A1"/>
+    <hyperlink ref="D85" location="'payments'!A1"/>
+    <hyperlink ref="I85" location="'payments'!A1"/>
+    <hyperlink ref="C86" location="'wallets'!A1"/>
+    <hyperlink ref="D86" location="'wallets'!A1"/>
+    <hyperlink ref="I86" location="'wallets'!A1"/>
+    <hyperlink ref="C87" location="'wallet_transactions'!A1"/>
+    <hyperlink ref="D87" location="'wallet_transactions'!A1"/>
+    <hyperlink ref="I87" location="'wallet_transactions'!A1"/>
+    <hyperlink ref="C88" location="'invoices'!A1"/>
+    <hyperlink ref="D88" location="'invoices'!A1"/>
+    <hyperlink ref="I88" location="'invoices'!A1"/>
+    <hyperlink ref="C89" location="'invoice_lines'!A1"/>
+    <hyperlink ref="D89" location="'invoice_lines'!A1"/>
+    <hyperlink ref="I89" location="'invoice_lines'!A1"/>
+    <hyperlink ref="C90" location="'subscription_plans'!A1"/>
+    <hyperlink ref="D90" location="'subscription_plans'!A1"/>
+    <hyperlink ref="I90" location="'subscription_plans'!A1"/>
+    <hyperlink ref="C91" location="'plan_features'!A1"/>
+    <hyperlink ref="D91" location="'plan_features'!A1"/>
+    <hyperlink ref="I91" location="'plan_features'!A1"/>
+    <hyperlink ref="C92" location="'subscriptions'!A1"/>
+    <hyperlink ref="D92" location="'subscriptions'!A1"/>
+    <hyperlink ref="I92" location="'subscriptions'!A1"/>
+    <hyperlink ref="C94" location="'driver_scores'!A1"/>
+    <hyperlink ref="D94" location="'driver_scores'!A1"/>
+    <hyperlink ref="I94" location="'driver_scores'!A1"/>
+    <hyperlink ref="C96" location="'promotion_campaigns'!A1"/>
+    <hyperlink ref="D96" location="'promotion_campaigns'!A1"/>
+    <hyperlink ref="I96" location="'promotion_campaigns'!A1"/>
+    <hyperlink ref="C97" location="'trips'!A1"/>
+    <hyperlink ref="D97" location="'trips'!A1"/>
+    <hyperlink ref="I97" location="'trips'!A1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -25610,7 +25661,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I58"/>
+  <dimension ref="A1:I59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -26387,16 +26438,16 @@
         </is>
       </c>
     </row>
-    <row r="41">
+    <row r="41" ht="27" customHeight="1">
       <c r="A41" s="6" t="n"/>
       <c r="B41" s="7" t="inlineStr">
         <is>
-          <t>charging_sessions</t>
+          <t>charging_station_commands</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>started_by</t>
+          <t>requested_by</t>
         </is>
       </c>
     </row>
@@ -26404,12 +26455,12 @@
       <c r="A42" s="6" t="n"/>
       <c r="B42" s="7" t="inlineStr">
         <is>
-          <t>charging_policy_versions</t>
+          <t>charging_sessions</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>created_by</t>
+          <t>started_by</t>
         </is>
       </c>
     </row>
@@ -26417,12 +26468,12 @@
       <c r="A43" s="6" t="n"/>
       <c r="B43" s="7" t="inlineStr">
         <is>
-          <t>organization_history</t>
+          <t>charging_policy_versions</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>changed_by</t>
+          <t>created_by</t>
         </is>
       </c>
     </row>
@@ -26430,12 +26481,12 @@
       <c r="A44" s="6" t="n"/>
       <c r="B44" s="7" t="inlineStr">
         <is>
-          <t>user_history</t>
+          <t>organization_history</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>user_id</t>
+          <t>changed_by</t>
         </is>
       </c>
     </row>
@@ -26448,7 +26499,7 @@
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>changed_by</t>
+          <t>user_id</t>
         </is>
       </c>
     </row>
@@ -26456,7 +26507,7 @@
       <c r="A46" s="6" t="n"/>
       <c r="B46" s="7" t="inlineStr">
         <is>
-          <t>membership_history</t>
+          <t>user_history</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
@@ -26465,11 +26516,11 @@
         </is>
       </c>
     </row>
-    <row r="47" ht="27" customHeight="1">
+    <row r="47">
       <c r="A47" s="6" t="n"/>
       <c r="B47" s="7" t="inlineStr">
         <is>
-          <t>organization_setting_history</t>
+          <t>membership_history</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
@@ -26478,11 +26529,11 @@
         </is>
       </c>
     </row>
-    <row r="48">
+    <row r="48" ht="27" customHeight="1">
       <c r="A48" s="6" t="n"/>
       <c r="B48" s="7" t="inlineStr">
         <is>
-          <t>vehicle_history</t>
+          <t>organization_setting_history</t>
         </is>
       </c>
       <c r="C48" s="6" t="inlineStr">
@@ -26495,7 +26546,7 @@
       <c r="A49" s="6" t="n"/>
       <c r="B49" s="7" t="inlineStr">
         <is>
-          <t>vehicle_model_history</t>
+          <t>vehicle_history</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
@@ -26508,7 +26559,7 @@
       <c r="A50" s="6" t="n"/>
       <c r="B50" s="7" t="inlineStr">
         <is>
-          <t>battery_model_history</t>
+          <t>vehicle_model_history</t>
         </is>
       </c>
       <c r="C50" s="6" t="inlineStr">
@@ -26521,7 +26572,7 @@
       <c r="A51" s="6" t="n"/>
       <c r="B51" s="7" t="inlineStr">
         <is>
-          <t>battery_history</t>
+          <t>battery_model_history</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
@@ -26534,7 +26585,7 @@
       <c r="A52" s="6" t="n"/>
       <c r="B52" s="7" t="inlineStr">
         <is>
-          <t>warranty_history</t>
+          <t>battery_history</t>
         </is>
       </c>
       <c r="C52" s="6" t="inlineStr">
@@ -26547,7 +26598,7 @@
       <c r="A53" s="6" t="n"/>
       <c r="B53" s="7" t="inlineStr">
         <is>
-          <t>telematic_history</t>
+          <t>warranty_history</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
@@ -26560,7 +26611,7 @@
       <c r="A54" s="6" t="n"/>
       <c r="B54" s="7" t="inlineStr">
         <is>
-          <t>driver_history</t>
+          <t>telematic_history</t>
         </is>
       </c>
       <c r="C54" s="6" t="inlineStr">
@@ -26569,11 +26620,11 @@
         </is>
       </c>
     </row>
-    <row r="55" ht="27" customHeight="1">
+    <row r="55">
       <c r="A55" s="6" t="n"/>
       <c r="B55" s="7" t="inlineStr">
         <is>
-          <t>charging_location_history</t>
+          <t>driver_history</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
@@ -26582,11 +26633,11 @@
         </is>
       </c>
     </row>
-    <row r="56">
+    <row r="56" ht="27" customHeight="1">
       <c r="A56" s="6" t="n"/>
       <c r="B56" s="7" t="inlineStr">
         <is>
-          <t>charging_station_history</t>
+          <t>charging_location_history</t>
         </is>
       </c>
       <c r="C56" s="6" t="inlineStr">
@@ -26599,7 +26650,7 @@
       <c r="A57" s="6" t="n"/>
       <c r="B57" s="7" t="inlineStr">
         <is>
-          <t>charging_evse_history</t>
+          <t>charging_station_history</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
@@ -26608,14 +26659,27 @@
         </is>
       </c>
     </row>
-    <row r="58" ht="27" customHeight="1">
+    <row r="58">
       <c r="A58" s="6" t="n"/>
       <c r="B58" s="7" t="inlineStr">
         <is>
+          <t>charging_evse_history</t>
+        </is>
+      </c>
+      <c r="C58" s="6" t="inlineStr">
+        <is>
+          <t>changed_by</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="27" customHeight="1">
+      <c r="A59" s="6" t="n"/>
+      <c r="B59" s="7" t="inlineStr">
+        <is>
           <t>charging_connector_history</t>
         </is>
       </c>
-      <c r="C58" s="6" t="inlineStr">
+      <c r="C59" s="6" t="inlineStr">
         <is>
           <t>changed_by</t>
         </is>
@@ -26644,24 +26708,25 @@
     <hyperlink ref="B38" location="'access_audit_logs'!A1"/>
     <hyperlink ref="B39" location="'charging_location_access'!A1"/>
     <hyperlink ref="B40" location="'charging_location_access'!A1"/>
-    <hyperlink ref="B41" location="'charging_sessions'!A1"/>
-    <hyperlink ref="B42" location="'charging_policy_versions'!A1"/>
-    <hyperlink ref="B43" location="'organization_history'!A1"/>
-    <hyperlink ref="B44" location="'user_history'!A1"/>
+    <hyperlink ref="B41" location="'charging_station_commands'!A1"/>
+    <hyperlink ref="B42" location="'charging_sessions'!A1"/>
+    <hyperlink ref="B43" location="'charging_policy_versions'!A1"/>
+    <hyperlink ref="B44" location="'organization_history'!A1"/>
     <hyperlink ref="B45" location="'user_history'!A1"/>
-    <hyperlink ref="B46" location="'membership_history'!A1"/>
-    <hyperlink ref="B47" location="'organization_setting_history'!A1"/>
-    <hyperlink ref="B48" location="'vehicle_history'!A1"/>
-    <hyperlink ref="B49" location="'vehicle_model_history'!A1"/>
-    <hyperlink ref="B50" location="'battery_model_history'!A1"/>
-    <hyperlink ref="B51" location="'battery_history'!A1"/>
-    <hyperlink ref="B52" location="'warranty_history'!A1"/>
-    <hyperlink ref="B53" location="'telematic_history'!A1"/>
-    <hyperlink ref="B54" location="'driver_history'!A1"/>
-    <hyperlink ref="B55" location="'charging_location_history'!A1"/>
-    <hyperlink ref="B56" location="'charging_station_history'!A1"/>
-    <hyperlink ref="B57" location="'charging_evse_history'!A1"/>
-    <hyperlink ref="B58" location="'charging_connector_history'!A1"/>
+    <hyperlink ref="B46" location="'user_history'!A1"/>
+    <hyperlink ref="B47" location="'membership_history'!A1"/>
+    <hyperlink ref="B48" location="'organization_setting_history'!A1"/>
+    <hyperlink ref="B49" location="'vehicle_history'!A1"/>
+    <hyperlink ref="B50" location="'vehicle_model_history'!A1"/>
+    <hyperlink ref="B51" location="'battery_model_history'!A1"/>
+    <hyperlink ref="B52" location="'battery_history'!A1"/>
+    <hyperlink ref="B53" location="'warranty_history'!A1"/>
+    <hyperlink ref="B54" location="'telematic_history'!A1"/>
+    <hyperlink ref="B55" location="'driver_history'!A1"/>
+    <hyperlink ref="B56" location="'charging_location_history'!A1"/>
+    <hyperlink ref="B57" location="'charging_station_history'!A1"/>
+    <hyperlink ref="B58" location="'charging_evse_history'!A1"/>
+    <hyperlink ref="B59" location="'charging_connector_history'!A1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -28517,7 +28582,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I56"/>
+  <dimension ref="A1:I57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -29817,11 +29882,11 @@
         </is>
       </c>
     </row>
-    <row r="54">
+    <row r="54" ht="27" customHeight="1">
       <c r="A54" s="6" t="n"/>
       <c r="B54" s="7" t="inlineStr">
         <is>
-          <t>charging_sessions</t>
+          <t>charging_station_commands</t>
         </is>
       </c>
       <c r="C54" s="6" t="inlineStr">
@@ -29834,7 +29899,7 @@
       <c r="A55" s="6" t="n"/>
       <c r="B55" s="7" t="inlineStr">
         <is>
-          <t>tariffs</t>
+          <t>charging_sessions</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
@@ -29847,10 +29912,23 @@
       <c r="A56" s="6" t="n"/>
       <c r="B56" s="7" t="inlineStr">
         <is>
+          <t>tariffs</t>
+        </is>
+      </c>
+      <c r="C56" s="6" t="inlineStr">
+        <is>
+          <t>station_id</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="6" t="n"/>
+      <c r="B57" s="7" t="inlineStr">
+        <is>
           <t>charging_station_history</t>
         </is>
       </c>
-      <c r="C56" s="6" t="inlineStr">
+      <c r="C57" s="6" t="inlineStr">
         <is>
           <t>station_id</t>
         </is>
@@ -29869,9 +29947,10 @@
     <hyperlink ref="B51" location="'charging_ocpp_messages'!A1"/>
     <hyperlink ref="B52" location="'charging_station_config_entries'!A1"/>
     <hyperlink ref="B53" location="'charging_station_config_capture'!A1"/>
-    <hyperlink ref="B54" location="'charging_sessions'!A1"/>
-    <hyperlink ref="B55" location="'tariffs'!A1"/>
-    <hyperlink ref="B56" location="'charging_station_history'!A1"/>
+    <hyperlink ref="B54" location="'charging_station_commands'!A1"/>
+    <hyperlink ref="B55" location="'charging_sessions'!A1"/>
+    <hyperlink ref="B56" location="'tariffs'!A1"/>
+    <hyperlink ref="B57" location="'charging_station_history'!A1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -31076,7 +31155,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -31630,11 +31709,11 @@
         </is>
       </c>
     </row>
-    <row r="25">
+    <row r="25" ht="27" customHeight="1">
       <c r="A25" s="6" t="n"/>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>charging_sessions</t>
+          <t>charging_station_commands</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
@@ -31647,10 +31726,23 @@
       <c r="A26" s="6" t="n"/>
       <c r="B26" s="7" t="inlineStr">
         <is>
+          <t>charging_sessions</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>evse_id</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="n"/>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
           <t>charging_evse_history</t>
         </is>
       </c>
-      <c r="C26" s="6" t="inlineStr">
+      <c r="C27" s="6" t="inlineStr">
         <is>
           <t>evse_id</t>
         </is>
@@ -31663,8 +31755,9 @@
     <hyperlink ref="A5" location="'charging_evse_history'!A1"/>
     <hyperlink ref="F9" location="'charging_stations'!A1"/>
     <hyperlink ref="B24" location="'charging_connectors'!A1"/>
-    <hyperlink ref="B25" location="'charging_sessions'!A1"/>
-    <hyperlink ref="B26" location="'charging_evse_history'!A1"/>
+    <hyperlink ref="B25" location="'charging_station_commands'!A1"/>
+    <hyperlink ref="B26" location="'charging_sessions'!A1"/>
+    <hyperlink ref="B27" location="'charging_evse_history'!A1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -36292,7 +36385,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I49"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -36309,7 +36402,654 @@
     <row r="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>38. charging_sessions: Phiên sạc</t>
+          <t>38. charging_station_commands: Lệnh gửi trụ sạc</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t>← Tổng quan</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>Miền nghiệp vụ: Trạm sạc (charging_stations)   ·   Chủ sở hữu dữ liệu: Nội bộ   ·   Tính năng: F-G2, F-H1</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>Mọi lệnh chúng ta gửi tới trụ sạc và câu trả lời (STN-10, CS-20): ai yêu cầu, vì sao, liên quan phiên sạc nào, và các kết quả không để lại bản tin trong nhật ký thô (chưa gửi, hết thời gian chờ). Gửi lệnh là khả năng của cổng OCPP nên bảng thuộc miền charging_stations, không thuộc charging_sessions. Ghi khi tạo lệnh và cập nhật một lần khi có trả lời; không có lịch sử thay đổi, không xóa mềm. Phần lớn câu trả lời chỉ là chấp nhận hay từ chối; kết quả thật đến sau bằng bản tin riêng. Bảng lệnh cho T-Box (telematic_commands, deferred.md 55) sẽ dùng cùng dạng. Ràng buộc kiểm tra (CS-20): lệnh NOT_SENT không có ocpp_message_id; lệnh đã có kết quả (không PENDING, không NOT_SENT) phải có answered_at.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5"/>
+    <row r="6" ht="27" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Cột</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Kiểu dữ liệu</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Cho phép rỗng</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>Khóa</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>Tham chiếu tới</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>Ý nghĩa</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>Ví dụ</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>Lưu lịch sử</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>command_id</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>uuid</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="n"/>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>Mã nội bộ của lệnh.</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>0000000c-5a6b-4c7d-8e9f-0a1b2c3d4e5f</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="n"/>
+    </row>
+    <row r="8" ht="27" customHeight="1">
+      <c r="A8" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>station_id</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>uuid</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>charging_stations.station_id (khi xóa: chặn xóa)</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>Trụ sạc nhận lệnh.</t>
+        </is>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>4b9d6f3a-2e8c-4a1b-9d5e-7f0c3a8b2d88</t>
+        </is>
+      </c>
+      <c r="I8" s="6" t="n"/>
+    </row>
+    <row r="9" ht="27" customHeight="1">
+      <c r="A9" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>evse_id</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>uuid</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>charging_evses.evse_id (khi xóa: chặn xóa)</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>Súng mà lệnh nhắm tới (mở khóa, ngừng phục vụ một súng); NULL nếu áp dụng cho cả trụ.</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>1e7a4c9f-6b3d-4e2a-8c5f-9d0b2e7a4c99</t>
+        </is>
+      </c>
+      <c r="I9" s="6" t="n"/>
+    </row>
+    <row r="10" ht="40.5" customHeight="1">
+      <c r="A10" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>session_id</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>uuid</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>charging_sessions.session_id (khi xóa: chặn xóa)</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>Phiên sạc mà lệnh liên quan: phiên PENDING mà lệnh bắt đầu từ xa khởi động (CE-10), hoặc phiên mà lệnh dừng từ xa kết thúc; NULL với mọi lệnh khác.</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>e5a2d8f1-4b7c-4e9a-b3d6-2c1f0e9a8dbb</t>
+        </is>
+      </c>
+      <c r="I10" s="6" t="n"/>
+    </row>
+    <row r="11" ht="94.5" customHeight="1">
+      <c r="A11" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>command_type</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>varchar(30)</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="n"/>
+      <c r="F11" s="6" t="n"/>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>Lệnh chúng ta yêu cầu, cùng một dạng cho cả hai phiên bản OCPP (CO-15); bộ chuyển đổi của từng phiên bản đổi nó thành bản tin của phiên bản đó. Giá trị: REMOTE_START | REMOTE_STOP | UNLOCK_CONNECTOR | RESET | CHANGE_AVAILABILITY | CHANGE_CONFIGURATION | GET_CONFIGURATION | TRIGGER_MESSAGE. Mỗi CHANGE_CONFIGURATION chỉ đặt một cấu hình, kể cả với 2.0.1, nên mỗi dòng có một câu trả lời (CS-20).</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>REMOTE_START</t>
+        </is>
+      </c>
+      <c r="I11" s="6" t="n"/>
+    </row>
+    <row r="12" ht="67.5" customHeight="1">
+      <c r="A12" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>parameters</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>jsonb</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="n"/>
+      <c r="F12" s="6" t="n"/>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>Những gì đã gửi ngoài các liên kết: kiểu khởi động lại, trạng thái phục vụ được yêu cầu, khóa và giá trị cấu hình, bản tin cần kích hoạt, remoteStartId của 2.0.1. Mã của lệnh bắt đầu từ xa không chép vào đây vì đã nằm ở phiên sạc. NULL nếu lệnh không có tham số.</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>{"remote_start_id": 1042}</t>
+        </is>
+      </c>
+      <c r="I12" s="6" t="n"/>
+    </row>
+    <row r="13" ht="54" customHeight="1">
+      <c r="A13" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>requested_by</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>uuid</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>users.user_id (khi xóa: chặn xóa)</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>Người dùng đã yêu cầu: tài xế quét mã với lệnh bắt đầu từ xa, nhân viên vận hành với lệnh thủ công; NULL khi hệ thống tự gửi (ví dụ yêu cầu cấu hình sau khi khởi động, CO-05).</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>9b2e7d4a-1c3f-4a8e-b6d2-5e0f1a9c3d22</t>
+        </is>
+      </c>
+      <c r="I13" s="6" t="n"/>
+    </row>
+    <row r="14" ht="40.5" customHeight="1">
+      <c r="A14" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>reason</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>varchar(200)</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="n"/>
+      <c r="F14" s="6" t="n"/>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>Lý do, do nhân viên vận hành nhập với lệnh thủ công; NULL với lệnh thường lệ (sạc bằng QR, yêu cầu cấu hình sau khi khởi động).</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>Súng 2 kẹt, mở khóa cho tài xế</t>
+        </is>
+      </c>
+      <c r="I14" s="6" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>requested_at</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>timestamptz</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="n"/>
+      <c r="F15" s="6" t="n"/>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>Thời điểm tạo lệnh, theo đồng hồ máy chủ của chúng ta.</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-15T08:29:11Z</t>
+        </is>
+      </c>
+      <c r="I15" s="6" t="n"/>
+    </row>
+    <row r="16" ht="40.5" customHeight="1">
+      <c r="A16" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>ocpp_message_id</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>varchar(36)</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="n"/>
+      <c r="F16" s="6" t="n"/>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>Mã bản tin của khung đã gửi; dùng để tìm khung đó và câu trả lời của trụ trong charging_ocpp_messages (CS-18). NULL khi chưa gửi gì.</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>7f3a9c1e-2b4d-4e8a-9c6f-1d0e2b7a5c33</t>
+        </is>
+      </c>
+      <c r="I16" s="6" t="n"/>
+    </row>
+    <row r="17" ht="81" customHeight="1">
+      <c r="A17" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>outcome</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>varchar(20)</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="n"/>
+      <c r="F17" s="6" t="n"/>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>Kết quả quan sát được, cùng một dạng (không có cột lý do vì là quan sát, không phải quyết định). PENDING: đã gửi, đang chờ trả lời. ACCEPTED / REJECTED: trụ chấp nhận hoặc từ chối. ERROR: trụ trả lời bằng lỗi OCPP. TIMEOUT: không có trả lời trong thời gian cấu hình. NOT_SENT: trụ không kết nối.</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="I17" s="6" t="n"/>
+    </row>
+    <row r="18" ht="54" customHeight="1">
+      <c r="A18" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>response_status</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>varchar(30)</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="n"/>
+      <c r="F18" s="6" t="n"/>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>Câu trả lời của trụ, đúng như gửi, có thể chi tiết hơn chấp nhận hay từ chối: Scheduled, RebootRequired, UnlockFailed, NotSupported, hoặc một mã lỗi như NotImplemented. NULL khi không có trả lời.</t>
+        </is>
+      </c>
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>Accepted</t>
+        </is>
+      </c>
+      <c r="I18" s="6" t="n"/>
+    </row>
+    <row r="19" ht="27" customHeight="1">
+      <c r="A19" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>answered_at</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>timestamptz</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="n"/>
+      <c r="F19" s="6" t="n"/>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>Thời điểm ghi nhận câu trả lời hoặc hết thời gian chờ; NULL khi PENDING hoặc NOT_SENT.</t>
+        </is>
+      </c>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-15T08:29:12Z</t>
+        </is>
+      </c>
+      <c r="I19" s="6" t="n"/>
+    </row>
+    <row r="20"/>
+    <row r="21">
+      <c r="A21" s="4" t="n"/>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>Chỉ mục (index)</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>Các cột</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>Duy nhất</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="n"/>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>Ghi chú</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="27" customHeight="1">
+      <c r="A22" s="6" t="n"/>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>ix_charging_station_commands_station_requested</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>station_id, requested_at</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="n"/>
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t>A charger's commands, newest first (STN-10)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="27" customHeight="1">
+      <c r="A23" s="6" t="n"/>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>ix_charging_station_commands_session_id</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>session_id</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="n"/>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>A session's remote start and stop</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A6:I19"/>
+  <hyperlinks>
+    <hyperlink ref="A2" location="'Tổng quan'!A1"/>
+    <hyperlink ref="F8" location="'charging_stations'!A1"/>
+    <hyperlink ref="F9" location="'charging_evses'!A1"/>
+    <hyperlink ref="F10" location="'charging_sessions'!A1"/>
+    <hyperlink ref="F13" location="'users'!A1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet55.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I50"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="7" max="7"/>
+    <col width="42" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>39. charging_sessions: Phiên sạc</t>
         </is>
       </c>
     </row>
@@ -37376,11 +38116,11 @@
         </is>
       </c>
     </row>
-    <row r="44">
+    <row r="44" ht="27" customHeight="1">
       <c r="A44" s="6" t="n"/>
       <c r="B44" s="7" t="inlineStr">
         <is>
-          <t>charging_session_events</t>
+          <t>charging_station_commands</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
@@ -37389,11 +38129,11 @@
         </is>
       </c>
     </row>
-    <row r="45" ht="27" customHeight="1">
+    <row r="45">
       <c r="A45" s="6" t="n"/>
       <c r="B45" s="7" t="inlineStr">
         <is>
-          <t>charging_session_measurements</t>
+          <t>charging_session_events</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
@@ -37402,11 +38142,11 @@
         </is>
       </c>
     </row>
-    <row r="46">
+    <row r="46" ht="27" customHeight="1">
       <c r="A46" s="6" t="n"/>
       <c r="B46" s="7" t="inlineStr">
         <is>
-          <t>policy_violations</t>
+          <t>charging_session_measurements</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
@@ -37419,7 +38159,7 @@
       <c r="A47" s="6" t="n"/>
       <c r="B47" s="7" t="inlineStr">
         <is>
-          <t>payments</t>
+          <t>policy_violations</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
@@ -37432,7 +38172,7 @@
       <c r="A48" s="6" t="n"/>
       <c r="B48" s="7" t="inlineStr">
         <is>
-          <t>wallet_transactions</t>
+          <t>payments</t>
         </is>
       </c>
       <c r="C48" s="6" t="inlineStr">
@@ -37445,10 +38185,23 @@
       <c r="A49" s="6" t="n"/>
       <c r="B49" s="7" t="inlineStr">
         <is>
+          <t>wallet_transactions</t>
+        </is>
+      </c>
+      <c r="C49" s="6" t="inlineStr">
+        <is>
+          <t>session_id</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="6" t="n"/>
+      <c r="B50" s="7" t="inlineStr">
+        <is>
           <t>invoice_lines</t>
         </is>
       </c>
-      <c r="C49" s="6" t="inlineStr">
+      <c r="C50" s="6" t="inlineStr">
         <is>
           <t>session_id</t>
         </is>
@@ -37464,18 +38217,19 @@
     <hyperlink ref="F11" location="'organizations'!A1"/>
     <hyperlink ref="F12" location="'users'!A1"/>
     <hyperlink ref="F13" location="'vehicles'!A1"/>
-    <hyperlink ref="B44" location="'charging_session_events'!A1"/>
-    <hyperlink ref="B45" location="'charging_session_measurements'!A1"/>
-    <hyperlink ref="B46" location="'policy_violations'!A1"/>
-    <hyperlink ref="B47" location="'payments'!A1"/>
-    <hyperlink ref="B48" location="'wallet_transactions'!A1"/>
-    <hyperlink ref="B49" location="'invoice_lines'!A1"/>
+    <hyperlink ref="B44" location="'charging_station_commands'!A1"/>
+    <hyperlink ref="B45" location="'charging_session_events'!A1"/>
+    <hyperlink ref="B46" location="'charging_session_measurements'!A1"/>
+    <hyperlink ref="B47" location="'policy_violations'!A1"/>
+    <hyperlink ref="B48" location="'payments'!A1"/>
+    <hyperlink ref="B49" location="'wallet_transactions'!A1"/>
+    <hyperlink ref="B50" location="'invoice_lines'!A1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet55.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet56.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -37498,7 +38252,7 @@
     <row r="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>39. charging_session_events: Sự kiện phiên sạc</t>
+          <t>40. charging_session_events: Sự kiện phiên sạc</t>
         </is>
       </c>
     </row>
@@ -37834,7 +38588,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet56.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet57.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -37857,7 +38611,7 @@
     <row r="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>40. charging_session_measurements: Số đo phiên sạc</t>
+          <t>41. charging_session_measurements: Số đo phiên sạc</t>
         </is>
       </c>
     </row>
@@ -38298,7 +39052,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet57.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet58.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -38321,7 +39075,7 @@
     <row r="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>41. notifications: Thông báo</t>
+          <t>42. notifications: Thông báo</t>
         </is>
       </c>
     </row>
@@ -38840,7 +39594,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet58.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet59.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -38863,7 +39617,7 @@
     <row r="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>42. support_cases: Ca hỗ trợ</t>
+          <t>43. support_cases: Ca hỗ trợ</t>
         </is>
       </c>
     </row>
@@ -39941,397 +40695,6 @@
     <hyperlink ref="F13" location="'vehicles'!A1"/>
     <hyperlink ref="F14" location="'drivers'!A1"/>
     <hyperlink ref="F15" location="'repair_partners'!A1"/>
-  </hyperlinks>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet59.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I17"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="40" customWidth="1" min="6" max="6"/>
-    <col width="60" customWidth="1" min="7" max="7"/>
-    <col width="42" customWidth="1" min="8" max="8"/>
-    <col width="11" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="9" t="inlineStr">
-        <is>
-          <t>43. repair_partners: Đối tác sửa chữa &amp; cứu hộ</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="10" t="inlineStr">
-        <is>
-          <t>← Tổng quan</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>Miền nghiệp vụ: CSKH &amp; cứu hộ (support)   ·   Chủ sở hữu dữ liệu: Nội bộ   ·   Tính năng: F-I4, F-I3</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="11" t="inlineStr">
-        <is>
-          <t>Một xưởng hoặc đơn vị cứu hộ mà CSKH có thể điều phối tới.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5"/>
-    <row r="6" ht="27" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>Cột</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>Kiểu dữ liệu</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>Cho phép rỗng</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>Khóa</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>Tham chiếu tới</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>Ý nghĩa</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>Ví dụ</t>
-        </is>
-      </c>
-      <c r="I6" s="4" t="inlineStr">
-        <is>
-          <t>Lưu lịch sử</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>partner_id</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>uuid</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
-      <c r="F7" s="6" t="n"/>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>Mã nội bộ của đối tác.</t>
-        </is>
-      </c>
-      <c r="H7" s="6" t="inlineStr">
-        <is>
-          <t>a9c6e3b1-5f2d-4a8c-b7e4-3d1f0a6c9bdd</t>
-        </is>
-      </c>
-      <c r="I7" s="6" t="n"/>
-    </row>
-    <row r="8" ht="27" customHeight="1">
-      <c r="A8" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>organization_id</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>uuid</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E8" s="6" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="F8" s="7" t="inlineStr">
-        <is>
-          <t>organizations.organization_id (khi xóa: chặn xóa)</t>
-        </is>
-      </c>
-      <c r="G8" s="6" t="inlineStr">
-        <is>
-          <t>Dòng của đối tác trong bảng organizations (loại PARTNER); kỹ thuật viên của đối tác là người dùng thuộc tổ chức đó.</t>
-        </is>
-      </c>
-      <c r="H8" s="6" t="inlineStr">
-        <is>
-          <t>0000001b-5a6b-4c7d-8e9f-0a1b2c3d4e5f</t>
-        </is>
-      </c>
-      <c r="I8" s="6" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>varchar(200)</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E9" s="6" t="n"/>
-      <c r="F9" s="6" t="n"/>
-      <c r="G9" s="6" t="inlineStr">
-        <is>
-          <t>Tên đối tác.</t>
-        </is>
-      </c>
-      <c r="H9" s="6" t="inlineStr">
-        <is>
-          <t>Garage Tín Phát - Thủ Đức</t>
-        </is>
-      </c>
-      <c r="I9" s="6" t="n"/>
-    </row>
-    <row r="10" ht="27" customHeight="1">
-      <c r="A10" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>partner_type</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>varchar(30)</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E10" s="6" t="n"/>
-      <c r="F10" s="6" t="n"/>
-      <c r="G10" s="6" t="inlineStr">
-        <is>
-          <t>Loại đối tác. Giá trị: G3_WORKSHOP | DEALER | THIRD_PARTY (mục 9 của feature-list).</t>
-        </is>
-      </c>
-      <c r="H10" s="6" t="inlineStr">
-        <is>
-          <t>THIRD_PARTY</t>
-        </is>
-      </c>
-      <c r="I10" s="6" t="n"/>
-    </row>
-    <row r="11" ht="27" customHeight="1">
-      <c r="A11" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>location</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>geography(POINT,4326)</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>có</t>
-        </is>
-      </c>
-      <c r="E11" s="6" t="n"/>
-      <c r="F11" s="6" t="n"/>
-      <c r="G11" s="6" t="inlineStr">
-        <is>
-          <t>Vị trí cơ sở (điểm WGS84, kinh độ trước).</t>
-        </is>
-      </c>
-      <c r="H11" s="6" t="inlineStr">
-        <is>
-          <t>POINT(106.7700 10.8500)</t>
-        </is>
-      </c>
-      <c r="I11" s="6" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>phone_number</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>varchar(20)</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>có</t>
-        </is>
-      </c>
-      <c r="E12" s="6" t="n"/>
-      <c r="F12" s="6" t="n"/>
-      <c r="G12" s="6" t="inlineStr">
-        <is>
-          <t>Số liên hệ để điều phối.</t>
-        </is>
-      </c>
-      <c r="H12" s="6" t="inlineStr">
-        <is>
-          <t>+842838123456</t>
-        </is>
-      </c>
-      <c r="I12" s="6" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>varchar(20)</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E13" s="6" t="n"/>
-      <c r="F13" s="6" t="n"/>
-      <c r="G13" s="6" t="inlineStr">
-        <is>
-          <t>Đối tác có nhận điều phối không.</t>
-        </is>
-      </c>
-      <c r="H13" s="6" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="I13" s="6" t="n"/>
-    </row>
-    <row r="14"/>
-    <row r="15">
-      <c r="A15" s="4" t="n"/>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>Được tham chiếu bởi bảng</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>Cột</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="6" t="n"/>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>support_cases</t>
-        </is>
-      </c>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>assigned_partner_id</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="6" t="n"/>
-      <c r="B17" s="7" t="inlineStr">
-        <is>
-          <t>maintenance_bookings</t>
-        </is>
-      </c>
-      <c r="C17" s="6" t="inlineStr">
-        <is>
-          <t>partner_id</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A6:I13"/>
-  <hyperlinks>
-    <hyperlink ref="A2" location="'Tổng quan'!A1"/>
-    <hyperlink ref="F8" location="'organizations'!A1"/>
-    <hyperlink ref="B16" location="'support_cases'!A1"/>
-    <hyperlink ref="B17" location="'maintenance_bookings'!A1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -40672,6 +41035,397 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:I17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="7" max="7"/>
+    <col width="42" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>44. repair_partners: Đối tác sửa chữa &amp; cứu hộ</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t>← Tổng quan</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>Miền nghiệp vụ: CSKH &amp; cứu hộ (support)   ·   Chủ sở hữu dữ liệu: Nội bộ   ·   Tính năng: F-I4, F-I3</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>Một xưởng hoặc đơn vị cứu hộ mà CSKH có thể điều phối tới.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5"/>
+    <row r="6" ht="27" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Cột</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Kiểu dữ liệu</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Cho phép rỗng</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>Khóa</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>Tham chiếu tới</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>Ý nghĩa</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>Ví dụ</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>Lưu lịch sử</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>partner_id</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>uuid</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="n"/>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>Mã nội bộ của đối tác.</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>a9c6e3b1-5f2d-4a8c-b7e4-3d1f0a6c9bdd</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="n"/>
+    </row>
+    <row r="8" ht="27" customHeight="1">
+      <c r="A8" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>organization_id</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>uuid</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>organizations.organization_id (khi xóa: chặn xóa)</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>Dòng của đối tác trong bảng organizations (loại PARTNER); kỹ thuật viên của đối tác là người dùng thuộc tổ chức đó.</t>
+        </is>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>0000001b-5a6b-4c7d-8e9f-0a1b2c3d4e5f</t>
+        </is>
+      </c>
+      <c r="I8" s="6" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>varchar(200)</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="n"/>
+      <c r="F9" s="6" t="n"/>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>Tên đối tác.</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>Garage Tín Phát - Thủ Đức</t>
+        </is>
+      </c>
+      <c r="I9" s="6" t="n"/>
+    </row>
+    <row r="10" ht="27" customHeight="1">
+      <c r="A10" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>partner_type</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>varchar(30)</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="n"/>
+      <c r="F10" s="6" t="n"/>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>Loại đối tác. Giá trị: G3_WORKSHOP | DEALER | THIRD_PARTY (mục 9 của feature-list).</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>THIRD_PARTY</t>
+        </is>
+      </c>
+      <c r="I10" s="6" t="n"/>
+    </row>
+    <row r="11" ht="27" customHeight="1">
+      <c r="A11" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>geography(POINT,4326)</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="n"/>
+      <c r="F11" s="6" t="n"/>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>Vị trí cơ sở (điểm WGS84, kinh độ trước).</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>POINT(106.7700 10.8500)</t>
+        </is>
+      </c>
+      <c r="I11" s="6" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>phone_number</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>varchar(20)</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="n"/>
+      <c r="F12" s="6" t="n"/>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>Số liên hệ để điều phối.</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>+842838123456</t>
+        </is>
+      </c>
+      <c r="I12" s="6" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>varchar(20)</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="n"/>
+      <c r="F13" s="6" t="n"/>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>Đối tác có nhận điều phối không.</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="I13" s="6" t="n"/>
+    </row>
+    <row r="14"/>
+    <row r="15">
+      <c r="A15" s="4" t="n"/>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>Được tham chiếu bởi bảng</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>Cột</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="n"/>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>support_cases</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>assigned_partner_id</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="n"/>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>maintenance_bookings</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>partner_id</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A6:I13"/>
+  <hyperlinks>
+    <hyperlink ref="A2" location="'Tổng quan'!A1"/>
+    <hyperlink ref="F8" location="'organizations'!A1"/>
+    <hyperlink ref="B16" location="'support_cases'!A1"/>
+    <hyperlink ref="B17" location="'maintenance_bookings'!A1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet61.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -40689,7 +41443,7 @@
     <row r="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>44. maintenance_bookings: Lịch bảo dưỡng</t>
+          <t>45. maintenance_bookings: Lịch bảo dưỡng</t>
         </is>
       </c>
     </row>
@@ -41033,7 +41787,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet61.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet62.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -41056,7 +41810,7 @@
     <row r="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>45. charging_policies: Chính sách sạc</t>
+          <t>46. charging_policies: Chính sách sạc</t>
         </is>
       </c>
     </row>
@@ -41353,7 +42107,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet62.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet63.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -41376,7 +42130,7 @@
     <row r="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>46. charging_policy_versions: Phiên bản chính sách sạc</t>
+          <t>47. charging_policy_versions: Phiên bản chính sách sạc</t>
         </is>
       </c>
     </row>
@@ -41878,415 +42632,6 @@
     <hyperlink ref="F8" location="'charging_policies'!A1"/>
     <hyperlink ref="F16" location="'users'!A1"/>
     <hyperlink ref="B22" location="'policy_violations'!A1"/>
-  </hyperlinks>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet63.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="40" customWidth="1" min="6" max="6"/>
-    <col width="60" customWidth="1" min="7" max="7"/>
-    <col width="42" customWidth="1" min="8" max="8"/>
-    <col width="11" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="9" t="inlineStr">
-        <is>
-          <t>47. charging_policy_assignments: Áp dụng chính sách sạc</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="10" t="inlineStr">
-        <is>
-          <t>← Tổng quan</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>Miền nghiệp vụ: Chính sách sạc (bảo hành) (policy)   ·   Chủ sở hữu dữ liệu: Khách hàng   ·   Tính năng: F-B1</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="11" t="inlineStr">
-        <is>
-          <t>Chính sách nào áp dụng cho một xe, một đội xe hay một dòng xe.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5"/>
-    <row r="6" ht="27" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>Cột</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>Kiểu dữ liệu</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>Cho phép rỗng</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>Khóa</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>Tham chiếu tới</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>Ý nghĩa</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>Ví dụ</t>
-        </is>
-      </c>
-      <c r="I6" s="4" t="inlineStr">
-        <is>
-          <t>Lưu lịch sử</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>assignment_id</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>uuid</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
-      <c r="F7" s="6" t="n"/>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>Mã nội bộ của lần áp dụng.</t>
-        </is>
-      </c>
-      <c r="H7" s="6" t="inlineStr">
-        <is>
-          <t>0000000e-5a6b-4c7d-8e9f-0a1b2c3d4e5f</t>
-        </is>
-      </c>
-      <c r="I7" s="6" t="n"/>
-    </row>
-    <row r="8" ht="27" customHeight="1">
-      <c r="A8" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>organization_id</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>uuid</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E8" s="6" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="F8" s="7" t="inlineStr">
-        <is>
-          <t>organizations.organization_id (khi xóa: chặn xóa)</t>
-        </is>
-      </c>
-      <c r="G8" s="6" t="inlineStr">
-        <is>
-          <t>Tổ chức khách hàng của lần áp dụng.</t>
-        </is>
-      </c>
-      <c r="H8" s="6" t="inlineStr">
-        <is>
-          <t>3f6c2a1e-8b4d-4e2a-9c1f-0a7d5b2e4c11</t>
-        </is>
-      </c>
-      <c r="I8" s="6" t="n"/>
-    </row>
-    <row r="9" ht="27" customHeight="1">
-      <c r="A9" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>policy_id</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>uuid</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E9" s="6" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="F9" s="7" t="inlineStr">
-        <is>
-          <t>charging_policies.policy_id (khi xóa: chặn xóa)</t>
-        </is>
-      </c>
-      <c r="G9" s="6" t="inlineStr">
-        <is>
-          <t>Chính sách được áp dụng.</t>
-        </is>
-      </c>
-      <c r="H9" s="6" t="inlineStr">
-        <is>
-          <t>b8e5a2d9-3c6f-4b1e-a9d7-5f2c0e8b1aee</t>
-        </is>
-      </c>
-      <c r="I9" s="6" t="n"/>
-    </row>
-    <row r="10" ht="27" customHeight="1">
-      <c r="A10" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>vehicle_id</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>uuid</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>có</t>
-        </is>
-      </c>
-      <c r="E10" s="6" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="F10" s="7" t="inlineStr">
-        <is>
-          <t>vehicles.vehicle_id (khi xóa: chặn xóa)</t>
-        </is>
-      </c>
-      <c r="G10" s="6" t="inlineStr">
-        <is>
-          <t>Xe được áp dụng, nếu phạm vi là một xe. Chỉ đúng một trong vehicle_id / fleet_id / vehicle_model có giá trị.</t>
-        </is>
-      </c>
-      <c r="H10" s="6" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="I10" s="6" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>fleet_id</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>uuid</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>có</t>
-        </is>
-      </c>
-      <c r="E11" s="6" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="F11" s="7" t="inlineStr">
-        <is>
-          <t>fleets.fleet_id (khi xóa: chặn xóa)</t>
-        </is>
-      </c>
-      <c r="G11" s="6" t="inlineStr">
-        <is>
-          <t>Đội xe được áp dụng, nếu phạm vi là một đội.</t>
-        </is>
-      </c>
-      <c r="H11" s="6" t="inlineStr">
-        <is>
-          <t>8d5f2b7e-1a9c-4f3d-b8e2-6c0a4d9f1e77</t>
-        </is>
-      </c>
-      <c r="I11" s="6" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>vehicle_model</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>varchar(50)</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>có</t>
-        </is>
-      </c>
-      <c r="E12" s="6" t="n"/>
-      <c r="F12" s="6" t="n"/>
-      <c r="G12" s="6" t="inlineStr">
-        <is>
-          <t>Dòng xe được áp dụng, nếu phạm vi là một dòng xe.</t>
-        </is>
-      </c>
-      <c r="H12" s="6" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="I12" s="6" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>assigned_at</t>
-        </is>
-      </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>timestamptz</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E13" s="6" t="n"/>
-      <c r="F13" s="6" t="n"/>
-      <c r="G13" s="6" t="inlineStr">
-        <is>
-          <t>Thời điểm bắt đầu áp dụng.</t>
-        </is>
-      </c>
-      <c r="H13" s="6" t="inlineStr">
-        <is>
-          <t>2026-10-01T00:00:00Z</t>
-        </is>
-      </c>
-      <c r="I13" s="6" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="B14" s="6" t="inlineStr">
-        <is>
-          <t>unassigned_at</t>
-        </is>
-      </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>timestamptz</t>
-        </is>
-      </c>
-      <c r="D14" s="6" t="inlineStr">
-        <is>
-          <t>có</t>
-        </is>
-      </c>
-      <c r="E14" s="6" t="n"/>
-      <c r="F14" s="6" t="n"/>
-      <c r="G14" s="6" t="inlineStr">
-        <is>
-          <t>Thời điểm kết thúc; NULL khi còn hiệu lực.</t>
-        </is>
-      </c>
-      <c r="H14" s="6" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="I14" s="6" t="n"/>
-    </row>
-  </sheetData>
-  <autoFilter ref="A6:I14"/>
-  <hyperlinks>
-    <hyperlink ref="A2" location="'Tổng quan'!A1"/>
-    <hyperlink ref="F8" location="'organizations'!A1"/>
-    <hyperlink ref="F9" location="'charging_policies'!A1"/>
-    <hyperlink ref="F10" location="'vehicles'!A1"/>
-    <hyperlink ref="F11" location="'fleets'!A1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -42315,7 +42660,7 @@
     <row r="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>48. policy_violations: Vi phạm chính sách sạc</t>
+          <t>48. charging_policy_assignments: Áp dụng chính sách sạc</t>
         </is>
       </c>
     </row>
@@ -42329,14 +42674,14 @@
     <row r="3">
       <c r="A3" s="11" t="inlineStr">
         <is>
-          <t>Miền nghiệp vụ: Chính sách sạc (bảo hành) (policy)   ·   Chủ sở hữu dữ liệu: Khách hàng   ·   Tính năng: F-B3, F-B6</t>
+          <t>Miền nghiệp vụ: Chính sách sạc (bảo hành) (policy)   ·   Chủ sở hữu dữ liệu: Khách hàng   ·   Tính năng: F-B1</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="11" t="inlineStr">
         <is>
-          <t>Một phiên sạc vi phạm chính sách, kèm bằng chứng. Hệ quả của vi phạm vẫn là câu hỏi kinh doanh còn mở (mục 3 của feature-list).</t>
+          <t>Chính sách nào áp dụng cho một xe, một đội xe hay một dòng xe.</t>
         </is>
       </c>
     </row>
@@ -42394,7 +42739,7 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>violation_id</t>
+          <t>assignment_id</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
@@ -42415,12 +42760,12 @@
       <c r="F7" s="6" t="n"/>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>Mã nội bộ của vi phạm.</t>
+          <t>Mã nội bộ của lần áp dụng.</t>
         </is>
       </c>
       <c r="H7" s="6" t="inlineStr">
         <is>
-          <t>0000000f-5a6b-4c7d-8e9f-0a1b2c3d4e5f</t>
+          <t>0000000e-5a6b-4c7d-8e9f-0a1b2c3d4e5f</t>
         </is>
       </c>
       <c r="I7" s="6" t="n"/>
@@ -42456,7 +42801,7 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>Tổ chức khách hàng sở hữu xe.</t>
+          <t>Tổ chức khách hàng của lần áp dụng.</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr">
@@ -42472,7 +42817,7 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>session_id</t>
+          <t>policy_id</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
@@ -42492,17 +42837,17 @@
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>charging_sessions.session_id (khi xóa: chặn xóa)</t>
+          <t>charging_policies.policy_id (khi xóa: chặn xóa)</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>Phiên sạc đã vi phạm chính sách.</t>
+          <t>Chính sách được áp dụng.</t>
         </is>
       </c>
       <c r="H9" s="6" t="inlineStr">
         <is>
-          <t>e5a2d8f1-4b7c-4e9a-b3d6-2c1f0e9a8dbb</t>
+          <t>b8e5a2d9-3c6f-4b1e-a9d7-5f2c0e8b1aee</t>
         </is>
       </c>
       <c r="I9" s="6" t="n"/>
@@ -42523,7 +42868,7 @@
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>không</t>
+          <t>có</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
@@ -42538,23 +42883,23 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>Xe liên quan.</t>
+          <t>Xe được áp dụng, nếu phạm vi là một xe. Chỉ đúng một trong vehicle_id / fleet_id / vehicle_model có giá trị.</t>
         </is>
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>7a4c1e9b-3d2f-4b8a-a6c5-1e0d9f8b7a44</t>
+          <t>NULL</t>
         </is>
       </c>
       <c r="I10" s="6" t="n"/>
     </row>
-    <row r="11" ht="27" customHeight="1">
+    <row r="11">
       <c r="A11" s="6" t="n">
         <v>5</v>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>policy_version_id</t>
+          <t>fleet_id</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
@@ -42564,7 +42909,7 @@
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>không</t>
+          <t>có</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
@@ -42574,17 +42919,17 @@
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>charging_policy_versions.version_id (khi xóa: chặn xóa)</t>
+          <t>fleets.fleet_id (khi xóa: chặn xóa)</t>
         </is>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>Đúng phiên bản chính sách bị vi phạm.</t>
+          <t>Đội xe được áp dụng, nếu phạm vi là một đội.</t>
         </is>
       </c>
       <c r="H11" s="6" t="inlineStr">
         <is>
-          <t>c7d4f1a8-2b5e-4c9d-8f6a-1e3b0d7c4aff</t>
+          <t>8d5f2b7e-1a9c-4f3d-b8e2-6c0a4d9f1e77</t>
         </is>
       </c>
       <c r="I11" s="6" t="n"/>
@@ -42595,29 +42940,29 @@
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>violation_type</t>
+          <t>vehicle_model</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>varchar(30)</t>
+          <t>varchar(50)</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>không</t>
+          <t>có</t>
         </is>
       </c>
       <c r="E12" s="6" t="n"/>
       <c r="F12" s="6" t="n"/>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>Quy tắc nào bị vi phạm.</t>
+          <t>Dòng xe được áp dụng, nếu phạm vi là một dòng xe.</t>
         </is>
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>SOC_ABOVE_MAX</t>
+          <t>NULL</t>
         </is>
       </c>
       <c r="I12" s="6" t="n"/>
@@ -42628,7 +42973,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>detected_at</t>
+          <t>assigned_at</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
@@ -42645,45 +42990,45 @@
       <c r="F13" s="6" t="n"/>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>Thời điểm phát hiện vi phạm.</t>
+          <t>Thời điểm bắt đầu áp dụng.</t>
         </is>
       </c>
       <c r="H13" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15T09:45:00Z</t>
+          <t>2026-10-01T00:00:00Z</t>
         </is>
       </c>
       <c r="I13" s="6" t="n"/>
     </row>
-    <row r="14" ht="27" customHeight="1">
+    <row r="14">
       <c r="A14" s="6" t="n">
         <v>8</v>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>evidence</t>
+          <t>unassigned_at</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>jsonb</t>
+          <t>timestamptz</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>không</t>
+          <t>có</t>
         </is>
       </c>
       <c r="E14" s="6" t="n"/>
       <c r="F14" s="6" t="n"/>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>Ảnh chụp dữ liệu chứng minh vi phạm, dạng JSON.</t>
+          <t>Thời điểm kết thúc; NULL khi còn hiệu lực.</t>
         </is>
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
-          <t>{"soc_end": 98.5, "soc_max": 90, "meter_stop_wh": 1712860}</t>
+          <t>NULL</t>
         </is>
       </c>
       <c r="I14" s="6" t="n"/>
@@ -42693,9 +43038,9 @@
   <hyperlinks>
     <hyperlink ref="A2" location="'Tổng quan'!A1"/>
     <hyperlink ref="F8" location="'organizations'!A1"/>
-    <hyperlink ref="F9" location="'charging_sessions'!A1"/>
+    <hyperlink ref="F9" location="'charging_policies'!A1"/>
     <hyperlink ref="F10" location="'vehicles'!A1"/>
-    <hyperlink ref="F11" location="'charging_policy_versions'!A1"/>
+    <hyperlink ref="F11" location="'fleets'!A1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -42724,7 +43069,416 @@
     <row r="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>49. tariffs: Biểu giá điện</t>
+          <t>49. policy_violations: Vi phạm chính sách sạc</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t>← Tổng quan</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>Miền nghiệp vụ: Chính sách sạc (bảo hành) (policy)   ·   Chủ sở hữu dữ liệu: Khách hàng   ·   Tính năng: F-B3, F-B6</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>Một phiên sạc vi phạm chính sách, kèm bằng chứng. Hệ quả của vi phạm vẫn là câu hỏi kinh doanh còn mở (mục 3 của feature-list).</t>
+        </is>
+      </c>
+    </row>
+    <row r="5"/>
+    <row r="6" ht="27" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Cột</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Kiểu dữ liệu</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Cho phép rỗng</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>Khóa</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>Tham chiếu tới</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>Ý nghĩa</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>Ví dụ</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>Lưu lịch sử</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>violation_id</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>uuid</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="n"/>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>Mã nội bộ của vi phạm.</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>0000000f-5a6b-4c7d-8e9f-0a1b2c3d4e5f</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="n"/>
+    </row>
+    <row r="8" ht="27" customHeight="1">
+      <c r="A8" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>organization_id</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>uuid</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>organizations.organization_id (khi xóa: chặn xóa)</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>Tổ chức khách hàng sở hữu xe.</t>
+        </is>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>3f6c2a1e-8b4d-4e2a-9c1f-0a7d5b2e4c11</t>
+        </is>
+      </c>
+      <c r="I8" s="6" t="n"/>
+    </row>
+    <row r="9" ht="27" customHeight="1">
+      <c r="A9" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>session_id</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>uuid</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>charging_sessions.session_id (khi xóa: chặn xóa)</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>Phiên sạc đã vi phạm chính sách.</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>e5a2d8f1-4b7c-4e9a-b3d6-2c1f0e9a8dbb</t>
+        </is>
+      </c>
+      <c r="I9" s="6" t="n"/>
+    </row>
+    <row r="10" ht="27" customHeight="1">
+      <c r="A10" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>vehicle_id</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>uuid</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>vehicles.vehicle_id (khi xóa: chặn xóa)</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>Xe liên quan.</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>7a4c1e9b-3d2f-4b8a-a6c5-1e0d9f8b7a44</t>
+        </is>
+      </c>
+      <c r="I10" s="6" t="n"/>
+    </row>
+    <row r="11" ht="27" customHeight="1">
+      <c r="A11" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>policy_version_id</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>uuid</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>charging_policy_versions.version_id (khi xóa: chặn xóa)</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>Đúng phiên bản chính sách bị vi phạm.</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>c7d4f1a8-2b5e-4c9d-8f6a-1e3b0d7c4aff</t>
+        </is>
+      </c>
+      <c r="I11" s="6" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>violation_type</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>varchar(30)</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="n"/>
+      <c r="F12" s="6" t="n"/>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>Quy tắc nào bị vi phạm.</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>SOC_ABOVE_MAX</t>
+        </is>
+      </c>
+      <c r="I12" s="6" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>detected_at</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>timestamptz</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="n"/>
+      <c r="F13" s="6" t="n"/>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>Thời điểm phát hiện vi phạm.</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-15T09:45:00Z</t>
+        </is>
+      </c>
+      <c r="I13" s="6" t="n"/>
+    </row>
+    <row r="14" ht="27" customHeight="1">
+      <c r="A14" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>jsonb</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="n"/>
+      <c r="F14" s="6" t="n"/>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>Ảnh chụp dữ liệu chứng minh vi phạm, dạng JSON.</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>{"soc_end": 98.5, "soc_max": 90, "meter_stop_wh": 1712860}</t>
+        </is>
+      </c>
+      <c r="I14" s="6" t="n"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A6:I14"/>
+  <hyperlinks>
+    <hyperlink ref="A2" location="'Tổng quan'!A1"/>
+    <hyperlink ref="F8" location="'organizations'!A1"/>
+    <hyperlink ref="F9" location="'charging_sessions'!A1"/>
+    <hyperlink ref="F10" location="'vehicles'!A1"/>
+    <hyperlink ref="F11" location="'charging_policy_versions'!A1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet66.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="7" max="7"/>
+    <col width="42" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>50. tariffs: Biểu giá điện</t>
         </is>
       </c>
     </row>
@@ -43083,7 +43837,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet66.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet67.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -43106,7 +43860,7 @@
     <row r="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>50. payments: Thanh toán</t>
+          <t>51. payments: Thanh toán</t>
         </is>
       </c>
     </row>
@@ -43563,359 +44317,6 @@
     <hyperlink ref="F8" location="'organizations'!A1"/>
     <hyperlink ref="F9" location="'charging_sessions'!A1"/>
     <hyperlink ref="B19" location="'wallet_transactions'!A1"/>
-  </hyperlinks>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet67.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I15"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="40" customWidth="1" min="6" max="6"/>
-    <col width="60" customWidth="1" min="7" max="7"/>
-    <col width="42" customWidth="1" min="8" max="8"/>
-    <col width="11" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="9" t="inlineStr">
-        <is>
-          <t>51. wallets: Ví</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="10" t="inlineStr">
-        <is>
-          <t>← Tổng quan</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>Miền nghiệp vụ: Thanh toán &amp; hóa đơn (billing)   ·   Chủ sở hữu dữ liệu: Khách hàng   ·   Tính năng: F-H2</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="11" t="inlineStr">
-        <is>
-          <t>Số dư trả trước của một tài xế hoặc của cả tổ chức.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5"/>
-    <row r="6" ht="27" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>Cột</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>Kiểu dữ liệu</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>Cho phép rỗng</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>Khóa</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>Tham chiếu tới</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>Ý nghĩa</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>Ví dụ</t>
-        </is>
-      </c>
-      <c r="I6" s="4" t="inlineStr">
-        <is>
-          <t>Lưu lịch sử</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>wallet_id</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>uuid</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
-      <c r="F7" s="6" t="n"/>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>Mã nội bộ của ví.</t>
-        </is>
-      </c>
-      <c r="H7" s="6" t="inlineStr">
-        <is>
-          <t>5c3a0e7d-2f9b-4c1e-a8d3-7b6f0c2e9a32</t>
-        </is>
-      </c>
-      <c r="I7" s="6" t="n"/>
-    </row>
-    <row r="8" ht="27" customHeight="1">
-      <c r="A8" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>organization_id</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>uuid</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E8" s="6" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="F8" s="7" t="inlineStr">
-        <is>
-          <t>organizations.organization_id (khi xóa: chặn xóa)</t>
-        </is>
-      </c>
-      <c r="G8" s="6" t="inlineStr">
-        <is>
-          <t>Tổ chức khách hàng sở hữu ví.</t>
-        </is>
-      </c>
-      <c r="H8" s="6" t="inlineStr">
-        <is>
-          <t>3f6c2a1e-8b4d-4e2a-9c1f-0a7d5b2e4c11</t>
-        </is>
-      </c>
-      <c r="I8" s="6" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>driver_id</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>uuid</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>có</t>
-        </is>
-      </c>
-      <c r="E9" s="6" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="F9" s="7" t="inlineStr">
-        <is>
-          <t>drivers.driver_id (khi xóa: chặn xóa)</t>
-        </is>
-      </c>
-      <c r="G9" s="6" t="inlineStr">
-        <is>
-          <t>Tài xế sở hữu ví; NULL với ví cấp tổ chức (quyết định D5).</t>
-        </is>
-      </c>
-      <c r="H9" s="6" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="I9" s="6" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>balance</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>numeric(14,2)</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E10" s="6" t="n"/>
-      <c r="F10" s="6" t="n"/>
-      <c r="G10" s="6" t="inlineStr">
-        <is>
-          <t>Số dư hiện tại; phải bằng tổng các giao dịch của ví.</t>
-        </is>
-      </c>
-      <c r="H10" s="6" t="inlineStr">
-        <is>
-          <t>12500000.00</t>
-        </is>
-      </c>
-      <c r="I10" s="6" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>currency</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>char(3)</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E11" s="6" t="n"/>
-      <c r="F11" s="6" t="n"/>
-      <c r="G11" s="6" t="inlineStr">
-        <is>
-          <t>Mã tiền tệ ISO 4217.</t>
-        </is>
-      </c>
-      <c r="H11" s="6" t="inlineStr">
-        <is>
-          <t>VND</t>
-        </is>
-      </c>
-      <c r="I11" s="6" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>varchar(20)</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E12" s="6" t="n"/>
-      <c r="F12" s="6" t="n"/>
-      <c r="G12" s="6" t="inlineStr">
-        <is>
-          <t>Ví có dùng được không.</t>
-        </is>
-      </c>
-      <c r="H12" s="6" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="I12" s="6" t="n"/>
-    </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" s="4" t="n"/>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>Được tham chiếu bởi bảng</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>Cột</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="6" t="n"/>
-      <c r="B15" s="7" t="inlineStr">
-        <is>
-          <t>wallet_transactions</t>
-        </is>
-      </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>wallet_id</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A6:I12"/>
-  <hyperlinks>
-    <hyperlink ref="A2" location="'Tổng quan'!A1"/>
-    <hyperlink ref="F8" location="'organizations'!A1"/>
-    <hyperlink ref="F9" location="'drivers'!A1"/>
-    <hyperlink ref="B15" location="'wallet_transactions'!A1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -43944,7 +44345,7 @@
     <row r="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>52. wallet_transactions: Giao dịch ví</t>
+          <t>52. wallets: Ví</t>
         </is>
       </c>
     </row>
@@ -43965,7 +44366,7 @@
     <row r="4">
       <c r="A4" s="11" t="inlineStr">
         <is>
-          <t>Biến động tiền vào/ra khỏi ví, chỉ ghi thêm.</t>
+          <t>Số dư trả trước của một tài xế hoặc của cả tổ chức.</t>
         </is>
       </c>
     </row>
@@ -44023,7 +44424,7 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>transaction_id</t>
+          <t>wallet_id</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
@@ -44044,12 +44445,12 @@
       <c r="F7" s="6" t="n"/>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>Mã nội bộ của giao dịch.</t>
+          <t>Mã nội bộ của ví.</t>
         </is>
       </c>
       <c r="H7" s="6" t="inlineStr">
         <is>
-          <t>00000010-5a6b-4c7d-8e9f-0a1b2c3d4e5f</t>
+          <t>5c3a0e7d-2f9b-4c1e-a8d3-7b6f0c2e9a32</t>
         </is>
       </c>
       <c r="I7" s="6" t="n"/>
@@ -44085,7 +44486,7 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>Tổ chức khách hàng của ví.</t>
+          <t>Tổ chức khách hàng sở hữu ví.</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr">
@@ -44101,7 +44502,7 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>wallet_id</t>
+          <t>driver_id</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
@@ -44111,7 +44512,7 @@
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>không</t>
+          <t>có</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
@@ -44121,33 +44522,33 @@
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>wallets.wallet_id (khi xóa: chặn xóa)</t>
+          <t>drivers.driver_id (khi xóa: chặn xóa)</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>Ví bị ảnh hưởng.</t>
+          <t>Tài xế sở hữu ví; NULL với ví cấp tổ chức (quyết định D5).</t>
         </is>
       </c>
       <c r="H9" s="6" t="inlineStr">
         <is>
-          <t>5c3a0e7d-2f9b-4c1e-a8d3-7b6f0c2e9a32</t>
+          <t>NULL</t>
         </is>
       </c>
       <c r="I9" s="6" t="n"/>
     </row>
-    <row r="10" ht="27" customHeight="1">
+    <row r="10">
       <c r="A10" s="6" t="n">
         <v>4</v>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>transaction_type</t>
+          <t>balance</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>varchar(20)</t>
+          <t>numeric(14,2)</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
@@ -44159,12 +44560,12 @@
       <c r="F10" s="6" t="n"/>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>Loại biến động tiền. Giá trị: TOP_UP | CHARGE | WITHDRAW | REFUND.</t>
+          <t>Số dư hiện tại; phải bằng tổng các giao dịch của ví.</t>
         </is>
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>CHARGE</t>
+          <t>12500000.00</t>
         </is>
       </c>
       <c r="I10" s="6" t="n"/>
@@ -44175,12 +44576,12 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>amount</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>numeric(14,2)</t>
+          <t>char(3)</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
@@ -44192,12 +44593,12 @@
       <c r="F11" s="6" t="n"/>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>Số tiền có dấu: dương là cộng tiền, âm là trừ tiền.</t>
+          <t>Mã tiền tệ ISO 4217.</t>
         </is>
       </c>
       <c r="H11" s="6" t="inlineStr">
         <is>
-          <t>-866250.00</t>
+          <t>VND</t>
         </is>
       </c>
       <c r="I11" s="6" t="n"/>
@@ -44208,12 +44609,12 @@
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>balance_after</t>
+          <t>status</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>numeric(14,2)</t>
+          <t>varchar(20)</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
@@ -44225,139 +44626,50 @@
       <c r="F12" s="6" t="n"/>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>Số dư ví ngay sau giao dịch.</t>
+          <t>Ví có dùng được không.</t>
         </is>
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>11633750.00</t>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="I12" s="6" t="n"/>
     </row>
-    <row r="13" ht="27" customHeight="1">
-      <c r="A13" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>session_id</t>
-        </is>
-      </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>uuid</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="inlineStr">
-        <is>
-          <t>có</t>
-        </is>
-      </c>
-      <c r="E13" s="6" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="F13" s="7" t="inlineStr">
-        <is>
-          <t>charging_sessions.session_id (khi xóa: chặn xóa)</t>
-        </is>
-      </c>
-      <c r="G13" s="6" t="inlineStr">
-        <is>
-          <t>Phiên sạc được trả tiền, với giao dịch CHARGE.</t>
-        </is>
-      </c>
-      <c r="H13" s="6" t="inlineStr">
-        <is>
-          <t>e5a2d8f1-4b7c-4e9a-b3d6-2c1f0e9a8dbb</t>
-        </is>
-      </c>
-      <c r="I13" s="6" t="n"/>
-    </row>
-    <row r="14" ht="27" customHeight="1">
-      <c r="A14" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="B14" s="6" t="inlineStr">
-        <is>
-          <t>payment_id</t>
-        </is>
-      </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>uuid</t>
-        </is>
-      </c>
-      <c r="D14" s="6" t="inlineStr">
-        <is>
-          <t>có</t>
-        </is>
-      </c>
-      <c r="E14" s="6" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="F14" s="7" t="inlineStr">
-        <is>
-          <t>payments.payment_id (khi xóa: chặn xóa)</t>
-        </is>
-      </c>
-      <c r="G14" s="6" t="inlineStr">
-        <is>
-          <t>Thanh toán qua cổng đứng sau một lần nạp tiền, nếu có.</t>
-        </is>
-      </c>
-      <c r="H14" s="6" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="I14" s="6" t="n"/>
+    <row r="13"/>
+    <row r="14">
+      <c r="A14" s="4" t="n"/>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>Được tham chiếu bởi bảng</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>Cột</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="B15" s="6" t="inlineStr">
-        <is>
-          <t>occurred_at</t>
+      <c r="A15" s="6" t="n"/>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>wallet_transactions</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>timestamptz</t>
-        </is>
-      </c>
-      <c r="D15" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E15" s="6" t="n"/>
-      <c r="F15" s="6" t="n"/>
-      <c r="G15" s="6" t="inlineStr">
-        <is>
-          <t>Thời điểm phát sinh giao dịch.</t>
-        </is>
-      </c>
-      <c r="H15" s="6" t="inlineStr">
-        <is>
-          <t>2026-09-15T09:46:12Z</t>
-        </is>
-      </c>
-      <c r="I15" s="6" t="n"/>
+          <t>wallet_id</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A6:I15"/>
+  <autoFilter ref="A6:I12"/>
   <hyperlinks>
     <hyperlink ref="A2" location="'Tổng quan'!A1"/>
     <hyperlink ref="F8" location="'organizations'!A1"/>
-    <hyperlink ref="F9" location="'wallets'!A1"/>
-    <hyperlink ref="F13" location="'charging_sessions'!A1"/>
-    <hyperlink ref="F14" location="'payments'!A1"/>
+    <hyperlink ref="F9" location="'drivers'!A1"/>
+    <hyperlink ref="B15" location="'wallet_transactions'!A1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -44369,7 +44681,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -44386,7 +44698,7 @@
     <row r="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>53. invoices: Hóa đơn</t>
+          <t>53. wallet_transactions: Giao dịch ví</t>
         </is>
       </c>
     </row>
@@ -44400,14 +44712,14 @@
     <row r="3">
       <c r="A3" s="11" t="inlineStr">
         <is>
-          <t>Miền nghiệp vụ: Thanh toán &amp; hóa đơn (billing)   ·   Chủ sở hữu dữ liệu: Khách hàng   ·   Tính năng: F-H3, F-H4</t>
+          <t>Miền nghiệp vụ: Thanh toán &amp; hóa đơn (billing)   ·   Chủ sở hữu dữ liệu: Khách hàng   ·   Tính năng: F-H2</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="11" t="inlineStr">
         <is>
-          <t>Một hóa đơn điện tử hợp lệ. Khi đã PHÁT HÀNH thì không sửa, chỉ điều chỉnh hoặc hủy bằng hóa đơn mới.</t>
+          <t>Biến động tiền vào/ra khỏi ví, chỉ ghi thêm.</t>
         </is>
       </c>
     </row>
@@ -44465,7 +44777,7 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>invoice_id</t>
+          <t>transaction_id</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
@@ -44486,12 +44798,12 @@
       <c r="F7" s="6" t="n"/>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>Mã nội bộ của hóa đơn.</t>
+          <t>Mã nội bộ của giao dịch.</t>
         </is>
       </c>
       <c r="H7" s="6" t="inlineStr">
         <is>
-          <t>7e5c2a9f-4b1d-4e3a-9c8f-0d6b1e4a7c43</t>
+          <t>00000010-5a6b-4c7d-8e9f-0a1b2c3d4e5f</t>
         </is>
       </c>
       <c r="I7" s="6" t="n"/>
@@ -44527,7 +44839,7 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>Tổ chức khách hàng được xuất hóa đơn.</t>
+          <t>Tổ chức khách hàng của ví.</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr">
@@ -44537,18 +44849,18 @@
       </c>
       <c r="I8" s="6" t="n"/>
     </row>
-    <row r="9" ht="27" customHeight="1">
+    <row r="9">
       <c r="A9" s="6" t="n">
         <v>3</v>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>invoice_type</t>
+          <t>wallet_id</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>varchar(20)</t>
+          <t>uuid</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
@@ -44556,49 +44868,57 @@
           <t>không</t>
         </is>
       </c>
-      <c r="E9" s="6" t="n"/>
-      <c r="F9" s="6" t="n"/>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>wallets.wallet_id (khi xóa: chặn xóa)</t>
+        </is>
+      </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>Hóa đơn lẻ theo phiên hay hóa đơn tổng hợp tháng cho đội xe. Giá trị: RETAIL | FLEET_MONTHLY.</t>
+          <t>Ví bị ảnh hưởng.</t>
         </is>
       </c>
       <c r="H9" s="6" t="inlineStr">
         <is>
-          <t>FLEET_MONTHLY</t>
+          <t>5c3a0e7d-2f9b-4c1e-a8d3-7b6f0c2e9a32</t>
         </is>
       </c>
       <c r="I9" s="6" t="n"/>
     </row>
-    <row r="10">
+    <row r="10" ht="27" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>4</v>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>period_start</t>
+          <t>transaction_type</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>varchar(20)</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>có</t>
+          <t>không</t>
         </is>
       </c>
       <c r="E10" s="6" t="n"/>
       <c r="F10" s="6" t="n"/>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>Ngày đầu kỳ; NULL với hóa đơn một phiên.</t>
+          <t>Loại biến động tiền. Giá trị: TOP_UP | CHARGE | WITHDRAW | REFUND.</t>
         </is>
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>CHARGE</t>
         </is>
       </c>
       <c r="I10" s="6" t="n"/>
@@ -44609,29 +44929,29 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>period_end</t>
+          <t>amount</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>numeric(14,2)</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>có</t>
+          <t>không</t>
         </is>
       </c>
       <c r="E11" s="6" t="n"/>
       <c r="F11" s="6" t="n"/>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>Ngày cuối kỳ; NULL với hóa đơn một phiên.</t>
+          <t>Số tiền có dấu: dương là cộng tiền, âm là trừ tiền.</t>
         </is>
       </c>
       <c r="H11" s="6" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>-866250.00</t>
         </is>
       </c>
       <c r="I11" s="6" t="n"/>
@@ -44642,7 +44962,7 @@
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>total_amount</t>
+          <t>balance_after</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
@@ -44659,45 +44979,53 @@
       <c r="F12" s="6" t="n"/>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>Tổng tiền hóa đơn, gồm thuế.</t>
+          <t>Số dư ví ngay sau giao dịch.</t>
         </is>
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>256800000.00</t>
+          <t>11633750.00</t>
         </is>
       </c>
       <c r="I12" s="6" t="n"/>
     </row>
-    <row r="13">
+    <row r="13" ht="27" customHeight="1">
       <c r="A13" s="6" t="n">
         <v>7</v>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>session_id</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>char(3)</t>
+          <t>uuid</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E13" s="6" t="n"/>
-      <c r="F13" s="6" t="n"/>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>charging_sessions.session_id (khi xóa: chặn xóa)</t>
+        </is>
+      </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>Mã tiền tệ ISO 4217.</t>
+          <t>Phiên sạc được trả tiền, với giao dịch CHARGE.</t>
         </is>
       </c>
       <c r="H13" s="6" t="inlineStr">
         <is>
-          <t>VND</t>
+          <t>e5a2d8f1-4b7c-4e9a-b3d6-2c1f0e9a8dbb</t>
         </is>
       </c>
       <c r="I13" s="6" t="n"/>
@@ -44708,12 +45036,12 @@
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>einvoice_number</t>
+          <t>payment_id</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>varchar(50)</t>
+          <t>uuid</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
@@ -44721,32 +45049,40 @@
           <t>có</t>
         </is>
       </c>
-      <c r="E14" s="6" t="n"/>
-      <c r="F14" s="6" t="n"/>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="F14" s="7" t="inlineStr">
+        <is>
+          <t>payments.payment_id (khi xóa: chặn xóa)</t>
+        </is>
+      </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>Số hóa đơn do nhà cung cấp hóa đơn điện tử cấp; NULL trước khi phát hành.</t>
+          <t>Thanh toán qua cổng đứng sau một lần nạp tiền, nếu có.</t>
         </is>
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
-          <t>C26TMP0001234</t>
+          <t>NULL</t>
         </is>
       </c>
       <c r="I14" s="6" t="n"/>
     </row>
-    <row r="15" ht="27" customHeight="1">
+    <row r="15">
       <c r="A15" s="6" t="n">
         <v>9</v>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>occurred_at</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>varchar(20)</t>
+          <t>timestamptz</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
@@ -44758,82 +45094,24 @@
       <c r="F15" s="6" t="n"/>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>Trạng thái hóa đơn; hóa đơn đã ISSUED không bao giờ bị sửa. Giá trị: DRAFT | ISSUED | ADJUSTED | CANCELLED.</t>
+          <t>Thời điểm phát sinh giao dịch.</t>
         </is>
       </c>
       <c r="H15" s="6" t="inlineStr">
         <is>
-          <t>ISSUED</t>
+          <t>2026-09-15T09:46:12Z</t>
         </is>
       </c>
       <c r="I15" s="6" t="n"/>
     </row>
-    <row r="16" ht="27" customHeight="1">
-      <c r="A16" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="B16" s="6" t="inlineStr">
-        <is>
-          <t>issued_at</t>
-        </is>
-      </c>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>timestamptz</t>
-        </is>
-      </c>
-      <c r="D16" s="6" t="inlineStr">
-        <is>
-          <t>có</t>
-        </is>
-      </c>
-      <c r="E16" s="6" t="n"/>
-      <c r="F16" s="6" t="n"/>
-      <c r="G16" s="6" t="inlineStr">
-        <is>
-          <t>Thời điểm phát hành hóa đơn điện tử; NULL trước khi phát hành.</t>
-        </is>
-      </c>
-      <c r="H16" s="6" t="inlineStr">
-        <is>
-          <t>2026-10-01T03:00:00Z</t>
-        </is>
-      </c>
-      <c r="I16" s="6" t="n"/>
-    </row>
-    <row r="17"/>
-    <row r="18">
-      <c r="A18" s="4" t="n"/>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>Được tham chiếu bởi bảng</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>Cột</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="6" t="n"/>
-      <c r="B19" s="7" t="inlineStr">
-        <is>
-          <t>invoice_lines</t>
-        </is>
-      </c>
-      <c r="C19" s="6" t="inlineStr">
-        <is>
-          <t>invoice_id</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A6:I16"/>
+  <autoFilter ref="A6:I15"/>
   <hyperlinks>
     <hyperlink ref="A2" location="'Tổng quan'!A1"/>
     <hyperlink ref="F8" location="'organizations'!A1"/>
-    <hyperlink ref="B19" location="'invoice_lines'!A1"/>
+    <hyperlink ref="F9" location="'wallets'!A1"/>
+    <hyperlink ref="F13" location="'charging_sessions'!A1"/>
+    <hyperlink ref="F14" location="'payments'!A1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -45518,6 +45796,482 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:I19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="7" max="7"/>
+    <col width="42" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>54. invoices: Hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t>← Tổng quan</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>Miền nghiệp vụ: Thanh toán &amp; hóa đơn (billing)   ·   Chủ sở hữu dữ liệu: Khách hàng   ·   Tính năng: F-H3, F-H4</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>Một hóa đơn điện tử hợp lệ. Khi đã PHÁT HÀNH thì không sửa, chỉ điều chỉnh hoặc hủy bằng hóa đơn mới.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5"/>
+    <row r="6" ht="27" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Cột</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Kiểu dữ liệu</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Cho phép rỗng</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>Khóa</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>Tham chiếu tới</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>Ý nghĩa</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>Ví dụ</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>Lưu lịch sử</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>invoice_id</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>uuid</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="n"/>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>Mã nội bộ của hóa đơn.</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>7e5c2a9f-4b1d-4e3a-9c8f-0d6b1e4a7c43</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="n"/>
+    </row>
+    <row r="8" ht="27" customHeight="1">
+      <c r="A8" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>organization_id</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>uuid</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>organizations.organization_id (khi xóa: chặn xóa)</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>Tổ chức khách hàng được xuất hóa đơn.</t>
+        </is>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>3f6c2a1e-8b4d-4e2a-9c1f-0a7d5b2e4c11</t>
+        </is>
+      </c>
+      <c r="I8" s="6" t="n"/>
+    </row>
+    <row r="9" ht="27" customHeight="1">
+      <c r="A9" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>invoice_type</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>varchar(20)</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="n"/>
+      <c r="F9" s="6" t="n"/>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn lẻ theo phiên hay hóa đơn tổng hợp tháng cho đội xe. Giá trị: RETAIL | FLEET_MONTHLY.</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>FLEET_MONTHLY</t>
+        </is>
+      </c>
+      <c r="I9" s="6" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>period_start</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="n"/>
+      <c r="F10" s="6" t="n"/>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>Ngày đầu kỳ; NULL với hóa đơn một phiên.</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="I10" s="6" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>period_end</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="n"/>
+      <c r="F11" s="6" t="n"/>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>Ngày cuối kỳ; NULL với hóa đơn một phiên.</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="I11" s="6" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>total_amount</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>numeric(14,2)</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="n"/>
+      <c r="F12" s="6" t="n"/>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>Tổng tiền hóa đơn, gồm thuế.</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>256800000.00</t>
+        </is>
+      </c>
+      <c r="I12" s="6" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>currency</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>char(3)</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="n"/>
+      <c r="F13" s="6" t="n"/>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>Mã tiền tệ ISO 4217.</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="I13" s="6" t="n"/>
+    </row>
+    <row r="14" ht="27" customHeight="1">
+      <c r="A14" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>einvoice_number</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>varchar(50)</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="n"/>
+      <c r="F14" s="6" t="n"/>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>Số hóa đơn do nhà cung cấp hóa đơn điện tử cấp; NULL trước khi phát hành.</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>C26TMP0001234</t>
+        </is>
+      </c>
+      <c r="I14" s="6" t="n"/>
+    </row>
+    <row r="15" ht="27" customHeight="1">
+      <c r="A15" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>varchar(20)</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="n"/>
+      <c r="F15" s="6" t="n"/>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>Trạng thái hóa đơn; hóa đơn đã ISSUED không bao giờ bị sửa. Giá trị: DRAFT | ISSUED | ADJUSTED | CANCELLED.</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>ISSUED</t>
+        </is>
+      </c>
+      <c r="I15" s="6" t="n"/>
+    </row>
+    <row r="16" ht="27" customHeight="1">
+      <c r="A16" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>issued_at</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>timestamptz</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="n"/>
+      <c r="F16" s="6" t="n"/>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>Thời điểm phát hành hóa đơn điện tử; NULL trước khi phát hành.</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-01T03:00:00Z</t>
+        </is>
+      </c>
+      <c r="I16" s="6" t="n"/>
+    </row>
+    <row r="17"/>
+    <row r="18">
+      <c r="A18" s="4" t="n"/>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>Được tham chiếu bởi bảng</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>Cột</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="n"/>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>invoice_lines</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>invoice_id</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A6:I16"/>
+  <hyperlinks>
+    <hyperlink ref="A2" location="'Tổng quan'!A1"/>
+    <hyperlink ref="F8" location="'organizations'!A1"/>
+    <hyperlink ref="B19" location="'invoice_lines'!A1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet71.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -45535,7 +46289,7 @@
     <row r="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>54. invoice_lines: Dòng hóa đơn</t>
+          <t>55. invoice_lines: Dòng hóa đơn</t>
         </is>
       </c>
     </row>
@@ -45954,7 +46708,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet71.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet72.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -45977,7 +46731,7 @@
     <row r="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>55. subscription_plans: Gói dịch vụ</t>
+          <t>56. subscription_plans: Gói dịch vụ</t>
         </is>
       </c>
     </row>
@@ -46340,7 +47094,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet72.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet73.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -46363,7 +47117,7 @@
     <row r="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>56. plan_features: Tính năng của gói dịch vụ</t>
+          <t>57. plan_features: Tính năng của gói dịch vụ</t>
         </is>
       </c>
     </row>
@@ -46630,401 +47384,6 @@
   <hyperlinks>
     <hyperlink ref="A2" location="'Tổng quan'!A1"/>
     <hyperlink ref="F8" location="'subscription_plans'!A1"/>
-  </hyperlinks>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet73.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I16"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="40" customWidth="1" min="6" max="6"/>
-    <col width="60" customWidth="1" min="7" max="7"/>
-    <col width="42" customWidth="1" min="8" max="8"/>
-    <col width="11" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="9" t="inlineStr">
-        <is>
-          <t>57. subscriptions: Thuê bao</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="10" t="inlineStr">
-        <is>
-          <t>← Tổng quan</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>Miền nghiệp vụ: Thanh toán &amp; hóa đơn (billing)   ·   Chủ sở hữu dữ liệu: Khách hàng   ·   Tính năng: F-H4</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="11" t="inlineStr">
-        <is>
-          <t>Một xe đăng ký một gói; quá hạn thanh toán sẽ khóa tính năng.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5"/>
-    <row r="6" ht="27" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>Cột</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>Kiểu dữ liệu</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>Cho phép rỗng</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>Khóa</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>Tham chiếu tới</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>Ý nghĩa</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>Ví dụ</t>
-        </is>
-      </c>
-      <c r="I6" s="4" t="inlineStr">
-        <is>
-          <t>Lưu lịch sử</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>subscription_id</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>uuid</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
-      <c r="F7" s="6" t="n"/>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>Mã nội bộ của thuê bao.</t>
-        </is>
-      </c>
-      <c r="H7" s="6" t="inlineStr">
-        <is>
-          <t>9a7e4c1b-6d3f-4a5c-b0e8-2f1d7c9b3e54</t>
-        </is>
-      </c>
-      <c r="I7" s="6" t="n"/>
-    </row>
-    <row r="8" ht="27" customHeight="1">
-      <c r="A8" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>organization_id</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>uuid</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E8" s="6" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="F8" s="7" t="inlineStr">
-        <is>
-          <t>organizations.organization_id (khi xóa: chặn xóa)</t>
-        </is>
-      </c>
-      <c r="G8" s="6" t="inlineStr">
-        <is>
-          <t>Tổ chức khách hàng đăng ký.</t>
-        </is>
-      </c>
-      <c r="H8" s="6" t="inlineStr">
-        <is>
-          <t>3f6c2a1e-8b4d-4e2a-9c1f-0a7d5b2e4c11</t>
-        </is>
-      </c>
-      <c r="I8" s="6" t="n"/>
-    </row>
-    <row r="9" ht="27" customHeight="1">
-      <c r="A9" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>plan_id</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>uuid</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E9" s="6" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="F9" s="7" t="inlineStr">
-        <is>
-          <t>subscription_plans.plan_id (khi xóa: chặn xóa)</t>
-        </is>
-      </c>
-      <c r="G9" s="6" t="inlineStr">
-        <is>
-          <t>Gói được đăng ký.</t>
-        </is>
-      </c>
-      <c r="H9" s="6" t="inlineStr">
-        <is>
-          <t>0c9a6e3d-8f5b-4c7e-a2d1-4b3f9e6c0a65</t>
-        </is>
-      </c>
-      <c r="I9" s="6" t="n"/>
-    </row>
-    <row r="10" ht="27" customHeight="1">
-      <c r="A10" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>vehicle_id</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>uuid</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E10" s="6" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="F10" s="7" t="inlineStr">
-        <is>
-          <t>vehicles.vehicle_id (khi xóa: chặn xóa)</t>
-        </is>
-      </c>
-      <c r="G10" s="6" t="inlineStr">
-        <is>
-          <t>Xe được áp dụng.</t>
-        </is>
-      </c>
-      <c r="H10" s="6" t="inlineStr">
-        <is>
-          <t>7a4c1e9b-3d2f-4b8a-a6c5-1e0d9f8b7a44</t>
-        </is>
-      </c>
-      <c r="I10" s="6" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>started_at</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>timestamptz</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E11" s="6" t="n"/>
-      <c r="F11" s="6" t="n"/>
-      <c r="G11" s="6" t="inlineStr">
-        <is>
-          <t>Thời điểm bắt đầu thuê bao.</t>
-        </is>
-      </c>
-      <c r="H11" s="6" t="inlineStr">
-        <is>
-          <t>2026-09-01T00:00:00Z</t>
-        </is>
-      </c>
-      <c r="I11" s="6" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>ends_at</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>timestamptz</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>có</t>
-        </is>
-      </c>
-      <c r="E12" s="6" t="n"/>
-      <c r="F12" s="6" t="n"/>
-      <c r="G12" s="6" t="inlineStr">
-        <is>
-          <t>Thời điểm kết thúc; NULL nếu tự gia hạn cho tới khi hủy.</t>
-        </is>
-      </c>
-      <c r="H12" s="6" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="I12" s="6" t="n"/>
-    </row>
-    <row r="13" ht="27" customHeight="1">
-      <c r="A13" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>varchar(20)</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E13" s="6" t="n"/>
-      <c r="F13" s="6" t="n"/>
-      <c r="G13" s="6" t="inlineStr">
-        <is>
-          <t>Trạng thái thuê bao; OVERDUE sẽ khóa các tính năng trả phí. Giá trị: ACTIVE | OVERDUE | EXPIRED | CANCELLED.</t>
-        </is>
-      </c>
-      <c r="H13" s="6" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="I13" s="6" t="n"/>
-    </row>
-    <row r="14"/>
-    <row r="15">
-      <c r="A15" s="4" t="n"/>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>Được tham chiếu bởi bảng</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>Cột</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="6" t="n"/>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>invoice_lines</t>
-        </is>
-      </c>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>subscription_id</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A6:I13"/>
-  <hyperlinks>
-    <hyperlink ref="A2" location="'Tổng quan'!A1"/>
-    <hyperlink ref="F8" location="'organizations'!A1"/>
-    <hyperlink ref="F9" location="'subscription_plans'!A1"/>
-    <hyperlink ref="F10" location="'vehicles'!A1"/>
-    <hyperlink ref="B16" location="'invoice_lines'!A1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -47053,7 +47412,402 @@
     <row r="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>58. driver_scores: Điểm tài xế</t>
+          <t>58. subscriptions: Thuê bao</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t>← Tổng quan</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>Miền nghiệp vụ: Thanh toán &amp; hóa đơn (billing)   ·   Chủ sở hữu dữ liệu: Khách hàng   ·   Tính năng: F-H4</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>Một xe đăng ký một gói; quá hạn thanh toán sẽ khóa tính năng.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5"/>
+    <row r="6" ht="27" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Cột</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Kiểu dữ liệu</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Cho phép rỗng</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>Khóa</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>Tham chiếu tới</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>Ý nghĩa</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>Ví dụ</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>Lưu lịch sử</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>subscription_id</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>uuid</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="n"/>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>Mã nội bộ của thuê bao.</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>9a7e4c1b-6d3f-4a5c-b0e8-2f1d7c9b3e54</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="n"/>
+    </row>
+    <row r="8" ht="27" customHeight="1">
+      <c r="A8" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>organization_id</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>uuid</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>organizations.organization_id (khi xóa: chặn xóa)</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>Tổ chức khách hàng đăng ký.</t>
+        </is>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>3f6c2a1e-8b4d-4e2a-9c1f-0a7d5b2e4c11</t>
+        </is>
+      </c>
+      <c r="I8" s="6" t="n"/>
+    </row>
+    <row r="9" ht="27" customHeight="1">
+      <c r="A9" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>plan_id</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>uuid</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>subscription_plans.plan_id (khi xóa: chặn xóa)</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>Gói được đăng ký.</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>0c9a6e3d-8f5b-4c7e-a2d1-4b3f9e6c0a65</t>
+        </is>
+      </c>
+      <c r="I9" s="6" t="n"/>
+    </row>
+    <row r="10" ht="27" customHeight="1">
+      <c r="A10" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>vehicle_id</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>uuid</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>vehicles.vehicle_id (khi xóa: chặn xóa)</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>Xe được áp dụng.</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>7a4c1e9b-3d2f-4b8a-a6c5-1e0d9f8b7a44</t>
+        </is>
+      </c>
+      <c r="I10" s="6" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>started_at</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>timestamptz</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="n"/>
+      <c r="F11" s="6" t="n"/>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>Thời điểm bắt đầu thuê bao.</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="I11" s="6" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>ends_at</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>timestamptz</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="n"/>
+      <c r="F12" s="6" t="n"/>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>Thời điểm kết thúc; NULL nếu tự gia hạn cho tới khi hủy.</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="I12" s="6" t="n"/>
+    </row>
+    <row r="13" ht="27" customHeight="1">
+      <c r="A13" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>varchar(20)</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="n"/>
+      <c r="F13" s="6" t="n"/>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>Trạng thái thuê bao; OVERDUE sẽ khóa các tính năng trả phí. Giá trị: ACTIVE | OVERDUE | EXPIRED | CANCELLED.</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="I13" s="6" t="n"/>
+    </row>
+    <row r="14"/>
+    <row r="15">
+      <c r="A15" s="4" t="n"/>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>Được tham chiếu bởi bảng</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>Cột</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="n"/>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>invoice_lines</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>subscription_id</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A6:I13"/>
+  <hyperlinks>
+    <hyperlink ref="A2" location="'Tổng quan'!A1"/>
+    <hyperlink ref="F8" location="'organizations'!A1"/>
+    <hyperlink ref="F9" location="'subscription_plans'!A1"/>
+    <hyperlink ref="F10" location="'vehicles'!A1"/>
+    <hyperlink ref="B16" location="'invoice_lines'!A1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet75.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="7" max="7"/>
+    <col width="42" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>59. driver_scores: Điểm tài xế</t>
         </is>
       </c>
     </row>
@@ -47433,7 +48187,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet75.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet76.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -47456,7 +48210,7 @@
     <row r="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>59. promotion_campaigns: Chiến dịch khuyến mãi</t>
+          <t>60. promotion_campaigns: Chiến dịch khuyến mãi</t>
         </is>
       </c>
     </row>
@@ -47740,7 +48494,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet76.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet77.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -47763,7 +48517,7 @@
     <row r="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>60. trips: Chuyến đi</t>
+          <t>61. trips: Chuyến đi</t>
         </is>
       </c>
     </row>

--- a/docs/design/domain-model/domain-model.xlsx
+++ b/docs/design/domain-model/domain-model.xlsx
@@ -3515,7 +3515,7 @@
         </is>
       </c>
     </row>
-    <row r="73" ht="27" customHeight="1">
+    <row r="73" ht="40.5" customHeight="1">
       <c r="A73" s="6" t="inlineStr">
         <is>
           <t>42</t>
@@ -3548,7 +3548,7 @@
       </c>
       <c r="G73" s="6" t="inlineStr">
         <is>
-          <t>Một cảnh báo (pin, bất thường, SOH, thiết bị mất kết nối...). Một bảng chung; mỗi loại cảnh báo là một giá trị enum và một cấu trúc payload.</t>
+          <t>Một cảnh báo (pin, bất thường, SOH, thiết bị mất kết nối...). Một bảng chung; mỗi loại cảnh báo là một giá trị enum và một cấu trúc payload. Được rà soát sau cùng, sau mọi miền phát sinh cảnh báo (NT-08, ghi các điểm cần quyết định).</t>
         </is>
       </c>
       <c r="H73" s="6" t="n">
@@ -39096,7 +39096,7 @@
     <row r="4">
       <c r="A4" s="11" t="inlineStr">
         <is>
-          <t>Một cảnh báo (pin, bất thường, SOH, thiết bị mất kết nối...). Một bảng chung; mỗi loại cảnh báo là một giá trị enum và một cấu trúc payload.</t>
+          <t>Một cảnh báo (pin, bất thường, SOH, thiết bị mất kết nối...). Một bảng chung; mỗi loại cảnh báo là một giá trị enum và một cấu trúc payload. Được rà soát sau cùng, sau mọi miền phát sinh cảnh báo (NT-08, ghi các điểm cần quyết định).</t>
         </is>
       </c>
     </row>

--- a/docs/design/domain-model/domain-model.xlsx
+++ b/docs/design/domain-model/domain-model.xlsx
@@ -136,7 +136,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="48" hidden="1">'charging_connector_history'!$A$7:$I$21</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="49" hidden="1">'charging_connector_state'!$A$7:$I$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="50" hidden="1">'charging_ocpp_messages'!$A$6:$I$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="51" hidden="1">'charging_station_config_capture'!$A$6:$I$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="51" hidden="1">'charging_station_config_capture'!$A$6:$I$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="52" hidden="1">'charging_station_config_entries'!$A$6:$I$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="53" hidden="1">'charging_station_commands'!$A$6:$I$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="54" hidden="1">'charging_sessions'!$A$6:$I$26</definedName>
@@ -3198,7 +3198,7 @@
         </is>
       </c>
     </row>
-    <row r="65" ht="67.5" customHeight="1">
+    <row r="65" ht="94.5" customHeight="1">
       <c r="A65" s="6" t="inlineStr">
         <is>
           <t>36</t>
@@ -3231,11 +3231,11 @@
       </c>
       <c r="G65" s="6" t="inlineStr">
         <is>
-          <t>Một lần chụp cấu hình của trụ sạc: một câu trả lời GetConfiguration (1.6J) hoặc một GetBaseReport được trả lời bằng nhiều phần NotifyReport (2.0.1). Các cấu hình nằm ở charging_station_configuration_entries. Chỉ ghi thêm: cấu hình hiện tại là lần chụp COMPLETE mới nhất, so hai lần chụp cho biết những gì đã đổi (CS-19). Đổi một cấu hình là lệnh gửi xuống trụ, không phải một lần chụp.</t>
+          <t>Một lần chụp cấu hình của trụ sạc: một câu trả lời GetConfiguration (1.6J) hoặc một GetBaseReport được trả lời bằng nhiều phần NotifyReport (2.0.1). Các cấu hình nằm ở charging_station_configuration_entries. Chỉ ghi thêm: cấu hình hiện tại là lần chụp COMPLETE mới nhất, so hai lần chụp cho biết những gì đã đổi (CS-19). Đổi một cấu hình là lệnh gửi xuống trụ, không phải một lần chụp. Mỗi lần chụp đến từ một lệnh GET_CONFIGURATION, nên trụ sạc, thời điểm yêu cầu và người yêu cầu được đọc từ lệnh (CS-21).</t>
         </is>
       </c>
       <c r="H65" s="6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I65" s="7" t="inlineStr">
         <is>
@@ -28582,7 +28582,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I57"/>
+  <dimension ref="A1:I56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -29873,7 +29873,7 @@
       <c r="A53" s="6" t="n"/>
       <c r="B53" s="7" t="inlineStr">
         <is>
-          <t>charging_station_configuration_captures</t>
+          <t>charging_station_commands</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
@@ -29882,11 +29882,11 @@
         </is>
       </c>
     </row>
-    <row r="54" ht="27" customHeight="1">
+    <row r="54">
       <c r="A54" s="6" t="n"/>
       <c r="B54" s="7" t="inlineStr">
         <is>
-          <t>charging_station_commands</t>
+          <t>charging_sessions</t>
         </is>
       </c>
       <c r="C54" s="6" t="inlineStr">
@@ -29899,7 +29899,7 @@
       <c r="A55" s="6" t="n"/>
       <c r="B55" s="7" t="inlineStr">
         <is>
-          <t>charging_sessions</t>
+          <t>tariffs</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
@@ -29912,23 +29912,10 @@
       <c r="A56" s="6" t="n"/>
       <c r="B56" s="7" t="inlineStr">
         <is>
-          <t>tariffs</t>
+          <t>charging_station_history</t>
         </is>
       </c>
       <c r="C56" s="6" t="inlineStr">
-        <is>
-          <t>station_id</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="6" t="n"/>
-      <c r="B57" s="7" t="inlineStr">
-        <is>
-          <t>charging_station_history</t>
-        </is>
-      </c>
-      <c r="C57" s="6" t="inlineStr">
         <is>
           <t>station_id</t>
         </is>
@@ -29946,11 +29933,10 @@
     <hyperlink ref="B50" location="'charging_evses'!A1"/>
     <hyperlink ref="B51" location="'charging_ocpp_messages'!A1"/>
     <hyperlink ref="B52" location="'charging_station_config_entries'!A1"/>
-    <hyperlink ref="B53" location="'charging_station_config_capture'!A1"/>
-    <hyperlink ref="B54" location="'charging_station_commands'!A1"/>
-    <hyperlink ref="B55" location="'charging_sessions'!A1"/>
-    <hyperlink ref="B56" location="'tariffs'!A1"/>
-    <hyperlink ref="B57" location="'charging_station_history'!A1"/>
+    <hyperlink ref="B53" location="'charging_station_commands'!A1"/>
+    <hyperlink ref="B54" location="'charging_sessions'!A1"/>
+    <hyperlink ref="B55" location="'tariffs'!A1"/>
+    <hyperlink ref="B56" location="'charging_station_history'!A1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -35301,7 +35287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -35339,7 +35325,7 @@
     <row r="4">
       <c r="A4" s="11" t="inlineStr">
         <is>
-          <t>Một lần chụp cấu hình của trụ sạc: một câu trả lời GetConfiguration (1.6J) hoặc một GetBaseReport được trả lời bằng nhiều phần NotifyReport (2.0.1). Các cấu hình nằm ở charging_station_configuration_entries. Chỉ ghi thêm: cấu hình hiện tại là lần chụp COMPLETE mới nhất, so hai lần chụp cho biết những gì đã đổi (CS-19). Đổi một cấu hình là lệnh gửi xuống trụ, không phải một lần chụp.</t>
+          <t>Một lần chụp cấu hình của trụ sạc: một câu trả lời GetConfiguration (1.6J) hoặc một GetBaseReport được trả lời bằng nhiều phần NotifyReport (2.0.1). Các cấu hình nằm ở charging_station_configuration_entries. Chỉ ghi thêm: cấu hình hiện tại là lần chụp COMPLETE mới nhất, so hai lần chụp cho biết những gì đã đổi (CS-19). Đổi một cấu hình là lệnh gửi xuống trụ, không phải một lần chụp. Mỗi lần chụp đến từ một lệnh GET_CONFIGURATION, nên trụ sạc, thời điểm yêu cầu và người yêu cầu được đọc từ lệnh (CS-21).</t>
         </is>
       </c>
     </row>
@@ -35428,13 +35414,13 @@
       </c>
       <c r="I7" s="6" t="n"/>
     </row>
-    <row r="8" ht="27" customHeight="1">
+    <row r="8" ht="54" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>2</v>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>station_id</t>
+          <t>command_id</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
@@ -35449,22 +35435,22 @@
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>FK</t>
+          <t>FK UQ</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>charging_stations.station_id (khi xóa: chặn xóa)</t>
+          <t>charging_station_commands.command_id (khi xóa: chặn xóa)</t>
         </is>
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>Trụ sạc.</t>
+          <t>Lệnh GET_CONFIGURATION đã yêu cầu lần chụp này (CS-21), kể cả lệnh tự động sau khi khởi động; mỗi lệnh cho một lần chụp. Trụ sạc, thời điểm yêu cầu và người yêu cầu được đọc từ lệnh.</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
-          <t>4b9d6f3a-2e8c-4a1b-9d5e-7f0c3a8b2d88</t>
+          <t>0000000c-5a6b-4c7d-8e9f-0a1b2c3d4e5f</t>
         </is>
       </c>
       <c r="I8" s="6" t="n"/>
@@ -35568,13 +35554,13 @@
       </c>
       <c r="I11" s="6" t="n"/>
     </row>
-    <row r="12">
+    <row r="12" ht="27" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>6</v>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>requested_at</t>
+          <t>captured_at</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
@@ -35584,143 +35570,110 @@
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>không</t>
+          <t>có</t>
         </is>
       </c>
       <c r="E12" s="6" t="n"/>
       <c r="F12" s="6" t="n"/>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>Thời điểm cổng OCPP hỏi trụ.</t>
+          <t>Thời điểm nhận câu trả lời (2.0.1: phần cuối cùng); NULL khi đang chờ hoặc thất bại.</t>
         </is>
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14T22:00:06Z</t>
+          <t>2026-09-14T22:00:10Z</t>
         </is>
       </c>
       <c r="I12" s="6" t="n"/>
     </row>
-    <row r="13" ht="27" customHeight="1">
+    <row r="13" ht="40.5" customHeight="1">
       <c r="A13" s="6" t="n">
         <v>7</v>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>captured_at</t>
+          <t>outcome</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>timestamptz</t>
+          <t>varchar(20)</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>có</t>
+          <t>không</t>
         </is>
       </c>
       <c r="E13" s="6" t="n"/>
       <c r="F13" s="6" t="n"/>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>Thời điểm nhận câu trả lời (2.0.1: phần cuối cùng); NULL khi đang chờ hoặc thất bại.</t>
+          <t>Kết quả quan sát được. PENDING: đã hỏi, chưa đủ. COMPLETE: đã nhận đủ. FAILED: không trả lời kịp, trả lời lỗi, hoặc thiếu phần.</t>
         </is>
       </c>
       <c r="H13" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14T22:00:10Z</t>
+          <t>COMPLETE</t>
         </is>
       </c>
       <c r="I13" s="6" t="n"/>
     </row>
-    <row r="14" ht="40.5" customHeight="1">
-      <c r="A14" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="B14" s="6" t="inlineStr">
-        <is>
-          <t>outcome</t>
-        </is>
-      </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>varchar(20)</t>
-        </is>
-      </c>
-      <c r="D14" s="6" t="inlineStr">
+    <row r="14"/>
+    <row r="15">
+      <c r="A15" s="4" t="n"/>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>Chỉ mục (index)</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>Các cột</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>Duy nhất</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="n"/>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>Ghi chú</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="40.5" customHeight="1">
+      <c r="A16" s="6" t="n"/>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>ix_charging_config_captures_ocpp_request_id</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>ocpp_request_id</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
         <is>
           <t>không</t>
         </is>
       </c>
-      <c r="E14" s="6" t="n"/>
-      <c r="F14" s="6" t="n"/>
-      <c r="G14" s="6" t="inlineStr">
-        <is>
-          <t>Kết quả quan sát được. PENDING: đã hỏi, chưa đủ. COMPLETE: đã nhận đủ. FAILED: không trả lời kịp, trả lời lỗi, hoặc thiếu phần.</t>
-        </is>
-      </c>
-      <c r="H14" s="6" t="inlineStr">
-        <is>
-          <t>COMPLETE</t>
-        </is>
-      </c>
-      <c r="I14" s="6" t="n"/>
-    </row>
-    <row r="15"/>
-    <row r="16">
-      <c r="A16" s="4" t="n"/>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>Chỉ mục (index)</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>Các cột</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="inlineStr">
-        <is>
-          <t>Duy nhất</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="n"/>
-      <c r="F16" s="4" t="inlineStr">
-        <is>
-          <t>Ghi chú</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="27" customHeight="1">
-      <c r="A17" s="6" t="n"/>
-      <c r="B17" s="6" t="inlineStr">
-        <is>
-          <t>ix_charging_config_captures_station_captured</t>
-        </is>
-      </c>
-      <c r="C17" s="6" t="inlineStr">
-        <is>
-          <t>station_id, captured_at</t>
-        </is>
-      </c>
-      <c r="D17" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E17" s="6" t="n"/>
-      <c r="F17" s="6" t="inlineStr">
-        <is>
-          <t>The latest complete snapshot of a charger</t>
+      <c r="E16" s="6" t="n"/>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>Finds the snapshot when a 2.0.1 NotifyReport part arrives, together with the command's charger</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A6:I14"/>
+  <autoFilter ref="A6:I13"/>
   <hyperlinks>
     <hyperlink ref="A2" location="'Tổng quan'!A1"/>
-    <hyperlink ref="F8" location="'charging_stations'!A1"/>
+    <hyperlink ref="F8" location="'charging_station_commands'!A1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -35890,7 +35843,7 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>[Sẽ bỏ: CS-19] Trụ sạc; nay nằm ở lần chụp.</t>
+          <t>[Sẽ bỏ: CS-19] Trụ sạc; nay đọc qua lệnh của lần chụp (CS-21).</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr">
@@ -36385,7 +36338,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -37013,6 +36966,33 @@
         </is>
       </c>
     </row>
+    <row r="24"/>
+    <row r="25">
+      <c r="A25" s="4" t="n"/>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>Được tham chiếu bởi bảng</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>Cột</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="27" customHeight="1">
+      <c r="A26" s="6" t="n"/>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>charging_station_configuration_captures</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>command_id</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A6:I19"/>
   <hyperlinks>
@@ -37021,6 +37001,7 @@
     <hyperlink ref="F9" location="'charging_evses'!A1"/>
     <hyperlink ref="F10" location="'charging_sessions'!A1"/>
     <hyperlink ref="F13" location="'users'!A1"/>
+    <hyperlink ref="B26" location="'charging_station_config_capture'!A1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/design/domain-model/domain-model.xlsx
+++ b/docs/design/domain-model/domain-model.xlsx
@@ -123,7 +123,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="34" hidden="1">'driving_sessions'!$A$6:$I$17</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="35" hidden="1">'fleets'!$A$7:$I$16</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="36" hidden="1">'fleet_history'!$A$7:$I$19</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="37" hidden="1">'fleet_vehicle_memberships'!$A$6:$I$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="37" hidden="1">'fleet_vehicle_memberships'!$A$6:$I$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="38" hidden="1">'geofences'!$A$6:$I$14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="39" hidden="1">'fleet_user_assignments'!$A$6:$I$12</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="40" hidden="1">'charging_locations'!$A$7:$I$18</definedName>
@@ -2545,7 +2545,7 @@
         </is>
       </c>
     </row>
-    <row r="50">
+    <row r="50" ht="81" customHeight="1">
       <c r="A50" s="6" t="inlineStr">
         <is>
           <t>25</t>
@@ -2578,11 +2578,11 @@
       </c>
       <c r="G50" s="6" t="inlineStr">
         <is>
-          <t>Xe nào thuộc đội nào, trong khoảng thời gian nào (lịch sử mở/đóng).</t>
+          <t>Xe nào thuộc đội nào, trong khoảng thời gian nào (lịch sử mở/đóng). Mỗi xe chỉ thuộc tối đa một đội tại một thời điểm và giai đoạn không có dữ liệu riêng, nên theo DM-22 lẽ ra đặt fleet_id trên vehicles; bảng được giữ vì miền xe không được phụ thuộc miền đội xe (FL-01, FL-09). Không có lịch sử thay đổi: dòng chỉ bị đóng (DM-20); added_by / removed_by cho biết ai thực hiện. Không có cột lý do: lý do xe rời đội rõ từ sự việc (chuyển đội, bán xe, đội bị xóa).</t>
         </is>
       </c>
       <c r="H50" s="6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I50" s="7" t="inlineStr">
         <is>
@@ -10584,7 +10584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I60"/>
+  <dimension ref="A1:I59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -11415,11 +11415,11 @@
         </is>
       </c>
     </row>
-    <row r="40" ht="27" customHeight="1">
+    <row r="40">
       <c r="A40" s="6" t="n"/>
       <c r="B40" s="7" t="inlineStr">
         <is>
-          <t>fleet_vehicle_memberships</t>
+          <t>fleet_user_assignments</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
@@ -11432,7 +11432,7 @@
       <c r="A41" s="6" t="n"/>
       <c r="B41" s="7" t="inlineStr">
         <is>
-          <t>fleet_user_assignments</t>
+          <t>geofences</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
@@ -11445,7 +11445,7 @@
       <c r="A42" s="6" t="n"/>
       <c r="B42" s="7" t="inlineStr">
         <is>
-          <t>geofences</t>
+          <t>charging_locations</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
@@ -11454,29 +11454,29 @@
         </is>
       </c>
     </row>
-    <row r="43">
+    <row r="43" ht="27" customHeight="1">
       <c r="A43" s="6" t="n"/>
       <c r="B43" s="7" t="inlineStr">
         <is>
-          <t>charging_locations</t>
+          <t>charging_location_access</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>organization_id</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="27" customHeight="1">
+          <t>allowed_organization_id</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
       <c r="A44" s="6" t="n"/>
       <c r="B44" s="7" t="inlineStr">
         <is>
-          <t>charging_location_access</t>
+          <t>charging_sessions</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>allowed_organization_id</t>
+          <t>organization_id</t>
         </is>
       </c>
     </row>
@@ -11484,7 +11484,7 @@
       <c r="A45" s="6" t="n"/>
       <c r="B45" s="7" t="inlineStr">
         <is>
-          <t>charging_sessions</t>
+          <t>notifications</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
@@ -11497,7 +11497,7 @@
       <c r="A46" s="6" t="n"/>
       <c r="B46" s="7" t="inlineStr">
         <is>
-          <t>notifications</t>
+          <t>support_cases</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
@@ -11510,7 +11510,7 @@
       <c r="A47" s="6" t="n"/>
       <c r="B47" s="7" t="inlineStr">
         <is>
-          <t>support_cases</t>
+          <t>repair_partners</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
@@ -11523,7 +11523,7 @@
       <c r="A48" s="6" t="n"/>
       <c r="B48" s="7" t="inlineStr">
         <is>
-          <t>repair_partners</t>
+          <t>maintenance_bookings</t>
         </is>
       </c>
       <c r="C48" s="6" t="inlineStr">
@@ -11532,11 +11532,11 @@
         </is>
       </c>
     </row>
-    <row r="49">
+    <row r="49" ht="27" customHeight="1">
       <c r="A49" s="6" t="n"/>
       <c r="B49" s="7" t="inlineStr">
         <is>
-          <t>maintenance_bookings</t>
+          <t>charging_policy_assignments</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
@@ -11545,11 +11545,11 @@
         </is>
       </c>
     </row>
-    <row r="50" ht="27" customHeight="1">
+    <row r="50">
       <c r="A50" s="6" t="n"/>
       <c r="B50" s="7" t="inlineStr">
         <is>
-          <t>charging_policy_assignments</t>
+          <t>policy_violations</t>
         </is>
       </c>
       <c r="C50" s="6" t="inlineStr">
@@ -11562,7 +11562,7 @@
       <c r="A51" s="6" t="n"/>
       <c r="B51" s="7" t="inlineStr">
         <is>
-          <t>policy_violations</t>
+          <t>payments</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
@@ -11575,7 +11575,7 @@
       <c r="A52" s="6" t="n"/>
       <c r="B52" s="7" t="inlineStr">
         <is>
-          <t>payments</t>
+          <t>wallets</t>
         </is>
       </c>
       <c r="C52" s="6" t="inlineStr">
@@ -11588,7 +11588,7 @@
       <c r="A53" s="6" t="n"/>
       <c r="B53" s="7" t="inlineStr">
         <is>
-          <t>wallets</t>
+          <t>wallet_transactions</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
@@ -11601,7 +11601,7 @@
       <c r="A54" s="6" t="n"/>
       <c r="B54" s="7" t="inlineStr">
         <is>
-          <t>wallet_transactions</t>
+          <t>invoices</t>
         </is>
       </c>
       <c r="C54" s="6" t="inlineStr">
@@ -11614,7 +11614,7 @@
       <c r="A55" s="6" t="n"/>
       <c r="B55" s="7" t="inlineStr">
         <is>
-          <t>invoices</t>
+          <t>invoice_lines</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
@@ -11627,7 +11627,7 @@
       <c r="A56" s="6" t="n"/>
       <c r="B56" s="7" t="inlineStr">
         <is>
-          <t>invoice_lines</t>
+          <t>subscriptions</t>
         </is>
       </c>
       <c r="C56" s="6" t="inlineStr">
@@ -11640,7 +11640,7 @@
       <c r="A57" s="6" t="n"/>
       <c r="B57" s="7" t="inlineStr">
         <is>
-          <t>subscriptions</t>
+          <t>driver_scores</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
@@ -11653,7 +11653,7 @@
       <c r="A58" s="6" t="n"/>
       <c r="B58" s="7" t="inlineStr">
         <is>
-          <t>driver_scores</t>
+          <t>trips</t>
         </is>
       </c>
       <c r="C58" s="6" t="inlineStr">
@@ -11666,23 +11666,10 @@
       <c r="A59" s="6" t="n"/>
       <c r="B59" s="7" t="inlineStr">
         <is>
-          <t>trips</t>
+          <t>organization_history</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
-        <is>
-          <t>organization_id</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="6" t="n"/>
-      <c r="B60" s="7" t="inlineStr">
-        <is>
-          <t>organization_history</t>
-        </is>
-      </c>
-      <c r="C60" s="6" t="inlineStr">
         <is>
           <t>organization_id</t>
         </is>
@@ -11708,27 +11695,26 @@
     <hyperlink ref="B37" location="'driver_vehicle_assignments'!A1"/>
     <hyperlink ref="B38" location="'driving_sessions'!A1"/>
     <hyperlink ref="B39" location="'fleets'!A1"/>
-    <hyperlink ref="B40" location="'fleet_vehicle_memberships'!A1"/>
-    <hyperlink ref="B41" location="'fleet_user_assignments'!A1"/>
-    <hyperlink ref="B42" location="'geofences'!A1"/>
-    <hyperlink ref="B43" location="'charging_locations'!A1"/>
-    <hyperlink ref="B44" location="'charging_location_access'!A1"/>
-    <hyperlink ref="B45" location="'charging_sessions'!A1"/>
-    <hyperlink ref="B46" location="'notifications'!A1"/>
-    <hyperlink ref="B47" location="'support_cases'!A1"/>
-    <hyperlink ref="B48" location="'repair_partners'!A1"/>
-    <hyperlink ref="B49" location="'maintenance_bookings'!A1"/>
-    <hyperlink ref="B50" location="'charging_policy_assignments'!A1"/>
-    <hyperlink ref="B51" location="'policy_violations'!A1"/>
-    <hyperlink ref="B52" location="'payments'!A1"/>
-    <hyperlink ref="B53" location="'wallets'!A1"/>
-    <hyperlink ref="B54" location="'wallet_transactions'!A1"/>
-    <hyperlink ref="B55" location="'invoices'!A1"/>
-    <hyperlink ref="B56" location="'invoice_lines'!A1"/>
-    <hyperlink ref="B57" location="'subscriptions'!A1"/>
-    <hyperlink ref="B58" location="'driver_scores'!A1"/>
-    <hyperlink ref="B59" location="'trips'!A1"/>
-    <hyperlink ref="B60" location="'organization_history'!A1"/>
+    <hyperlink ref="B40" location="'fleet_user_assignments'!A1"/>
+    <hyperlink ref="B41" location="'geofences'!A1"/>
+    <hyperlink ref="B42" location="'charging_locations'!A1"/>
+    <hyperlink ref="B43" location="'charging_location_access'!A1"/>
+    <hyperlink ref="B44" location="'charging_sessions'!A1"/>
+    <hyperlink ref="B45" location="'notifications'!A1"/>
+    <hyperlink ref="B46" location="'support_cases'!A1"/>
+    <hyperlink ref="B47" location="'repair_partners'!A1"/>
+    <hyperlink ref="B48" location="'maintenance_bookings'!A1"/>
+    <hyperlink ref="B49" location="'charging_policy_assignments'!A1"/>
+    <hyperlink ref="B50" location="'policy_violations'!A1"/>
+    <hyperlink ref="B51" location="'payments'!A1"/>
+    <hyperlink ref="B52" location="'wallets'!A1"/>
+    <hyperlink ref="B53" location="'wallet_transactions'!A1"/>
+    <hyperlink ref="B54" location="'invoices'!A1"/>
+    <hyperlink ref="B55" location="'invoice_lines'!A1"/>
+    <hyperlink ref="B56" location="'subscriptions'!A1"/>
+    <hyperlink ref="B57" location="'driver_scores'!A1"/>
+    <hyperlink ref="B58" location="'trips'!A1"/>
+    <hyperlink ref="B59" location="'organization_history'!A1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -25089,7 +25075,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -25127,7 +25113,7 @@
     <row r="4">
       <c r="A4" s="11" t="inlineStr">
         <is>
-          <t>Xe nào thuộc đội nào, trong khoảng thời gian nào (lịch sử mở/đóng).</t>
+          <t>Xe nào thuộc đội nào, trong khoảng thời gian nào (lịch sử mở/đóng). Mỗi xe chỉ thuộc tối đa một đội tại một thời điểm và giai đoạn không có dữ liệu riêng, nên theo DM-22 lẽ ra đặt fleet_id trên vehicles; bảng được giữ vì miền xe không được phụ thuộc miền đội xe (FL-01, FL-09). Không có lịch sử thay đổi: dòng chỉ bị đóng (DM-20); added_by / removed_by cho biết ai thực hiện. Không có cột lý do: lý do xe rời đội rõ từ sự việc (chuyển đội, bán xe, đội bị xóa).</t>
         </is>
       </c>
     </row>
@@ -25179,13 +25165,13 @@
         </is>
       </c>
     </row>
-    <row r="7">
+    <row r="7" ht="54" customHeight="1">
       <c r="A7" s="6" t="n">
         <v>1</v>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>membership_id</t>
+          <t>fleet_vehicle_membership_id</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
@@ -25206,7 +25192,7 @@
       <c r="F7" s="6" t="n"/>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>Mã nội bộ của giai đoạn thành viên.</t>
+          <t>[Hiện tên là membership_id, sẽ đổi tên] Mã nội bộ của một giai đoạn thành viên. Đổi tên vì memberships.membership_id (miền danh tính) là một người trong một tổ chức, một khái niệm khác (FL-09).</t>
         </is>
       </c>
       <c r="H7" s="6" t="inlineStr">
@@ -25222,7 +25208,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>organization_id</t>
+          <t>fleet_id</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
@@ -25232,7 +25218,7 @@
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>có</t>
+          <t>không</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
@@ -25242,28 +25228,28 @@
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>organizations.organization_id (khi xóa: chặn xóa)</t>
+          <t>fleets.fleet_id (khi xóa: chặn xóa)</t>
         </is>
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>Tổ chức khách hàng của giai đoạn thành viên.</t>
+          <t>Đội xe chứa xe; dòng đọc tổ chức qua đội xe (DM-24), vì đội xe không bao giờ chuyển sang tổ chức khác.</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
-          <t>3f6c2a1e-8b4d-4e2a-9c1f-0a7d5b2e4c11</t>
+          <t>8d5f2b7e-1a9c-4f3d-b8e2-6c0a4d9f1e77</t>
         </is>
       </c>
       <c r="I8" s="6" t="n"/>
     </row>
-    <row r="9">
+    <row r="9" ht="27" customHeight="1">
       <c r="A9" s="6" t="n">
         <v>3</v>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>fleet_id</t>
+          <t>vehicle_id</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
@@ -25283,17 +25269,17 @@
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>fleets.fleet_id (khi xóa: chặn xóa)</t>
+          <t>vehicles.vehicle_id (khi xóa: chặn xóa)</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>Đội xe chứa xe.</t>
+          <t>Xe thuộc đội; xe phải thuộc tổ chức của đội khi được thêm vào.</t>
         </is>
       </c>
       <c r="H9" s="6" t="inlineStr">
         <is>
-          <t>8d5f2b7e-1a9c-4f3d-b8e2-6c0a4d9f1e77</t>
+          <t>7a4c1e9b-3d2f-4b8a-a6c5-1e0d9f8b7a44</t>
         </is>
       </c>
       <c r="I9" s="6" t="n"/>
@@ -25304,12 +25290,12 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>vehicle_id</t>
+          <t>added_at</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>uuid</t>
+          <t>timestamptz</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
@@ -25317,35 +25303,27 @@
           <t>không</t>
         </is>
       </c>
-      <c r="E10" s="6" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="F10" s="7" t="inlineStr">
-        <is>
-          <t>vehicles.vehicle_id (khi xóa: chặn xóa)</t>
-        </is>
-      </c>
+      <c r="E10" s="6" t="n"/>
+      <c r="F10" s="6" t="n"/>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>Xe thuộc đội.</t>
+          <t>[Hiện tên là joined_at, sẽ đổi tên] Thời điểm xe được thêm vào đội (FL-09).</t>
         </is>
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>7a4c1e9b-3d2f-4b8a-a6c5-1e0d9f8b7a44</t>
+          <t>2026-09-01T00:00:00Z</t>
         </is>
       </c>
       <c r="I10" s="6" t="n"/>
     </row>
-    <row r="11">
+    <row r="11" ht="27" customHeight="1">
       <c r="A11" s="6" t="n">
         <v>5</v>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>joined_at</t>
+          <t>removed_at</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
@@ -25355,19 +25333,19 @@
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>không</t>
+          <t>có</t>
         </is>
       </c>
       <c r="E11" s="6" t="n"/>
       <c r="F11" s="6" t="n"/>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>Thời điểm xe vào đội.</t>
+          <t>[Hiện tên là left_at, sẽ đổi tên] Thời điểm xe bị đưa ra khỏi đội; NULL khi vẫn còn trong đội (FL-09).</t>
         </is>
       </c>
       <c r="H11" s="6" t="inlineStr">
         <is>
-          <t>2026-09-01T00:00:00Z</t>
+          <t>NULL</t>
         </is>
       </c>
       <c r="I11" s="6" t="n"/>
@@ -25378,12 +25356,12 @@
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>left_at</t>
+          <t>added_by</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>timestamptz</t>
+          <t>uuid</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
@@ -25391,60 +25369,76 @@
           <t>có</t>
         </is>
       </c>
-      <c r="E12" s="6" t="n"/>
-      <c r="F12" s="6" t="n"/>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>users.user_id (khi xóa: chặn xóa)</t>
+        </is>
+      </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>Thời điểm xe rời đội; NULL khi vẫn còn trong đội.</t>
+          <t>Người dùng đã thêm xe vào đội.</t>
         </is>
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>NULL</t>
+          <t>9b2e7d4a-1c3f-4a8e-b6d2-5e0f1a9c3d22</t>
         </is>
       </c>
       <c r="I12" s="6" t="n"/>
     </row>
-    <row r="13">
+    <row r="13" ht="40.5" customHeight="1">
       <c r="A13" s="6" t="n">
         <v>7</v>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>removed_by</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>timestamptz</t>
+          <t>uuid</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E13" s="6" t="n"/>
-      <c r="F13" s="6" t="n"/>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>users.user_id (khi xóa: chặn xóa)</t>
+        </is>
+      </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>Thời điểm tạo bản ghi (UTC).</t>
+          <t>Người dùng đã đưa xe ra khỏi đội; NULL khi vẫn là thành viên, hoặc khi hệ thống tự đóng (xe được bán, VH-12, hoặc đội bị xóa, FL-06).</t>
         </is>
       </c>
       <c r="H13" s="6" t="inlineStr">
         <is>
-          <t>2026-09-01T02:00:00Z</t>
+          <t>NULL</t>
         </is>
       </c>
       <c r="I13" s="6" t="n"/>
     </row>
-    <row r="14" ht="27" customHeight="1">
+    <row r="14">
       <c r="A14" s="6" t="n">
         <v>8</v>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>updated_at</t>
+          <t>created_at</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
@@ -25461,71 +25455,84 @@
       <c r="F14" s="6" t="n"/>
       <c r="G14" s="6" t="inlineStr">
         <is>
+          <t>Thời điểm tạo bản ghi (UTC).</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-01T02:00:00Z</t>
+        </is>
+      </c>
+      <c r="I14" s="6" t="n"/>
+    </row>
+    <row r="15" ht="27" customHeight="1">
+      <c r="A15" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>updated_at</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>timestamptz</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="n"/>
+      <c r="F15" s="6" t="n"/>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
           <t>Thời điểm bản ghi được sửa gần nhất (thay đổi khi xe rời đội).</t>
         </is>
       </c>
-      <c r="H14" s="6" t="inlineStr">
+      <c r="H15" s="6" t="inlineStr">
         <is>
           <t>2026-09-10T07:15:00Z</t>
         </is>
       </c>
-      <c r="I14" s="6" t="n"/>
-    </row>
-    <row r="15"/>
-    <row r="16">
-      <c r="A16" s="4" t="n"/>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="I15" s="6" t="n"/>
+    </row>
+    <row r="16"/>
+    <row r="17">
+      <c r="A17" s="4" t="n"/>
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>Chỉ mục (index)</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C17" s="4" t="inlineStr">
         <is>
           <t>Các cột</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="D17" s="4" t="inlineStr">
         <is>
           <t>Duy nhất</t>
         </is>
       </c>
-      <c r="E16" s="4" t="n"/>
-      <c r="F16" s="4" t="inlineStr">
+      <c r="E17" s="4" t="n"/>
+      <c r="F17" s="4" t="inlineStr">
         <is>
           <t>Ghi chú</t>
         </is>
       </c>
-    </row>
-    <row r="17" ht="27" customHeight="1">
-      <c r="A17" s="6" t="n"/>
-      <c r="B17" s="6" t="inlineStr">
-        <is>
-          <t>ix_fleet_vehicle_memberships_fleet_id</t>
-        </is>
-      </c>
-      <c r="C17" s="6" t="inlineStr">
-        <is>
-          <t>fleet_id</t>
-        </is>
-      </c>
-      <c r="D17" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E17" s="6" t="n"/>
-      <c r="F17" s="6" t="n"/>
     </row>
     <row r="18" ht="27" customHeight="1">
       <c r="A18" s="6" t="n"/>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>ix_fleet_vehicle_memberships_fleet_time</t>
+          <t>ix_fleet_vehicle_memberships_fleet_id</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>fleet_id, joined_at</t>
+          <t>fleet_id</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
@@ -25534,18 +25541,22 @@
         </is>
       </c>
       <c r="E18" s="6" t="n"/>
-      <c r="F18" s="6" t="n"/>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>Dropped: covered by ix_fleet_vehicle_memberships_fleet_time (FL-09)</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="27" customHeight="1">
       <c r="A19" s="6" t="n"/>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>ix_fleet_vehicle_memberships_vehicle_id</t>
+          <t>ix_fleet_vehicle_memberships_fleet_time</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>vehicle_id</t>
+          <t>fleet_id, added_at</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
@@ -25560,33 +25571,54 @@
       <c r="A20" s="6" t="n"/>
       <c r="B20" s="6" t="inlineStr">
         <is>
+          <t>ix_fleet_vehicle_memberships_vehicle_id</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>vehicle_id</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="n"/>
+      <c r="F20" s="6" t="n"/>
+    </row>
+    <row r="21" ht="27" customHeight="1">
+      <c r="A21" s="6" t="n"/>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
           <t>uq_fleet_vehicle_memberships_active_vehicle</t>
         </is>
       </c>
-      <c r="C20" s="6" t="inlineStr">
+      <c r="C21" s="6" t="inlineStr">
         <is>
           <t>vehicle_id</t>
         </is>
       </c>
-      <c r="D20" s="6" t="inlineStr">
+      <c r="D21" s="6" t="inlineStr">
         <is>
           <t>có</t>
         </is>
       </c>
-      <c r="E20" s="6" t="n"/>
-      <c r="F20" s="6" t="inlineStr">
-        <is>
-          <t>WHERE left_at IS NULL</t>
+      <c r="E21" s="6" t="n"/>
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t>WHERE removed_at IS NULL (built as left_at)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A6:I14"/>
+  <autoFilter ref="A6:I15"/>
   <hyperlinks>
     <hyperlink ref="A2" location="'Tổng quan'!A1"/>
-    <hyperlink ref="F8" location="'organizations'!A1"/>
-    <hyperlink ref="F9" location="'fleets'!A1"/>
-    <hyperlink ref="F10" location="'vehicles'!A1"/>
+    <hyperlink ref="F8" location="'fleets'!A1"/>
+    <hyperlink ref="F9" location="'vehicles'!A1"/>
+    <hyperlink ref="F12" location="'users'!A1"/>
+    <hyperlink ref="F13" location="'users'!A1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -26034,7 +26066,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I60"/>
+  <dimension ref="A1:I62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -26785,42 +26817,42 @@
         </is>
       </c>
     </row>
-    <row r="39">
+    <row r="39" ht="27" customHeight="1">
       <c r="A39" s="6" t="n"/>
       <c r="B39" s="7" t="inlineStr">
         <is>
-          <t>charging_location_access</t>
+          <t>fleet_vehicle_memberships</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>granted_by</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
+          <t>added_by</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="27" customHeight="1">
       <c r="A40" s="6" t="n"/>
       <c r="B40" s="7" t="inlineStr">
         <is>
-          <t>charging_location_access</t>
+          <t>fleet_vehicle_memberships</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>revoked_by</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="27" customHeight="1">
+          <t>removed_by</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
       <c r="A41" s="6" t="n"/>
       <c r="B41" s="7" t="inlineStr">
         <is>
-          <t>charging_station_commands</t>
+          <t>charging_location_access</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>requested_by</t>
+          <t>granted_by</t>
         </is>
       </c>
     </row>
@@ -26828,25 +26860,25 @@
       <c r="A42" s="6" t="n"/>
       <c r="B42" s="7" t="inlineStr">
         <is>
-          <t>charging_sessions</t>
+          <t>charging_location_access</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>started_by</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
+          <t>revoked_by</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="27" customHeight="1">
       <c r="A43" s="6" t="n"/>
       <c r="B43" s="7" t="inlineStr">
         <is>
-          <t>charging_policy_versions</t>
+          <t>charging_station_commands</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>created_by</t>
+          <t>requested_by</t>
         </is>
       </c>
     </row>
@@ -26854,12 +26886,12 @@
       <c r="A44" s="6" t="n"/>
       <c r="B44" s="7" t="inlineStr">
         <is>
-          <t>organization_history</t>
+          <t>charging_sessions</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>changed_by</t>
+          <t>started_by</t>
         </is>
       </c>
     </row>
@@ -26867,12 +26899,12 @@
       <c r="A45" s="6" t="n"/>
       <c r="B45" s="7" t="inlineStr">
         <is>
-          <t>user_history</t>
+          <t>charging_policy_versions</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>user_id</t>
+          <t>created_by</t>
         </is>
       </c>
     </row>
@@ -26880,7 +26912,7 @@
       <c r="A46" s="6" t="n"/>
       <c r="B46" s="7" t="inlineStr">
         <is>
-          <t>user_history</t>
+          <t>organization_history</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
@@ -26893,20 +26925,20 @@
       <c r="A47" s="6" t="n"/>
       <c r="B47" s="7" t="inlineStr">
         <is>
-          <t>membership_history</t>
+          <t>user_history</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>changed_by</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="27" customHeight="1">
+          <t>user_id</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
       <c r="A48" s="6" t="n"/>
       <c r="B48" s="7" t="inlineStr">
         <is>
-          <t>organization_setting_history</t>
+          <t>user_history</t>
         </is>
       </c>
       <c r="C48" s="6" t="inlineStr">
@@ -26919,7 +26951,7 @@
       <c r="A49" s="6" t="n"/>
       <c r="B49" s="7" t="inlineStr">
         <is>
-          <t>vehicle_history</t>
+          <t>membership_history</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
@@ -26928,11 +26960,11 @@
         </is>
       </c>
     </row>
-    <row r="50">
+    <row r="50" ht="27" customHeight="1">
       <c r="A50" s="6" t="n"/>
       <c r="B50" s="7" t="inlineStr">
         <is>
-          <t>vehicle_model_history</t>
+          <t>organization_setting_history</t>
         </is>
       </c>
       <c r="C50" s="6" t="inlineStr">
@@ -26945,7 +26977,7 @@
       <c r="A51" s="6" t="n"/>
       <c r="B51" s="7" t="inlineStr">
         <is>
-          <t>battery_model_history</t>
+          <t>vehicle_history</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
@@ -26958,7 +26990,7 @@
       <c r="A52" s="6" t="n"/>
       <c r="B52" s="7" t="inlineStr">
         <is>
-          <t>battery_history</t>
+          <t>vehicle_model_history</t>
         </is>
       </c>
       <c r="C52" s="6" t="inlineStr">
@@ -26971,7 +27003,7 @@
       <c r="A53" s="6" t="n"/>
       <c r="B53" s="7" t="inlineStr">
         <is>
-          <t>warranty_history</t>
+          <t>battery_model_history</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
@@ -26984,7 +27016,7 @@
       <c r="A54" s="6" t="n"/>
       <c r="B54" s="7" t="inlineStr">
         <is>
-          <t>telematic_history</t>
+          <t>battery_history</t>
         </is>
       </c>
       <c r="C54" s="6" t="inlineStr">
@@ -26997,7 +27029,7 @@
       <c r="A55" s="6" t="n"/>
       <c r="B55" s="7" t="inlineStr">
         <is>
-          <t>driver_history</t>
+          <t>warranty_history</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
@@ -27010,7 +27042,7 @@
       <c r="A56" s="6" t="n"/>
       <c r="B56" s="7" t="inlineStr">
         <is>
-          <t>fleet_history</t>
+          <t>telematic_history</t>
         </is>
       </c>
       <c r="C56" s="6" t="inlineStr">
@@ -27019,11 +27051,11 @@
         </is>
       </c>
     </row>
-    <row r="57" ht="27" customHeight="1">
+    <row r="57">
       <c r="A57" s="6" t="n"/>
       <c r="B57" s="7" t="inlineStr">
         <is>
-          <t>charging_location_history</t>
+          <t>driver_history</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
@@ -27036,7 +27068,7 @@
       <c r="A58" s="6" t="n"/>
       <c r="B58" s="7" t="inlineStr">
         <is>
-          <t>charging_station_history</t>
+          <t>fleet_history</t>
         </is>
       </c>
       <c r="C58" s="6" t="inlineStr">
@@ -27045,11 +27077,11 @@
         </is>
       </c>
     </row>
-    <row r="59">
+    <row r="59" ht="27" customHeight="1">
       <c r="A59" s="6" t="n"/>
       <c r="B59" s="7" t="inlineStr">
         <is>
-          <t>charging_evse_history</t>
+          <t>charging_location_history</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
@@ -27058,14 +27090,40 @@
         </is>
       </c>
     </row>
-    <row r="60" ht="27" customHeight="1">
+    <row r="60">
       <c r="A60" s="6" t="n"/>
       <c r="B60" s="7" t="inlineStr">
         <is>
+          <t>charging_station_history</t>
+        </is>
+      </c>
+      <c r="C60" s="6" t="inlineStr">
+        <is>
+          <t>changed_by</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="6" t="n"/>
+      <c r="B61" s="7" t="inlineStr">
+        <is>
+          <t>charging_evse_history</t>
+        </is>
+      </c>
+      <c r="C61" s="6" t="inlineStr">
+        <is>
+          <t>changed_by</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="27" customHeight="1">
+      <c r="A62" s="6" t="n"/>
+      <c r="B62" s="7" t="inlineStr">
+        <is>
           <t>charging_connector_history</t>
         </is>
       </c>
-      <c r="C60" s="6" t="inlineStr">
+      <c r="C62" s="6" t="inlineStr">
         <is>
           <t>changed_by</t>
         </is>
@@ -27092,28 +27150,30 @@
     <hyperlink ref="B36" location="'user_role_assignments'!A1"/>
     <hyperlink ref="B37" location="'user_role_assignments'!A1"/>
     <hyperlink ref="B38" location="'access_audit_logs'!A1"/>
-    <hyperlink ref="B39" location="'charging_location_access'!A1"/>
-    <hyperlink ref="B40" location="'charging_location_access'!A1"/>
-    <hyperlink ref="B41" location="'charging_station_commands'!A1"/>
-    <hyperlink ref="B42" location="'charging_sessions'!A1"/>
-    <hyperlink ref="B43" location="'charging_policy_versions'!A1"/>
-    <hyperlink ref="B44" location="'organization_history'!A1"/>
-    <hyperlink ref="B45" location="'user_history'!A1"/>
-    <hyperlink ref="B46" location="'user_history'!A1"/>
-    <hyperlink ref="B47" location="'membership_history'!A1"/>
-    <hyperlink ref="B48" location="'organization_setting_history'!A1"/>
-    <hyperlink ref="B49" location="'vehicle_history'!A1"/>
-    <hyperlink ref="B50" location="'vehicle_model_history'!A1"/>
-    <hyperlink ref="B51" location="'battery_model_history'!A1"/>
-    <hyperlink ref="B52" location="'battery_history'!A1"/>
-    <hyperlink ref="B53" location="'warranty_history'!A1"/>
-    <hyperlink ref="B54" location="'telematic_history'!A1"/>
-    <hyperlink ref="B55" location="'driver_history'!A1"/>
-    <hyperlink ref="B56" location="'fleet_history'!A1"/>
-    <hyperlink ref="B57" location="'charging_location_history'!A1"/>
-    <hyperlink ref="B58" location="'charging_station_history'!A1"/>
-    <hyperlink ref="B59" location="'charging_evse_history'!A1"/>
-    <hyperlink ref="B60" location="'charging_connector_history'!A1"/>
+    <hyperlink ref="B39" location="'fleet_vehicle_memberships'!A1"/>
+    <hyperlink ref="B40" location="'fleet_vehicle_memberships'!A1"/>
+    <hyperlink ref="B41" location="'charging_location_access'!A1"/>
+    <hyperlink ref="B42" location="'charging_location_access'!A1"/>
+    <hyperlink ref="B43" location="'charging_station_commands'!A1"/>
+    <hyperlink ref="B44" location="'charging_sessions'!A1"/>
+    <hyperlink ref="B45" location="'charging_policy_versions'!A1"/>
+    <hyperlink ref="B46" location="'organization_history'!A1"/>
+    <hyperlink ref="B47" location="'user_history'!A1"/>
+    <hyperlink ref="B48" location="'user_history'!A1"/>
+    <hyperlink ref="B49" location="'membership_history'!A1"/>
+    <hyperlink ref="B50" location="'organization_setting_history'!A1"/>
+    <hyperlink ref="B51" location="'vehicle_history'!A1"/>
+    <hyperlink ref="B52" location="'vehicle_model_history'!A1"/>
+    <hyperlink ref="B53" location="'battery_model_history'!A1"/>
+    <hyperlink ref="B54" location="'battery_history'!A1"/>
+    <hyperlink ref="B55" location="'warranty_history'!A1"/>
+    <hyperlink ref="B56" location="'telematic_history'!A1"/>
+    <hyperlink ref="B57" location="'driver_history'!A1"/>
+    <hyperlink ref="B58" location="'fleet_history'!A1"/>
+    <hyperlink ref="B59" location="'charging_location_history'!A1"/>
+    <hyperlink ref="B60" location="'charging_station_history'!A1"/>
+    <hyperlink ref="B61" location="'charging_evse_history'!A1"/>
+    <hyperlink ref="B62" location="'charging_connector_history'!A1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/design/domain-model/domain-model.xlsx
+++ b/docs/design/domain-model/domain-model.xlsx
@@ -125,7 +125,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="36" hidden="1">'fleet_history'!$A$7:$I$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="37" hidden="1">'fleet_vehicle_memberships'!$A$6:$I$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="38" hidden="1">'geofences'!$A$6:$I$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="39" hidden="1">'fleet_user_assignments'!$A$6:$I$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="39" hidden="1">'fleet_user_assignments'!$A$6:$I$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="40" hidden="1">'charging_locations'!$A$7:$I$18</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="41" hidden="1">'charging_location_history'!$A$7:$I$22</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="42" hidden="1">'charging_location_access'!$A$6:$I$15</definedName>
@@ -2635,7 +2635,7 @@
         </is>
       </c>
     </row>
-    <row r="52" ht="67.5" customHeight="1">
+    <row r="52" ht="121.5" customHeight="1">
       <c r="A52" s="6" t="inlineStr">
         <is>
           <t>27</t>
@@ -2668,11 +2668,11 @@
       </c>
       <c r="G52" s="6" t="inlineStr">
         <is>
-          <t>Giới hạn vai trò cấp đội xe của một người dùng trong một số đội xe của tổ chức lớn (ví dụ một quản lý cho đội Hà Nội, một quản lý khác cho đội TP.HCM). Người dùng không có dòng nào đang hiệu lực ở đây thì quản lý mọi đội xe của tổ chức. Nằm ở miền Đội xe, không ở miền Danh tính, để miền Danh tính không phụ thuộc miền nào.</t>
+          <t>Giới hạn vai trò cấp đội xe của một người dùng trong một số đội xe của tổ chức lớn (ví dụ một quản lý cho đội Hà Nội, một quản lý khác cho đội TP.HCM). Người dùng không có dòng nào đang hiệu lực ở đây thì quản lý mọi đội xe của tổ chức. Phạm vi xem là hợp của các đội được giao và mọi đội bên dưới, mỗi xe một lần, gồm các xe đang thuộc các đội đó (FL-10). Được phép giao một đội đã nằm dưới một đội cha được giao (giữ quyền khi cây thay đổi); portal sẽ cảnh báo. Nằm ở miền Đội xe, không ở miền Danh tính, để miền Danh tính không phụ thuộc miền nào. Không có lịch sử thay đổi: dòng chỉ bị đóng (DM-20); assigned_by / unassigned_by cho biết ai thực hiện.</t>
         </is>
       </c>
       <c r="H52" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I52" s="7" t="inlineStr">
         <is>
@@ -10584,7 +10584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I59"/>
+  <dimension ref="A1:I58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -11419,7 +11419,7 @@
       <c r="A40" s="6" t="n"/>
       <c r="B40" s="7" t="inlineStr">
         <is>
-          <t>fleet_user_assignments</t>
+          <t>geofences</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
@@ -11432,7 +11432,7 @@
       <c r="A41" s="6" t="n"/>
       <c r="B41" s="7" t="inlineStr">
         <is>
-          <t>geofences</t>
+          <t>charging_locations</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
@@ -11441,29 +11441,29 @@
         </is>
       </c>
     </row>
-    <row r="42">
+    <row r="42" ht="27" customHeight="1">
       <c r="A42" s="6" t="n"/>
       <c r="B42" s="7" t="inlineStr">
         <is>
-          <t>charging_locations</t>
+          <t>charging_location_access</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>organization_id</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="27" customHeight="1">
+          <t>allowed_organization_id</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
       <c r="A43" s="6" t="n"/>
       <c r="B43" s="7" t="inlineStr">
         <is>
-          <t>charging_location_access</t>
+          <t>charging_sessions</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>allowed_organization_id</t>
+          <t>organization_id</t>
         </is>
       </c>
     </row>
@@ -11471,7 +11471,7 @@
       <c r="A44" s="6" t="n"/>
       <c r="B44" s="7" t="inlineStr">
         <is>
-          <t>charging_sessions</t>
+          <t>notifications</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
@@ -11484,7 +11484,7 @@
       <c r="A45" s="6" t="n"/>
       <c r="B45" s="7" t="inlineStr">
         <is>
-          <t>notifications</t>
+          <t>support_cases</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
@@ -11497,7 +11497,7 @@
       <c r="A46" s="6" t="n"/>
       <c r="B46" s="7" t="inlineStr">
         <is>
-          <t>support_cases</t>
+          <t>repair_partners</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
@@ -11510,7 +11510,7 @@
       <c r="A47" s="6" t="n"/>
       <c r="B47" s="7" t="inlineStr">
         <is>
-          <t>repair_partners</t>
+          <t>maintenance_bookings</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
@@ -11519,11 +11519,11 @@
         </is>
       </c>
     </row>
-    <row r="48">
+    <row r="48" ht="27" customHeight="1">
       <c r="A48" s="6" t="n"/>
       <c r="B48" s="7" t="inlineStr">
         <is>
-          <t>maintenance_bookings</t>
+          <t>charging_policy_assignments</t>
         </is>
       </c>
       <c r="C48" s="6" t="inlineStr">
@@ -11532,11 +11532,11 @@
         </is>
       </c>
     </row>
-    <row r="49" ht="27" customHeight="1">
+    <row r="49">
       <c r="A49" s="6" t="n"/>
       <c r="B49" s="7" t="inlineStr">
         <is>
-          <t>charging_policy_assignments</t>
+          <t>policy_violations</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
@@ -11549,7 +11549,7 @@
       <c r="A50" s="6" t="n"/>
       <c r="B50" s="7" t="inlineStr">
         <is>
-          <t>policy_violations</t>
+          <t>payments</t>
         </is>
       </c>
       <c r="C50" s="6" t="inlineStr">
@@ -11562,7 +11562,7 @@
       <c r="A51" s="6" t="n"/>
       <c r="B51" s="7" t="inlineStr">
         <is>
-          <t>payments</t>
+          <t>wallets</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
@@ -11575,7 +11575,7 @@
       <c r="A52" s="6" t="n"/>
       <c r="B52" s="7" t="inlineStr">
         <is>
-          <t>wallets</t>
+          <t>wallet_transactions</t>
         </is>
       </c>
       <c r="C52" s="6" t="inlineStr">
@@ -11588,7 +11588,7 @@
       <c r="A53" s="6" t="n"/>
       <c r="B53" s="7" t="inlineStr">
         <is>
-          <t>wallet_transactions</t>
+          <t>invoices</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
@@ -11601,7 +11601,7 @@
       <c r="A54" s="6" t="n"/>
       <c r="B54" s="7" t="inlineStr">
         <is>
-          <t>invoices</t>
+          <t>invoice_lines</t>
         </is>
       </c>
       <c r="C54" s="6" t="inlineStr">
@@ -11614,7 +11614,7 @@
       <c r="A55" s="6" t="n"/>
       <c r="B55" s="7" t="inlineStr">
         <is>
-          <t>invoice_lines</t>
+          <t>subscriptions</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
@@ -11627,7 +11627,7 @@
       <c r="A56" s="6" t="n"/>
       <c r="B56" s="7" t="inlineStr">
         <is>
-          <t>subscriptions</t>
+          <t>driver_scores</t>
         </is>
       </c>
       <c r="C56" s="6" t="inlineStr">
@@ -11640,7 +11640,7 @@
       <c r="A57" s="6" t="n"/>
       <c r="B57" s="7" t="inlineStr">
         <is>
-          <t>driver_scores</t>
+          <t>trips</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
@@ -11653,23 +11653,10 @@
       <c r="A58" s="6" t="n"/>
       <c r="B58" s="7" t="inlineStr">
         <is>
-          <t>trips</t>
+          <t>organization_history</t>
         </is>
       </c>
       <c r="C58" s="6" t="inlineStr">
-        <is>
-          <t>organization_id</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="6" t="n"/>
-      <c r="B59" s="7" t="inlineStr">
-        <is>
-          <t>organization_history</t>
-        </is>
-      </c>
-      <c r="C59" s="6" t="inlineStr">
         <is>
           <t>organization_id</t>
         </is>
@@ -11695,26 +11682,25 @@
     <hyperlink ref="B37" location="'driver_vehicle_assignments'!A1"/>
     <hyperlink ref="B38" location="'driving_sessions'!A1"/>
     <hyperlink ref="B39" location="'fleets'!A1"/>
-    <hyperlink ref="B40" location="'fleet_user_assignments'!A1"/>
-    <hyperlink ref="B41" location="'geofences'!A1"/>
-    <hyperlink ref="B42" location="'charging_locations'!A1"/>
-    <hyperlink ref="B43" location="'charging_location_access'!A1"/>
-    <hyperlink ref="B44" location="'charging_sessions'!A1"/>
-    <hyperlink ref="B45" location="'notifications'!A1"/>
-    <hyperlink ref="B46" location="'support_cases'!A1"/>
-    <hyperlink ref="B47" location="'repair_partners'!A1"/>
-    <hyperlink ref="B48" location="'maintenance_bookings'!A1"/>
-    <hyperlink ref="B49" location="'charging_policy_assignments'!A1"/>
-    <hyperlink ref="B50" location="'policy_violations'!A1"/>
-    <hyperlink ref="B51" location="'payments'!A1"/>
-    <hyperlink ref="B52" location="'wallets'!A1"/>
-    <hyperlink ref="B53" location="'wallet_transactions'!A1"/>
-    <hyperlink ref="B54" location="'invoices'!A1"/>
-    <hyperlink ref="B55" location="'invoice_lines'!A1"/>
-    <hyperlink ref="B56" location="'subscriptions'!A1"/>
-    <hyperlink ref="B57" location="'driver_scores'!A1"/>
-    <hyperlink ref="B58" location="'trips'!A1"/>
-    <hyperlink ref="B59" location="'organization_history'!A1"/>
+    <hyperlink ref="B40" location="'geofences'!A1"/>
+    <hyperlink ref="B41" location="'charging_locations'!A1"/>
+    <hyperlink ref="B42" location="'charging_location_access'!A1"/>
+    <hyperlink ref="B43" location="'charging_sessions'!A1"/>
+    <hyperlink ref="B44" location="'notifications'!A1"/>
+    <hyperlink ref="B45" location="'support_cases'!A1"/>
+    <hyperlink ref="B46" location="'repair_partners'!A1"/>
+    <hyperlink ref="B47" location="'maintenance_bookings'!A1"/>
+    <hyperlink ref="B48" location="'charging_policy_assignments'!A1"/>
+    <hyperlink ref="B49" location="'policy_violations'!A1"/>
+    <hyperlink ref="B50" location="'payments'!A1"/>
+    <hyperlink ref="B51" location="'wallets'!A1"/>
+    <hyperlink ref="B52" location="'wallet_transactions'!A1"/>
+    <hyperlink ref="B53" location="'invoices'!A1"/>
+    <hyperlink ref="B54" location="'invoice_lines'!A1"/>
+    <hyperlink ref="B55" location="'subscriptions'!A1"/>
+    <hyperlink ref="B56" location="'driver_scores'!A1"/>
+    <hyperlink ref="B57" location="'trips'!A1"/>
+    <hyperlink ref="B58" location="'organization_history'!A1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -26066,7 +26052,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I62"/>
+  <dimension ref="A1:I64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -26847,12 +26833,12 @@
       <c r="A41" s="6" t="n"/>
       <c r="B41" s="7" t="inlineStr">
         <is>
-          <t>charging_location_access</t>
+          <t>fleet_user_assignments</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>granted_by</t>
+          <t>assigned_by</t>
         </is>
       </c>
     </row>
@@ -26860,25 +26846,25 @@
       <c r="A42" s="6" t="n"/>
       <c r="B42" s="7" t="inlineStr">
         <is>
-          <t>charging_location_access</t>
+          <t>fleet_user_assignments</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>revoked_by</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="27" customHeight="1">
+          <t>unassigned_by</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
       <c r="A43" s="6" t="n"/>
       <c r="B43" s="7" t="inlineStr">
         <is>
-          <t>charging_station_commands</t>
+          <t>charging_location_access</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>requested_by</t>
+          <t>granted_by</t>
         </is>
       </c>
     </row>
@@ -26886,25 +26872,25 @@
       <c r="A44" s="6" t="n"/>
       <c r="B44" s="7" t="inlineStr">
         <is>
-          <t>charging_sessions</t>
+          <t>charging_location_access</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>started_by</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
+          <t>revoked_by</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="27" customHeight="1">
       <c r="A45" s="6" t="n"/>
       <c r="B45" s="7" t="inlineStr">
         <is>
-          <t>charging_policy_versions</t>
+          <t>charging_station_commands</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>created_by</t>
+          <t>requested_by</t>
         </is>
       </c>
     </row>
@@ -26912,12 +26898,12 @@
       <c r="A46" s="6" t="n"/>
       <c r="B46" s="7" t="inlineStr">
         <is>
-          <t>organization_history</t>
+          <t>charging_sessions</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>changed_by</t>
+          <t>started_by</t>
         </is>
       </c>
     </row>
@@ -26925,12 +26911,12 @@
       <c r="A47" s="6" t="n"/>
       <c r="B47" s="7" t="inlineStr">
         <is>
-          <t>user_history</t>
+          <t>charging_policy_versions</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>user_id</t>
+          <t>created_by</t>
         </is>
       </c>
     </row>
@@ -26938,7 +26924,7 @@
       <c r="A48" s="6" t="n"/>
       <c r="B48" s="7" t="inlineStr">
         <is>
-          <t>user_history</t>
+          <t>organization_history</t>
         </is>
       </c>
       <c r="C48" s="6" t="inlineStr">
@@ -26951,20 +26937,20 @@
       <c r="A49" s="6" t="n"/>
       <c r="B49" s="7" t="inlineStr">
         <is>
-          <t>membership_history</t>
+          <t>user_history</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>changed_by</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="27" customHeight="1">
+          <t>user_id</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
       <c r="A50" s="6" t="n"/>
       <c r="B50" s="7" t="inlineStr">
         <is>
-          <t>organization_setting_history</t>
+          <t>user_history</t>
         </is>
       </c>
       <c r="C50" s="6" t="inlineStr">
@@ -26977,7 +26963,7 @@
       <c r="A51" s="6" t="n"/>
       <c r="B51" s="7" t="inlineStr">
         <is>
-          <t>vehicle_history</t>
+          <t>membership_history</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
@@ -26986,11 +26972,11 @@
         </is>
       </c>
     </row>
-    <row r="52">
+    <row r="52" ht="27" customHeight="1">
       <c r="A52" s="6" t="n"/>
       <c r="B52" s="7" t="inlineStr">
         <is>
-          <t>vehicle_model_history</t>
+          <t>organization_setting_history</t>
         </is>
       </c>
       <c r="C52" s="6" t="inlineStr">
@@ -27003,7 +26989,7 @@
       <c r="A53" s="6" t="n"/>
       <c r="B53" s="7" t="inlineStr">
         <is>
-          <t>battery_model_history</t>
+          <t>vehicle_history</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
@@ -27016,7 +27002,7 @@
       <c r="A54" s="6" t="n"/>
       <c r="B54" s="7" t="inlineStr">
         <is>
-          <t>battery_history</t>
+          <t>vehicle_model_history</t>
         </is>
       </c>
       <c r="C54" s="6" t="inlineStr">
@@ -27029,7 +27015,7 @@
       <c r="A55" s="6" t="n"/>
       <c r="B55" s="7" t="inlineStr">
         <is>
-          <t>warranty_history</t>
+          <t>battery_model_history</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
@@ -27042,7 +27028,7 @@
       <c r="A56" s="6" t="n"/>
       <c r="B56" s="7" t="inlineStr">
         <is>
-          <t>telematic_history</t>
+          <t>battery_history</t>
         </is>
       </c>
       <c r="C56" s="6" t="inlineStr">
@@ -27055,7 +27041,7 @@
       <c r="A57" s="6" t="n"/>
       <c r="B57" s="7" t="inlineStr">
         <is>
-          <t>driver_history</t>
+          <t>warranty_history</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
@@ -27068,7 +27054,7 @@
       <c r="A58" s="6" t="n"/>
       <c r="B58" s="7" t="inlineStr">
         <is>
-          <t>fleet_history</t>
+          <t>telematic_history</t>
         </is>
       </c>
       <c r="C58" s="6" t="inlineStr">
@@ -27077,11 +27063,11 @@
         </is>
       </c>
     </row>
-    <row r="59" ht="27" customHeight="1">
+    <row r="59">
       <c r="A59" s="6" t="n"/>
       <c r="B59" s="7" t="inlineStr">
         <is>
-          <t>charging_location_history</t>
+          <t>driver_history</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
@@ -27094,7 +27080,7 @@
       <c r="A60" s="6" t="n"/>
       <c r="B60" s="7" t="inlineStr">
         <is>
-          <t>charging_station_history</t>
+          <t>fleet_history</t>
         </is>
       </c>
       <c r="C60" s="6" t="inlineStr">
@@ -27103,11 +27089,11 @@
         </is>
       </c>
     </row>
-    <row r="61">
+    <row r="61" ht="27" customHeight="1">
       <c r="A61" s="6" t="n"/>
       <c r="B61" s="7" t="inlineStr">
         <is>
-          <t>charging_evse_history</t>
+          <t>charging_location_history</t>
         </is>
       </c>
       <c r="C61" s="6" t="inlineStr">
@@ -27116,14 +27102,40 @@
         </is>
       </c>
     </row>
-    <row r="62" ht="27" customHeight="1">
+    <row r="62">
       <c r="A62" s="6" t="n"/>
       <c r="B62" s="7" t="inlineStr">
         <is>
+          <t>charging_station_history</t>
+        </is>
+      </c>
+      <c r="C62" s="6" t="inlineStr">
+        <is>
+          <t>changed_by</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="6" t="n"/>
+      <c r="B63" s="7" t="inlineStr">
+        <is>
+          <t>charging_evse_history</t>
+        </is>
+      </c>
+      <c r="C63" s="6" t="inlineStr">
+        <is>
+          <t>changed_by</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="27" customHeight="1">
+      <c r="A64" s="6" t="n"/>
+      <c r="B64" s="7" t="inlineStr">
+        <is>
           <t>charging_connector_history</t>
         </is>
       </c>
-      <c r="C62" s="6" t="inlineStr">
+      <c r="C64" s="6" t="inlineStr">
         <is>
           <t>changed_by</t>
         </is>
@@ -27152,28 +27164,30 @@
     <hyperlink ref="B38" location="'access_audit_logs'!A1"/>
     <hyperlink ref="B39" location="'fleet_vehicle_memberships'!A1"/>
     <hyperlink ref="B40" location="'fleet_vehicle_memberships'!A1"/>
-    <hyperlink ref="B41" location="'charging_location_access'!A1"/>
-    <hyperlink ref="B42" location="'charging_location_access'!A1"/>
-    <hyperlink ref="B43" location="'charging_station_commands'!A1"/>
-    <hyperlink ref="B44" location="'charging_sessions'!A1"/>
-    <hyperlink ref="B45" location="'charging_policy_versions'!A1"/>
-    <hyperlink ref="B46" location="'organization_history'!A1"/>
-    <hyperlink ref="B47" location="'user_history'!A1"/>
-    <hyperlink ref="B48" location="'user_history'!A1"/>
-    <hyperlink ref="B49" location="'membership_history'!A1"/>
-    <hyperlink ref="B50" location="'organization_setting_history'!A1"/>
-    <hyperlink ref="B51" location="'vehicle_history'!A1"/>
-    <hyperlink ref="B52" location="'vehicle_model_history'!A1"/>
-    <hyperlink ref="B53" location="'battery_model_history'!A1"/>
-    <hyperlink ref="B54" location="'battery_history'!A1"/>
-    <hyperlink ref="B55" location="'warranty_history'!A1"/>
-    <hyperlink ref="B56" location="'telematic_history'!A1"/>
-    <hyperlink ref="B57" location="'driver_history'!A1"/>
-    <hyperlink ref="B58" location="'fleet_history'!A1"/>
-    <hyperlink ref="B59" location="'charging_location_history'!A1"/>
-    <hyperlink ref="B60" location="'charging_station_history'!A1"/>
-    <hyperlink ref="B61" location="'charging_evse_history'!A1"/>
-    <hyperlink ref="B62" location="'charging_connector_history'!A1"/>
+    <hyperlink ref="B41" location="'fleet_user_assignments'!A1"/>
+    <hyperlink ref="B42" location="'fleet_user_assignments'!A1"/>
+    <hyperlink ref="B43" location="'charging_location_access'!A1"/>
+    <hyperlink ref="B44" location="'charging_location_access'!A1"/>
+    <hyperlink ref="B45" location="'charging_station_commands'!A1"/>
+    <hyperlink ref="B46" location="'charging_sessions'!A1"/>
+    <hyperlink ref="B47" location="'charging_policy_versions'!A1"/>
+    <hyperlink ref="B48" location="'organization_history'!A1"/>
+    <hyperlink ref="B49" location="'user_history'!A1"/>
+    <hyperlink ref="B50" location="'user_history'!A1"/>
+    <hyperlink ref="B51" location="'membership_history'!A1"/>
+    <hyperlink ref="B52" location="'organization_setting_history'!A1"/>
+    <hyperlink ref="B53" location="'vehicle_history'!A1"/>
+    <hyperlink ref="B54" location="'vehicle_model_history'!A1"/>
+    <hyperlink ref="B55" location="'battery_model_history'!A1"/>
+    <hyperlink ref="B56" location="'battery_history'!A1"/>
+    <hyperlink ref="B57" location="'warranty_history'!A1"/>
+    <hyperlink ref="B58" location="'telematic_history'!A1"/>
+    <hyperlink ref="B59" location="'driver_history'!A1"/>
+    <hyperlink ref="B60" location="'fleet_history'!A1"/>
+    <hyperlink ref="B61" location="'charging_location_history'!A1"/>
+    <hyperlink ref="B62" location="'charging_station_history'!A1"/>
+    <hyperlink ref="B63" location="'charging_evse_history'!A1"/>
+    <hyperlink ref="B64" location="'charging_connector_history'!A1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -27185,7 +27199,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -27223,7 +27237,7 @@
     <row r="4">
       <c r="A4" s="11" t="inlineStr">
         <is>
-          <t>Giới hạn vai trò cấp đội xe của một người dùng trong một số đội xe của tổ chức lớn (ví dụ một quản lý cho đội Hà Nội, một quản lý khác cho đội TP.HCM). Người dùng không có dòng nào đang hiệu lực ở đây thì quản lý mọi đội xe của tổ chức. Nằm ở miền Đội xe, không ở miền Danh tính, để miền Danh tính không phụ thuộc miền nào.</t>
+          <t>Giới hạn vai trò cấp đội xe của một người dùng trong một số đội xe của tổ chức lớn (ví dụ một quản lý cho đội Hà Nội, một quản lý khác cho đội TP.HCM). Người dùng không có dòng nào đang hiệu lực ở đây thì quản lý mọi đội xe của tổ chức. Phạm vi xem là hợp của các đội được giao và mọi đội bên dưới, mỗi xe một lần, gồm các xe đang thuộc các đội đó (FL-10). Được phép giao một đội đã nằm dưới một đội cha được giao (giữ quyền khi cây thay đổi); portal sẽ cảnh báo. Nằm ở miền Đội xe, không ở miền Danh tính, để miền Danh tính không phụ thuộc miền nào. Không có lịch sử thay đổi: dòng chỉ bị đóng (DM-20); assigned_by / unassigned_by cho biết ai thực hiện.</t>
         </is>
       </c>
     </row>
@@ -27281,7 +27295,7 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>assignment_id</t>
+          <t>fleet_user_assignment_id</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
@@ -27312,13 +27326,13 @@
       </c>
       <c r="I7" s="6" t="n"/>
     </row>
-    <row r="8" ht="27" customHeight="1">
+    <row r="8" ht="40.5" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>2</v>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>organization_id</t>
+          <t>fleet_id</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
@@ -27338,28 +27352,28 @@
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>organizations.organization_id (khi xóa: chặn xóa)</t>
+          <t>fleets.fleet_id (khi xóa: chặn xóa)</t>
         </is>
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>Tổ chức của đội xe và người dùng.</t>
+          <t>Đội xe mà người dùng được giới hạn trong đó, cùng mọi đội xe nằm dưới. Phải thuộc tổ chức của thành viên (dịch vụ kiểm tra; dòng đọc tổ chức qua một trong hai, DM-24).</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
-          <t>3f6c2a1e-8b4d-4e2a-9c1f-0a7d5b2e4c11</t>
+          <t>8d5f2b7e-1a9c-4f3d-b8e2-6c0a4d9f1e77</t>
         </is>
       </c>
       <c r="I8" s="6" t="n"/>
     </row>
-    <row r="9" ht="27" customHeight="1">
+    <row r="9" ht="40.5" customHeight="1">
       <c r="A9" s="6" t="n">
         <v>3</v>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>fleet_id</t>
+          <t>membership_id</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
@@ -27379,33 +27393,33 @@
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>fleets.fleet_id (khi xóa: chặn xóa)</t>
+          <t>memberships.membership_id (khi xóa: chặn xóa)</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>Đội xe mà người dùng được giới hạn trong đó, cùng mọi đội xe nằm dưới.</t>
+          <t>Thành viên (người trong tổ chức này) có các vai trò cấp đội xe (FLEET_MANAGER, DISPATCHER) chỉ áp dụng cho các đội xe được liệt kê.</t>
         </is>
       </c>
       <c r="H9" s="6" t="inlineStr">
         <is>
-          <t>8d5f2b7e-1a9c-4f3d-b8e2-6c0a4d9f1e77</t>
+          <t>00000022-5a6b-4c7d-8e9f-0a1b2c3d4e5f</t>
         </is>
       </c>
       <c r="I9" s="6" t="n"/>
     </row>
-    <row r="10" ht="40.5" customHeight="1">
+    <row r="10">
       <c r="A10" s="6" t="n">
         <v>4</v>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>membership_id</t>
+          <t>assigned_at</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>uuid</t>
+          <t>timestamptz</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
@@ -27413,57 +27427,57 @@
           <t>không</t>
         </is>
       </c>
-      <c r="E10" s="6" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="F10" s="7" t="inlineStr">
-        <is>
-          <t>memberships.membership_id (khi xóa: chặn xóa)</t>
-        </is>
-      </c>
+      <c r="E10" s="6" t="n"/>
+      <c r="F10" s="6" t="n"/>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>Thành viên (người trong tổ chức này) có các vai trò cấp đội xe (FLEET_MANAGER, DISPATCHER) chỉ áp dụng cho các đội xe được liệt kê.</t>
+          <t>Thời điểm người dùng được giao đội xe này.</t>
         </is>
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>00000022-5a6b-4c7d-8e9f-0a1b2c3d4e5f</t>
+          <t>2026-09-01T02:00:00Z</t>
         </is>
       </c>
       <c r="I10" s="6" t="n"/>
     </row>
-    <row r="11">
+    <row r="11" ht="27" customHeight="1">
       <c r="A11" s="6" t="n">
         <v>5</v>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>assigned_at</t>
+          <t>assigned_by</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>timestamptz</t>
+          <t>uuid</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E11" s="6" t="n"/>
-      <c r="F11" s="6" t="n"/>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>users.user_id (khi xóa: chặn xóa)</t>
+        </is>
+      </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>Thời điểm người dùng được giao đội xe này.</t>
+          <t>Ai đã giao (thường là ORG_ADMIN); NULL khi hệ thống tự giao.</t>
         </is>
       </c>
       <c r="H11" s="6" t="inlineStr">
         <is>
-          <t>2026-09-01T02:00:00Z</t>
+          <t>9b2e7d4a-1c3f-4a8e-b6d2-5e0f1a9c3d22</t>
         </is>
       </c>
       <c r="I11" s="6" t="n"/>
@@ -27501,62 +27515,104 @@
       </c>
       <c r="I12" s="6" t="n"/>
     </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" s="4" t="n"/>
-      <c r="B14" s="4" t="inlineStr">
+    <row r="13" ht="27" customHeight="1">
+      <c r="A13" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>unassigned_by</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>uuid</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>users.user_id (khi xóa: chặn xóa)</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>Ai đã thu lại; NULL khi còn hiệu lực, hoặc khi hệ thống tự kết thúc (thành viên rời tổ chức hoặc đội bị xóa).</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="I13" s="6" t="n"/>
+    </row>
+    <row r="14"/>
+    <row r="15">
+      <c r="A15" s="4" t="n"/>
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>Chỉ mục (index)</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>Các cột</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="D15" s="4" t="inlineStr">
         <is>
           <t>Duy nhất</t>
         </is>
       </c>
-      <c r="E14" s="4" t="n"/>
-      <c r="F14" s="4" t="inlineStr">
+      <c r="E15" s="4" t="n"/>
+      <c r="F15" s="4" t="inlineStr">
         <is>
           <t>Ghi chú</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="27" customHeight="1">
-      <c r="A15" s="6" t="n"/>
-      <c r="B15" s="6" t="inlineStr">
+    <row r="16" ht="27" customHeight="1">
+      <c r="A16" s="6" t="n"/>
+      <c r="B16" s="6" t="inlineStr">
         <is>
           <t>uq_fleet_user_assignments_active</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr">
+      <c r="C16" s="6" t="inlineStr">
         <is>
           <t>fleet_id, membership_id</t>
         </is>
       </c>
-      <c r="D15" s="6" t="inlineStr">
+      <c r="D16" s="6" t="inlineStr">
         <is>
           <t>có</t>
         </is>
       </c>
-      <c r="E15" s="6" t="n"/>
-      <c r="F15" s="6" t="inlineStr">
+      <c r="E16" s="6" t="n"/>
+      <c r="F16" s="6" t="inlineStr">
         <is>
           <t>WHERE unassigned_at IS NULL</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A6:I12"/>
+  <autoFilter ref="A6:I13"/>
   <hyperlinks>
     <hyperlink ref="A2" location="'Tổng quan'!A1"/>
-    <hyperlink ref="F8" location="'organizations'!A1"/>
-    <hyperlink ref="F9" location="'fleets'!A1"/>
-    <hyperlink ref="F10" location="'memberships'!A1"/>
+    <hyperlink ref="F8" location="'fleets'!A1"/>
+    <hyperlink ref="F9" location="'memberships'!A1"/>
+    <hyperlink ref="F11" location="'users'!A1"/>
+    <hyperlink ref="F13" location="'users'!A1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/design/domain-model/domain-model.xlsx
+++ b/docs/design/domain-model/domain-model.xlsx
@@ -74,17 +74,18 @@
     <sheet name="charging_policy_assignments" sheetId="65" state="visible" r:id="rId65"/>
     <sheet name="policy_violations" sheetId="66" state="visible" r:id="rId66"/>
     <sheet name="tariffs" sheetId="67" state="visible" r:id="rId67"/>
-    <sheet name="payments" sheetId="68" state="visible" r:id="rId68"/>
-    <sheet name="wallets" sheetId="69" state="visible" r:id="rId69"/>
-    <sheet name="wallet_transactions" sheetId="70" state="visible" r:id="rId70"/>
-    <sheet name="invoices" sheetId="71" state="visible" r:id="rId71"/>
-    <sheet name="invoice_lines" sheetId="72" state="visible" r:id="rId72"/>
-    <sheet name="subscription_plans" sheetId="73" state="visible" r:id="rId73"/>
-    <sheet name="plan_features" sheetId="74" state="visible" r:id="rId74"/>
-    <sheet name="subscriptions" sheetId="75" state="visible" r:id="rId75"/>
-    <sheet name="driver_scores" sheetId="76" state="visible" r:id="rId76"/>
-    <sheet name="promotion_campaigns" sheetId="77" state="visible" r:id="rId77"/>
-    <sheet name="trips" sheetId="78" state="visible" r:id="rId78"/>
+    <sheet name="tariff_history" sheetId="68" state="visible" r:id="rId68"/>
+    <sheet name="payments" sheetId="69" state="visible" r:id="rId69"/>
+    <sheet name="wallets" sheetId="70" state="visible" r:id="rId70"/>
+    <sheet name="wallet_transactions" sheetId="71" state="visible" r:id="rId71"/>
+    <sheet name="invoices" sheetId="72" state="visible" r:id="rId72"/>
+    <sheet name="invoice_lines" sheetId="73" state="visible" r:id="rId73"/>
+    <sheet name="subscription_plans" sheetId="74" state="visible" r:id="rId74"/>
+    <sheet name="plan_features" sheetId="75" state="visible" r:id="rId75"/>
+    <sheet name="subscriptions" sheetId="76" state="visible" r:id="rId76"/>
+    <sheet name="driver_scores" sheetId="77" state="visible" r:id="rId77"/>
+    <sheet name="promotion_campaigns" sheetId="78" state="visible" r:id="rId78"/>
+    <sheet name="trips" sheetId="79" state="visible" r:id="rId79"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'organizations'!$A$7:$I$20</definedName>
@@ -152,18 +153,19 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="63" hidden="1">'charging_policy_versions'!$A$6:$I$16</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="64" hidden="1">'charging_policy_assignments'!$A$6:$I$14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="65" hidden="1">'policy_violations'!$A$6:$I$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="66" hidden="1">'tariffs'!$A$6:$I$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="67" hidden="1">'payments'!$A$6:$I$16</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="68" hidden="1">'wallets'!$A$6:$I$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="69" hidden="1">'wallet_transactions'!$A$6:$I$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="70" hidden="1">'invoices'!$A$6:$I$16</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="71" hidden="1">'invoice_lines'!$A$6:$I$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="72" hidden="1">'subscription_plans'!$A$6:$I$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="73" hidden="1">'plan_features'!$A$6:$I$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="74" hidden="1">'subscriptions'!$A$6:$I$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="75" hidden="1">'driver_scores'!$A$6:$I$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="76" hidden="1">'promotion_campaigns'!$A$6:$I$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="77" hidden="1">'trips'!$A$6:$I$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="66" hidden="1">'tariffs'!$A$7:$I$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="67" hidden="1">'tariff_history'!$A$7:$I$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="68" hidden="1">'payments'!$A$6:$I$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="69" hidden="1">'wallets'!$A$6:$I$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="70" hidden="1">'wallet_transactions'!$A$6:$I$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="71" hidden="1">'invoices'!$A$6:$I$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="72" hidden="1">'invoice_lines'!$A$6:$I$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="73" hidden="1">'subscription_plans'!$A$6:$I$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="74" hidden="1">'plan_features'!$A$6:$I$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="75" hidden="1">'subscriptions'!$A$6:$I$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="76" hidden="1">'driver_scores'!$A$6:$I$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="77" hidden="1">'promotion_campaigns'!$A$6:$I$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="78" hidden="1">'trips'!$A$6:$I$14</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -652,7 +654,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I120"/>
+  <dimension ref="A1:I121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -683,7 +685,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>77 bảng trong 16 miền nghiệp vụ: 58 bảng chính, 16 bảng lịch sử (N.h), 3 bảng trạng thái. Bấm vào tên bảng hoặc «→ Mở» để mở sheet chi tiết của bảng; chú giải và các quyết định còn mở nằm ở cuối trang.</t>
+          <t>78 bảng trong 16 miền nghiệp vụ: 58 bảng chính, 17 bảng lịch sử (N.h), 3 bảng trạng thái. Bấm vào tên bảng hoặc «→ Mở» để mở sheet chi tiết của bảng; chú giải và các quyết định còn mở nằm ở cuối trang.</t>
         </is>
       </c>
     </row>
@@ -3979,7 +3981,7 @@
       </c>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t>9 bảng</t>
+          <t>10 bảng</t>
         </is>
       </c>
       <c r="D84" s="5" t="n"/>
@@ -3997,7 +3999,7 @@
         </is>
       </c>
     </row>
-    <row r="85" ht="27" customHeight="1">
+    <row r="85" ht="81" customHeight="1">
       <c r="A85" s="6" t="inlineStr">
         <is>
           <t>50</t>
@@ -4015,12 +4017,12 @@
       </c>
       <c r="D85" s="7" t="inlineStr">
         <is>
-          <t>Biểu giá điện</t>
+          <t>Biểu giá</t>
         </is>
       </c>
       <c r="E85" s="6" t="inlineStr">
         <is>
-          <t>Nội bộ</t>
+          <t>Khách hàng</t>
         </is>
       </c>
       <c r="F85" s="6" t="inlineStr">
@@ -4030,11 +4032,11 @@
       </c>
       <c r="G85" s="6" t="inlineStr">
         <is>
-          <t>Giá điện. Ai sở hữu biểu giá (G3 Energy hay G3 Network) là mục 5 của feature-list.</t>
+          <t>Giá của ai và áp dụng ở đâu (BL-08); giá cụ thể là các phiên bản không sửa được trong tariff_versions, nên biên nhận luôn hiện đúng giá đã tính. Giá tại một trạm là biểu giá ACTIVE của chính trạm đó, nếu không có thì là biểu giá mặc định của chủ sở hữu. Bật lịch sử thay đổi; không xóa mềm. Sau này: giá riêng theo hợp đồng của một khách hàng, và giá khác nhau theo từng trụ trong cùng một trạm.</t>
         </is>
       </c>
       <c r="H85" s="6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I85" s="7" t="inlineStr">
         <is>
@@ -4042,10 +4044,10 @@
         </is>
       </c>
     </row>
-    <row r="86" ht="27" customHeight="1">
+    <row r="86" ht="40.5" customHeight="1">
       <c r="A86" s="6" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>50.h</t>
         </is>
       </c>
       <c r="B86" s="6" t="inlineStr">
@@ -4055,12 +4057,12 @@
       </c>
       <c r="C86" s="7" t="inlineStr">
         <is>
-          <t>payments</t>
+          <t>tariff_history</t>
         </is>
       </c>
       <c r="D86" s="7" t="inlineStr">
         <is>
-          <t>Thanh toán</t>
+          <t>Lịch sử biểu giá</t>
         </is>
       </c>
       <c r="E86" s="6" t="inlineStr">
@@ -4070,16 +4072,16 @@
       </c>
       <c r="F86" s="6" t="inlineStr">
         <is>
-          <t>F-H1</t>
+          <t>F-C8, F-H1</t>
         </is>
       </c>
       <c r="G86" s="6" t="inlineStr">
         <is>
-          <t>Một lần thanh toán qua cổng thanh toán hoặc ví, thường cho một phiên sạc.</t>
+          <t>Mọi phiên bản trước đây của một dòng trong bảng tariffs: bản sao toàn bộ dòng, chụp ngay trước khi thay đổi và được trigger ghi trong cùng giao dịch. Do công cụ domain-model tự sinh từ @tracked *, không bao giờ viết tay.</t>
         </is>
       </c>
       <c r="H86" s="6" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="I86" s="7" t="inlineStr">
         <is>
@@ -4090,7 +4092,7 @@
     <row r="87" ht="27" customHeight="1">
       <c r="A87" s="6" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B87" s="6" t="inlineStr">
@@ -4100,12 +4102,12 @@
       </c>
       <c r="C87" s="7" t="inlineStr">
         <is>
-          <t>wallets</t>
+          <t>payments</t>
         </is>
       </c>
       <c r="D87" s="7" t="inlineStr">
         <is>
-          <t>Ví</t>
+          <t>Thanh toán</t>
         </is>
       </c>
       <c r="E87" s="6" t="inlineStr">
@@ -4115,16 +4117,16 @@
       </c>
       <c r="F87" s="6" t="inlineStr">
         <is>
-          <t>F-H2</t>
+          <t>F-H1</t>
         </is>
       </c>
       <c r="G87" s="6" t="inlineStr">
         <is>
-          <t>Số dư trả trước của một tài xế hoặc của cả tổ chức.</t>
+          <t>Một lần thanh toán qua cổng thanh toán hoặc ví, thường cho một phiên sạc.</t>
         </is>
       </c>
       <c r="H87" s="6" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I87" s="7" t="inlineStr">
         <is>
@@ -4135,7 +4137,7 @@
     <row r="88" ht="27" customHeight="1">
       <c r="A88" s="6" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>52</t>
         </is>
       </c>
       <c r="B88" s="6" t="inlineStr">
@@ -4145,12 +4147,12 @@
       </c>
       <c r="C88" s="7" t="inlineStr">
         <is>
-          <t>wallet_transactions</t>
+          <t>wallets</t>
         </is>
       </c>
       <c r="D88" s="7" t="inlineStr">
         <is>
-          <t>Giao dịch ví</t>
+          <t>Ví</t>
         </is>
       </c>
       <c r="E88" s="6" t="inlineStr">
@@ -4165,11 +4167,11 @@
       </c>
       <c r="G88" s="6" t="inlineStr">
         <is>
-          <t>Biến động tiền vào/ra khỏi ví, chỉ ghi thêm.</t>
+          <t>Số dư trả trước của một tài xế hoặc của cả tổ chức.</t>
         </is>
       </c>
       <c r="H88" s="6" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I88" s="7" t="inlineStr">
         <is>
@@ -4180,7 +4182,7 @@
     <row r="89" ht="27" customHeight="1">
       <c r="A89" s="6" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>53</t>
         </is>
       </c>
       <c r="B89" s="6" t="inlineStr">
@@ -4190,12 +4192,12 @@
       </c>
       <c r="C89" s="7" t="inlineStr">
         <is>
-          <t>invoices</t>
+          <t>wallet_transactions</t>
         </is>
       </c>
       <c r="D89" s="7" t="inlineStr">
         <is>
-          <t>Hóa đơn</t>
+          <t>Giao dịch ví</t>
         </is>
       </c>
       <c r="E89" s="6" t="inlineStr">
@@ -4205,16 +4207,16 @@
       </c>
       <c r="F89" s="6" t="inlineStr">
         <is>
-          <t>F-H3, F-H4</t>
+          <t>F-H2</t>
         </is>
       </c>
       <c r="G89" s="6" t="inlineStr">
         <is>
-          <t>Một hóa đơn điện tử hợp lệ. Khi đã PHÁT HÀNH thì không sửa, chỉ điều chỉnh hoặc hủy bằng hóa đơn mới.</t>
+          <t>Biến động tiền vào/ra khỏi ví, chỉ ghi thêm.</t>
         </is>
       </c>
       <c r="H89" s="6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I89" s="7" t="inlineStr">
         <is>
@@ -4225,617 +4227,662 @@
     <row r="90" ht="27" customHeight="1">
       <c r="A90" s="6" t="inlineStr">
         <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="B90" s="6" t="inlineStr">
+        <is>
+          <t>Thanh toán &amp; hóa đơn (billing)</t>
+        </is>
+      </c>
+      <c r="C90" s="7" t="inlineStr">
+        <is>
+          <t>invoices</t>
+        </is>
+      </c>
+      <c r="D90" s="7" t="inlineStr">
+        <is>
+          <t>Hóa đơn</t>
+        </is>
+      </c>
+      <c r="E90" s="6" t="inlineStr">
+        <is>
+          <t>Khách hàng</t>
+        </is>
+      </c>
+      <c r="F90" s="6" t="inlineStr">
+        <is>
+          <t>F-H3, F-H4</t>
+        </is>
+      </c>
+      <c r="G90" s="6" t="inlineStr">
+        <is>
+          <t>Một hóa đơn điện tử hợp lệ. Khi đã PHÁT HÀNH thì không sửa, chỉ điều chỉnh hoặc hủy bằng hóa đơn mới.</t>
+        </is>
+      </c>
+      <c r="H90" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="I90" s="7" t="inlineStr">
+        <is>
+          <t>→ Mở</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="27" customHeight="1">
+      <c r="A91" s="6" t="inlineStr">
+        <is>
           <t>55</t>
         </is>
       </c>
-      <c r="B90" s="6" t="inlineStr">
+      <c r="B91" s="6" t="inlineStr">
         <is>
           <t>Thanh toán &amp; hóa đơn (billing)</t>
         </is>
       </c>
-      <c r="C90" s="7" t="inlineStr">
+      <c r="C91" s="7" t="inlineStr">
         <is>
           <t>invoice_lines</t>
         </is>
       </c>
-      <c r="D90" s="7" t="inlineStr">
+      <c r="D91" s="7" t="inlineStr">
         <is>
           <t>Dòng hóa đơn</t>
         </is>
       </c>
-      <c r="E90" s="6" t="inlineStr">
+      <c r="E91" s="6" t="inlineStr">
         <is>
           <t>Khách hàng</t>
         </is>
       </c>
-      <c r="F90" s="6" t="inlineStr">
+      <c r="F91" s="6" t="inlineStr">
         <is>
           <t>F-H3, F-H4</t>
         </is>
       </c>
-      <c r="G90" s="6" t="inlineStr">
+      <c r="G91" s="6" t="inlineStr">
         <is>
           <t>Một dòng của hóa đơn: một phiên sạc hoặc một kỳ thuê bao.</t>
         </is>
       </c>
-      <c r="H90" s="6" t="n">
+      <c r="H91" s="6" t="n">
         <v>9</v>
       </c>
-      <c r="I90" s="7" t="inlineStr">
+      <c r="I91" s="7" t="inlineStr">
         <is>
           <t>→ Mở</t>
         </is>
       </c>
     </row>
-    <row r="91" ht="54" customHeight="1">
-      <c r="A91" s="6" t="inlineStr">
+    <row r="92" ht="54" customHeight="1">
+      <c r="A92" s="6" t="inlineStr">
         <is>
           <t>56</t>
         </is>
       </c>
-      <c r="B91" s="6" t="inlineStr">
+      <c r="B92" s="6" t="inlineStr">
         <is>
           <t>Thanh toán &amp; hóa đơn (billing)</t>
         </is>
       </c>
-      <c r="C91" s="7" t="inlineStr">
+      <c r="C92" s="7" t="inlineStr">
         <is>
           <t>subscription_plans</t>
         </is>
       </c>
-      <c r="D91" s="7" t="inlineStr">
+      <c r="D92" s="7" t="inlineStr">
         <is>
           <t>Gói dịch vụ</t>
         </is>
       </c>
-      <c r="E91" s="6" t="inlineStr">
+      <c r="E92" s="6" t="inlineStr">
         <is>
           <t>Nội bộ</t>
         </is>
       </c>
-      <c r="F91" s="6" t="inlineStr">
+      <c r="F92" s="6" t="inlineStr">
         <is>
           <t>F-H4</t>
         </is>
       </c>
-      <c r="G91" s="6" t="inlineStr">
+      <c r="G92" s="6" t="inlineStr">
         <is>
           <t>Một gói dịch vụ: mỗi gói là một dòng (GUEST là gói mặc định miễn phí, STANDARD, ADVANCED, PRO, ..., hoặc gói riêng cho một khách hàng); tính năng của gói nằm ở plan_features. Giá được tính theo từng tính năng (xem ghi chú của miền thanh toán).</t>
         </is>
       </c>
-      <c r="H91" s="6" t="n">
+      <c r="H92" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="I91" s="7" t="inlineStr">
+      <c r="I92" s="7" t="inlineStr">
         <is>
           <t>→ Mở</t>
         </is>
       </c>
     </row>
-    <row r="92" ht="40.5" customHeight="1">
-      <c r="A92" s="6" t="inlineStr">
+    <row r="93" ht="40.5" customHeight="1">
+      <c r="A93" s="6" t="inlineStr">
         <is>
           <t>57</t>
         </is>
       </c>
-      <c r="B92" s="6" t="inlineStr">
+      <c r="B93" s="6" t="inlineStr">
         <is>
           <t>Thanh toán &amp; hóa đơn (billing)</t>
         </is>
       </c>
-      <c r="C92" s="7" t="inlineStr">
+      <c r="C93" s="7" t="inlineStr">
         <is>
           <t>plan_features</t>
         </is>
       </c>
-      <c r="D92" s="7" t="inlineStr">
+      <c r="D93" s="7" t="inlineStr">
         <is>
           <t>Tính năng của gói dịch vụ</t>
         </is>
       </c>
-      <c r="E92" s="6" t="inlineStr">
+      <c r="E93" s="6" t="inlineStr">
         <is>
           <t>Nội bộ</t>
         </is>
       </c>
-      <c r="F92" s="6" t="inlineStr">
+      <c r="F93" s="6" t="inlineStr">
         <is>
           <t>F-H4</t>
         </is>
       </c>
-      <c r="G92" s="6" t="inlineStr">
+      <c r="G93" s="6" t="inlineStr">
         <is>
           <t>Mỗi gói dịch vụ gồm những tính năng nào. Gói dịch vụ là dữ liệu, nên G3 có thể tạo gói mới (Pro, Max, gói riêng cho một khách hàng) trên portal mà không cần lập trình viên; chỉ tính năng hoàn toàn mới mới cần viết mã.</t>
         </is>
       </c>
-      <c r="H92" s="6" t="n">
+      <c r="H93" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="I92" s="7" t="inlineStr">
+      <c r="I93" s="7" t="inlineStr">
         <is>
           <t>→ Mở</t>
         </is>
       </c>
     </row>
-    <row r="93" ht="27" customHeight="1">
-      <c r="A93" s="6" t="inlineStr">
+    <row r="94" ht="27" customHeight="1">
+      <c r="A94" s="6" t="inlineStr">
         <is>
           <t>58</t>
         </is>
       </c>
-      <c r="B93" s="6" t="inlineStr">
+      <c r="B94" s="6" t="inlineStr">
         <is>
           <t>Thanh toán &amp; hóa đơn (billing)</t>
         </is>
       </c>
-      <c r="C93" s="7" t="inlineStr">
+      <c r="C94" s="7" t="inlineStr">
         <is>
           <t>subscriptions</t>
         </is>
       </c>
-      <c r="D93" s="7" t="inlineStr">
+      <c r="D94" s="7" t="inlineStr">
         <is>
           <t>Thuê bao</t>
         </is>
       </c>
-      <c r="E93" s="6" t="inlineStr">
+      <c r="E94" s="6" t="inlineStr">
         <is>
           <t>Khách hàng</t>
         </is>
       </c>
-      <c r="F93" s="6" t="inlineStr">
+      <c r="F94" s="6" t="inlineStr">
         <is>
           <t>F-H4</t>
         </is>
       </c>
-      <c r="G93" s="6" t="inlineStr">
+      <c r="G94" s="6" t="inlineStr">
         <is>
           <t>Một xe đăng ký một gói; quá hạn thanh toán sẽ khóa tính năng.</t>
         </is>
       </c>
-      <c r="H93" s="6" t="n">
+      <c r="H94" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="I93" s="7" t="inlineStr">
+      <c r="I94" s="7" t="inlineStr">
         <is>
           <t>→ Mở</t>
         </is>
       </c>
     </row>
-    <row r="94" ht="27" customHeight="1">
-      <c r="A94" s="5" t="n"/>
-      <c r="B94" s="5" t="inlineStr">
+    <row r="95" ht="27" customHeight="1">
+      <c r="A95" s="5" t="n"/>
+      <c r="B95" s="5" t="inlineStr">
         <is>
           <t>Chấm điểm tài xế (scoring)</t>
         </is>
       </c>
-      <c r="C94" s="5" t="inlineStr">
+      <c r="C95" s="5" t="inlineStr">
         <is>
           <t>1 bảng</t>
         </is>
       </c>
-      <c r="D94" s="5" t="n"/>
-      <c r="E94" s="5" t="n"/>
-      <c r="F94" s="5" t="n"/>
-      <c r="G94" s="5" t="inlineStr">
+      <c r="D95" s="5" t="n"/>
+      <c r="E95" s="5" t="n"/>
+      <c r="F95" s="5" t="n"/>
+      <c r="G95" s="5" t="inlineStr">
         <is>
           <t>Chấm điểm an toàn cho tài xế từ hành vi lái xe.
 • Mỗi tuần, mỗi tài xế có một điểm, tính từ dữ liệu vận hành của xe họ lái.</t>
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" s="6" t="inlineStr">
+    <row r="96">
+      <c r="A96" s="6" t="inlineStr">
         <is>
           <t>59</t>
         </is>
       </c>
-      <c r="B95" s="6" t="inlineStr">
+      <c r="B96" s="6" t="inlineStr">
         <is>
           <t>Chấm điểm tài xế (scoring)</t>
         </is>
       </c>
-      <c r="C95" s="7" t="inlineStr">
+      <c r="C96" s="7" t="inlineStr">
         <is>
           <t>driver_scores</t>
         </is>
       </c>
-      <c r="D95" s="7" t="inlineStr">
+      <c r="D96" s="7" t="inlineStr">
         <is>
           <t>Điểm tài xế</t>
         </is>
       </c>
-      <c r="E95" s="6" t="inlineStr">
+      <c r="E96" s="6" t="inlineStr">
         <is>
           <t>Khách hàng</t>
         </is>
       </c>
-      <c r="F95" s="6" t="inlineStr">
+      <c r="F96" s="6" t="inlineStr">
         <is>
           <t>F-K1</t>
         </is>
       </c>
-      <c r="G95" s="6" t="inlineStr">
+      <c r="G96" s="6" t="inlineStr">
         <is>
           <t>Điểm an toàn hằng tuần của tài xế, tính từ dữ liệu vận hành xe.</t>
         </is>
       </c>
-      <c r="H95" s="6" t="n">
+      <c r="H96" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="I95" s="7" t="inlineStr">
+      <c r="I96" s="7" t="inlineStr">
         <is>
           <t>→ Mở</t>
         </is>
       </c>
     </row>
-    <row r="96" ht="27" customHeight="1">
-      <c r="A96" s="5" t="n"/>
-      <c r="B96" s="5" t="inlineStr">
+    <row r="97" ht="27" customHeight="1">
+      <c r="A97" s="5" t="n"/>
+      <c r="B97" s="5" t="inlineStr">
         <is>
           <t>Chưa phân miền (unassigned)</t>
         </is>
       </c>
-      <c r="C96" s="5" t="inlineStr">
+      <c r="C97" s="5" t="inlineStr">
         <is>
           <t>2 bảng</t>
         </is>
       </c>
-      <c r="D96" s="5" t="n"/>
-      <c r="E96" s="5" t="n"/>
-      <c r="F96" s="5" t="n"/>
-      <c r="G96" s="5" t="inlineStr">
+      <c r="D97" s="5" t="n"/>
+      <c r="E97" s="5" t="n"/>
+      <c r="F97" s="5" t="n"/>
+      <c r="G97" s="5" t="inlineStr">
         <is>
           <t>Các tính năng chưa được quyết định thuộc miền nghiệp vụ nào (xem feature-list.md).</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="6" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="B97" s="6" t="inlineStr">
-        <is>
-          <t>Chưa phân miền (unassigned)</t>
-        </is>
-      </c>
-      <c r="C97" s="7" t="inlineStr">
-        <is>
-          <t>promotion_campaigns</t>
-        </is>
-      </c>
-      <c r="D97" s="7" t="inlineStr">
-        <is>
-          <t>Chiến dịch khuyến mãi</t>
-        </is>
-      </c>
-      <c r="E97" s="6" t="inlineStr">
-        <is>
-          <t>Nội bộ</t>
-        </is>
-      </c>
-      <c r="F97" s="6" t="inlineStr">
-        <is>
-          <t>F-F4</t>
-        </is>
-      </c>
-      <c r="G97" s="6" t="inlineStr">
-        <is>
-          <t>Một chiến dịch nhắc bảo dưỡng hoặc khuyến mãi.</t>
-        </is>
-      </c>
-      <c r="H97" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="I97" s="7" t="inlineStr">
-        <is>
-          <t>→ Mở</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="6" t="inlineStr">
         <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="B98" s="6" t="inlineStr">
+        <is>
+          <t>Chưa phân miền (unassigned)</t>
+        </is>
+      </c>
+      <c r="C98" s="7" t="inlineStr">
+        <is>
+          <t>promotion_campaigns</t>
+        </is>
+      </c>
+      <c r="D98" s="7" t="inlineStr">
+        <is>
+          <t>Chiến dịch khuyến mãi</t>
+        </is>
+      </c>
+      <c r="E98" s="6" t="inlineStr">
+        <is>
+          <t>Nội bộ</t>
+        </is>
+      </c>
+      <c r="F98" s="6" t="inlineStr">
+        <is>
+          <t>F-F4</t>
+        </is>
+      </c>
+      <c r="G98" s="6" t="inlineStr">
+        <is>
+          <t>Một chiến dịch nhắc bảo dưỡng hoặc khuyến mãi.</t>
+        </is>
+      </c>
+      <c r="H98" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="I98" s="7" t="inlineStr">
+        <is>
+          <t>→ Mở</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="6" t="inlineStr">
+        <is>
           <t>61</t>
         </is>
       </c>
-      <c r="B98" s="6" t="inlineStr">
+      <c r="B99" s="6" t="inlineStr">
         <is>
           <t>Chưa phân miền (unassigned)</t>
         </is>
       </c>
-      <c r="C98" s="7" t="inlineStr">
+      <c r="C99" s="7" t="inlineStr">
         <is>
           <t>trips</t>
         </is>
       </c>
-      <c r="D98" s="7" t="inlineStr">
+      <c r="D99" s="7" t="inlineStr">
         <is>
           <t>Chuyến đi</t>
         </is>
       </c>
-      <c r="E98" s="6" t="inlineStr">
+      <c r="E99" s="6" t="inlineStr">
         <is>
           <t>Khách hàng</t>
         </is>
       </c>
-      <c r="F98" s="6" t="inlineStr">
+      <c r="F99" s="6" t="inlineStr">
         <is>
           <t>F-A9</t>
         </is>
       </c>
-      <c r="G98" s="6" t="inlineStr">
+      <c r="G99" s="6" t="inlineStr">
         <is>
           <t>Một chuyến đi của xe. F-A9 đang tạm dừng: chưa có khái niệm chuyến đi.</t>
         </is>
       </c>
-      <c r="H98" s="6" t="n">
+      <c r="H99" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="I98" s="7" t="inlineStr">
+      <c r="I99" s="7" t="inlineStr">
         <is>
           <t>→ Mở</t>
         </is>
       </c>
     </row>
-    <row r="99"/>
-    <row r="100" ht="27" customHeight="1">
-      <c r="A100" s="4" t="inlineStr">
+    <row r="100"/>
+    <row r="101" ht="27" customHeight="1">
+      <c r="A101" s="4" t="inlineStr">
         <is>
           <t>Chú giải</t>
         </is>
       </c>
-      <c r="B100" s="4" t="inlineStr">
+      <c r="B101" s="4" t="inlineStr">
         <is>
           <t>Ý nghĩa</t>
         </is>
       </c>
     </row>
-    <row r="101" ht="108" customHeight="1">
-      <c r="A101" s="6" t="inlineStr">
+    <row r="102" ht="108" customHeight="1">
+      <c r="A102" s="6" t="inlineStr">
         <is>
           <t>Chủ sở hữu dữ liệu: Khách hàng</t>
         </is>
       </c>
-      <c r="B101" s="6" t="inlineStr">
+      <c r="B102" s="6" t="inlineStr">
         <is>
           <t>Thuộc về một tổ chức (thường là khách hàng; công ty G3 cũng có thể sở hữu); có cột organization_id hoặc lấy qua bảng cha (DM-24).</t>
-        </is>
-      </c>
-    </row>
-    <row r="102" ht="94.5" customHeight="1">
-      <c r="A102" s="6" t="inlineStr">
-        <is>
-          <t>Chủ sở hữu dữ liệu: Nội bộ</t>
-        </is>
-      </c>
-      <c r="B102" s="6" t="inlineStr">
-        <is>
-          <t>Dữ liệu của chính chúng ta (đơn vị vận hành nền tảng), dùng chung cho mọi tổ chức.</t>
         </is>
       </c>
     </row>
     <row r="103" ht="94.5" customHeight="1">
       <c r="A103" s="6" t="inlineStr">
         <is>
+          <t>Chủ sở hữu dữ liệu: Nội bộ</t>
+        </is>
+      </c>
+      <c r="B103" s="6" t="inlineStr">
+        <is>
+          <t>Dữ liệu của chính chúng ta (đơn vị vận hành nền tảng), dùng chung cho mọi tổ chức.</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="94.5" customHeight="1">
+      <c r="A104" s="6" t="inlineStr">
+        <is>
           <t>Chủ sở hữu dữ liệu: Hai bên</t>
         </is>
       </c>
-      <c r="B103" s="6" t="inlineStr">
+      <c r="B104" s="6" t="inlineStr">
         <is>
           <t>Tài sản của G3 được khách hàng sử dụng; cả hai bên cùng liên quan.</t>
         </is>
       </c>
     </row>
-    <row r="104" ht="121.5" customHeight="1">
-      <c r="A104" s="6" t="inlineStr">
+    <row r="105" ht="121.5" customHeight="1">
+      <c r="A105" s="6" t="inlineStr">
         <is>
           <t>Chủ sở hữu dữ liệu: Chưa quyết định</t>
         </is>
       </c>
-      <c r="B104" s="6" t="inlineStr">
+      <c r="B105" s="6" t="inlineStr">
         <is>
           <t>Đang chờ một quyết định còn mở (xem cuối trang).</t>
         </is>
       </c>
     </row>
-    <row r="105" ht="81" customHeight="1">
-      <c r="A105" s="6" t="inlineStr">
+    <row r="106" ht="81" customHeight="1">
+      <c r="A106" s="6" t="inlineStr">
         <is>
           <t>Miền nghiệp vụ (domain)</t>
         </is>
       </c>
-      <c r="B105" s="6" t="inlineStr">
+      <c r="B106" s="6" t="inlineStr">
         <is>
           <t>Một phần của hệ thống sở hữu dữ liệu riêng, ví dụ Xe, Trạm sạc, Thanh toán. Mỗi miền gồm một hoặc nhiều bảng.</t>
         </is>
       </c>
     </row>
-    <row r="106" ht="54" customHeight="1">
-      <c r="A106" s="6" t="inlineStr">
+    <row r="107" ht="54" customHeight="1">
+      <c r="A107" s="6" t="inlineStr">
         <is>
           <t>Bảng</t>
         </is>
       </c>
-      <c r="B106" s="6" t="inlineStr">
+      <c r="B107" s="6" t="inlineStr">
         <is>
           <t>Một loại dữ liệu được lưu, ví dụ Xe hoặc Phiên sạc. Mỗi bảng có một sheet riêng liệt kê từng cột.</t>
         </is>
       </c>
     </row>
-    <row r="107" ht="40.5" customHeight="1">
-      <c r="A107" s="6" t="inlineStr">
+    <row r="108" ht="40.5" customHeight="1">
+      <c r="A108" s="6" t="inlineStr">
         <is>
           <t>Tính năng</t>
         </is>
       </c>
-      <c r="B107" s="6" t="inlineStr">
+      <c r="B108" s="6" t="inlineStr">
         <is>
           <t>Mã tính năng trong danh sách tính năng (feature-list.md), ví dụ F-B2.</t>
         </is>
       </c>
     </row>
-    <row r="108" ht="67.5" customHeight="1">
-      <c r="A108" s="6" t="inlineStr">
+    <row r="109" ht="67.5" customHeight="1">
+      <c r="A109" s="6" t="inlineStr">
         <is>
           <t>PK / FK / UQ</t>
         </is>
       </c>
-      <c r="B108" s="6" t="inlineStr">
+      <c r="B109" s="6" t="inlineStr">
         <is>
           <t>PK: khóa chính (định danh duy nhất của dòng). FK: khóa ngoại (trỏ tới dòng của bảng khác). UQ: giá trị không được trùng.</t>
         </is>
       </c>
     </row>
-    <row r="109" ht="54" customHeight="1">
-      <c r="A109" s="6" t="inlineStr">
+    <row r="110" ht="54" customHeight="1">
+      <c r="A110" s="6" t="inlineStr">
         <is>
           <t>Ví dụ</t>
         </is>
       </c>
-      <c r="B109" s="6" t="inlineStr">
+      <c r="B110" s="6" t="inlineStr">
         <is>
           <t>Giá trị mẫu. Các mã ví dụ khớp nhau giữa các bảng, nên có thể lần theo một bản ghi mẫu qua nhiều sheet.</t>
         </is>
       </c>
     </row>
-    <row r="110" ht="40.5" customHeight="1">
-      <c r="A110" s="6" t="inlineStr">
+    <row r="111" ht="40.5" customHeight="1">
+      <c r="A111" s="6" t="inlineStr">
         <is>
           <t>NULL</t>
         </is>
       </c>
-      <c r="B110" s="6" t="inlineStr">
+      <c r="B111" s="6" t="inlineStr">
         <is>
           <t>Ô không có giá trị. Ý nghĩa của NULL được giải thích trong cột Ý nghĩa.</t>
         </is>
       </c>
     </row>
-    <row r="111" ht="81" customHeight="1">
-      <c r="A111" s="6" t="inlineStr">
+    <row r="112" ht="81" customHeight="1">
+      <c r="A112" s="6" t="inlineStr">
         <is>
           <t>🔍 Lưu lịch sử</t>
         </is>
       </c>
-      <c r="B111" s="6" t="inlineStr">
+      <c r="B112" s="6" t="inlineStr">
         <is>
           <t>Cột được theo dõi: khi cột này thay đổi, toàn bộ dòng cũ được chép sang bảng lịch sử (tên kết thúc bằng _history) kèm thời điểm và người thay đổi.</t>
         </is>
       </c>
     </row>
-    <row r="112"/>
-    <row r="113">
-      <c r="A113" s="8" t="inlineStr">
+    <row r="113"/>
+    <row r="114">
+      <c r="A114" s="8" t="inlineStr">
         <is>
           <t>Các view (giai đoạn đọc từ lịch sử)</t>
         </is>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" s="4" t="inlineStr">
+    <row r="115">
+      <c r="A115" s="4" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="B114" s="4" t="inlineStr">
+      <c r="B115" s="4" t="inlineStr">
         <is>
           <t>Mỗi dòng là</t>
         </is>
       </c>
-      <c r="C114" s="4" t="inlineStr">
+      <c r="C115" s="4" t="inlineStr">
         <is>
           <t>Các cột</t>
         </is>
       </c>
-      <c r="D114" s="4" t="inlineStr">
+      <c r="D115" s="4" t="inlineStr">
         <is>
           <t>Được dùng bởi</t>
-        </is>
-      </c>
-    </row>
-    <row r="115" ht="94.5" customHeight="1">
-      <c r="A115" s="6" t="inlineStr">
-        <is>
-          <t>vehicle_ownership_periods</t>
-        </is>
-      </c>
-      <c r="B115" s="6" t="inlineStr">
-        <is>
-          <t>một giai đoạn xe thuộc một chủ</t>
-        </is>
-      </c>
-      <c r="C115" s="6" t="inlineStr">
-        <is>
-          <t>vehicle_id, organization_id, owned_from, owned_until (NULL với chủ hiện tại)</t>
-        </is>
-      </c>
-      <c r="D115" s="6" t="inlineStr">
-        <is>
-          <t>lịch sử sở hữu và ngày bàn giao đầu tiên (VEH-02), "ngày đó xe của ai"</t>
         </is>
       </c>
     </row>
     <row r="116" ht="94.5" customHeight="1">
       <c r="A116" s="6" t="inlineStr">
         <is>
+          <t>vehicle_ownership_periods</t>
+        </is>
+      </c>
+      <c r="B116" s="6" t="inlineStr">
+        <is>
+          <t>một giai đoạn xe thuộc một chủ</t>
+        </is>
+      </c>
+      <c r="C116" s="6" t="inlineStr">
+        <is>
+          <t>vehicle_id, organization_id, owned_from, owned_until (NULL với chủ hiện tại)</t>
+        </is>
+      </c>
+      <c r="D116" s="6" t="inlineStr">
+        <is>
+          <t>lịch sử sở hữu và ngày bàn giao đầu tiên (VEH-02), "ngày đó xe của ai"</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="94.5" customHeight="1">
+      <c r="A117" s="6" t="inlineStr">
+        <is>
           <t>battery_installation_periods</t>
         </is>
       </c>
-      <c r="B116" s="6" t="inlineStr">
+      <c r="B117" s="6" t="inlineStr">
         <is>
           <t>một lần pin nằm trên một xe</t>
         </is>
       </c>
-      <c r="C116" s="6" t="inlineStr">
+      <c r="C117" s="6" t="inlineStr">
         <is>
           <t>battery_id, vehicle_id, installed_from, installed_until (NULL khi đang lắp)</t>
         </is>
       </c>
-      <c r="D116" s="6" t="inlineStr">
+      <c r="D117" s="6" t="inlineStr">
         <is>
           <t>lịch sử sức khỏe pin qua các xe (MON-07), bộ đếm bảo hành pin (WAR-01)</t>
         </is>
       </c>
     </row>
-    <row r="117"/>
-    <row r="118">
-      <c r="A118" s="8" t="inlineStr">
+    <row r="118"/>
+    <row r="119">
+      <c r="A119" s="8" t="inlineStr">
         <is>
           <t>Các quyết định còn mở</t>
         </is>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" s="4" t="inlineStr">
+    <row r="120">
+      <c r="A120" s="4" t="inlineStr">
         <is>
           <t>Mã</t>
         </is>
       </c>
-      <c r="B119" s="4" t="inlineStr">
+      <c r="B120" s="4" t="inlineStr">
         <is>
           <t>Câu hỏi</t>
         </is>
       </c>
-      <c r="C119" s="4" t="inlineStr">
+      <c r="C120" s="4" t="inlineStr">
         <is>
           <t>Ảnh hưởng tới</t>
         </is>
       </c>
     </row>
-    <row r="120" ht="54" customHeight="1">
-      <c r="A120" s="6" t="inlineStr">
+    <row r="121" ht="54" customHeight="1">
+      <c r="A121" s="6" t="inlineStr">
         <is>
           <t>D5</t>
         </is>
       </c>
-      <c r="B120" s="6" t="inlineStr">
+      <c r="B121" s="6" t="inlineStr">
         <is>
           <t>Ai trả tiền khi tài xế của đội xe sạc: ví của tài xế, ví của đội xe, hay tùy trường hợp?</t>
         </is>
       </c>
-      <c r="C120" s="6" t="inlineStr">
+      <c r="C121" s="6" t="inlineStr">
         <is>
           <t>wallets, payments</t>
         </is>
@@ -5041,39 +5088,42 @@
     <hyperlink ref="C85" location="'tariffs'!A1"/>
     <hyperlink ref="D85" location="'tariffs'!A1"/>
     <hyperlink ref="I85" location="'tariffs'!A1"/>
-    <hyperlink ref="C86" location="'payments'!A1"/>
-    <hyperlink ref="D86" location="'payments'!A1"/>
-    <hyperlink ref="I86" location="'payments'!A1"/>
-    <hyperlink ref="C87" location="'wallets'!A1"/>
-    <hyperlink ref="D87" location="'wallets'!A1"/>
-    <hyperlink ref="I87" location="'wallets'!A1"/>
-    <hyperlink ref="C88" location="'wallet_transactions'!A1"/>
-    <hyperlink ref="D88" location="'wallet_transactions'!A1"/>
-    <hyperlink ref="I88" location="'wallet_transactions'!A1"/>
-    <hyperlink ref="C89" location="'invoices'!A1"/>
-    <hyperlink ref="D89" location="'invoices'!A1"/>
-    <hyperlink ref="I89" location="'invoices'!A1"/>
-    <hyperlink ref="C90" location="'invoice_lines'!A1"/>
-    <hyperlink ref="D90" location="'invoice_lines'!A1"/>
-    <hyperlink ref="I90" location="'invoice_lines'!A1"/>
-    <hyperlink ref="C91" location="'subscription_plans'!A1"/>
-    <hyperlink ref="D91" location="'subscription_plans'!A1"/>
-    <hyperlink ref="I91" location="'subscription_plans'!A1"/>
-    <hyperlink ref="C92" location="'plan_features'!A1"/>
-    <hyperlink ref="D92" location="'plan_features'!A1"/>
-    <hyperlink ref="I92" location="'plan_features'!A1"/>
-    <hyperlink ref="C93" location="'subscriptions'!A1"/>
-    <hyperlink ref="D93" location="'subscriptions'!A1"/>
-    <hyperlink ref="I93" location="'subscriptions'!A1"/>
-    <hyperlink ref="C95" location="'driver_scores'!A1"/>
-    <hyperlink ref="D95" location="'driver_scores'!A1"/>
-    <hyperlink ref="I95" location="'driver_scores'!A1"/>
-    <hyperlink ref="C97" location="'promotion_campaigns'!A1"/>
-    <hyperlink ref="D97" location="'promotion_campaigns'!A1"/>
-    <hyperlink ref="I97" location="'promotion_campaigns'!A1"/>
-    <hyperlink ref="C98" location="'trips'!A1"/>
-    <hyperlink ref="D98" location="'trips'!A1"/>
-    <hyperlink ref="I98" location="'trips'!A1"/>
+    <hyperlink ref="C86" location="'tariff_history'!A1"/>
+    <hyperlink ref="D86" location="'tariff_history'!A1"/>
+    <hyperlink ref="I86" location="'tariff_history'!A1"/>
+    <hyperlink ref="C87" location="'payments'!A1"/>
+    <hyperlink ref="D87" location="'payments'!A1"/>
+    <hyperlink ref="I87" location="'payments'!A1"/>
+    <hyperlink ref="C88" location="'wallets'!A1"/>
+    <hyperlink ref="D88" location="'wallets'!A1"/>
+    <hyperlink ref="I88" location="'wallets'!A1"/>
+    <hyperlink ref="C89" location="'wallet_transactions'!A1"/>
+    <hyperlink ref="D89" location="'wallet_transactions'!A1"/>
+    <hyperlink ref="I89" location="'wallet_transactions'!A1"/>
+    <hyperlink ref="C90" location="'invoices'!A1"/>
+    <hyperlink ref="D90" location="'invoices'!A1"/>
+    <hyperlink ref="I90" location="'invoices'!A1"/>
+    <hyperlink ref="C91" location="'invoice_lines'!A1"/>
+    <hyperlink ref="D91" location="'invoice_lines'!A1"/>
+    <hyperlink ref="I91" location="'invoice_lines'!A1"/>
+    <hyperlink ref="C92" location="'subscription_plans'!A1"/>
+    <hyperlink ref="D92" location="'subscription_plans'!A1"/>
+    <hyperlink ref="I92" location="'subscription_plans'!A1"/>
+    <hyperlink ref="C93" location="'plan_features'!A1"/>
+    <hyperlink ref="D93" location="'plan_features'!A1"/>
+    <hyperlink ref="I93" location="'plan_features'!A1"/>
+    <hyperlink ref="C94" location="'subscriptions'!A1"/>
+    <hyperlink ref="D94" location="'subscriptions'!A1"/>
+    <hyperlink ref="I94" location="'subscriptions'!A1"/>
+    <hyperlink ref="C96" location="'driver_scores'!A1"/>
+    <hyperlink ref="D96" location="'driver_scores'!A1"/>
+    <hyperlink ref="I96" location="'driver_scores'!A1"/>
+    <hyperlink ref="C98" location="'promotion_campaigns'!A1"/>
+    <hyperlink ref="D98" location="'promotion_campaigns'!A1"/>
+    <hyperlink ref="I98" location="'promotion_campaigns'!A1"/>
+    <hyperlink ref="C99" location="'trips'!A1"/>
+    <hyperlink ref="D99" location="'trips'!A1"/>
+    <hyperlink ref="I99" location="'trips'!A1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10584,7 +10634,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I58"/>
+  <dimension ref="A1:I59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -11549,7 +11599,7 @@
       <c r="A50" s="6" t="n"/>
       <c r="B50" s="7" t="inlineStr">
         <is>
-          <t>payments</t>
+          <t>tariffs</t>
         </is>
       </c>
       <c r="C50" s="6" t="inlineStr">
@@ -11562,7 +11612,7 @@
       <c r="A51" s="6" t="n"/>
       <c r="B51" s="7" t="inlineStr">
         <is>
-          <t>wallets</t>
+          <t>payments</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
@@ -11575,7 +11625,7 @@
       <c r="A52" s="6" t="n"/>
       <c r="B52" s="7" t="inlineStr">
         <is>
-          <t>wallet_transactions</t>
+          <t>wallets</t>
         </is>
       </c>
       <c r="C52" s="6" t="inlineStr">
@@ -11588,7 +11638,7 @@
       <c r="A53" s="6" t="n"/>
       <c r="B53" s="7" t="inlineStr">
         <is>
-          <t>invoices</t>
+          <t>wallet_transactions</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
@@ -11601,7 +11651,7 @@
       <c r="A54" s="6" t="n"/>
       <c r="B54" s="7" t="inlineStr">
         <is>
-          <t>invoice_lines</t>
+          <t>invoices</t>
         </is>
       </c>
       <c r="C54" s="6" t="inlineStr">
@@ -11614,7 +11664,7 @@
       <c r="A55" s="6" t="n"/>
       <c r="B55" s="7" t="inlineStr">
         <is>
-          <t>subscriptions</t>
+          <t>invoice_lines</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
@@ -11627,7 +11677,7 @@
       <c r="A56" s="6" t="n"/>
       <c r="B56" s="7" t="inlineStr">
         <is>
-          <t>driver_scores</t>
+          <t>subscriptions</t>
         </is>
       </c>
       <c r="C56" s="6" t="inlineStr">
@@ -11640,7 +11690,7 @@
       <c r="A57" s="6" t="n"/>
       <c r="B57" s="7" t="inlineStr">
         <is>
-          <t>trips</t>
+          <t>driver_scores</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
@@ -11653,10 +11703,23 @@
       <c r="A58" s="6" t="n"/>
       <c r="B58" s="7" t="inlineStr">
         <is>
+          <t>trips</t>
+        </is>
+      </c>
+      <c r="C58" s="6" t="inlineStr">
+        <is>
+          <t>organization_id</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="6" t="n"/>
+      <c r="B59" s="7" t="inlineStr">
+        <is>
           <t>organization_history</t>
         </is>
       </c>
-      <c r="C58" s="6" t="inlineStr">
+      <c r="C59" s="6" t="inlineStr">
         <is>
           <t>organization_id</t>
         </is>
@@ -11692,15 +11755,16 @@
     <hyperlink ref="B47" location="'maintenance_bookings'!A1"/>
     <hyperlink ref="B48" location="'charging_policy_assignments'!A1"/>
     <hyperlink ref="B49" location="'policy_violations'!A1"/>
-    <hyperlink ref="B50" location="'payments'!A1"/>
-    <hyperlink ref="B51" location="'wallets'!A1"/>
-    <hyperlink ref="B52" location="'wallet_transactions'!A1"/>
-    <hyperlink ref="B53" location="'invoices'!A1"/>
-    <hyperlink ref="B54" location="'invoice_lines'!A1"/>
-    <hyperlink ref="B55" location="'subscriptions'!A1"/>
-    <hyperlink ref="B56" location="'driver_scores'!A1"/>
-    <hyperlink ref="B57" location="'trips'!A1"/>
-    <hyperlink ref="B58" location="'organization_history'!A1"/>
+    <hyperlink ref="B50" location="'tariffs'!A1"/>
+    <hyperlink ref="B51" location="'payments'!A1"/>
+    <hyperlink ref="B52" location="'wallets'!A1"/>
+    <hyperlink ref="B53" location="'wallet_transactions'!A1"/>
+    <hyperlink ref="B54" location="'invoices'!A1"/>
+    <hyperlink ref="B55" location="'invoice_lines'!A1"/>
+    <hyperlink ref="B56" location="'subscriptions'!A1"/>
+    <hyperlink ref="B57" location="'driver_scores'!A1"/>
+    <hyperlink ref="B58" location="'trips'!A1"/>
+    <hyperlink ref="B59" location="'organization_history'!A1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -26052,7 +26116,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I64"/>
+  <dimension ref="A1:I65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -27136,6 +27200,19 @@
         </is>
       </c>
       <c r="C64" s="6" t="inlineStr">
+        <is>
+          <t>changed_by</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="6" t="n"/>
+      <c r="B65" s="7" t="inlineStr">
+        <is>
+          <t>tariff_history</t>
+        </is>
+      </c>
+      <c r="C65" s="6" t="inlineStr">
         <is>
           <t>changed_by</t>
         </is>
@@ -27188,6 +27265,7 @@
     <hyperlink ref="B62" location="'charging_station_history'!A1"/>
     <hyperlink ref="B63" location="'charging_evse_history'!A1"/>
     <hyperlink ref="B64" location="'charging_connector_history'!A1"/>
+    <hyperlink ref="B65" location="'tariff_history'!A1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -27624,7 +27702,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I27"/>
+  <dimension ref="A1:I28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -28245,14 +28323,27 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="27" customHeight="1">
+    <row r="27">
       <c r="A27" s="6" t="n"/>
       <c r="B27" s="7" t="inlineStr">
         <is>
+          <t>tariffs</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>location_id</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="27" customHeight="1">
+      <c r="A28" s="6" t="n"/>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
           <t>charging_location_history</t>
         </is>
       </c>
-      <c r="C27" s="6" t="inlineStr">
+      <c r="C28" s="6" t="inlineStr">
         <is>
           <t>location_id</t>
         </is>
@@ -28266,7 +28357,8 @@
     <hyperlink ref="F9" location="'organizations'!A1"/>
     <hyperlink ref="B25" location="'charging_location_access'!A1"/>
     <hyperlink ref="B26" location="'charging_stations'!A1"/>
-    <hyperlink ref="B27" location="'charging_location_history'!A1"/>
+    <hyperlink ref="B27" location="'tariffs'!A1"/>
+    <hyperlink ref="B28" location="'charging_location_history'!A1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -29468,7 +29560,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I56"/>
+  <dimension ref="A1:I55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -30785,23 +30877,10 @@
       <c r="A55" s="6" t="n"/>
       <c r="B55" s="7" t="inlineStr">
         <is>
-          <t>tariffs</t>
+          <t>charging_station_history</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
-        <is>
-          <t>station_id</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="6" t="n"/>
-      <c r="B56" s="7" t="inlineStr">
-        <is>
-          <t>charging_station_history</t>
-        </is>
-      </c>
-      <c r="C56" s="6" t="inlineStr">
         <is>
           <t>station_id</t>
         </is>
@@ -30821,8 +30900,7 @@
     <hyperlink ref="B52" location="'charging_station_config_entries'!A1"/>
     <hyperlink ref="B53" location="'charging_station_commands'!A1"/>
     <hyperlink ref="B54" location="'charging_sessions'!A1"/>
-    <hyperlink ref="B55" location="'tariffs'!A1"/>
-    <hyperlink ref="B56" location="'charging_station_history'!A1"/>
+    <hyperlink ref="B55" location="'charging_station_history'!A1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -44328,7 +44406,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -44345,7 +44423,7 @@
     <row r="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>50. tariffs: Biểu giá điện</t>
+          <t>50. tariffs: Biểu giá</t>
         </is>
       </c>
     </row>
@@ -44359,114 +44437,84 @@
     <row r="3">
       <c r="A3" s="11" t="inlineStr">
         <is>
-          <t>Miền nghiệp vụ: Thanh toán &amp; hóa đơn (billing)   ·   Chủ sở hữu dữ liệu: Nội bộ   ·   Tính năng: F-C8, F-H1</t>
+          <t>Miền nghiệp vụ: Thanh toán &amp; hóa đơn (billing)   ·   Chủ sở hữu dữ liệu: Khách hàng   ·   Tính năng: F-C8, F-H1</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="11" t="inlineStr">
         <is>
-          <t>Giá điện. Ai sở hữu biểu giá (G3 Energy hay G3 Network) là mục 5 của feature-list.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5"/>
-    <row r="6" ht="27" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
+          <t>Giá của ai và áp dụng ở đâu (BL-08); giá cụ thể là các phiên bản không sửa được trong tariff_versions, nên biên nhận luôn hiện đúng giá đã tính. Giá tại một trạm là biểu giá ACTIVE của chính trạm đó, nếu không có thì là biểu giá mặc định của chủ sở hữu. Bật lịch sử thay đổi; không xóa mềm. Sau này: giá riêng theo hợp đồng của một khách hàng, và giá khác nhau theo từng trụ trong cùng một trạm.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>🔍 Lưu lịch sử: khi một cột có dấu 🔍 thay đổi, toàn bộ dòng cũ được chép sang bảng tariff_history.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6"/>
+    <row r="7" ht="27" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>Cột</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>Kiểu dữ liệu</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>Cho phép rỗng</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>Khóa</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>Tham chiếu tới</t>
         </is>
       </c>
-      <c r="G6" s="4" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>Ý nghĩa</t>
         </is>
       </c>
-      <c r="H6" s="4" t="inlineStr">
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>Ví dụ</t>
         </is>
       </c>
-      <c r="I6" s="4" t="inlineStr">
+      <c r="I7" s="4" t="inlineStr">
         <is>
           <t>Lưu lịch sử</t>
         </is>
       </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>tariff_id</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>uuid</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
-      <c r="F7" s="6" t="n"/>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>Mã nội bộ của biểu giá.</t>
-        </is>
-      </c>
-      <c r="H7" s="6" t="inlineStr">
-        <is>
-          <t>f2b9e6c3-1d8a-4f5b-a3c7-9e0d4b1f8a10</t>
-        </is>
-      </c>
-      <c r="I7" s="6" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>tariff_code</t>
+          <t>tariff_id</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>varchar(50)</t>
+          <t>uuid</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
@@ -44474,106 +44522,126 @@
           <t>không</t>
         </is>
       </c>
-      <c r="E8" s="6" t="n"/>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
       <c r="F8" s="6" t="n"/>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>Mã biểu giá in trên biên nhận.</t>
+          <t>Mã nội bộ của biểu giá.</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
-          <t>TOU-2026-Q4</t>
+          <t>f2b9e6c3-1d8a-4f5b-a3c7-9e0d4b1f8a10</t>
         </is>
       </c>
       <c r="I8" s="6" t="n"/>
     </row>
-    <row r="9" ht="27" customHeight="1">
+    <row r="9" ht="67.5" customHeight="1">
       <c r="A9" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>organization_id</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>uuid</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>organizations.organization_id (khi xóa: chặn xóa)</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>Chủ sở hữu: tổ chức có các trạm được định giá bởi biểu giá này (BL-08): tổ chức nội bộ của chúng ta với mạng công cộng, hoặc khách hàng với các trụ riêng của mình (CS-10). Tổ chức nội bộ nào sở hữu mạng công cộng (G3 Energy hay G3 Network, PAY-09) là dữ liệu, không phải thiết kế.</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>3f6c2a1e-8b4d-4e2a-9c1f-0a7d5b2e4c11</t>
+        </is>
+      </c>
+      <c r="I9" s="6" t="inlineStr">
+        <is>
+          <t>🔍</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="40.5" customHeight="1">
+      <c r="A10" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>station_id</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>location_id</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
         <is>
           <t>uuid</t>
         </is>
       </c>
-      <c r="D9" s="6" t="inlineStr">
+      <c r="D10" s="6" t="inlineStr">
         <is>
           <t>có</t>
         </is>
       </c>
-      <c r="E9" s="6" t="inlineStr">
+      <c r="E10" s="6" t="inlineStr">
         <is>
           <t>FK</t>
         </is>
       </c>
-      <c r="F9" s="7" t="inlineStr">
-        <is>
-          <t>charging_stations.station_id (khi xóa: chặn xóa)</t>
-        </is>
-      </c>
-      <c r="G9" s="6" t="inlineStr">
-        <is>
-          <t>Trạm áp dụng; NULL nếu áp dụng toàn mạng.</t>
-        </is>
-      </c>
-      <c r="H9" s="6" t="inlineStr">
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>charging_locations.location_id (khi xóa: chặn xóa)</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>Trạm được định giá; NULL là biểu giá mặc định của chủ sở hữu cho mọi trạm của mình. Trạm phải thuộc chủ sở hữu. Tài xế thấy một giá cho mỗi địa điểm.</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
         <is>
           <t>NULL</t>
         </is>
       </c>
-      <c r="I9" s="6" t="n"/>
-    </row>
-    <row r="10" ht="27" customHeight="1">
-      <c r="A10" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>price_per_kwh</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>numeric(12,2)</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E10" s="6" t="n"/>
-      <c r="F10" s="6" t="n"/>
-      <c r="G10" s="6" t="inlineStr">
-        <is>
-          <t>Đơn giá điện cơ bản cho mỗi kWh, theo đơn vị tiền tệ của biểu giá.</t>
-        </is>
-      </c>
-      <c r="H10" s="6" t="inlineStr">
-        <is>
-          <t>4500.00</t>
-        </is>
-      </c>
-      <c r="I10" s="6" t="n"/>
+      <c r="I10" s="6" t="inlineStr">
+        <is>
+          <t>🔍</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>name</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>char(3)</t>
+          <t>varchar(100)</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
@@ -44585,61 +44653,69 @@
       <c r="F11" s="6" t="n"/>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>Mã tiền tệ ISO 4217.</t>
+          <t>Tên hiển thị trên ứng dụng và biên nhận.</t>
         </is>
       </c>
       <c r="H11" s="6" t="inlineStr">
         <is>
-          <t>VND</t>
-        </is>
-      </c>
-      <c r="I11" s="6" t="n"/>
-    </row>
-    <row r="12" ht="27" customHeight="1">
+          <t>Giá chuẩn 2026</t>
+        </is>
+      </c>
+      <c r="I11" s="6" t="inlineStr">
+        <is>
+          <t>🔍</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
       <c r="A12" s="6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>schedule</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>jsonb</t>
+          <t>char(3)</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>có</t>
+          <t>không</t>
         </is>
       </c>
       <c r="E12" s="6" t="n"/>
       <c r="F12" s="6" t="n"/>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>Các khung giờ giá theo thời điểm trong ngày, dạng JSON.</t>
+          <t>Mã tiền tệ ISO 4217.</t>
         </is>
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>[{"from": "22:00", "to": "04:00", "price_per_kwh": 3200}]</t>
-        </is>
-      </c>
-      <c r="I12" s="6" t="n"/>
-    </row>
-    <row r="13">
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="I12" s="6" t="inlineStr">
+        <is>
+          <t>🔍</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="27" customHeight="1">
       <c r="A13" s="6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>valid_from</t>
+          <t>status</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>timestamptz</t>
+          <t>varchar(20)</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
@@ -44651,28 +44727,32 @@
       <c r="F13" s="6" t="n"/>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>Thời điểm biểu giá có hiệu lực.</t>
+          <t>Do chủ sở hữu quyết định. ACTIVE: đang dùng. INACTIVE: đã ngừng.</t>
         </is>
       </c>
       <c r="H13" s="6" t="inlineStr">
         <is>
-          <t>2026-10-01T00:00:00Z</t>
-        </is>
-      </c>
-      <c r="I13" s="6" t="n"/>
-    </row>
-    <row r="14">
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="I13" s="6" t="inlineStr">
+        <is>
+          <t>🔍</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="27" customHeight="1">
       <c r="A14" s="6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>valid_to</t>
+          <t>status_reason</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>timestamptz</t>
+          <t>varchar(200)</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
@@ -44684,7 +44764,7 @@
       <c r="F14" s="6" t="n"/>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>Thời điểm hết hiệu lực; NULL nếu không thời hạn.</t>
+          <t>Lý do biểu giá có trạng thái hiện tại, ví dụ vì sao ngừng dùng (DM-19); NULL nếu không cần giải thích.</t>
         </is>
       </c>
       <c r="H14" s="6" t="inlineStr">
@@ -44692,19 +44772,805 @@
           <t>NULL</t>
         </is>
       </c>
-      <c r="I14" s="6" t="n"/>
+      <c r="I14" s="6" t="inlineStr">
+        <is>
+          <t>🔍</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>created_at</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>timestamptz</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="n"/>
+      <c r="F15" s="6" t="n"/>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>Thời điểm tạo bản ghi (UTC).</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-01T02:00:00Z</t>
+        </is>
+      </c>
+      <c r="I15" s="6" t="inlineStr">
+        <is>
+          <t>🔍</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>updated_at</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>timestamptz</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="n"/>
+      <c r="F16" s="6" t="n"/>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>Thời điểm bản ghi được sửa gần nhất (UTC).</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-10T07:15:00Z</t>
+        </is>
+      </c>
+      <c r="I16" s="6" t="inlineStr">
+        <is>
+          <t>🔍</t>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
+    <row r="18">
+      <c r="A18" s="4" t="n"/>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>Chỉ mục (index)</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>Các cột</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>Duy nhất</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="n"/>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>Ghi chú</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="40.5" customHeight="1">
+      <c r="A19" s="6" t="n"/>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>uq_tariffs_active_owner_location</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>organization_id, location_id</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="n"/>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>WHERE status = ACTIVE, NULLS NOT DISTINCT: one active tariff per location and one default per owner</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="n"/>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>ix_tariffs_location_id</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>location_id</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="n"/>
+      <c r="F20" s="6" t="n"/>
+    </row>
+    <row r="21"/>
+    <row r="22">
+      <c r="A22" s="4" t="n"/>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>Được tham chiếu bởi bảng</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>Cột</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="n"/>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>tariff_history</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>tariff_id</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A6:I14"/>
+  <autoFilter ref="A7:I16"/>
   <hyperlinks>
     <hyperlink ref="A2" location="'Tổng quan'!A1"/>
-    <hyperlink ref="F9" location="'charging_stations'!A1"/>
+    <hyperlink ref="A5" location="'tariff_history'!A1"/>
+    <hyperlink ref="F9" location="'organizations'!A1"/>
+    <hyperlink ref="F10" location="'charging_locations'!A1"/>
+    <hyperlink ref="B23" location="'tariff_history'!A1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet68.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I23"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="7" max="7"/>
+    <col width="42" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>50.h. tariff_history: Lịch sử biểu giá</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t>← Tổng quan</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>Miền nghiệp vụ: Thanh toán &amp; hóa đơn (billing)   ·   Chủ sở hữu dữ liệu: Khách hàng   ·   Tính năng: F-C8, F-H1</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>Mọi phiên bản trước đây của một dòng trong bảng tariffs: bản sao toàn bộ dòng, chụp ngay trước khi thay đổi và được trigger ghi trong cùng giao dịch. Do công cụ domain-model tự sinh từ @tracked *, không bao giờ viết tay.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>Bảng lịch sử của: tariffs</t>
+        </is>
+      </c>
+    </row>
+    <row r="6"/>
+    <row r="7" ht="27" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Cột</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Kiểu dữ liệu</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Cho phép rỗng</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>Khóa</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>Tham chiếu tới</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>Ý nghĩa</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>Ví dụ</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>Lưu lịch sử</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>history_id</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>bigint</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="n"/>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>Mã tự tăng của dòng lịch sử.</t>
+        </is>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>1024</t>
+        </is>
+      </c>
+      <c r="I8" s="6" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>tariff_id</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>uuid</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>tariffs.tariff_id (khi xóa: chặn xóa)</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>Giá trị trước khi thay đổi (tariffs.tariff_id).</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>f2b9e6c3-1d8a-4f5b-a3c7-9e0d4b1f8a10</t>
+        </is>
+      </c>
+      <c r="I9" s="6" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>organization_id</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>uuid</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="n"/>
+      <c r="F10" s="6" t="n"/>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>Giá trị trước khi thay đổi (tariffs.organization_id).</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>3f6c2a1e-8b4d-4e2a-9c1f-0a7d5b2e4c11</t>
+        </is>
+      </c>
+      <c r="I10" s="6" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>location_id</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>uuid</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="n"/>
+      <c r="F11" s="6" t="n"/>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>Giá trị trước khi thay đổi (tariffs.location_id).</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="I11" s="6" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>varchar(100)</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="n"/>
+      <c r="F12" s="6" t="n"/>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>Giá trị trước khi thay đổi (tariffs.name).</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>Giá chuẩn 2026</t>
+        </is>
+      </c>
+      <c r="I12" s="6" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>currency</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>char(3)</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="n"/>
+      <c r="F13" s="6" t="n"/>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>Giá trị trước khi thay đổi (tariffs.currency).</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="I13" s="6" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>varchar(20)</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="n"/>
+      <c r="F14" s="6" t="n"/>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>Giá trị trước khi thay đổi (tariffs.status).</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="I14" s="6" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>status_reason</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>varchar(200)</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="n"/>
+      <c r="F15" s="6" t="n"/>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>Giá trị trước khi thay đổi (tariffs.status_reason).</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="I15" s="6" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>created_at</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>timestamptz</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="n"/>
+      <c r="F16" s="6" t="n"/>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>Giá trị trước khi thay đổi (tariffs.created_at).</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-01T02:00:00Z</t>
+        </is>
+      </c>
+      <c r="I16" s="6" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>updated_at</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>timestamptz</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="n"/>
+      <c r="F17" s="6" t="n"/>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>Giá trị trước khi thay đổi (tariffs.updated_at).</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-10T07:15:00Z</t>
+        </is>
+      </c>
+      <c r="I17" s="6" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>changed_at</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>timestamptz</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="n"/>
+      <c r="F18" s="6" t="n"/>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>Thời điểm phiên bản này của dòng bị thay thế.</t>
+        </is>
+      </c>
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-10T07:15:00Z</t>
+        </is>
+      </c>
+      <c r="I18" s="6" t="n"/>
+    </row>
+    <row r="19" ht="27" customHeight="1">
+      <c r="A19" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>changed_by</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>uuid</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="F19" s="7" t="inlineStr">
+        <is>
+          <t>users.user_id (khi xóa: chặn xóa)</t>
+        </is>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>Người dùng đã thực hiện thay đổi; NULL nếu do hệ thống thực hiện.</t>
+        </is>
+      </c>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>9b2e7d4a-1c3f-4a8e-b6d2-5e0f1a9c3d22</t>
+        </is>
+      </c>
+      <c r="I19" s="6" t="n"/>
+    </row>
+    <row r="20" ht="40.5" customHeight="1">
+      <c r="A20" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>change_reason</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>varchar(200)</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="n"/>
+      <c r="F20" s="6" t="n"/>
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t>Lý do thay đổi dòng, do ứng dụng đặt cho giao dịch: người dùng nhập với quyết định quản trị, văn bản cố định với thao tác thường lệ. Thay đổi không có lý do sẽ bị từ chối.</t>
+        </is>
+      </c>
+      <c r="H20" s="6" t="inlineStr">
+        <is>
+          <t>Customer moved to a new office</t>
+        </is>
+      </c>
+      <c r="I20" s="6" t="n"/>
+    </row>
+    <row r="21"/>
+    <row r="22">
+      <c r="A22" s="4" t="n"/>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>Chỉ mục (index)</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>Các cột</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>Duy nhất</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="n"/>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>Ghi chú</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="27" customHeight="1">
+      <c r="A23" s="6" t="n"/>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>ix_tariff_history_tariff_id_time</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>tariff_id, changed_at</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="n"/>
+      <c r="F23" s="6" t="n"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A7:I20"/>
+  <hyperlinks>
+    <hyperlink ref="A2" location="'Tổng quan'!A1"/>
+    <hyperlink ref="A5" location="'tariffs'!A1"/>
+    <hyperlink ref="F9" location="'tariffs'!A1"/>
+    <hyperlink ref="F19" location="'users'!A1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet69.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -45184,359 +46050,6 @@
     <hyperlink ref="F8" location="'organizations'!A1"/>
     <hyperlink ref="F9" location="'charging_sessions'!A1"/>
     <hyperlink ref="B19" location="'wallet_transactions'!A1"/>
-  </hyperlinks>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet69.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I15"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="40" customWidth="1" min="6" max="6"/>
-    <col width="60" customWidth="1" min="7" max="7"/>
-    <col width="42" customWidth="1" min="8" max="8"/>
-    <col width="11" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="9" t="inlineStr">
-        <is>
-          <t>52. wallets: Ví</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="10" t="inlineStr">
-        <is>
-          <t>← Tổng quan</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>Miền nghiệp vụ: Thanh toán &amp; hóa đơn (billing)   ·   Chủ sở hữu dữ liệu: Khách hàng   ·   Tính năng: F-H2</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="11" t="inlineStr">
-        <is>
-          <t>Số dư trả trước của một tài xế hoặc của cả tổ chức.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5"/>
-    <row r="6" ht="27" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>Cột</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>Kiểu dữ liệu</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>Cho phép rỗng</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>Khóa</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>Tham chiếu tới</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>Ý nghĩa</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>Ví dụ</t>
-        </is>
-      </c>
-      <c r="I6" s="4" t="inlineStr">
-        <is>
-          <t>Lưu lịch sử</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>wallet_id</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>uuid</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
-      <c r="F7" s="6" t="n"/>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>Mã nội bộ của ví.</t>
-        </is>
-      </c>
-      <c r="H7" s="6" t="inlineStr">
-        <is>
-          <t>5c3a0e7d-2f9b-4c1e-a8d3-7b6f0c2e9a32</t>
-        </is>
-      </c>
-      <c r="I7" s="6" t="n"/>
-    </row>
-    <row r="8" ht="27" customHeight="1">
-      <c r="A8" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>organization_id</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>uuid</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E8" s="6" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="F8" s="7" t="inlineStr">
-        <is>
-          <t>organizations.organization_id (khi xóa: chặn xóa)</t>
-        </is>
-      </c>
-      <c r="G8" s="6" t="inlineStr">
-        <is>
-          <t>Tổ chức khách hàng sở hữu ví.</t>
-        </is>
-      </c>
-      <c r="H8" s="6" t="inlineStr">
-        <is>
-          <t>3f6c2a1e-8b4d-4e2a-9c1f-0a7d5b2e4c11</t>
-        </is>
-      </c>
-      <c r="I8" s="6" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>driver_id</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>uuid</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>có</t>
-        </is>
-      </c>
-      <c r="E9" s="6" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="F9" s="7" t="inlineStr">
-        <is>
-          <t>drivers.driver_id (khi xóa: chặn xóa)</t>
-        </is>
-      </c>
-      <c r="G9" s="6" t="inlineStr">
-        <is>
-          <t>Tài xế sở hữu ví; NULL với ví cấp tổ chức (quyết định D5).</t>
-        </is>
-      </c>
-      <c r="H9" s="6" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="I9" s="6" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>balance</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>numeric(14,2)</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E10" s="6" t="n"/>
-      <c r="F10" s="6" t="n"/>
-      <c r="G10" s="6" t="inlineStr">
-        <is>
-          <t>Số dư hiện tại; phải bằng tổng các giao dịch của ví.</t>
-        </is>
-      </c>
-      <c r="H10" s="6" t="inlineStr">
-        <is>
-          <t>12500000.00</t>
-        </is>
-      </c>
-      <c r="I10" s="6" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>currency</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>char(3)</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E11" s="6" t="n"/>
-      <c r="F11" s="6" t="n"/>
-      <c r="G11" s="6" t="inlineStr">
-        <is>
-          <t>Mã tiền tệ ISO 4217.</t>
-        </is>
-      </c>
-      <c r="H11" s="6" t="inlineStr">
-        <is>
-          <t>VND</t>
-        </is>
-      </c>
-      <c r="I11" s="6" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>varchar(20)</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E12" s="6" t="n"/>
-      <c r="F12" s="6" t="n"/>
-      <c r="G12" s="6" t="inlineStr">
-        <is>
-          <t>Ví có dùng được không.</t>
-        </is>
-      </c>
-      <c r="H12" s="6" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="I12" s="6" t="n"/>
-    </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" s="4" t="n"/>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>Được tham chiếu bởi bảng</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>Cột</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="6" t="n"/>
-      <c r="B15" s="7" t="inlineStr">
-        <is>
-          <t>wallet_transactions</t>
-        </is>
-      </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>wallet_id</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A6:I12"/>
-  <hyperlinks>
-    <hyperlink ref="A2" location="'Tổng quan'!A1"/>
-    <hyperlink ref="F8" location="'organizations'!A1"/>
-    <hyperlink ref="F9" location="'drivers'!A1"/>
-    <hyperlink ref="B15" location="'wallet_transactions'!A1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -46238,6 +46751,359 @@
     <row r="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
+          <t>52. wallets: Ví</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t>← Tổng quan</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>Miền nghiệp vụ: Thanh toán &amp; hóa đơn (billing)   ·   Chủ sở hữu dữ liệu: Khách hàng   ·   Tính năng: F-H2</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>Số dư trả trước của một tài xế hoặc của cả tổ chức.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5"/>
+    <row r="6" ht="27" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Cột</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Kiểu dữ liệu</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Cho phép rỗng</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>Khóa</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>Tham chiếu tới</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>Ý nghĩa</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>Ví dụ</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>Lưu lịch sử</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>wallet_id</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>uuid</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="n"/>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>Mã nội bộ của ví.</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>5c3a0e7d-2f9b-4c1e-a8d3-7b6f0c2e9a32</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="n"/>
+    </row>
+    <row r="8" ht="27" customHeight="1">
+      <c r="A8" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>organization_id</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>uuid</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>organizations.organization_id (khi xóa: chặn xóa)</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>Tổ chức khách hàng sở hữu ví.</t>
+        </is>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>3f6c2a1e-8b4d-4e2a-9c1f-0a7d5b2e4c11</t>
+        </is>
+      </c>
+      <c r="I8" s="6" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>driver_id</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>uuid</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>drivers.driver_id (khi xóa: chặn xóa)</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>Tài xế sở hữu ví; NULL với ví cấp tổ chức (quyết định D5).</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="I9" s="6" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>balance</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>numeric(14,2)</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="n"/>
+      <c r="F10" s="6" t="n"/>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>Số dư hiện tại; phải bằng tổng các giao dịch của ví.</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>12500000.00</t>
+        </is>
+      </c>
+      <c r="I10" s="6" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>currency</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>char(3)</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="n"/>
+      <c r="F11" s="6" t="n"/>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>Mã tiền tệ ISO 4217.</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="I11" s="6" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>varchar(20)</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="n"/>
+      <c r="F12" s="6" t="n"/>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>Ví có dùng được không.</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="I12" s="6" t="n"/>
+    </row>
+    <row r="13"/>
+    <row r="14">
+      <c r="A14" s="4" t="n"/>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>Được tham chiếu bởi bảng</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>Cột</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="n"/>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>wallet_transactions</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>wallet_id</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A6:I12"/>
+  <hyperlinks>
+    <hyperlink ref="A2" location="'Tổng quan'!A1"/>
+    <hyperlink ref="F8" location="'organizations'!A1"/>
+    <hyperlink ref="F9" location="'drivers'!A1"/>
+    <hyperlink ref="B15" location="'wallet_transactions'!A1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet71.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="7" max="7"/>
+    <col width="42" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
           <t>53. wallet_transactions: Giao dịch ví</t>
         </is>
       </c>
@@ -46657,7 +47523,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet71.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet72.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -47133,7 +47999,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet72.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet73.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -47575,7 +48441,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet73.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet74.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -47961,7 +48827,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet74.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet75.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -48251,401 +49117,6 @@
   <hyperlinks>
     <hyperlink ref="A2" location="'Tổng quan'!A1"/>
     <hyperlink ref="F8" location="'subscription_plans'!A1"/>
-  </hyperlinks>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet75.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I16"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="40" customWidth="1" min="6" max="6"/>
-    <col width="60" customWidth="1" min="7" max="7"/>
-    <col width="42" customWidth="1" min="8" max="8"/>
-    <col width="11" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="9" t="inlineStr">
-        <is>
-          <t>58. subscriptions: Thuê bao</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="10" t="inlineStr">
-        <is>
-          <t>← Tổng quan</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>Miền nghiệp vụ: Thanh toán &amp; hóa đơn (billing)   ·   Chủ sở hữu dữ liệu: Khách hàng   ·   Tính năng: F-H4</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="11" t="inlineStr">
-        <is>
-          <t>Một xe đăng ký một gói; quá hạn thanh toán sẽ khóa tính năng.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5"/>
-    <row r="6" ht="27" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>Cột</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>Kiểu dữ liệu</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>Cho phép rỗng</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>Khóa</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>Tham chiếu tới</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>Ý nghĩa</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>Ví dụ</t>
-        </is>
-      </c>
-      <c r="I6" s="4" t="inlineStr">
-        <is>
-          <t>Lưu lịch sử</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>subscription_id</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>uuid</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
-      <c r="F7" s="6" t="n"/>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>Mã nội bộ của thuê bao.</t>
-        </is>
-      </c>
-      <c r="H7" s="6" t="inlineStr">
-        <is>
-          <t>9a7e4c1b-6d3f-4a5c-b0e8-2f1d7c9b3e54</t>
-        </is>
-      </c>
-      <c r="I7" s="6" t="n"/>
-    </row>
-    <row r="8" ht="27" customHeight="1">
-      <c r="A8" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>organization_id</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>uuid</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E8" s="6" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="F8" s="7" t="inlineStr">
-        <is>
-          <t>organizations.organization_id (khi xóa: chặn xóa)</t>
-        </is>
-      </c>
-      <c r="G8" s="6" t="inlineStr">
-        <is>
-          <t>Tổ chức khách hàng đăng ký.</t>
-        </is>
-      </c>
-      <c r="H8" s="6" t="inlineStr">
-        <is>
-          <t>3f6c2a1e-8b4d-4e2a-9c1f-0a7d5b2e4c11</t>
-        </is>
-      </c>
-      <c r="I8" s="6" t="n"/>
-    </row>
-    <row r="9" ht="27" customHeight="1">
-      <c r="A9" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>plan_id</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>uuid</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E9" s="6" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="F9" s="7" t="inlineStr">
-        <is>
-          <t>subscription_plans.plan_id (khi xóa: chặn xóa)</t>
-        </is>
-      </c>
-      <c r="G9" s="6" t="inlineStr">
-        <is>
-          <t>Gói được đăng ký.</t>
-        </is>
-      </c>
-      <c r="H9" s="6" t="inlineStr">
-        <is>
-          <t>0c9a6e3d-8f5b-4c7e-a2d1-4b3f9e6c0a65</t>
-        </is>
-      </c>
-      <c r="I9" s="6" t="n"/>
-    </row>
-    <row r="10" ht="27" customHeight="1">
-      <c r="A10" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>vehicle_id</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>uuid</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E10" s="6" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="F10" s="7" t="inlineStr">
-        <is>
-          <t>vehicles.vehicle_id (khi xóa: chặn xóa)</t>
-        </is>
-      </c>
-      <c r="G10" s="6" t="inlineStr">
-        <is>
-          <t>Xe được áp dụng.</t>
-        </is>
-      </c>
-      <c r="H10" s="6" t="inlineStr">
-        <is>
-          <t>7a4c1e9b-3d2f-4b8a-a6c5-1e0d9f8b7a44</t>
-        </is>
-      </c>
-      <c r="I10" s="6" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>started_at</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>timestamptz</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E11" s="6" t="n"/>
-      <c r="F11" s="6" t="n"/>
-      <c r="G11" s="6" t="inlineStr">
-        <is>
-          <t>Thời điểm bắt đầu thuê bao.</t>
-        </is>
-      </c>
-      <c r="H11" s="6" t="inlineStr">
-        <is>
-          <t>2026-09-01T00:00:00Z</t>
-        </is>
-      </c>
-      <c r="I11" s="6" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>ends_at</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>timestamptz</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>có</t>
-        </is>
-      </c>
-      <c r="E12" s="6" t="n"/>
-      <c r="F12" s="6" t="n"/>
-      <c r="G12" s="6" t="inlineStr">
-        <is>
-          <t>Thời điểm kết thúc; NULL nếu tự gia hạn cho tới khi hủy.</t>
-        </is>
-      </c>
-      <c r="H12" s="6" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="I12" s="6" t="n"/>
-    </row>
-    <row r="13" ht="27" customHeight="1">
-      <c r="A13" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>varchar(20)</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E13" s="6" t="n"/>
-      <c r="F13" s="6" t="n"/>
-      <c r="G13" s="6" t="inlineStr">
-        <is>
-          <t>Trạng thái thuê bao; OVERDUE sẽ khóa các tính năng trả phí. Giá trị: ACTIVE | OVERDUE | EXPIRED | CANCELLED.</t>
-        </is>
-      </c>
-      <c r="H13" s="6" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="I13" s="6" t="n"/>
-    </row>
-    <row r="14"/>
-    <row r="15">
-      <c r="A15" s="4" t="n"/>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>Được tham chiếu bởi bảng</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>Cột</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="6" t="n"/>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>invoice_lines</t>
-        </is>
-      </c>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>subscription_id</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A6:I13"/>
-  <hyperlinks>
-    <hyperlink ref="A2" location="'Tổng quan'!A1"/>
-    <hyperlink ref="F8" location="'organizations'!A1"/>
-    <hyperlink ref="F9" location="'subscription_plans'!A1"/>
-    <hyperlink ref="F10" location="'vehicles'!A1"/>
-    <hyperlink ref="B16" location="'invoice_lines'!A1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -48674,6 +49145,401 @@
     <row r="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
+          <t>58. subscriptions: Thuê bao</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t>← Tổng quan</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>Miền nghiệp vụ: Thanh toán &amp; hóa đơn (billing)   ·   Chủ sở hữu dữ liệu: Khách hàng   ·   Tính năng: F-H4</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>Một xe đăng ký một gói; quá hạn thanh toán sẽ khóa tính năng.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5"/>
+    <row r="6" ht="27" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Cột</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Kiểu dữ liệu</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Cho phép rỗng</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>Khóa</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>Tham chiếu tới</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>Ý nghĩa</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>Ví dụ</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>Lưu lịch sử</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>subscription_id</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>uuid</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="n"/>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>Mã nội bộ của thuê bao.</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>9a7e4c1b-6d3f-4a5c-b0e8-2f1d7c9b3e54</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="n"/>
+    </row>
+    <row r="8" ht="27" customHeight="1">
+      <c r="A8" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>organization_id</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>uuid</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>organizations.organization_id (khi xóa: chặn xóa)</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>Tổ chức khách hàng đăng ký.</t>
+        </is>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>3f6c2a1e-8b4d-4e2a-9c1f-0a7d5b2e4c11</t>
+        </is>
+      </c>
+      <c r="I8" s="6" t="n"/>
+    </row>
+    <row r="9" ht="27" customHeight="1">
+      <c r="A9" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>plan_id</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>uuid</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>subscription_plans.plan_id (khi xóa: chặn xóa)</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>Gói được đăng ký.</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>0c9a6e3d-8f5b-4c7e-a2d1-4b3f9e6c0a65</t>
+        </is>
+      </c>
+      <c r="I9" s="6" t="n"/>
+    </row>
+    <row r="10" ht="27" customHeight="1">
+      <c r="A10" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>vehicle_id</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>uuid</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>vehicles.vehicle_id (khi xóa: chặn xóa)</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>Xe được áp dụng.</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>7a4c1e9b-3d2f-4b8a-a6c5-1e0d9f8b7a44</t>
+        </is>
+      </c>
+      <c r="I10" s="6" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>started_at</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>timestamptz</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="n"/>
+      <c r="F11" s="6" t="n"/>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>Thời điểm bắt đầu thuê bao.</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="I11" s="6" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>ends_at</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>timestamptz</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="n"/>
+      <c r="F12" s="6" t="n"/>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>Thời điểm kết thúc; NULL nếu tự gia hạn cho tới khi hủy.</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="I12" s="6" t="n"/>
+    </row>
+    <row r="13" ht="27" customHeight="1">
+      <c r="A13" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>varchar(20)</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="n"/>
+      <c r="F13" s="6" t="n"/>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>Trạng thái thuê bao; OVERDUE sẽ khóa các tính năng trả phí. Giá trị: ACTIVE | OVERDUE | EXPIRED | CANCELLED.</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="I13" s="6" t="n"/>
+    </row>
+    <row r="14"/>
+    <row r="15">
+      <c r="A15" s="4" t="n"/>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>Được tham chiếu bởi bảng</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>Cột</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="n"/>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>invoice_lines</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>subscription_id</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A6:I13"/>
+  <hyperlinks>
+    <hyperlink ref="A2" location="'Tổng quan'!A1"/>
+    <hyperlink ref="F8" location="'organizations'!A1"/>
+    <hyperlink ref="F9" location="'subscription_plans'!A1"/>
+    <hyperlink ref="F10" location="'vehicles'!A1"/>
+    <hyperlink ref="B16" location="'invoice_lines'!A1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet77.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="7" max="7"/>
+    <col width="42" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
           <t>59. driver_scores: Điểm tài xế</t>
         </is>
       </c>
@@ -49054,7 +49920,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet77.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet78.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -49361,7 +50227,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet78.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet79.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/docs/design/domain-model/domain-model.xlsx
+++ b/docs/design/domain-model/domain-model.xlsx
@@ -75,17 +75,18 @@
     <sheet name="policy_violations" sheetId="66" state="visible" r:id="rId66"/>
     <sheet name="tariffs" sheetId="67" state="visible" r:id="rId67"/>
     <sheet name="tariff_history" sheetId="68" state="visible" r:id="rId68"/>
-    <sheet name="payments" sheetId="69" state="visible" r:id="rId69"/>
-    <sheet name="wallets" sheetId="70" state="visible" r:id="rId70"/>
-    <sheet name="wallet_transactions" sheetId="71" state="visible" r:id="rId71"/>
-    <sheet name="invoices" sheetId="72" state="visible" r:id="rId72"/>
-    <sheet name="invoice_lines" sheetId="73" state="visible" r:id="rId73"/>
-    <sheet name="subscription_plans" sheetId="74" state="visible" r:id="rId74"/>
-    <sheet name="plan_features" sheetId="75" state="visible" r:id="rId75"/>
-    <sheet name="subscriptions" sheetId="76" state="visible" r:id="rId76"/>
-    <sheet name="driver_scores" sheetId="77" state="visible" r:id="rId77"/>
-    <sheet name="promotion_campaigns" sheetId="78" state="visible" r:id="rId78"/>
-    <sheet name="trips" sheetId="79" state="visible" r:id="rId79"/>
+    <sheet name="tariff_versions" sheetId="69" state="visible" r:id="rId69"/>
+    <sheet name="payments" sheetId="70" state="visible" r:id="rId70"/>
+    <sheet name="wallets" sheetId="71" state="visible" r:id="rId71"/>
+    <sheet name="wallet_transactions" sheetId="72" state="visible" r:id="rId72"/>
+    <sheet name="invoices" sheetId="73" state="visible" r:id="rId73"/>
+    <sheet name="invoice_lines" sheetId="74" state="visible" r:id="rId74"/>
+    <sheet name="subscription_plans" sheetId="75" state="visible" r:id="rId75"/>
+    <sheet name="plan_features" sheetId="76" state="visible" r:id="rId76"/>
+    <sheet name="subscriptions" sheetId="77" state="visible" r:id="rId77"/>
+    <sheet name="driver_scores" sheetId="78" state="visible" r:id="rId78"/>
+    <sheet name="promotion_campaigns" sheetId="79" state="visible" r:id="rId79"/>
+    <sheet name="trips" sheetId="80" state="visible" r:id="rId80"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'organizations'!$A$7:$I$20</definedName>
@@ -155,17 +156,18 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="65" hidden="1">'policy_violations'!$A$6:$I$14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="66" hidden="1">'tariffs'!$A$7:$I$16</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="67" hidden="1">'tariff_history'!$A$7:$I$20</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="68" hidden="1">'payments'!$A$6:$I$16</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="69" hidden="1">'wallets'!$A$6:$I$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="70" hidden="1">'wallet_transactions'!$A$6:$I$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="71" hidden="1">'invoices'!$A$6:$I$16</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="72" hidden="1">'invoice_lines'!$A$6:$I$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="73" hidden="1">'subscription_plans'!$A$6:$I$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="74" hidden="1">'plan_features'!$A$6:$I$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="75" hidden="1">'subscriptions'!$A$6:$I$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="76" hidden="1">'driver_scores'!$A$6:$I$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="77" hidden="1">'promotion_campaigns'!$A$6:$I$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="78" hidden="1">'trips'!$A$6:$I$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="68" hidden="1">'tariff_versions'!$A$6:$I$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="69" hidden="1">'payments'!$A$6:$I$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="70" hidden="1">'wallets'!$A$6:$I$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="71" hidden="1">'wallet_transactions'!$A$6:$I$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="72" hidden="1">'invoices'!$A$6:$I$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="73" hidden="1">'invoice_lines'!$A$6:$I$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="74" hidden="1">'subscription_plans'!$A$6:$I$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="75" hidden="1">'plan_features'!$A$6:$I$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="76" hidden="1">'subscriptions'!$A$6:$I$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="77" hidden="1">'driver_scores'!$A$6:$I$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="78" hidden="1">'promotion_campaigns'!$A$6:$I$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="79" hidden="1">'trips'!$A$6:$I$14</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -654,7 +656,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I121"/>
+  <dimension ref="A1:I122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -685,7 +687,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>78 bảng trong 16 miền nghiệp vụ: 58 bảng chính, 17 bảng lịch sử (N.h), 3 bảng trạng thái. Bấm vào tên bảng hoặc «→ Mở» để mở sheet chi tiết của bảng; chú giải và các quyết định còn mở nằm ở cuối trang.</t>
+          <t>79 bảng trong 16 miền nghiệp vụ: 59 bảng chính, 17 bảng lịch sử (N.h), 3 bảng trạng thái. Bấm vào tên bảng hoặc «→ Mở» để mở sheet chi tiết của bảng; chú giải và các quyết định còn mở nằm ở cuối trang.</t>
         </is>
       </c>
     </row>
@@ -3981,7 +3983,7 @@
       </c>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t>10 bảng</t>
+          <t>11 bảng</t>
         </is>
       </c>
       <c r="D84" s="5" t="n"/>
@@ -4089,7 +4091,7 @@
         </is>
       </c>
     </row>
-    <row r="87" ht="27" customHeight="1">
+    <row r="87" ht="81" customHeight="1">
       <c r="A87" s="6" t="inlineStr">
         <is>
           <t>51</t>
@@ -4102,12 +4104,12 @@
       </c>
       <c r="C87" s="7" t="inlineStr">
         <is>
-          <t>payments</t>
+          <t>tariff_versions</t>
         </is>
       </c>
       <c r="D87" s="7" t="inlineStr">
         <is>
-          <t>Thanh toán</t>
+          <t>Phiên bản biểu giá</t>
         </is>
       </c>
       <c r="E87" s="6" t="inlineStr">
@@ -4117,12 +4119,12 @@
       </c>
       <c r="F87" s="6" t="inlineStr">
         <is>
-          <t>F-H1</t>
+          <t>F-C8, F-H1</t>
         </is>
       </c>
       <c r="G87" s="6" t="inlineStr">
         <is>
-          <t>Một lần thanh toán qua cổng thanh toán hoặc ví, thường cho một phiên sạc.</t>
+          <t>Một bộ giá không sửa được của biểu giá (BL-09); đổi giá là tạo phiên bản mới. Phiên bản hiện hành là phiên bản mới nhất có effective_from đã tới. Khi quét mã, ứng dụng hiện giá của khung giờ đó, và giá này được chốt cho cả phiên (PAY-09) trên bản ghi tính tiền của phiên, không ghi trên charging_sessions. Không có lịch sử thay đổi: phiên bản không bao giờ bị sửa. Ràng buộc kiểm tra (BL-09): giá không âm; thuế suất từ 0 đến 100.</t>
         </is>
       </c>
       <c r="H87" s="6" t="n">
@@ -4147,12 +4149,12 @@
       </c>
       <c r="C88" s="7" t="inlineStr">
         <is>
-          <t>wallets</t>
+          <t>payments</t>
         </is>
       </c>
       <c r="D88" s="7" t="inlineStr">
         <is>
-          <t>Ví</t>
+          <t>Thanh toán</t>
         </is>
       </c>
       <c r="E88" s="6" t="inlineStr">
@@ -4162,16 +4164,16 @@
       </c>
       <c r="F88" s="6" t="inlineStr">
         <is>
-          <t>F-H2</t>
+          <t>F-H1</t>
         </is>
       </c>
       <c r="G88" s="6" t="inlineStr">
         <is>
-          <t>Số dư trả trước của một tài xế hoặc của cả tổ chức.</t>
+          <t>Một lần thanh toán qua cổng thanh toán hoặc ví, thường cho một phiên sạc.</t>
         </is>
       </c>
       <c r="H88" s="6" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I88" s="7" t="inlineStr">
         <is>
@@ -4192,12 +4194,12 @@
       </c>
       <c r="C89" s="7" t="inlineStr">
         <is>
-          <t>wallet_transactions</t>
+          <t>wallets</t>
         </is>
       </c>
       <c r="D89" s="7" t="inlineStr">
         <is>
-          <t>Giao dịch ví</t>
+          <t>Ví</t>
         </is>
       </c>
       <c r="E89" s="6" t="inlineStr">
@@ -4212,11 +4214,11 @@
       </c>
       <c r="G89" s="6" t="inlineStr">
         <is>
-          <t>Biến động tiền vào/ra khỏi ví, chỉ ghi thêm.</t>
+          <t>Số dư trả trước của một tài xế hoặc của cả tổ chức.</t>
         </is>
       </c>
       <c r="H89" s="6" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I89" s="7" t="inlineStr">
         <is>
@@ -4237,12 +4239,12 @@
       </c>
       <c r="C90" s="7" t="inlineStr">
         <is>
-          <t>invoices</t>
+          <t>wallet_transactions</t>
         </is>
       </c>
       <c r="D90" s="7" t="inlineStr">
         <is>
-          <t>Hóa đơn</t>
+          <t>Giao dịch ví</t>
         </is>
       </c>
       <c r="E90" s="6" t="inlineStr">
@@ -4252,16 +4254,16 @@
       </c>
       <c r="F90" s="6" t="inlineStr">
         <is>
-          <t>F-H3, F-H4</t>
+          <t>F-H2</t>
         </is>
       </c>
       <c r="G90" s="6" t="inlineStr">
         <is>
-          <t>Một hóa đơn điện tử hợp lệ. Khi đã PHÁT HÀNH thì không sửa, chỉ điều chỉnh hoặc hủy bằng hóa đơn mới.</t>
+          <t>Biến động tiền vào/ra khỏi ví, chỉ ghi thêm.</t>
         </is>
       </c>
       <c r="H90" s="6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I90" s="7" t="inlineStr">
         <is>
@@ -4282,303 +4284,303 @@
       </c>
       <c r="C91" s="7" t="inlineStr">
         <is>
+          <t>invoices</t>
+        </is>
+      </c>
+      <c r="D91" s="7" t="inlineStr">
+        <is>
+          <t>Hóa đơn</t>
+        </is>
+      </c>
+      <c r="E91" s="6" t="inlineStr">
+        <is>
+          <t>Khách hàng</t>
+        </is>
+      </c>
+      <c r="F91" s="6" t="inlineStr">
+        <is>
+          <t>F-H3, F-H4</t>
+        </is>
+      </c>
+      <c r="G91" s="6" t="inlineStr">
+        <is>
+          <t>Một hóa đơn điện tử hợp lệ. Khi đã PHÁT HÀNH thì không sửa, chỉ điều chỉnh hoặc hủy bằng hóa đơn mới.</t>
+        </is>
+      </c>
+      <c r="H91" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="I91" s="7" t="inlineStr">
+        <is>
+          <t>→ Mở</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="27" customHeight="1">
+      <c r="A92" s="6" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="B92" s="6" t="inlineStr">
+        <is>
+          <t>Thanh toán &amp; hóa đơn (billing)</t>
+        </is>
+      </c>
+      <c r="C92" s="7" t="inlineStr">
+        <is>
           <t>invoice_lines</t>
         </is>
       </c>
-      <c r="D91" s="7" t="inlineStr">
+      <c r="D92" s="7" t="inlineStr">
         <is>
           <t>Dòng hóa đơn</t>
         </is>
       </c>
-      <c r="E91" s="6" t="inlineStr">
+      <c r="E92" s="6" t="inlineStr">
         <is>
           <t>Khách hàng</t>
         </is>
       </c>
-      <c r="F91" s="6" t="inlineStr">
+      <c r="F92" s="6" t="inlineStr">
         <is>
           <t>F-H3, F-H4</t>
         </is>
       </c>
-      <c r="G91" s="6" t="inlineStr">
+      <c r="G92" s="6" t="inlineStr">
         <is>
           <t>Một dòng của hóa đơn: một phiên sạc hoặc một kỳ thuê bao.</t>
         </is>
       </c>
-      <c r="H91" s="6" t="n">
+      <c r="H92" s="6" t="n">
         <v>9</v>
       </c>
-      <c r="I91" s="7" t="inlineStr">
+      <c r="I92" s="7" t="inlineStr">
         <is>
           <t>→ Mở</t>
         </is>
       </c>
     </row>
-    <row r="92" ht="54" customHeight="1">
-      <c r="A92" s="6" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="B92" s="6" t="inlineStr">
+    <row r="93" ht="54" customHeight="1">
+      <c r="A93" s="6" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="B93" s="6" t="inlineStr">
         <is>
           <t>Thanh toán &amp; hóa đơn (billing)</t>
         </is>
       </c>
-      <c r="C92" s="7" t="inlineStr">
+      <c r="C93" s="7" t="inlineStr">
         <is>
           <t>subscription_plans</t>
         </is>
       </c>
-      <c r="D92" s="7" t="inlineStr">
+      <c r="D93" s="7" t="inlineStr">
         <is>
           <t>Gói dịch vụ</t>
         </is>
       </c>
-      <c r="E92" s="6" t="inlineStr">
+      <c r="E93" s="6" t="inlineStr">
         <is>
           <t>Nội bộ</t>
         </is>
       </c>
-      <c r="F92" s="6" t="inlineStr">
+      <c r="F93" s="6" t="inlineStr">
         <is>
           <t>F-H4</t>
         </is>
       </c>
-      <c r="G92" s="6" t="inlineStr">
+      <c r="G93" s="6" t="inlineStr">
         <is>
           <t>Một gói dịch vụ: mỗi gói là một dòng (GUEST là gói mặc định miễn phí, STANDARD, ADVANCED, PRO, ..., hoặc gói riêng cho một khách hàng); tính năng của gói nằm ở plan_features. Giá được tính theo từng tính năng (xem ghi chú của miền thanh toán).</t>
         </is>
       </c>
-      <c r="H92" s="6" t="n">
+      <c r="H93" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="I92" s="7" t="inlineStr">
+      <c r="I93" s="7" t="inlineStr">
         <is>
           <t>→ Mở</t>
         </is>
       </c>
     </row>
-    <row r="93" ht="40.5" customHeight="1">
-      <c r="A93" s="6" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="B93" s="6" t="inlineStr">
+    <row r="94" ht="40.5" customHeight="1">
+      <c r="A94" s="6" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="B94" s="6" t="inlineStr">
         <is>
           <t>Thanh toán &amp; hóa đơn (billing)</t>
         </is>
       </c>
-      <c r="C93" s="7" t="inlineStr">
+      <c r="C94" s="7" t="inlineStr">
         <is>
           <t>plan_features</t>
         </is>
       </c>
-      <c r="D93" s="7" t="inlineStr">
+      <c r="D94" s="7" t="inlineStr">
         <is>
           <t>Tính năng của gói dịch vụ</t>
         </is>
       </c>
-      <c r="E93" s="6" t="inlineStr">
+      <c r="E94" s="6" t="inlineStr">
         <is>
           <t>Nội bộ</t>
         </is>
       </c>
-      <c r="F93" s="6" t="inlineStr">
+      <c r="F94" s="6" t="inlineStr">
         <is>
           <t>F-H4</t>
         </is>
       </c>
-      <c r="G93" s="6" t="inlineStr">
+      <c r="G94" s="6" t="inlineStr">
         <is>
           <t>Mỗi gói dịch vụ gồm những tính năng nào. Gói dịch vụ là dữ liệu, nên G3 có thể tạo gói mới (Pro, Max, gói riêng cho một khách hàng) trên portal mà không cần lập trình viên; chỉ tính năng hoàn toàn mới mới cần viết mã.</t>
         </is>
       </c>
-      <c r="H93" s="6" t="n">
+      <c r="H94" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="I93" s="7" t="inlineStr">
+      <c r="I94" s="7" t="inlineStr">
         <is>
           <t>→ Mở</t>
         </is>
       </c>
     </row>
-    <row r="94" ht="27" customHeight="1">
-      <c r="A94" s="6" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="B94" s="6" t="inlineStr">
+    <row r="95" ht="27" customHeight="1">
+      <c r="A95" s="6" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="B95" s="6" t="inlineStr">
         <is>
           <t>Thanh toán &amp; hóa đơn (billing)</t>
         </is>
       </c>
-      <c r="C94" s="7" t="inlineStr">
+      <c r="C95" s="7" t="inlineStr">
         <is>
           <t>subscriptions</t>
         </is>
       </c>
-      <c r="D94" s="7" t="inlineStr">
+      <c r="D95" s="7" t="inlineStr">
         <is>
           <t>Thuê bao</t>
         </is>
       </c>
-      <c r="E94" s="6" t="inlineStr">
+      <c r="E95" s="6" t="inlineStr">
         <is>
           <t>Khách hàng</t>
         </is>
       </c>
-      <c r="F94" s="6" t="inlineStr">
+      <c r="F95" s="6" t="inlineStr">
         <is>
           <t>F-H4</t>
         </is>
       </c>
-      <c r="G94" s="6" t="inlineStr">
+      <c r="G95" s="6" t="inlineStr">
         <is>
           <t>Một xe đăng ký một gói; quá hạn thanh toán sẽ khóa tính năng.</t>
         </is>
       </c>
-      <c r="H94" s="6" t="n">
+      <c r="H95" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="I94" s="7" t="inlineStr">
+      <c r="I95" s="7" t="inlineStr">
         <is>
           <t>→ Mở</t>
         </is>
       </c>
     </row>
-    <row r="95" ht="27" customHeight="1">
-      <c r="A95" s="5" t="n"/>
-      <c r="B95" s="5" t="inlineStr">
+    <row r="96" ht="27" customHeight="1">
+      <c r="A96" s="5" t="n"/>
+      <c r="B96" s="5" t="inlineStr">
         <is>
           <t>Chấm điểm tài xế (scoring)</t>
         </is>
       </c>
-      <c r="C95" s="5" t="inlineStr">
+      <c r="C96" s="5" t="inlineStr">
         <is>
           <t>1 bảng</t>
         </is>
       </c>
-      <c r="D95" s="5" t="n"/>
-      <c r="E95" s="5" t="n"/>
-      <c r="F95" s="5" t="n"/>
-      <c r="G95" s="5" t="inlineStr">
+      <c r="D96" s="5" t="n"/>
+      <c r="E96" s="5" t="n"/>
+      <c r="F96" s="5" t="n"/>
+      <c r="G96" s="5" t="inlineStr">
         <is>
           <t>Chấm điểm an toàn cho tài xế từ hành vi lái xe.
 • Mỗi tuần, mỗi tài xế có một điểm, tính từ dữ liệu vận hành của xe họ lái.</t>
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" s="6" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="B96" s="6" t="inlineStr">
+    <row r="97">
+      <c r="A97" s="6" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="B97" s="6" t="inlineStr">
         <is>
           <t>Chấm điểm tài xế (scoring)</t>
         </is>
       </c>
-      <c r="C96" s="7" t="inlineStr">
+      <c r="C97" s="7" t="inlineStr">
         <is>
           <t>driver_scores</t>
         </is>
       </c>
-      <c r="D96" s="7" t="inlineStr">
+      <c r="D97" s="7" t="inlineStr">
         <is>
           <t>Điểm tài xế</t>
         </is>
       </c>
-      <c r="E96" s="6" t="inlineStr">
+      <c r="E97" s="6" t="inlineStr">
         <is>
           <t>Khách hàng</t>
         </is>
       </c>
-      <c r="F96" s="6" t="inlineStr">
+      <c r="F97" s="6" t="inlineStr">
         <is>
           <t>F-K1</t>
         </is>
       </c>
-      <c r="G96" s="6" t="inlineStr">
+      <c r="G97" s="6" t="inlineStr">
         <is>
           <t>Điểm an toàn hằng tuần của tài xế, tính từ dữ liệu vận hành xe.</t>
         </is>
       </c>
-      <c r="H96" s="6" t="n">
+      <c r="H97" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="I96" s="7" t="inlineStr">
+      <c r="I97" s="7" t="inlineStr">
         <is>
           <t>→ Mở</t>
         </is>
       </c>
     </row>
-    <row r="97" ht="27" customHeight="1">
-      <c r="A97" s="5" t="n"/>
-      <c r="B97" s="5" t="inlineStr">
+    <row r="98" ht="27" customHeight="1">
+      <c r="A98" s="5" t="n"/>
+      <c r="B98" s="5" t="inlineStr">
         <is>
           <t>Chưa phân miền (unassigned)</t>
         </is>
       </c>
-      <c r="C97" s="5" t="inlineStr">
+      <c r="C98" s="5" t="inlineStr">
         <is>
           <t>2 bảng</t>
         </is>
       </c>
-      <c r="D97" s="5" t="n"/>
-      <c r="E97" s="5" t="n"/>
-      <c r="F97" s="5" t="n"/>
-      <c r="G97" s="5" t="inlineStr">
+      <c r="D98" s="5" t="n"/>
+      <c r="E98" s="5" t="n"/>
+      <c r="F98" s="5" t="n"/>
+      <c r="G98" s="5" t="inlineStr">
         <is>
           <t>Các tính năng chưa được quyết định thuộc miền nghiệp vụ nào (xem feature-list.md).</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="6" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="B98" s="6" t="inlineStr">
-        <is>
-          <t>Chưa phân miền (unassigned)</t>
-        </is>
-      </c>
-      <c r="C98" s="7" t="inlineStr">
-        <is>
-          <t>promotion_campaigns</t>
-        </is>
-      </c>
-      <c r="D98" s="7" t="inlineStr">
-        <is>
-          <t>Chiến dịch khuyến mãi</t>
-        </is>
-      </c>
-      <c r="E98" s="6" t="inlineStr">
-        <is>
-          <t>Nội bộ</t>
-        </is>
-      </c>
-      <c r="F98" s="6" t="inlineStr">
-        <is>
-          <t>F-F4</t>
-        </is>
-      </c>
-      <c r="G98" s="6" t="inlineStr">
-        <is>
-          <t>Một chiến dịch nhắc bảo dưỡng hoặc khuyến mãi.</t>
-        </is>
-      </c>
-      <c r="H98" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="I98" s="7" t="inlineStr">
-        <is>
-          <t>→ Mở</t>
         </is>
       </c>
     </row>
@@ -4595,294 +4597,339 @@
       </c>
       <c r="C99" s="7" t="inlineStr">
         <is>
+          <t>promotion_campaigns</t>
+        </is>
+      </c>
+      <c r="D99" s="7" t="inlineStr">
+        <is>
+          <t>Chiến dịch khuyến mãi</t>
+        </is>
+      </c>
+      <c r="E99" s="6" t="inlineStr">
+        <is>
+          <t>Nội bộ</t>
+        </is>
+      </c>
+      <c r="F99" s="6" t="inlineStr">
+        <is>
+          <t>F-F4</t>
+        </is>
+      </c>
+      <c r="G99" s="6" t="inlineStr">
+        <is>
+          <t>Một chiến dịch nhắc bảo dưỡng hoặc khuyến mãi.</t>
+        </is>
+      </c>
+      <c r="H99" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="I99" s="7" t="inlineStr">
+        <is>
+          <t>→ Mở</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="6" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="B100" s="6" t="inlineStr">
+        <is>
+          <t>Chưa phân miền (unassigned)</t>
+        </is>
+      </c>
+      <c r="C100" s="7" t="inlineStr">
+        <is>
           <t>trips</t>
         </is>
       </c>
-      <c r="D99" s="7" t="inlineStr">
+      <c r="D100" s="7" t="inlineStr">
         <is>
           <t>Chuyến đi</t>
         </is>
       </c>
-      <c r="E99" s="6" t="inlineStr">
+      <c r="E100" s="6" t="inlineStr">
         <is>
           <t>Khách hàng</t>
         </is>
       </c>
-      <c r="F99" s="6" t="inlineStr">
+      <c r="F100" s="6" t="inlineStr">
         <is>
           <t>F-A9</t>
         </is>
       </c>
-      <c r="G99" s="6" t="inlineStr">
+      <c r="G100" s="6" t="inlineStr">
         <is>
           <t>Một chuyến đi của xe. F-A9 đang tạm dừng: chưa có khái niệm chuyến đi.</t>
         </is>
       </c>
-      <c r="H99" s="6" t="n">
+      <c r="H100" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="I99" s="7" t="inlineStr">
+      <c r="I100" s="7" t="inlineStr">
         <is>
           <t>→ Mở</t>
         </is>
       </c>
     </row>
-    <row r="100"/>
-    <row r="101" ht="27" customHeight="1">
-      <c r="A101" s="4" t="inlineStr">
+    <row r="101"/>
+    <row r="102" ht="27" customHeight="1">
+      <c r="A102" s="4" t="inlineStr">
         <is>
           <t>Chú giải</t>
         </is>
       </c>
-      <c r="B101" s="4" t="inlineStr">
+      <c r="B102" s="4" t="inlineStr">
         <is>
           <t>Ý nghĩa</t>
         </is>
       </c>
     </row>
-    <row r="102" ht="108" customHeight="1">
-      <c r="A102" s="6" t="inlineStr">
+    <row r="103" ht="108" customHeight="1">
+      <c r="A103" s="6" t="inlineStr">
         <is>
           <t>Chủ sở hữu dữ liệu: Khách hàng</t>
         </is>
       </c>
-      <c r="B102" s="6" t="inlineStr">
+      <c r="B103" s="6" t="inlineStr">
         <is>
           <t>Thuộc về một tổ chức (thường là khách hàng; công ty G3 cũng có thể sở hữu); có cột organization_id hoặc lấy qua bảng cha (DM-24).</t>
-        </is>
-      </c>
-    </row>
-    <row r="103" ht="94.5" customHeight="1">
-      <c r="A103" s="6" t="inlineStr">
-        <is>
-          <t>Chủ sở hữu dữ liệu: Nội bộ</t>
-        </is>
-      </c>
-      <c r="B103" s="6" t="inlineStr">
-        <is>
-          <t>Dữ liệu của chính chúng ta (đơn vị vận hành nền tảng), dùng chung cho mọi tổ chức.</t>
         </is>
       </c>
     </row>
     <row r="104" ht="94.5" customHeight="1">
       <c r="A104" s="6" t="inlineStr">
         <is>
+          <t>Chủ sở hữu dữ liệu: Nội bộ</t>
+        </is>
+      </c>
+      <c r="B104" s="6" t="inlineStr">
+        <is>
+          <t>Dữ liệu của chính chúng ta (đơn vị vận hành nền tảng), dùng chung cho mọi tổ chức.</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="94.5" customHeight="1">
+      <c r="A105" s="6" t="inlineStr">
+        <is>
           <t>Chủ sở hữu dữ liệu: Hai bên</t>
         </is>
       </c>
-      <c r="B104" s="6" t="inlineStr">
+      <c r="B105" s="6" t="inlineStr">
         <is>
           <t>Tài sản của G3 được khách hàng sử dụng; cả hai bên cùng liên quan.</t>
         </is>
       </c>
     </row>
-    <row r="105" ht="121.5" customHeight="1">
-      <c r="A105" s="6" t="inlineStr">
+    <row r="106" ht="121.5" customHeight="1">
+      <c r="A106" s="6" t="inlineStr">
         <is>
           <t>Chủ sở hữu dữ liệu: Chưa quyết định</t>
         </is>
       </c>
-      <c r="B105" s="6" t="inlineStr">
+      <c r="B106" s="6" t="inlineStr">
         <is>
           <t>Đang chờ một quyết định còn mở (xem cuối trang).</t>
         </is>
       </c>
     </row>
-    <row r="106" ht="81" customHeight="1">
-      <c r="A106" s="6" t="inlineStr">
+    <row r="107" ht="81" customHeight="1">
+      <c r="A107" s="6" t="inlineStr">
         <is>
           <t>Miền nghiệp vụ (domain)</t>
         </is>
       </c>
-      <c r="B106" s="6" t="inlineStr">
+      <c r="B107" s="6" t="inlineStr">
         <is>
           <t>Một phần của hệ thống sở hữu dữ liệu riêng, ví dụ Xe, Trạm sạc, Thanh toán. Mỗi miền gồm một hoặc nhiều bảng.</t>
         </is>
       </c>
     </row>
-    <row r="107" ht="54" customHeight="1">
-      <c r="A107" s="6" t="inlineStr">
+    <row r="108" ht="54" customHeight="1">
+      <c r="A108" s="6" t="inlineStr">
         <is>
           <t>Bảng</t>
         </is>
       </c>
-      <c r="B107" s="6" t="inlineStr">
+      <c r="B108" s="6" t="inlineStr">
         <is>
           <t>Một loại dữ liệu được lưu, ví dụ Xe hoặc Phiên sạc. Mỗi bảng có một sheet riêng liệt kê từng cột.</t>
         </is>
       </c>
     </row>
-    <row r="108" ht="40.5" customHeight="1">
-      <c r="A108" s="6" t="inlineStr">
+    <row r="109" ht="40.5" customHeight="1">
+      <c r="A109" s="6" t="inlineStr">
         <is>
           <t>Tính năng</t>
         </is>
       </c>
-      <c r="B108" s="6" t="inlineStr">
+      <c r="B109" s="6" t="inlineStr">
         <is>
           <t>Mã tính năng trong danh sách tính năng (feature-list.md), ví dụ F-B2.</t>
         </is>
       </c>
     </row>
-    <row r="109" ht="67.5" customHeight="1">
-      <c r="A109" s="6" t="inlineStr">
+    <row r="110" ht="67.5" customHeight="1">
+      <c r="A110" s="6" t="inlineStr">
         <is>
           <t>PK / FK / UQ</t>
         </is>
       </c>
-      <c r="B109" s="6" t="inlineStr">
+      <c r="B110" s="6" t="inlineStr">
         <is>
           <t>PK: khóa chính (định danh duy nhất của dòng). FK: khóa ngoại (trỏ tới dòng của bảng khác). UQ: giá trị không được trùng.</t>
         </is>
       </c>
     </row>
-    <row r="110" ht="54" customHeight="1">
-      <c r="A110" s="6" t="inlineStr">
+    <row r="111" ht="54" customHeight="1">
+      <c r="A111" s="6" t="inlineStr">
         <is>
           <t>Ví dụ</t>
         </is>
       </c>
-      <c r="B110" s="6" t="inlineStr">
+      <c r="B111" s="6" t="inlineStr">
         <is>
           <t>Giá trị mẫu. Các mã ví dụ khớp nhau giữa các bảng, nên có thể lần theo một bản ghi mẫu qua nhiều sheet.</t>
         </is>
       </c>
     </row>
-    <row r="111" ht="40.5" customHeight="1">
-      <c r="A111" s="6" t="inlineStr">
+    <row r="112" ht="40.5" customHeight="1">
+      <c r="A112" s="6" t="inlineStr">
         <is>
           <t>NULL</t>
         </is>
       </c>
-      <c r="B111" s="6" t="inlineStr">
+      <c r="B112" s="6" t="inlineStr">
         <is>
           <t>Ô không có giá trị. Ý nghĩa của NULL được giải thích trong cột Ý nghĩa.</t>
         </is>
       </c>
     </row>
-    <row r="112" ht="81" customHeight="1">
-      <c r="A112" s="6" t="inlineStr">
+    <row r="113" ht="81" customHeight="1">
+      <c r="A113" s="6" t="inlineStr">
         <is>
           <t>🔍 Lưu lịch sử</t>
         </is>
       </c>
-      <c r="B112" s="6" t="inlineStr">
+      <c r="B113" s="6" t="inlineStr">
         <is>
           <t>Cột được theo dõi: khi cột này thay đổi, toàn bộ dòng cũ được chép sang bảng lịch sử (tên kết thúc bằng _history) kèm thời điểm và người thay đổi.</t>
         </is>
       </c>
     </row>
-    <row r="113"/>
-    <row r="114">
-      <c r="A114" s="8" t="inlineStr">
+    <row r="114"/>
+    <row r="115">
+      <c r="A115" s="8" t="inlineStr">
         <is>
           <t>Các view (giai đoạn đọc từ lịch sử)</t>
         </is>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" s="4" t="inlineStr">
+    <row r="116">
+      <c r="A116" s="4" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="B115" s="4" t="inlineStr">
+      <c r="B116" s="4" t="inlineStr">
         <is>
           <t>Mỗi dòng là</t>
         </is>
       </c>
-      <c r="C115" s="4" t="inlineStr">
+      <c r="C116" s="4" t="inlineStr">
         <is>
           <t>Các cột</t>
         </is>
       </c>
-      <c r="D115" s="4" t="inlineStr">
+      <c r="D116" s="4" t="inlineStr">
         <is>
           <t>Được dùng bởi</t>
-        </is>
-      </c>
-    </row>
-    <row r="116" ht="94.5" customHeight="1">
-      <c r="A116" s="6" t="inlineStr">
-        <is>
-          <t>vehicle_ownership_periods</t>
-        </is>
-      </c>
-      <c r="B116" s="6" t="inlineStr">
-        <is>
-          <t>một giai đoạn xe thuộc một chủ</t>
-        </is>
-      </c>
-      <c r="C116" s="6" t="inlineStr">
-        <is>
-          <t>vehicle_id, organization_id, owned_from, owned_until (NULL với chủ hiện tại)</t>
-        </is>
-      </c>
-      <c r="D116" s="6" t="inlineStr">
-        <is>
-          <t>lịch sử sở hữu và ngày bàn giao đầu tiên (VEH-02), "ngày đó xe của ai"</t>
         </is>
       </c>
     </row>
     <row r="117" ht="94.5" customHeight="1">
       <c r="A117" s="6" t="inlineStr">
         <is>
+          <t>vehicle_ownership_periods</t>
+        </is>
+      </c>
+      <c r="B117" s="6" t="inlineStr">
+        <is>
+          <t>một giai đoạn xe thuộc một chủ</t>
+        </is>
+      </c>
+      <c r="C117" s="6" t="inlineStr">
+        <is>
+          <t>vehicle_id, organization_id, owned_from, owned_until (NULL với chủ hiện tại)</t>
+        </is>
+      </c>
+      <c r="D117" s="6" t="inlineStr">
+        <is>
+          <t>lịch sử sở hữu và ngày bàn giao đầu tiên (VEH-02), "ngày đó xe của ai"</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="94.5" customHeight="1">
+      <c r="A118" s="6" t="inlineStr">
+        <is>
           <t>battery_installation_periods</t>
         </is>
       </c>
-      <c r="B117" s="6" t="inlineStr">
+      <c r="B118" s="6" t="inlineStr">
         <is>
           <t>một lần pin nằm trên một xe</t>
         </is>
       </c>
-      <c r="C117" s="6" t="inlineStr">
+      <c r="C118" s="6" t="inlineStr">
         <is>
           <t>battery_id, vehicle_id, installed_from, installed_until (NULL khi đang lắp)</t>
         </is>
       </c>
-      <c r="D117" s="6" t="inlineStr">
+      <c r="D118" s="6" t="inlineStr">
         <is>
           <t>lịch sử sức khỏe pin qua các xe (MON-07), bộ đếm bảo hành pin (WAR-01)</t>
         </is>
       </c>
     </row>
-    <row r="118"/>
-    <row r="119">
-      <c r="A119" s="8" t="inlineStr">
+    <row r="119"/>
+    <row r="120">
+      <c r="A120" s="8" t="inlineStr">
         <is>
           <t>Các quyết định còn mở</t>
         </is>
       </c>
     </row>
-    <row r="120">
-      <c r="A120" s="4" t="inlineStr">
+    <row r="121">
+      <c r="A121" s="4" t="inlineStr">
         <is>
           <t>Mã</t>
         </is>
       </c>
-      <c r="B120" s="4" t="inlineStr">
+      <c r="B121" s="4" t="inlineStr">
         <is>
           <t>Câu hỏi</t>
         </is>
       </c>
-      <c r="C120" s="4" t="inlineStr">
+      <c r="C121" s="4" t="inlineStr">
         <is>
           <t>Ảnh hưởng tới</t>
         </is>
       </c>
     </row>
-    <row r="121" ht="54" customHeight="1">
-      <c r="A121" s="6" t="inlineStr">
+    <row r="122" ht="54" customHeight="1">
+      <c r="A122" s="6" t="inlineStr">
         <is>
           <t>D5</t>
         </is>
       </c>
-      <c r="B121" s="6" t="inlineStr">
+      <c r="B122" s="6" t="inlineStr">
         <is>
           <t>Ai trả tiền khi tài xế của đội xe sạc: ví của tài xế, ví của đội xe, hay tùy trường hợp?</t>
         </is>
       </c>
-      <c r="C121" s="6" t="inlineStr">
+      <c r="C122" s="6" t="inlineStr">
         <is>
           <t>wallets, payments</t>
         </is>
@@ -5091,39 +5138,42 @@
     <hyperlink ref="C86" location="'tariff_history'!A1"/>
     <hyperlink ref="D86" location="'tariff_history'!A1"/>
     <hyperlink ref="I86" location="'tariff_history'!A1"/>
-    <hyperlink ref="C87" location="'payments'!A1"/>
-    <hyperlink ref="D87" location="'payments'!A1"/>
-    <hyperlink ref="I87" location="'payments'!A1"/>
-    <hyperlink ref="C88" location="'wallets'!A1"/>
-    <hyperlink ref="D88" location="'wallets'!A1"/>
-    <hyperlink ref="I88" location="'wallets'!A1"/>
-    <hyperlink ref="C89" location="'wallet_transactions'!A1"/>
-    <hyperlink ref="D89" location="'wallet_transactions'!A1"/>
-    <hyperlink ref="I89" location="'wallet_transactions'!A1"/>
-    <hyperlink ref="C90" location="'invoices'!A1"/>
-    <hyperlink ref="D90" location="'invoices'!A1"/>
-    <hyperlink ref="I90" location="'invoices'!A1"/>
-    <hyperlink ref="C91" location="'invoice_lines'!A1"/>
-    <hyperlink ref="D91" location="'invoice_lines'!A1"/>
-    <hyperlink ref="I91" location="'invoice_lines'!A1"/>
-    <hyperlink ref="C92" location="'subscription_plans'!A1"/>
-    <hyperlink ref="D92" location="'subscription_plans'!A1"/>
-    <hyperlink ref="I92" location="'subscription_plans'!A1"/>
-    <hyperlink ref="C93" location="'plan_features'!A1"/>
-    <hyperlink ref="D93" location="'plan_features'!A1"/>
-    <hyperlink ref="I93" location="'plan_features'!A1"/>
-    <hyperlink ref="C94" location="'subscriptions'!A1"/>
-    <hyperlink ref="D94" location="'subscriptions'!A1"/>
-    <hyperlink ref="I94" location="'subscriptions'!A1"/>
-    <hyperlink ref="C96" location="'driver_scores'!A1"/>
-    <hyperlink ref="D96" location="'driver_scores'!A1"/>
-    <hyperlink ref="I96" location="'driver_scores'!A1"/>
-    <hyperlink ref="C98" location="'promotion_campaigns'!A1"/>
-    <hyperlink ref="D98" location="'promotion_campaigns'!A1"/>
-    <hyperlink ref="I98" location="'promotion_campaigns'!A1"/>
-    <hyperlink ref="C99" location="'trips'!A1"/>
-    <hyperlink ref="D99" location="'trips'!A1"/>
-    <hyperlink ref="I99" location="'trips'!A1"/>
+    <hyperlink ref="C87" location="'tariff_versions'!A1"/>
+    <hyperlink ref="D87" location="'tariff_versions'!A1"/>
+    <hyperlink ref="I87" location="'tariff_versions'!A1"/>
+    <hyperlink ref="C88" location="'payments'!A1"/>
+    <hyperlink ref="D88" location="'payments'!A1"/>
+    <hyperlink ref="I88" location="'payments'!A1"/>
+    <hyperlink ref="C89" location="'wallets'!A1"/>
+    <hyperlink ref="D89" location="'wallets'!A1"/>
+    <hyperlink ref="I89" location="'wallets'!A1"/>
+    <hyperlink ref="C90" location="'wallet_transactions'!A1"/>
+    <hyperlink ref="D90" location="'wallet_transactions'!A1"/>
+    <hyperlink ref="I90" location="'wallet_transactions'!A1"/>
+    <hyperlink ref="C91" location="'invoices'!A1"/>
+    <hyperlink ref="D91" location="'invoices'!A1"/>
+    <hyperlink ref="I91" location="'invoices'!A1"/>
+    <hyperlink ref="C92" location="'invoice_lines'!A1"/>
+    <hyperlink ref="D92" location="'invoice_lines'!A1"/>
+    <hyperlink ref="I92" location="'invoice_lines'!A1"/>
+    <hyperlink ref="C93" location="'subscription_plans'!A1"/>
+    <hyperlink ref="D93" location="'subscription_plans'!A1"/>
+    <hyperlink ref="I93" location="'subscription_plans'!A1"/>
+    <hyperlink ref="C94" location="'plan_features'!A1"/>
+    <hyperlink ref="D94" location="'plan_features'!A1"/>
+    <hyperlink ref="I94" location="'plan_features'!A1"/>
+    <hyperlink ref="C95" location="'subscriptions'!A1"/>
+    <hyperlink ref="D95" location="'subscriptions'!A1"/>
+    <hyperlink ref="I95" location="'subscriptions'!A1"/>
+    <hyperlink ref="C97" location="'driver_scores'!A1"/>
+    <hyperlink ref="D97" location="'driver_scores'!A1"/>
+    <hyperlink ref="I97" location="'driver_scores'!A1"/>
+    <hyperlink ref="C99" location="'promotion_campaigns'!A1"/>
+    <hyperlink ref="D99" location="'promotion_campaigns'!A1"/>
+    <hyperlink ref="I99" location="'promotion_campaigns'!A1"/>
+    <hyperlink ref="C100" location="'trips'!A1"/>
+    <hyperlink ref="D100" location="'trips'!A1"/>
+    <hyperlink ref="I100" location="'trips'!A1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -26116,7 +26166,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I65"/>
+  <dimension ref="A1:I66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -26988,12 +27038,12 @@
       <c r="A48" s="6" t="n"/>
       <c r="B48" s="7" t="inlineStr">
         <is>
-          <t>organization_history</t>
+          <t>tariff_versions</t>
         </is>
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>changed_by</t>
+          <t>created_by</t>
         </is>
       </c>
     </row>
@@ -27001,12 +27051,12 @@
       <c r="A49" s="6" t="n"/>
       <c r="B49" s="7" t="inlineStr">
         <is>
-          <t>user_history</t>
+          <t>organization_history</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>user_id</t>
+          <t>changed_by</t>
         </is>
       </c>
     </row>
@@ -27019,7 +27069,7 @@
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>changed_by</t>
+          <t>user_id</t>
         </is>
       </c>
     </row>
@@ -27027,7 +27077,7 @@
       <c r="A51" s="6" t="n"/>
       <c r="B51" s="7" t="inlineStr">
         <is>
-          <t>membership_history</t>
+          <t>user_history</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
@@ -27036,11 +27086,11 @@
         </is>
       </c>
     </row>
-    <row r="52" ht="27" customHeight="1">
+    <row r="52">
       <c r="A52" s="6" t="n"/>
       <c r="B52" s="7" t="inlineStr">
         <is>
-          <t>organization_setting_history</t>
+          <t>membership_history</t>
         </is>
       </c>
       <c r="C52" s="6" t="inlineStr">
@@ -27049,11 +27099,11 @@
         </is>
       </c>
     </row>
-    <row r="53">
+    <row r="53" ht="27" customHeight="1">
       <c r="A53" s="6" t="n"/>
       <c r="B53" s="7" t="inlineStr">
         <is>
-          <t>vehicle_history</t>
+          <t>organization_setting_history</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
@@ -27066,7 +27116,7 @@
       <c r="A54" s="6" t="n"/>
       <c r="B54" s="7" t="inlineStr">
         <is>
-          <t>vehicle_model_history</t>
+          <t>vehicle_history</t>
         </is>
       </c>
       <c r="C54" s="6" t="inlineStr">
@@ -27079,7 +27129,7 @@
       <c r="A55" s="6" t="n"/>
       <c r="B55" s="7" t="inlineStr">
         <is>
-          <t>battery_model_history</t>
+          <t>vehicle_model_history</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
@@ -27092,7 +27142,7 @@
       <c r="A56" s="6" t="n"/>
       <c r="B56" s="7" t="inlineStr">
         <is>
-          <t>battery_history</t>
+          <t>battery_model_history</t>
         </is>
       </c>
       <c r="C56" s="6" t="inlineStr">
@@ -27105,7 +27155,7 @@
       <c r="A57" s="6" t="n"/>
       <c r="B57" s="7" t="inlineStr">
         <is>
-          <t>warranty_history</t>
+          <t>battery_history</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
@@ -27118,7 +27168,7 @@
       <c r="A58" s="6" t="n"/>
       <c r="B58" s="7" t="inlineStr">
         <is>
-          <t>telematic_history</t>
+          <t>warranty_history</t>
         </is>
       </c>
       <c r="C58" s="6" t="inlineStr">
@@ -27131,7 +27181,7 @@
       <c r="A59" s="6" t="n"/>
       <c r="B59" s="7" t="inlineStr">
         <is>
-          <t>driver_history</t>
+          <t>telematic_history</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
@@ -27144,7 +27194,7 @@
       <c r="A60" s="6" t="n"/>
       <c r="B60" s="7" t="inlineStr">
         <is>
-          <t>fleet_history</t>
+          <t>driver_history</t>
         </is>
       </c>
       <c r="C60" s="6" t="inlineStr">
@@ -27153,11 +27203,11 @@
         </is>
       </c>
     </row>
-    <row r="61" ht="27" customHeight="1">
+    <row r="61">
       <c r="A61" s="6" t="n"/>
       <c r="B61" s="7" t="inlineStr">
         <is>
-          <t>charging_location_history</t>
+          <t>fleet_history</t>
         </is>
       </c>
       <c r="C61" s="6" t="inlineStr">
@@ -27166,11 +27216,11 @@
         </is>
       </c>
     </row>
-    <row r="62">
+    <row r="62" ht="27" customHeight="1">
       <c r="A62" s="6" t="n"/>
       <c r="B62" s="7" t="inlineStr">
         <is>
-          <t>charging_station_history</t>
+          <t>charging_location_history</t>
         </is>
       </c>
       <c r="C62" s="6" t="inlineStr">
@@ -27183,7 +27233,7 @@
       <c r="A63" s="6" t="n"/>
       <c r="B63" s="7" t="inlineStr">
         <is>
-          <t>charging_evse_history</t>
+          <t>charging_station_history</t>
         </is>
       </c>
       <c r="C63" s="6" t="inlineStr">
@@ -27192,11 +27242,11 @@
         </is>
       </c>
     </row>
-    <row r="64" ht="27" customHeight="1">
+    <row r="64">
       <c r="A64" s="6" t="n"/>
       <c r="B64" s="7" t="inlineStr">
         <is>
-          <t>charging_connector_history</t>
+          <t>charging_evse_history</t>
         </is>
       </c>
       <c r="C64" s="6" t="inlineStr">
@@ -27205,14 +27255,27 @@
         </is>
       </c>
     </row>
-    <row r="65">
+    <row r="65" ht="27" customHeight="1">
       <c r="A65" s="6" t="n"/>
       <c r="B65" s="7" t="inlineStr">
         <is>
+          <t>charging_connector_history</t>
+        </is>
+      </c>
+      <c r="C65" s="6" t="inlineStr">
+        <is>
+          <t>changed_by</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="6" t="n"/>
+      <c r="B66" s="7" t="inlineStr">
+        <is>
           <t>tariff_history</t>
         </is>
       </c>
-      <c r="C65" s="6" t="inlineStr">
+      <c r="C66" s="6" t="inlineStr">
         <is>
           <t>changed_by</t>
         </is>
@@ -27248,24 +27311,25 @@
     <hyperlink ref="B45" location="'charging_station_commands'!A1"/>
     <hyperlink ref="B46" location="'charging_sessions'!A1"/>
     <hyperlink ref="B47" location="'charging_policy_versions'!A1"/>
-    <hyperlink ref="B48" location="'organization_history'!A1"/>
-    <hyperlink ref="B49" location="'user_history'!A1"/>
+    <hyperlink ref="B48" location="'tariff_versions'!A1"/>
+    <hyperlink ref="B49" location="'organization_history'!A1"/>
     <hyperlink ref="B50" location="'user_history'!A1"/>
-    <hyperlink ref="B51" location="'membership_history'!A1"/>
-    <hyperlink ref="B52" location="'organization_setting_history'!A1"/>
-    <hyperlink ref="B53" location="'vehicle_history'!A1"/>
-    <hyperlink ref="B54" location="'vehicle_model_history'!A1"/>
-    <hyperlink ref="B55" location="'battery_model_history'!A1"/>
-    <hyperlink ref="B56" location="'battery_history'!A1"/>
-    <hyperlink ref="B57" location="'warranty_history'!A1"/>
-    <hyperlink ref="B58" location="'telematic_history'!A1"/>
-    <hyperlink ref="B59" location="'driver_history'!A1"/>
-    <hyperlink ref="B60" location="'fleet_history'!A1"/>
-    <hyperlink ref="B61" location="'charging_location_history'!A1"/>
-    <hyperlink ref="B62" location="'charging_station_history'!A1"/>
-    <hyperlink ref="B63" location="'charging_evse_history'!A1"/>
-    <hyperlink ref="B64" location="'charging_connector_history'!A1"/>
-    <hyperlink ref="B65" location="'tariff_history'!A1"/>
+    <hyperlink ref="B51" location="'user_history'!A1"/>
+    <hyperlink ref="B52" location="'membership_history'!A1"/>
+    <hyperlink ref="B53" location="'organization_setting_history'!A1"/>
+    <hyperlink ref="B54" location="'vehicle_history'!A1"/>
+    <hyperlink ref="B55" location="'vehicle_model_history'!A1"/>
+    <hyperlink ref="B56" location="'battery_model_history'!A1"/>
+    <hyperlink ref="B57" location="'battery_history'!A1"/>
+    <hyperlink ref="B58" location="'warranty_history'!A1"/>
+    <hyperlink ref="B59" location="'telematic_history'!A1"/>
+    <hyperlink ref="B60" location="'driver_history'!A1"/>
+    <hyperlink ref="B61" location="'fleet_history'!A1"/>
+    <hyperlink ref="B62" location="'charging_location_history'!A1"/>
+    <hyperlink ref="B63" location="'charging_station_history'!A1"/>
+    <hyperlink ref="B64" location="'charging_evse_history'!A1"/>
+    <hyperlink ref="B65" location="'charging_connector_history'!A1"/>
+    <hyperlink ref="B66" location="'tariff_history'!A1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -44406,7 +44470,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:I24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -44939,10 +45003,23 @@
       <c r="A23" s="6" t="n"/>
       <c r="B23" s="7" t="inlineStr">
         <is>
+          <t>tariff_versions</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>tariff_id</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="n"/>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
           <t>tariff_history</t>
         </is>
       </c>
-      <c r="C23" s="6" t="inlineStr">
+      <c r="C24" s="6" t="inlineStr">
         <is>
           <t>tariff_id</t>
         </is>
@@ -44955,7 +45032,8 @@
     <hyperlink ref="A5" location="'tariff_history'!A1"/>
     <hyperlink ref="F9" location="'organizations'!A1"/>
     <hyperlink ref="F10" location="'charging_locations'!A1"/>
-    <hyperlink ref="B23" location="'tariff_history'!A1"/>
+    <hyperlink ref="B23" location="'tariff_versions'!A1"/>
+    <hyperlink ref="B24" location="'tariff_history'!A1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -45576,7 +45654,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -45593,7 +45671,7 @@
     <row r="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>51. payments: Thanh toán</t>
+          <t>51. tariff_versions: Phiên bản biểu giá</t>
         </is>
       </c>
     </row>
@@ -45607,14 +45685,14 @@
     <row r="3">
       <c r="A3" s="11" t="inlineStr">
         <is>
-          <t>Miền nghiệp vụ: Thanh toán &amp; hóa đơn (billing)   ·   Chủ sở hữu dữ liệu: Khách hàng   ·   Tính năng: F-H1</t>
+          <t>Miền nghiệp vụ: Thanh toán &amp; hóa đơn (billing)   ·   Chủ sở hữu dữ liệu: Khách hàng   ·   Tính năng: F-C8, F-H1</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="11" t="inlineStr">
         <is>
-          <t>Một lần thanh toán qua cổng thanh toán hoặc ví, thường cho một phiên sạc.</t>
+          <t>Một bộ giá không sửa được của biểu giá (BL-09); đổi giá là tạo phiên bản mới. Phiên bản hiện hành là phiên bản mới nhất có effective_from đã tới. Khi quét mã, ứng dụng hiện giá của khung giờ đó, và giá này được chốt cho cả phiên (PAY-09) trên bản ghi tính tiền của phiên, không ghi trên charging_sessions. Không có lịch sử thay đổi: phiên bản không bao giờ bị sửa. Ràng buộc kiểm tra (BL-09): giá không âm; thuế suất từ 0 đến 100.</t>
         </is>
       </c>
     </row>
@@ -45672,7 +45750,7 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>payment_id</t>
+          <t>tariff_version_id</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
@@ -45693,23 +45771,23 @@
       <c r="F7" s="6" t="n"/>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>Mã nội bộ của thanh toán.</t>
+          <t>Mã nội bộ của phiên bản biểu giá.</t>
         </is>
       </c>
       <c r="H7" s="6" t="inlineStr">
         <is>
-          <t>3e1c8b5f-9a2d-4e7b-b4f1-6c0a9e3d2b21</t>
+          <t>1a7c3e9f-5b2d-4f8a-9c6e-0d3b8f1a7c55</t>
         </is>
       </c>
       <c r="I7" s="6" t="n"/>
     </row>
-    <row r="8" ht="27" customHeight="1">
+    <row r="8">
       <c r="A8" s="6" t="n">
         <v>2</v>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>organization_id</t>
+          <t>tariff_id</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
@@ -45729,74 +45807,66 @@
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>organizations.organization_id (khi xóa: chặn xóa)</t>
+          <t>tariffs.tariff_id (khi xóa: chặn xóa)</t>
         </is>
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>Tổ chức khách hàng đã thanh toán.</t>
+          <t>Biểu giá chứa phiên bản này.</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
-          <t>3f6c2a1e-8b4d-4e2a-9c1f-0a7d5b2e4c11</t>
+          <t>f2b9e6c3-1d8a-4f5b-a3c7-9e0d4b1f8a10</t>
         </is>
       </c>
       <c r="I8" s="6" t="n"/>
     </row>
-    <row r="9" ht="27" customHeight="1">
+    <row r="9">
       <c r="A9" s="6" t="n">
         <v>3</v>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>session_id</t>
+          <t>version_no</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>uuid</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>có</t>
-        </is>
-      </c>
-      <c r="E9" s="6" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="F9" s="7" t="inlineStr">
-        <is>
-          <t>charging_sessions.session_id (khi xóa: chặn xóa)</t>
-        </is>
-      </c>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="n"/>
+      <c r="F9" s="6" t="n"/>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>Phiên sạc được thanh toán; NULL với các khoản khác.</t>
+          <t>Số phiên bản trong biểu giá, bắt đầu từ 1.</t>
         </is>
       </c>
       <c r="H9" s="6" t="inlineStr">
         <is>
-          <t>e5a2d8f1-4b7c-4e9a-b3d6-2c1f0e9a8dbb</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I9" s="6" t="n"/>
     </row>
-    <row r="10">
+    <row r="10" ht="27" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>4</v>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>amount</t>
+          <t>effective_from</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>numeric(14,2)</t>
+          <t>timestamptz</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
@@ -45808,28 +45878,28 @@
       <c r="F10" s="6" t="n"/>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>Số tiền đã thanh toán.</t>
+          <t>Thời điểm phiên bản này thay phiên bản trước: lúc ban hành hoặc muộn hơn, không bao giờ sớm hơn.</t>
         </is>
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>866250.00</t>
+          <t>2026-10-15T00:00:00Z</t>
         </is>
       </c>
       <c r="I10" s="6" t="n"/>
     </row>
-    <row r="11">
+    <row r="11" ht="27" customHeight="1">
       <c r="A11" s="6" t="n">
         <v>5</v>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>price_per_kwh</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>char(3)</t>
+          <t>numeric(12,2)</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
@@ -45841,78 +45911,78 @@
       <c r="F11" s="6" t="n"/>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>Mã tiền tệ ISO 4217.</t>
+          <t>Đơn giá thường cho mỗi kWh, chưa gồm VAT, theo tiền tệ của biểu giá.</t>
         </is>
       </c>
       <c r="H11" s="6" t="inlineStr">
         <is>
-          <t>VND</t>
+          <t>4500.00</t>
         </is>
       </c>
       <c r="I11" s="6" t="n"/>
     </row>
-    <row r="12">
+    <row r="12" ht="54" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>6</v>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>method</t>
+          <t>time_periods</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>varchar(20)</t>
+          <t>jsonb</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>không</t>
+          <t>có</t>
         </is>
       </c>
       <c r="E12" s="6" t="n"/>
       <c r="F12" s="6" t="n"/>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>Phương thức thanh toán. Giá trị: VNPAY | MOMO | WALLET.</t>
+          <t>Giá theo khung giờ thay cho giá thường trong một số giờ, theo giờ Việt Nam: danh sách {days, from, to, price_per_kwh}; NULL nếu một giá cả ngày. Ghi một lần và đọc cả khối nên dùng JSON thay vì nhiều dòng.</t>
         </is>
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>VNPAY</t>
+          <t>[{"days": ["MON", "TUE", "WED", "THU", "FRI", "SAT"], "from": "22:00", "to": "04:00", "price_per_kwh": 3200}]</t>
         </is>
       </c>
       <c r="I12" s="6" t="n"/>
     </row>
-    <row r="13" ht="27" customHeight="1">
+    <row r="13" ht="40.5" customHeight="1">
       <c r="A13" s="6" t="n">
         <v>7</v>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>gateway_reference</t>
+          <t>vat_rate_percent</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>varchar(100)</t>
+          <t>numeric(4,2)</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>có</t>
+          <t>không</t>
         </is>
       </c>
       <c r="E13" s="6" t="n"/>
       <c r="F13" s="6" t="n"/>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>Mã tham chiếu/token của cổng thanh toán (không bao giờ lưu dữ liệu thẻ) (NF-05).</t>
+          <t>Thuế suất VAT áp dụng cho phiên bản này; giá lưu chưa gồm VAT và hiển thị đã gồm VAT; hóa đơn điện tử cần tách riêng (PAY-11).</t>
         </is>
       </c>
       <c r="H13" s="6" t="inlineStr">
         <is>
-          <t>VNP14592873</t>
+          <t>10.00</t>
         </is>
       </c>
       <c r="I13" s="6" t="n"/>
@@ -45923,12 +45993,12 @@
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>change_reason</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>varchar(20)</t>
+          <t>varchar(200)</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
@@ -45940,12 +46010,12 @@
       <c r="F14" s="6" t="n"/>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>Trạng thái thanh toán.</t>
+          <t>Lý do ban hành phiên bản này.</t>
         </is>
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
-          <t>SUCCEEDED</t>
+          <t>Theo khung giờ cao điểm mới của EVN</t>
         </is>
       </c>
       <c r="I14" s="6" t="n"/>
@@ -45956,29 +46026,37 @@
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>paid_at</t>
+          <t>created_by</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>timestamptz</t>
+          <t>uuid</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>có</t>
-        </is>
-      </c>
-      <c r="E15" s="6" t="n"/>
-      <c r="F15" s="6" t="n"/>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>users.user_id (khi xóa: chặn xóa)</t>
+        </is>
+      </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>Thời điểm cổng thanh toán xác nhận; NULL cho tới lúc đó.</t>
+          <t>Người dùng đã ban hành.</t>
         </is>
       </c>
       <c r="H15" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15T09:46:12Z</t>
+          <t>9b2e7d4a-1c3f-4a8e-b6d2-5e0f1a9c3d22</t>
         </is>
       </c>
       <c r="I15" s="6" t="n"/>
@@ -46006,12 +46084,12 @@
       <c r="F16" s="6" t="n"/>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>Thời điểm tạo bản ghi (UTC).</t>
+          <t>Thời điểm ban hành (UTC).</t>
         </is>
       </c>
       <c r="H16" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15T09:45:00Z</t>
+          <t>2026-10-10T03:00:00Z</t>
         </is>
       </c>
       <c r="I16" s="6" t="n"/>
@@ -46021,25 +46099,67 @@
       <c r="A18" s="4" t="n"/>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>Được tham chiếu bởi bảng</t>
+          <t>Chỉ mục (index)</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>Cột</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
+          <t>Các cột</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>Duy nhất</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="n"/>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>Ghi chú</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="27" customHeight="1">
       <c r="A19" s="6" t="n"/>
-      <c r="B19" s="7" t="inlineStr">
-        <is>
-          <t>wallet_transactions</t>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>uq_tariff_versions_tariff_version_no</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>payment_id</t>
+          <t>tariff_id, version_no</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="n"/>
+      <c r="F19" s="6" t="n"/>
+    </row>
+    <row r="20" ht="27" customHeight="1">
+      <c r="A20" s="6" t="n"/>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>ix_tariff_versions_tariff_effective</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>tariff_id, effective_from</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="n"/>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>The current version: the newest whose effective_from has passed</t>
         </is>
       </c>
     </row>
@@ -46047,9 +46167,8 @@
   <autoFilter ref="A6:I16"/>
   <hyperlinks>
     <hyperlink ref="A2" location="'Tổng quan'!A1"/>
-    <hyperlink ref="F8" location="'organizations'!A1"/>
-    <hyperlink ref="F9" location="'charging_sessions'!A1"/>
-    <hyperlink ref="B19" location="'wallet_transactions'!A1"/>
+    <hyperlink ref="F8" location="'tariffs'!A1"/>
+    <hyperlink ref="F15" location="'users'!A1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -46734,7 +46853,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -46751,7 +46870,7 @@
     <row r="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>52. wallets: Ví</t>
+          <t>52. payments: Thanh toán</t>
         </is>
       </c>
     </row>
@@ -46765,14 +46884,14 @@
     <row r="3">
       <c r="A3" s="11" t="inlineStr">
         <is>
-          <t>Miền nghiệp vụ: Thanh toán &amp; hóa đơn (billing)   ·   Chủ sở hữu dữ liệu: Khách hàng   ·   Tính năng: F-H2</t>
+          <t>Miền nghiệp vụ: Thanh toán &amp; hóa đơn (billing)   ·   Chủ sở hữu dữ liệu: Khách hàng   ·   Tính năng: F-H1</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="11" t="inlineStr">
         <is>
-          <t>Số dư trả trước của một tài xế hoặc của cả tổ chức.</t>
+          <t>Một lần thanh toán qua cổng thanh toán hoặc ví, thường cho một phiên sạc.</t>
         </is>
       </c>
     </row>
@@ -46830,7 +46949,7 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>wallet_id</t>
+          <t>payment_id</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
@@ -46851,12 +46970,12 @@
       <c r="F7" s="6" t="n"/>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>Mã nội bộ của ví.</t>
+          <t>Mã nội bộ của thanh toán.</t>
         </is>
       </c>
       <c r="H7" s="6" t="inlineStr">
         <is>
-          <t>5c3a0e7d-2f9b-4c1e-a8d3-7b6f0c2e9a32</t>
+          <t>3e1c8b5f-9a2d-4e7b-b4f1-6c0a9e3d2b21</t>
         </is>
       </c>
       <c r="I7" s="6" t="n"/>
@@ -46892,7 +47011,7 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>Tổ chức khách hàng sở hữu ví.</t>
+          <t>Tổ chức khách hàng đã thanh toán.</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr">
@@ -46902,13 +47021,13 @@
       </c>
       <c r="I8" s="6" t="n"/>
     </row>
-    <row r="9">
+    <row r="9" ht="27" customHeight="1">
       <c r="A9" s="6" t="n">
         <v>3</v>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>driver_id</t>
+          <t>session_id</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
@@ -46928,17 +47047,17 @@
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>drivers.driver_id (khi xóa: chặn xóa)</t>
+          <t>charging_sessions.session_id (khi xóa: chặn xóa)</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>Tài xế sở hữu ví; NULL với ví cấp tổ chức (quyết định D5).</t>
+          <t>Phiên sạc được thanh toán; NULL với các khoản khác.</t>
         </is>
       </c>
       <c r="H9" s="6" t="inlineStr">
         <is>
-          <t>NULL</t>
+          <t>e5a2d8f1-4b7c-4e9a-b3d6-2c1f0e9a8dbb</t>
         </is>
       </c>
       <c r="I9" s="6" t="n"/>
@@ -46949,7 +47068,7 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>balance</t>
+          <t>amount</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
@@ -46966,12 +47085,12 @@
       <c r="F10" s="6" t="n"/>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>Số dư hiện tại; phải bằng tổng các giao dịch của ví.</t>
+          <t>Số tiền đã thanh toán.</t>
         </is>
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>12500000.00</t>
+          <t>866250.00</t>
         </is>
       </c>
       <c r="I10" s="6" t="n"/>
@@ -47015,7 +47134,7 @@
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>method</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
@@ -47032,50 +47151,182 @@
       <c r="F12" s="6" t="n"/>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>Ví có dùng được không.</t>
+          <t>Phương thức thanh toán. Giá trị: VNPAY | MOMO | WALLET.</t>
         </is>
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>ACTIVE</t>
+          <t>VNPAY</t>
         </is>
       </c>
       <c r="I12" s="6" t="n"/>
     </row>
-    <row r="13"/>
+    <row r="13" ht="27" customHeight="1">
+      <c r="A13" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>gateway_reference</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>varchar(100)</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="n"/>
+      <c r="F13" s="6" t="n"/>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>Mã tham chiếu/token của cổng thanh toán (không bao giờ lưu dữ liệu thẻ) (NF-05).</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>VNP14592873</t>
+        </is>
+      </c>
+      <c r="I13" s="6" t="n"/>
+    </row>
     <row r="14">
-      <c r="A14" s="4" t="n"/>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="A14" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>varchar(20)</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="n"/>
+      <c r="F14" s="6" t="n"/>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>Trạng thái thanh toán.</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>SUCCEEDED</t>
+        </is>
+      </c>
+      <c r="I14" s="6" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>paid_at</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>timestamptz</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="n"/>
+      <c r="F15" s="6" t="n"/>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>Thời điểm cổng thanh toán xác nhận; NULL cho tới lúc đó.</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-15T09:46:12Z</t>
+        </is>
+      </c>
+      <c r="I15" s="6" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>created_at</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>timestamptz</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="n"/>
+      <c r="F16" s="6" t="n"/>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>Thời điểm tạo bản ghi (UTC).</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-15T09:45:00Z</t>
+        </is>
+      </c>
+      <c r="I16" s="6" t="n"/>
+    </row>
+    <row r="17"/>
+    <row r="18">
+      <c r="A18" s="4" t="n"/>
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t>Được tham chiếu bởi bảng</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C18" s="4" t="inlineStr">
         <is>
           <t>Cột</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="6" t="n"/>
-      <c r="B15" s="7" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="6" t="n"/>
+      <c r="B19" s="7" t="inlineStr">
         <is>
           <t>wallet_transactions</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>wallet_id</t>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>payment_id</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A6:I12"/>
+  <autoFilter ref="A6:I16"/>
   <hyperlinks>
     <hyperlink ref="A2" location="'Tổng quan'!A1"/>
     <hyperlink ref="F8" location="'organizations'!A1"/>
-    <hyperlink ref="F9" location="'drivers'!A1"/>
-    <hyperlink ref="B15" location="'wallet_transactions'!A1"/>
+    <hyperlink ref="F9" location="'charging_sessions'!A1"/>
+    <hyperlink ref="B19" location="'wallet_transactions'!A1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -47104,7 +47355,360 @@
     <row r="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>53. wallet_transactions: Giao dịch ví</t>
+          <t>53. wallets: Ví</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t>← Tổng quan</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>Miền nghiệp vụ: Thanh toán &amp; hóa đơn (billing)   ·   Chủ sở hữu dữ liệu: Khách hàng   ·   Tính năng: F-H2</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>Số dư trả trước của một tài xế hoặc của cả tổ chức.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5"/>
+    <row r="6" ht="27" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Cột</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Kiểu dữ liệu</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Cho phép rỗng</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>Khóa</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>Tham chiếu tới</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>Ý nghĩa</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>Ví dụ</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>Lưu lịch sử</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>wallet_id</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>uuid</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="n"/>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>Mã nội bộ của ví.</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>5c3a0e7d-2f9b-4c1e-a8d3-7b6f0c2e9a32</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="n"/>
+    </row>
+    <row r="8" ht="27" customHeight="1">
+      <c r="A8" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>organization_id</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>uuid</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>organizations.organization_id (khi xóa: chặn xóa)</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>Tổ chức khách hàng sở hữu ví.</t>
+        </is>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>3f6c2a1e-8b4d-4e2a-9c1f-0a7d5b2e4c11</t>
+        </is>
+      </c>
+      <c r="I8" s="6" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>driver_id</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>uuid</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>drivers.driver_id (khi xóa: chặn xóa)</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>Tài xế sở hữu ví; NULL với ví cấp tổ chức (quyết định D5).</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="I9" s="6" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>balance</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>numeric(14,2)</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="n"/>
+      <c r="F10" s="6" t="n"/>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>Số dư hiện tại; phải bằng tổng các giao dịch của ví.</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>12500000.00</t>
+        </is>
+      </c>
+      <c r="I10" s="6" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>currency</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>char(3)</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="n"/>
+      <c r="F11" s="6" t="n"/>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>Mã tiền tệ ISO 4217.</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="I11" s="6" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>varchar(20)</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="n"/>
+      <c r="F12" s="6" t="n"/>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>Ví có dùng được không.</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="I12" s="6" t="n"/>
+    </row>
+    <row r="13"/>
+    <row r="14">
+      <c r="A14" s="4" t="n"/>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>Được tham chiếu bởi bảng</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>Cột</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="n"/>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>wallet_transactions</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>wallet_id</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A6:I12"/>
+  <hyperlinks>
+    <hyperlink ref="A2" location="'Tổng quan'!A1"/>
+    <hyperlink ref="F8" location="'organizations'!A1"/>
+    <hyperlink ref="F9" location="'drivers'!A1"/>
+    <hyperlink ref="B15" location="'wallet_transactions'!A1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet72.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="7" max="7"/>
+    <col width="42" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>54. wallet_transactions: Giao dịch ví</t>
         </is>
       </c>
     </row>
@@ -47523,7 +48127,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet72.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet73.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -47546,7 +48150,7 @@
     <row r="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>54. invoices: Hóa đơn</t>
+          <t>55. invoices: Hóa đơn</t>
         </is>
       </c>
     </row>
@@ -47999,7 +48603,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet73.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet74.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -48022,7 +48626,7 @@
     <row r="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>55. invoice_lines: Dòng hóa đơn</t>
+          <t>56. invoice_lines: Dòng hóa đơn</t>
         </is>
       </c>
     </row>
@@ -48441,7 +49045,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet74.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet75.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -48464,7 +49068,7 @@
     <row r="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>56. subscription_plans: Gói dịch vụ</t>
+          <t>57. subscription_plans: Gói dịch vụ</t>
         </is>
       </c>
     </row>
@@ -48827,7 +49431,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet75.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet76.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -48850,7 +49454,7 @@
     <row r="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>57. plan_features: Tính năng của gói dịch vụ</t>
+          <t>58. plan_features: Tính năng của gói dịch vụ</t>
         </is>
       </c>
     </row>
@@ -49117,401 +49721,6 @@
   <hyperlinks>
     <hyperlink ref="A2" location="'Tổng quan'!A1"/>
     <hyperlink ref="F8" location="'subscription_plans'!A1"/>
-  </hyperlinks>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet76.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I16"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="40" customWidth="1" min="6" max="6"/>
-    <col width="60" customWidth="1" min="7" max="7"/>
-    <col width="42" customWidth="1" min="8" max="8"/>
-    <col width="11" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="9" t="inlineStr">
-        <is>
-          <t>58. subscriptions: Thuê bao</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="10" t="inlineStr">
-        <is>
-          <t>← Tổng quan</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>Miền nghiệp vụ: Thanh toán &amp; hóa đơn (billing)   ·   Chủ sở hữu dữ liệu: Khách hàng   ·   Tính năng: F-H4</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="11" t="inlineStr">
-        <is>
-          <t>Một xe đăng ký một gói; quá hạn thanh toán sẽ khóa tính năng.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5"/>
-    <row r="6" ht="27" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>Cột</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>Kiểu dữ liệu</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>Cho phép rỗng</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>Khóa</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>Tham chiếu tới</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>Ý nghĩa</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>Ví dụ</t>
-        </is>
-      </c>
-      <c r="I6" s="4" t="inlineStr">
-        <is>
-          <t>Lưu lịch sử</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>subscription_id</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>uuid</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
-      <c r="F7" s="6" t="n"/>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>Mã nội bộ của thuê bao.</t>
-        </is>
-      </c>
-      <c r="H7" s="6" t="inlineStr">
-        <is>
-          <t>9a7e4c1b-6d3f-4a5c-b0e8-2f1d7c9b3e54</t>
-        </is>
-      </c>
-      <c r="I7" s="6" t="n"/>
-    </row>
-    <row r="8" ht="27" customHeight="1">
-      <c r="A8" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>organization_id</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>uuid</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E8" s="6" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="F8" s="7" t="inlineStr">
-        <is>
-          <t>organizations.organization_id (khi xóa: chặn xóa)</t>
-        </is>
-      </c>
-      <c r="G8" s="6" t="inlineStr">
-        <is>
-          <t>Tổ chức khách hàng đăng ký.</t>
-        </is>
-      </c>
-      <c r="H8" s="6" t="inlineStr">
-        <is>
-          <t>3f6c2a1e-8b4d-4e2a-9c1f-0a7d5b2e4c11</t>
-        </is>
-      </c>
-      <c r="I8" s="6" t="n"/>
-    </row>
-    <row r="9" ht="27" customHeight="1">
-      <c r="A9" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>plan_id</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>uuid</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E9" s="6" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="F9" s="7" t="inlineStr">
-        <is>
-          <t>subscription_plans.plan_id (khi xóa: chặn xóa)</t>
-        </is>
-      </c>
-      <c r="G9" s="6" t="inlineStr">
-        <is>
-          <t>Gói được đăng ký.</t>
-        </is>
-      </c>
-      <c r="H9" s="6" t="inlineStr">
-        <is>
-          <t>0c9a6e3d-8f5b-4c7e-a2d1-4b3f9e6c0a65</t>
-        </is>
-      </c>
-      <c r="I9" s="6" t="n"/>
-    </row>
-    <row r="10" ht="27" customHeight="1">
-      <c r="A10" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>vehicle_id</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>uuid</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E10" s="6" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="F10" s="7" t="inlineStr">
-        <is>
-          <t>vehicles.vehicle_id (khi xóa: chặn xóa)</t>
-        </is>
-      </c>
-      <c r="G10" s="6" t="inlineStr">
-        <is>
-          <t>Xe được áp dụng.</t>
-        </is>
-      </c>
-      <c r="H10" s="6" t="inlineStr">
-        <is>
-          <t>7a4c1e9b-3d2f-4b8a-a6c5-1e0d9f8b7a44</t>
-        </is>
-      </c>
-      <c r="I10" s="6" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>started_at</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>timestamptz</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E11" s="6" t="n"/>
-      <c r="F11" s="6" t="n"/>
-      <c r="G11" s="6" t="inlineStr">
-        <is>
-          <t>Thời điểm bắt đầu thuê bao.</t>
-        </is>
-      </c>
-      <c r="H11" s="6" t="inlineStr">
-        <is>
-          <t>2026-09-01T00:00:00Z</t>
-        </is>
-      </c>
-      <c r="I11" s="6" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>ends_at</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>timestamptz</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>có</t>
-        </is>
-      </c>
-      <c r="E12" s="6" t="n"/>
-      <c r="F12" s="6" t="n"/>
-      <c r="G12" s="6" t="inlineStr">
-        <is>
-          <t>Thời điểm kết thúc; NULL nếu tự gia hạn cho tới khi hủy.</t>
-        </is>
-      </c>
-      <c r="H12" s="6" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="I12" s="6" t="n"/>
-    </row>
-    <row r="13" ht="27" customHeight="1">
-      <c r="A13" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>varchar(20)</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E13" s="6" t="n"/>
-      <c r="F13" s="6" t="n"/>
-      <c r="G13" s="6" t="inlineStr">
-        <is>
-          <t>Trạng thái thuê bao; OVERDUE sẽ khóa các tính năng trả phí. Giá trị: ACTIVE | OVERDUE | EXPIRED | CANCELLED.</t>
-        </is>
-      </c>
-      <c r="H13" s="6" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="I13" s="6" t="n"/>
-    </row>
-    <row r="14"/>
-    <row r="15">
-      <c r="A15" s="4" t="n"/>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>Được tham chiếu bởi bảng</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>Cột</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="6" t="n"/>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>invoice_lines</t>
-        </is>
-      </c>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>subscription_id</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A6:I13"/>
-  <hyperlinks>
-    <hyperlink ref="A2" location="'Tổng quan'!A1"/>
-    <hyperlink ref="F8" location="'organizations'!A1"/>
-    <hyperlink ref="F9" location="'subscription_plans'!A1"/>
-    <hyperlink ref="F10" location="'vehicles'!A1"/>
-    <hyperlink ref="B16" location="'invoice_lines'!A1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -49540,7 +49749,402 @@
     <row r="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>59. driver_scores: Điểm tài xế</t>
+          <t>59. subscriptions: Thuê bao</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t>← Tổng quan</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>Miền nghiệp vụ: Thanh toán &amp; hóa đơn (billing)   ·   Chủ sở hữu dữ liệu: Khách hàng   ·   Tính năng: F-H4</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>Một xe đăng ký một gói; quá hạn thanh toán sẽ khóa tính năng.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5"/>
+    <row r="6" ht="27" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Cột</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Kiểu dữ liệu</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Cho phép rỗng</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>Khóa</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>Tham chiếu tới</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>Ý nghĩa</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>Ví dụ</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>Lưu lịch sử</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>subscription_id</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>uuid</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="n"/>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>Mã nội bộ của thuê bao.</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>9a7e4c1b-6d3f-4a5c-b0e8-2f1d7c9b3e54</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="n"/>
+    </row>
+    <row r="8" ht="27" customHeight="1">
+      <c r="A8" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>organization_id</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>uuid</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>organizations.organization_id (khi xóa: chặn xóa)</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>Tổ chức khách hàng đăng ký.</t>
+        </is>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>3f6c2a1e-8b4d-4e2a-9c1f-0a7d5b2e4c11</t>
+        </is>
+      </c>
+      <c r="I8" s="6" t="n"/>
+    </row>
+    <row r="9" ht="27" customHeight="1">
+      <c r="A9" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>plan_id</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>uuid</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>subscription_plans.plan_id (khi xóa: chặn xóa)</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>Gói được đăng ký.</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>0c9a6e3d-8f5b-4c7e-a2d1-4b3f9e6c0a65</t>
+        </is>
+      </c>
+      <c r="I9" s="6" t="n"/>
+    </row>
+    <row r="10" ht="27" customHeight="1">
+      <c r="A10" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>vehicle_id</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>uuid</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>vehicles.vehicle_id (khi xóa: chặn xóa)</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>Xe được áp dụng.</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>7a4c1e9b-3d2f-4b8a-a6c5-1e0d9f8b7a44</t>
+        </is>
+      </c>
+      <c r="I10" s="6" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>started_at</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>timestamptz</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="n"/>
+      <c r="F11" s="6" t="n"/>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>Thời điểm bắt đầu thuê bao.</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="I11" s="6" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>ends_at</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>timestamptz</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="n"/>
+      <c r="F12" s="6" t="n"/>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>Thời điểm kết thúc; NULL nếu tự gia hạn cho tới khi hủy.</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="I12" s="6" t="n"/>
+    </row>
+    <row r="13" ht="27" customHeight="1">
+      <c r="A13" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>varchar(20)</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="n"/>
+      <c r="F13" s="6" t="n"/>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>Trạng thái thuê bao; OVERDUE sẽ khóa các tính năng trả phí. Giá trị: ACTIVE | OVERDUE | EXPIRED | CANCELLED.</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="I13" s="6" t="n"/>
+    </row>
+    <row r="14"/>
+    <row r="15">
+      <c r="A15" s="4" t="n"/>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>Được tham chiếu bởi bảng</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>Cột</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="n"/>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>invoice_lines</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>subscription_id</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A6:I13"/>
+  <hyperlinks>
+    <hyperlink ref="A2" location="'Tổng quan'!A1"/>
+    <hyperlink ref="F8" location="'organizations'!A1"/>
+    <hyperlink ref="F9" location="'subscription_plans'!A1"/>
+    <hyperlink ref="F10" location="'vehicles'!A1"/>
+    <hyperlink ref="B16" location="'invoice_lines'!A1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet78.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="7" max="7"/>
+    <col width="42" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>60. driver_scores: Điểm tài xế</t>
         </is>
       </c>
     </row>
@@ -49920,7 +50524,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet78.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet79.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -49943,7 +50547,7 @@
     <row r="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>60. promotion_campaigns: Chiến dịch khuyến mãi</t>
+          <t>61. promotion_campaigns: Chiến dịch khuyến mãi</t>
         </is>
       </c>
     </row>
@@ -50222,406 +50826,6 @@
   <autoFilter ref="A6:I12"/>
   <hyperlinks>
     <hyperlink ref="A2" location="'Tổng quan'!A1"/>
-  </hyperlinks>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet79.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="40" customWidth="1" min="6" max="6"/>
-    <col width="60" customWidth="1" min="7" max="7"/>
-    <col width="42" customWidth="1" min="8" max="8"/>
-    <col width="11" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="9" t="inlineStr">
-        <is>
-          <t>61. trips: Chuyến đi</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="10" t="inlineStr">
-        <is>
-          <t>← Tổng quan</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>Miền nghiệp vụ: Chưa phân miền (unassigned)   ·   Chủ sở hữu dữ liệu: Khách hàng   ·   Tính năng: F-A9</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="11" t="inlineStr">
-        <is>
-          <t>Một chuyến đi của xe. F-A9 đang tạm dừng: chưa có khái niệm chuyến đi.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5"/>
-    <row r="6" ht="27" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>Cột</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>Kiểu dữ liệu</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>Cho phép rỗng</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>Khóa</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>Tham chiếu tới</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>Ý nghĩa</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>Ví dụ</t>
-        </is>
-      </c>
-      <c r="I6" s="4" t="inlineStr">
-        <is>
-          <t>Lưu lịch sử</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>trip_id</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>uuid</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
-      <c r="F7" s="6" t="n"/>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>Mã nội bộ của chuyến đi.</t>
-        </is>
-      </c>
-      <c r="H7" s="6" t="inlineStr">
-        <is>
-          <t>2e1c8a5f-0b7d-4e9c-b4a3-6d5f1e8c2b76</t>
-        </is>
-      </c>
-      <c r="I7" s="6" t="n"/>
-    </row>
-    <row r="8" ht="27" customHeight="1">
-      <c r="A8" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>organization_id</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>uuid</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E8" s="6" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="F8" s="7" t="inlineStr">
-        <is>
-          <t>organizations.organization_id (khi xóa: chặn xóa)</t>
-        </is>
-      </c>
-      <c r="G8" s="6" t="inlineStr">
-        <is>
-          <t>Tổ chức khách hàng sở hữu xe.</t>
-        </is>
-      </c>
-      <c r="H8" s="6" t="inlineStr">
-        <is>
-          <t>3f6c2a1e-8b4d-4e2a-9c1f-0a7d5b2e4c11</t>
-        </is>
-      </c>
-      <c r="I8" s="6" t="n"/>
-    </row>
-    <row r="9" ht="27" customHeight="1">
-      <c r="A9" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>vehicle_id</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>uuid</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E9" s="6" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="F9" s="7" t="inlineStr">
-        <is>
-          <t>vehicles.vehicle_id (khi xóa: chặn xóa)</t>
-        </is>
-      </c>
-      <c r="G9" s="6" t="inlineStr">
-        <is>
-          <t>Xe thực hiện chuyến.</t>
-        </is>
-      </c>
-      <c r="H9" s="6" t="inlineStr">
-        <is>
-          <t>7a4c1e9b-3d2f-4b8a-a6c5-1e0d9f8b7a44</t>
-        </is>
-      </c>
-      <c r="I9" s="6" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>driver_id</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>uuid</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>có</t>
-        </is>
-      </c>
-      <c r="E10" s="6" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="F10" s="7" t="inlineStr">
-        <is>
-          <t>drivers.driver_id (khi xóa: chặn xóa)</t>
-        </is>
-      </c>
-      <c r="G10" s="6" t="inlineStr">
-        <is>
-          <t>Tài xế của chuyến, nếu biết.</t>
-        </is>
-      </c>
-      <c r="H10" s="6" t="inlineStr">
-        <is>
-          <t>6e3b9d2a-4c1f-4e8b-9a7d-0c2e5f1b8d66</t>
-        </is>
-      </c>
-      <c r="I10" s="6" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>started_at</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>timestamptz</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E11" s="6" t="n"/>
-      <c r="F11" s="6" t="n"/>
-      <c r="G11" s="6" t="inlineStr">
-        <is>
-          <t>Thời điểm bắt đầu chuyến.</t>
-        </is>
-      </c>
-      <c r="H11" s="6" t="inlineStr">
-        <is>
-          <t>2026-09-15T00:30:00Z</t>
-        </is>
-      </c>
-      <c r="I11" s="6" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>ended_at</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>timestamptz</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>có</t>
-        </is>
-      </c>
-      <c r="E12" s="6" t="n"/>
-      <c r="F12" s="6" t="n"/>
-      <c r="G12" s="6" t="inlineStr">
-        <is>
-          <t>Thời điểm kết thúc; NULL khi đang chạy.</t>
-        </is>
-      </c>
-      <c r="H12" s="6" t="inlineStr">
-        <is>
-          <t>2026-09-15T06:10:00Z</t>
-        </is>
-      </c>
-      <c r="I12" s="6" t="n"/>
-    </row>
-    <row r="13" ht="27" customHeight="1">
-      <c r="A13" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>declared_load_status</t>
-        </is>
-      </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>varchar(20)</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="inlineStr">
-        <is>
-          <t>có</t>
-        </is>
-      </c>
-      <c r="E13" s="6" t="n"/>
-      <c r="F13" s="6" t="n"/>
-      <c r="G13" s="6" t="inlineStr">
-        <is>
-          <t>Trạng thái tải do tài xế khai báo. Giá trị: LOADED | EMPTY.</t>
-        </is>
-      </c>
-      <c r="H13" s="6" t="inlineStr">
-        <is>
-          <t>LOADED</t>
-        </is>
-      </c>
-      <c r="I13" s="6" t="n"/>
-    </row>
-    <row r="14" ht="27" customHeight="1">
-      <c r="A14" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="B14" s="6" t="inlineStr">
-        <is>
-          <t>inferred_load_status</t>
-        </is>
-      </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>varchar(20)</t>
-        </is>
-      </c>
-      <c r="D14" s="6" t="inlineStr">
-        <is>
-          <t>có</t>
-        </is>
-      </c>
-      <c r="E14" s="6" t="n"/>
-      <c r="F14" s="6" t="n"/>
-      <c r="G14" s="6" t="inlineStr">
-        <is>
-          <t>Trạng thái tải suy ra từ dữ liệu vận hành. Giá trị: LOADED | EMPTY.</t>
-        </is>
-      </c>
-      <c r="H14" s="6" t="inlineStr">
-        <is>
-          <t>LOADED</t>
-        </is>
-      </c>
-      <c r="I14" s="6" t="n"/>
-    </row>
-  </sheetData>
-  <autoFilter ref="A6:I14"/>
-  <hyperlinks>
-    <hyperlink ref="A2" location="'Tổng quan'!A1"/>
-    <hyperlink ref="F8" location="'organizations'!A1"/>
-    <hyperlink ref="F9" location="'vehicles'!A1"/>
-    <hyperlink ref="F10" location="'drivers'!A1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -51269,6 +51473,406 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet80.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="7" max="7"/>
+    <col width="42" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>62. trips: Chuyến đi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t>← Tổng quan</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>Miền nghiệp vụ: Chưa phân miền (unassigned)   ·   Chủ sở hữu dữ liệu: Khách hàng   ·   Tính năng: F-A9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>Một chuyến đi của xe. F-A9 đang tạm dừng: chưa có khái niệm chuyến đi.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5"/>
+    <row r="6" ht="27" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Cột</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Kiểu dữ liệu</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Cho phép rỗng</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>Khóa</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>Tham chiếu tới</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>Ý nghĩa</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>Ví dụ</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>Lưu lịch sử</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>trip_id</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>uuid</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="n"/>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>Mã nội bộ của chuyến đi.</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>2e1c8a5f-0b7d-4e9c-b4a3-6d5f1e8c2b76</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="n"/>
+    </row>
+    <row r="8" ht="27" customHeight="1">
+      <c r="A8" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>organization_id</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>uuid</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>organizations.organization_id (khi xóa: chặn xóa)</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>Tổ chức khách hàng sở hữu xe.</t>
+        </is>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>3f6c2a1e-8b4d-4e2a-9c1f-0a7d5b2e4c11</t>
+        </is>
+      </c>
+      <c r="I8" s="6" t="n"/>
+    </row>
+    <row r="9" ht="27" customHeight="1">
+      <c r="A9" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>vehicle_id</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>uuid</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>vehicles.vehicle_id (khi xóa: chặn xóa)</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>Xe thực hiện chuyến.</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>7a4c1e9b-3d2f-4b8a-a6c5-1e0d9f8b7a44</t>
+        </is>
+      </c>
+      <c r="I9" s="6" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>driver_id</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>uuid</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>drivers.driver_id (khi xóa: chặn xóa)</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>Tài xế của chuyến, nếu biết.</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>6e3b9d2a-4c1f-4e8b-9a7d-0c2e5f1b8d66</t>
+        </is>
+      </c>
+      <c r="I10" s="6" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>started_at</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>timestamptz</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="n"/>
+      <c r="F11" s="6" t="n"/>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>Thời điểm bắt đầu chuyến.</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-15T00:30:00Z</t>
+        </is>
+      </c>
+      <c r="I11" s="6" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>ended_at</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>timestamptz</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="n"/>
+      <c r="F12" s="6" t="n"/>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>Thời điểm kết thúc; NULL khi đang chạy.</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-15T06:10:00Z</t>
+        </is>
+      </c>
+      <c r="I12" s="6" t="n"/>
+    </row>
+    <row r="13" ht="27" customHeight="1">
+      <c r="A13" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>declared_load_status</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>varchar(20)</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="n"/>
+      <c r="F13" s="6" t="n"/>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>Trạng thái tải do tài xế khai báo. Giá trị: LOADED | EMPTY.</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>LOADED</t>
+        </is>
+      </c>
+      <c r="I13" s="6" t="n"/>
+    </row>
+    <row r="14" ht="27" customHeight="1">
+      <c r="A14" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>inferred_load_status</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>varchar(20)</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="n"/>
+      <c r="F14" s="6" t="n"/>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>Trạng thái tải suy ra từ dữ liệu vận hành. Giá trị: LOADED | EMPTY.</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>LOADED</t>
+        </is>
+      </c>
+      <c r="I14" s="6" t="n"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A6:I14"/>
+  <hyperlinks>
+    <hyperlink ref="A2" location="'Tổng quan'!A1"/>
+    <hyperlink ref="F8" location="'organizations'!A1"/>
+    <hyperlink ref="F9" location="'vehicles'!A1"/>
+    <hyperlink ref="F10" location="'drivers'!A1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/docs/design/domain-model/domain-model.xlsx
+++ b/docs/design/domain-model/domain-model.xlsx
@@ -76,17 +76,19 @@
     <sheet name="tariffs" sheetId="67" state="visible" r:id="rId67"/>
     <sheet name="tariff_history" sheetId="68" state="visible" r:id="rId68"/>
     <sheet name="tariff_versions" sheetId="69" state="visible" r:id="rId69"/>
-    <sheet name="payments" sheetId="70" state="visible" r:id="rId70"/>
-    <sheet name="wallets" sheetId="71" state="visible" r:id="rId71"/>
-    <sheet name="wallet_transactions" sheetId="72" state="visible" r:id="rId72"/>
-    <sheet name="invoices" sheetId="73" state="visible" r:id="rId73"/>
-    <sheet name="invoice_lines" sheetId="74" state="visible" r:id="rId74"/>
-    <sheet name="subscription_plans" sheetId="75" state="visible" r:id="rId75"/>
-    <sheet name="plan_features" sheetId="76" state="visible" r:id="rId76"/>
-    <sheet name="subscriptions" sheetId="77" state="visible" r:id="rId77"/>
-    <sheet name="driver_scores" sheetId="78" state="visible" r:id="rId78"/>
-    <sheet name="promotion_campaigns" sheetId="79" state="visible" r:id="rId79"/>
-    <sheet name="trips" sheetId="80" state="visible" r:id="rId80"/>
+    <sheet name="charging_session_charges" sheetId="70" state="visible" r:id="rId70"/>
+    <sheet name="charging_session_charge_history" sheetId="71" state="visible" r:id="rId71"/>
+    <sheet name="payments" sheetId="72" state="visible" r:id="rId72"/>
+    <sheet name="wallets" sheetId="73" state="visible" r:id="rId73"/>
+    <sheet name="wallet_transactions" sheetId="74" state="visible" r:id="rId74"/>
+    <sheet name="invoices" sheetId="75" state="visible" r:id="rId75"/>
+    <sheet name="invoice_lines" sheetId="76" state="visible" r:id="rId76"/>
+    <sheet name="subscription_plans" sheetId="77" state="visible" r:id="rId77"/>
+    <sheet name="plan_features" sheetId="78" state="visible" r:id="rId78"/>
+    <sheet name="subscriptions" sheetId="79" state="visible" r:id="rId79"/>
+    <sheet name="driver_scores" sheetId="80" state="visible" r:id="rId80"/>
+    <sheet name="promotion_campaigns" sheetId="81" state="visible" r:id="rId81"/>
+    <sheet name="trips" sheetId="82" state="visible" r:id="rId82"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'organizations'!$A$7:$I$20</definedName>
@@ -157,17 +159,19 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="66" hidden="1">'tariffs'!$A$7:$I$16</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="67" hidden="1">'tariff_history'!$A$7:$I$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="68" hidden="1">'tariff_versions'!$A$6:$I$16</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="69" hidden="1">'payments'!$A$6:$I$16</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="70" hidden="1">'wallets'!$A$6:$I$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="71" hidden="1">'wallet_transactions'!$A$6:$I$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="72" hidden="1">'invoices'!$A$6:$I$16</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="73" hidden="1">'invoice_lines'!$A$6:$I$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="74" hidden="1">'subscription_plans'!$A$6:$I$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="75" hidden="1">'plan_features'!$A$6:$I$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="76" hidden="1">'subscriptions'!$A$6:$I$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="77" hidden="1">'driver_scores'!$A$6:$I$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="78" hidden="1">'promotion_campaigns'!$A$6:$I$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="79" hidden="1">'trips'!$A$6:$I$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="69" hidden="1">'charging_session_charges'!$A$7:$I$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="70" hidden="1">'charging_session_charge_history'!$A$7:$I$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="71" hidden="1">'payments'!$A$6:$I$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="72" hidden="1">'wallets'!$A$6:$I$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="73" hidden="1">'wallet_transactions'!$A$6:$I$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="74" hidden="1">'invoices'!$A$6:$I$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="75" hidden="1">'invoice_lines'!$A$6:$I$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="76" hidden="1">'subscription_plans'!$A$6:$I$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="77" hidden="1">'plan_features'!$A$6:$I$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="78" hidden="1">'subscriptions'!$A$6:$I$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="79" hidden="1">'driver_scores'!$A$6:$I$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="80" hidden="1">'promotion_campaigns'!$A$6:$I$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="81" hidden="1">'trips'!$A$6:$I$14</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -656,7 +660,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I122"/>
+  <dimension ref="A1:I124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -687,7 +691,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>79 bảng trong 16 miền nghiệp vụ: 59 bảng chính, 17 bảng lịch sử (N.h), 3 bảng trạng thái. Bấm vào tên bảng hoặc «→ Mở» để mở sheet chi tiết của bảng; chú giải và các quyết định còn mở nằm ở cuối trang.</t>
+          <t>81 bảng trong 16 miền nghiệp vụ: 60 bảng chính, 18 bảng lịch sử (N.h), 3 bảng trạng thái. Bấm vào tên bảng hoặc «→ Mở» để mở sheet chi tiết của bảng; chú giải và các quyết định còn mở nằm ở cuối trang.</t>
         </is>
       </c>
     </row>
@@ -3983,7 +3987,7 @@
       </c>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t>11 bảng</t>
+          <t>13 bảng</t>
         </is>
       </c>
       <c r="D84" s="5" t="n"/>
@@ -4136,7 +4140,7 @@
         </is>
       </c>
     </row>
-    <row r="88" ht="27" customHeight="1">
+    <row r="88" ht="108" customHeight="1">
       <c r="A88" s="6" t="inlineStr">
         <is>
           <t>52</t>
@@ -4149,31 +4153,31 @@
       </c>
       <c r="C88" s="7" t="inlineStr">
         <is>
-          <t>payments</t>
+          <t>charging_session_charges</t>
         </is>
       </c>
       <c r="D88" s="7" t="inlineStr">
         <is>
-          <t>Thanh toán</t>
+          <t>Phí phiên sạc</t>
         </is>
       </c>
       <c r="E88" s="6" t="inlineStr">
         <is>
-          <t>Khách hàng</t>
+          <t>Hai bên</t>
         </is>
       </c>
       <c r="F88" s="6" t="inlineStr">
         <is>
-          <t>F-H1</t>
+          <t>F-H1, F-H3</t>
         </is>
       </c>
       <c r="G88" s="6" t="inlineStr">
         <is>
-          <t>Một lần thanh toán qua cổng thanh toán hoặc ví, thường cho một phiên sạc.</t>
+          <t>Chi phí của một lần sạc (BL-10, CE-12, PAY-10): đơn giá chốt khi quét mã, số kWh tính tiền và số tiền. Thuộc miền thanh toán, trỏ tới phiên sạc, không bao giờ ngược lại. Số tiền là số đã thu sau làm tròn nên được lưu cố định, giống nhau trên biên nhận, thanh toán và hóa đơn điện tử. Bật lịch sử thay đổi: cho tính tiền một khoản bị giữ là quyết định của con người. Không sửa sau khi BILLED; sai sót được điều chỉnh bằng hoàn tiền hoặc hóa đơn điều chỉnh. Ràng buộc kiểm tra (BL-10): khoản BILLED phải đủ điện năng, nguồn, số tiền và thời điểm; khoản QUOTED hoặc VOID không có các giá trị đó.</t>
         </is>
       </c>
       <c r="H88" s="6" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="I88" s="7" t="inlineStr">
         <is>
@@ -4181,10 +4185,10 @@
         </is>
       </c>
     </row>
-    <row r="89" ht="27" customHeight="1">
+    <row r="89" ht="54" customHeight="1">
       <c r="A89" s="6" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>52.h</t>
         </is>
       </c>
       <c r="B89" s="6" t="inlineStr">
@@ -4194,31 +4198,31 @@
       </c>
       <c r="C89" s="7" t="inlineStr">
         <is>
-          <t>wallets</t>
+          <t>charging_session_charge_history</t>
         </is>
       </c>
       <c r="D89" s="7" t="inlineStr">
         <is>
-          <t>Ví</t>
+          <t>Lịch sử phí phiên sạc</t>
         </is>
       </c>
       <c r="E89" s="6" t="inlineStr">
         <is>
-          <t>Khách hàng</t>
+          <t>Hai bên</t>
         </is>
       </c>
       <c r="F89" s="6" t="inlineStr">
         <is>
-          <t>F-H2</t>
+          <t>F-H1, F-H3</t>
         </is>
       </c>
       <c r="G89" s="6" t="inlineStr">
         <is>
-          <t>Số dư trả trước của một tài xế hoặc của cả tổ chức.</t>
+          <t>Mọi phiên bản trước đây của một dòng trong bảng charging_session_charges: bản sao toàn bộ dòng, chụp ngay trước khi thay đổi và được trigger ghi trong cùng giao dịch. Do công cụ domain-model tự sinh từ @tracked *, không bao giờ viết tay.</t>
         </is>
       </c>
       <c r="H89" s="6" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="I89" s="7" t="inlineStr">
         <is>
@@ -4229,7 +4233,7 @@
     <row r="90" ht="27" customHeight="1">
       <c r="A90" s="6" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>53</t>
         </is>
       </c>
       <c r="B90" s="6" t="inlineStr">
@@ -4239,12 +4243,12 @@
       </c>
       <c r="C90" s="7" t="inlineStr">
         <is>
-          <t>wallet_transactions</t>
+          <t>payments</t>
         </is>
       </c>
       <c r="D90" s="7" t="inlineStr">
         <is>
-          <t>Giao dịch ví</t>
+          <t>Thanh toán</t>
         </is>
       </c>
       <c r="E90" s="6" t="inlineStr">
@@ -4254,16 +4258,16 @@
       </c>
       <c r="F90" s="6" t="inlineStr">
         <is>
-          <t>F-H2</t>
+          <t>F-H1</t>
         </is>
       </c>
       <c r="G90" s="6" t="inlineStr">
         <is>
-          <t>Biến động tiền vào/ra khỏi ví, chỉ ghi thêm.</t>
+          <t>Một lần thanh toán qua cổng thanh toán hoặc ví, thường cho một phiên sạc.</t>
         </is>
       </c>
       <c r="H90" s="6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I90" s="7" t="inlineStr">
         <is>
@@ -4274,7 +4278,7 @@
     <row r="91" ht="27" customHeight="1">
       <c r="A91" s="6" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>54</t>
         </is>
       </c>
       <c r="B91" s="6" t="inlineStr">
@@ -4284,12 +4288,12 @@
       </c>
       <c r="C91" s="7" t="inlineStr">
         <is>
-          <t>invoices</t>
+          <t>wallets</t>
         </is>
       </c>
       <c r="D91" s="7" t="inlineStr">
         <is>
-          <t>Hóa đơn</t>
+          <t>Ví</t>
         </is>
       </c>
       <c r="E91" s="6" t="inlineStr">
@@ -4299,16 +4303,16 @@
       </c>
       <c r="F91" s="6" t="inlineStr">
         <is>
-          <t>F-H3, F-H4</t>
+          <t>F-H2</t>
         </is>
       </c>
       <c r="G91" s="6" t="inlineStr">
         <is>
-          <t>Một hóa đơn điện tử hợp lệ. Khi đã PHÁT HÀNH thì không sửa, chỉ điều chỉnh hoặc hủy bằng hóa đơn mới.</t>
+          <t>Số dư trả trước của một tài xế hoặc của cả tổ chức.</t>
         </is>
       </c>
       <c r="H91" s="6" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="I91" s="7" t="inlineStr">
         <is>
@@ -4319,7 +4323,7 @@
     <row r="92" ht="27" customHeight="1">
       <c r="A92" s="6" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>55</t>
         </is>
       </c>
       <c r="B92" s="6" t="inlineStr">
@@ -4329,12 +4333,12 @@
       </c>
       <c r="C92" s="7" t="inlineStr">
         <is>
-          <t>invoice_lines</t>
+          <t>wallet_transactions</t>
         </is>
       </c>
       <c r="D92" s="7" t="inlineStr">
         <is>
-          <t>Dòng hóa đơn</t>
+          <t>Giao dịch ví</t>
         </is>
       </c>
       <c r="E92" s="6" t="inlineStr">
@@ -4344,12 +4348,12 @@
       </c>
       <c r="F92" s="6" t="inlineStr">
         <is>
-          <t>F-H3, F-H4</t>
+          <t>F-H2</t>
         </is>
       </c>
       <c r="G92" s="6" t="inlineStr">
         <is>
-          <t>Một dòng của hóa đơn: một phiên sạc hoặc một kỳ thuê bao.</t>
+          <t>Biến động tiền vào/ra khỏi ví, chỉ ghi thêm.</t>
         </is>
       </c>
       <c r="H92" s="6" t="n">
@@ -4361,130 +4365,130 @@
         </is>
       </c>
     </row>
-    <row r="93" ht="54" customHeight="1">
+    <row r="93" ht="27" customHeight="1">
       <c r="A93" s="6" t="inlineStr">
         <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="B93" s="6" t="inlineStr">
+        <is>
+          <t>Thanh toán &amp; hóa đơn (billing)</t>
+        </is>
+      </c>
+      <c r="C93" s="7" t="inlineStr">
+        <is>
+          <t>invoices</t>
+        </is>
+      </c>
+      <c r="D93" s="7" t="inlineStr">
+        <is>
+          <t>Hóa đơn</t>
+        </is>
+      </c>
+      <c r="E93" s="6" t="inlineStr">
+        <is>
+          <t>Khách hàng</t>
+        </is>
+      </c>
+      <c r="F93" s="6" t="inlineStr">
+        <is>
+          <t>F-H3, F-H4</t>
+        </is>
+      </c>
+      <c r="G93" s="6" t="inlineStr">
+        <is>
+          <t>Một hóa đơn điện tử hợp lệ. Khi đã PHÁT HÀNH thì không sửa, chỉ điều chỉnh hoặc hủy bằng hóa đơn mới.</t>
+        </is>
+      </c>
+      <c r="H93" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="I93" s="7" t="inlineStr">
+        <is>
+          <t>→ Mở</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="27" customHeight="1">
+      <c r="A94" s="6" t="inlineStr">
+        <is>
           <t>57</t>
         </is>
       </c>
-      <c r="B93" s="6" t="inlineStr">
+      <c r="B94" s="6" t="inlineStr">
         <is>
           <t>Thanh toán &amp; hóa đơn (billing)</t>
         </is>
       </c>
-      <c r="C93" s="7" t="inlineStr">
+      <c r="C94" s="7" t="inlineStr">
+        <is>
+          <t>invoice_lines</t>
+        </is>
+      </c>
+      <c r="D94" s="7" t="inlineStr">
+        <is>
+          <t>Dòng hóa đơn</t>
+        </is>
+      </c>
+      <c r="E94" s="6" t="inlineStr">
+        <is>
+          <t>Khách hàng</t>
+        </is>
+      </c>
+      <c r="F94" s="6" t="inlineStr">
+        <is>
+          <t>F-H3, F-H4</t>
+        </is>
+      </c>
+      <c r="G94" s="6" t="inlineStr">
+        <is>
+          <t>Một dòng của hóa đơn: một phiên sạc hoặc một kỳ thuê bao.</t>
+        </is>
+      </c>
+      <c r="H94" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="I94" s="7" t="inlineStr">
+        <is>
+          <t>→ Mở</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="54" customHeight="1">
+      <c r="A95" s="6" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="B95" s="6" t="inlineStr">
+        <is>
+          <t>Thanh toán &amp; hóa đơn (billing)</t>
+        </is>
+      </c>
+      <c r="C95" s="7" t="inlineStr">
         <is>
           <t>subscription_plans</t>
         </is>
       </c>
-      <c r="D93" s="7" t="inlineStr">
+      <c r="D95" s="7" t="inlineStr">
         <is>
           <t>Gói dịch vụ</t>
         </is>
       </c>
-      <c r="E93" s="6" t="inlineStr">
+      <c r="E95" s="6" t="inlineStr">
         <is>
           <t>Nội bộ</t>
         </is>
       </c>
-      <c r="F93" s="6" t="inlineStr">
+      <c r="F95" s="6" t="inlineStr">
         <is>
           <t>F-H4</t>
         </is>
       </c>
-      <c r="G93" s="6" t="inlineStr">
+      <c r="G95" s="6" t="inlineStr">
         <is>
           <t>Một gói dịch vụ: mỗi gói là một dòng (GUEST là gói mặc định miễn phí, STANDARD, ADVANCED, PRO, ..., hoặc gói riêng cho một khách hàng); tính năng của gói nằm ở plan_features. Giá được tính theo từng tính năng (xem ghi chú của miền thanh toán).</t>
-        </is>
-      </c>
-      <c r="H93" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="I93" s="7" t="inlineStr">
-        <is>
-          <t>→ Mở</t>
-        </is>
-      </c>
-    </row>
-    <row r="94" ht="40.5" customHeight="1">
-      <c r="A94" s="6" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="B94" s="6" t="inlineStr">
-        <is>
-          <t>Thanh toán &amp; hóa đơn (billing)</t>
-        </is>
-      </c>
-      <c r="C94" s="7" t="inlineStr">
-        <is>
-          <t>plan_features</t>
-        </is>
-      </c>
-      <c r="D94" s="7" t="inlineStr">
-        <is>
-          <t>Tính năng của gói dịch vụ</t>
-        </is>
-      </c>
-      <c r="E94" s="6" t="inlineStr">
-        <is>
-          <t>Nội bộ</t>
-        </is>
-      </c>
-      <c r="F94" s="6" t="inlineStr">
-        <is>
-          <t>F-H4</t>
-        </is>
-      </c>
-      <c r="G94" s="6" t="inlineStr">
-        <is>
-          <t>Mỗi gói dịch vụ gồm những tính năng nào. Gói dịch vụ là dữ liệu, nên G3 có thể tạo gói mới (Pro, Max, gói riêng cho một khách hàng) trên portal mà không cần lập trình viên; chỉ tính năng hoàn toàn mới mới cần viết mã.</t>
-        </is>
-      </c>
-      <c r="H94" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="I94" s="7" t="inlineStr">
-        <is>
-          <t>→ Mở</t>
-        </is>
-      </c>
-    </row>
-    <row r="95" ht="27" customHeight="1">
-      <c r="A95" s="6" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="B95" s="6" t="inlineStr">
-        <is>
-          <t>Thanh toán &amp; hóa đơn (billing)</t>
-        </is>
-      </c>
-      <c r="C95" s="7" t="inlineStr">
-        <is>
-          <t>subscriptions</t>
-        </is>
-      </c>
-      <c r="D95" s="7" t="inlineStr">
-        <is>
-          <t>Thuê bao</t>
-        </is>
-      </c>
-      <c r="E95" s="6" t="inlineStr">
-        <is>
-          <t>Khách hàng</t>
-        </is>
-      </c>
-      <c r="F95" s="6" t="inlineStr">
-        <is>
-          <t>F-H4</t>
-        </is>
-      </c>
-      <c r="G95" s="6" t="inlineStr">
-        <is>
-          <t>Một xe đăng ký một gói; quá hạn thanh toán sẽ khóa tính năng.</t>
         </is>
       </c>
       <c r="H95" s="6" t="n">
@@ -4496,29 +4500,52 @@
         </is>
       </c>
     </row>
-    <row r="96" ht="27" customHeight="1">
-      <c r="A96" s="5" t="n"/>
-      <c r="B96" s="5" t="inlineStr">
-        <is>
-          <t>Chấm điểm tài xế (scoring)</t>
-        </is>
-      </c>
-      <c r="C96" s="5" t="inlineStr">
-        <is>
-          <t>1 bảng</t>
-        </is>
-      </c>
-      <c r="D96" s="5" t="n"/>
-      <c r="E96" s="5" t="n"/>
-      <c r="F96" s="5" t="n"/>
-      <c r="G96" s="5" t="inlineStr">
-        <is>
-          <t>Chấm điểm an toàn cho tài xế từ hành vi lái xe.
-• Mỗi tuần, mỗi tài xế có một điểm, tính từ dữ liệu vận hành của xe họ lái.</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
+    <row r="96" ht="40.5" customHeight="1">
+      <c r="A96" s="6" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="B96" s="6" t="inlineStr">
+        <is>
+          <t>Thanh toán &amp; hóa đơn (billing)</t>
+        </is>
+      </c>
+      <c r="C96" s="7" t="inlineStr">
+        <is>
+          <t>plan_features</t>
+        </is>
+      </c>
+      <c r="D96" s="7" t="inlineStr">
+        <is>
+          <t>Tính năng của gói dịch vụ</t>
+        </is>
+      </c>
+      <c r="E96" s="6" t="inlineStr">
+        <is>
+          <t>Nội bộ</t>
+        </is>
+      </c>
+      <c r="F96" s="6" t="inlineStr">
+        <is>
+          <t>F-H4</t>
+        </is>
+      </c>
+      <c r="G96" s="6" t="inlineStr">
+        <is>
+          <t>Mỗi gói dịch vụ gồm những tính năng nào. Gói dịch vụ là dữ liệu, nên G3 có thể tạo gói mới (Pro, Max, gói riêng cho một khách hàng) trên portal mà không cần lập trình viên; chỉ tính năng hoàn toàn mới mới cần viết mã.</t>
+        </is>
+      </c>
+      <c r="H96" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="I96" s="7" t="inlineStr">
+        <is>
+          <t>→ Mở</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="27" customHeight="1">
       <c r="A97" s="6" t="inlineStr">
         <is>
           <t>60</t>
@@ -4526,17 +4553,17 @@
       </c>
       <c r="B97" s="6" t="inlineStr">
         <is>
-          <t>Chấm điểm tài xế (scoring)</t>
+          <t>Thanh toán &amp; hóa đơn (billing)</t>
         </is>
       </c>
       <c r="C97" s="7" t="inlineStr">
         <is>
-          <t>driver_scores</t>
+          <t>subscriptions</t>
         </is>
       </c>
       <c r="D97" s="7" t="inlineStr">
         <is>
-          <t>Điểm tài xế</t>
+          <t>Thuê bao</t>
         </is>
       </c>
       <c r="E97" s="6" t="inlineStr">
@@ -4546,12 +4573,12 @@
       </c>
       <c r="F97" s="6" t="inlineStr">
         <is>
-          <t>F-K1</t>
+          <t>F-H4</t>
         </is>
       </c>
       <c r="G97" s="6" t="inlineStr">
         <is>
-          <t>Điểm an toàn hằng tuần của tài xế, tính từ dữ liệu vận hành xe.</t>
+          <t>Một xe đăng ký một gói; quá hạn thanh toán sẽ khóa tính năng.</t>
         </is>
       </c>
       <c r="H97" s="6" t="n">
@@ -4567,12 +4594,12 @@
       <c r="A98" s="5" t="n"/>
       <c r="B98" s="5" t="inlineStr">
         <is>
-          <t>Chưa phân miền (unassigned)</t>
+          <t>Chấm điểm tài xế (scoring)</t>
         </is>
       </c>
       <c r="C98" s="5" t="inlineStr">
         <is>
-          <t>2 bảng</t>
+          <t>1 bảng</t>
         </is>
       </c>
       <c r="D98" s="5" t="n"/>
@@ -4580,7 +4607,8 @@
       <c r="F98" s="5" t="n"/>
       <c r="G98" s="5" t="inlineStr">
         <is>
-          <t>Các tính năng chưa được quyết định thuộc miền nghiệp vụ nào (xem feature-list.md).</t>
+          <t>Chấm điểm an toàn cho tài xế từ hành vi lái xe.
+• Mỗi tuần, mỗi tài xế có một điểm, tính từ dữ liệu vận hành của xe họ lái.</t>
         </is>
       </c>
     </row>
@@ -4592,344 +4620,410 @@
       </c>
       <c r="B99" s="6" t="inlineStr">
         <is>
+          <t>Chấm điểm tài xế (scoring)</t>
+        </is>
+      </c>
+      <c r="C99" s="7" t="inlineStr">
+        <is>
+          <t>driver_scores</t>
+        </is>
+      </c>
+      <c r="D99" s="7" t="inlineStr">
+        <is>
+          <t>Điểm tài xế</t>
+        </is>
+      </c>
+      <c r="E99" s="6" t="inlineStr">
+        <is>
+          <t>Khách hàng</t>
+        </is>
+      </c>
+      <c r="F99" s="6" t="inlineStr">
+        <is>
+          <t>F-K1</t>
+        </is>
+      </c>
+      <c r="G99" s="6" t="inlineStr">
+        <is>
+          <t>Điểm an toàn hằng tuần của tài xế, tính từ dữ liệu vận hành xe.</t>
+        </is>
+      </c>
+      <c r="H99" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="I99" s="7" t="inlineStr">
+        <is>
+          <t>→ Mở</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="27" customHeight="1">
+      <c r="A100" s="5" t="n"/>
+      <c r="B100" s="5" t="inlineStr">
+        <is>
           <t>Chưa phân miền (unassigned)</t>
         </is>
       </c>
-      <c r="C99" s="7" t="inlineStr">
+      <c r="C100" s="5" t="inlineStr">
+        <is>
+          <t>2 bảng</t>
+        </is>
+      </c>
+      <c r="D100" s="5" t="n"/>
+      <c r="E100" s="5" t="n"/>
+      <c r="F100" s="5" t="n"/>
+      <c r="G100" s="5" t="inlineStr">
+        <is>
+          <t>Các tính năng chưa được quyết định thuộc miền nghiệp vụ nào (xem feature-list.md).</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="6" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="B101" s="6" t="inlineStr">
+        <is>
+          <t>Chưa phân miền (unassigned)</t>
+        </is>
+      </c>
+      <c r="C101" s="7" t="inlineStr">
         <is>
           <t>promotion_campaigns</t>
         </is>
       </c>
-      <c r="D99" s="7" t="inlineStr">
+      <c r="D101" s="7" t="inlineStr">
         <is>
           <t>Chiến dịch khuyến mãi</t>
         </is>
       </c>
-      <c r="E99" s="6" t="inlineStr">
+      <c r="E101" s="6" t="inlineStr">
         <is>
           <t>Nội bộ</t>
         </is>
       </c>
-      <c r="F99" s="6" t="inlineStr">
+      <c r="F101" s="6" t="inlineStr">
         <is>
           <t>F-F4</t>
         </is>
       </c>
-      <c r="G99" s="6" t="inlineStr">
+      <c r="G101" s="6" t="inlineStr">
         <is>
           <t>Một chiến dịch nhắc bảo dưỡng hoặc khuyến mãi.</t>
         </is>
       </c>
-      <c r="H99" s="6" t="n">
+      <c r="H101" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="I99" s="7" t="inlineStr">
+      <c r="I101" s="7" t="inlineStr">
         <is>
           <t>→ Mở</t>
         </is>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" s="6" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="B100" s="6" t="inlineStr">
+    <row r="102">
+      <c r="A102" s="6" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="B102" s="6" t="inlineStr">
         <is>
           <t>Chưa phân miền (unassigned)</t>
         </is>
       </c>
-      <c r="C100" s="7" t="inlineStr">
+      <c r="C102" s="7" t="inlineStr">
         <is>
           <t>trips</t>
         </is>
       </c>
-      <c r="D100" s="7" t="inlineStr">
+      <c r="D102" s="7" t="inlineStr">
         <is>
           <t>Chuyến đi</t>
         </is>
       </c>
-      <c r="E100" s="6" t="inlineStr">
+      <c r="E102" s="6" t="inlineStr">
         <is>
           <t>Khách hàng</t>
         </is>
       </c>
-      <c r="F100" s="6" t="inlineStr">
+      <c r="F102" s="6" t="inlineStr">
         <is>
           <t>F-A9</t>
         </is>
       </c>
-      <c r="G100" s="6" t="inlineStr">
+      <c r="G102" s="6" t="inlineStr">
         <is>
           <t>Một chuyến đi của xe. F-A9 đang tạm dừng: chưa có khái niệm chuyến đi.</t>
         </is>
       </c>
-      <c r="H100" s="6" t="n">
+      <c r="H102" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="I100" s="7" t="inlineStr">
+      <c r="I102" s="7" t="inlineStr">
         <is>
           <t>→ Mở</t>
         </is>
       </c>
     </row>
-    <row r="101"/>
-    <row r="102" ht="27" customHeight="1">
-      <c r="A102" s="4" t="inlineStr">
+    <row r="103"/>
+    <row r="104" ht="27" customHeight="1">
+      <c r="A104" s="4" t="inlineStr">
         <is>
           <t>Chú giải</t>
         </is>
       </c>
-      <c r="B102" s="4" t="inlineStr">
+      <c r="B104" s="4" t="inlineStr">
         <is>
           <t>Ý nghĩa</t>
         </is>
       </c>
     </row>
-    <row r="103" ht="108" customHeight="1">
-      <c r="A103" s="6" t="inlineStr">
+    <row r="105" ht="108" customHeight="1">
+      <c r="A105" s="6" t="inlineStr">
         <is>
           <t>Chủ sở hữu dữ liệu: Khách hàng</t>
         </is>
       </c>
-      <c r="B103" s="6" t="inlineStr">
+      <c r="B105" s="6" t="inlineStr">
         <is>
           <t>Thuộc về một tổ chức (thường là khách hàng; công ty G3 cũng có thể sở hữu); có cột organization_id hoặc lấy qua bảng cha (DM-24).</t>
         </is>
       </c>
     </row>
-    <row r="104" ht="94.5" customHeight="1">
-      <c r="A104" s="6" t="inlineStr">
+    <row r="106" ht="94.5" customHeight="1">
+      <c r="A106" s="6" t="inlineStr">
         <is>
           <t>Chủ sở hữu dữ liệu: Nội bộ</t>
         </is>
       </c>
-      <c r="B104" s="6" t="inlineStr">
+      <c r="B106" s="6" t="inlineStr">
         <is>
           <t>Dữ liệu của chính chúng ta (đơn vị vận hành nền tảng), dùng chung cho mọi tổ chức.</t>
         </is>
       </c>
     </row>
-    <row r="105" ht="94.5" customHeight="1">
-      <c r="A105" s="6" t="inlineStr">
+    <row r="107" ht="94.5" customHeight="1">
+      <c r="A107" s="6" t="inlineStr">
         <is>
           <t>Chủ sở hữu dữ liệu: Hai bên</t>
         </is>
       </c>
-      <c r="B105" s="6" t="inlineStr">
+      <c r="B107" s="6" t="inlineStr">
         <is>
           <t>Tài sản của G3 được khách hàng sử dụng; cả hai bên cùng liên quan.</t>
         </is>
       </c>
     </row>
-    <row r="106" ht="121.5" customHeight="1">
-      <c r="A106" s="6" t="inlineStr">
+    <row r="108" ht="121.5" customHeight="1">
+      <c r="A108" s="6" t="inlineStr">
         <is>
           <t>Chủ sở hữu dữ liệu: Chưa quyết định</t>
         </is>
       </c>
-      <c r="B106" s="6" t="inlineStr">
+      <c r="B108" s="6" t="inlineStr">
         <is>
           <t>Đang chờ một quyết định còn mở (xem cuối trang).</t>
         </is>
       </c>
     </row>
-    <row r="107" ht="81" customHeight="1">
-      <c r="A107" s="6" t="inlineStr">
+    <row r="109" ht="81" customHeight="1">
+      <c r="A109" s="6" t="inlineStr">
         <is>
           <t>Miền nghiệp vụ (domain)</t>
         </is>
       </c>
-      <c r="B107" s="6" t="inlineStr">
+      <c r="B109" s="6" t="inlineStr">
         <is>
           <t>Một phần của hệ thống sở hữu dữ liệu riêng, ví dụ Xe, Trạm sạc, Thanh toán. Mỗi miền gồm một hoặc nhiều bảng.</t>
         </is>
       </c>
     </row>
-    <row r="108" ht="54" customHeight="1">
-      <c r="A108" s="6" t="inlineStr">
+    <row r="110" ht="54" customHeight="1">
+      <c r="A110" s="6" t="inlineStr">
         <is>
           <t>Bảng</t>
         </is>
       </c>
-      <c r="B108" s="6" t="inlineStr">
+      <c r="B110" s="6" t="inlineStr">
         <is>
           <t>Một loại dữ liệu được lưu, ví dụ Xe hoặc Phiên sạc. Mỗi bảng có một sheet riêng liệt kê từng cột.</t>
         </is>
       </c>
     </row>
-    <row r="109" ht="40.5" customHeight="1">
-      <c r="A109" s="6" t="inlineStr">
+    <row r="111" ht="40.5" customHeight="1">
+      <c r="A111" s="6" t="inlineStr">
         <is>
           <t>Tính năng</t>
         </is>
       </c>
-      <c r="B109" s="6" t="inlineStr">
+      <c r="B111" s="6" t="inlineStr">
         <is>
           <t>Mã tính năng trong danh sách tính năng (feature-list.md), ví dụ F-B2.</t>
         </is>
       </c>
     </row>
-    <row r="110" ht="67.5" customHeight="1">
-      <c r="A110" s="6" t="inlineStr">
+    <row r="112" ht="67.5" customHeight="1">
+      <c r="A112" s="6" t="inlineStr">
         <is>
           <t>PK / FK / UQ</t>
         </is>
       </c>
-      <c r="B110" s="6" t="inlineStr">
+      <c r="B112" s="6" t="inlineStr">
         <is>
           <t>PK: khóa chính (định danh duy nhất của dòng). FK: khóa ngoại (trỏ tới dòng của bảng khác). UQ: giá trị không được trùng.</t>
         </is>
       </c>
     </row>
-    <row r="111" ht="54" customHeight="1">
-      <c r="A111" s="6" t="inlineStr">
+    <row r="113" ht="54" customHeight="1">
+      <c r="A113" s="6" t="inlineStr">
         <is>
           <t>Ví dụ</t>
         </is>
       </c>
-      <c r="B111" s="6" t="inlineStr">
+      <c r="B113" s="6" t="inlineStr">
         <is>
           <t>Giá trị mẫu. Các mã ví dụ khớp nhau giữa các bảng, nên có thể lần theo một bản ghi mẫu qua nhiều sheet.</t>
         </is>
       </c>
     </row>
-    <row r="112" ht="40.5" customHeight="1">
-      <c r="A112" s="6" t="inlineStr">
+    <row r="114" ht="40.5" customHeight="1">
+      <c r="A114" s="6" t="inlineStr">
         <is>
           <t>NULL</t>
         </is>
       </c>
-      <c r="B112" s="6" t="inlineStr">
+      <c r="B114" s="6" t="inlineStr">
         <is>
           <t>Ô không có giá trị. Ý nghĩa của NULL được giải thích trong cột Ý nghĩa.</t>
         </is>
       </c>
     </row>
-    <row r="113" ht="81" customHeight="1">
-      <c r="A113" s="6" t="inlineStr">
+    <row r="115" ht="81" customHeight="1">
+      <c r="A115" s="6" t="inlineStr">
         <is>
           <t>🔍 Lưu lịch sử</t>
         </is>
       </c>
-      <c r="B113" s="6" t="inlineStr">
+      <c r="B115" s="6" t="inlineStr">
         <is>
           <t>Cột được theo dõi: khi cột này thay đổi, toàn bộ dòng cũ được chép sang bảng lịch sử (tên kết thúc bằng _history) kèm thời điểm và người thay đổi.</t>
         </is>
       </c>
     </row>
-    <row r="114"/>
-    <row r="115">
-      <c r="A115" s="8" t="inlineStr">
+    <row r="116"/>
+    <row r="117">
+      <c r="A117" s="8" t="inlineStr">
         <is>
           <t>Các view (giai đoạn đọc từ lịch sử)</t>
         </is>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" s="4" t="inlineStr">
+    <row r="118">
+      <c r="A118" s="4" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="B116" s="4" t="inlineStr">
+      <c r="B118" s="4" t="inlineStr">
         <is>
           <t>Mỗi dòng là</t>
         </is>
       </c>
-      <c r="C116" s="4" t="inlineStr">
+      <c r="C118" s="4" t="inlineStr">
         <is>
           <t>Các cột</t>
         </is>
       </c>
-      <c r="D116" s="4" t="inlineStr">
+      <c r="D118" s="4" t="inlineStr">
         <is>
           <t>Được dùng bởi</t>
         </is>
       </c>
     </row>
-    <row r="117" ht="94.5" customHeight="1">
-      <c r="A117" s="6" t="inlineStr">
+    <row r="119" ht="94.5" customHeight="1">
+      <c r="A119" s="6" t="inlineStr">
         <is>
           <t>vehicle_ownership_periods</t>
         </is>
       </c>
-      <c r="B117" s="6" t="inlineStr">
+      <c r="B119" s="6" t="inlineStr">
         <is>
           <t>một giai đoạn xe thuộc một chủ</t>
         </is>
       </c>
-      <c r="C117" s="6" t="inlineStr">
+      <c r="C119" s="6" t="inlineStr">
         <is>
           <t>vehicle_id, organization_id, owned_from, owned_until (NULL với chủ hiện tại)</t>
         </is>
       </c>
-      <c r="D117" s="6" t="inlineStr">
+      <c r="D119" s="6" t="inlineStr">
         <is>
           <t>lịch sử sở hữu và ngày bàn giao đầu tiên (VEH-02), "ngày đó xe của ai"</t>
         </is>
       </c>
     </row>
-    <row r="118" ht="94.5" customHeight="1">
-      <c r="A118" s="6" t="inlineStr">
+    <row r="120" ht="94.5" customHeight="1">
+      <c r="A120" s="6" t="inlineStr">
         <is>
           <t>battery_installation_periods</t>
         </is>
       </c>
-      <c r="B118" s="6" t="inlineStr">
+      <c r="B120" s="6" t="inlineStr">
         <is>
           <t>một lần pin nằm trên một xe</t>
         </is>
       </c>
-      <c r="C118" s="6" t="inlineStr">
+      <c r="C120" s="6" t="inlineStr">
         <is>
           <t>battery_id, vehicle_id, installed_from, installed_until (NULL khi đang lắp)</t>
         </is>
       </c>
-      <c r="D118" s="6" t="inlineStr">
+      <c r="D120" s="6" t="inlineStr">
         <is>
           <t>lịch sử sức khỏe pin qua các xe (MON-07), bộ đếm bảo hành pin (WAR-01)</t>
         </is>
       </c>
     </row>
-    <row r="119"/>
-    <row r="120">
-      <c r="A120" s="8" t="inlineStr">
+    <row r="121"/>
+    <row r="122">
+      <c r="A122" s="8" t="inlineStr">
         <is>
           <t>Các quyết định còn mở</t>
         </is>
       </c>
     </row>
-    <row r="121">
-      <c r="A121" s="4" t="inlineStr">
+    <row r="123">
+      <c r="A123" s="4" t="inlineStr">
         <is>
           <t>Mã</t>
         </is>
       </c>
-      <c r="B121" s="4" t="inlineStr">
+      <c r="B123" s="4" t="inlineStr">
         <is>
           <t>Câu hỏi</t>
         </is>
       </c>
-      <c r="C121" s="4" t="inlineStr">
+      <c r="C123" s="4" t="inlineStr">
         <is>
           <t>Ảnh hưởng tới</t>
         </is>
       </c>
     </row>
-    <row r="122" ht="54" customHeight="1">
-      <c r="A122" s="6" t="inlineStr">
+    <row r="124" ht="54" customHeight="1">
+      <c r="A124" s="6" t="inlineStr">
         <is>
           <t>D5</t>
         </is>
       </c>
-      <c r="B122" s="6" t="inlineStr">
+      <c r="B124" s="6" t="inlineStr">
         <is>
           <t>Ai trả tiền khi tài xế của đội xe sạc: ví của tài xế, ví của đội xe, hay tùy trường hợp?</t>
         </is>
       </c>
-      <c r="C122" s="6" t="inlineStr">
+      <c r="C124" s="6" t="inlineStr">
         <is>
           <t>wallets, payments</t>
         </is>
@@ -5141,39 +5235,45 @@
     <hyperlink ref="C87" location="'tariff_versions'!A1"/>
     <hyperlink ref="D87" location="'tariff_versions'!A1"/>
     <hyperlink ref="I87" location="'tariff_versions'!A1"/>
-    <hyperlink ref="C88" location="'payments'!A1"/>
-    <hyperlink ref="D88" location="'payments'!A1"/>
-    <hyperlink ref="I88" location="'payments'!A1"/>
-    <hyperlink ref="C89" location="'wallets'!A1"/>
-    <hyperlink ref="D89" location="'wallets'!A1"/>
-    <hyperlink ref="I89" location="'wallets'!A1"/>
-    <hyperlink ref="C90" location="'wallet_transactions'!A1"/>
-    <hyperlink ref="D90" location="'wallet_transactions'!A1"/>
-    <hyperlink ref="I90" location="'wallet_transactions'!A1"/>
-    <hyperlink ref="C91" location="'invoices'!A1"/>
-    <hyperlink ref="D91" location="'invoices'!A1"/>
-    <hyperlink ref="I91" location="'invoices'!A1"/>
-    <hyperlink ref="C92" location="'invoice_lines'!A1"/>
-    <hyperlink ref="D92" location="'invoice_lines'!A1"/>
-    <hyperlink ref="I92" location="'invoice_lines'!A1"/>
-    <hyperlink ref="C93" location="'subscription_plans'!A1"/>
-    <hyperlink ref="D93" location="'subscription_plans'!A1"/>
-    <hyperlink ref="I93" location="'subscription_plans'!A1"/>
-    <hyperlink ref="C94" location="'plan_features'!A1"/>
-    <hyperlink ref="D94" location="'plan_features'!A1"/>
-    <hyperlink ref="I94" location="'plan_features'!A1"/>
-    <hyperlink ref="C95" location="'subscriptions'!A1"/>
-    <hyperlink ref="D95" location="'subscriptions'!A1"/>
-    <hyperlink ref="I95" location="'subscriptions'!A1"/>
-    <hyperlink ref="C97" location="'driver_scores'!A1"/>
-    <hyperlink ref="D97" location="'driver_scores'!A1"/>
-    <hyperlink ref="I97" location="'driver_scores'!A1"/>
-    <hyperlink ref="C99" location="'promotion_campaigns'!A1"/>
-    <hyperlink ref="D99" location="'promotion_campaigns'!A1"/>
-    <hyperlink ref="I99" location="'promotion_campaigns'!A1"/>
-    <hyperlink ref="C100" location="'trips'!A1"/>
-    <hyperlink ref="D100" location="'trips'!A1"/>
-    <hyperlink ref="I100" location="'trips'!A1"/>
+    <hyperlink ref="C88" location="'charging_session_charges'!A1"/>
+    <hyperlink ref="D88" location="'charging_session_charges'!A1"/>
+    <hyperlink ref="I88" location="'charging_session_charges'!A1"/>
+    <hyperlink ref="C89" location="'charging_session_charge_history'!A1"/>
+    <hyperlink ref="D89" location="'charging_session_charge_history'!A1"/>
+    <hyperlink ref="I89" location="'charging_session_charge_history'!A1"/>
+    <hyperlink ref="C90" location="'payments'!A1"/>
+    <hyperlink ref="D90" location="'payments'!A1"/>
+    <hyperlink ref="I90" location="'payments'!A1"/>
+    <hyperlink ref="C91" location="'wallets'!A1"/>
+    <hyperlink ref="D91" location="'wallets'!A1"/>
+    <hyperlink ref="I91" location="'wallets'!A1"/>
+    <hyperlink ref="C92" location="'wallet_transactions'!A1"/>
+    <hyperlink ref="D92" location="'wallet_transactions'!A1"/>
+    <hyperlink ref="I92" location="'wallet_transactions'!A1"/>
+    <hyperlink ref="C93" location="'invoices'!A1"/>
+    <hyperlink ref="D93" location="'invoices'!A1"/>
+    <hyperlink ref="I93" location="'invoices'!A1"/>
+    <hyperlink ref="C94" location="'invoice_lines'!A1"/>
+    <hyperlink ref="D94" location="'invoice_lines'!A1"/>
+    <hyperlink ref="I94" location="'invoice_lines'!A1"/>
+    <hyperlink ref="C95" location="'subscription_plans'!A1"/>
+    <hyperlink ref="D95" location="'subscription_plans'!A1"/>
+    <hyperlink ref="I95" location="'subscription_plans'!A1"/>
+    <hyperlink ref="C96" location="'plan_features'!A1"/>
+    <hyperlink ref="D96" location="'plan_features'!A1"/>
+    <hyperlink ref="I96" location="'plan_features'!A1"/>
+    <hyperlink ref="C97" location="'subscriptions'!A1"/>
+    <hyperlink ref="D97" location="'subscriptions'!A1"/>
+    <hyperlink ref="I97" location="'subscriptions'!A1"/>
+    <hyperlink ref="C99" location="'driver_scores'!A1"/>
+    <hyperlink ref="D99" location="'driver_scores'!A1"/>
+    <hyperlink ref="I99" location="'driver_scores'!A1"/>
+    <hyperlink ref="C101" location="'promotion_campaigns'!A1"/>
+    <hyperlink ref="D101" location="'promotion_campaigns'!A1"/>
+    <hyperlink ref="I101" location="'promotion_campaigns'!A1"/>
+    <hyperlink ref="C102" location="'trips'!A1"/>
+    <hyperlink ref="D102" location="'trips'!A1"/>
+    <hyperlink ref="I102" location="'trips'!A1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -26166,7 +26266,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I66"/>
+  <dimension ref="A1:I67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -27276,6 +27376,19 @@
         </is>
       </c>
       <c r="C66" s="6" t="inlineStr">
+        <is>
+          <t>changed_by</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="27" customHeight="1">
+      <c r="A67" s="6" t="n"/>
+      <c r="B67" s="7" t="inlineStr">
+        <is>
+          <t>charging_session_charge_history</t>
+        </is>
+      </c>
+      <c r="C67" s="6" t="inlineStr">
         <is>
           <t>changed_by</t>
         </is>
@@ -27330,6 +27443,7 @@
     <hyperlink ref="B64" location="'charging_evse_history'!A1"/>
     <hyperlink ref="B65" location="'charging_connector_history'!A1"/>
     <hyperlink ref="B66" location="'tariff_history'!A1"/>
+    <hyperlink ref="B67" location="'charging_session_charge_history'!A1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -38041,7 +38155,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I50"/>
+  <dimension ref="A1:I51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -39181,7 +39295,7 @@
       <c r="A48" s="6" t="n"/>
       <c r="B48" s="7" t="inlineStr">
         <is>
-          <t>payments</t>
+          <t>charging_session_charges</t>
         </is>
       </c>
       <c r="C48" s="6" t="inlineStr">
@@ -39194,7 +39308,7 @@
       <c r="A49" s="6" t="n"/>
       <c r="B49" s="7" t="inlineStr">
         <is>
-          <t>wallet_transactions</t>
+          <t>payments</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
@@ -39207,10 +39321,23 @@
       <c r="A50" s="6" t="n"/>
       <c r="B50" s="7" t="inlineStr">
         <is>
+          <t>wallet_transactions</t>
+        </is>
+      </c>
+      <c r="C50" s="6" t="inlineStr">
+        <is>
+          <t>session_id</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="6" t="n"/>
+      <c r="B51" s="7" t="inlineStr">
+        <is>
           <t>invoice_lines</t>
         </is>
       </c>
-      <c r="C50" s="6" t="inlineStr">
+      <c r="C51" s="6" t="inlineStr">
         <is>
           <t>session_id</t>
         </is>
@@ -39230,9 +39357,10 @@
     <hyperlink ref="B45" location="'charging_session_events'!A1"/>
     <hyperlink ref="B46" location="'charging_session_measurements'!A1"/>
     <hyperlink ref="B47" location="'policy_violations'!A1"/>
-    <hyperlink ref="B48" location="'payments'!A1"/>
-    <hyperlink ref="B49" location="'wallet_transactions'!A1"/>
-    <hyperlink ref="B50" location="'invoice_lines'!A1"/>
+    <hyperlink ref="B48" location="'charging_session_charges'!A1"/>
+    <hyperlink ref="B49" location="'payments'!A1"/>
+    <hyperlink ref="B50" location="'wallet_transactions'!A1"/>
+    <hyperlink ref="B51" location="'invoice_lines'!A1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -45654,7 +45782,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -46163,12 +46291,40 @@
         </is>
       </c>
     </row>
+    <row r="21"/>
+    <row r="22">
+      <c r="A22" s="4" t="n"/>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>Được tham chiếu bởi bảng</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>Cột</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="n"/>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>charging_session_charges</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>tariff_version_id</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A6:I16"/>
   <hyperlinks>
     <hyperlink ref="A2" location="'Tổng quan'!A1"/>
     <hyperlink ref="F8" location="'tariffs'!A1"/>
     <hyperlink ref="F15" location="'users'!A1"/>
+    <hyperlink ref="B23" location="'charging_session_charges'!A1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -46853,6 +47009,1526 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:I28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="7" max="7"/>
+    <col width="42" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>52. charging_session_charges: Phí phiên sạc</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t>← Tổng quan</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>Miền nghiệp vụ: Thanh toán &amp; hóa đơn (billing)   ·   Chủ sở hữu dữ liệu: Hai bên   ·   Tính năng: F-H1, F-H3</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>Chi phí của một lần sạc (BL-10, CE-12, PAY-10): đơn giá chốt khi quét mã, số kWh tính tiền và số tiền. Thuộc miền thanh toán, trỏ tới phiên sạc, không bao giờ ngược lại. Số tiền là số đã thu sau làm tròn nên được lưu cố định, giống nhau trên biên nhận, thanh toán và hóa đơn điện tử. Bật lịch sử thay đổi: cho tính tiền một khoản bị giữ là quyết định của con người. Không sửa sau khi BILLED; sai sót được điều chỉnh bằng hoàn tiền hoặc hóa đơn điều chỉnh. Ràng buộc kiểm tra (BL-10): khoản BILLED phải đủ điện năng, nguồn, số tiền và thời điểm; khoản QUOTED hoặc VOID không có các giá trị đó.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>🔍 Lưu lịch sử: khi một cột có dấu 🔍 thay đổi, toàn bộ dòng cũ được chép sang bảng charging_session_charge_history.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6"/>
+    <row r="7" ht="27" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Cột</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Kiểu dữ liệu</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Cho phép rỗng</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>Khóa</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>Tham chiếu tới</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>Ý nghĩa</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>Ví dụ</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>Lưu lịch sử</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="27" customHeight="1">
+      <c r="A8" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>charging_session_charge_id</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>uuid</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="n"/>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>Mã nội bộ của khoản phí sạc.</t>
+        </is>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>2b8d4f0a-6c3e-4a9b-8d7f-1e4c9a2b8d66</t>
+        </is>
+      </c>
+      <c r="I8" s="6" t="n"/>
+    </row>
+    <row r="9" ht="27" customHeight="1">
+      <c r="A9" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>session_id</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>uuid</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>FK UQ</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>charging_sessions.session_id (khi xóa: chặn xóa)</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>Phiên sạc; mỗi phiên một khoản phí. Bên trả tiền đọc từ phiên (charging_sessions.organization_id, DM-24).</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>e5a2d8f1-4b7c-4e9a-b3d6-2c1f0e9a8dbb</t>
+        </is>
+      </c>
+      <c r="I9" s="6" t="inlineStr">
+        <is>
+          <t>🔍</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="27" customHeight="1">
+      <c r="A10" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>tariff_version_id</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>uuid</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>tariff_versions.tariff_version_id (khi xóa: chặn xóa)</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>Phiên bản biểu giá có giá đã hiển thị khi quét mã.</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>1a7c3e9f-5b2d-4f8a-9c6e-0d3b8f1a7c55</t>
+        </is>
+      </c>
+      <c r="I10" s="6" t="inlineStr">
+        <is>
+          <t>🔍</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="27" customHeight="1">
+      <c r="A11" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>price_per_kwh</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>numeric(12,2)</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="n"/>
+      <c r="F11" s="6" t="n"/>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>Đơn giá của khung giờ lúc quét mã, chưa gồm VAT, được chốt cho cả phiên (PAY-09).</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>4500.00</t>
+        </is>
+      </c>
+      <c r="I11" s="6" t="inlineStr">
+        <is>
+          <t>🔍</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>vat_rate_percent</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>numeric(4,2)</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="n"/>
+      <c r="F12" s="6" t="n"/>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>Thuế suất VAT được chốt cùng đơn giá.</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>10.00</t>
+        </is>
+      </c>
+      <c r="I12" s="6" t="inlineStr">
+        <is>
+          <t>🔍</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="54" customHeight="1">
+      <c r="A13" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>varchar(20)</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="n"/>
+      <c r="F13" s="6" t="n"/>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>QUOTED: giá đã chốt khi quét, phiên chưa xong. BILLED: đã tính tiền. ON_HOLD: không tự tính tiền, chờ xem xét (ví dụ chỉ số dừng và số đo cuối lệch nhau, CE-12). VOID: không thu phí (phiên ABANDONED).</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>BILLED</t>
+        </is>
+      </c>
+      <c r="I13" s="6" t="inlineStr">
+        <is>
+          <t>🔍</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="40.5" customHeight="1">
+      <c r="A14" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>status_reason</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>varchar(200)</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="n"/>
+      <c r="F14" s="6" t="n"/>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>Lý do khoản phí có trạng thái hiện tại: vì sao bị giữ lại, hoặc người xem xét đã kiểm tra gì trước khi cho tính tiền (DM-19); NULL nếu không cần giải thích.</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="I14" s="6" t="inlineStr">
+        <is>
+          <t>🔍</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="27" customHeight="1">
+      <c r="A15" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>energy_wh</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>numeric(24,3)</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="n"/>
+      <c r="F15" s="6" t="n"/>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>Điện năng tính tiền (Wh): thường là meter_stop_wh trừ meter_start_wh; NULL cho tới khi tính tiền.</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>192520.000</t>
+        </is>
+      </c>
+      <c r="I15" s="6" t="inlineStr">
+        <is>
+          <t>🔍</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="40.5" customHeight="1">
+      <c r="A16" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>energy_source</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>varchar(20)</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="n"/>
+      <c r="F16" s="6" t="n"/>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>Nguồn của energy_wh. METER_STOP: chỉ số đóng phiên của trụ. LAST_MEASUREMENT: số đo mới nhất, khi thiếu chỉ số dừng (CE-12).</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>METER_STOP</t>
+        </is>
+      </c>
+      <c r="I16" s="6" t="inlineStr">
+        <is>
+          <t>🔍</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="40.5" customHeight="1">
+      <c r="A17" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>amount_before_vat</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>numeric(14,2)</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="n"/>
+      <c r="F17" s="6" t="n"/>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>energy_wh / 1000 x đơn giá, làm tròn tới đồng; là số tiền đã thu nên được lưu, không tính lại. NULL cho tới khi tính tiền.</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>866340.00</t>
+        </is>
+      </c>
+      <c r="I17" s="6" t="inlineStr">
+        <is>
+          <t>🔍</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="27" customHeight="1">
+      <c r="A18" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>vat_amount</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>numeric(14,2)</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="n"/>
+      <c r="F18" s="6" t="n"/>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>VAT trên amount_before_vat, đã làm tròn; tổng tiền là tổng hai số. NULL cho tới khi tính tiền.</t>
+        </is>
+      </c>
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>86634.00</t>
+        </is>
+      </c>
+      <c r="I18" s="6" t="inlineStr">
+        <is>
+          <t>🔍</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>billed_at</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>timestamptz</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="n"/>
+      <c r="F19" s="6" t="n"/>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>Thời điểm chốt số tiền.</t>
+        </is>
+      </c>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-15T09:45:05Z</t>
+        </is>
+      </c>
+      <c r="I19" s="6" t="inlineStr">
+        <is>
+          <t>🔍</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>created_at</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>timestamptz</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="n"/>
+      <c r="F20" s="6" t="n"/>
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t>Thời điểm tạo bản ghi (UTC): thời điểm quét mã.</t>
+        </is>
+      </c>
+      <c r="H20" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-15T08:29:10Z</t>
+        </is>
+      </c>
+      <c r="I20" s="6" t="inlineStr">
+        <is>
+          <t>🔍</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>updated_at</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>timestamptz</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="n"/>
+      <c r="F21" s="6" t="n"/>
+      <c r="G21" s="6" t="inlineStr">
+        <is>
+          <t>Thời điểm bản ghi được sửa gần nhất (UTC).</t>
+        </is>
+      </c>
+      <c r="H21" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-15T09:45:05Z</t>
+        </is>
+      </c>
+      <c r="I21" s="6" t="inlineStr">
+        <is>
+          <t>🔍</t>
+        </is>
+      </c>
+    </row>
+    <row r="22"/>
+    <row r="23">
+      <c r="A23" s="4" t="n"/>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>Chỉ mục (index)</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>Các cột</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>Duy nhất</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="n"/>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>Ghi chú</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="27" customHeight="1">
+      <c r="A24" s="6" t="n"/>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>ix_charging_session_charges_tariff_version_id</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>tariff_version_id</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E24" s="6" t="n"/>
+      <c r="F24" s="6" t="n"/>
+    </row>
+    <row r="25" ht="27" customHeight="1">
+      <c r="A25" s="6" t="n"/>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>ix_charging_session_charges_status_created</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>status, created_at</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E25" s="6" t="n"/>
+      <c r="F25" s="6" t="inlineStr">
+        <is>
+          <t>Held charges waiting for review</t>
+        </is>
+      </c>
+    </row>
+    <row r="26"/>
+    <row r="27">
+      <c r="A27" s="4" t="n"/>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>Được tham chiếu bởi bảng</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>Cột</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="27" customHeight="1">
+      <c r="A28" s="6" t="n"/>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>charging_session_charge_history</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>charging_session_charge_id</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A7:I21"/>
+  <hyperlinks>
+    <hyperlink ref="A2" location="'Tổng quan'!A1"/>
+    <hyperlink ref="A5" location="'charging_session_charge_history'!A1"/>
+    <hyperlink ref="F9" location="'charging_sessions'!A1"/>
+    <hyperlink ref="F10" location="'tariff_versions'!A1"/>
+    <hyperlink ref="B28" location="'charging_session_charge_history'!A1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet71.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="7" max="7"/>
+    <col width="42" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>52.h. charging_session_charge_history: Lịch sử phí phiên sạc</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t>← Tổng quan</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>Miền nghiệp vụ: Thanh toán &amp; hóa đơn (billing)   ·   Chủ sở hữu dữ liệu: Hai bên   ·   Tính năng: F-H1, F-H3</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>Mọi phiên bản trước đây của một dòng trong bảng charging_session_charges: bản sao toàn bộ dòng, chụp ngay trước khi thay đổi và được trigger ghi trong cùng giao dịch. Do công cụ domain-model tự sinh từ @tracked *, không bao giờ viết tay.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>Bảng lịch sử của: charging_session_charges</t>
+        </is>
+      </c>
+    </row>
+    <row r="6"/>
+    <row r="7" ht="27" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Cột</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Kiểu dữ liệu</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Cho phép rỗng</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>Khóa</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>Tham chiếu tới</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>Ý nghĩa</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>Ví dụ</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>Lưu lịch sử</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>history_id</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>bigint</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="n"/>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>Mã tự tăng của dòng lịch sử.</t>
+        </is>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>1024</t>
+        </is>
+      </c>
+      <c r="I8" s="6" t="n"/>
+    </row>
+    <row r="9" ht="27" customHeight="1">
+      <c r="A9" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>charging_session_charge_id</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>uuid</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>charging_session_charges.charging_session_charge_id (khi xóa: chặn xóa)</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>Giá trị trước khi thay đổi (charging_session_charges.charging_session_charge_id).</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>2b8d4f0a-6c3e-4a9b-8d7f-1e4c9a2b8d66</t>
+        </is>
+      </c>
+      <c r="I9" s="6" t="n"/>
+    </row>
+    <row r="10" ht="27" customHeight="1">
+      <c r="A10" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>session_id</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>uuid</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="n"/>
+      <c r="F10" s="6" t="n"/>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>Giá trị trước khi thay đổi (charging_session_charges.session_id).</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>e5a2d8f1-4b7c-4e9a-b3d6-2c1f0e9a8dbb</t>
+        </is>
+      </c>
+      <c r="I10" s="6" t="n"/>
+    </row>
+    <row r="11" ht="27" customHeight="1">
+      <c r="A11" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>tariff_version_id</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>uuid</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="n"/>
+      <c r="F11" s="6" t="n"/>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>Giá trị trước khi thay đổi (charging_session_charges.tariff_version_id).</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>1a7c3e9f-5b2d-4f8a-9c6e-0d3b8f1a7c55</t>
+        </is>
+      </c>
+      <c r="I11" s="6" t="n"/>
+    </row>
+    <row r="12" ht="27" customHeight="1">
+      <c r="A12" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>price_per_kwh</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>numeric(12,2)</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="n"/>
+      <c r="F12" s="6" t="n"/>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>Giá trị trước khi thay đổi (charging_session_charges.price_per_kwh).</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>4500.00</t>
+        </is>
+      </c>
+      <c r="I12" s="6" t="n"/>
+    </row>
+    <row r="13" ht="27" customHeight="1">
+      <c r="A13" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>vat_rate_percent</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>numeric(4,2)</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="n"/>
+      <c r="F13" s="6" t="n"/>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>Giá trị trước khi thay đổi (charging_session_charges.vat_rate_percent).</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>10.00</t>
+        </is>
+      </c>
+      <c r="I13" s="6" t="n"/>
+    </row>
+    <row r="14" ht="27" customHeight="1">
+      <c r="A14" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>varchar(20)</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="n"/>
+      <c r="F14" s="6" t="n"/>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>Giá trị trước khi thay đổi (charging_session_charges.status).</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>BILLED</t>
+        </is>
+      </c>
+      <c r="I14" s="6" t="n"/>
+    </row>
+    <row r="15" ht="27" customHeight="1">
+      <c r="A15" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>status_reason</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>varchar(200)</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="n"/>
+      <c r="F15" s="6" t="n"/>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>Giá trị trước khi thay đổi (charging_session_charges.status_reason).</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="I15" s="6" t="n"/>
+    </row>
+    <row r="16" ht="27" customHeight="1">
+      <c r="A16" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>energy_wh</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>numeric(24,3)</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="n"/>
+      <c r="F16" s="6" t="n"/>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>Giá trị trước khi thay đổi (charging_session_charges.energy_wh).</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>192520.000</t>
+        </is>
+      </c>
+      <c r="I16" s="6" t="n"/>
+    </row>
+    <row r="17" ht="27" customHeight="1">
+      <c r="A17" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>energy_source</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>varchar(20)</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="n"/>
+      <c r="F17" s="6" t="n"/>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>Giá trị trước khi thay đổi (charging_session_charges.energy_source).</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>METER_STOP</t>
+        </is>
+      </c>
+      <c r="I17" s="6" t="n"/>
+    </row>
+    <row r="18" ht="27" customHeight="1">
+      <c r="A18" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>amount_before_vat</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>numeric(14,2)</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="n"/>
+      <c r="F18" s="6" t="n"/>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>Giá trị trước khi thay đổi (charging_session_charges.amount_before_vat).</t>
+        </is>
+      </c>
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>866340.00</t>
+        </is>
+      </c>
+      <c r="I18" s="6" t="n"/>
+    </row>
+    <row r="19" ht="27" customHeight="1">
+      <c r="A19" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>vat_amount</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>numeric(14,2)</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="n"/>
+      <c r="F19" s="6" t="n"/>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>Giá trị trước khi thay đổi (charging_session_charges.vat_amount).</t>
+        </is>
+      </c>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>86634.00</t>
+        </is>
+      </c>
+      <c r="I19" s="6" t="n"/>
+    </row>
+    <row r="20" ht="27" customHeight="1">
+      <c r="A20" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>billed_at</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>timestamptz</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="n"/>
+      <c r="F20" s="6" t="n"/>
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t>Giá trị trước khi thay đổi (charging_session_charges.billed_at).</t>
+        </is>
+      </c>
+      <c r="H20" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-15T09:45:05Z</t>
+        </is>
+      </c>
+      <c r="I20" s="6" t="n"/>
+    </row>
+    <row r="21" ht="27" customHeight="1">
+      <c r="A21" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>created_at</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>timestamptz</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="n"/>
+      <c r="F21" s="6" t="n"/>
+      <c r="G21" s="6" t="inlineStr">
+        <is>
+          <t>Giá trị trước khi thay đổi (charging_session_charges.created_at).</t>
+        </is>
+      </c>
+      <c r="H21" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-15T08:29:10Z</t>
+        </is>
+      </c>
+      <c r="I21" s="6" t="n"/>
+    </row>
+    <row r="22" ht="27" customHeight="1">
+      <c r="A22" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>updated_at</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>timestamptz</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="n"/>
+      <c r="F22" s="6" t="n"/>
+      <c r="G22" s="6" t="inlineStr">
+        <is>
+          <t>Giá trị trước khi thay đổi (charging_session_charges.updated_at).</t>
+        </is>
+      </c>
+      <c r="H22" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-15T09:45:05Z</t>
+        </is>
+      </c>
+      <c r="I22" s="6" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>changed_at</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>timestamptz</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="n"/>
+      <c r="F23" s="6" t="n"/>
+      <c r="G23" s="6" t="inlineStr">
+        <is>
+          <t>Thời điểm phiên bản này của dòng bị thay thế.</t>
+        </is>
+      </c>
+      <c r="H23" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-10T07:15:00Z</t>
+        </is>
+      </c>
+      <c r="I23" s="6" t="n"/>
+    </row>
+    <row r="24" ht="27" customHeight="1">
+      <c r="A24" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>changed_by</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>uuid</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="F24" s="7" t="inlineStr">
+        <is>
+          <t>users.user_id (khi xóa: chặn xóa)</t>
+        </is>
+      </c>
+      <c r="G24" s="6" t="inlineStr">
+        <is>
+          <t>Người dùng đã thực hiện thay đổi; NULL nếu do hệ thống thực hiện.</t>
+        </is>
+      </c>
+      <c r="H24" s="6" t="inlineStr">
+        <is>
+          <t>9b2e7d4a-1c3f-4a8e-b6d2-5e0f1a9c3d22</t>
+        </is>
+      </c>
+      <c r="I24" s="6" t="n"/>
+    </row>
+    <row r="25" ht="40.5" customHeight="1">
+      <c r="A25" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>change_reason</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>varchar(200)</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E25" s="6" t="n"/>
+      <c r="F25" s="6" t="n"/>
+      <c r="G25" s="6" t="inlineStr">
+        <is>
+          <t>Lý do thay đổi dòng, do ứng dụng đặt cho giao dịch: người dùng nhập với quyết định quản trị, văn bản cố định với thao tác thường lệ. Thay đổi không có lý do sẽ bị từ chối.</t>
+        </is>
+      </c>
+      <c r="H25" s="6" t="inlineStr">
+        <is>
+          <t>Customer moved to a new office</t>
+        </is>
+      </c>
+      <c r="I25" s="6" t="n"/>
+    </row>
+    <row r="26"/>
+    <row r="27">
+      <c r="A27" s="4" t="n"/>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>Chỉ mục (index)</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>Các cột</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>Duy nhất</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="n"/>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>Ghi chú</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="40.5" customHeight="1">
+      <c r="A28" s="6" t="n"/>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>ix_charging_session_charge_history_charging_session_charge_id_time</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>charging_session_charge_id, changed_at</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E28" s="6" t="n"/>
+      <c r="F28" s="6" t="n"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A7:I25"/>
+  <hyperlinks>
+    <hyperlink ref="A2" location="'Tổng quan'!A1"/>
+    <hyperlink ref="A5" location="'charging_session_charges'!A1"/>
+    <hyperlink ref="F9" location="'charging_session_charges'!A1"/>
+    <hyperlink ref="F24" location="'users'!A1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet72.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:I19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -46870,7 +48546,7 @@
     <row r="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>52. payments: Thanh toán</t>
+          <t>53. payments: Thanh toán</t>
         </is>
       </c>
     </row>
@@ -47332,7 +49008,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet71.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet73.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -47355,7 +49031,7 @@
     <row r="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>53. wallets: Ví</t>
+          <t>54. wallets: Ví</t>
         </is>
       </c>
     </row>
@@ -47680,924 +49356,6 @@
     <hyperlink ref="F8" location="'organizations'!A1"/>
     <hyperlink ref="F9" location="'drivers'!A1"/>
     <hyperlink ref="B15" location="'wallet_transactions'!A1"/>
-  </hyperlinks>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet72.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I15"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="40" customWidth="1" min="6" max="6"/>
-    <col width="60" customWidth="1" min="7" max="7"/>
-    <col width="42" customWidth="1" min="8" max="8"/>
-    <col width="11" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="9" t="inlineStr">
-        <is>
-          <t>54. wallet_transactions: Giao dịch ví</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="10" t="inlineStr">
-        <is>
-          <t>← Tổng quan</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>Miền nghiệp vụ: Thanh toán &amp; hóa đơn (billing)   ·   Chủ sở hữu dữ liệu: Khách hàng   ·   Tính năng: F-H2</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="11" t="inlineStr">
-        <is>
-          <t>Biến động tiền vào/ra khỏi ví, chỉ ghi thêm.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5"/>
-    <row r="6" ht="27" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>Cột</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>Kiểu dữ liệu</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>Cho phép rỗng</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>Khóa</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>Tham chiếu tới</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>Ý nghĩa</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>Ví dụ</t>
-        </is>
-      </c>
-      <c r="I6" s="4" t="inlineStr">
-        <is>
-          <t>Lưu lịch sử</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>transaction_id</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>uuid</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
-      <c r="F7" s="6" t="n"/>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>Mã nội bộ của giao dịch.</t>
-        </is>
-      </c>
-      <c r="H7" s="6" t="inlineStr">
-        <is>
-          <t>00000010-5a6b-4c7d-8e9f-0a1b2c3d4e5f</t>
-        </is>
-      </c>
-      <c r="I7" s="6" t="n"/>
-    </row>
-    <row r="8" ht="27" customHeight="1">
-      <c r="A8" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>organization_id</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>uuid</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E8" s="6" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="F8" s="7" t="inlineStr">
-        <is>
-          <t>organizations.organization_id (khi xóa: chặn xóa)</t>
-        </is>
-      </c>
-      <c r="G8" s="6" t="inlineStr">
-        <is>
-          <t>Tổ chức khách hàng của ví.</t>
-        </is>
-      </c>
-      <c r="H8" s="6" t="inlineStr">
-        <is>
-          <t>3f6c2a1e-8b4d-4e2a-9c1f-0a7d5b2e4c11</t>
-        </is>
-      </c>
-      <c r="I8" s="6" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>wallet_id</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>uuid</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E9" s="6" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="F9" s="7" t="inlineStr">
-        <is>
-          <t>wallets.wallet_id (khi xóa: chặn xóa)</t>
-        </is>
-      </c>
-      <c r="G9" s="6" t="inlineStr">
-        <is>
-          <t>Ví bị ảnh hưởng.</t>
-        </is>
-      </c>
-      <c r="H9" s="6" t="inlineStr">
-        <is>
-          <t>5c3a0e7d-2f9b-4c1e-a8d3-7b6f0c2e9a32</t>
-        </is>
-      </c>
-      <c r="I9" s="6" t="n"/>
-    </row>
-    <row r="10" ht="27" customHeight="1">
-      <c r="A10" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>transaction_type</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>varchar(20)</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E10" s="6" t="n"/>
-      <c r="F10" s="6" t="n"/>
-      <c r="G10" s="6" t="inlineStr">
-        <is>
-          <t>Loại biến động tiền. Giá trị: TOP_UP | CHARGE | WITHDRAW | REFUND.</t>
-        </is>
-      </c>
-      <c r="H10" s="6" t="inlineStr">
-        <is>
-          <t>CHARGE</t>
-        </is>
-      </c>
-      <c r="I10" s="6" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>amount</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>numeric(14,2)</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E11" s="6" t="n"/>
-      <c r="F11" s="6" t="n"/>
-      <c r="G11" s="6" t="inlineStr">
-        <is>
-          <t>Số tiền có dấu: dương là cộng tiền, âm là trừ tiền.</t>
-        </is>
-      </c>
-      <c r="H11" s="6" t="inlineStr">
-        <is>
-          <t>-866250.00</t>
-        </is>
-      </c>
-      <c r="I11" s="6" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>balance_after</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>numeric(14,2)</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E12" s="6" t="n"/>
-      <c r="F12" s="6" t="n"/>
-      <c r="G12" s="6" t="inlineStr">
-        <is>
-          <t>Số dư ví ngay sau giao dịch.</t>
-        </is>
-      </c>
-      <c r="H12" s="6" t="inlineStr">
-        <is>
-          <t>11633750.00</t>
-        </is>
-      </c>
-      <c r="I12" s="6" t="n"/>
-    </row>
-    <row r="13" ht="27" customHeight="1">
-      <c r="A13" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>session_id</t>
-        </is>
-      </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>uuid</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="inlineStr">
-        <is>
-          <t>có</t>
-        </is>
-      </c>
-      <c r="E13" s="6" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="F13" s="7" t="inlineStr">
-        <is>
-          <t>charging_sessions.session_id (khi xóa: chặn xóa)</t>
-        </is>
-      </c>
-      <c r="G13" s="6" t="inlineStr">
-        <is>
-          <t>Phiên sạc được trả tiền, với giao dịch CHARGE.</t>
-        </is>
-      </c>
-      <c r="H13" s="6" t="inlineStr">
-        <is>
-          <t>e5a2d8f1-4b7c-4e9a-b3d6-2c1f0e9a8dbb</t>
-        </is>
-      </c>
-      <c r="I13" s="6" t="n"/>
-    </row>
-    <row r="14" ht="27" customHeight="1">
-      <c r="A14" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="B14" s="6" t="inlineStr">
-        <is>
-          <t>payment_id</t>
-        </is>
-      </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>uuid</t>
-        </is>
-      </c>
-      <c r="D14" s="6" t="inlineStr">
-        <is>
-          <t>có</t>
-        </is>
-      </c>
-      <c r="E14" s="6" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="F14" s="7" t="inlineStr">
-        <is>
-          <t>payments.payment_id (khi xóa: chặn xóa)</t>
-        </is>
-      </c>
-      <c r="G14" s="6" t="inlineStr">
-        <is>
-          <t>Thanh toán qua cổng đứng sau một lần nạp tiền, nếu có.</t>
-        </is>
-      </c>
-      <c r="H14" s="6" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="I14" s="6" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="B15" s="6" t="inlineStr">
-        <is>
-          <t>occurred_at</t>
-        </is>
-      </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>timestamptz</t>
-        </is>
-      </c>
-      <c r="D15" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E15" s="6" t="n"/>
-      <c r="F15" s="6" t="n"/>
-      <c r="G15" s="6" t="inlineStr">
-        <is>
-          <t>Thời điểm phát sinh giao dịch.</t>
-        </is>
-      </c>
-      <c r="H15" s="6" t="inlineStr">
-        <is>
-          <t>2026-09-15T09:46:12Z</t>
-        </is>
-      </c>
-      <c r="I15" s="6" t="n"/>
-    </row>
-  </sheetData>
-  <autoFilter ref="A6:I15"/>
-  <hyperlinks>
-    <hyperlink ref="A2" location="'Tổng quan'!A1"/>
-    <hyperlink ref="F8" location="'organizations'!A1"/>
-    <hyperlink ref="F9" location="'wallets'!A1"/>
-    <hyperlink ref="F13" location="'charging_sessions'!A1"/>
-    <hyperlink ref="F14" location="'payments'!A1"/>
-  </hyperlinks>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet73.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I19"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="40" customWidth="1" min="6" max="6"/>
-    <col width="60" customWidth="1" min="7" max="7"/>
-    <col width="42" customWidth="1" min="8" max="8"/>
-    <col width="11" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="9" t="inlineStr">
-        <is>
-          <t>55. invoices: Hóa đơn</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="10" t="inlineStr">
-        <is>
-          <t>← Tổng quan</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>Miền nghiệp vụ: Thanh toán &amp; hóa đơn (billing)   ·   Chủ sở hữu dữ liệu: Khách hàng   ·   Tính năng: F-H3, F-H4</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="11" t="inlineStr">
-        <is>
-          <t>Một hóa đơn điện tử hợp lệ. Khi đã PHÁT HÀNH thì không sửa, chỉ điều chỉnh hoặc hủy bằng hóa đơn mới.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5"/>
-    <row r="6" ht="27" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>Cột</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>Kiểu dữ liệu</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>Cho phép rỗng</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>Khóa</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>Tham chiếu tới</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>Ý nghĩa</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>Ví dụ</t>
-        </is>
-      </c>
-      <c r="I6" s="4" t="inlineStr">
-        <is>
-          <t>Lưu lịch sử</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>invoice_id</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>uuid</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
-      <c r="F7" s="6" t="n"/>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>Mã nội bộ của hóa đơn.</t>
-        </is>
-      </c>
-      <c r="H7" s="6" t="inlineStr">
-        <is>
-          <t>7e5c2a9f-4b1d-4e3a-9c8f-0d6b1e4a7c43</t>
-        </is>
-      </c>
-      <c r="I7" s="6" t="n"/>
-    </row>
-    <row r="8" ht="27" customHeight="1">
-      <c r="A8" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>organization_id</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>uuid</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E8" s="6" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="F8" s="7" t="inlineStr">
-        <is>
-          <t>organizations.organization_id (khi xóa: chặn xóa)</t>
-        </is>
-      </c>
-      <c r="G8" s="6" t="inlineStr">
-        <is>
-          <t>Tổ chức khách hàng được xuất hóa đơn.</t>
-        </is>
-      </c>
-      <c r="H8" s="6" t="inlineStr">
-        <is>
-          <t>3f6c2a1e-8b4d-4e2a-9c1f-0a7d5b2e4c11</t>
-        </is>
-      </c>
-      <c r="I8" s="6" t="n"/>
-    </row>
-    <row r="9" ht="27" customHeight="1">
-      <c r="A9" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>invoice_type</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>varchar(20)</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E9" s="6" t="n"/>
-      <c r="F9" s="6" t="n"/>
-      <c r="G9" s="6" t="inlineStr">
-        <is>
-          <t>Hóa đơn lẻ theo phiên hay hóa đơn tổng hợp tháng cho đội xe. Giá trị: RETAIL | FLEET_MONTHLY.</t>
-        </is>
-      </c>
-      <c r="H9" s="6" t="inlineStr">
-        <is>
-          <t>FLEET_MONTHLY</t>
-        </is>
-      </c>
-      <c r="I9" s="6" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>period_start</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>có</t>
-        </is>
-      </c>
-      <c r="E10" s="6" t="n"/>
-      <c r="F10" s="6" t="n"/>
-      <c r="G10" s="6" t="inlineStr">
-        <is>
-          <t>Ngày đầu kỳ; NULL với hóa đơn một phiên.</t>
-        </is>
-      </c>
-      <c r="H10" s="6" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="I10" s="6" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>period_end</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>có</t>
-        </is>
-      </c>
-      <c r="E11" s="6" t="n"/>
-      <c r="F11" s="6" t="n"/>
-      <c r="G11" s="6" t="inlineStr">
-        <is>
-          <t>Ngày cuối kỳ; NULL với hóa đơn một phiên.</t>
-        </is>
-      </c>
-      <c r="H11" s="6" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="I11" s="6" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>total_amount</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>numeric(14,2)</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E12" s="6" t="n"/>
-      <c r="F12" s="6" t="n"/>
-      <c r="G12" s="6" t="inlineStr">
-        <is>
-          <t>Tổng tiền hóa đơn, gồm thuế.</t>
-        </is>
-      </c>
-      <c r="H12" s="6" t="inlineStr">
-        <is>
-          <t>256800000.00</t>
-        </is>
-      </c>
-      <c r="I12" s="6" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>currency</t>
-        </is>
-      </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>char(3)</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E13" s="6" t="n"/>
-      <c r="F13" s="6" t="n"/>
-      <c r="G13" s="6" t="inlineStr">
-        <is>
-          <t>Mã tiền tệ ISO 4217.</t>
-        </is>
-      </c>
-      <c r="H13" s="6" t="inlineStr">
-        <is>
-          <t>VND</t>
-        </is>
-      </c>
-      <c r="I13" s="6" t="n"/>
-    </row>
-    <row r="14" ht="27" customHeight="1">
-      <c r="A14" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="B14" s="6" t="inlineStr">
-        <is>
-          <t>einvoice_number</t>
-        </is>
-      </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>varchar(50)</t>
-        </is>
-      </c>
-      <c r="D14" s="6" t="inlineStr">
-        <is>
-          <t>có</t>
-        </is>
-      </c>
-      <c r="E14" s="6" t="n"/>
-      <c r="F14" s="6" t="n"/>
-      <c r="G14" s="6" t="inlineStr">
-        <is>
-          <t>Số hóa đơn do nhà cung cấp hóa đơn điện tử cấp; NULL trước khi phát hành.</t>
-        </is>
-      </c>
-      <c r="H14" s="6" t="inlineStr">
-        <is>
-          <t>C26TMP0001234</t>
-        </is>
-      </c>
-      <c r="I14" s="6" t="n"/>
-    </row>
-    <row r="15" ht="27" customHeight="1">
-      <c r="A15" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="B15" s="6" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>varchar(20)</t>
-        </is>
-      </c>
-      <c r="D15" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E15" s="6" t="n"/>
-      <c r="F15" s="6" t="n"/>
-      <c r="G15" s="6" t="inlineStr">
-        <is>
-          <t>Trạng thái hóa đơn; hóa đơn đã ISSUED không bao giờ bị sửa. Giá trị: DRAFT | ISSUED | ADJUSTED | CANCELLED.</t>
-        </is>
-      </c>
-      <c r="H15" s="6" t="inlineStr">
-        <is>
-          <t>ISSUED</t>
-        </is>
-      </c>
-      <c r="I15" s="6" t="n"/>
-    </row>
-    <row r="16" ht="27" customHeight="1">
-      <c r="A16" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="B16" s="6" t="inlineStr">
-        <is>
-          <t>issued_at</t>
-        </is>
-      </c>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>timestamptz</t>
-        </is>
-      </c>
-      <c r="D16" s="6" t="inlineStr">
-        <is>
-          <t>có</t>
-        </is>
-      </c>
-      <c r="E16" s="6" t="n"/>
-      <c r="F16" s="6" t="n"/>
-      <c r="G16" s="6" t="inlineStr">
-        <is>
-          <t>Thời điểm phát hành hóa đơn điện tử; NULL trước khi phát hành.</t>
-        </is>
-      </c>
-      <c r="H16" s="6" t="inlineStr">
-        <is>
-          <t>2026-10-01T03:00:00Z</t>
-        </is>
-      </c>
-      <c r="I16" s="6" t="n"/>
-    </row>
-    <row r="17"/>
-    <row r="18">
-      <c r="A18" s="4" t="n"/>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>Được tham chiếu bởi bảng</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>Cột</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="6" t="n"/>
-      <c r="B19" s="7" t="inlineStr">
-        <is>
-          <t>invoice_lines</t>
-        </is>
-      </c>
-      <c r="C19" s="6" t="inlineStr">
-        <is>
-          <t>invoice_id</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A6:I16"/>
-  <hyperlinks>
-    <hyperlink ref="A2" location="'Tổng quan'!A1"/>
-    <hyperlink ref="F8" location="'organizations'!A1"/>
-    <hyperlink ref="B19" location="'invoice_lines'!A1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -48626,7 +49384,925 @@
     <row r="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>56. invoice_lines: Dòng hóa đơn</t>
+          <t>55. wallet_transactions: Giao dịch ví</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t>← Tổng quan</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>Miền nghiệp vụ: Thanh toán &amp; hóa đơn (billing)   ·   Chủ sở hữu dữ liệu: Khách hàng   ·   Tính năng: F-H2</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>Biến động tiền vào/ra khỏi ví, chỉ ghi thêm.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5"/>
+    <row r="6" ht="27" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Cột</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Kiểu dữ liệu</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Cho phép rỗng</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>Khóa</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>Tham chiếu tới</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>Ý nghĩa</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>Ví dụ</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>Lưu lịch sử</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>transaction_id</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>uuid</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="n"/>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>Mã nội bộ của giao dịch.</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>00000010-5a6b-4c7d-8e9f-0a1b2c3d4e5f</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="n"/>
+    </row>
+    <row r="8" ht="27" customHeight="1">
+      <c r="A8" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>organization_id</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>uuid</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>organizations.organization_id (khi xóa: chặn xóa)</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>Tổ chức khách hàng của ví.</t>
+        </is>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>3f6c2a1e-8b4d-4e2a-9c1f-0a7d5b2e4c11</t>
+        </is>
+      </c>
+      <c r="I8" s="6" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>wallet_id</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>uuid</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>wallets.wallet_id (khi xóa: chặn xóa)</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>Ví bị ảnh hưởng.</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>5c3a0e7d-2f9b-4c1e-a8d3-7b6f0c2e9a32</t>
+        </is>
+      </c>
+      <c r="I9" s="6" t="n"/>
+    </row>
+    <row r="10" ht="27" customHeight="1">
+      <c r="A10" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>transaction_type</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>varchar(20)</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="n"/>
+      <c r="F10" s="6" t="n"/>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>Loại biến động tiền. Giá trị: TOP_UP | CHARGE | WITHDRAW | REFUND.</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>CHARGE</t>
+        </is>
+      </c>
+      <c r="I10" s="6" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>numeric(14,2)</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="n"/>
+      <c r="F11" s="6" t="n"/>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>Số tiền có dấu: dương là cộng tiền, âm là trừ tiền.</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>-866250.00</t>
+        </is>
+      </c>
+      <c r="I11" s="6" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>balance_after</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>numeric(14,2)</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="n"/>
+      <c r="F12" s="6" t="n"/>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>Số dư ví ngay sau giao dịch.</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>11633750.00</t>
+        </is>
+      </c>
+      <c r="I12" s="6" t="n"/>
+    </row>
+    <row r="13" ht="27" customHeight="1">
+      <c r="A13" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>session_id</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>uuid</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>charging_sessions.session_id (khi xóa: chặn xóa)</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>Phiên sạc được trả tiền, với giao dịch CHARGE.</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>e5a2d8f1-4b7c-4e9a-b3d6-2c1f0e9a8dbb</t>
+        </is>
+      </c>
+      <c r="I13" s="6" t="n"/>
+    </row>
+    <row r="14" ht="27" customHeight="1">
+      <c r="A14" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>payment_id</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>uuid</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="F14" s="7" t="inlineStr">
+        <is>
+          <t>payments.payment_id (khi xóa: chặn xóa)</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>Thanh toán qua cổng đứng sau một lần nạp tiền, nếu có.</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="I14" s="6" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>occurred_at</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>timestamptz</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="n"/>
+      <c r="F15" s="6" t="n"/>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>Thời điểm phát sinh giao dịch.</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-15T09:46:12Z</t>
+        </is>
+      </c>
+      <c r="I15" s="6" t="n"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A6:I15"/>
+  <hyperlinks>
+    <hyperlink ref="A2" location="'Tổng quan'!A1"/>
+    <hyperlink ref="F8" location="'organizations'!A1"/>
+    <hyperlink ref="F9" location="'wallets'!A1"/>
+    <hyperlink ref="F13" location="'charging_sessions'!A1"/>
+    <hyperlink ref="F14" location="'payments'!A1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet75.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="7" max="7"/>
+    <col width="42" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>56. invoices: Hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t>← Tổng quan</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>Miền nghiệp vụ: Thanh toán &amp; hóa đơn (billing)   ·   Chủ sở hữu dữ liệu: Khách hàng   ·   Tính năng: F-H3, F-H4</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>Một hóa đơn điện tử hợp lệ. Khi đã PHÁT HÀNH thì không sửa, chỉ điều chỉnh hoặc hủy bằng hóa đơn mới.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5"/>
+    <row r="6" ht="27" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Cột</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Kiểu dữ liệu</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Cho phép rỗng</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>Khóa</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>Tham chiếu tới</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>Ý nghĩa</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>Ví dụ</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>Lưu lịch sử</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>invoice_id</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>uuid</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="n"/>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>Mã nội bộ của hóa đơn.</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>7e5c2a9f-4b1d-4e3a-9c8f-0d6b1e4a7c43</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="n"/>
+    </row>
+    <row r="8" ht="27" customHeight="1">
+      <c r="A8" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>organization_id</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>uuid</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>organizations.organization_id (khi xóa: chặn xóa)</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>Tổ chức khách hàng được xuất hóa đơn.</t>
+        </is>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>3f6c2a1e-8b4d-4e2a-9c1f-0a7d5b2e4c11</t>
+        </is>
+      </c>
+      <c r="I8" s="6" t="n"/>
+    </row>
+    <row r="9" ht="27" customHeight="1">
+      <c r="A9" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>invoice_type</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>varchar(20)</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="n"/>
+      <c r="F9" s="6" t="n"/>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn lẻ theo phiên hay hóa đơn tổng hợp tháng cho đội xe. Giá trị: RETAIL | FLEET_MONTHLY.</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>FLEET_MONTHLY</t>
+        </is>
+      </c>
+      <c r="I9" s="6" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>period_start</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="n"/>
+      <c r="F10" s="6" t="n"/>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>Ngày đầu kỳ; NULL với hóa đơn một phiên.</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="I10" s="6" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>period_end</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="n"/>
+      <c r="F11" s="6" t="n"/>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>Ngày cuối kỳ; NULL với hóa đơn một phiên.</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="I11" s="6" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>total_amount</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>numeric(14,2)</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="n"/>
+      <c r="F12" s="6" t="n"/>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>Tổng tiền hóa đơn, gồm thuế.</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>256800000.00</t>
+        </is>
+      </c>
+      <c r="I12" s="6" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>currency</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>char(3)</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="n"/>
+      <c r="F13" s="6" t="n"/>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>Mã tiền tệ ISO 4217.</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="I13" s="6" t="n"/>
+    </row>
+    <row r="14" ht="27" customHeight="1">
+      <c r="A14" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>einvoice_number</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>varchar(50)</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="n"/>
+      <c r="F14" s="6" t="n"/>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>Số hóa đơn do nhà cung cấp hóa đơn điện tử cấp; NULL trước khi phát hành.</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>C26TMP0001234</t>
+        </is>
+      </c>
+      <c r="I14" s="6" t="n"/>
+    </row>
+    <row r="15" ht="27" customHeight="1">
+      <c r="A15" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>varchar(20)</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="n"/>
+      <c r="F15" s="6" t="n"/>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>Trạng thái hóa đơn; hóa đơn đã ISSUED không bao giờ bị sửa. Giá trị: DRAFT | ISSUED | ADJUSTED | CANCELLED.</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>ISSUED</t>
+        </is>
+      </c>
+      <c r="I15" s="6" t="n"/>
+    </row>
+    <row r="16" ht="27" customHeight="1">
+      <c r="A16" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>issued_at</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>timestamptz</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="n"/>
+      <c r="F16" s="6" t="n"/>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>Thời điểm phát hành hóa đơn điện tử; NULL trước khi phát hành.</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-01T03:00:00Z</t>
+        </is>
+      </c>
+      <c r="I16" s="6" t="n"/>
+    </row>
+    <row r="17"/>
+    <row r="18">
+      <c r="A18" s="4" t="n"/>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>Được tham chiếu bởi bảng</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>Cột</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="n"/>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>invoice_lines</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>invoice_id</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A6:I16"/>
+  <hyperlinks>
+    <hyperlink ref="A2" location="'Tổng quan'!A1"/>
+    <hyperlink ref="F8" location="'organizations'!A1"/>
+    <hyperlink ref="B19" location="'invoice_lines'!A1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet76.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="7" max="7"/>
+    <col width="42" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>57. invoice_lines: Dòng hóa đơn</t>
         </is>
       </c>
     </row>
@@ -49045,7 +50721,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet75.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet77.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -49068,7 +50744,7 @@
     <row r="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>57. subscription_plans: Gói dịch vụ</t>
+          <t>58. subscription_plans: Gói dịch vụ</t>
         </is>
       </c>
     </row>
@@ -49431,7 +51107,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet76.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet78.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -49454,7 +51130,7 @@
     <row r="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>58. plan_features: Tính năng của gói dịch vụ</t>
+          <t>59. plan_features: Tính năng của gói dịch vụ</t>
         </is>
       </c>
     </row>
@@ -49726,7 +51402,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet77.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet79.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -49749,7 +51425,7 @@
     <row r="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>59. subscriptions: Thuê bao</t>
+          <t>60. subscriptions: Thuê bao</t>
         </is>
       </c>
     </row>
@@ -50116,716 +51792,6 @@
     <hyperlink ref="F9" location="'subscription_plans'!A1"/>
     <hyperlink ref="F10" location="'vehicles'!A1"/>
     <hyperlink ref="B16" location="'invoice_lines'!A1"/>
-  </hyperlinks>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet78.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I16"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="40" customWidth="1" min="6" max="6"/>
-    <col width="60" customWidth="1" min="7" max="7"/>
-    <col width="42" customWidth="1" min="8" max="8"/>
-    <col width="11" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="9" t="inlineStr">
-        <is>
-          <t>60. driver_scores: Điểm tài xế</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="10" t="inlineStr">
-        <is>
-          <t>← Tổng quan</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>Miền nghiệp vụ: Chấm điểm tài xế (scoring)   ·   Chủ sở hữu dữ liệu: Khách hàng   ·   Tính năng: F-K1</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="11" t="inlineStr">
-        <is>
-          <t>Điểm an toàn hằng tuần của tài xế, tính từ dữ liệu vận hành xe.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5"/>
-    <row r="6" ht="27" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>Cột</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>Kiểu dữ liệu</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>Cho phép rỗng</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>Khóa</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>Tham chiếu tới</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>Ý nghĩa</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>Ví dụ</t>
-        </is>
-      </c>
-      <c r="I6" s="4" t="inlineStr">
-        <is>
-          <t>Lưu lịch sử</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>score_id</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>uuid</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
-      <c r="F7" s="6" t="n"/>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>Mã nội bộ của điểm.</t>
-        </is>
-      </c>
-      <c r="H7" s="6" t="inlineStr">
-        <is>
-          <t>00000012-5a6b-4c7d-8e9f-0a1b2c3d4e5f</t>
-        </is>
-      </c>
-      <c r="I7" s="6" t="n"/>
-    </row>
-    <row r="8" ht="27" customHeight="1">
-      <c r="A8" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>organization_id</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>uuid</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E8" s="6" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="F8" s="7" t="inlineStr">
-        <is>
-          <t>organizations.organization_id (khi xóa: chặn xóa)</t>
-        </is>
-      </c>
-      <c r="G8" s="6" t="inlineStr">
-        <is>
-          <t>Tổ chức khách hàng của tài xế.</t>
-        </is>
-      </c>
-      <c r="H8" s="6" t="inlineStr">
-        <is>
-          <t>3f6c2a1e-8b4d-4e2a-9c1f-0a7d5b2e4c11</t>
-        </is>
-      </c>
-      <c r="I8" s="6" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>driver_id</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>uuid</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E9" s="6" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="F9" s="7" t="inlineStr">
-        <is>
-          <t>drivers.driver_id (khi xóa: chặn xóa)</t>
-        </is>
-      </c>
-      <c r="G9" s="6" t="inlineStr">
-        <is>
-          <t>Tài xế được chấm điểm.</t>
-        </is>
-      </c>
-      <c r="H9" s="6" t="inlineStr">
-        <is>
-          <t>6e3b9d2a-4c1f-4e8b-9a7d-0c2e5f1b8d66</t>
-        </is>
-      </c>
-      <c r="I9" s="6" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>week_start</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E10" s="6" t="n"/>
-      <c r="F10" s="6" t="n"/>
-      <c r="G10" s="6" t="inlineStr">
-        <is>
-          <t>Thứ Hai của tuần được chấm.</t>
-        </is>
-      </c>
-      <c r="H10" s="6" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="I10" s="6" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>score</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>numeric(5,2)</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E11" s="6" t="n"/>
-      <c r="F11" s="6" t="n"/>
-      <c r="G11" s="6" t="inlineStr">
-        <is>
-          <t>Điểm an toàn từ 0 đến 100.</t>
-        </is>
-      </c>
-      <c r="H11" s="6" t="inlineStr">
-        <is>
-          <t>86.50</t>
-        </is>
-      </c>
-      <c r="I11" s="6" t="n"/>
-    </row>
-    <row r="12" ht="27" customHeight="1">
-      <c r="A12" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>breakdown</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>jsonb</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>có</t>
-        </is>
-      </c>
-      <c r="E12" s="6" t="n"/>
-      <c r="F12" s="6" t="n"/>
-      <c r="G12" s="6" t="inlineStr">
-        <is>
-          <t>Mức đóng góp của từng yếu tố, dạng JSON.</t>
-        </is>
-      </c>
-      <c r="H12" s="6" t="inlineStr">
-        <is>
-          <t>{"harsh_braking": -6.0, "speeding": -4.5, "continuous_driving": -3.0}</t>
-        </is>
-      </c>
-      <c r="I12" s="6" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>computed_at</t>
-        </is>
-      </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>timestamptz</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E13" s="6" t="n"/>
-      <c r="F13" s="6" t="n"/>
-      <c r="G13" s="6" t="inlineStr">
-        <is>
-          <t>Thời điểm tính điểm.</t>
-        </is>
-      </c>
-      <c r="H13" s="6" t="inlineStr">
-        <is>
-          <t>2026-09-21T17:00:00Z</t>
-        </is>
-      </c>
-      <c r="I13" s="6" t="n"/>
-    </row>
-    <row r="14"/>
-    <row r="15">
-      <c r="A15" s="4" t="n"/>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>Chỉ mục (index)</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>Các cột</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>Duy nhất</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="n"/>
-      <c r="F15" s="4" t="inlineStr">
-        <is>
-          <t>Ghi chú</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="27" customHeight="1">
-      <c r="A16" s="6" t="n"/>
-      <c r="B16" s="6" t="inlineStr">
-        <is>
-          <t>(không tên)</t>
-        </is>
-      </c>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>driver_id, week_start</t>
-        </is>
-      </c>
-      <c r="D16" s="6" t="inlineStr">
-        <is>
-          <t>có</t>
-        </is>
-      </c>
-      <c r="E16" s="6" t="n"/>
-      <c r="F16" s="6" t="n"/>
-    </row>
-  </sheetData>
-  <autoFilter ref="A6:I13"/>
-  <hyperlinks>
-    <hyperlink ref="A2" location="'Tổng quan'!A1"/>
-    <hyperlink ref="F8" location="'organizations'!A1"/>
-    <hyperlink ref="F9" location="'drivers'!A1"/>
-  </hyperlinks>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet79.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="40" customWidth="1" min="6" max="6"/>
-    <col width="60" customWidth="1" min="7" max="7"/>
-    <col width="42" customWidth="1" min="8" max="8"/>
-    <col width="11" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="9" t="inlineStr">
-        <is>
-          <t>61. promotion_campaigns: Chiến dịch khuyến mãi</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="10" t="inlineStr">
-        <is>
-          <t>← Tổng quan</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>Miền nghiệp vụ: Chưa phân miền (unassigned)   ·   Chủ sở hữu dữ liệu: Nội bộ   ·   Tính năng: F-F4</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="11" t="inlineStr">
-        <is>
-          <t>Một chiến dịch nhắc bảo dưỡng hoặc khuyến mãi.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5"/>
-    <row r="6" ht="27" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>Cột</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>Kiểu dữ liệu</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>Cho phép rỗng</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>Khóa</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>Tham chiếu tới</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>Ý nghĩa</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>Ví dụ</t>
-        </is>
-      </c>
-      <c r="I6" s="4" t="inlineStr">
-        <is>
-          <t>Lưu lịch sử</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>campaign_id</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>uuid</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
-      <c r="F7" s="6" t="n"/>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>Mã nội bộ của chiến dịch.</t>
-        </is>
-      </c>
-      <c r="H7" s="6" t="inlineStr">
-        <is>
-          <t>00000013-5a6b-4c7d-8e9f-0a1b2c3d4e5f</t>
-        </is>
-      </c>
-      <c r="I7" s="6" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>varchar(200)</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E8" s="6" t="n"/>
-      <c r="F8" s="6" t="n"/>
-      <c r="G8" s="6" t="inlineStr">
-        <is>
-          <t>Tên chiến dịch.</t>
-        </is>
-      </c>
-      <c r="H8" s="6" t="inlineStr">
-        <is>
-          <t>Giảm 10% sạc đêm tháng 10</t>
-        </is>
-      </c>
-      <c r="I8" s="6" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>starts_at</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>timestamptz</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E9" s="6" t="n"/>
-      <c r="F9" s="6" t="n"/>
-      <c r="G9" s="6" t="inlineStr">
-        <is>
-          <t>Thời điểm bắt đầu.</t>
-        </is>
-      </c>
-      <c r="H9" s="6" t="inlineStr">
-        <is>
-          <t>2026-10-01T00:00:00Z</t>
-        </is>
-      </c>
-      <c r="I9" s="6" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>ends_at</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>timestamptz</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>có</t>
-        </is>
-      </c>
-      <c r="E10" s="6" t="n"/>
-      <c r="F10" s="6" t="n"/>
-      <c r="G10" s="6" t="inlineStr">
-        <is>
-          <t>Thời điểm kết thúc; NULL nếu không thời hạn.</t>
-        </is>
-      </c>
-      <c r="H10" s="6" t="inlineStr">
-        <is>
-          <t>2026-10-31T16:59:59Z</t>
-        </is>
-      </c>
-      <c r="I10" s="6" t="n"/>
-    </row>
-    <row r="11" ht="27" customHeight="1">
-      <c r="A11" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>target</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>jsonb</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>có</t>
-        </is>
-      </c>
-      <c r="E11" s="6" t="n"/>
-      <c r="F11" s="6" t="n"/>
-      <c r="G11" s="6" t="inlineStr">
-        <is>
-          <t>Đối tượng nhận, dạng tiêu chí JSON.</t>
-        </is>
-      </c>
-      <c r="H11" s="6" t="inlineStr">
-        <is>
-          <t>{"vehicle_models": ["EVT-400"], "organizations": "all"}</t>
-        </is>
-      </c>
-      <c r="I11" s="6" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>varchar(20)</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E12" s="6" t="n"/>
-      <c r="F12" s="6" t="n"/>
-      <c r="G12" s="6" t="inlineStr">
-        <is>
-          <t>Trạng thái chiến dịch.</t>
-        </is>
-      </c>
-      <c r="H12" s="6" t="inlineStr">
-        <is>
-          <t>SCHEDULED</t>
-        </is>
-      </c>
-      <c r="I12" s="6" t="n"/>
-    </row>
-  </sheetData>
-  <autoFilter ref="A6:I12"/>
-  <hyperlinks>
-    <hyperlink ref="A2" location="'Tổng quan'!A1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -51479,6 +52445,716 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:I16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="7" max="7"/>
+    <col width="42" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>61. driver_scores: Điểm tài xế</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t>← Tổng quan</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>Miền nghiệp vụ: Chấm điểm tài xế (scoring)   ·   Chủ sở hữu dữ liệu: Khách hàng   ·   Tính năng: F-K1</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>Điểm an toàn hằng tuần của tài xế, tính từ dữ liệu vận hành xe.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5"/>
+    <row r="6" ht="27" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Cột</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Kiểu dữ liệu</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Cho phép rỗng</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>Khóa</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>Tham chiếu tới</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>Ý nghĩa</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>Ví dụ</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>Lưu lịch sử</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>score_id</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>uuid</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="n"/>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>Mã nội bộ của điểm.</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>00000012-5a6b-4c7d-8e9f-0a1b2c3d4e5f</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="n"/>
+    </row>
+    <row r="8" ht="27" customHeight="1">
+      <c r="A8" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>organization_id</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>uuid</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>organizations.organization_id (khi xóa: chặn xóa)</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>Tổ chức khách hàng của tài xế.</t>
+        </is>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>3f6c2a1e-8b4d-4e2a-9c1f-0a7d5b2e4c11</t>
+        </is>
+      </c>
+      <c r="I8" s="6" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>driver_id</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>uuid</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>drivers.driver_id (khi xóa: chặn xóa)</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>Tài xế được chấm điểm.</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>6e3b9d2a-4c1f-4e8b-9a7d-0c2e5f1b8d66</t>
+        </is>
+      </c>
+      <c r="I9" s="6" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>week_start</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="n"/>
+      <c r="F10" s="6" t="n"/>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>Thứ Hai của tuần được chấm.</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="I10" s="6" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>score</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>numeric(5,2)</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="n"/>
+      <c r="F11" s="6" t="n"/>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>Điểm an toàn từ 0 đến 100.</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>86.50</t>
+        </is>
+      </c>
+      <c r="I11" s="6" t="n"/>
+    </row>
+    <row r="12" ht="27" customHeight="1">
+      <c r="A12" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>breakdown</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>jsonb</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="n"/>
+      <c r="F12" s="6" t="n"/>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>Mức đóng góp của từng yếu tố, dạng JSON.</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>{"harsh_braking": -6.0, "speeding": -4.5, "continuous_driving": -3.0}</t>
+        </is>
+      </c>
+      <c r="I12" s="6" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>computed_at</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>timestamptz</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="n"/>
+      <c r="F13" s="6" t="n"/>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>Thời điểm tính điểm.</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-21T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="I13" s="6" t="n"/>
+    </row>
+    <row r="14"/>
+    <row r="15">
+      <c r="A15" s="4" t="n"/>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>Chỉ mục (index)</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>Các cột</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>Duy nhất</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="n"/>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>Ghi chú</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="27" customHeight="1">
+      <c r="A16" s="6" t="n"/>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>(không tên)</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>driver_id, week_start</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="n"/>
+      <c r="F16" s="6" t="n"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A6:I13"/>
+  <hyperlinks>
+    <hyperlink ref="A2" location="'Tổng quan'!A1"/>
+    <hyperlink ref="F8" location="'organizations'!A1"/>
+    <hyperlink ref="F9" location="'drivers'!A1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet81.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="7" max="7"/>
+    <col width="42" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>62. promotion_campaigns: Chiến dịch khuyến mãi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t>← Tổng quan</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>Miền nghiệp vụ: Chưa phân miền (unassigned)   ·   Chủ sở hữu dữ liệu: Nội bộ   ·   Tính năng: F-F4</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>Một chiến dịch nhắc bảo dưỡng hoặc khuyến mãi.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5"/>
+    <row r="6" ht="27" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Cột</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Kiểu dữ liệu</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Cho phép rỗng</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>Khóa</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>Tham chiếu tới</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>Ý nghĩa</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>Ví dụ</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>Lưu lịch sử</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>campaign_id</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>uuid</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="n"/>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>Mã nội bộ của chiến dịch.</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>00000013-5a6b-4c7d-8e9f-0a1b2c3d4e5f</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>varchar(200)</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="n"/>
+      <c r="F8" s="6" t="n"/>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>Tên chiến dịch.</t>
+        </is>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>Giảm 10% sạc đêm tháng 10</t>
+        </is>
+      </c>
+      <c r="I8" s="6" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>starts_at</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>timestamptz</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="n"/>
+      <c r="F9" s="6" t="n"/>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>Thời điểm bắt đầu.</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="I9" s="6" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>ends_at</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>timestamptz</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="n"/>
+      <c r="F10" s="6" t="n"/>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>Thời điểm kết thúc; NULL nếu không thời hạn.</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-31T16:59:59Z</t>
+        </is>
+      </c>
+      <c r="I10" s="6" t="n"/>
+    </row>
+    <row r="11" ht="27" customHeight="1">
+      <c r="A11" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>jsonb</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="n"/>
+      <c r="F11" s="6" t="n"/>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>Đối tượng nhận, dạng tiêu chí JSON.</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>{"vehicle_models": ["EVT-400"], "organizations": "all"}</t>
+        </is>
+      </c>
+      <c r="I11" s="6" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>varchar(20)</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="n"/>
+      <c r="F12" s="6" t="n"/>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>Trạng thái chiến dịch.</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>SCHEDULED</t>
+        </is>
+      </c>
+      <c r="I12" s="6" t="n"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A6:I12"/>
+  <hyperlinks>
+    <hyperlink ref="A2" location="'Tổng quan'!A1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet82.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:I14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -51496,7 +53172,7 @@
     <row r="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>62. trips: Chuyến đi</t>
+          <t>63. trips: Chuyến đi</t>
         </is>
       </c>
     </row>

--- a/docs/design/domain-model/domain-model.xlsx
+++ b/docs/design/domain-model/domain-model.xlsx
@@ -76,8 +76,8 @@
     <sheet name="tariffs" sheetId="67" state="visible" r:id="rId67"/>
     <sheet name="tariff_history" sheetId="68" state="visible" r:id="rId68"/>
     <sheet name="tariff_versions" sheetId="69" state="visible" r:id="rId69"/>
-    <sheet name="charging_session_charges" sheetId="70" state="visible" r:id="rId70"/>
-    <sheet name="charging_session_charge_history" sheetId="71" state="visible" r:id="rId71"/>
+    <sheet name="charging_session_bills" sheetId="70" state="visible" r:id="rId70"/>
+    <sheet name="charging_session_bill_history" sheetId="71" state="visible" r:id="rId71"/>
     <sheet name="payments" sheetId="72" state="visible" r:id="rId72"/>
     <sheet name="wallets" sheetId="73" state="visible" r:id="rId73"/>
     <sheet name="wallet_transactions" sheetId="74" state="visible" r:id="rId74"/>
@@ -159,8 +159,8 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="66" hidden="1">'tariffs'!$A$7:$I$16</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="67" hidden="1">'tariff_history'!$A$7:$I$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="68" hidden="1">'tariff_versions'!$A$6:$I$16</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="69" hidden="1">'charging_session_charges'!$A$7:$I$21</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="70" hidden="1">'charging_session_charge_history'!$A$7:$I$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="69" hidden="1">'charging_session_bills'!$A$7:$I$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="70" hidden="1">'charging_session_bill_history'!$A$7:$I$25</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="71" hidden="1">'payments'!$A$6:$I$16</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="72" hidden="1">'wallets'!$A$6:$I$12</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="73" hidden="1">'wallet_transactions'!$A$6:$I$15</definedName>
@@ -4153,12 +4153,12 @@
       </c>
       <c r="C88" s="7" t="inlineStr">
         <is>
-          <t>charging_session_charges</t>
+          <t>charging_session_bills</t>
         </is>
       </c>
       <c r="D88" s="7" t="inlineStr">
         <is>
-          <t>Phí phiên sạc</t>
+          <t>Phiếu tính tiền phiên sạc</t>
         </is>
       </c>
       <c r="E88" s="6" t="inlineStr">
@@ -4173,7 +4173,7 @@
       </c>
       <c r="G88" s="6" t="inlineStr">
         <is>
-          <t>Chi phí của một lần sạc (BL-10, CE-12, PAY-10): đơn giá chốt khi quét mã, số kWh tính tiền và số tiền. Thuộc miền thanh toán, trỏ tới phiên sạc, không bao giờ ngược lại. Số tiền là số đã thu sau làm tròn nên được lưu cố định, giống nhau trên biên nhận, thanh toán và hóa đơn điện tử. Bật lịch sử thay đổi: cho tính tiền một khoản bị giữ là quyết định của con người. Không sửa sau khi BILLED; sai sót được điều chỉnh bằng hoàn tiền hoặc hóa đơn điều chỉnh. Ràng buộc kiểm tra (BL-10): khoản BILLED phải đủ điện năng, nguồn, số tiền và thời điểm; khoản QUOTED hoặc VOID không có các giá trị đó.</t>
+          <t>Phiếu tính tiền của một phiên sạc (BL-10, BL-11, CE-12, PAY-10): đơn giá chốt khi quét mã, số kWh tính tiền và số tiền. Thuộc miền thanh toán, trỏ tới phiên sạc, không bao giờ ngược lại. Số tiền là số đã thu sau làm tròn nên được lưu cố định, giống nhau trên biên nhận, thanh toán và hóa đơn điện tử. Bật lịch sử thay đổi: cho tính tiền một phiếu bị giữ là quyết định của con người. Không sửa sau khi BILLED; sai sót được điều chỉnh bằng hoàn tiền hoặc hóa đơn điều chỉnh. Ràng buộc kiểm tra (BL-10): khoản BILLED phải đủ điện năng, nguồn, số tiền và thời điểm; khoản QUOTED hoặc VOID không có các giá trị đó.</t>
         </is>
       </c>
       <c r="H88" s="6" t="n">
@@ -4198,12 +4198,12 @@
       </c>
       <c r="C89" s="7" t="inlineStr">
         <is>
-          <t>charging_session_charge_history</t>
+          <t>charging_session_bill_history</t>
         </is>
       </c>
       <c r="D89" s="7" t="inlineStr">
         <is>
-          <t>Lịch sử phí phiên sạc</t>
+          <t>Lịch sử phiếu tính tiền phiên sạc</t>
         </is>
       </c>
       <c r="E89" s="6" t="inlineStr">
@@ -4218,7 +4218,7 @@
       </c>
       <c r="G89" s="6" t="inlineStr">
         <is>
-          <t>Mọi phiên bản trước đây của một dòng trong bảng charging_session_charges: bản sao toàn bộ dòng, chụp ngay trước khi thay đổi và được trigger ghi trong cùng giao dịch. Do công cụ domain-model tự sinh từ @tracked *, không bao giờ viết tay.</t>
+          <t>Mọi phiên bản trước đây của một dòng trong bảng charging_session_bills: bản sao toàn bộ dòng, chụp ngay trước khi thay đổi và được trigger ghi trong cùng giao dịch. Do công cụ domain-model tự sinh từ @tracked *, không bao giờ viết tay.</t>
         </is>
       </c>
       <c r="H89" s="6" t="n">
@@ -5235,12 +5235,12 @@
     <hyperlink ref="C87" location="'tariff_versions'!A1"/>
     <hyperlink ref="D87" location="'tariff_versions'!A1"/>
     <hyperlink ref="I87" location="'tariff_versions'!A1"/>
-    <hyperlink ref="C88" location="'charging_session_charges'!A1"/>
-    <hyperlink ref="D88" location="'charging_session_charges'!A1"/>
-    <hyperlink ref="I88" location="'charging_session_charges'!A1"/>
-    <hyperlink ref="C89" location="'charging_session_charge_history'!A1"/>
-    <hyperlink ref="D89" location="'charging_session_charge_history'!A1"/>
-    <hyperlink ref="I89" location="'charging_session_charge_history'!A1"/>
+    <hyperlink ref="C88" location="'charging_session_bills'!A1"/>
+    <hyperlink ref="D88" location="'charging_session_bills'!A1"/>
+    <hyperlink ref="I88" location="'charging_session_bills'!A1"/>
+    <hyperlink ref="C89" location="'charging_session_bill_history'!A1"/>
+    <hyperlink ref="D89" location="'charging_session_bill_history'!A1"/>
+    <hyperlink ref="I89" location="'charging_session_bill_history'!A1"/>
     <hyperlink ref="C90" location="'payments'!A1"/>
     <hyperlink ref="D90" location="'payments'!A1"/>
     <hyperlink ref="I90" location="'payments'!A1"/>
@@ -27385,7 +27385,7 @@
       <c r="A67" s="6" t="n"/>
       <c r="B67" s="7" t="inlineStr">
         <is>
-          <t>charging_session_charge_history</t>
+          <t>charging_session_bill_history</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
@@ -27443,7 +27443,7 @@
     <hyperlink ref="B64" location="'charging_evse_history'!A1"/>
     <hyperlink ref="B65" location="'charging_connector_history'!A1"/>
     <hyperlink ref="B66" location="'tariff_history'!A1"/>
-    <hyperlink ref="B67" location="'charging_session_charge_history'!A1"/>
+    <hyperlink ref="B67" location="'charging_session_bill_history'!A1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -39295,7 +39295,7 @@
       <c r="A48" s="6" t="n"/>
       <c r="B48" s="7" t="inlineStr">
         <is>
-          <t>charging_session_charges</t>
+          <t>charging_session_bills</t>
         </is>
       </c>
       <c r="C48" s="6" t="inlineStr">
@@ -39357,7 +39357,7 @@
     <hyperlink ref="B45" location="'charging_session_events'!A1"/>
     <hyperlink ref="B46" location="'charging_session_measurements'!A1"/>
     <hyperlink ref="B47" location="'policy_violations'!A1"/>
-    <hyperlink ref="B48" location="'charging_session_charges'!A1"/>
+    <hyperlink ref="B48" location="'charging_session_bills'!A1"/>
     <hyperlink ref="B49" location="'payments'!A1"/>
     <hyperlink ref="B50" location="'wallet_transactions'!A1"/>
     <hyperlink ref="B51" location="'invoice_lines'!A1"/>
@@ -46309,7 +46309,7 @@
       <c r="A23" s="6" t="n"/>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>charging_session_charges</t>
+          <t>charging_session_bills</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
@@ -46324,7 +46324,7 @@
     <hyperlink ref="A2" location="'Tổng quan'!A1"/>
     <hyperlink ref="F8" location="'tariffs'!A1"/>
     <hyperlink ref="F15" location="'users'!A1"/>
-    <hyperlink ref="B23" location="'charging_session_charges'!A1"/>
+    <hyperlink ref="B23" location="'charging_session_bills'!A1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -47026,7 +47026,7 @@
     <row r="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>52. charging_session_charges: Phí phiên sạc</t>
+          <t>52. charging_session_bills: Phiếu tính tiền phiên sạc</t>
         </is>
       </c>
     </row>
@@ -47047,14 +47047,14 @@
     <row r="4">
       <c r="A4" s="11" t="inlineStr">
         <is>
-          <t>Chi phí của một lần sạc (BL-10, CE-12, PAY-10): đơn giá chốt khi quét mã, số kWh tính tiền và số tiền. Thuộc miền thanh toán, trỏ tới phiên sạc, không bao giờ ngược lại. Số tiền là số đã thu sau làm tròn nên được lưu cố định, giống nhau trên biên nhận, thanh toán và hóa đơn điện tử. Bật lịch sử thay đổi: cho tính tiền một khoản bị giữ là quyết định của con người. Không sửa sau khi BILLED; sai sót được điều chỉnh bằng hoàn tiền hoặc hóa đơn điều chỉnh. Ràng buộc kiểm tra (BL-10): khoản BILLED phải đủ điện năng, nguồn, số tiền và thời điểm; khoản QUOTED hoặc VOID không có các giá trị đó.</t>
+          <t>Phiếu tính tiền của một phiên sạc (BL-10, BL-11, CE-12, PAY-10): đơn giá chốt khi quét mã, số kWh tính tiền và số tiền. Thuộc miền thanh toán, trỏ tới phiên sạc, không bao giờ ngược lại. Số tiền là số đã thu sau làm tròn nên được lưu cố định, giống nhau trên biên nhận, thanh toán và hóa đơn điện tử. Bật lịch sử thay đổi: cho tính tiền một phiếu bị giữ là quyết định của con người. Không sửa sau khi BILLED; sai sót được điều chỉnh bằng hoàn tiền hoặc hóa đơn điều chỉnh. Ràng buộc kiểm tra (BL-10): khoản BILLED phải đủ điện năng, nguồn, số tiền và thời điểm; khoản QUOTED hoặc VOID không có các giá trị đó.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="10" t="inlineStr">
         <is>
-          <t>🔍 Lưu lịch sử: khi một cột có dấu 🔍 thay đổi, toàn bộ dòng cũ được chép sang bảng charging_session_charge_history.</t>
+          <t>🔍 Lưu lịch sử: khi một cột có dấu 🔍 thay đổi, toàn bộ dòng cũ được chép sang bảng charging_session_bill_history.</t>
         </is>
       </c>
     </row>
@@ -47106,13 +47106,13 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="27" customHeight="1">
+    <row r="8">
       <c r="A8" s="6" t="n">
         <v>1</v>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>charging_session_charge_id</t>
+          <t>charging_session_bill_id</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
@@ -47133,7 +47133,7 @@
       <c r="F8" s="6" t="n"/>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>Mã nội bộ của khoản phí sạc.</t>
+          <t>Mã nội bộ của phiếu tính tiền.</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr">
@@ -47174,7 +47174,7 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>Phiên sạc; mỗi phiên một khoản phí. Bên trả tiền đọc từ phiên (charging_sessions.organization_id, DM-24).</t>
+          <t>Phiên sạc; mỗi phiên một phiếu tính tiền. Bên trả tiền đọc từ phiên (charging_sessions.organization_id, DM-24).</t>
         </is>
       </c>
       <c r="H9" s="6" t="inlineStr">
@@ -47669,7 +47669,7 @@
       <c r="A24" s="6" t="n"/>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>ix_charging_session_charges_tariff_version_id</t>
+          <t>ix_charging_session_bills_tariff_version_id</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
@@ -47689,7 +47689,7 @@
       <c r="A25" s="6" t="n"/>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>ix_charging_session_charges_status_created</t>
+          <t>ix_charging_session_bills_status_created</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
@@ -47727,12 +47727,12 @@
       <c r="A28" s="6" t="n"/>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>charging_session_charge_history</t>
+          <t>charging_session_bill_history</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>charging_session_charge_id</t>
+          <t>charging_session_bill_id</t>
         </is>
       </c>
     </row>
@@ -47740,10 +47740,10 @@
   <autoFilter ref="A7:I21"/>
   <hyperlinks>
     <hyperlink ref="A2" location="'Tổng quan'!A1"/>
-    <hyperlink ref="A5" location="'charging_session_charge_history'!A1"/>
+    <hyperlink ref="A5" location="'charging_session_bill_history'!A1"/>
     <hyperlink ref="F9" location="'charging_sessions'!A1"/>
     <hyperlink ref="F10" location="'tariff_versions'!A1"/>
-    <hyperlink ref="B28" location="'charging_session_charge_history'!A1"/>
+    <hyperlink ref="B28" location="'charging_session_bill_history'!A1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -47772,7 +47772,7 @@
     <row r="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>52.h. charging_session_charge_history: Lịch sử phí phiên sạc</t>
+          <t>52.h. charging_session_bill_history: Lịch sử phiếu tính tiền phiên sạc</t>
         </is>
       </c>
     </row>
@@ -47793,14 +47793,14 @@
     <row r="4">
       <c r="A4" s="11" t="inlineStr">
         <is>
-          <t>Mọi phiên bản trước đây của một dòng trong bảng charging_session_charges: bản sao toàn bộ dòng, chụp ngay trước khi thay đổi và được trigger ghi trong cùng giao dịch. Do công cụ domain-model tự sinh từ @tracked *, không bao giờ viết tay.</t>
+          <t>Mọi phiên bản trước đây của một dòng trong bảng charging_session_bills: bản sao toàn bộ dòng, chụp ngay trước khi thay đổi và được trigger ghi trong cùng giao dịch. Do công cụ domain-model tự sinh từ @tracked *, không bao giờ viết tay.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="10" t="inlineStr">
         <is>
-          <t>Bảng lịch sử của: charging_session_charges</t>
+          <t>Bảng lịch sử của: charging_session_bills</t>
         </is>
       </c>
     </row>
@@ -47895,7 +47895,7 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>charging_session_charge_id</t>
+          <t>charging_session_bill_id</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
@@ -47915,12 +47915,12 @@
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>charging_session_charges.charging_session_charge_id (khi xóa: chặn xóa)</t>
+          <t>charging_session_bills.charging_session_bill_id (khi xóa: chặn xóa)</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>Giá trị trước khi thay đổi (charging_session_charges.charging_session_charge_id).</t>
+          <t>Giá trị trước khi thay đổi (charging_session_bills.charging_session_bill_id).</t>
         </is>
       </c>
       <c r="H9" s="6" t="inlineStr">
@@ -47953,7 +47953,7 @@
       <c r="F10" s="6" t="n"/>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>Giá trị trước khi thay đổi (charging_session_charges.session_id).</t>
+          <t>Giá trị trước khi thay đổi (charging_session_bills.session_id).</t>
         </is>
       </c>
       <c r="H10" s="6" t="inlineStr">
@@ -47986,7 +47986,7 @@
       <c r="F11" s="6" t="n"/>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>Giá trị trước khi thay đổi (charging_session_charges.tariff_version_id).</t>
+          <t>Giá trị trước khi thay đổi (charging_session_bills.tariff_version_id).</t>
         </is>
       </c>
       <c r="H11" s="6" t="inlineStr">
@@ -48019,7 +48019,7 @@
       <c r="F12" s="6" t="n"/>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>Giá trị trước khi thay đổi (charging_session_charges.price_per_kwh).</t>
+          <t>Giá trị trước khi thay đổi (charging_session_bills.price_per_kwh).</t>
         </is>
       </c>
       <c r="H12" s="6" t="inlineStr">
@@ -48052,7 +48052,7 @@
       <c r="F13" s="6" t="n"/>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>Giá trị trước khi thay đổi (charging_session_charges.vat_rate_percent).</t>
+          <t>Giá trị trước khi thay đổi (charging_session_bills.vat_rate_percent).</t>
         </is>
       </c>
       <c r="H13" s="6" t="inlineStr">
@@ -48085,7 +48085,7 @@
       <c r="F14" s="6" t="n"/>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>Giá trị trước khi thay đổi (charging_session_charges.status).</t>
+          <t>Giá trị trước khi thay đổi (charging_session_bills.status).</t>
         </is>
       </c>
       <c r="H14" s="6" t="inlineStr">
@@ -48118,7 +48118,7 @@
       <c r="F15" s="6" t="n"/>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>Giá trị trước khi thay đổi (charging_session_charges.status_reason).</t>
+          <t>Giá trị trước khi thay đổi (charging_session_bills.status_reason).</t>
         </is>
       </c>
       <c r="H15" s="6" t="inlineStr">
@@ -48151,7 +48151,7 @@
       <c r="F16" s="6" t="n"/>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>Giá trị trước khi thay đổi (charging_session_charges.energy_wh).</t>
+          <t>Giá trị trước khi thay đổi (charging_session_bills.energy_wh).</t>
         </is>
       </c>
       <c r="H16" s="6" t="inlineStr">
@@ -48184,7 +48184,7 @@
       <c r="F17" s="6" t="n"/>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>Giá trị trước khi thay đổi (charging_session_charges.energy_source).</t>
+          <t>Giá trị trước khi thay đổi (charging_session_bills.energy_source).</t>
         </is>
       </c>
       <c r="H17" s="6" t="inlineStr">
@@ -48217,7 +48217,7 @@
       <c r="F18" s="6" t="n"/>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>Giá trị trước khi thay đổi (charging_session_charges.amount_before_vat).</t>
+          <t>Giá trị trước khi thay đổi (charging_session_bills.amount_before_vat).</t>
         </is>
       </c>
       <c r="H18" s="6" t="inlineStr">
@@ -48250,7 +48250,7 @@
       <c r="F19" s="6" t="n"/>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>Giá trị trước khi thay đổi (charging_session_charges.vat_amount).</t>
+          <t>Giá trị trước khi thay đổi (charging_session_bills.vat_amount).</t>
         </is>
       </c>
       <c r="H19" s="6" t="inlineStr">
@@ -48283,7 +48283,7 @@
       <c r="F20" s="6" t="n"/>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>Giá trị trước khi thay đổi (charging_session_charges.billed_at).</t>
+          <t>Giá trị trước khi thay đổi (charging_session_bills.billed_at).</t>
         </is>
       </c>
       <c r="H20" s="6" t="inlineStr">
@@ -48316,7 +48316,7 @@
       <c r="F21" s="6" t="n"/>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>Giá trị trước khi thay đổi (charging_session_charges.created_at).</t>
+          <t>Giá trị trước khi thay đổi (charging_session_bills.created_at).</t>
         </is>
       </c>
       <c r="H21" s="6" t="inlineStr">
@@ -48349,7 +48349,7 @@
       <c r="F22" s="6" t="n"/>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>Giá trị trước khi thay đổi (charging_session_charges.updated_at).</t>
+          <t>Giá trị trước khi thay đổi (charging_session_bills.updated_at).</t>
         </is>
       </c>
       <c r="H22" s="6" t="inlineStr">
@@ -48495,12 +48495,12 @@
       <c r="A28" s="6" t="n"/>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>ix_charging_session_charge_history_charging_session_charge_id_time</t>
+          <t>ix_charging_session_bill_history_charging_session_bill_id_time</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>charging_session_charge_id, changed_at</t>
+          <t>charging_session_bill_id, changed_at</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
@@ -48515,8 +48515,8 @@
   <autoFilter ref="A7:I25"/>
   <hyperlinks>
     <hyperlink ref="A2" location="'Tổng quan'!A1"/>
-    <hyperlink ref="A5" location="'charging_session_charges'!A1"/>
-    <hyperlink ref="F9" location="'charging_session_charges'!A1"/>
+    <hyperlink ref="A5" location="'charging_session_bills'!A1"/>
+    <hyperlink ref="F9" location="'charging_session_bills'!A1"/>
     <hyperlink ref="F24" location="'users'!A1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/design/domain-model/domain-model.xlsx
+++ b/docs/design/domain-model/domain-model.xlsx
@@ -80,15 +80,16 @@
     <sheet name="charging_session_bill_history" sheetId="71" state="visible" r:id="rId71"/>
     <sheet name="payments" sheetId="72" state="visible" r:id="rId72"/>
     <sheet name="wallets" sheetId="73" state="visible" r:id="rId73"/>
-    <sheet name="wallet_transactions" sheetId="74" state="visible" r:id="rId74"/>
-    <sheet name="invoices" sheetId="75" state="visible" r:id="rId75"/>
-    <sheet name="invoice_lines" sheetId="76" state="visible" r:id="rId76"/>
-    <sheet name="subscription_plans" sheetId="77" state="visible" r:id="rId77"/>
-    <sheet name="plan_features" sheetId="78" state="visible" r:id="rId78"/>
-    <sheet name="subscriptions" sheetId="79" state="visible" r:id="rId79"/>
-    <sheet name="driver_scores" sheetId="80" state="visible" r:id="rId80"/>
-    <sheet name="promotion_campaigns" sheetId="81" state="visible" r:id="rId81"/>
-    <sheet name="trips" sheetId="82" state="visible" r:id="rId82"/>
+    <sheet name="wallet_history" sheetId="74" state="visible" r:id="rId74"/>
+    <sheet name="wallet_transactions" sheetId="75" state="visible" r:id="rId75"/>
+    <sheet name="invoices" sheetId="76" state="visible" r:id="rId76"/>
+    <sheet name="invoice_lines" sheetId="77" state="visible" r:id="rId77"/>
+    <sheet name="subscription_plans" sheetId="78" state="visible" r:id="rId78"/>
+    <sheet name="plan_features" sheetId="79" state="visible" r:id="rId79"/>
+    <sheet name="subscriptions" sheetId="80" state="visible" r:id="rId80"/>
+    <sheet name="driver_scores" sheetId="81" state="visible" r:id="rId81"/>
+    <sheet name="promotion_campaigns" sheetId="82" state="visible" r:id="rId82"/>
+    <sheet name="trips" sheetId="83" state="visible" r:id="rId83"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'organizations'!$A$7:$I$20</definedName>
@@ -161,17 +162,18 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="68" hidden="1">'tariff_versions'!$A$6:$I$16</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="69" hidden="1">'charging_session_bills'!$A$7:$I$21</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="70" hidden="1">'charging_session_bill_history'!$A$7:$I$25</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="71" hidden="1">'payments'!$A$6:$I$16</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="72" hidden="1">'wallets'!$A$6:$I$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="73" hidden="1">'wallet_transactions'!$A$6:$I$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="74" hidden="1">'invoices'!$A$6:$I$16</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="75" hidden="1">'invoice_lines'!$A$6:$I$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="76" hidden="1">'subscription_plans'!$A$6:$I$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="77" hidden="1">'plan_features'!$A$6:$I$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="78" hidden="1">'subscriptions'!$A$6:$I$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="79" hidden="1">'driver_scores'!$A$6:$I$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="80" hidden="1">'promotion_campaigns'!$A$6:$I$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="81" hidden="1">'trips'!$A$6:$I$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="71" hidden="1">'payments'!$A$6:$I$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="72" hidden="1">'wallets'!$A$7:$I$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="73" hidden="1">'wallet_history'!$A$7:$I$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="74" hidden="1">'wallet_transactions'!$A$6:$I$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="75" hidden="1">'invoices'!$A$6:$I$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="76" hidden="1">'invoice_lines'!$A$6:$I$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="77" hidden="1">'subscription_plans'!$A$6:$I$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="78" hidden="1">'plan_features'!$A$6:$I$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="79" hidden="1">'subscriptions'!$A$6:$I$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="80" hidden="1">'driver_scores'!$A$6:$I$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="81" hidden="1">'promotion_campaigns'!$A$6:$I$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="82" hidden="1">'trips'!$A$6:$I$14</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -691,7 +693,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>81 bảng trong 16 miền nghiệp vụ: 60 bảng chính, 18 bảng lịch sử (N.h), 3 bảng trạng thái. Bấm vào tên bảng hoặc «→ Mở» để mở sheet chi tiết của bảng; chú giải và các quyết định còn mở nằm ở cuối trang.</t>
+          <t>82 bảng trong 16 miền nghiệp vụ: 60 bảng chính, 19 bảng lịch sử (N.h), 3 bảng trạng thái. Bấm vào tên bảng hoặc «→ Mở» để mở sheet chi tiết của bảng; chú giải và các quyết định còn mở nằm ở cuối trang.</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3980,7 @@
         </is>
       </c>
     </row>
-    <row r="84" ht="283.5" customHeight="1">
+    <row r="84" ht="297" customHeight="1">
       <c r="A84" s="5" t="n"/>
       <c r="B84" s="5" t="inlineStr">
         <is>
@@ -3987,7 +3989,7 @@
       </c>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t>13 bảng</t>
+          <t>14 bảng</t>
         </is>
       </c>
       <c r="D84" s="5" t="n"/>
@@ -3997,7 +3999,7 @@
         <is>
           <t>Tiền: giá điện, thanh toán, ví trả trước, hóa đơn điện tử và thuê bao SaaS.
 • Biểu giá định giá điện cho toàn mạng hoặc từng trạm, theo khung giờ.
-• Một thanh toán thường cho một phiên sạc; một ví thuộc một tổ chức hoặc một tài xế (D5).
+• Một ví là số dư trả trước của một người (khi ra mắt) hoặc một tổ chức (sau này); giao dịch ví là sổ chỉ ghi thêm. Một thanh toán là tiền thật qua cổng: nạp tiền hoặc hoàn tiền khi ra mắt (BL-12 đến BL-14).
 • Một hóa đơn thuộc một tổ chức và có các dòng hóa đơn cho phiên sạc hoặc kỳ thuê bao.
 • Một thuê bao đưa một xe vào một gói dịch vụ.
 • Muốn tính tiền một phiên sạc phải biết phiên đó của ai.
@@ -4230,7 +4232,7 @@
         </is>
       </c>
     </row>
-    <row r="90" ht="27" customHeight="1">
+    <row r="90" ht="81" customHeight="1">
       <c r="A90" s="6" t="inlineStr">
         <is>
           <t>53</t>
@@ -4263,11 +4265,11 @@
       </c>
       <c r="G90" s="6" t="inlineStr">
         <is>
-          <t>Một lần thanh toán qua cổng thanh toán hoặc ví, thường cho một phiên sạc.</t>
+          <t>Tiền đi qua cổng thanh toán hoặc ngân hàng (BL-12): chỉ tiền thật vào hoặc ra. Trả tiền phiên sạc bằng ví là giao dịch ví, không phải thanh toán. Khi ra mắt chỉ có TOP_UP và REFUND; SESSION_BILL và INVOICE đến cùng các phương thức sau. Không có lịch sử thay đổi (trạng thái do cổng báo); không xóa mềm (chứng từ tài chính). Thẻ đã lưu (mã hóa token) là bảng sau này. Ràng buộc kiểm tra (BL-12): liên kết có giá trị khớp với mục đích.</t>
         </is>
       </c>
       <c r="H90" s="6" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="I90" s="7" t="inlineStr">
         <is>
@@ -4275,7 +4277,7 @@
         </is>
       </c>
     </row>
-    <row r="91" ht="27" customHeight="1">
+    <row r="91" ht="135" customHeight="1">
       <c r="A91" s="6" t="inlineStr">
         <is>
           <t>54</t>
@@ -4308,11 +4310,11 @@
       </c>
       <c r="G91" s="6" t="inlineStr">
         <is>
-          <t>Số dư trả trước của một tài xế hoặc của cả tổ chức.</t>
+          <t>Số dư trả trước chỉ dùng cho dịch vụ của chính chúng ta (BL-13). Khi ra mắt, mỗi người tự nạp tiền vào ví của mình và trả từng phiên sạc từ đó; ví của tổ chức được chuẩn bị cho các phương thức sau. Để bắt đầu sạc, số dư phải bằng hoặc cao hơn mức tối thiểu đặt trong backend (BL-14); kiểm tra khi quét mã, không bằng ràng buộc cơ sở dữ liệu, vì lần trừ tiền cuối phiên có thể làm số dư âm, sau đó người dùng không thể sạc tiếp cho tới khi nạp lại trên mức tối thiểu. Bật lịch sử thay đổi cho các quyết định (khóa ví), trừ cột balance vì mọi giao dịch đều làm thay đổi nó. Không xóa mềm. Không gọi là ví điện tử khi giới thiệu ra bên ngoài (câu hỏi mở 11). Ràng buộc kiểm tra (BL-13): chỉ đúng một chủ sở hữu.</t>
         </is>
       </c>
       <c r="H91" s="6" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I91" s="7" t="inlineStr">
         <is>
@@ -4320,85 +4322,85 @@
         </is>
       </c>
     </row>
-    <row r="92" ht="27" customHeight="1">
+    <row r="92" ht="40.5" customHeight="1">
       <c r="A92" s="6" t="inlineStr">
         <is>
+          <t>54.h</t>
+        </is>
+      </c>
+      <c r="B92" s="6" t="inlineStr">
+        <is>
+          <t>Thanh toán &amp; hóa đơn (billing)</t>
+        </is>
+      </c>
+      <c r="C92" s="7" t="inlineStr">
+        <is>
+          <t>wallet_history</t>
+        </is>
+      </c>
+      <c r="D92" s="7" t="inlineStr">
+        <is>
+          <t>Lịch sử ví</t>
+        </is>
+      </c>
+      <c r="E92" s="6" t="inlineStr">
+        <is>
+          <t>Khách hàng</t>
+        </is>
+      </c>
+      <c r="F92" s="6" t="inlineStr">
+        <is>
+          <t>F-H2</t>
+        </is>
+      </c>
+      <c r="G92" s="6" t="inlineStr">
+        <is>
+          <t>Mọi phiên bản trước đây của một dòng trong bảng wallets: bản sao toàn bộ dòng, chụp ngay trước khi thay đổi và được trigger ghi trong cùng giao dịch. Do công cụ domain-model tự sinh từ @tracked *, không bao giờ viết tay.</t>
+        </is>
+      </c>
+      <c r="H92" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="I92" s="7" t="inlineStr">
+        <is>
+          <t>→ Mở</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="54" customHeight="1">
+      <c r="A93" s="6" t="inlineStr">
+        <is>
           <t>55</t>
         </is>
       </c>
-      <c r="B92" s="6" t="inlineStr">
+      <c r="B93" s="6" t="inlineStr">
         <is>
           <t>Thanh toán &amp; hóa đơn (billing)</t>
         </is>
       </c>
-      <c r="C92" s="7" t="inlineStr">
+      <c r="C93" s="7" t="inlineStr">
         <is>
           <t>wallet_transactions</t>
         </is>
       </c>
-      <c r="D92" s="7" t="inlineStr">
+      <c r="D93" s="7" t="inlineStr">
         <is>
           <t>Giao dịch ví</t>
         </is>
       </c>
-      <c r="E92" s="6" t="inlineStr">
+      <c r="E93" s="6" t="inlineStr">
         <is>
           <t>Khách hàng</t>
         </is>
       </c>
-      <c r="F92" s="6" t="inlineStr">
+      <c r="F93" s="6" t="inlineStr">
         <is>
           <t>F-H2</t>
         </is>
       </c>
-      <c r="G92" s="6" t="inlineStr">
-        <is>
-          <t>Biến động tiền vào/ra khỏi ví, chỉ ghi thêm.</t>
-        </is>
-      </c>
-      <c r="H92" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="I92" s="7" t="inlineStr">
-        <is>
-          <t>→ Mở</t>
-        </is>
-      </c>
-    </row>
-    <row r="93" ht="27" customHeight="1">
-      <c r="A93" s="6" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="B93" s="6" t="inlineStr">
-        <is>
-          <t>Thanh toán &amp; hóa đơn (billing)</t>
-        </is>
-      </c>
-      <c r="C93" s="7" t="inlineStr">
-        <is>
-          <t>invoices</t>
-        </is>
-      </c>
-      <c r="D93" s="7" t="inlineStr">
-        <is>
-          <t>Hóa đơn</t>
-        </is>
-      </c>
-      <c r="E93" s="6" t="inlineStr">
-        <is>
-          <t>Khách hàng</t>
-        </is>
-      </c>
-      <c r="F93" s="6" t="inlineStr">
-        <is>
-          <t>F-H3, F-H4</t>
-        </is>
-      </c>
       <c r="G93" s="6" t="inlineStr">
         <is>
-          <t>Một hóa đơn điện tử hợp lệ. Khi đã PHÁT HÀNH thì không sửa, chỉ điều chỉnh hoặc hủy bằng hóa đơn mới.</t>
+          <t>Sổ giao dịch chỉ ghi thêm của ví (BL-14): mọi lần nạp, trả tiền phiên sạc, hoàn tiền và điều chỉnh của nhân viên, kèm số dư ngay sau đó. Không bao giờ sửa hay xóa; sai sót được sửa bằng một ADJUSTMENT. Ràng buộc kiểm tra (BL-14): liên kết và dấu số tiền khớp với loại giao dịch.</t>
         </is>
       </c>
       <c r="H93" s="6" t="n">
@@ -4413,619 +4415,647 @@
     <row r="94" ht="27" customHeight="1">
       <c r="A94" s="6" t="inlineStr">
         <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="B94" s="6" t="inlineStr">
+        <is>
+          <t>Thanh toán &amp; hóa đơn (billing)</t>
+        </is>
+      </c>
+      <c r="C94" s="7" t="inlineStr">
+        <is>
+          <t>invoices</t>
+        </is>
+      </c>
+      <c r="D94" s="7" t="inlineStr">
+        <is>
+          <t>Hóa đơn</t>
+        </is>
+      </c>
+      <c r="E94" s="6" t="inlineStr">
+        <is>
+          <t>Khách hàng</t>
+        </is>
+      </c>
+      <c r="F94" s="6" t="inlineStr">
+        <is>
+          <t>F-H3, F-H4</t>
+        </is>
+      </c>
+      <c r="G94" s="6" t="inlineStr">
+        <is>
+          <t>Một hóa đơn điện tử hợp lệ. Khi đã PHÁT HÀNH thì không sửa, chỉ điều chỉnh hoặc hủy bằng hóa đơn mới.</t>
+        </is>
+      </c>
+      <c r="H94" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="I94" s="7" t="inlineStr">
+        <is>
+          <t>→ Mở</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="27" customHeight="1">
+      <c r="A95" s="6" t="inlineStr">
+        <is>
           <t>57</t>
         </is>
       </c>
-      <c r="B94" s="6" t="inlineStr">
+      <c r="B95" s="6" t="inlineStr">
         <is>
           <t>Thanh toán &amp; hóa đơn (billing)</t>
         </is>
       </c>
-      <c r="C94" s="7" t="inlineStr">
+      <c r="C95" s="7" t="inlineStr">
         <is>
           <t>invoice_lines</t>
         </is>
       </c>
-      <c r="D94" s="7" t="inlineStr">
+      <c r="D95" s="7" t="inlineStr">
         <is>
           <t>Dòng hóa đơn</t>
         </is>
       </c>
-      <c r="E94" s="6" t="inlineStr">
+      <c r="E95" s="6" t="inlineStr">
         <is>
           <t>Khách hàng</t>
         </is>
       </c>
-      <c r="F94" s="6" t="inlineStr">
+      <c r="F95" s="6" t="inlineStr">
         <is>
           <t>F-H3, F-H4</t>
         </is>
       </c>
-      <c r="G94" s="6" t="inlineStr">
+      <c r="G95" s="6" t="inlineStr">
         <is>
           <t>Một dòng của hóa đơn: một phiên sạc hoặc một kỳ thuê bao.</t>
         </is>
       </c>
-      <c r="H94" s="6" t="n">
+      <c r="H95" s="6" t="n">
         <v>9</v>
       </c>
-      <c r="I94" s="7" t="inlineStr">
+      <c r="I95" s="7" t="inlineStr">
         <is>
           <t>→ Mở</t>
         </is>
       </c>
     </row>
-    <row r="95" ht="54" customHeight="1">
-      <c r="A95" s="6" t="inlineStr">
+    <row r="96" ht="54" customHeight="1">
+      <c r="A96" s="6" t="inlineStr">
         <is>
           <t>58</t>
         </is>
       </c>
-      <c r="B95" s="6" t="inlineStr">
+      <c r="B96" s="6" t="inlineStr">
         <is>
           <t>Thanh toán &amp; hóa đơn (billing)</t>
         </is>
       </c>
-      <c r="C95" s="7" t="inlineStr">
+      <c r="C96" s="7" t="inlineStr">
         <is>
           <t>subscription_plans</t>
         </is>
       </c>
-      <c r="D95" s="7" t="inlineStr">
+      <c r="D96" s="7" t="inlineStr">
         <is>
           <t>Gói dịch vụ</t>
         </is>
       </c>
-      <c r="E95" s="6" t="inlineStr">
+      <c r="E96" s="6" t="inlineStr">
         <is>
           <t>Nội bộ</t>
         </is>
       </c>
-      <c r="F95" s="6" t="inlineStr">
+      <c r="F96" s="6" t="inlineStr">
         <is>
           <t>F-H4</t>
         </is>
       </c>
-      <c r="G95" s="6" t="inlineStr">
+      <c r="G96" s="6" t="inlineStr">
         <is>
           <t>Một gói dịch vụ: mỗi gói là một dòng (GUEST là gói mặc định miễn phí, STANDARD, ADVANCED, PRO, ..., hoặc gói riêng cho một khách hàng); tính năng của gói nằm ở plan_features. Giá được tính theo từng tính năng (xem ghi chú của miền thanh toán).</t>
         </is>
       </c>
-      <c r="H95" s="6" t="n">
+      <c r="H96" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="I95" s="7" t="inlineStr">
+      <c r="I96" s="7" t="inlineStr">
         <is>
           <t>→ Mở</t>
         </is>
       </c>
     </row>
-    <row r="96" ht="40.5" customHeight="1">
-      <c r="A96" s="6" t="inlineStr">
+    <row r="97" ht="40.5" customHeight="1">
+      <c r="A97" s="6" t="inlineStr">
         <is>
           <t>59</t>
         </is>
       </c>
-      <c r="B96" s="6" t="inlineStr">
+      <c r="B97" s="6" t="inlineStr">
         <is>
           <t>Thanh toán &amp; hóa đơn (billing)</t>
         </is>
       </c>
-      <c r="C96" s="7" t="inlineStr">
+      <c r="C97" s="7" t="inlineStr">
         <is>
           <t>plan_features</t>
         </is>
       </c>
-      <c r="D96" s="7" t="inlineStr">
+      <c r="D97" s="7" t="inlineStr">
         <is>
           <t>Tính năng của gói dịch vụ</t>
         </is>
       </c>
-      <c r="E96" s="6" t="inlineStr">
+      <c r="E97" s="6" t="inlineStr">
         <is>
           <t>Nội bộ</t>
         </is>
       </c>
-      <c r="F96" s="6" t="inlineStr">
+      <c r="F97" s="6" t="inlineStr">
         <is>
           <t>F-H4</t>
         </is>
       </c>
-      <c r="G96" s="6" t="inlineStr">
+      <c r="G97" s="6" t="inlineStr">
         <is>
           <t>Mỗi gói dịch vụ gồm những tính năng nào. Gói dịch vụ là dữ liệu, nên G3 có thể tạo gói mới (Pro, Max, gói riêng cho một khách hàng) trên portal mà không cần lập trình viên; chỉ tính năng hoàn toàn mới mới cần viết mã.</t>
         </is>
       </c>
-      <c r="H96" s="6" t="n">
+      <c r="H97" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="I96" s="7" t="inlineStr">
+      <c r="I97" s="7" t="inlineStr">
         <is>
           <t>→ Mở</t>
         </is>
       </c>
     </row>
-    <row r="97" ht="27" customHeight="1">
-      <c r="A97" s="6" t="inlineStr">
+    <row r="98" ht="27" customHeight="1">
+      <c r="A98" s="6" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="B97" s="6" t="inlineStr">
+      <c r="B98" s="6" t="inlineStr">
         <is>
           <t>Thanh toán &amp; hóa đơn (billing)</t>
         </is>
       </c>
-      <c r="C97" s="7" t="inlineStr">
+      <c r="C98" s="7" t="inlineStr">
         <is>
           <t>subscriptions</t>
         </is>
       </c>
-      <c r="D97" s="7" t="inlineStr">
+      <c r="D98" s="7" t="inlineStr">
         <is>
           <t>Thuê bao</t>
         </is>
       </c>
-      <c r="E97" s="6" t="inlineStr">
+      <c r="E98" s="6" t="inlineStr">
         <is>
           <t>Khách hàng</t>
         </is>
       </c>
-      <c r="F97" s="6" t="inlineStr">
+      <c r="F98" s="6" t="inlineStr">
         <is>
           <t>F-H4</t>
         </is>
       </c>
-      <c r="G97" s="6" t="inlineStr">
+      <c r="G98" s="6" t="inlineStr">
         <is>
           <t>Một xe đăng ký một gói; quá hạn thanh toán sẽ khóa tính năng.</t>
         </is>
       </c>
-      <c r="H97" s="6" t="n">
+      <c r="H98" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="I97" s="7" t="inlineStr">
+      <c r="I98" s="7" t="inlineStr">
         <is>
           <t>→ Mở</t>
         </is>
       </c>
     </row>
-    <row r="98" ht="27" customHeight="1">
-      <c r="A98" s="5" t="n"/>
-      <c r="B98" s="5" t="inlineStr">
+    <row r="99" ht="27" customHeight="1">
+      <c r="A99" s="5" t="n"/>
+      <c r="B99" s="5" t="inlineStr">
         <is>
           <t>Chấm điểm tài xế (scoring)</t>
         </is>
       </c>
-      <c r="C98" s="5" t="inlineStr">
+      <c r="C99" s="5" t="inlineStr">
         <is>
           <t>1 bảng</t>
         </is>
       </c>
-      <c r="D98" s="5" t="n"/>
-      <c r="E98" s="5" t="n"/>
-      <c r="F98" s="5" t="n"/>
-      <c r="G98" s="5" t="inlineStr">
+      <c r="D99" s="5" t="n"/>
+      <c r="E99" s="5" t="n"/>
+      <c r="F99" s="5" t="n"/>
+      <c r="G99" s="5" t="inlineStr">
         <is>
           <t>Chấm điểm an toàn cho tài xế từ hành vi lái xe.
 • Mỗi tuần, mỗi tài xế có một điểm, tính từ dữ liệu vận hành của xe họ lái.</t>
         </is>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" s="6" t="inlineStr">
+    <row r="100">
+      <c r="A100" s="6" t="inlineStr">
         <is>
           <t>61</t>
         </is>
       </c>
-      <c r="B99" s="6" t="inlineStr">
+      <c r="B100" s="6" t="inlineStr">
         <is>
           <t>Chấm điểm tài xế (scoring)</t>
         </is>
       </c>
-      <c r="C99" s="7" t="inlineStr">
+      <c r="C100" s="7" t="inlineStr">
         <is>
           <t>driver_scores</t>
         </is>
       </c>
-      <c r="D99" s="7" t="inlineStr">
+      <c r="D100" s="7" t="inlineStr">
         <is>
           <t>Điểm tài xế</t>
         </is>
       </c>
-      <c r="E99" s="6" t="inlineStr">
+      <c r="E100" s="6" t="inlineStr">
         <is>
           <t>Khách hàng</t>
         </is>
       </c>
-      <c r="F99" s="6" t="inlineStr">
+      <c r="F100" s="6" t="inlineStr">
         <is>
           <t>F-K1</t>
         </is>
       </c>
-      <c r="G99" s="6" t="inlineStr">
+      <c r="G100" s="6" t="inlineStr">
         <is>
           <t>Điểm an toàn hằng tuần của tài xế, tính từ dữ liệu vận hành xe.</t>
         </is>
       </c>
-      <c r="H99" s="6" t="n">
+      <c r="H100" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="I99" s="7" t="inlineStr">
+      <c r="I100" s="7" t="inlineStr">
         <is>
           <t>→ Mở</t>
         </is>
       </c>
     </row>
-    <row r="100" ht="27" customHeight="1">
-      <c r="A100" s="5" t="n"/>
-      <c r="B100" s="5" t="inlineStr">
+    <row r="101" ht="27" customHeight="1">
+      <c r="A101" s="5" t="n"/>
+      <c r="B101" s="5" t="inlineStr">
         <is>
           <t>Chưa phân miền (unassigned)</t>
         </is>
       </c>
-      <c r="C100" s="5" t="inlineStr">
+      <c r="C101" s="5" t="inlineStr">
         <is>
           <t>2 bảng</t>
         </is>
       </c>
-      <c r="D100" s="5" t="n"/>
-      <c r="E100" s="5" t="n"/>
-      <c r="F100" s="5" t="n"/>
-      <c r="G100" s="5" t="inlineStr">
+      <c r="D101" s="5" t="n"/>
+      <c r="E101" s="5" t="n"/>
+      <c r="F101" s="5" t="n"/>
+      <c r="G101" s="5" t="inlineStr">
         <is>
           <t>Các tính năng chưa được quyết định thuộc miền nghiệp vụ nào (xem feature-list.md).</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="6" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="B101" s="6" t="inlineStr">
-        <is>
-          <t>Chưa phân miền (unassigned)</t>
-        </is>
-      </c>
-      <c r="C101" s="7" t="inlineStr">
-        <is>
-          <t>promotion_campaigns</t>
-        </is>
-      </c>
-      <c r="D101" s="7" t="inlineStr">
-        <is>
-          <t>Chiến dịch khuyến mãi</t>
-        </is>
-      </c>
-      <c r="E101" s="6" t="inlineStr">
-        <is>
-          <t>Nội bộ</t>
-        </is>
-      </c>
-      <c r="F101" s="6" t="inlineStr">
-        <is>
-          <t>F-F4</t>
-        </is>
-      </c>
-      <c r="G101" s="6" t="inlineStr">
-        <is>
-          <t>Một chiến dịch nhắc bảo dưỡng hoặc khuyến mãi.</t>
-        </is>
-      </c>
-      <c r="H101" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="I101" s="7" t="inlineStr">
-        <is>
-          <t>→ Mở</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="6" t="inlineStr">
         <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="B102" s="6" t="inlineStr">
+        <is>
+          <t>Chưa phân miền (unassigned)</t>
+        </is>
+      </c>
+      <c r="C102" s="7" t="inlineStr">
+        <is>
+          <t>promotion_campaigns</t>
+        </is>
+      </c>
+      <c r="D102" s="7" t="inlineStr">
+        <is>
+          <t>Chiến dịch khuyến mãi</t>
+        </is>
+      </c>
+      <c r="E102" s="6" t="inlineStr">
+        <is>
+          <t>Nội bộ</t>
+        </is>
+      </c>
+      <c r="F102" s="6" t="inlineStr">
+        <is>
+          <t>F-F4</t>
+        </is>
+      </c>
+      <c r="G102" s="6" t="inlineStr">
+        <is>
+          <t>Một chiến dịch nhắc bảo dưỡng hoặc khuyến mãi.</t>
+        </is>
+      </c>
+      <c r="H102" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="I102" s="7" t="inlineStr">
+        <is>
+          <t>→ Mở</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="6" t="inlineStr">
+        <is>
           <t>63</t>
         </is>
       </c>
-      <c r="B102" s="6" t="inlineStr">
+      <c r="B103" s="6" t="inlineStr">
         <is>
           <t>Chưa phân miền (unassigned)</t>
         </is>
       </c>
-      <c r="C102" s="7" t="inlineStr">
+      <c r="C103" s="7" t="inlineStr">
         <is>
           <t>trips</t>
         </is>
       </c>
-      <c r="D102" s="7" t="inlineStr">
+      <c r="D103" s="7" t="inlineStr">
         <is>
           <t>Chuyến đi</t>
         </is>
       </c>
-      <c r="E102" s="6" t="inlineStr">
+      <c r="E103" s="6" t="inlineStr">
         <is>
           <t>Khách hàng</t>
         </is>
       </c>
-      <c r="F102" s="6" t="inlineStr">
+      <c r="F103" s="6" t="inlineStr">
         <is>
           <t>F-A9</t>
         </is>
       </c>
-      <c r="G102" s="6" t="inlineStr">
+      <c r="G103" s="6" t="inlineStr">
         <is>
           <t>Một chuyến đi của xe. F-A9 đang tạm dừng: chưa có khái niệm chuyến đi.</t>
         </is>
       </c>
-      <c r="H102" s="6" t="n">
+      <c r="H103" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="I102" s="7" t="inlineStr">
+      <c r="I103" s="7" t="inlineStr">
         <is>
           <t>→ Mở</t>
         </is>
       </c>
     </row>
-    <row r="103"/>
-    <row r="104" ht="27" customHeight="1">
-      <c r="A104" s="4" t="inlineStr">
+    <row r="104"/>
+    <row r="105" ht="27" customHeight="1">
+      <c r="A105" s="4" t="inlineStr">
         <is>
           <t>Chú giải</t>
         </is>
       </c>
-      <c r="B104" s="4" t="inlineStr">
+      <c r="B105" s="4" t="inlineStr">
         <is>
           <t>Ý nghĩa</t>
         </is>
       </c>
     </row>
-    <row r="105" ht="108" customHeight="1">
-      <c r="A105" s="6" t="inlineStr">
+    <row r="106" ht="108" customHeight="1">
+      <c r="A106" s="6" t="inlineStr">
         <is>
           <t>Chủ sở hữu dữ liệu: Khách hàng</t>
         </is>
       </c>
-      <c r="B105" s="6" t="inlineStr">
+      <c r="B106" s="6" t="inlineStr">
         <is>
           <t>Thuộc về một tổ chức (thường là khách hàng; công ty G3 cũng có thể sở hữu); có cột organization_id hoặc lấy qua bảng cha (DM-24).</t>
-        </is>
-      </c>
-    </row>
-    <row r="106" ht="94.5" customHeight="1">
-      <c r="A106" s="6" t="inlineStr">
-        <is>
-          <t>Chủ sở hữu dữ liệu: Nội bộ</t>
-        </is>
-      </c>
-      <c r="B106" s="6" t="inlineStr">
-        <is>
-          <t>Dữ liệu của chính chúng ta (đơn vị vận hành nền tảng), dùng chung cho mọi tổ chức.</t>
         </is>
       </c>
     </row>
     <row r="107" ht="94.5" customHeight="1">
       <c r="A107" s="6" t="inlineStr">
         <is>
+          <t>Chủ sở hữu dữ liệu: Nội bộ</t>
+        </is>
+      </c>
+      <c r="B107" s="6" t="inlineStr">
+        <is>
+          <t>Dữ liệu của chính chúng ta (đơn vị vận hành nền tảng), dùng chung cho mọi tổ chức.</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="94.5" customHeight="1">
+      <c r="A108" s="6" t="inlineStr">
+        <is>
           <t>Chủ sở hữu dữ liệu: Hai bên</t>
         </is>
       </c>
-      <c r="B107" s="6" t="inlineStr">
+      <c r="B108" s="6" t="inlineStr">
         <is>
           <t>Tài sản của G3 được khách hàng sử dụng; cả hai bên cùng liên quan.</t>
         </is>
       </c>
     </row>
-    <row r="108" ht="121.5" customHeight="1">
-      <c r="A108" s="6" t="inlineStr">
+    <row r="109" ht="121.5" customHeight="1">
+      <c r="A109" s="6" t="inlineStr">
         <is>
           <t>Chủ sở hữu dữ liệu: Chưa quyết định</t>
         </is>
       </c>
-      <c r="B108" s="6" t="inlineStr">
+      <c r="B109" s="6" t="inlineStr">
         <is>
           <t>Đang chờ một quyết định còn mở (xem cuối trang).</t>
         </is>
       </c>
     </row>
-    <row r="109" ht="81" customHeight="1">
-      <c r="A109" s="6" t="inlineStr">
+    <row r="110" ht="81" customHeight="1">
+      <c r="A110" s="6" t="inlineStr">
         <is>
           <t>Miền nghiệp vụ (domain)</t>
         </is>
       </c>
-      <c r="B109" s="6" t="inlineStr">
+      <c r="B110" s="6" t="inlineStr">
         <is>
           <t>Một phần của hệ thống sở hữu dữ liệu riêng, ví dụ Xe, Trạm sạc, Thanh toán. Mỗi miền gồm một hoặc nhiều bảng.</t>
         </is>
       </c>
     </row>
-    <row r="110" ht="54" customHeight="1">
-      <c r="A110" s="6" t="inlineStr">
+    <row r="111" ht="54" customHeight="1">
+      <c r="A111" s="6" t="inlineStr">
         <is>
           <t>Bảng</t>
         </is>
       </c>
-      <c r="B110" s="6" t="inlineStr">
+      <c r="B111" s="6" t="inlineStr">
         <is>
           <t>Một loại dữ liệu được lưu, ví dụ Xe hoặc Phiên sạc. Mỗi bảng có một sheet riêng liệt kê từng cột.</t>
         </is>
       </c>
     </row>
-    <row r="111" ht="40.5" customHeight="1">
-      <c r="A111" s="6" t="inlineStr">
+    <row r="112" ht="40.5" customHeight="1">
+      <c r="A112" s="6" t="inlineStr">
         <is>
           <t>Tính năng</t>
         </is>
       </c>
-      <c r="B111" s="6" t="inlineStr">
+      <c r="B112" s="6" t="inlineStr">
         <is>
           <t>Mã tính năng trong danh sách tính năng (feature-list.md), ví dụ F-B2.</t>
         </is>
       </c>
     </row>
-    <row r="112" ht="67.5" customHeight="1">
-      <c r="A112" s="6" t="inlineStr">
+    <row r="113" ht="67.5" customHeight="1">
+      <c r="A113" s="6" t="inlineStr">
         <is>
           <t>PK / FK / UQ</t>
         </is>
       </c>
-      <c r="B112" s="6" t="inlineStr">
+      <c r="B113" s="6" t="inlineStr">
         <is>
           <t>PK: khóa chính (định danh duy nhất của dòng). FK: khóa ngoại (trỏ tới dòng của bảng khác). UQ: giá trị không được trùng.</t>
         </is>
       </c>
     </row>
-    <row r="113" ht="54" customHeight="1">
-      <c r="A113" s="6" t="inlineStr">
+    <row r="114" ht="54" customHeight="1">
+      <c r="A114" s="6" t="inlineStr">
         <is>
           <t>Ví dụ</t>
         </is>
       </c>
-      <c r="B113" s="6" t="inlineStr">
+      <c r="B114" s="6" t="inlineStr">
         <is>
           <t>Giá trị mẫu. Các mã ví dụ khớp nhau giữa các bảng, nên có thể lần theo một bản ghi mẫu qua nhiều sheet.</t>
         </is>
       </c>
     </row>
-    <row r="114" ht="40.5" customHeight="1">
-      <c r="A114" s="6" t="inlineStr">
+    <row r="115" ht="40.5" customHeight="1">
+      <c r="A115" s="6" t="inlineStr">
         <is>
           <t>NULL</t>
         </is>
       </c>
-      <c r="B114" s="6" t="inlineStr">
+      <c r="B115" s="6" t="inlineStr">
         <is>
           <t>Ô không có giá trị. Ý nghĩa của NULL được giải thích trong cột Ý nghĩa.</t>
         </is>
       </c>
     </row>
-    <row r="115" ht="81" customHeight="1">
-      <c r="A115" s="6" t="inlineStr">
+    <row r="116" ht="81" customHeight="1">
+      <c r="A116" s="6" t="inlineStr">
         <is>
           <t>🔍 Lưu lịch sử</t>
         </is>
       </c>
-      <c r="B115" s="6" t="inlineStr">
+      <c r="B116" s="6" t="inlineStr">
         <is>
           <t>Cột được theo dõi: khi cột này thay đổi, toàn bộ dòng cũ được chép sang bảng lịch sử (tên kết thúc bằng _history) kèm thời điểm và người thay đổi.</t>
         </is>
       </c>
     </row>
-    <row r="116"/>
-    <row r="117">
-      <c r="A117" s="8" t="inlineStr">
+    <row r="117"/>
+    <row r="118">
+      <c r="A118" s="8" t="inlineStr">
         <is>
           <t>Các view (giai đoạn đọc từ lịch sử)</t>
         </is>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" s="4" t="inlineStr">
+    <row r="119">
+      <c r="A119" s="4" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="B118" s="4" t="inlineStr">
+      <c r="B119" s="4" t="inlineStr">
         <is>
           <t>Mỗi dòng là</t>
         </is>
       </c>
-      <c r="C118" s="4" t="inlineStr">
+      <c r="C119" s="4" t="inlineStr">
         <is>
           <t>Các cột</t>
         </is>
       </c>
-      <c r="D118" s="4" t="inlineStr">
+      <c r="D119" s="4" t="inlineStr">
         <is>
           <t>Được dùng bởi</t>
-        </is>
-      </c>
-    </row>
-    <row r="119" ht="94.5" customHeight="1">
-      <c r="A119" s="6" t="inlineStr">
-        <is>
-          <t>vehicle_ownership_periods</t>
-        </is>
-      </c>
-      <c r="B119" s="6" t="inlineStr">
-        <is>
-          <t>một giai đoạn xe thuộc một chủ</t>
-        </is>
-      </c>
-      <c r="C119" s="6" t="inlineStr">
-        <is>
-          <t>vehicle_id, organization_id, owned_from, owned_until (NULL với chủ hiện tại)</t>
-        </is>
-      </c>
-      <c r="D119" s="6" t="inlineStr">
-        <is>
-          <t>lịch sử sở hữu và ngày bàn giao đầu tiên (VEH-02), "ngày đó xe của ai"</t>
         </is>
       </c>
     </row>
     <row r="120" ht="94.5" customHeight="1">
       <c r="A120" s="6" t="inlineStr">
         <is>
+          <t>vehicle_ownership_periods</t>
+        </is>
+      </c>
+      <c r="B120" s="6" t="inlineStr">
+        <is>
+          <t>một giai đoạn xe thuộc một chủ</t>
+        </is>
+      </c>
+      <c r="C120" s="6" t="inlineStr">
+        <is>
+          <t>vehicle_id, organization_id, owned_from, owned_until (NULL với chủ hiện tại)</t>
+        </is>
+      </c>
+      <c r="D120" s="6" t="inlineStr">
+        <is>
+          <t>lịch sử sở hữu và ngày bàn giao đầu tiên (VEH-02), "ngày đó xe của ai"</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="94.5" customHeight="1">
+      <c r="A121" s="6" t="inlineStr">
+        <is>
           <t>battery_installation_periods</t>
         </is>
       </c>
-      <c r="B120" s="6" t="inlineStr">
+      <c r="B121" s="6" t="inlineStr">
         <is>
           <t>một lần pin nằm trên một xe</t>
         </is>
       </c>
-      <c r="C120" s="6" t="inlineStr">
+      <c r="C121" s="6" t="inlineStr">
         <is>
           <t>battery_id, vehicle_id, installed_from, installed_until (NULL khi đang lắp)</t>
         </is>
       </c>
-      <c r="D120" s="6" t="inlineStr">
+      <c r="D121" s="6" t="inlineStr">
         <is>
           <t>lịch sử sức khỏe pin qua các xe (MON-07), bộ đếm bảo hành pin (WAR-01)</t>
         </is>
       </c>
     </row>
-    <row r="121"/>
-    <row r="122">
-      <c r="A122" s="8" t="inlineStr">
+    <row r="122"/>
+    <row r="123">
+      <c r="A123" s="8" t="inlineStr">
         <is>
           <t>Các quyết định còn mở</t>
         </is>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" s="4" t="inlineStr">
+    <row r="124">
+      <c r="A124" s="4" t="inlineStr">
         <is>
           <t>Mã</t>
         </is>
       </c>
-      <c r="B123" s="4" t="inlineStr">
+      <c r="B124" s="4" t="inlineStr">
         <is>
           <t>Câu hỏi</t>
         </is>
       </c>
-      <c r="C123" s="4" t="inlineStr">
+      <c r="C124" s="4" t="inlineStr">
         <is>
           <t>Ảnh hưởng tới</t>
-        </is>
-      </c>
-    </row>
-    <row r="124" ht="54" customHeight="1">
-      <c r="A124" s="6" t="inlineStr">
-        <is>
-          <t>D5</t>
-        </is>
-      </c>
-      <c r="B124" s="6" t="inlineStr">
-        <is>
-          <t>Ai trả tiền khi tài xế của đội xe sạc: ví của tài xế, ví của đội xe, hay tùy trường hợp?</t>
-        </is>
-      </c>
-      <c r="C124" s="6" t="inlineStr">
-        <is>
-          <t>wallets, payments</t>
         </is>
       </c>
     </row>
@@ -5247,33 +5277,36 @@
     <hyperlink ref="C91" location="'wallets'!A1"/>
     <hyperlink ref="D91" location="'wallets'!A1"/>
     <hyperlink ref="I91" location="'wallets'!A1"/>
-    <hyperlink ref="C92" location="'wallet_transactions'!A1"/>
-    <hyperlink ref="D92" location="'wallet_transactions'!A1"/>
-    <hyperlink ref="I92" location="'wallet_transactions'!A1"/>
-    <hyperlink ref="C93" location="'invoices'!A1"/>
-    <hyperlink ref="D93" location="'invoices'!A1"/>
-    <hyperlink ref="I93" location="'invoices'!A1"/>
-    <hyperlink ref="C94" location="'invoice_lines'!A1"/>
-    <hyperlink ref="D94" location="'invoice_lines'!A1"/>
-    <hyperlink ref="I94" location="'invoice_lines'!A1"/>
-    <hyperlink ref="C95" location="'subscription_plans'!A1"/>
-    <hyperlink ref="D95" location="'subscription_plans'!A1"/>
-    <hyperlink ref="I95" location="'subscription_plans'!A1"/>
-    <hyperlink ref="C96" location="'plan_features'!A1"/>
-    <hyperlink ref="D96" location="'plan_features'!A1"/>
-    <hyperlink ref="I96" location="'plan_features'!A1"/>
-    <hyperlink ref="C97" location="'subscriptions'!A1"/>
-    <hyperlink ref="D97" location="'subscriptions'!A1"/>
-    <hyperlink ref="I97" location="'subscriptions'!A1"/>
-    <hyperlink ref="C99" location="'driver_scores'!A1"/>
-    <hyperlink ref="D99" location="'driver_scores'!A1"/>
-    <hyperlink ref="I99" location="'driver_scores'!A1"/>
-    <hyperlink ref="C101" location="'promotion_campaigns'!A1"/>
-    <hyperlink ref="D101" location="'promotion_campaigns'!A1"/>
-    <hyperlink ref="I101" location="'promotion_campaigns'!A1"/>
-    <hyperlink ref="C102" location="'trips'!A1"/>
-    <hyperlink ref="D102" location="'trips'!A1"/>
-    <hyperlink ref="I102" location="'trips'!A1"/>
+    <hyperlink ref="C92" location="'wallet_history'!A1"/>
+    <hyperlink ref="D92" location="'wallet_history'!A1"/>
+    <hyperlink ref="I92" location="'wallet_history'!A1"/>
+    <hyperlink ref="C93" location="'wallet_transactions'!A1"/>
+    <hyperlink ref="D93" location="'wallet_transactions'!A1"/>
+    <hyperlink ref="I93" location="'wallet_transactions'!A1"/>
+    <hyperlink ref="C94" location="'invoices'!A1"/>
+    <hyperlink ref="D94" location="'invoices'!A1"/>
+    <hyperlink ref="I94" location="'invoices'!A1"/>
+    <hyperlink ref="C95" location="'invoice_lines'!A1"/>
+    <hyperlink ref="D95" location="'invoice_lines'!A1"/>
+    <hyperlink ref="I95" location="'invoice_lines'!A1"/>
+    <hyperlink ref="C96" location="'subscription_plans'!A1"/>
+    <hyperlink ref="D96" location="'subscription_plans'!A1"/>
+    <hyperlink ref="I96" location="'subscription_plans'!A1"/>
+    <hyperlink ref="C97" location="'plan_features'!A1"/>
+    <hyperlink ref="D97" location="'plan_features'!A1"/>
+    <hyperlink ref="I97" location="'plan_features'!A1"/>
+    <hyperlink ref="C98" location="'subscriptions'!A1"/>
+    <hyperlink ref="D98" location="'subscriptions'!A1"/>
+    <hyperlink ref="I98" location="'subscriptions'!A1"/>
+    <hyperlink ref="C100" location="'driver_scores'!A1"/>
+    <hyperlink ref="D100" location="'driver_scores'!A1"/>
+    <hyperlink ref="I100" location="'driver_scores'!A1"/>
+    <hyperlink ref="C102" location="'promotion_campaigns'!A1"/>
+    <hyperlink ref="D102" location="'promotion_campaigns'!A1"/>
+    <hyperlink ref="I102" location="'promotion_campaigns'!A1"/>
+    <hyperlink ref="C103" location="'trips'!A1"/>
+    <hyperlink ref="D103" location="'trips'!A1"/>
+    <hyperlink ref="I103" location="'trips'!A1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10784,7 +10817,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I59"/>
+  <dimension ref="A1:I58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -11762,7 +11795,7 @@
       <c r="A51" s="6" t="n"/>
       <c r="B51" s="7" t="inlineStr">
         <is>
-          <t>payments</t>
+          <t>invoices</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
@@ -11775,7 +11808,7 @@
       <c r="A52" s="6" t="n"/>
       <c r="B52" s="7" t="inlineStr">
         <is>
-          <t>wallets</t>
+          <t>invoice_lines</t>
         </is>
       </c>
       <c r="C52" s="6" t="inlineStr">
@@ -11788,7 +11821,7 @@
       <c r="A53" s="6" t="n"/>
       <c r="B53" s="7" t="inlineStr">
         <is>
-          <t>wallet_transactions</t>
+          <t>subscriptions</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
@@ -11801,7 +11834,7 @@
       <c r="A54" s="6" t="n"/>
       <c r="B54" s="7" t="inlineStr">
         <is>
-          <t>invoices</t>
+          <t>payments</t>
         </is>
       </c>
       <c r="C54" s="6" t="inlineStr">
@@ -11814,7 +11847,7 @@
       <c r="A55" s="6" t="n"/>
       <c r="B55" s="7" t="inlineStr">
         <is>
-          <t>invoice_lines</t>
+          <t>wallets</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
@@ -11827,7 +11860,7 @@
       <c r="A56" s="6" t="n"/>
       <c r="B56" s="7" t="inlineStr">
         <is>
-          <t>subscriptions</t>
+          <t>driver_scores</t>
         </is>
       </c>
       <c r="C56" s="6" t="inlineStr">
@@ -11840,7 +11873,7 @@
       <c r="A57" s="6" t="n"/>
       <c r="B57" s="7" t="inlineStr">
         <is>
-          <t>driver_scores</t>
+          <t>trips</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
@@ -11853,23 +11886,10 @@
       <c r="A58" s="6" t="n"/>
       <c r="B58" s="7" t="inlineStr">
         <is>
-          <t>trips</t>
+          <t>organization_history</t>
         </is>
       </c>
       <c r="C58" s="6" t="inlineStr">
-        <is>
-          <t>organization_id</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="6" t="n"/>
-      <c r="B59" s="7" t="inlineStr">
-        <is>
-          <t>organization_history</t>
-        </is>
-      </c>
-      <c r="C59" s="6" t="inlineStr">
         <is>
           <t>organization_id</t>
         </is>
@@ -11906,15 +11926,14 @@
     <hyperlink ref="B48" location="'charging_policy_assignments'!A1"/>
     <hyperlink ref="B49" location="'policy_violations'!A1"/>
     <hyperlink ref="B50" location="'tariffs'!A1"/>
-    <hyperlink ref="B51" location="'payments'!A1"/>
-    <hyperlink ref="B52" location="'wallets'!A1"/>
-    <hyperlink ref="B53" location="'wallet_transactions'!A1"/>
-    <hyperlink ref="B54" location="'invoices'!A1"/>
-    <hyperlink ref="B55" location="'invoice_lines'!A1"/>
-    <hyperlink ref="B56" location="'subscriptions'!A1"/>
-    <hyperlink ref="B57" location="'driver_scores'!A1"/>
-    <hyperlink ref="B58" location="'trips'!A1"/>
-    <hyperlink ref="B59" location="'organization_history'!A1"/>
+    <hyperlink ref="B51" location="'invoices'!A1"/>
+    <hyperlink ref="B52" location="'invoice_lines'!A1"/>
+    <hyperlink ref="B53" location="'subscriptions'!A1"/>
+    <hyperlink ref="B54" location="'payments'!A1"/>
+    <hyperlink ref="B55" location="'wallets'!A1"/>
+    <hyperlink ref="B56" location="'driver_scores'!A1"/>
+    <hyperlink ref="B57" location="'trips'!A1"/>
+    <hyperlink ref="B58" location="'organization_history'!A1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -21401,7 +21420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I34"/>
+  <dimension ref="A1:I33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -22079,7 +22098,7 @@
       <c r="A31" s="6" t="n"/>
       <c r="B31" s="7" t="inlineStr">
         <is>
-          <t>wallets</t>
+          <t>driver_scores</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
@@ -22092,7 +22111,7 @@
       <c r="A32" s="6" t="n"/>
       <c r="B32" s="7" t="inlineStr">
         <is>
-          <t>driver_scores</t>
+          <t>trips</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
@@ -22105,23 +22124,10 @@
       <c r="A33" s="6" t="n"/>
       <c r="B33" s="7" t="inlineStr">
         <is>
-          <t>trips</t>
+          <t>driver_history</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
-        <is>
-          <t>driver_id</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="6" t="n"/>
-      <c r="B34" s="7" t="inlineStr">
-        <is>
-          <t>driver_history</t>
-        </is>
-      </c>
-      <c r="C34" s="6" t="inlineStr">
         <is>
           <t>driver_id</t>
         </is>
@@ -22136,10 +22142,9 @@
     <hyperlink ref="B28" location="'driver_vehicle_assignments'!A1"/>
     <hyperlink ref="B29" location="'driving_sessions'!A1"/>
     <hyperlink ref="B30" location="'support_cases'!A1"/>
-    <hyperlink ref="B31" location="'wallets'!A1"/>
-    <hyperlink ref="B32" location="'driver_scores'!A1"/>
-    <hyperlink ref="B33" location="'trips'!A1"/>
-    <hyperlink ref="B34" location="'driver_history'!A1"/>
+    <hyperlink ref="B31" location="'driver_scores'!A1"/>
+    <hyperlink ref="B32" location="'trips'!A1"/>
+    <hyperlink ref="B33" location="'driver_history'!A1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -26266,7 +26271,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I67"/>
+  <dimension ref="A1:I71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -27151,12 +27156,12 @@
       <c r="A49" s="6" t="n"/>
       <c r="B49" s="7" t="inlineStr">
         <is>
-          <t>organization_history</t>
+          <t>payments</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>changed_by</t>
+          <t>paid_by</t>
         </is>
       </c>
     </row>
@@ -27164,7 +27169,7 @@
       <c r="A50" s="6" t="n"/>
       <c r="B50" s="7" t="inlineStr">
         <is>
-          <t>user_history</t>
+          <t>wallets</t>
         </is>
       </c>
       <c r="C50" s="6" t="inlineStr">
@@ -27177,12 +27182,12 @@
       <c r="A51" s="6" t="n"/>
       <c r="B51" s="7" t="inlineStr">
         <is>
-          <t>user_history</t>
+          <t>wallet_transactions</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>changed_by</t>
+          <t>created_by</t>
         </is>
       </c>
     </row>
@@ -27190,7 +27195,7 @@
       <c r="A52" s="6" t="n"/>
       <c r="B52" s="7" t="inlineStr">
         <is>
-          <t>membership_history</t>
+          <t>organization_history</t>
         </is>
       </c>
       <c r="C52" s="6" t="inlineStr">
@@ -27199,16 +27204,16 @@
         </is>
       </c>
     </row>
-    <row r="53" ht="27" customHeight="1">
+    <row r="53">
       <c r="A53" s="6" t="n"/>
       <c r="B53" s="7" t="inlineStr">
         <is>
-          <t>organization_setting_history</t>
+          <t>user_history</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>changed_by</t>
+          <t>user_id</t>
         </is>
       </c>
     </row>
@@ -27216,7 +27221,7 @@
       <c r="A54" s="6" t="n"/>
       <c r="B54" s="7" t="inlineStr">
         <is>
-          <t>vehicle_history</t>
+          <t>user_history</t>
         </is>
       </c>
       <c r="C54" s="6" t="inlineStr">
@@ -27229,7 +27234,7 @@
       <c r="A55" s="6" t="n"/>
       <c r="B55" s="7" t="inlineStr">
         <is>
-          <t>vehicle_model_history</t>
+          <t>membership_history</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
@@ -27238,11 +27243,11 @@
         </is>
       </c>
     </row>
-    <row r="56">
+    <row r="56" ht="27" customHeight="1">
       <c r="A56" s="6" t="n"/>
       <c r="B56" s="7" t="inlineStr">
         <is>
-          <t>battery_model_history</t>
+          <t>organization_setting_history</t>
         </is>
       </c>
       <c r="C56" s="6" t="inlineStr">
@@ -27255,7 +27260,7 @@
       <c r="A57" s="6" t="n"/>
       <c r="B57" s="7" t="inlineStr">
         <is>
-          <t>battery_history</t>
+          <t>vehicle_history</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
@@ -27268,7 +27273,7 @@
       <c r="A58" s="6" t="n"/>
       <c r="B58" s="7" t="inlineStr">
         <is>
-          <t>warranty_history</t>
+          <t>vehicle_model_history</t>
         </is>
       </c>
       <c r="C58" s="6" t="inlineStr">
@@ -27281,7 +27286,7 @@
       <c r="A59" s="6" t="n"/>
       <c r="B59" s="7" t="inlineStr">
         <is>
-          <t>telematic_history</t>
+          <t>battery_model_history</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
@@ -27294,7 +27299,7 @@
       <c r="A60" s="6" t="n"/>
       <c r="B60" s="7" t="inlineStr">
         <is>
-          <t>driver_history</t>
+          <t>battery_history</t>
         </is>
       </c>
       <c r="C60" s="6" t="inlineStr">
@@ -27307,7 +27312,7 @@
       <c r="A61" s="6" t="n"/>
       <c r="B61" s="7" t="inlineStr">
         <is>
-          <t>fleet_history</t>
+          <t>warranty_history</t>
         </is>
       </c>
       <c r="C61" s="6" t="inlineStr">
@@ -27316,11 +27321,11 @@
         </is>
       </c>
     </row>
-    <row r="62" ht="27" customHeight="1">
+    <row r="62">
       <c r="A62" s="6" t="n"/>
       <c r="B62" s="7" t="inlineStr">
         <is>
-          <t>charging_location_history</t>
+          <t>telematic_history</t>
         </is>
       </c>
       <c r="C62" s="6" t="inlineStr">
@@ -27333,7 +27338,7 @@
       <c r="A63" s="6" t="n"/>
       <c r="B63" s="7" t="inlineStr">
         <is>
-          <t>charging_station_history</t>
+          <t>driver_history</t>
         </is>
       </c>
       <c r="C63" s="6" t="inlineStr">
@@ -27346,7 +27351,7 @@
       <c r="A64" s="6" t="n"/>
       <c r="B64" s="7" t="inlineStr">
         <is>
-          <t>charging_evse_history</t>
+          <t>fleet_history</t>
         </is>
       </c>
       <c r="C64" s="6" t="inlineStr">
@@ -27359,7 +27364,7 @@
       <c r="A65" s="6" t="n"/>
       <c r="B65" s="7" t="inlineStr">
         <is>
-          <t>charging_connector_history</t>
+          <t>charging_location_history</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
@@ -27372,7 +27377,7 @@
       <c r="A66" s="6" t="n"/>
       <c r="B66" s="7" t="inlineStr">
         <is>
-          <t>tariff_history</t>
+          <t>charging_station_history</t>
         </is>
       </c>
       <c r="C66" s="6" t="inlineStr">
@@ -27381,14 +27386,66 @@
         </is>
       </c>
     </row>
-    <row r="67" ht="27" customHeight="1">
+    <row r="67">
       <c r="A67" s="6" t="n"/>
       <c r="B67" s="7" t="inlineStr">
         <is>
+          <t>charging_evse_history</t>
+        </is>
+      </c>
+      <c r="C67" s="6" t="inlineStr">
+        <is>
+          <t>changed_by</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="27" customHeight="1">
+      <c r="A68" s="6" t="n"/>
+      <c r="B68" s="7" t="inlineStr">
+        <is>
+          <t>charging_connector_history</t>
+        </is>
+      </c>
+      <c r="C68" s="6" t="inlineStr">
+        <is>
+          <t>changed_by</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="6" t="n"/>
+      <c r="B69" s="7" t="inlineStr">
+        <is>
+          <t>tariff_history</t>
+        </is>
+      </c>
+      <c r="C69" s="6" t="inlineStr">
+        <is>
+          <t>changed_by</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="27" customHeight="1">
+      <c r="A70" s="6" t="n"/>
+      <c r="B70" s="7" t="inlineStr">
+        <is>
           <t>charging_session_bill_history</t>
         </is>
       </c>
-      <c r="C67" s="6" t="inlineStr">
+      <c r="C70" s="6" t="inlineStr">
+        <is>
+          <t>changed_by</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="6" t="n"/>
+      <c r="B71" s="7" t="inlineStr">
+        <is>
+          <t>wallet_history</t>
+        </is>
+      </c>
+      <c r="C71" s="6" t="inlineStr">
         <is>
           <t>changed_by</t>
         </is>
@@ -27425,25 +27482,29 @@
     <hyperlink ref="B46" location="'charging_sessions'!A1"/>
     <hyperlink ref="B47" location="'charging_policy_versions'!A1"/>
     <hyperlink ref="B48" location="'tariff_versions'!A1"/>
-    <hyperlink ref="B49" location="'organization_history'!A1"/>
-    <hyperlink ref="B50" location="'user_history'!A1"/>
-    <hyperlink ref="B51" location="'user_history'!A1"/>
-    <hyperlink ref="B52" location="'membership_history'!A1"/>
-    <hyperlink ref="B53" location="'organization_setting_history'!A1"/>
-    <hyperlink ref="B54" location="'vehicle_history'!A1"/>
-    <hyperlink ref="B55" location="'vehicle_model_history'!A1"/>
-    <hyperlink ref="B56" location="'battery_model_history'!A1"/>
-    <hyperlink ref="B57" location="'battery_history'!A1"/>
-    <hyperlink ref="B58" location="'warranty_history'!A1"/>
-    <hyperlink ref="B59" location="'telematic_history'!A1"/>
-    <hyperlink ref="B60" location="'driver_history'!A1"/>
-    <hyperlink ref="B61" location="'fleet_history'!A1"/>
-    <hyperlink ref="B62" location="'charging_location_history'!A1"/>
-    <hyperlink ref="B63" location="'charging_station_history'!A1"/>
-    <hyperlink ref="B64" location="'charging_evse_history'!A1"/>
-    <hyperlink ref="B65" location="'charging_connector_history'!A1"/>
-    <hyperlink ref="B66" location="'tariff_history'!A1"/>
-    <hyperlink ref="B67" location="'charging_session_bill_history'!A1"/>
+    <hyperlink ref="B49" location="'payments'!A1"/>
+    <hyperlink ref="B50" location="'wallets'!A1"/>
+    <hyperlink ref="B51" location="'wallet_transactions'!A1"/>
+    <hyperlink ref="B52" location="'organization_history'!A1"/>
+    <hyperlink ref="B53" location="'user_history'!A1"/>
+    <hyperlink ref="B54" location="'user_history'!A1"/>
+    <hyperlink ref="B55" location="'membership_history'!A1"/>
+    <hyperlink ref="B56" location="'organization_setting_history'!A1"/>
+    <hyperlink ref="B57" location="'vehicle_history'!A1"/>
+    <hyperlink ref="B58" location="'vehicle_model_history'!A1"/>
+    <hyperlink ref="B59" location="'battery_model_history'!A1"/>
+    <hyperlink ref="B60" location="'battery_history'!A1"/>
+    <hyperlink ref="B61" location="'warranty_history'!A1"/>
+    <hyperlink ref="B62" location="'telematic_history'!A1"/>
+    <hyperlink ref="B63" location="'driver_history'!A1"/>
+    <hyperlink ref="B64" location="'fleet_history'!A1"/>
+    <hyperlink ref="B65" location="'charging_location_history'!A1"/>
+    <hyperlink ref="B66" location="'charging_station_history'!A1"/>
+    <hyperlink ref="B67" location="'charging_evse_history'!A1"/>
+    <hyperlink ref="B68" location="'charging_connector_history'!A1"/>
+    <hyperlink ref="B69" location="'tariff_history'!A1"/>
+    <hyperlink ref="B70" location="'charging_session_bill_history'!A1"/>
+    <hyperlink ref="B71" location="'wallet_history'!A1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -38155,7 +38216,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I51"/>
+  <dimension ref="A1:I49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -38436,7 +38497,7 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>Tổ chức trả tiền: tổ chức mà người quét mã đại diện, ghi một lần khi quét và không đổi (DM-24 trường hợp C). Ví nào trong tổ chức trả tiền là câu hỏi mở D5.</t>
+          <t>Tổ chức trả tiền: tổ chức mà người quét mã đại diện, ghi một lần khi quét và không đổi (DM-24 trường hợp C). Khi ra mắt, ví của chính người quét mã trả tiền (BL-13).</t>
         </is>
       </c>
       <c r="H11" s="6" t="inlineStr">
@@ -39308,36 +39369,10 @@
       <c r="A49" s="6" t="n"/>
       <c r="B49" s="7" t="inlineStr">
         <is>
-          <t>payments</t>
+          <t>invoice_lines</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
-        <is>
-          <t>session_id</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="6" t="n"/>
-      <c r="B50" s="7" t="inlineStr">
-        <is>
-          <t>wallet_transactions</t>
-        </is>
-      </c>
-      <c r="C50" s="6" t="inlineStr">
-        <is>
-          <t>session_id</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="6" t="n"/>
-      <c r="B51" s="7" t="inlineStr">
-        <is>
-          <t>invoice_lines</t>
-        </is>
-      </c>
-      <c r="C51" s="6" t="inlineStr">
         <is>
           <t>session_id</t>
         </is>
@@ -39358,9 +39393,7 @@
     <hyperlink ref="B46" location="'charging_session_measurements'!A1"/>
     <hyperlink ref="B47" location="'policy_violations'!A1"/>
     <hyperlink ref="B48" location="'charging_session_bills'!A1"/>
-    <hyperlink ref="B49" location="'payments'!A1"/>
-    <hyperlink ref="B50" location="'wallet_transactions'!A1"/>
-    <hyperlink ref="B51" location="'invoice_lines'!A1"/>
+    <hyperlink ref="B49" location="'invoice_lines'!A1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -47009,7 +47042,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I28"/>
+  <dimension ref="A1:I30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -47727,10 +47760,36 @@
       <c r="A28" s="6" t="n"/>
       <c r="B28" s="7" t="inlineStr">
         <is>
+          <t>payments</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>charging_session_bill_id</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="27" customHeight="1">
+      <c r="A29" s="6" t="n"/>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>wallet_transactions</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>charging_session_bill_id</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="27" customHeight="1">
+      <c r="A30" s="6" t="n"/>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
           <t>charging_session_bill_history</t>
         </is>
       </c>
-      <c r="C28" s="6" t="inlineStr">
+      <c r="C30" s="6" t="inlineStr">
         <is>
           <t>charging_session_bill_id</t>
         </is>
@@ -47743,7 +47802,9 @@
     <hyperlink ref="A5" location="'charging_session_bill_history'!A1"/>
     <hyperlink ref="F9" location="'charging_sessions'!A1"/>
     <hyperlink ref="F10" location="'tariff_versions'!A1"/>
-    <hyperlink ref="B28" location="'charging_session_bill_history'!A1"/>
+    <hyperlink ref="B28" location="'payments'!A1"/>
+    <hyperlink ref="B29" location="'wallet_transactions'!A1"/>
+    <hyperlink ref="B30" location="'charging_session_bill_history'!A1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -48529,7 +48590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:I30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -48567,7 +48628,7 @@
     <row r="4">
       <c r="A4" s="11" t="inlineStr">
         <is>
-          <t>Một lần thanh toán qua cổng thanh toán hoặc ví, thường cho một phiên sạc.</t>
+          <t>Tiền đi qua cổng thanh toán hoặc ngân hàng (BL-12): chỉ tiền thật vào hoặc ra. Trả tiền phiên sạc bằng ví là giao dịch ví, không phải thanh toán. Khi ra mắt chỉ có TOP_UP và REFUND; SESSION_BILL và INVOICE đến cùng các phương thức sau. Không có lịch sử thay đổi (trạng thái do cổng báo); không xóa mềm (chứng từ tài chính). Thẻ đã lưu (mã hóa token) là bảng sau này. Ràng buộc kiểm tra (BL-12): liên kết có giá trị khớp với mục đích.</t>
         </is>
       </c>
     </row>
@@ -48687,7 +48748,7 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>Tổ chức khách hàng đã thanh toán.</t>
+          <t>Tổ chức thanh toán hoặc nhận hoàn tiền, ghi một lần (DM-24 trường hợp C).</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr">
@@ -48703,7 +48764,7 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>session_id</t>
+          <t>paid_by</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
@@ -48723,33 +48784,33 @@
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>charging_sessions.session_id (khi xóa: chặn xóa)</t>
+          <t>users.user_id (khi xóa: chặn xóa)</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>Phiên sạc được thanh toán; NULL với các khoản khác.</t>
+          <t>Người dùng đã thanh toán trên ứng dụng; NULL với chuyển khoản ngân hàng.</t>
         </is>
       </c>
       <c r="H9" s="6" t="inlineStr">
         <is>
-          <t>e5a2d8f1-4b7c-4e9a-b3d6-2c1f0e9a8dbb</t>
+          <t>9b2e7d4a-1c3f-4a8e-b6d2-5e0f1a9c3d22</t>
         </is>
       </c>
       <c r="I9" s="6" t="n"/>
     </row>
-    <row r="10">
+    <row r="10" ht="67.5" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>4</v>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>amount</t>
+          <t>purpose</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>numeric(14,2)</t>
+          <t>varchar(20)</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
@@ -48761,78 +48822,94 @@
       <c r="F10" s="6" t="n"/>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>Số tiền đã thanh toán.</t>
+          <t>Tiền dùng cho việc gì (BL-12). TOP_UP: nạp tiền vào ví (khi ra mắt). REFUND: hoàn tiền, ví dụ số dư ví chưa dùng (khi ra mắt). SESSION_BILL: trả trực tiếp một phiếu tính tiền phiên sạc (sau này). INVOICE: trả một hóa đơn (sau này, thanh toán doanh nghiệp).</t>
         </is>
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>866250.00</t>
+          <t>TOP_UP</t>
         </is>
       </c>
       <c r="I10" s="6" t="n"/>
     </row>
-    <row r="11">
+    <row r="11" ht="27" customHeight="1">
       <c r="A11" s="6" t="n">
         <v>5</v>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>charging_session_bill_id</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>char(3)</t>
+          <t>uuid</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E11" s="6" t="n"/>
-      <c r="F11" s="6" t="n"/>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>charging_session_bills.charging_session_bill_id (khi xóa: chặn xóa)</t>
+        </is>
+      </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>Mã tiền tệ ISO 4217.</t>
+          <t>Phiếu tính tiền được trả; chỉ có giá trị với SESSION_BILL.</t>
         </is>
       </c>
       <c r="H11" s="6" t="inlineStr">
         <is>
-          <t>VND</t>
+          <t>NULL</t>
         </is>
       </c>
       <c r="I11" s="6" t="n"/>
     </row>
-    <row r="12">
+    <row r="12" ht="27" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>6</v>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>method</t>
+          <t>invoice_id</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>varchar(20)</t>
+          <t>uuid</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E12" s="6" t="n"/>
-      <c r="F12" s="6" t="n"/>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>invoices.invoice_id (khi xóa: chặn xóa)</t>
+        </is>
+      </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>Phương thức thanh toán. Giá trị: VNPAY | MOMO | WALLET.</t>
+          <t>Hóa đơn được trả; chỉ có giá trị với INVOICE.</t>
         </is>
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>VNPAY</t>
+          <t>NULL</t>
         </is>
       </c>
       <c r="I12" s="6" t="n"/>
@@ -48843,12 +48920,12 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>gateway_reference</t>
+          <t>refund_of_payment_id</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>varchar(100)</t>
+          <t>uuid</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
@@ -48856,16 +48933,24 @@
           <t>có</t>
         </is>
       </c>
-      <c r="E13" s="6" t="n"/>
-      <c r="F13" s="6" t="n"/>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>payments.payment_id (khi xóa: chặn xóa)</t>
+        </is>
+      </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>Mã tham chiếu/token của cổng thanh toán (không bao giờ lưu dữ liệu thẻ) (NF-05).</t>
+          <t>Thanh toán mà lần hoàn tiền này trả lại; chỉ có giá trị với REFUND.</t>
         </is>
       </c>
       <c r="H13" s="6" t="inlineStr">
         <is>
-          <t>VNP14592873</t>
+          <t>NULL</t>
         </is>
       </c>
       <c r="I13" s="6" t="n"/>
@@ -48876,12 +48961,12 @@
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>amount</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>varchar(20)</t>
+          <t>numeric(14,2)</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
@@ -48893,12 +48978,12 @@
       <c r="F14" s="6" t="n"/>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>Trạng thái thanh toán.</t>
+          <t>Số tiền, luôn dương; mục đích cho biết chiều tiền.</t>
         </is>
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
-          <t>SUCCEEDED</t>
+          <t>500000.00</t>
         </is>
       </c>
       <c r="I14" s="6" t="n"/>
@@ -48909,45 +48994,45 @@
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>paid_at</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>timestamptz</t>
+          <t>char(3)</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>có</t>
+          <t>không</t>
         </is>
       </c>
       <c r="E15" s="6" t="n"/>
       <c r="F15" s="6" t="n"/>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>Thời điểm cổng thanh toán xác nhận; NULL cho tới lúc đó.</t>
+          <t>Mã tiền tệ ISO 4217.</t>
         </is>
       </c>
       <c r="H15" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15T09:46:12Z</t>
+          <t>VND</t>
         </is>
       </c>
       <c r="I15" s="6" t="n"/>
     </row>
-    <row r="16">
+    <row r="16" ht="27" customHeight="1">
       <c r="A16" s="6" t="n">
         <v>10</v>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>method</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>timestamptz</t>
+          <t>varchar(20)</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
@@ -48959,56 +49044,2582 @@
       <c r="F16" s="6" t="n"/>
       <c r="G16" s="6" t="inlineStr">
         <is>
+          <t>Cách chuyển tiền. Trả bằng ví không phải là thanh toán (không có tiền vào) mà là giao dịch ví.</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>VNPAY</t>
+        </is>
+      </c>
+      <c r="I16" s="6" t="n"/>
+    </row>
+    <row r="17" ht="27" customHeight="1">
+      <c r="A17" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>gateway_reference</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>varchar(100)</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="n"/>
+      <c r="F17" s="6" t="n"/>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>Mã giao dịch của cổng thanh toán, dùng để đối soát; không bao giờ là dữ liệu thẻ (NF-05).</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>VNP14592873</t>
+        </is>
+      </c>
+      <c r="I17" s="6" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>gateway_result_code</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>varchar(30)</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="n"/>
+      <c r="F18" s="6" t="n"/>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>Mã kết quả của cổng thanh toán, đúng như gửi về (PAY-06).</t>
+        </is>
+      </c>
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="I18" s="6" t="n"/>
+    </row>
+    <row r="19" ht="27" customHeight="1">
+      <c r="A19" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>varchar(20)</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="n"/>
+      <c r="F19" s="6" t="n"/>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>Theo cổng thanh toán báo về; là trạng thái quan sát nên không có cột lý do.</t>
+        </is>
+      </c>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>SUCCEEDED</t>
+        </is>
+      </c>
+      <c r="I19" s="6" t="n"/>
+    </row>
+    <row r="20" ht="27" customHeight="1">
+      <c r="A20" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>completed_at</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>timestamptz</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="n"/>
+      <c r="F20" s="6" t="n"/>
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t>Thời điểm cổng xác nhận thành công hay thất bại; NULL khi PENDING.</t>
+        </is>
+      </c>
+      <c r="H20" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-15T09:46:12Z</t>
+        </is>
+      </c>
+      <c r="I20" s="6" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>created_at</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>timestamptz</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="n"/>
+      <c r="F21" s="6" t="n"/>
+      <c r="G21" s="6" t="inlineStr">
+        <is>
           <t>Thời điểm tạo bản ghi (UTC).</t>
         </is>
       </c>
-      <c r="H16" s="6" t="inlineStr">
+      <c r="H21" s="6" t="inlineStr">
         <is>
           <t>2026-09-15T09:45:00Z</t>
         </is>
       </c>
-      <c r="I16" s="6" t="n"/>
-    </row>
-    <row r="17"/>
-    <row r="18">
-      <c r="A18" s="4" t="n"/>
-      <c r="B18" s="4" t="inlineStr">
+      <c r="I21" s="6" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>updated_at</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>timestamptz</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="n"/>
+      <c r="F22" s="6" t="n"/>
+      <c r="G22" s="6" t="inlineStr">
+        <is>
+          <t>Thời điểm bản ghi được sửa gần nhất (UTC).</t>
+        </is>
+      </c>
+      <c r="H22" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-15T09:46:12Z</t>
+        </is>
+      </c>
+      <c r="I22" s="6" t="n"/>
+    </row>
+    <row r="23"/>
+    <row r="24">
+      <c r="A24" s="4" t="n"/>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>Chỉ mục (index)</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>Các cột</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>Duy nhất</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="n"/>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>Ghi chú</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="40.5" customHeight="1">
+      <c r="A25" s="6" t="n"/>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>uq_payments_method_gateway_reference</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>method, gateway_reference</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E25" s="6" t="n"/>
+      <c r="F25" s="6" t="inlineStr">
+        <is>
+          <t>WHERE gateway_reference IS NOT NULL: the same gateway callback is never recorded twice</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="27" customHeight="1">
+      <c r="A26" s="6" t="n"/>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>ix_payments_organization_created</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>organization_id, created_at</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E26" s="6" t="n"/>
+      <c r="F26" s="6" t="n"/>
+    </row>
+    <row r="27"/>
+    <row r="28">
+      <c r="A28" s="4" t="n"/>
+      <c r="B28" s="4" t="inlineStr">
         <is>
           <t>Được tham chiếu bởi bảng</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="C28" s="4" t="inlineStr">
         <is>
           <t>Cột</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="6" t="n"/>
-      <c r="B19" s="7" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="6" t="n"/>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>payments</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>refund_of_payment_id</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="n"/>
+      <c r="B30" s="7" t="inlineStr">
         <is>
           <t>wallet_transactions</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr">
+      <c r="C30" s="6" t="inlineStr">
         <is>
           <t>payment_id</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A6:I16"/>
+  <autoFilter ref="A6:I22"/>
   <hyperlinks>
     <hyperlink ref="A2" location="'Tổng quan'!A1"/>
     <hyperlink ref="F8" location="'organizations'!A1"/>
-    <hyperlink ref="F9" location="'charging_sessions'!A1"/>
-    <hyperlink ref="B19" location="'wallet_transactions'!A1"/>
+    <hyperlink ref="F9" location="'users'!A1"/>
+    <hyperlink ref="F11" location="'charging_session_bills'!A1"/>
+    <hyperlink ref="F12" location="'invoices'!A1"/>
+    <hyperlink ref="F13" location="'payments'!A1"/>
+    <hyperlink ref="B29" location="'payments'!A1"/>
+    <hyperlink ref="B30" location="'wallet_transactions'!A1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet73.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="7" max="7"/>
+    <col width="42" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>54. wallets: Ví</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t>← Tổng quan</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>Miền nghiệp vụ: Thanh toán &amp; hóa đơn (billing)   ·   Chủ sở hữu dữ liệu: Khách hàng   ·   Tính năng: F-H2</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>Số dư trả trước chỉ dùng cho dịch vụ của chính chúng ta (BL-13). Khi ra mắt, mỗi người tự nạp tiền vào ví của mình và trả từng phiên sạc từ đó; ví của tổ chức được chuẩn bị cho các phương thức sau. Để bắt đầu sạc, số dư phải bằng hoặc cao hơn mức tối thiểu đặt trong backend (BL-14); kiểm tra khi quét mã, không bằng ràng buộc cơ sở dữ liệu, vì lần trừ tiền cuối phiên có thể làm số dư âm, sau đó người dùng không thể sạc tiếp cho tới khi nạp lại trên mức tối thiểu. Bật lịch sử thay đổi cho các quyết định (khóa ví), trừ cột balance vì mọi giao dịch đều làm thay đổi nó. Không xóa mềm. Không gọi là ví điện tử khi giới thiệu ra bên ngoài (câu hỏi mở 11). Ràng buộc kiểm tra (BL-13): chỉ đúng một chủ sở hữu.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>🔍 Lưu lịch sử: khi một cột có dấu 🔍 thay đổi, toàn bộ dòng cũ được chép sang bảng wallet_history.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6"/>
+    <row r="7" ht="27" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Cột</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Kiểu dữ liệu</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Cho phép rỗng</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>Khóa</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>Tham chiếu tới</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>Ý nghĩa</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>Ví dụ</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>Lưu lịch sử</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>wallet_id</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>uuid</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="n"/>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>Mã nội bộ của ví.</t>
+        </is>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>5c3a0e7d-2f9b-4c1e-a8d3-7b6f0c2e9a32</t>
+        </is>
+      </c>
+      <c r="I8" s="6" t="n"/>
+    </row>
+    <row r="9" ht="40.5" customHeight="1">
+      <c r="A9" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>user_id</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>uuid</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>users.user_id (khi xóa: chặn xóa)</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>Người sở hữu ví (phương thức khi ra mắt, BL-13): ví đi theo người đó sang mọi tổ chức họ lái xe cho. Chỉ đúng một trong user_id và organization_id có giá trị.</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>9b2e7d4a-1c3f-4a8e-b6d2-5e0f1a9c3d22</t>
+        </is>
+      </c>
+      <c r="I9" s="6" t="inlineStr">
+        <is>
+          <t>🔍</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="40.5" customHeight="1">
+      <c r="A10" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>organization_id</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>uuid</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>organizations.organization_id (khi xóa: chặn xóa)</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>Tổ chức sở hữu ví (phương thức sau này: tổ chức trả trước và tài xế dùng, hoặc tổ chức phân bổ cho tài xế); NULL với ví cá nhân.</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="I10" s="6" t="inlineStr">
+        <is>
+          <t>🔍</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="27" customHeight="1">
+      <c r="A11" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>balance</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>numeric(14,2)</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="n"/>
+      <c r="F11" s="6" t="n"/>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>Số dư hiện tại, luôn bằng tổng các giao dịch. Có thể âm khi một phiên sạc tốn nhiều hơn số dư (BL-14).</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>1250000.00</t>
+        </is>
+      </c>
+      <c r="I11" s="6" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>currency</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>char(3)</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="n"/>
+      <c r="F12" s="6" t="n"/>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>Mã tiền tệ ISO 4217.</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="I12" s="6" t="inlineStr">
+        <is>
+          <t>🔍</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="40.5" customHeight="1">
+      <c r="A13" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>varchar(20)</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="n"/>
+      <c r="F13" s="6" t="n"/>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>Do chúng ta quyết định. ACTIVE: dùng được. BLOCKED: không nạp tiền và không bắt đầu sạc, ví dụ khi đang kiểm tra gian lận.</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="I13" s="6" t="inlineStr">
+        <is>
+          <t>🔍</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="27" customHeight="1">
+      <c r="A14" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>status_reason</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>varchar(200)</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="n"/>
+      <c r="F14" s="6" t="n"/>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>Lý do ví có trạng thái hiện tại, ví dụ vì sao bị khóa (DM-19); NULL nếu không cần giải thích.</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="I14" s="6" t="inlineStr">
+        <is>
+          <t>🔍</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>created_at</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>timestamptz</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="n"/>
+      <c r="F15" s="6" t="n"/>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>Thời điểm tạo bản ghi (UTC).</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-01T02:00:00Z</t>
+        </is>
+      </c>
+      <c r="I15" s="6" t="inlineStr">
+        <is>
+          <t>🔍</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>updated_at</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>timestamptz</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="n"/>
+      <c r="F16" s="6" t="n"/>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>Thời điểm bản ghi được sửa gần nhất (UTC).</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-15T09:46:12Z</t>
+        </is>
+      </c>
+      <c r="I16" s="6" t="inlineStr">
+        <is>
+          <t>🔍</t>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
+    <row r="18">
+      <c r="A18" s="4" t="n"/>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>Chỉ mục (index)</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>Các cột</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>Duy nhất</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="n"/>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>Ghi chú</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="27" customHeight="1">
+      <c r="A19" s="6" t="n"/>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>uq_wallets_user_id</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>user_id</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="n"/>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>WHERE user_id IS NOT NULL: one wallet per person</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="27" customHeight="1">
+      <c r="A20" s="6" t="n"/>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>uq_wallets_organization_id</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>organization_id</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="n"/>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>WHERE organization_id IS NOT NULL: one wallet per organization</t>
+        </is>
+      </c>
+    </row>
+    <row r="21"/>
+    <row r="22">
+      <c r="A22" s="4" t="n"/>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>Được tham chiếu bởi bảng</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>Cột</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="n"/>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>wallet_transactions</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>wallet_id</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="n"/>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>wallet_history</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>wallet_id</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A7:I16"/>
+  <hyperlinks>
+    <hyperlink ref="A2" location="'Tổng quan'!A1"/>
+    <hyperlink ref="A5" location="'wallet_history'!A1"/>
+    <hyperlink ref="F9" location="'users'!A1"/>
+    <hyperlink ref="F10" location="'organizations'!A1"/>
+    <hyperlink ref="B23" location="'wallet_transactions'!A1"/>
+    <hyperlink ref="B24" location="'wallet_history'!A1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet74.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I23"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="7" max="7"/>
+    <col width="42" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>54.h. wallet_history: Lịch sử ví</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t>← Tổng quan</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>Miền nghiệp vụ: Thanh toán &amp; hóa đơn (billing)   ·   Chủ sở hữu dữ liệu: Khách hàng   ·   Tính năng: F-H2</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>Mọi phiên bản trước đây của một dòng trong bảng wallets: bản sao toàn bộ dòng, chụp ngay trước khi thay đổi và được trigger ghi trong cùng giao dịch. Do công cụ domain-model tự sinh từ @tracked *, không bao giờ viết tay.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>Bảng lịch sử của: wallets</t>
+        </is>
+      </c>
+    </row>
+    <row r="6"/>
+    <row r="7" ht="27" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Cột</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Kiểu dữ liệu</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Cho phép rỗng</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>Khóa</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>Tham chiếu tới</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>Ý nghĩa</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>Ví dụ</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>Lưu lịch sử</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>history_id</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>bigint</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="n"/>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>Mã tự tăng của dòng lịch sử.</t>
+        </is>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>1024</t>
+        </is>
+      </c>
+      <c r="I8" s="6" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>wallet_id</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>uuid</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>wallets.wallet_id (khi xóa: chặn xóa)</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>Giá trị trước khi thay đổi (wallets.wallet_id).</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>5c3a0e7d-2f9b-4c1e-a8d3-7b6f0c2e9a32</t>
+        </is>
+      </c>
+      <c r="I9" s="6" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>user_id</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>uuid</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="n"/>
+      <c r="F10" s="6" t="n"/>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>Giá trị trước khi thay đổi (wallets.user_id).</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>9b2e7d4a-1c3f-4a8e-b6d2-5e0f1a9c3d22</t>
+        </is>
+      </c>
+      <c r="I10" s="6" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>organization_id</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>uuid</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="n"/>
+      <c r="F11" s="6" t="n"/>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>Giá trị trước khi thay đổi (wallets.organization_id).</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="I11" s="6" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>balance</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>numeric(14,2)</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="n"/>
+      <c r="F12" s="6" t="n"/>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>Giá trị trước khi thay đổi (wallets.balance).</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>1250000.00</t>
+        </is>
+      </c>
+      <c r="I12" s="6" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>currency</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>char(3)</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="n"/>
+      <c r="F13" s="6" t="n"/>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>Giá trị trước khi thay đổi (wallets.currency).</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="I13" s="6" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>varchar(20)</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="n"/>
+      <c r="F14" s="6" t="n"/>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>Giá trị trước khi thay đổi (wallets.status).</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="I14" s="6" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>status_reason</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>varchar(200)</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="n"/>
+      <c r="F15" s="6" t="n"/>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>Giá trị trước khi thay đổi (wallets.status_reason).</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="I15" s="6" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>created_at</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>timestamptz</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="n"/>
+      <c r="F16" s="6" t="n"/>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>Giá trị trước khi thay đổi (wallets.created_at).</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-01T02:00:00Z</t>
+        </is>
+      </c>
+      <c r="I16" s="6" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>updated_at</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>timestamptz</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="n"/>
+      <c r="F17" s="6" t="n"/>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>Giá trị trước khi thay đổi (wallets.updated_at).</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-15T09:46:12Z</t>
+        </is>
+      </c>
+      <c r="I17" s="6" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>changed_at</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>timestamptz</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="n"/>
+      <c r="F18" s="6" t="n"/>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>Thời điểm phiên bản này của dòng bị thay thế.</t>
+        </is>
+      </c>
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-10T07:15:00Z</t>
+        </is>
+      </c>
+      <c r="I18" s="6" t="n"/>
+    </row>
+    <row r="19" ht="27" customHeight="1">
+      <c r="A19" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>changed_by</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>uuid</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="F19" s="7" t="inlineStr">
+        <is>
+          <t>users.user_id (khi xóa: chặn xóa)</t>
+        </is>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>Người dùng đã thực hiện thay đổi; NULL nếu do hệ thống thực hiện.</t>
+        </is>
+      </c>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>9b2e7d4a-1c3f-4a8e-b6d2-5e0f1a9c3d22</t>
+        </is>
+      </c>
+      <c r="I19" s="6" t="n"/>
+    </row>
+    <row r="20" ht="40.5" customHeight="1">
+      <c r="A20" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>change_reason</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>varchar(200)</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="n"/>
+      <c r="F20" s="6" t="n"/>
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t>Lý do thay đổi dòng, do ứng dụng đặt cho giao dịch: người dùng nhập với quyết định quản trị, văn bản cố định với thao tác thường lệ. Thay đổi không có lý do sẽ bị từ chối.</t>
+        </is>
+      </c>
+      <c r="H20" s="6" t="inlineStr">
+        <is>
+          <t>Customer moved to a new office</t>
+        </is>
+      </c>
+      <c r="I20" s="6" t="n"/>
+    </row>
+    <row r="21"/>
+    <row r="22">
+      <c r="A22" s="4" t="n"/>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>Chỉ mục (index)</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>Các cột</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>Duy nhất</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="n"/>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>Ghi chú</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="27" customHeight="1">
+      <c r="A23" s="6" t="n"/>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>ix_wallet_history_wallet_id_time</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>wallet_id, changed_at</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="n"/>
+      <c r="F23" s="6" t="n"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A7:I20"/>
+  <hyperlinks>
+    <hyperlink ref="A2" location="'Tổng quan'!A1"/>
+    <hyperlink ref="A5" location="'wallets'!A1"/>
+    <hyperlink ref="F9" location="'wallets'!A1"/>
+    <hyperlink ref="F19" location="'users'!A1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet75.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="7" max="7"/>
+    <col width="42" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>55. wallet_transactions: Giao dịch ví</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t>← Tổng quan</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>Miền nghiệp vụ: Thanh toán &amp; hóa đơn (billing)   ·   Chủ sở hữu dữ liệu: Khách hàng   ·   Tính năng: F-H2</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>Sổ giao dịch chỉ ghi thêm của ví (BL-14): mọi lần nạp, trả tiền phiên sạc, hoàn tiền và điều chỉnh của nhân viên, kèm số dư ngay sau đó. Không bao giờ sửa hay xóa; sai sót được sửa bằng một ADJUSTMENT. Ràng buộc kiểm tra (BL-14): liên kết và dấu số tiền khớp với loại giao dịch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5"/>
+    <row r="6" ht="27" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Cột</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Kiểu dữ liệu</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Cho phép rỗng</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>Khóa</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>Tham chiếu tới</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>Ý nghĩa</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>Ví dụ</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>Lưu lịch sử</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>wallet_transaction_id</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>uuid</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="n"/>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>Mã nội bộ của giao dịch.</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>00000010-5a6b-4c7d-8e9f-0a1b2c3d4e5f</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>wallet_id</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>uuid</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>wallets.wallet_id (khi xóa: chặn xóa)</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>Ví bị ảnh hưởng; dòng đọc chủ sở hữu qua ví (DM-24).</t>
+        </is>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>5c3a0e7d-2f9b-4c1e-a8d3-7b6f0c2e9a32</t>
+        </is>
+      </c>
+      <c r="I8" s="6" t="n"/>
+    </row>
+    <row r="9" ht="81" customHeight="1">
+      <c r="A9" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>transaction_type</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>varchar(20)</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="n"/>
+      <c r="F9" s="6" t="n"/>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>Loại giao dịch (BL-14). TOP_UP (+, từ một thanh toán). SESSION_BILL (-, trả một phiếu tính tiền phiên sạc). REFUND (-, hoàn số dư chưa dùng qua một thanh toán). ADJUSTMENT (+/-, do nhân viên của chúng ta điều chỉnh, kèm lý do). Sau này có TRANSFER_IN / TRANSFER_OUT khi tổ chức phân bổ cho tài xế.</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>SESSION_BILL</t>
+        </is>
+      </c>
+      <c r="I9" s="6" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>numeric(14,2)</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="n"/>
+      <c r="F10" s="6" t="n"/>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>Số tiền có dấu: dương là cộng, âm là trừ.</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>-952974.00</t>
+        </is>
+      </c>
+      <c r="I10" s="6" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>balance_after</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>numeric(14,2)</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="n"/>
+      <c r="F11" s="6" t="n"/>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>Số dư ví ngay sau giao dịch này.</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>297026.00</t>
+        </is>
+      </c>
+      <c r="I11" s="6" t="n"/>
+    </row>
+    <row r="12" ht="27" customHeight="1">
+      <c r="A12" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>payment_id</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>uuid</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>payments.payment_id (khi xóa: chặn xóa)</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>Thanh toán qua cổng đứng sau một lần TOP_UP hoặc REFUND.</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="I12" s="6" t="n"/>
+    </row>
+    <row r="13" ht="40.5" customHeight="1">
+      <c r="A13" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>charging_session_bill_id</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>uuid</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>charging_session_bills.charging_session_bill_id (khi xóa: chặn xóa)</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>Phiếu tính tiền được trả, với SESSION_BILL; duy nhất, nên mỗi phiếu chỉ trả một lần. Phiếu đã trả hay chưa được đọc từ đây.</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>2b8d4f0a-6c3e-4a9b-8d7f-1e4c9a2b8d66</t>
+        </is>
+      </c>
+      <c r="I13" s="6" t="n"/>
+    </row>
+    <row r="14" ht="27" customHeight="1">
+      <c r="A14" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>created_by</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>uuid</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="F14" s="7" t="inlineStr">
+        <is>
+          <t>users.user_id (khi xóa: chặn xóa)</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>Nhân viên của chúng ta, với ADJUSTMENT; NULL khi hệ thống tự ghi.</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="I14" s="6" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>reason</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>varchar(200)</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="n"/>
+      <c r="F15" s="6" t="n"/>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>Lý do, bắt buộc với ADJUSTMENT; NULL với loại khác.</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="I15" s="6" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>occurred_at</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>timestamptz</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="n"/>
+      <c r="F16" s="6" t="n"/>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>Thời điểm phát sinh giao dịch.</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-15T09:45:06Z</t>
+        </is>
+      </c>
+      <c r="I16" s="6" t="n"/>
+    </row>
+    <row r="17"/>
+    <row r="18">
+      <c r="A18" s="4" t="n"/>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>Chỉ mục (index)</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>Các cột</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>Duy nhất</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="n"/>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>Ghi chú</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="27" customHeight="1">
+      <c r="A19" s="6" t="n"/>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>ix_wallet_transactions_wallet_time</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>wallet_id, occurred_at</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="n"/>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>A wallet's statement</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="27" customHeight="1">
+      <c r="A20" s="6" t="n"/>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>uq_wallet_transactions_session_bill</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>charging_session_bill_id</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="n"/>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>WHERE charging_session_bill_id IS NOT NULL</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="27" customHeight="1">
+      <c r="A21" s="6" t="n"/>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>ix_wallet_transactions_payment_id</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>payment_id</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="n"/>
+      <c r="F21" s="6" t="n"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A6:I16"/>
+  <hyperlinks>
+    <hyperlink ref="A2" location="'Tổng quan'!A1"/>
+    <hyperlink ref="F8" location="'wallets'!A1"/>
+    <hyperlink ref="F12" location="'payments'!A1"/>
+    <hyperlink ref="F13" location="'charging_session_bills'!A1"/>
+    <hyperlink ref="F14" location="'users'!A1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet76.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="7" max="7"/>
+    <col width="42" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>56. invoices: Hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t>← Tổng quan</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>Miền nghiệp vụ: Thanh toán &amp; hóa đơn (billing)   ·   Chủ sở hữu dữ liệu: Khách hàng   ·   Tính năng: F-H3, F-H4</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>Một hóa đơn điện tử hợp lệ. Khi đã PHÁT HÀNH thì không sửa, chỉ điều chỉnh hoặc hủy bằng hóa đơn mới.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5"/>
+    <row r="6" ht="27" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Cột</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Kiểu dữ liệu</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Cho phép rỗng</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>Khóa</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>Tham chiếu tới</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>Ý nghĩa</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>Ví dụ</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>Lưu lịch sử</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>invoice_id</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>uuid</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="n"/>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>Mã nội bộ của hóa đơn.</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>7e5c2a9f-4b1d-4e3a-9c8f-0d6b1e4a7c43</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="n"/>
+    </row>
+    <row r="8" ht="27" customHeight="1">
+      <c r="A8" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>organization_id</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>uuid</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>organizations.organization_id (khi xóa: chặn xóa)</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>Tổ chức khách hàng được xuất hóa đơn.</t>
+        </is>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>3f6c2a1e-8b4d-4e2a-9c1f-0a7d5b2e4c11</t>
+        </is>
+      </c>
+      <c r="I8" s="6" t="n"/>
+    </row>
+    <row r="9" ht="27" customHeight="1">
+      <c r="A9" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>invoice_type</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>varchar(20)</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="n"/>
+      <c r="F9" s="6" t="n"/>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn lẻ theo phiên hay hóa đơn tổng hợp tháng cho đội xe. Giá trị: RETAIL | FLEET_MONTHLY.</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>FLEET_MONTHLY</t>
+        </is>
+      </c>
+      <c r="I9" s="6" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>period_start</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="n"/>
+      <c r="F10" s="6" t="n"/>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>Ngày đầu kỳ; NULL với hóa đơn một phiên.</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="I10" s="6" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>period_end</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="n"/>
+      <c r="F11" s="6" t="n"/>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>Ngày cuối kỳ; NULL với hóa đơn một phiên.</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="I11" s="6" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>total_amount</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>numeric(14,2)</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="n"/>
+      <c r="F12" s="6" t="n"/>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>Tổng tiền hóa đơn, gồm thuế.</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>256800000.00</t>
+        </is>
+      </c>
+      <c r="I12" s="6" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>currency</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>char(3)</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="n"/>
+      <c r="F13" s="6" t="n"/>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>Mã tiền tệ ISO 4217.</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="I13" s="6" t="n"/>
+    </row>
+    <row r="14" ht="27" customHeight="1">
+      <c r="A14" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>einvoice_number</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>varchar(50)</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="n"/>
+      <c r="F14" s="6" t="n"/>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>Số hóa đơn do nhà cung cấp hóa đơn điện tử cấp; NULL trước khi phát hành.</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>C26TMP0001234</t>
+        </is>
+      </c>
+      <c r="I14" s="6" t="n"/>
+    </row>
+    <row r="15" ht="27" customHeight="1">
+      <c r="A15" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>varchar(20)</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="n"/>
+      <c r="F15" s="6" t="n"/>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>Trạng thái hóa đơn; hóa đơn đã ISSUED không bao giờ bị sửa. Giá trị: DRAFT | ISSUED | ADJUSTED | CANCELLED.</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>ISSUED</t>
+        </is>
+      </c>
+      <c r="I15" s="6" t="n"/>
+    </row>
+    <row r="16" ht="27" customHeight="1">
+      <c r="A16" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>issued_at</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>timestamptz</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="n"/>
+      <c r="F16" s="6" t="n"/>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>Thời điểm phát hành hóa đơn điện tử; NULL trước khi phát hành.</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-01T03:00:00Z</t>
+        </is>
+      </c>
+      <c r="I16" s="6" t="n"/>
+    </row>
+    <row r="17"/>
+    <row r="18">
+      <c r="A18" s="4" t="n"/>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>Được tham chiếu bởi bảng</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>Cột</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="n"/>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>invoice_lines</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>invoice_id</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="n"/>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>payments</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>invoice_id</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A6:I16"/>
+  <hyperlinks>
+    <hyperlink ref="A2" location="'Tổng quan'!A1"/>
+    <hyperlink ref="F8" location="'organizations'!A1"/>
+    <hyperlink ref="B19" location="'invoice_lines'!A1"/>
+    <hyperlink ref="B20" location="'payments'!A1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet77.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -49031,1277 +51642,6 @@
     <row r="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>54. wallets: Ví</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="10" t="inlineStr">
-        <is>
-          <t>← Tổng quan</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>Miền nghiệp vụ: Thanh toán &amp; hóa đơn (billing)   ·   Chủ sở hữu dữ liệu: Khách hàng   ·   Tính năng: F-H2</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="11" t="inlineStr">
-        <is>
-          <t>Số dư trả trước của một tài xế hoặc của cả tổ chức.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5"/>
-    <row r="6" ht="27" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>Cột</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>Kiểu dữ liệu</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>Cho phép rỗng</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>Khóa</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>Tham chiếu tới</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>Ý nghĩa</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>Ví dụ</t>
-        </is>
-      </c>
-      <c r="I6" s="4" t="inlineStr">
-        <is>
-          <t>Lưu lịch sử</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>wallet_id</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>uuid</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
-      <c r="F7" s="6" t="n"/>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>Mã nội bộ của ví.</t>
-        </is>
-      </c>
-      <c r="H7" s="6" t="inlineStr">
-        <is>
-          <t>5c3a0e7d-2f9b-4c1e-a8d3-7b6f0c2e9a32</t>
-        </is>
-      </c>
-      <c r="I7" s="6" t="n"/>
-    </row>
-    <row r="8" ht="27" customHeight="1">
-      <c r="A8" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>organization_id</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>uuid</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E8" s="6" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="F8" s="7" t="inlineStr">
-        <is>
-          <t>organizations.organization_id (khi xóa: chặn xóa)</t>
-        </is>
-      </c>
-      <c r="G8" s="6" t="inlineStr">
-        <is>
-          <t>Tổ chức khách hàng sở hữu ví.</t>
-        </is>
-      </c>
-      <c r="H8" s="6" t="inlineStr">
-        <is>
-          <t>3f6c2a1e-8b4d-4e2a-9c1f-0a7d5b2e4c11</t>
-        </is>
-      </c>
-      <c r="I8" s="6" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>driver_id</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>uuid</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>có</t>
-        </is>
-      </c>
-      <c r="E9" s="6" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="F9" s="7" t="inlineStr">
-        <is>
-          <t>drivers.driver_id (khi xóa: chặn xóa)</t>
-        </is>
-      </c>
-      <c r="G9" s="6" t="inlineStr">
-        <is>
-          <t>Tài xế sở hữu ví; NULL với ví cấp tổ chức (quyết định D5).</t>
-        </is>
-      </c>
-      <c r="H9" s="6" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="I9" s="6" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>balance</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>numeric(14,2)</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E10" s="6" t="n"/>
-      <c r="F10" s="6" t="n"/>
-      <c r="G10" s="6" t="inlineStr">
-        <is>
-          <t>Số dư hiện tại; phải bằng tổng các giao dịch của ví.</t>
-        </is>
-      </c>
-      <c r="H10" s="6" t="inlineStr">
-        <is>
-          <t>12500000.00</t>
-        </is>
-      </c>
-      <c r="I10" s="6" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>currency</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>char(3)</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E11" s="6" t="n"/>
-      <c r="F11" s="6" t="n"/>
-      <c r="G11" s="6" t="inlineStr">
-        <is>
-          <t>Mã tiền tệ ISO 4217.</t>
-        </is>
-      </c>
-      <c r="H11" s="6" t="inlineStr">
-        <is>
-          <t>VND</t>
-        </is>
-      </c>
-      <c r="I11" s="6" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>varchar(20)</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E12" s="6" t="n"/>
-      <c r="F12" s="6" t="n"/>
-      <c r="G12" s="6" t="inlineStr">
-        <is>
-          <t>Ví có dùng được không.</t>
-        </is>
-      </c>
-      <c r="H12" s="6" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="I12" s="6" t="n"/>
-    </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" s="4" t="n"/>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>Được tham chiếu bởi bảng</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>Cột</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="6" t="n"/>
-      <c r="B15" s="7" t="inlineStr">
-        <is>
-          <t>wallet_transactions</t>
-        </is>
-      </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>wallet_id</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A6:I12"/>
-  <hyperlinks>
-    <hyperlink ref="A2" location="'Tổng quan'!A1"/>
-    <hyperlink ref="F8" location="'organizations'!A1"/>
-    <hyperlink ref="F9" location="'drivers'!A1"/>
-    <hyperlink ref="B15" location="'wallet_transactions'!A1"/>
-  </hyperlinks>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet74.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I15"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="40" customWidth="1" min="6" max="6"/>
-    <col width="60" customWidth="1" min="7" max="7"/>
-    <col width="42" customWidth="1" min="8" max="8"/>
-    <col width="11" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="9" t="inlineStr">
-        <is>
-          <t>55. wallet_transactions: Giao dịch ví</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="10" t="inlineStr">
-        <is>
-          <t>← Tổng quan</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>Miền nghiệp vụ: Thanh toán &amp; hóa đơn (billing)   ·   Chủ sở hữu dữ liệu: Khách hàng   ·   Tính năng: F-H2</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="11" t="inlineStr">
-        <is>
-          <t>Biến động tiền vào/ra khỏi ví, chỉ ghi thêm.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5"/>
-    <row r="6" ht="27" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>Cột</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>Kiểu dữ liệu</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>Cho phép rỗng</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>Khóa</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>Tham chiếu tới</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>Ý nghĩa</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>Ví dụ</t>
-        </is>
-      </c>
-      <c r="I6" s="4" t="inlineStr">
-        <is>
-          <t>Lưu lịch sử</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>transaction_id</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>uuid</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
-      <c r="F7" s="6" t="n"/>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>Mã nội bộ của giao dịch.</t>
-        </is>
-      </c>
-      <c r="H7" s="6" t="inlineStr">
-        <is>
-          <t>00000010-5a6b-4c7d-8e9f-0a1b2c3d4e5f</t>
-        </is>
-      </c>
-      <c r="I7" s="6" t="n"/>
-    </row>
-    <row r="8" ht="27" customHeight="1">
-      <c r="A8" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>organization_id</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>uuid</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E8" s="6" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="F8" s="7" t="inlineStr">
-        <is>
-          <t>organizations.organization_id (khi xóa: chặn xóa)</t>
-        </is>
-      </c>
-      <c r="G8" s="6" t="inlineStr">
-        <is>
-          <t>Tổ chức khách hàng của ví.</t>
-        </is>
-      </c>
-      <c r="H8" s="6" t="inlineStr">
-        <is>
-          <t>3f6c2a1e-8b4d-4e2a-9c1f-0a7d5b2e4c11</t>
-        </is>
-      </c>
-      <c r="I8" s="6" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>wallet_id</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>uuid</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E9" s="6" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="F9" s="7" t="inlineStr">
-        <is>
-          <t>wallets.wallet_id (khi xóa: chặn xóa)</t>
-        </is>
-      </c>
-      <c r="G9" s="6" t="inlineStr">
-        <is>
-          <t>Ví bị ảnh hưởng.</t>
-        </is>
-      </c>
-      <c r="H9" s="6" t="inlineStr">
-        <is>
-          <t>5c3a0e7d-2f9b-4c1e-a8d3-7b6f0c2e9a32</t>
-        </is>
-      </c>
-      <c r="I9" s="6" t="n"/>
-    </row>
-    <row r="10" ht="27" customHeight="1">
-      <c r="A10" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>transaction_type</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>varchar(20)</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E10" s="6" t="n"/>
-      <c r="F10" s="6" t="n"/>
-      <c r="G10" s="6" t="inlineStr">
-        <is>
-          <t>Loại biến động tiền. Giá trị: TOP_UP | CHARGE | WITHDRAW | REFUND.</t>
-        </is>
-      </c>
-      <c r="H10" s="6" t="inlineStr">
-        <is>
-          <t>CHARGE</t>
-        </is>
-      </c>
-      <c r="I10" s="6" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>amount</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>numeric(14,2)</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E11" s="6" t="n"/>
-      <c r="F11" s="6" t="n"/>
-      <c r="G11" s="6" t="inlineStr">
-        <is>
-          <t>Số tiền có dấu: dương là cộng tiền, âm là trừ tiền.</t>
-        </is>
-      </c>
-      <c r="H11" s="6" t="inlineStr">
-        <is>
-          <t>-866250.00</t>
-        </is>
-      </c>
-      <c r="I11" s="6" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>balance_after</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>numeric(14,2)</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E12" s="6" t="n"/>
-      <c r="F12" s="6" t="n"/>
-      <c r="G12" s="6" t="inlineStr">
-        <is>
-          <t>Số dư ví ngay sau giao dịch.</t>
-        </is>
-      </c>
-      <c r="H12" s="6" t="inlineStr">
-        <is>
-          <t>11633750.00</t>
-        </is>
-      </c>
-      <c r="I12" s="6" t="n"/>
-    </row>
-    <row r="13" ht="27" customHeight="1">
-      <c r="A13" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>session_id</t>
-        </is>
-      </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>uuid</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="inlineStr">
-        <is>
-          <t>có</t>
-        </is>
-      </c>
-      <c r="E13" s="6" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="F13" s="7" t="inlineStr">
-        <is>
-          <t>charging_sessions.session_id (khi xóa: chặn xóa)</t>
-        </is>
-      </c>
-      <c r="G13" s="6" t="inlineStr">
-        <is>
-          <t>Phiên sạc được trả tiền, với giao dịch CHARGE.</t>
-        </is>
-      </c>
-      <c r="H13" s="6" t="inlineStr">
-        <is>
-          <t>e5a2d8f1-4b7c-4e9a-b3d6-2c1f0e9a8dbb</t>
-        </is>
-      </c>
-      <c r="I13" s="6" t="n"/>
-    </row>
-    <row r="14" ht="27" customHeight="1">
-      <c r="A14" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="B14" s="6" t="inlineStr">
-        <is>
-          <t>payment_id</t>
-        </is>
-      </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>uuid</t>
-        </is>
-      </c>
-      <c r="D14" s="6" t="inlineStr">
-        <is>
-          <t>có</t>
-        </is>
-      </c>
-      <c r="E14" s="6" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="F14" s="7" t="inlineStr">
-        <is>
-          <t>payments.payment_id (khi xóa: chặn xóa)</t>
-        </is>
-      </c>
-      <c r="G14" s="6" t="inlineStr">
-        <is>
-          <t>Thanh toán qua cổng đứng sau một lần nạp tiền, nếu có.</t>
-        </is>
-      </c>
-      <c r="H14" s="6" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="I14" s="6" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="B15" s="6" t="inlineStr">
-        <is>
-          <t>occurred_at</t>
-        </is>
-      </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>timestamptz</t>
-        </is>
-      </c>
-      <c r="D15" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E15" s="6" t="n"/>
-      <c r="F15" s="6" t="n"/>
-      <c r="G15" s="6" t="inlineStr">
-        <is>
-          <t>Thời điểm phát sinh giao dịch.</t>
-        </is>
-      </c>
-      <c r="H15" s="6" t="inlineStr">
-        <is>
-          <t>2026-09-15T09:46:12Z</t>
-        </is>
-      </c>
-      <c r="I15" s="6" t="n"/>
-    </row>
-  </sheetData>
-  <autoFilter ref="A6:I15"/>
-  <hyperlinks>
-    <hyperlink ref="A2" location="'Tổng quan'!A1"/>
-    <hyperlink ref="F8" location="'organizations'!A1"/>
-    <hyperlink ref="F9" location="'wallets'!A1"/>
-    <hyperlink ref="F13" location="'charging_sessions'!A1"/>
-    <hyperlink ref="F14" location="'payments'!A1"/>
-  </hyperlinks>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet75.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I19"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="40" customWidth="1" min="6" max="6"/>
-    <col width="60" customWidth="1" min="7" max="7"/>
-    <col width="42" customWidth="1" min="8" max="8"/>
-    <col width="11" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="9" t="inlineStr">
-        <is>
-          <t>56. invoices: Hóa đơn</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="10" t="inlineStr">
-        <is>
-          <t>← Tổng quan</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>Miền nghiệp vụ: Thanh toán &amp; hóa đơn (billing)   ·   Chủ sở hữu dữ liệu: Khách hàng   ·   Tính năng: F-H3, F-H4</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="11" t="inlineStr">
-        <is>
-          <t>Một hóa đơn điện tử hợp lệ. Khi đã PHÁT HÀNH thì không sửa, chỉ điều chỉnh hoặc hủy bằng hóa đơn mới.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5"/>
-    <row r="6" ht="27" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>Cột</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>Kiểu dữ liệu</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>Cho phép rỗng</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>Khóa</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>Tham chiếu tới</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>Ý nghĩa</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>Ví dụ</t>
-        </is>
-      </c>
-      <c r="I6" s="4" t="inlineStr">
-        <is>
-          <t>Lưu lịch sử</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>invoice_id</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>uuid</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
-      <c r="F7" s="6" t="n"/>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>Mã nội bộ của hóa đơn.</t>
-        </is>
-      </c>
-      <c r="H7" s="6" t="inlineStr">
-        <is>
-          <t>7e5c2a9f-4b1d-4e3a-9c8f-0d6b1e4a7c43</t>
-        </is>
-      </c>
-      <c r="I7" s="6" t="n"/>
-    </row>
-    <row r="8" ht="27" customHeight="1">
-      <c r="A8" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>organization_id</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>uuid</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E8" s="6" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="F8" s="7" t="inlineStr">
-        <is>
-          <t>organizations.organization_id (khi xóa: chặn xóa)</t>
-        </is>
-      </c>
-      <c r="G8" s="6" t="inlineStr">
-        <is>
-          <t>Tổ chức khách hàng được xuất hóa đơn.</t>
-        </is>
-      </c>
-      <c r="H8" s="6" t="inlineStr">
-        <is>
-          <t>3f6c2a1e-8b4d-4e2a-9c1f-0a7d5b2e4c11</t>
-        </is>
-      </c>
-      <c r="I8" s="6" t="n"/>
-    </row>
-    <row r="9" ht="27" customHeight="1">
-      <c r="A9" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>invoice_type</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>varchar(20)</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E9" s="6" t="n"/>
-      <c r="F9" s="6" t="n"/>
-      <c r="G9" s="6" t="inlineStr">
-        <is>
-          <t>Hóa đơn lẻ theo phiên hay hóa đơn tổng hợp tháng cho đội xe. Giá trị: RETAIL | FLEET_MONTHLY.</t>
-        </is>
-      </c>
-      <c r="H9" s="6" t="inlineStr">
-        <is>
-          <t>FLEET_MONTHLY</t>
-        </is>
-      </c>
-      <c r="I9" s="6" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>period_start</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>có</t>
-        </is>
-      </c>
-      <c r="E10" s="6" t="n"/>
-      <c r="F10" s="6" t="n"/>
-      <c r="G10" s="6" t="inlineStr">
-        <is>
-          <t>Ngày đầu kỳ; NULL với hóa đơn một phiên.</t>
-        </is>
-      </c>
-      <c r="H10" s="6" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="I10" s="6" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>period_end</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>có</t>
-        </is>
-      </c>
-      <c r="E11" s="6" t="n"/>
-      <c r="F11" s="6" t="n"/>
-      <c r="G11" s="6" t="inlineStr">
-        <is>
-          <t>Ngày cuối kỳ; NULL với hóa đơn một phiên.</t>
-        </is>
-      </c>
-      <c r="H11" s="6" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="I11" s="6" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>total_amount</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>numeric(14,2)</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E12" s="6" t="n"/>
-      <c r="F12" s="6" t="n"/>
-      <c r="G12" s="6" t="inlineStr">
-        <is>
-          <t>Tổng tiền hóa đơn, gồm thuế.</t>
-        </is>
-      </c>
-      <c r="H12" s="6" t="inlineStr">
-        <is>
-          <t>256800000.00</t>
-        </is>
-      </c>
-      <c r="I12" s="6" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>currency</t>
-        </is>
-      </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>char(3)</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E13" s="6" t="n"/>
-      <c r="F13" s="6" t="n"/>
-      <c r="G13" s="6" t="inlineStr">
-        <is>
-          <t>Mã tiền tệ ISO 4217.</t>
-        </is>
-      </c>
-      <c r="H13" s="6" t="inlineStr">
-        <is>
-          <t>VND</t>
-        </is>
-      </c>
-      <c r="I13" s="6" t="n"/>
-    </row>
-    <row r="14" ht="27" customHeight="1">
-      <c r="A14" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="B14" s="6" t="inlineStr">
-        <is>
-          <t>einvoice_number</t>
-        </is>
-      </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>varchar(50)</t>
-        </is>
-      </c>
-      <c r="D14" s="6" t="inlineStr">
-        <is>
-          <t>có</t>
-        </is>
-      </c>
-      <c r="E14" s="6" t="n"/>
-      <c r="F14" s="6" t="n"/>
-      <c r="G14" s="6" t="inlineStr">
-        <is>
-          <t>Số hóa đơn do nhà cung cấp hóa đơn điện tử cấp; NULL trước khi phát hành.</t>
-        </is>
-      </c>
-      <c r="H14" s="6" t="inlineStr">
-        <is>
-          <t>C26TMP0001234</t>
-        </is>
-      </c>
-      <c r="I14" s="6" t="n"/>
-    </row>
-    <row r="15" ht="27" customHeight="1">
-      <c r="A15" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="B15" s="6" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>varchar(20)</t>
-        </is>
-      </c>
-      <c r="D15" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E15" s="6" t="n"/>
-      <c r="F15" s="6" t="n"/>
-      <c r="G15" s="6" t="inlineStr">
-        <is>
-          <t>Trạng thái hóa đơn; hóa đơn đã ISSUED không bao giờ bị sửa. Giá trị: DRAFT | ISSUED | ADJUSTED | CANCELLED.</t>
-        </is>
-      </c>
-      <c r="H15" s="6" t="inlineStr">
-        <is>
-          <t>ISSUED</t>
-        </is>
-      </c>
-      <c r="I15" s="6" t="n"/>
-    </row>
-    <row r="16" ht="27" customHeight="1">
-      <c r="A16" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="B16" s="6" t="inlineStr">
-        <is>
-          <t>issued_at</t>
-        </is>
-      </c>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>timestamptz</t>
-        </is>
-      </c>
-      <c r="D16" s="6" t="inlineStr">
-        <is>
-          <t>có</t>
-        </is>
-      </c>
-      <c r="E16" s="6" t="n"/>
-      <c r="F16" s="6" t="n"/>
-      <c r="G16" s="6" t="inlineStr">
-        <is>
-          <t>Thời điểm phát hành hóa đơn điện tử; NULL trước khi phát hành.</t>
-        </is>
-      </c>
-      <c r="H16" s="6" t="inlineStr">
-        <is>
-          <t>2026-10-01T03:00:00Z</t>
-        </is>
-      </c>
-      <c r="I16" s="6" t="n"/>
-    </row>
-    <row r="17"/>
-    <row r="18">
-      <c r="A18" s="4" t="n"/>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>Được tham chiếu bởi bảng</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>Cột</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="6" t="n"/>
-      <c r="B19" s="7" t="inlineStr">
-        <is>
-          <t>invoice_lines</t>
-        </is>
-      </c>
-      <c r="C19" s="6" t="inlineStr">
-        <is>
-          <t>invoice_id</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A6:I16"/>
-  <hyperlinks>
-    <hyperlink ref="A2" location="'Tổng quan'!A1"/>
-    <hyperlink ref="F8" location="'organizations'!A1"/>
-    <hyperlink ref="B19" location="'invoice_lines'!A1"/>
-  </hyperlinks>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet76.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I15"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="40" customWidth="1" min="6" max="6"/>
-    <col width="60" customWidth="1" min="7" max="7"/>
-    <col width="42" customWidth="1" min="8" max="8"/>
-    <col width="11" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="9" t="inlineStr">
-        <is>
           <t>57. invoice_lines: Dòng hóa đơn</t>
         </is>
       </c>
@@ -50721,7 +52061,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet77.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet78.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -51107,7 +52447,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet78.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet79.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -51397,401 +52737,6 @@
   <hyperlinks>
     <hyperlink ref="A2" location="'Tổng quan'!A1"/>
     <hyperlink ref="F8" location="'subscription_plans'!A1"/>
-  </hyperlinks>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet79.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I16"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="40" customWidth="1" min="6" max="6"/>
-    <col width="60" customWidth="1" min="7" max="7"/>
-    <col width="42" customWidth="1" min="8" max="8"/>
-    <col width="11" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="9" t="inlineStr">
-        <is>
-          <t>60. subscriptions: Thuê bao</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="10" t="inlineStr">
-        <is>
-          <t>← Tổng quan</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>Miền nghiệp vụ: Thanh toán &amp; hóa đơn (billing)   ·   Chủ sở hữu dữ liệu: Khách hàng   ·   Tính năng: F-H4</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="11" t="inlineStr">
-        <is>
-          <t>Một xe đăng ký một gói; quá hạn thanh toán sẽ khóa tính năng.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5"/>
-    <row r="6" ht="27" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>Cột</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>Kiểu dữ liệu</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>Cho phép rỗng</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>Khóa</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>Tham chiếu tới</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>Ý nghĩa</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>Ví dụ</t>
-        </is>
-      </c>
-      <c r="I6" s="4" t="inlineStr">
-        <is>
-          <t>Lưu lịch sử</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>subscription_id</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>uuid</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
-      <c r="F7" s="6" t="n"/>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>Mã nội bộ của thuê bao.</t>
-        </is>
-      </c>
-      <c r="H7" s="6" t="inlineStr">
-        <is>
-          <t>9a7e4c1b-6d3f-4a5c-b0e8-2f1d7c9b3e54</t>
-        </is>
-      </c>
-      <c r="I7" s="6" t="n"/>
-    </row>
-    <row r="8" ht="27" customHeight="1">
-      <c r="A8" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>organization_id</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>uuid</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E8" s="6" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="F8" s="7" t="inlineStr">
-        <is>
-          <t>organizations.organization_id (khi xóa: chặn xóa)</t>
-        </is>
-      </c>
-      <c r="G8" s="6" t="inlineStr">
-        <is>
-          <t>Tổ chức khách hàng đăng ký.</t>
-        </is>
-      </c>
-      <c r="H8" s="6" t="inlineStr">
-        <is>
-          <t>3f6c2a1e-8b4d-4e2a-9c1f-0a7d5b2e4c11</t>
-        </is>
-      </c>
-      <c r="I8" s="6" t="n"/>
-    </row>
-    <row r="9" ht="27" customHeight="1">
-      <c r="A9" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>plan_id</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>uuid</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E9" s="6" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="F9" s="7" t="inlineStr">
-        <is>
-          <t>subscription_plans.plan_id (khi xóa: chặn xóa)</t>
-        </is>
-      </c>
-      <c r="G9" s="6" t="inlineStr">
-        <is>
-          <t>Gói được đăng ký.</t>
-        </is>
-      </c>
-      <c r="H9" s="6" t="inlineStr">
-        <is>
-          <t>0c9a6e3d-8f5b-4c7e-a2d1-4b3f9e6c0a65</t>
-        </is>
-      </c>
-      <c r="I9" s="6" t="n"/>
-    </row>
-    <row r="10" ht="27" customHeight="1">
-      <c r="A10" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>vehicle_id</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>uuid</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E10" s="6" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="F10" s="7" t="inlineStr">
-        <is>
-          <t>vehicles.vehicle_id (khi xóa: chặn xóa)</t>
-        </is>
-      </c>
-      <c r="G10" s="6" t="inlineStr">
-        <is>
-          <t>Xe được áp dụng.</t>
-        </is>
-      </c>
-      <c r="H10" s="6" t="inlineStr">
-        <is>
-          <t>7a4c1e9b-3d2f-4b8a-a6c5-1e0d9f8b7a44</t>
-        </is>
-      </c>
-      <c r="I10" s="6" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>started_at</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>timestamptz</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E11" s="6" t="n"/>
-      <c r="F11" s="6" t="n"/>
-      <c r="G11" s="6" t="inlineStr">
-        <is>
-          <t>Thời điểm bắt đầu thuê bao.</t>
-        </is>
-      </c>
-      <c r="H11" s="6" t="inlineStr">
-        <is>
-          <t>2026-09-01T00:00:00Z</t>
-        </is>
-      </c>
-      <c r="I11" s="6" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>ends_at</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>timestamptz</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>có</t>
-        </is>
-      </c>
-      <c r="E12" s="6" t="n"/>
-      <c r="F12" s="6" t="n"/>
-      <c r="G12" s="6" t="inlineStr">
-        <is>
-          <t>Thời điểm kết thúc; NULL nếu tự gia hạn cho tới khi hủy.</t>
-        </is>
-      </c>
-      <c r="H12" s="6" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="I12" s="6" t="n"/>
-    </row>
-    <row r="13" ht="27" customHeight="1">
-      <c r="A13" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>varchar(20)</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E13" s="6" t="n"/>
-      <c r="F13" s="6" t="n"/>
-      <c r="G13" s="6" t="inlineStr">
-        <is>
-          <t>Trạng thái thuê bao; OVERDUE sẽ khóa các tính năng trả phí. Giá trị: ACTIVE | OVERDUE | EXPIRED | CANCELLED.</t>
-        </is>
-      </c>
-      <c r="H13" s="6" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="I13" s="6" t="n"/>
-    </row>
-    <row r="14"/>
-    <row r="15">
-      <c r="A15" s="4" t="n"/>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>Được tham chiếu bởi bảng</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>Cột</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="6" t="n"/>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>invoice_lines</t>
-        </is>
-      </c>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>subscription_id</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A6:I13"/>
-  <hyperlinks>
-    <hyperlink ref="A2" location="'Tổng quan'!A1"/>
-    <hyperlink ref="F8" location="'organizations'!A1"/>
-    <hyperlink ref="F9" location="'subscription_plans'!A1"/>
-    <hyperlink ref="F10" location="'vehicles'!A1"/>
-    <hyperlink ref="B16" location="'invoice_lines'!A1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -52462,6 +53407,401 @@
     <row r="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
+          <t>60. subscriptions: Thuê bao</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t>← Tổng quan</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>Miền nghiệp vụ: Thanh toán &amp; hóa đơn (billing)   ·   Chủ sở hữu dữ liệu: Khách hàng   ·   Tính năng: F-H4</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>Một xe đăng ký một gói; quá hạn thanh toán sẽ khóa tính năng.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5"/>
+    <row r="6" ht="27" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Cột</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Kiểu dữ liệu</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Cho phép rỗng</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>Khóa</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>Tham chiếu tới</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>Ý nghĩa</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>Ví dụ</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>Lưu lịch sử</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>subscription_id</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>uuid</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="n"/>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>Mã nội bộ của thuê bao.</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>9a7e4c1b-6d3f-4a5c-b0e8-2f1d7c9b3e54</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="n"/>
+    </row>
+    <row r="8" ht="27" customHeight="1">
+      <c r="A8" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>organization_id</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>uuid</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>organizations.organization_id (khi xóa: chặn xóa)</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>Tổ chức khách hàng đăng ký.</t>
+        </is>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>3f6c2a1e-8b4d-4e2a-9c1f-0a7d5b2e4c11</t>
+        </is>
+      </c>
+      <c r="I8" s="6" t="n"/>
+    </row>
+    <row r="9" ht="27" customHeight="1">
+      <c r="A9" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>plan_id</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>uuid</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>subscription_plans.plan_id (khi xóa: chặn xóa)</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>Gói được đăng ký.</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>0c9a6e3d-8f5b-4c7e-a2d1-4b3f9e6c0a65</t>
+        </is>
+      </c>
+      <c r="I9" s="6" t="n"/>
+    </row>
+    <row r="10" ht="27" customHeight="1">
+      <c r="A10" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>vehicle_id</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>uuid</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>vehicles.vehicle_id (khi xóa: chặn xóa)</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>Xe được áp dụng.</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>7a4c1e9b-3d2f-4b8a-a6c5-1e0d9f8b7a44</t>
+        </is>
+      </c>
+      <c r="I10" s="6" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>started_at</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>timestamptz</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="n"/>
+      <c r="F11" s="6" t="n"/>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>Thời điểm bắt đầu thuê bao.</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="I11" s="6" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>ends_at</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>timestamptz</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="n"/>
+      <c r="F12" s="6" t="n"/>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>Thời điểm kết thúc; NULL nếu tự gia hạn cho tới khi hủy.</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="I12" s="6" t="n"/>
+    </row>
+    <row r="13" ht="27" customHeight="1">
+      <c r="A13" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>varchar(20)</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="n"/>
+      <c r="F13" s="6" t="n"/>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>Trạng thái thuê bao; OVERDUE sẽ khóa các tính năng trả phí. Giá trị: ACTIVE | OVERDUE | EXPIRED | CANCELLED.</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="I13" s="6" t="n"/>
+    </row>
+    <row r="14"/>
+    <row r="15">
+      <c r="A15" s="4" t="n"/>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>Được tham chiếu bởi bảng</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>Cột</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="n"/>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>invoice_lines</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>subscription_id</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A6:I13"/>
+  <hyperlinks>
+    <hyperlink ref="A2" location="'Tổng quan'!A1"/>
+    <hyperlink ref="F8" location="'organizations'!A1"/>
+    <hyperlink ref="F9" location="'subscription_plans'!A1"/>
+    <hyperlink ref="F10" location="'vehicles'!A1"/>
+    <hyperlink ref="B16" location="'invoice_lines'!A1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet81.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="7" max="7"/>
+    <col width="42" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
           <t>61. driver_scores: Điểm tài xế</t>
         </is>
       </c>
@@ -52842,7 +54182,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet81.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet82.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -53149,7 +54489,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet82.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet83.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/docs/design/domain-model/domain-model.xlsx
+++ b/docs/design/domain-model/domain-model.xlsx
@@ -162,9 +162,9 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="68" hidden="1">'tariff_versions'!$A$6:$I$16</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="69" hidden="1">'charging_session_bills'!$A$7:$I$21</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="70" hidden="1">'charging_session_bill_history'!$A$7:$I$25</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="71" hidden="1">'payments'!$A$6:$I$22</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="72" hidden="1">'wallets'!$A$7:$I$16</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="73" hidden="1">'wallet_history'!$A$7:$I$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="71" hidden="1">'payments'!$A$6:$I$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="72" hidden="1">'wallets'!$A$7:$I$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="73" hidden="1">'wallet_history'!$A$7:$I$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="74" hidden="1">'wallet_transactions'!$A$6:$I$16</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="75" hidden="1">'invoices'!$A$6:$I$16</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="76" hidden="1">'invoice_lines'!$A$6:$I$15</definedName>
@@ -3999,7 +3999,7 @@
         <is>
           <t>Tiền: giá điện, thanh toán, ví trả trước, hóa đơn điện tử và thuê bao SaaS.
 • Biểu giá định giá điện cho toàn mạng hoặc từng trạm, theo khung giờ.
-• Một ví là số dư trả trước của một người (khi ra mắt) hoặc một tổ chức (sau này); giao dịch ví là sổ chỉ ghi thêm. Một thanh toán là tiền thật qua cổng: nạp tiền hoặc hoàn tiền khi ra mắt (BL-12 đến BL-14).
+• Một ví là số dư trả trước để sạc của một người; giao dịch ví là sổ chỉ ghi thêm. Một thanh toán là tiền thật vào hoặc ra: nạp bằng chuyển khoản VietQR, hoặc hoàn tiền (BL-12 đến BL-15).
 • Một hóa đơn thuộc một tổ chức và có các dòng hóa đơn cho phiên sạc hoặc kỳ thuê bao.
 • Một thuê bao đưa một xe vào một gói dịch vụ.
 • Muốn tính tiền một phiên sạc phải biết phiên đó của ai.
@@ -4232,7 +4232,7 @@
         </is>
       </c>
     </row>
-    <row r="90" ht="81" customHeight="1">
+    <row r="90" ht="94.5" customHeight="1">
       <c r="A90" s="6" t="inlineStr">
         <is>
           <t>53</t>
@@ -4255,21 +4255,21 @@
       </c>
       <c r="E90" s="6" t="inlineStr">
         <is>
-          <t>Khách hàng</t>
+          <t>Nội bộ</t>
         </is>
       </c>
       <c r="F90" s="6" t="inlineStr">
         <is>
-          <t>F-H1</t>
+          <t>F-H1, F-H2</t>
         </is>
       </c>
       <c r="G90" s="6" t="inlineStr">
         <is>
-          <t>Tiền đi qua cổng thanh toán hoặc ngân hàng (BL-12): chỉ tiền thật vào hoặc ra. Trả tiền phiên sạc bằng ví là giao dịch ví, không phải thanh toán. Khi ra mắt chỉ có TOP_UP và REFUND; SESSION_BILL và INVOICE đến cùng các phương thức sau. Không có lịch sử thay đổi (trạng thái do cổng báo); không xóa mềm (chứng từ tài chính). Thẻ đã lưu (mã hóa token) là bảng sau này. Ràng buộc kiểm tra (BL-12): liên kết có giá trị khớp với mục đích.</t>
+          <t>Tiền thật vào hoặc ra khỏi ví của một người (BL-12, BL-15): chỉ nạp tiền và hoàn tiền. Khi ra mắt, tài xế nạp bằng chuyển khoản qua mã VietQR mang nội dung chuyển khoản duy nhất; dịch vụ nhận thông báo ngân hàng ghép giao dịch đến và ví được cộng đúng số tiền thực nhận. MoMo, ZaloPay và thẻ đến sau như giá trị mới. Trả tiền phiên sạc bằng ví là giao dịch ví, không phải thanh toán. Không có lịch sử thay đổi; không xóa mềm. Ràng buộc kiểm tra (BL-15): chỉ REFUND mới có refund_of_payment_id.</t>
         </is>
       </c>
       <c r="H90" s="6" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I90" s="7" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
     </row>
-    <row r="91" ht="135" customHeight="1">
+    <row r="91" ht="121.5" customHeight="1">
       <c r="A91" s="6" t="inlineStr">
         <is>
           <t>54</t>
@@ -4300,7 +4300,7 @@
       </c>
       <c r="E91" s="6" t="inlineStr">
         <is>
-          <t>Khách hàng</t>
+          <t>Nội bộ</t>
         </is>
       </c>
       <c r="F91" s="6" t="inlineStr">
@@ -4310,11 +4310,11 @@
       </c>
       <c r="G91" s="6" t="inlineStr">
         <is>
-          <t>Số dư trả trước chỉ dùng cho dịch vụ của chính chúng ta (BL-13). Khi ra mắt, mỗi người tự nạp tiền vào ví của mình và trả từng phiên sạc từ đó; ví của tổ chức được chuẩn bị cho các phương thức sau. Để bắt đầu sạc, số dư phải bằng hoặc cao hơn mức tối thiểu đặt trong backend (BL-14); kiểm tra khi quét mã, không bằng ràng buộc cơ sở dữ liệu, vì lần trừ tiền cuối phiên có thể làm số dư âm, sau đó người dùng không thể sạc tiếp cho tới khi nạp lại trên mức tối thiểu. Bật lịch sử thay đổi cho các quyết định (khóa ví), trừ cột balance vì mọi giao dịch đều làm thay đổi nó. Không xóa mềm. Không gọi là ví điện tử khi giới thiệu ra bên ngoài (câu hỏi mở 11). Ràng buộc kiểm tra (BL-13): chỉ đúng một chủ sở hữu.</t>
+          <t>Số dư trả trước để sạc của một người, chỉ dùng cho dịch vụ của chính chúng ta (BL-13, BL-15): người đó nạp tiền và trả từng phiên sạc từ ví. Ví của tổ chức chỉ được thêm cùng các phương thức thanh toán doanh nghiệp. Để bắt đầu sạc, số dư phải bằng hoặc cao hơn mức tối thiểu đặt trong backend (BL-14); kiểm tra khi quét mã, không bằng ràng buộc cơ sở dữ liệu, vì lần trừ tiền cuối phiên có thể làm số dư âm, sau đó người dùng không thể sạc tiếp cho tới khi nạp lại trên mức tối thiểu. Bật lịch sử thay đổi cho các quyết định (khóa ví), trừ cột balance vì mọi giao dịch đều làm thay đổi nó. Không xóa mềm. Không gọi là ví điện tử khi giới thiệu ra bên ngoài (câu hỏi mở 11).</t>
         </is>
       </c>
       <c r="H91" s="6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I91" s="7" t="inlineStr">
         <is>
@@ -4345,7 +4345,7 @@
       </c>
       <c r="E92" s="6" t="inlineStr">
         <is>
-          <t>Khách hàng</t>
+          <t>Nội bộ</t>
         </is>
       </c>
       <c r="F92" s="6" t="inlineStr">
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="H92" s="6" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I92" s="7" t="inlineStr">
         <is>
@@ -4390,7 +4390,7 @@
       </c>
       <c r="E93" s="6" t="inlineStr">
         <is>
-          <t>Khách hàng</t>
+          <t>Nội bộ</t>
         </is>
       </c>
       <c r="F93" s="6" t="inlineStr">
@@ -10817,7 +10817,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I58"/>
+  <dimension ref="A1:I56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -11834,7 +11834,7 @@
       <c r="A54" s="6" t="n"/>
       <c r="B54" s="7" t="inlineStr">
         <is>
-          <t>payments</t>
+          <t>driver_scores</t>
         </is>
       </c>
       <c r="C54" s="6" t="inlineStr">
@@ -11847,7 +11847,7 @@
       <c r="A55" s="6" t="n"/>
       <c r="B55" s="7" t="inlineStr">
         <is>
-          <t>wallets</t>
+          <t>trips</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
@@ -11860,36 +11860,10 @@
       <c r="A56" s="6" t="n"/>
       <c r="B56" s="7" t="inlineStr">
         <is>
-          <t>driver_scores</t>
+          <t>organization_history</t>
         </is>
       </c>
       <c r="C56" s="6" t="inlineStr">
-        <is>
-          <t>organization_id</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="6" t="n"/>
-      <c r="B57" s="7" t="inlineStr">
-        <is>
-          <t>trips</t>
-        </is>
-      </c>
-      <c r="C57" s="6" t="inlineStr">
-        <is>
-          <t>organization_id</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="6" t="n"/>
-      <c r="B58" s="7" t="inlineStr">
-        <is>
-          <t>organization_history</t>
-        </is>
-      </c>
-      <c r="C58" s="6" t="inlineStr">
         <is>
           <t>organization_id</t>
         </is>
@@ -11929,11 +11903,9 @@
     <hyperlink ref="B51" location="'invoices'!A1"/>
     <hyperlink ref="B52" location="'invoice_lines'!A1"/>
     <hyperlink ref="B53" location="'subscriptions'!A1"/>
-    <hyperlink ref="B54" location="'payments'!A1"/>
-    <hyperlink ref="B55" location="'wallets'!A1"/>
-    <hyperlink ref="B56" location="'driver_scores'!A1"/>
-    <hyperlink ref="B57" location="'trips'!A1"/>
-    <hyperlink ref="B58" location="'organization_history'!A1"/>
+    <hyperlink ref="B54" location="'driver_scores'!A1"/>
+    <hyperlink ref="B55" location="'trips'!A1"/>
+    <hyperlink ref="B56" location="'organization_history'!A1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -27161,7 +27133,7 @@
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>paid_by</t>
+          <t>user_id</t>
         </is>
       </c>
     </row>
@@ -47042,7 +47014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I30"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -47760,7 +47732,7 @@
       <c r="A28" s="6" t="n"/>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>payments</t>
+          <t>wallet_transactions</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
@@ -47773,23 +47745,10 @@
       <c r="A29" s="6" t="n"/>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>wallet_transactions</t>
+          <t>charging_session_bill_history</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
-        <is>
-          <t>charging_session_bill_id</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="27" customHeight="1">
-      <c r="A30" s="6" t="n"/>
-      <c r="B30" s="7" t="inlineStr">
-        <is>
-          <t>charging_session_bill_history</t>
-        </is>
-      </c>
-      <c r="C30" s="6" t="inlineStr">
         <is>
           <t>charging_session_bill_id</t>
         </is>
@@ -47802,9 +47761,8 @@
     <hyperlink ref="A5" location="'charging_session_bill_history'!A1"/>
     <hyperlink ref="F9" location="'charging_sessions'!A1"/>
     <hyperlink ref="F10" location="'tariff_versions'!A1"/>
-    <hyperlink ref="B28" location="'payments'!A1"/>
-    <hyperlink ref="B29" location="'wallet_transactions'!A1"/>
-    <hyperlink ref="B30" location="'charging_session_bill_history'!A1"/>
+    <hyperlink ref="B28" location="'wallet_transactions'!A1"/>
+    <hyperlink ref="B29" location="'charging_session_bill_history'!A1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -48590,7 +48548,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I30"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -48621,14 +48579,14 @@
     <row r="3">
       <c r="A3" s="11" t="inlineStr">
         <is>
-          <t>Miền nghiệp vụ: Thanh toán &amp; hóa đơn (billing)   ·   Chủ sở hữu dữ liệu: Khách hàng   ·   Tính năng: F-H1</t>
+          <t>Miền nghiệp vụ: Thanh toán &amp; hóa đơn (billing)   ·   Chủ sở hữu dữ liệu: Nội bộ   ·   Tính năng: F-H1, F-H2</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="11" t="inlineStr">
         <is>
-          <t>Tiền đi qua cổng thanh toán hoặc ngân hàng (BL-12): chỉ tiền thật vào hoặc ra. Trả tiền phiên sạc bằng ví là giao dịch ví, không phải thanh toán. Khi ra mắt chỉ có TOP_UP và REFUND; SESSION_BILL và INVOICE đến cùng các phương thức sau. Không có lịch sử thay đổi (trạng thái do cổng báo); không xóa mềm (chứng từ tài chính). Thẻ đã lưu (mã hóa token) là bảng sau này. Ràng buộc kiểm tra (BL-12): liên kết có giá trị khớp với mục đích.</t>
+          <t>Tiền thật vào hoặc ra khỏi ví của một người (BL-12, BL-15): chỉ nạp tiền và hoàn tiền. Khi ra mắt, tài xế nạp bằng chuyển khoản qua mã VietQR mang nội dung chuyển khoản duy nhất; dịch vụ nhận thông báo ngân hàng ghép giao dịch đến và ví được cộng đúng số tiền thực nhận. MoMo, ZaloPay và thẻ đến sau như giá trị mới. Trả tiền phiên sạc bằng ví là giao dịch ví, không phải thanh toán. Không có lịch sử thay đổi; không xóa mềm. Ràng buộc kiểm tra (BL-15): chỉ REFUND mới có refund_of_payment_id.</t>
         </is>
       </c>
     </row>
@@ -48723,7 +48681,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>organization_id</t>
+          <t>user_id</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
@@ -48743,280 +48701,256 @@
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>organizations.organization_id (khi xóa: chặn xóa)</t>
+          <t>users.user_id (khi xóa: chặn xóa)</t>
         </is>
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>Tổ chức thanh toán hoặc nhận hoàn tiền, ghi một lần (DM-24 trường hợp C).</t>
+          <t>Người nạp tiền vào ví của mình, hoặc nhận hoàn tiền (BL-15).</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
-          <t>3f6c2a1e-8b4d-4e2a-9c1f-0a7d5b2e4c11</t>
+          <t>9b2e7d4a-1c3f-4a8e-b6d2-5e0f1a9c3d22</t>
         </is>
       </c>
       <c r="I8" s="6" t="n"/>
     </row>
-    <row r="9" ht="27" customHeight="1">
+    <row r="9" ht="40.5" customHeight="1">
       <c r="A9" s="6" t="n">
         <v>3</v>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>paid_by</t>
+          <t>purpose</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>uuid</t>
+          <t>varchar(20)</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>có</t>
-        </is>
-      </c>
-      <c r="E9" s="6" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="F9" s="7" t="inlineStr">
-        <is>
-          <t>users.user_id (khi xóa: chặn xóa)</t>
-        </is>
-      </c>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="n"/>
+      <c r="F9" s="6" t="n"/>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>Người dùng đã thanh toán trên ứng dụng; NULL với chuyển khoản ngân hàng.</t>
+          <t>TOP_UP: nạp tiền vào ví của người đó. REFUND: hoàn lại số dư chưa dùng (BL-15). Trả trực tiếp phiếu tính tiền hay hóa đơn đến cùng các phương thức sau.</t>
         </is>
       </c>
       <c r="H9" s="6" t="inlineStr">
         <is>
-          <t>9b2e7d4a-1c3f-4a8e-b6d2-5e0f1a9c3d22</t>
+          <t>TOP_UP</t>
         </is>
       </c>
       <c r="I9" s="6" t="n"/>
     </row>
-    <row r="10" ht="67.5" customHeight="1">
+    <row r="10" ht="27" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>4</v>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>purpose</t>
+          <t>refund_of_payment_id</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>varchar(20)</t>
+          <t>uuid</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E10" s="6" t="n"/>
-      <c r="F10" s="6" t="n"/>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>payments.payment_id (khi xóa: chặn xóa)</t>
+        </is>
+      </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>Tiền dùng cho việc gì (BL-12). TOP_UP: nạp tiền vào ví (khi ra mắt). REFUND: hoàn tiền, ví dụ số dư ví chưa dùng (khi ra mắt). SESSION_BILL: trả trực tiếp một phiếu tính tiền phiên sạc (sau này). INVOICE: trả một hóa đơn (sau này, thanh toán doanh nghiệp).</t>
+          <t>Lần nạp mà khoản hoàn tiền trả lại qua; chỉ có giá trị với REFUND (hoàn tiền qua đúng kênh đã nạp, câu hỏi mở 11).</t>
         </is>
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>TOP_UP</t>
+          <t>NULL</t>
         </is>
       </c>
       <c r="I10" s="6" t="n"/>
     </row>
-    <row r="11" ht="27" customHeight="1">
+    <row r="11" ht="40.5" customHeight="1">
       <c r="A11" s="6" t="n">
         <v>5</v>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>charging_session_bill_id</t>
+          <t>amount</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>uuid</t>
+          <t>numeric(14,2)</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>có</t>
-        </is>
-      </c>
-      <c r="E11" s="6" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="F11" s="7" t="inlineStr">
-        <is>
-          <t>charging_session_bills.charging_session_bill_id (khi xóa: chặn xóa)</t>
-        </is>
-      </c>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="n"/>
+      <c r="F11" s="6" t="n"/>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>Phiếu tính tiền được trả; chỉ có giá trị với SESSION_BILL.</t>
+          <t>Số tiền, luôn dương; mục đích cho biết chiều tiền. Với chuyển khoản là số tiền thực nhận, có thể khác số tài xế định nạp.</t>
         </is>
       </c>
       <c r="H11" s="6" t="inlineStr">
         <is>
-          <t>NULL</t>
+          <t>500000.00</t>
         </is>
       </c>
       <c r="I11" s="6" t="n"/>
     </row>
-    <row r="12" ht="27" customHeight="1">
+    <row r="12">
       <c r="A12" s="6" t="n">
         <v>6</v>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>invoice_id</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>uuid</t>
+          <t>char(3)</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>có</t>
-        </is>
-      </c>
-      <c r="E12" s="6" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="F12" s="7" t="inlineStr">
-        <is>
-          <t>invoices.invoice_id (khi xóa: chặn xóa)</t>
-        </is>
-      </c>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="n"/>
+      <c r="F12" s="6" t="n"/>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>Hóa đơn được trả; chỉ có giá trị với INVOICE.</t>
+          <t>Mã tiền tệ ISO 4217.</t>
         </is>
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>NULL</t>
+          <t>VND</t>
         </is>
       </c>
       <c r="I12" s="6" t="n"/>
     </row>
-    <row r="13" ht="27" customHeight="1">
+    <row r="13" ht="54" customHeight="1">
       <c r="A13" s="6" t="n">
         <v>7</v>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>refund_of_payment_id</t>
+          <t>method</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>uuid</t>
+          <t>varchar(20)</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>có</t>
-        </is>
-      </c>
-      <c r="E13" s="6" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="F13" s="7" t="inlineStr">
-        <is>
-          <t>payments.payment_id (khi xóa: chặn xóa)</t>
-        </is>
-      </c>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="n"/>
+      <c r="F13" s="6" t="n"/>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>Thanh toán mà lần hoàn tiền này trả lại; chỉ có giá trị với REFUND.</t>
+          <t>Cách chuyển tiền. Khi ra mắt: BANK_TRANSFER qua mã VietQR (BL-15). Sau này: MOMO, ZALOPAY, CARD là giá trị mới, không đổi bảng. Trả bằng ví không phải thanh toán mà là giao dịch ví.</t>
         </is>
       </c>
       <c r="H13" s="6" t="inlineStr">
         <is>
-          <t>NULL</t>
+          <t>BANK_TRANSFER</t>
         </is>
       </c>
       <c r="I13" s="6" t="n"/>
     </row>
-    <row r="14">
+    <row r="14" ht="40.5" customHeight="1">
       <c r="A14" s="6" t="n">
         <v>8</v>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>amount</t>
+          <t>transfer_code</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>numeric(14,2)</t>
+          <t>varchar(20)</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>không</t>
+          <t>có</t>
         </is>
       </c>
       <c r="E14" s="6" t="n"/>
       <c r="F14" s="6" t="n"/>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>Số tiền, luôn dương; mục đích cho biết chiều tiền.</t>
+          <t>Nội dung chuyển khoản duy nhất mà giao dịch của tài xế phải có, nằm trong mã VietQR; dùng để ghép giao dịch đến với dòng này. Có giá trị với lần nạp BANK_TRANSFER.</t>
         </is>
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
-          <t>500000.00</t>
+          <t>G3NAP7K2Q9</t>
         </is>
       </c>
       <c r="I14" s="6" t="n"/>
     </row>
-    <row r="15">
+    <row r="15" ht="27" customHeight="1">
       <c r="A15" s="6" t="n">
         <v>9</v>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>gateway_reference</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>char(3)</t>
+          <t>varchar(100)</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>không</t>
+          <t>có</t>
         </is>
       </c>
       <c r="E15" s="6" t="n"/>
       <c r="F15" s="6" t="n"/>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>Mã tiền tệ ISO 4217.</t>
+          <t>Mã giao dịch của ngân hàng hoặc cổng thanh toán, dùng để đối soát; không bao giờ là dữ liệu thẻ (NF-05).</t>
         </is>
       </c>
       <c r="H15" s="6" t="inlineStr">
         <is>
-          <t>VND</t>
+          <t>FT26283912345</t>
         </is>
       </c>
       <c r="I15" s="6" t="n"/>
@@ -49027,78 +48961,78 @@
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>method</t>
+          <t>gateway_result_code</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>varchar(20)</t>
+          <t>varchar(30)</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>không</t>
+          <t>có</t>
         </is>
       </c>
       <c r="E16" s="6" t="n"/>
       <c r="F16" s="6" t="n"/>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>Cách chuyển tiền. Trả bằng ví không phải là thanh toán (không có tiền vào) mà là giao dịch ví.</t>
+          <t>Mã kết quả của ngân hàng hoặc cổng, đúng như gửi về; NULL nếu không có.</t>
         </is>
       </c>
       <c r="H16" s="6" t="inlineStr">
         <is>
-          <t>VNPAY</t>
+          <t>NULL</t>
         </is>
       </c>
       <c r="I16" s="6" t="n"/>
     </row>
-    <row r="17" ht="27" customHeight="1">
+    <row r="17" ht="40.5" customHeight="1">
       <c r="A17" s="6" t="n">
         <v>11</v>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>gateway_reference</t>
+          <t>status</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>varchar(100)</t>
+          <t>varchar(20)</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>có</t>
+          <t>không</t>
         </is>
       </c>
       <c r="E17" s="6" t="n"/>
       <c r="F17" s="6" t="n"/>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>Mã giao dịch của cổng thanh toán, dùng để đối soát; không bao giờ là dữ liệu thẻ (NF-05).</t>
+          <t>PENDING: đã hiện mã QR, chưa nhận tiền. SUCCEEDED: đã nhận tiền (hoặc đã chuyển hoàn). FAILED: thất bại hoặc hết hạn chưa trả. Là trạng thái quan sát nên không có cột lý do.</t>
         </is>
       </c>
       <c r="H17" s="6" t="inlineStr">
         <is>
-          <t>VNP14592873</t>
+          <t>SUCCEEDED</t>
         </is>
       </c>
       <c r="I17" s="6" t="n"/>
     </row>
-    <row r="18">
+    <row r="18" ht="27" customHeight="1">
       <c r="A18" s="6" t="n">
         <v>12</v>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>gateway_result_code</t>
+          <t>completed_at</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>varchar(30)</t>
+          <t>timestamptz</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
@@ -49110,28 +49044,28 @@
       <c r="F18" s="6" t="n"/>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>Mã kết quả của cổng thanh toán, đúng như gửi về (PAY-06).</t>
+          <t>Thời điểm xác nhận đã nhận hoặc đã chuyển tiền, hoặc yêu cầu thất bại; NULL khi PENDING.</t>
         </is>
       </c>
       <c r="H18" s="6" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>2026-09-15T09:46:12Z</t>
         </is>
       </c>
       <c r="I18" s="6" t="n"/>
     </row>
-    <row r="19" ht="27" customHeight="1">
+    <row r="19">
       <c r="A19" s="6" t="n">
         <v>13</v>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>created_at</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>varchar(20)</t>
+          <t>timestamptz</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
@@ -49143,23 +49077,23 @@
       <c r="F19" s="6" t="n"/>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>Theo cổng thanh toán báo về; là trạng thái quan sát nên không có cột lý do.</t>
+          <t>Thời điểm tạo bản ghi (UTC): lúc hiện mã QR.</t>
         </is>
       </c>
       <c r="H19" s="6" t="inlineStr">
         <is>
-          <t>SUCCEEDED</t>
+          <t>2026-09-15T09:45:00Z</t>
         </is>
       </c>
       <c r="I19" s="6" t="n"/>
     </row>
-    <row r="20" ht="27" customHeight="1">
+    <row r="20">
       <c r="A20" s="6" t="n">
         <v>14</v>
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>completed_at</t>
+          <t>updated_at</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
@@ -49169,14 +49103,14 @@
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>có</t>
+          <t>không</t>
         </is>
       </c>
       <c r="E20" s="6" t="n"/>
       <c r="F20" s="6" t="n"/>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>Thời điểm cổng xác nhận thành công hay thất bại; NULL khi PENDING.</t>
+          <t>Thời điểm bản ghi được sửa gần nhất (UTC).</t>
         </is>
       </c>
       <c r="H20" s="6" t="inlineStr">
@@ -49186,152 +49120,123 @@
       </c>
       <c r="I20" s="6" t="n"/>
     </row>
-    <row r="21">
-      <c r="A21" s="6" t="n">
-        <v>15</v>
-      </c>
-      <c r="B21" s="6" t="inlineStr">
-        <is>
-          <t>created_at</t>
-        </is>
-      </c>
-      <c r="C21" s="6" t="inlineStr">
-        <is>
-          <t>timestamptz</t>
-        </is>
-      </c>
-      <c r="D21" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E21" s="6" t="n"/>
-      <c r="F21" s="6" t="n"/>
-      <c r="G21" s="6" t="inlineStr">
-        <is>
-          <t>Thời điểm tạo bản ghi (UTC).</t>
-        </is>
-      </c>
-      <c r="H21" s="6" t="inlineStr">
-        <is>
-          <t>2026-09-15T09:45:00Z</t>
-        </is>
-      </c>
-      <c r="I21" s="6" t="n"/>
-    </row>
+    <row r="21"/>
     <row r="22">
-      <c r="A22" s="6" t="n">
-        <v>16</v>
-      </c>
-      <c r="B22" s="6" t="inlineStr">
-        <is>
-          <t>updated_at</t>
-        </is>
-      </c>
-      <c r="C22" s="6" t="inlineStr">
-        <is>
-          <t>timestamptz</t>
-        </is>
-      </c>
-      <c r="D22" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E22" s="6" t="n"/>
-      <c r="F22" s="6" t="n"/>
-      <c r="G22" s="6" t="inlineStr">
-        <is>
-          <t>Thời điểm bản ghi được sửa gần nhất (UTC).</t>
-        </is>
-      </c>
-      <c r="H22" s="6" t="inlineStr">
-        <is>
-          <t>2026-09-15T09:46:12Z</t>
-        </is>
-      </c>
-      <c r="I22" s="6" t="n"/>
-    </row>
-    <row r="23"/>
-    <row r="24">
-      <c r="A24" s="4" t="n"/>
-      <c r="B24" s="4" t="inlineStr">
+      <c r="A22" s="4" t="n"/>
+      <c r="B22" s="4" t="inlineStr">
         <is>
           <t>Chỉ mục (index)</t>
         </is>
       </c>
-      <c r="C24" s="4" t="inlineStr">
+      <c r="C22" s="4" t="inlineStr">
         <is>
           <t>Các cột</t>
         </is>
       </c>
-      <c r="D24" s="4" t="inlineStr">
+      <c r="D22" s="4" t="inlineStr">
         <is>
           <t>Duy nhất</t>
         </is>
       </c>
-      <c r="E24" s="4" t="n"/>
-      <c r="F24" s="4" t="inlineStr">
+      <c r="E22" s="4" t="n"/>
+      <c r="F22" s="4" t="inlineStr">
         <is>
           <t>Ghi chú</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="40.5" customHeight="1">
+    <row r="23" ht="27" customHeight="1">
+      <c r="A23" s="6" t="n"/>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>uq_payments_transfer_code</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>transfer_code</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="n"/>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>WHERE transfer_code IS NOT NULL</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="40.5" customHeight="1">
+      <c r="A24" s="6" t="n"/>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>uq_payments_method_gateway_reference</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>method, gateway_reference</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E24" s="6" t="n"/>
+      <c r="F24" s="6" t="inlineStr">
+        <is>
+          <t>WHERE gateway_reference IS NOT NULL: the same bank notification is never recorded twice</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
       <c r="A25" s="6" t="n"/>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>uq_payments_method_gateway_reference</t>
+          <t>ix_payments_user_created</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>method, gateway_reference</t>
+          <t>user_id, created_at</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>có</t>
+          <t>không</t>
         </is>
       </c>
       <c r="E25" s="6" t="n"/>
-      <c r="F25" s="6" t="inlineStr">
-        <is>
-          <t>WHERE gateway_reference IS NOT NULL: the same gateway callback is never recorded twice</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="27" customHeight="1">
-      <c r="A26" s="6" t="n"/>
-      <c r="B26" s="6" t="inlineStr">
-        <is>
-          <t>ix_payments_organization_created</t>
-        </is>
-      </c>
-      <c r="C26" s="6" t="inlineStr">
-        <is>
-          <t>organization_id, created_at</t>
-        </is>
-      </c>
-      <c r="D26" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E26" s="6" t="n"/>
-      <c r="F26" s="6" t="n"/>
-    </row>
-    <row r="27"/>
+      <c r="F25" s="6" t="n"/>
+    </row>
+    <row r="26"/>
+    <row r="27">
+      <c r="A27" s="4" t="n"/>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>Được tham chiếu bởi bảng</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>Cột</t>
+        </is>
+      </c>
+    </row>
     <row r="28">
-      <c r="A28" s="4" t="n"/>
-      <c r="B28" s="4" t="inlineStr">
-        <is>
-          <t>Được tham chiếu bởi bảng</t>
-        </is>
-      </c>
-      <c r="C28" s="4" t="inlineStr">
-        <is>
-          <t>Cột</t>
+      <c r="A28" s="6" t="n"/>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>payments</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>refund_of_payment_id</t>
         </is>
       </c>
     </row>
@@ -49339,39 +49244,23 @@
       <c r="A29" s="6" t="n"/>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>payments</t>
+          <t>wallet_transactions</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>refund_of_payment_id</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="6" t="n"/>
-      <c r="B30" s="7" t="inlineStr">
-        <is>
-          <t>wallet_transactions</t>
-        </is>
-      </c>
-      <c r="C30" s="6" t="inlineStr">
-        <is>
           <t>payment_id</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A6:I22"/>
+  <autoFilter ref="A6:I20"/>
   <hyperlinks>
     <hyperlink ref="A2" location="'Tổng quan'!A1"/>
-    <hyperlink ref="F8" location="'organizations'!A1"/>
-    <hyperlink ref="F9" location="'users'!A1"/>
-    <hyperlink ref="F11" location="'charging_session_bills'!A1"/>
-    <hyperlink ref="F12" location="'invoices'!A1"/>
-    <hyperlink ref="F13" location="'payments'!A1"/>
-    <hyperlink ref="B29" location="'payments'!A1"/>
-    <hyperlink ref="B30" location="'wallet_transactions'!A1"/>
+    <hyperlink ref="F8" location="'users'!A1"/>
+    <hyperlink ref="F10" location="'payments'!A1"/>
+    <hyperlink ref="B28" location="'payments'!A1"/>
+    <hyperlink ref="B29" location="'wallet_transactions'!A1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -49383,7 +49272,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -49414,14 +49303,14 @@
     <row r="3">
       <c r="A3" s="11" t="inlineStr">
         <is>
-          <t>Miền nghiệp vụ: Thanh toán &amp; hóa đơn (billing)   ·   Chủ sở hữu dữ liệu: Khách hàng   ·   Tính năng: F-H2</t>
+          <t>Miền nghiệp vụ: Thanh toán &amp; hóa đơn (billing)   ·   Chủ sở hữu dữ liệu: Nội bộ   ·   Tính năng: F-H2</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="11" t="inlineStr">
         <is>
-          <t>Số dư trả trước chỉ dùng cho dịch vụ của chính chúng ta (BL-13). Khi ra mắt, mỗi người tự nạp tiền vào ví của mình và trả từng phiên sạc từ đó; ví của tổ chức được chuẩn bị cho các phương thức sau. Để bắt đầu sạc, số dư phải bằng hoặc cao hơn mức tối thiểu đặt trong backend (BL-14); kiểm tra khi quét mã, không bằng ràng buộc cơ sở dữ liệu, vì lần trừ tiền cuối phiên có thể làm số dư âm, sau đó người dùng không thể sạc tiếp cho tới khi nạp lại trên mức tối thiểu. Bật lịch sử thay đổi cho các quyết định (khóa ví), trừ cột balance vì mọi giao dịch đều làm thay đổi nó. Không xóa mềm. Không gọi là ví điện tử khi giới thiệu ra bên ngoài (câu hỏi mở 11). Ràng buộc kiểm tra (BL-13): chỉ đúng một chủ sở hữu.</t>
+          <t>Số dư trả trước để sạc của một người, chỉ dùng cho dịch vụ của chính chúng ta (BL-13, BL-15): người đó nạp tiền và trả từng phiên sạc từ ví. Ví của tổ chức chỉ được thêm cùng các phương thức thanh toán doanh nghiệp. Để bắt đầu sạc, số dư phải bằng hoặc cao hơn mức tối thiểu đặt trong backend (BL-14); kiểm tra khi quét mã, không bằng ràng buộc cơ sở dữ liệu, vì lần trừ tiền cuối phiên có thể làm số dư âm, sau đó người dùng không thể sạc tiếp cho tới khi nạp lại trên mức tối thiểu. Bật lịch sử thay đổi cho các quyết định (khóa ví), trừ cột balance vì mọi giao dịch đều làm thay đổi nó. Không xóa mềm. Không gọi là ví điện tử khi giới thiệu ra bên ngoài (câu hỏi mở 11).</t>
         </is>
       </c>
     </row>
@@ -49533,7 +49422,7 @@
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>có</t>
+          <t>không</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
@@ -49548,7 +49437,7 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>Người sở hữu ví (phương thức khi ra mắt, BL-13): ví đi theo người đó sang mọi tổ chức họ lái xe cho. Chỉ đúng một trong user_id và organization_id có giá trị.</t>
+          <t>Người sở hữu ví (BL-13, BL-15): ví đi theo người đó sang mọi tổ chức họ lái xe cho. Ví của tổ chức chỉ được thêm cùng các phương thức thanh toán doanh nghiệp.</t>
         </is>
       </c>
       <c r="H9" s="6" t="inlineStr">
@@ -49562,63 +49451,51 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="40.5" customHeight="1">
+    <row r="10" ht="27" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>3</v>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>organization_id</t>
+          <t>balance</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>uuid</t>
+          <t>numeric(14,2)</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>có</t>
-        </is>
-      </c>
-      <c r="E10" s="6" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="F10" s="7" t="inlineStr">
-        <is>
-          <t>organizations.organization_id (khi xóa: chặn xóa)</t>
-        </is>
-      </c>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="n"/>
+      <c r="F10" s="6" t="n"/>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>Tổ chức sở hữu ví (phương thức sau này: tổ chức trả trước và tài xế dùng, hoặc tổ chức phân bổ cho tài xế); NULL với ví cá nhân.</t>
+          <t>Số dư hiện tại, luôn bằng tổng các giao dịch. Có thể âm khi một phiên sạc tốn nhiều hơn số dư (BL-14).</t>
         </is>
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="I10" s="6" t="inlineStr">
-        <is>
-          <t>🔍</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="27" customHeight="1">
+          <t>1250000.00</t>
+        </is>
+      </c>
+      <c r="I10" s="6" t="n"/>
+    </row>
+    <row r="11">
       <c r="A11" s="6" t="n">
         <v>4</v>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>balance</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>numeric(14,2)</t>
+          <t>char(3)</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
@@ -49630,28 +49507,32 @@
       <c r="F11" s="6" t="n"/>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>Số dư hiện tại, luôn bằng tổng các giao dịch. Có thể âm khi một phiên sạc tốn nhiều hơn số dư (BL-14).</t>
+          <t>Mã tiền tệ ISO 4217.</t>
         </is>
       </c>
       <c r="H11" s="6" t="inlineStr">
         <is>
-          <t>1250000.00</t>
-        </is>
-      </c>
-      <c r="I11" s="6" t="n"/>
-    </row>
-    <row r="12">
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="I11" s="6" t="inlineStr">
+        <is>
+          <t>🔍</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="40.5" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>5</v>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>status</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>char(3)</t>
+          <t>varchar(20)</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
@@ -49663,12 +49544,12 @@
       <c r="F12" s="6" t="n"/>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>Mã tiền tệ ISO 4217.</t>
+          <t>Do chúng ta quyết định. ACTIVE: dùng được. BLOCKED: không nạp tiền và không bắt đầu sạc, ví dụ khi đang kiểm tra gian lận.</t>
         </is>
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>VND</t>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="I12" s="6" t="inlineStr">
@@ -49677,35 +49558,35 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="40.5" customHeight="1">
+    <row r="13" ht="27" customHeight="1">
       <c r="A13" s="6" t="n">
         <v>6</v>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>status_reason</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>varchar(20)</t>
+          <t>varchar(200)</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>không</t>
+          <t>có</t>
         </is>
       </c>
       <c r="E13" s="6" t="n"/>
       <c r="F13" s="6" t="n"/>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>Do chúng ta quyết định. ACTIVE: dùng được. BLOCKED: không nạp tiền và không bắt đầu sạc, ví dụ khi đang kiểm tra gian lận.</t>
+          <t>Lý do ví có trạng thái hiện tại, ví dụ vì sao bị khóa (DM-19); NULL nếu không cần giải thích.</t>
         </is>
       </c>
       <c r="H13" s="6" t="inlineStr">
         <is>
-          <t>ACTIVE</t>
+          <t>NULL</t>
         </is>
       </c>
       <c r="I13" s="6" t="inlineStr">
@@ -49714,35 +49595,35 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="27" customHeight="1">
+    <row r="14">
       <c r="A14" s="6" t="n">
         <v>7</v>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>status_reason</t>
+          <t>created_at</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>varchar(200)</t>
+          <t>timestamptz</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>có</t>
+          <t>không</t>
         </is>
       </c>
       <c r="E14" s="6" t="n"/>
       <c r="F14" s="6" t="n"/>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>Lý do ví có trạng thái hiện tại, ví dụ vì sao bị khóa (DM-19); NULL nếu không cần giải thích.</t>
+          <t>Thời điểm tạo bản ghi (UTC).</t>
         </is>
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
-          <t>NULL</t>
+          <t>2026-09-01T02:00:00Z</t>
         </is>
       </c>
       <c r="I14" s="6" t="inlineStr">
@@ -49757,7 +49638,7 @@
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>updated_at</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
@@ -49774,12 +49655,12 @@
       <c r="F15" s="6" t="n"/>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>Thời điểm tạo bản ghi (UTC).</t>
+          <t>Thời điểm bản ghi được sửa gần nhất (UTC).</t>
         </is>
       </c>
       <c r="H15" s="6" t="inlineStr">
         <is>
-          <t>2026-09-01T02:00:00Z</t>
+          <t>2026-09-15T09:46:12Z</t>
         </is>
       </c>
       <c r="I15" s="6" t="inlineStr">
@@ -49788,165 +49669,103 @@
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="B16" s="6" t="inlineStr">
-        <is>
-          <t>updated_at</t>
-        </is>
-      </c>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>timestamptz</t>
-        </is>
-      </c>
-      <c r="D16" s="6" t="inlineStr">
-        <is>
-          <t>không</t>
-        </is>
-      </c>
-      <c r="E16" s="6" t="n"/>
-      <c r="F16" s="6" t="n"/>
-      <c r="G16" s="6" t="inlineStr">
-        <is>
-          <t>Thời điểm bản ghi được sửa gần nhất (UTC).</t>
-        </is>
-      </c>
-      <c r="H16" s="6" t="inlineStr">
-        <is>
-          <t>2026-09-15T09:46:12Z</t>
-        </is>
-      </c>
-      <c r="I16" s="6" t="inlineStr">
-        <is>
-          <t>🔍</t>
-        </is>
-      </c>
-    </row>
-    <row r="17"/>
+    <row r="16"/>
+    <row r="17">
+      <c r="A17" s="4" t="n"/>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>Chỉ mục (index)</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>Các cột</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>Duy nhất</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="n"/>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>Ghi chú</t>
+        </is>
+      </c>
+    </row>
     <row r="18">
-      <c r="A18" s="4" t="n"/>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>Chỉ mục (index)</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>Các cột</t>
-        </is>
-      </c>
-      <c r="D18" s="4" t="inlineStr">
-        <is>
-          <t>Duy nhất</t>
-        </is>
-      </c>
-      <c r="E18" s="4" t="n"/>
-      <c r="F18" s="4" t="inlineStr">
-        <is>
-          <t>Ghi chú</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="27" customHeight="1">
-      <c r="A19" s="6" t="n"/>
-      <c r="B19" s="6" t="inlineStr">
+      <c r="A18" s="6" t="n"/>
+      <c r="B18" s="6" t="inlineStr">
         <is>
           <t>uq_wallets_user_id</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr">
+      <c r="C18" s="6" t="inlineStr">
         <is>
           <t>user_id</t>
         </is>
       </c>
-      <c r="D19" s="6" t="inlineStr">
+      <c r="D18" s="6" t="inlineStr">
         <is>
           <t>có</t>
         </is>
       </c>
-      <c r="E19" s="6" t="n"/>
-      <c r="F19" s="6" t="inlineStr">
-        <is>
-          <t>WHERE user_id IS NOT NULL: one wallet per person</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="27" customHeight="1">
-      <c r="A20" s="6" t="n"/>
-      <c r="B20" s="6" t="inlineStr">
-        <is>
-          <t>uq_wallets_organization_id</t>
-        </is>
-      </c>
-      <c r="C20" s="6" t="inlineStr">
-        <is>
-          <t>organization_id</t>
-        </is>
-      </c>
-      <c r="D20" s="6" t="inlineStr">
-        <is>
-          <t>có</t>
-        </is>
-      </c>
-      <c r="E20" s="6" t="n"/>
-      <c r="F20" s="6" t="inlineStr">
-        <is>
-          <t>WHERE organization_id IS NOT NULL: one wallet per organization</t>
-        </is>
-      </c>
-    </row>
-    <row r="21"/>
+      <c r="E18" s="6" t="n"/>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>One wallet per person</t>
+        </is>
+      </c>
+    </row>
+    <row r="19"/>
+    <row r="20">
+      <c r="A20" s="4" t="n"/>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>Được tham chiếu bởi bảng</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>Cột</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="n"/>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>wallet_transactions</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>wallet_id</t>
+        </is>
+      </c>
+    </row>
     <row r="22">
-      <c r="A22" s="4" t="n"/>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>Được tham chiếu bởi bảng</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="inlineStr">
-        <is>
-          <t>Cột</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="6" t="n"/>
-      <c r="B23" s="7" t="inlineStr">
-        <is>
-          <t>wallet_transactions</t>
-        </is>
-      </c>
-      <c r="C23" s="6" t="inlineStr">
+      <c r="A22" s="6" t="n"/>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>wallet_history</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
         <is>
           <t>wallet_id</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="6" t="n"/>
-      <c r="B24" s="7" t="inlineStr">
-        <is>
-          <t>wallet_history</t>
-        </is>
-      </c>
-      <c r="C24" s="6" t="inlineStr">
-        <is>
-          <t>wallet_id</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-